--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -423,7 +423,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>index</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -912,7 +912,7 @@
         <v>16.79000091552734</v>
       </c>
       <c r="H2" t="n">
-        <v>13426800</v>
+        <v>21403900</v>
       </c>
       <c r="I2" t="n">
         <v>0.006027750485229966</v>
@@ -1184,82 +1184,82 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.61000061035156</v>
+        <v>28.57999992370605</v>
       </c>
       <c r="D3" t="n">
-        <v>28.61000061035156</v>
+        <v>28.57999992370605</v>
       </c>
       <c r="E3" t="n">
         <v>29.11000061035156</v>
       </c>
       <c r="F3" t="n">
-        <v>28.57999992370605</v>
+        <v>28.39999961853027</v>
       </c>
       <c r="G3" t="n">
         <v>29.10000038146973</v>
       </c>
       <c r="H3" t="n">
-        <v>751300</v>
+        <v>1125000</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002440714577383929</v>
+        <v>-0.003486763612470356</v>
       </c>
       <c r="J3" t="n">
-        <v>28.55777782864041</v>
+        <v>28.55444441901313</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1828671055027994</v>
+        <v>0.08949746777740943</v>
       </c>
       <c r="M3" t="n">
-        <v>28.58900012969971</v>
+        <v>28.58600006103516</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07345650619673308</v>
+        <v>-0.02098977582135255</v>
       </c>
       <c r="P3" t="n">
-        <v>29.95576931880071</v>
+        <v>29.95461544623742</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.49251926774759</v>
+        <v>-4.588994056687278</v>
       </c>
       <c r="S3" t="n">
-        <v>30.41279998779297</v>
+        <v>30.41219997406006</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.927765211243327</v>
+        <v>-6.024556105499668</v>
       </c>
       <c r="V3" t="n">
-        <v>29.26993333180745</v>
+        <v>29.26973332722982</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.254643746450721</v>
+        <v>-2.356473138353128</v>
       </c>
       <c r="Y3" t="n">
-        <v>27.9786999797821</v>
+        <v>27.97854997634888</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.256361557276243</v>
+        <v>2.149682338311321</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2640937691365127</v>
+        <v>0.2640315631837619</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.45</v>
+        <v>17.43</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1449,16 +1449,16 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.310000419616699</v>
+        <v>9.270000457763672</v>
       </c>
       <c r="D4" t="n">
-        <v>9.310000419616699</v>
+        <v>9.270000457763672</v>
       </c>
       <c r="E4" t="n">
         <v>9.390000343322754</v>
@@ -1486,88 +1486,88 @@
         <v>9.25</v>
       </c>
       <c r="H4" t="n">
-        <v>12429500</v>
+        <v>19179200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02195398139152083</v>
+        <v>0.01756320605008499</v>
       </c>
       <c r="J4" t="n">
-        <v>8.668888727823893</v>
+        <v>8.664444287618002</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>7.395546441092013</v>
+        <v>6.988978750905527</v>
       </c>
       <c r="M4" t="n">
-        <v>8.660999870300293</v>
+        <v>8.656999874114991</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>7.493367498386819</v>
+        <v>7.080981778474939</v>
       </c>
       <c r="P4" t="n">
-        <v>8.970384561098539</v>
+        <v>8.968846101027269</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>3.785967660639173</v>
+        <v>3.357782632728073</v>
       </c>
       <c r="S4" t="n">
-        <v>8.905199947357177</v>
+        <v>8.904399948120117</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>4.545664046315499</v>
+        <v>4.105841064795608</v>
       </c>
       <c r="V4" t="n">
-        <v>8.628666613896687</v>
+        <v>8.628399947484334</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>7.896165609443139</v>
+        <v>7.43591528191041</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.900999953746796</v>
+        <v>8.900799953937531</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.594994584824576</v>
+        <v>4.147947439969307</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5226949119142523</v>
+        <v>0.521139125970367</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE4" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>8.9</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>9.4</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>9.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>9.6</v>
       </c>
       <c r="AJ4" t="n">
         <v>2</v>
@@ -1694,13 +1694,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>17.9</v>
+        <v>17.83</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.47999954223633</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="D5" t="n">
-        <v>12.47999954223633</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="E5" t="n">
         <v>12.68000030517578</v>
@@ -1769,67 +1769,67 @@
         <v>12.64000034332275</v>
       </c>
       <c r="H5" t="n">
-        <v>1179500</v>
+        <v>2011100</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001600036621093759</v>
+        <v>-0.0008000183105468794</v>
       </c>
       <c r="J5" t="n">
-        <v>12.50777774386936</v>
+        <v>12.50888888041178</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2220874259349971</v>
+        <v>-0.1510054927676149</v>
       </c>
       <c r="M5" t="n">
-        <v>12.52799997329712</v>
+        <v>12.5289999961853</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3831452040477448</v>
+        <v>-0.3112796318861229</v>
       </c>
       <c r="P5" t="n">
-        <v>13.30615381094126</v>
+        <v>13.30653843512902</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.208813459119985</v>
+        <v>-6.136371739288766</v>
       </c>
       <c r="S5" t="n">
-        <v>12.95479993820191</v>
+        <v>12.95499994277954</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.665053865984116</v>
+        <v>-3.589349083097017</v>
       </c>
       <c r="V5" t="n">
-        <v>12.10246664047241</v>
+        <v>12.10253330866496</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>3.119470707743085</v>
+        <v>3.201531882385276</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.68834996700287</v>
+        <v>11.68839996814728</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.772979740240048</v>
+        <v>6.858079849725975</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2387754551763168</v>
+        <v>0.2388315209808099</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>7</v>
       </c>
       <c r="CM5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -2033,82 +2033,82 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53.0099983215332</v>
+        <v>52.75</v>
       </c>
       <c r="D6" t="n">
-        <v>53.0099983215332</v>
+        <v>52.75</v>
       </c>
       <c r="E6" t="n">
         <v>53.72000122070312</v>
       </c>
       <c r="F6" t="n">
-        <v>52.70999908447266</v>
+        <v>52.59999847412109</v>
       </c>
       <c r="G6" t="n">
         <v>53.47000122070312</v>
       </c>
       <c r="H6" t="n">
-        <v>3390400</v>
+        <v>4719500</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.009344048134622973</v>
+        <v>-0.01420292179727778</v>
       </c>
       <c r="J6" t="n">
-        <v>54.1555553012424</v>
+        <v>54.12666659884982</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.115308343413695</v>
+        <v>-2.543416554824525</v>
       </c>
       <c r="M6" t="n">
-        <v>54.27499961853027</v>
+        <v>54.24899978637696</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.330725575104712</v>
+        <v>-2.763184191929352</v>
       </c>
       <c r="P6" t="n">
-        <v>58.26923047579252</v>
+        <v>58.25923054034893</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.025744996656892</v>
+        <v>-9.456408004793971</v>
       </c>
       <c r="S6" t="n">
-        <v>59.24059989929199</v>
+        <v>59.23539993286133</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-10.51745186299718</v>
+        <v>-10.94852054719309</v>
       </c>
       <c r="V6" t="n">
-        <v>58.20400001525879</v>
+        <v>58.20226669311523</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.923788214493724</v>
+        <v>-9.367790986326286</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.50984998703003</v>
+        <v>55.50854999542236</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-4.50343797736964</v>
+        <v>-4.969594766301504</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2914759521119187</v>
+        <v>0.2921697279763685</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.21</v>
+        <v>16.13</v>
       </c>
       <c r="CA6" t="n">
         <v>0.3</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CC6" t="n">
         <v>4</v>
@@ -2316,82 +2316,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58.2400016784668</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="D7" t="n">
-        <v>58.2400016784668</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="E7" t="n">
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>57.90999984741211</v>
+        <v>57.83000183105469</v>
       </c>
       <c r="G7" t="n">
         <v>59</v>
       </c>
       <c r="H7" t="n">
-        <v>319900</v>
+        <v>512500</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.009692223797210908</v>
+        <v>-0.01343310486447513</v>
       </c>
       <c r="J7" t="n">
-        <v>59.56111102634006</v>
+        <v>59.53666644626193</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.218073714724728</v>
+        <v>-2.547448621207589</v>
       </c>
       <c r="M7" t="n">
-        <v>59.69099998474121</v>
+        <v>59.6689998626709</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.430849385410417</v>
+        <v>-2.763578086950387</v>
       </c>
       <c r="P7" t="n">
-        <v>64.03769243680514</v>
+        <v>64.02923085139348</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.053559767256965</v>
+        <v>-9.385135997614482</v>
       </c>
       <c r="S7" t="n">
-        <v>65.00459999084472</v>
+        <v>65.00019996643067</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-10.40633787967414</v>
+        <v>-10.73873543815545</v>
       </c>
       <c r="V7" t="n">
-        <v>58.48537350972494</v>
+        <v>58.48390683492025</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4195439244605999</v>
+        <v>-0.7932205665842783</v>
       </c>
       <c r="Y7" t="n">
-        <v>53.84579418182373</v>
+        <v>53.84469417572021</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.160725574600932</v>
+        <v>7.754350444293539</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3055046326323761</v>
+        <v>0.305993274806622</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.81</v>
+        <v>17.74</v>
       </c>
       <c r="CA7" t="n">
         <v>0.27</v>
@@ -2603,82 +2603,82 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.45999908447266</v>
+        <v>20.40999984741211</v>
       </c>
       <c r="D8" t="n">
-        <v>20.45999908447266</v>
+        <v>20.40999984741211</v>
       </c>
       <c r="E8" t="n">
         <v>21.01000022888184</v>
       </c>
       <c r="F8" t="n">
-        <v>20.43000030517578</v>
+        <v>20.20999908447266</v>
       </c>
       <c r="G8" t="n">
         <v>20.63999938964844</v>
       </c>
       <c r="H8" t="n">
-        <v>576100</v>
+        <v>771200</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001951264172065592</v>
+        <v>-0.004390251345750773</v>
       </c>
       <c r="J8" t="n">
-        <v>19.92111100090874</v>
+        <v>19.91555553012424</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2.705110591167977</v>
+        <v>2.482704118094887</v>
       </c>
       <c r="M8" t="n">
-        <v>19.81399993896484</v>
+        <v>19.80900001525879</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.260316682637283</v>
+        <v>3.033973606392915</v>
       </c>
       <c r="P8" t="n">
-        <v>20.74230766296387</v>
+        <v>20.74038461538462</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.361027823318246</v>
+        <v>-1.592953911411255</v>
       </c>
       <c r="S8" t="n">
-        <v>22.66080005645752</v>
+        <v>22.65980007171631</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.711929704607725</v>
+        <v>-9.928596974305933</v>
       </c>
       <c r="V8" t="n">
-        <v>25.12593335469564</v>
+        <v>25.12560002644857</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-18.57019281375667</v>
+        <v>-18.76810971309167</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.70315004348755</v>
+        <v>26.70290004730225</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.37982952890419</v>
+        <v>-23.56635492303354</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4460988469572981</v>
+        <v>0.446185318384313</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2830,7 +2830,7 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
       <c r="CA8" t="n">
         <v>0.52</v>
@@ -2886,82 +2886,82 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.76000022888184</v>
+        <v>16.6299991607666</v>
       </c>
       <c r="D9" t="n">
-        <v>16.76000022888184</v>
+        <v>16.6299991607666</v>
       </c>
       <c r="E9" t="n">
         <v>17.28000068664551</v>
       </c>
       <c r="F9" t="n">
-        <v>16.70000076293945</v>
+        <v>16.55999946594238</v>
       </c>
       <c r="G9" t="n">
         <v>17.14999961853027</v>
       </c>
       <c r="H9" t="n">
-        <v>6540400</v>
+        <v>10749600</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01062575557857237</v>
+        <v>-0.01829996242725984</v>
       </c>
       <c r="J9" t="n">
-        <v>16.74888918134901</v>
+        <v>16.7344446182251</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06633901157573274</v>
+        <v>-0.624134590906871</v>
       </c>
       <c r="M9" t="n">
-        <v>16.76700029373169</v>
+        <v>16.75400018692017</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.04174905902799976</v>
+        <v>-0.7401278785371624</v>
       </c>
       <c r="P9" t="n">
-        <v>17.64000015992385</v>
+        <v>17.63500011884249</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-4.988661695373874</v>
+        <v>-5.69889963880451</v>
       </c>
       <c r="S9" t="n">
-        <v>17.91680013656616</v>
+        <v>17.91420011520386</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.456509526628191</v>
+        <v>-7.168620123582016</v>
       </c>
       <c r="V9" t="n">
-        <v>15.97906675338745</v>
+        <v>15.97820007960002</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>4.887228319068333</v>
+        <v>4.079302286361791</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.22025005817413</v>
+        <v>15.21960005283356</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.11645777712285</v>
+        <v>9.26699192512919</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.352351687184162</v>
+        <v>0.3542295992318979</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>17.1</v>
+        <v>16.97</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3154,13 +3154,13 @@
         <v>5</v>
       </c>
       <c r="CM9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -3173,106 +3173,106 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.30999946594238</v>
+        <v>21.19000053405762</v>
       </c>
       <c r="D10" t="n">
-        <v>21.30999946594238</v>
+        <v>21.19000053405762</v>
       </c>
       <c r="E10" t="n">
         <v>21.5</v>
       </c>
       <c r="F10" t="n">
-        <v>21.19000053405762</v>
+        <v>21.14999961853027</v>
       </c>
       <c r="G10" t="n">
         <v>21.44000053405762</v>
       </c>
       <c r="H10" t="n">
-        <v>6033100</v>
+        <v>8558200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.009474128366095291</v>
+        <v>0.003789669417007202</v>
       </c>
       <c r="J10" t="n">
-        <v>20.87555567423503</v>
+        <v>20.86222245958116</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2.081112467073409</v>
+        <v>1.571156069836273</v>
       </c>
       <c r="M10" t="n">
-        <v>20.86400012969971</v>
+        <v>20.85200023651123</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.137650179592355</v>
+        <v>1.620949039481393</v>
       </c>
       <c r="P10" t="n">
-        <v>21.69230776566726</v>
+        <v>21.68769242213322</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.762414141707678</v>
+        <v>-2.294812552614825</v>
       </c>
       <c r="S10" t="n">
-        <v>22.707799949646</v>
+        <v>22.7053999710083</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.15559625680692</v>
+        <v>-6.674180762662814</v>
       </c>
       <c r="V10" t="n">
-        <v>22.94493333180746</v>
+        <v>22.94413333892822</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.125467928898456</v>
+        <v>-7.645234531018221</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.45190001487732</v>
+        <v>22.4513000202179</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-5.08598625585487</v>
+        <v>-5.617935197625309</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2870743980723636</v>
+        <v>0.2850811782542741</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AF10" t="n">
         <v>21.1</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>21.2</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>21.3</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>21.4</v>
       </c>
-      <c r="AH10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>21.6</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.49</v>
+        <v>8.44</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3472,82 +3472,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.65999984741211</v>
+        <v>15.67000007629395</v>
       </c>
       <c r="D11" t="n">
-        <v>15.65999984741211</v>
+        <v>15.67000007629395</v>
       </c>
       <c r="E11" t="n">
         <v>15.85000038146973</v>
       </c>
       <c r="F11" t="n">
-        <v>15.64000034332275</v>
+        <v>15.56999969482422</v>
       </c>
       <c r="G11" t="n">
         <v>15.69999980926514</v>
       </c>
       <c r="H11" t="n">
-        <v>1410100</v>
+        <v>2021000</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005134783318216041</v>
+        <v>0.005776646535854635</v>
       </c>
       <c r="J11" t="n">
-        <v>15.46555550893148</v>
+        <v>15.4666666454739</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.257273548100731</v>
+        <v>1.314655804517156</v>
       </c>
       <c r="M11" t="n">
-        <v>15.47299995422363</v>
+        <v>15.47399997711182</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.208556154215145</v>
+        <v>1.266641459687477</v>
       </c>
       <c r="P11" t="n">
-        <v>16.16846150618333</v>
+        <v>16.16884613037109</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.144774526486453</v>
+        <v>-3.085229768747261</v>
       </c>
       <c r="S11" t="n">
-        <v>16.52599996566773</v>
+        <v>16.52619997024536</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.240228246730643</v>
+        <v>-5.180863692155265</v>
       </c>
       <c r="V11" t="n">
-        <v>16.61666664759318</v>
+        <v>16.61673331578573</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.757272625551762</v>
+        <v>-5.697469060253824</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.06865000247955</v>
+        <v>16.06870000362396</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.543151758264608</v>
+        <v>-2.481220803425911</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2192973167212598</v>
+        <v>0.2195445080725569</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.99</v>
+        <v>7</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3736,13 +3736,13 @@
         <v>9</v>
       </c>
       <c r="CG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CH11" t="n">
         <v>1</v>
       </c>
       <c r="CI11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="n">
@@ -3752,13 +3752,13 @@
         <v>6</v>
       </c>
       <c r="CM11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN11" t="n">
         <v>1</v>
       </c>
       <c r="CO11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -3771,82 +3771,82 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.04999923706055</v>
+        <v>18.06999969482422</v>
       </c>
       <c r="D12" t="n">
-        <v>18.04999923706055</v>
+        <v>18.06999969482422</v>
       </c>
       <c r="E12" t="n">
         <v>18.20000076293945</v>
       </c>
       <c r="F12" t="n">
-        <v>17.98999977111816</v>
+        <v>17.92000007629395</v>
       </c>
       <c r="G12" t="n">
         <v>18.10000038146973</v>
       </c>
       <c r="H12" t="n">
-        <v>8882600</v>
+        <v>13236800</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0117712490289521</v>
+        <v>0.01289235091194563</v>
       </c>
       <c r="J12" t="n">
-        <v>17.78666665818956</v>
+        <v>17.78888893127441</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.480505504103209</v>
+        <v>1.580260378463477</v>
       </c>
       <c r="M12" t="n">
-        <v>17.79200000762939</v>
+        <v>17.79400005340576</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.450085596450766</v>
+        <v>1.55108261543268</v>
       </c>
       <c r="P12" t="n">
-        <v>18.65999999413123</v>
+        <v>18.66076924250676</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-3.269028709874267</v>
+        <v>-3.165837056367678</v>
       </c>
       <c r="S12" t="n">
-        <v>19.06160003662109</v>
+        <v>19.06200004577637</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.307008842998816</v>
+        <v>-5.204072755061979</v>
       </c>
       <c r="V12" t="n">
-        <v>19.29766666412354</v>
+        <v>19.29780000050863</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.465379720660938</v>
+        <v>-6.362384860720119</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.68314999580383</v>
+        <v>18.68324999809265</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.388886557595966</v>
+        <v>-3.282353462759634</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2615072192464402</v>
+        <v>0.2621234219128852</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.06</v>
+        <v>8.07</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35.09000015258789</v>
+        <v>34.88000106811523</v>
       </c>
       <c r="D13" t="n">
-        <v>35.09000015258789</v>
+        <v>34.88000106811523</v>
       </c>
       <c r="E13" t="n">
         <v>35.38999938964844</v>
@@ -4085,88 +4085,88 @@
         <v>34.84999847412109</v>
       </c>
       <c r="H13" t="n">
-        <v>1661100</v>
+        <v>2061500</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01065665088929024</v>
+        <v>0.004608290374042534</v>
       </c>
       <c r="J13" t="n">
-        <v>34.5</v>
+        <v>34.47666676839193</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.710145369819973</v>
+        <v>1.169876143865161</v>
       </c>
       <c r="M13" t="n">
-        <v>34.49799995422363</v>
+        <v>34.47700004577636</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.716042086932003</v>
+        <v>1.168898169225254</v>
       </c>
       <c r="P13" t="n">
-        <v>34.37038465646597</v>
+        <v>34.36230776860164</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>2.093708008550144</v>
+        <v>1.5065731411283</v>
       </c>
       <c r="S13" t="n">
-        <v>34.70299995422364</v>
+        <v>34.69879997253418</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.115177935264223</v>
+        <v>0.5222114186210525</v>
       </c>
       <c r="V13" t="n">
-        <v>34.78653334299723</v>
+        <v>34.78513334910075</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8723686450686515</v>
+        <v>0.2727248967609326</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.29579997062683</v>
+        <v>34.29474997520447</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.315735987034169</v>
+        <v>1.706532613108159</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1618711205408884</v>
+        <v>0.1590600858735742</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AE13" t="n">
         <v>34.7</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>34.8</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>35</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>35.2</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>35.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>36.4</v>
       </c>
       <c r="AJ13" t="n">
         <v>1</v>
@@ -4313,13 +4313,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>7.42</v>
+        <v>7.37</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.39</v>
+        <v>5.36</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4369,82 +4369,82 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.910000085830688</v>
+        <v>3.890000104904175</v>
       </c>
       <c r="D14" t="n">
-        <v>3.910000085830688</v>
+        <v>3.890000104904175</v>
       </c>
       <c r="E14" t="n">
         <v>4.03000020980835</v>
       </c>
       <c r="F14" t="n">
-        <v>3.900000095367432</v>
+        <v>3.890000104904175</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>5397900</v>
+        <v>7081900</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.005089053584423131</v>
+        <v>-0.01017810716884615</v>
       </c>
       <c r="J14" t="n">
-        <v>4.078888919618395</v>
+        <v>4.076666699515449</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.140559772917448</v>
+        <v>-4.578902529202619</v>
       </c>
       <c r="M14" t="n">
-        <v>4.080000042915344</v>
+        <v>4.078000044822693</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.166665570993061</v>
+        <v>-4.610101467683818</v>
       </c>
       <c r="P14" t="n">
-        <v>4.049230795640212</v>
+        <v>4.048461565604577</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-3.438448358128478</v>
+        <v>-3.914115476522707</v>
       </c>
       <c r="S14" t="n">
-        <v>4.105200023651123</v>
+        <v>4.104800024032593</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.754943405822782</v>
+        <v>-5.232896069743164</v>
       </c>
       <c r="V14" t="n">
-        <v>5.331733338038126</v>
+        <v>5.33160000483195</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-26.66549810479796</v>
+        <v>-27.03878570450286</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.518450000286102</v>
+        <v>5.51835000038147</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-29.14676973374814</v>
+        <v>-29.50791260729623</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.4828640447358539</v>
+        <v>0.4833561034516354</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4596,13 +4596,13 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>5.51</v>
+        <v>5.48</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CC14" t="n">
         <v>8</v>
@@ -4656,82 +4656,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.27999877929688</v>
+        <v>55.06000137329102</v>
       </c>
       <c r="D15" t="n">
-        <v>55.27999877929688</v>
+        <v>55.06000137329102</v>
       </c>
       <c r="E15" t="n">
         <v>56.47999954223633</v>
       </c>
       <c r="F15" t="n">
-        <v>55.15999984741211</v>
+        <v>54.70999908447266</v>
       </c>
       <c r="G15" t="n">
         <v>56.36000061035156</v>
       </c>
       <c r="H15" t="n">
-        <v>2578300</v>
+        <v>4154100</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.003963985958614913</v>
+        <v>-0.00792790318394565</v>
       </c>
       <c r="J15" t="n">
-        <v>54.5477778116862</v>
+        <v>54.52333365546333</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.342347932373168</v>
+        <v>0.9842899944800334</v>
       </c>
       <c r="M15" t="n">
-        <v>54.63199996948242</v>
+        <v>54.61000022888184</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.186115848177674</v>
+        <v>0.8240269960137889</v>
       </c>
       <c r="P15" t="n">
-        <v>57.41269214336689</v>
+        <v>57.40423070467435</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.71467228665119</v>
+        <v>-4.083722231979064</v>
       </c>
       <c r="S15" t="n">
-        <v>57.84039978027344</v>
+        <v>57.83599983215332</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.426665463418513</v>
+        <v>-4.799776033817292</v>
       </c>
       <c r="V15" t="n">
-        <v>55.77513320922851</v>
+        <v>55.77366655985514</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8877332987699872</v>
+        <v>-1.279573731804485</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.22154993057251</v>
+        <v>53.22044994354248</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.867698049774224</v>
+        <v>3.456474779337589</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2872990940845164</v>
+        <v>0.2874515428253042</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4903,13 +4903,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ15" t="n">
-        <v>12.42</v>
+        <v>12.37</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CC15" t="n">
         <v>6</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.26000022888184</v>
+        <v>23.27000045776367</v>
       </c>
       <c r="D16" t="n">
-        <v>23.26000022888184</v>
+        <v>23.27000045776367</v>
       </c>
       <c r="E16" t="n">
         <v>23.35000038146973</v>
@@ -4978,67 +4978,67 @@
         <v>23.20000076293945</v>
       </c>
       <c r="H16" t="n">
-        <v>448300</v>
+        <v>755300</v>
       </c>
       <c r="I16" t="n">
-        <v>0.007798973386949459</v>
+        <v>0.008232258868530629</v>
       </c>
       <c r="J16" t="n">
-        <v>22.98444451226128</v>
+        <v>22.98555564880371</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.198879165748618</v>
+        <v>1.237493725650983</v>
       </c>
       <c r="M16" t="n">
-        <v>22.97100009918213</v>
+        <v>22.97200012207031</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25810860847107</v>
+        <v>1.297232866575932</v>
       </c>
       <c r="P16" t="n">
-        <v>23.23384622427134</v>
+        <v>23.2342308484591</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1125685534716957</v>
+        <v>0.153952198968297</v>
       </c>
       <c r="S16" t="n">
-        <v>23.27479995727539</v>
+        <v>23.27499996185303</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.06358691984774315</v>
+        <v>-0.02148014649859904</v>
       </c>
       <c r="V16" t="n">
-        <v>21.88579995473226</v>
+        <v>21.88586662292481</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>6.27895839764559</v>
+        <v>6.324327287040245</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.57374995231628</v>
+        <v>20.57379995346069</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.05668768596618</v>
+        <v>13.10501954136797</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2553192183134387</v>
+        <v>0.2554684770309464</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.04999923706055</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="D17" t="n">
-        <v>20.04999923706055</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="E17" t="n">
         <v>20.17000007629395</v>
@@ -5269,91 +5269,91 @@
         <v>19.92000007629395</v>
       </c>
       <c r="H17" t="n">
-        <v>1817900</v>
+        <v>2728100</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0009965350307817866</v>
+        <v>-0.004484312603706742</v>
       </c>
       <c r="J17" t="n">
-        <v>19.59444448682997</v>
+        <v>19.58666674296061</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.324917915058873</v>
+        <v>2.008166087867286</v>
       </c>
       <c r="M17" t="n">
-        <v>19.45400009155274</v>
+        <v>19.44700012207031</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.063632891451482</v>
+        <v>2.740779641180315</v>
       </c>
       <c r="P17" t="n">
-        <v>19.00576921609732</v>
+        <v>19.00307692014254</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>5.494279179601942</v>
+        <v>5.140865482990742</v>
       </c>
       <c r="S17" t="n">
-        <v>19.36379993438721</v>
+        <v>19.36239994049072</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>3.543722332385566</v>
+        <v>3.18968518181509</v>
       </c>
       <c r="V17" t="n">
-        <v>17.29446662902832</v>
+        <v>17.29399996439616</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>15.93303029887684</v>
+        <v>15.53139576367492</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.61649995326996</v>
+        <v>17.61614995479584</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.8137501220206</v>
+        <v>13.41865046282122</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3934422329260836</v>
+        <v>0.3935227894429228</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AE17" t="n">
         <v>19.8</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AF17" t="n">
         <v>19.9</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
         <v>20</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
         <v>20.6</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
         <v>20.7</v>
       </c>
-      <c r="AI17" t="n">
-        <v>20.8</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -5477,13 +5477,13 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>40.1</v>
+        <v>39.96</v>
       </c>
       <c r="CA17" t="n">
         <v>1.14</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CC17" t="n">
         <v>10</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.64999961853027</v>
+        <v>11.51000022888184</v>
       </c>
       <c r="D18" t="n">
-        <v>11.64999961853027</v>
+        <v>11.51000022888184</v>
       </c>
       <c r="E18" t="n">
         <v>11.93000030517578</v>
@@ -5548,67 +5548,67 @@
         <v>11.84000015258789</v>
       </c>
       <c r="H18" t="n">
-        <v>1631100</v>
+        <v>2088100</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.002568551871716451</v>
+        <v>-0.0145548006722751</v>
       </c>
       <c r="J18" t="n">
-        <v>12.0722221798367</v>
+        <v>12.05666669209798</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.497471758030009</v>
+        <v>-4.534142621479577</v>
       </c>
       <c r="M18" t="n">
-        <v>12.07999992370605</v>
+        <v>12.06599998474121</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.559605197777686</v>
+        <v>-4.60798737412977</v>
       </c>
       <c r="P18" t="n">
-        <v>10.37192296981812</v>
+        <v>10.36653837790856</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>12.32246568385931</v>
+        <v>11.03031512824022</v>
       </c>
       <c r="S18" t="n">
-        <v>10.16519994735718</v>
+        <v>10.16239995956421</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>14.60669420043356</v>
+        <v>13.26064979413993</v>
       </c>
       <c r="V18" t="n">
-        <v>9.023266655604045</v>
+        <v>9.022333326339721</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>29.110665385189</v>
+        <v>27.5723231736478</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.790299987792968</v>
+        <v>8.789599990844726</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>32.53244638645496</v>
+        <v>30.95021662954727</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9894659761546709</v>
+        <v>0.9910297819613113</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5756,13 +5756,13 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0.59</v>
+        <v>-0.58</v>
       </c>
       <c r="CC18" t="n">
         <v>1</v>
@@ -5797,13 +5797,13 @@
         <v>10</v>
       </c>
       <c r="CM18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN18" t="n">
         <v>-1</v>
       </c>
       <c r="CO18" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.4399995803833</v>
+        <v>11.42000007629395</v>
       </c>
       <c r="D19" t="n">
-        <v>11.4399995803833</v>
+        <v>11.42000007629395</v>
       </c>
       <c r="E19" t="n">
         <v>11.72000026702881</v>
@@ -5831,67 +5831,67 @@
         <v>11.65999984741211</v>
       </c>
       <c r="H19" t="n">
-        <v>1987100</v>
+        <v>3194300</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006156525552223124</v>
+        <v>0.004397554198603659</v>
       </c>
       <c r="J19" t="n">
-        <v>11.20555538601345</v>
+        <v>11.20333321889242</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.092213962571412</v>
+        <v>1.933949951931801</v>
       </c>
       <c r="M19" t="n">
-        <v>11.1899998664856</v>
+        <v>11.18799991607666</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.234135092766725</v>
+        <v>2.073651787250301</v>
       </c>
       <c r="P19" t="n">
-        <v>11.43615374198327</v>
+        <v>11.43538453028752</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.03362877490808367</v>
+        <v>-0.1345337706207514</v>
       </c>
       <c r="S19" t="n">
-        <v>11.8421999168396</v>
+        <v>11.84179992675781</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.396331249942584</v>
+        <v>-3.561957245289753</v>
       </c>
       <c r="V19" t="n">
-        <v>13.17993330637614</v>
+        <v>13.17979997634888</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.20138490496837</v>
+        <v>-13.35225043788896</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.02184997081757</v>
+        <v>14.02174997329712</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-18.41305102969752</v>
+        <v>-18.55510119605556</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5953765924370386</v>
+        <v>0.5951170461259218</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6043,7 +6043,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
@@ -6081,7 +6081,7 @@
         <v>1</v>
       </c>
       <c r="CL19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM19" t="n">
         <v>9</v>
@@ -6090,7 +6090,7 @@
         <v>-1</v>
       </c>
       <c r="CO19" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.22999954223633</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D20" t="n">
-        <v>11.22999954223633</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="E20" t="n">
         <v>11.35000038146973</v>
@@ -6118,67 +6118,67 @@
         <v>11.35000038146973</v>
       </c>
       <c r="H20" t="n">
-        <v>3529000</v>
+        <v>5318400</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002678547632328998</v>
+        <v>0.0008928775939409661</v>
       </c>
       <c r="J20" t="n">
-        <v>11.32111114925808</v>
+        <v>11.31888898213704</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8047938565440739</v>
+        <v>-0.9620108843007099</v>
       </c>
       <c r="M20" t="n">
-        <v>11.31700000762939</v>
+        <v>11.31500005722046</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7687590822162622</v>
+        <v>-0.9279718828324927</v>
       </c>
       <c r="P20" t="n">
-        <v>11.97769238398625</v>
+        <v>11.97692317229051</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-6.242378062318283</v>
+        <v>-6.403340182709602</v>
       </c>
       <c r="S20" t="n">
-        <v>12.36580009460449</v>
+        <v>12.3654001045227</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.185014666893585</v>
+        <v>-9.343814649015188</v>
       </c>
       <c r="V20" t="n">
-        <v>11.69826669692993</v>
+        <v>11.69813336690267</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.002876381818974</v>
+        <v>-4.172745458149445</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.51185002803802</v>
+        <v>11.51175003051758</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.448350917665075</v>
+        <v>-2.62123475206349</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2217282113089539</v>
+        <v>0.2211363442500854</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6326,10 +6326,10 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.64</v>
+        <v>6.63</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="CB20" t="n">
         <v>1.11</v>
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.519999980926514</v>
+        <v>4.630000114440918</v>
       </c>
       <c r="D21" t="n">
-        <v>4.519999980926514</v>
+        <v>4.630000114440918</v>
       </c>
       <c r="E21" t="n">
-        <v>4.550000190734863</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="F21" t="n">
         <v>4.460000038146973</v>
@@ -6397,67 +6397,67 @@
         <v>4.480000019073486</v>
       </c>
       <c r="H21" t="n">
-        <v>3490000</v>
+        <v>8445100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00221723980868993</v>
+        <v>0.02660751207740697</v>
       </c>
       <c r="J21" t="n">
-        <v>4.445555528004964</v>
+        <v>4.45777776506212</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.674581555726474</v>
+        <v>3.863412634173736</v>
       </c>
       <c r="M21" t="n">
-        <v>4.477999973297119</v>
+        <v>4.48899998664856</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9379188896794568</v>
+        <v>3.141014217236103</v>
       </c>
       <c r="P21" t="n">
-        <v>4.662692308425903</v>
+        <v>4.666923082791842</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
       </c>
       <c r="R21" t="n">
-        <v>-3.060299030273386</v>
+        <v>-0.7911629931735569</v>
       </c>
       <c r="S21" t="n">
-        <v>4.795600004196167</v>
+        <v>4.797800006866455</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-5.746935170333276</v>
+        <v>-3.497434077814576</v>
       </c>
       <c r="V21" t="n">
-        <v>5.34240000406901</v>
+        <v>5.34313333829244</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-15.39383090963088</v>
+        <v>-13.34672333068569</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.311800012588501</v>
+        <v>5.312350013256073</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-14.90643529096522</v>
+        <v>-12.84459602835781</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5012494765791459</v>
+        <v>0.5083386969086204</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6609,13 +6609,13 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>11.02</v>
+        <v>11.29</v>
       </c>
       <c r="CA21" t="n">
         <v>0.01</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="CC21" t="n">
         <v>3</v>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CM21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CN21" t="n">
         <v>-1</v>
       </c>
       <c r="CO21" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -6678,13 +6678,13 @@
         <v>2.619999885559082</v>
       </c>
       <c r="F22" t="n">
-        <v>2.519999980926514</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
         <v>2.599999904632568</v>
       </c>
       <c r="H22" t="n">
-        <v>7885500</v>
+        <v>12527900</v>
       </c>
       <c r="I22" t="n">
         <v>-0.003937004178520276</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="CL22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM22" t="n">
         <v>6</v>
@@ -6939,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="CO22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.84999847412109</v>
+        <v>43.79000091552734</v>
       </c>
       <c r="D23" t="n">
-        <v>43.84999847412109</v>
+        <v>43.79000091552734</v>
       </c>
       <c r="E23" t="n">
         <v>44.29999923706055</v>
@@ -6967,67 +6967,67 @@
         <v>44.13999938964844</v>
       </c>
       <c r="H23" t="n">
-        <v>938000</v>
+        <v>1365200</v>
       </c>
       <c r="I23" t="n">
-        <v>0.005964632269398251</v>
+        <v>0.004588225791221534</v>
       </c>
       <c r="J23" t="n">
-        <v>43.8977779812283</v>
+        <v>43.89111158582899</v>
       </c>
       <c r="K23" t="n">
         <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1088426551513374</v>
+        <v>-0.2303670758119879</v>
       </c>
       <c r="M23" t="n">
-        <v>44.02900009155273</v>
+        <v>44.02300033569336</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4065539009730555</v>
+        <v>-0.5292674701617366</v>
       </c>
       <c r="P23" t="n">
-        <v>47.86923071054312</v>
+        <v>47.86692311213567</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-8.396274969877044</v>
+        <v>-8.517201297976689</v>
       </c>
       <c r="S23" t="n">
-        <v>48.91199974060059</v>
+        <v>48.91079978942871</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.34920120486846</v>
+        <v>-10.46966906275809</v>
       </c>
       <c r="V23" t="n">
-        <v>48.78840001424154</v>
+        <v>48.78800003051758</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-10.12208135269635</v>
+        <v>-10.24432055395572</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.29479999542237</v>
+        <v>46.2945000076294</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-5.280941966577271</v>
+        <v>-5.4099279432531</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2747441786598346</v>
+        <v>0.2742017392505117</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7179,7 +7179,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.77</v>
+        <v>8.76</v>
       </c>
       <c r="CA23" t="n">
         <v>0.51</v>
@@ -7220,13 +7220,13 @@
         <v>2</v>
       </c>
       <c r="CM23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -7239,82 +7239,82 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.73999977111816</v>
+        <v>14.64000034332275</v>
       </c>
       <c r="D24" t="n">
-        <v>14.73999977111816</v>
+        <v>14.64000034332275</v>
       </c>
       <c r="E24" t="n">
         <v>15.05000019073486</v>
       </c>
       <c r="F24" t="n">
-        <v>14.72999954223633</v>
+        <v>14.60999965667725</v>
       </c>
       <c r="G24" t="n">
         <v>14.98999977111816</v>
       </c>
       <c r="H24" t="n">
-        <v>9756700</v>
+        <v>15852600</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.002706357413782334</v>
+        <v>-0.009472218685912859</v>
       </c>
       <c r="J24" t="n">
-        <v>14.83777766757541</v>
+        <v>14.82666662004259</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6589793879370494</v>
+        <v>-1.258990179677346</v>
       </c>
       <c r="M24" t="n">
-        <v>14.84699993133545</v>
+        <v>14.83699998855591</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7206853957846114</v>
+        <v>-1.327759286817442</v>
       </c>
       <c r="P24" t="n">
-        <v>15.48038445986234</v>
+        <v>15.47653832802406</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-4.782728043117106</v>
+        <v>-5.405200872255437</v>
       </c>
       <c r="S24" t="n">
-        <v>15.60279989242554</v>
+        <v>15.60079990386963</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.529777522342153</v>
+        <v>-6.15865575141796</v>
       </c>
       <c r="V24" t="n">
-        <v>14.1401332728068</v>
+        <v>14.13946660995483</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>4.242297344290077</v>
+        <v>3.539976062573119</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.49614995002747</v>
+        <v>13.49564995288849</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>9.216330773563813</v>
+        <v>8.479401840067279</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2277991240596569</v>
+        <v>0.2282796465917406</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7466,13 +7466,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>16.2</v>
+        <v>16.09</v>
       </c>
       <c r="CA24" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="CB24" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CC24" t="n">
         <v>3</v>
@@ -7500,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="CL24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM24" t="n">
         <v>4</v>
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="CO24" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -7522,82 +7522,82 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.179999828338623</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="D25" t="n">
-        <v>4.179999828338623</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="E25" t="n">
         <v>4.369999885559082</v>
       </c>
       <c r="F25" t="n">
-        <v>4.159999847412109</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="G25" t="n">
         <v>4.340000152587891</v>
       </c>
       <c r="H25" t="n">
-        <v>13846100</v>
+        <v>29719000</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.02336457396440272</v>
+        <v>-0.03271035898594565</v>
       </c>
       <c r="J25" t="n">
-        <v>4.312222215864393</v>
+        <v>4.307777775658502</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.066223884273227</v>
+        <v>-3.894767044877537</v>
       </c>
       <c r="M25" t="n">
-        <v>4.346000003814697</v>
+        <v>4.342000007629395</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.819608268071044</v>
+        <v>-4.652237236040103</v>
       </c>
       <c r="P25" t="n">
-        <v>4.798461528924795</v>
+        <v>4.796923068853525</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-12.88874979737</v>
+        <v>-13.69467871255512</v>
       </c>
       <c r="S25" t="n">
-        <v>5.052199983596802</v>
+        <v>5.051399984359741</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-17.26376940916807</v>
+        <v>-18.04252525430659</v>
       </c>
       <c r="V25" t="n">
-        <v>5.588799997965495</v>
+        <v>5.588533331553141</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-25.20756101738694</v>
+        <v>-25.91974278634168</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.75964998960495</v>
+        <v>5.759449989795685</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-27.4261485353674</v>
+        <v>-28.11813847119695</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4311668064627621</v>
+        <v>0.4347223835394273</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7749,13 +7749,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.74</v>
+        <v>-1.72</v>
       </c>
       <c r="CA25" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7809,10 +7809,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50.52999877929688</v>
+        <v>51.25</v>
       </c>
       <c r="D26" t="n">
-        <v>50.52999877929688</v>
+        <v>51.25</v>
       </c>
       <c r="E26" t="n">
         <v>51.43999862670898</v>
@@ -7824,67 +7824,67 @@
         <v>50.59999847412109</v>
       </c>
       <c r="H26" t="n">
-        <v>7595400</v>
+        <v>10867600</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0512579727426048</v>
+        <v>-0.0377393613382927</v>
       </c>
       <c r="J26" t="n">
-        <v>52.33222198486328</v>
+        <v>52.41222212049696</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.443811742004164</v>
+        <v>-2.217463930121083</v>
       </c>
       <c r="M26" t="n">
-        <v>52.32399978637695</v>
+        <v>52.39599990844727</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.428638893059475</v>
+        <v>-2.187189690910943</v>
       </c>
       <c r="P26" t="n">
-        <v>53.91346124502329</v>
+        <v>53.94115359966572</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-6.275728524179544</v>
+        <v>-4.989054590190291</v>
       </c>
       <c r="S26" t="n">
-        <v>55.16399993896484</v>
+        <v>55.17839996337891</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.400408173437695</v>
+        <v>-7.119452477756022</v>
       </c>
       <c r="V26" t="n">
-        <v>48.7107332611084</v>
+        <v>48.71553326924642</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.734835007382264</v>
+        <v>5.202584392837919</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.27769992828369</v>
+        <v>44.28129993438721</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>14.12064958464418</v>
+        <v>15.73734302276244</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3102084098623191</v>
+        <v>0.2942747187431597</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8036,13 +8036,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.19</v>
+        <v>14.4</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8074,16 +8074,16 @@
         <v>0</v>
       </c>
       <c r="CL26" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM26" t="n">
         <v>3</v>
       </c>
-      <c r="CM26" t="n">
-        <v>2</v>
-      </c>
       <c r="CN26" t="n">
         <v>0</v>
       </c>
       <c r="CO26" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.539999961853027</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="D27" t="n">
-        <v>6.539999961853027</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="E27" t="n">
         <v>6.869999885559082</v>
@@ -8111,67 +8111,67 @@
         <v>6.840000152587891</v>
       </c>
       <c r="H27" t="n">
-        <v>6217100</v>
+        <v>9175100</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.02242153872712416</v>
+        <v>-0.02092673621646612</v>
       </c>
       <c r="J27" t="n">
-        <v>6.402222262488471</v>
+        <v>6.403333399030897</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2.152029306633345</v>
+        <v>2.290475640799262</v>
       </c>
       <c r="M27" t="n">
-        <v>6.429000043869019</v>
+        <v>6.430000066757202</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.726550275728539</v>
+        <v>1.866253852749647</v>
       </c>
       <c r="P27" t="n">
-        <v>6.449615368476281</v>
+        <v>6.449999992664043</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.40139509432637</v>
+        <v>1.550390669527997</v>
       </c>
       <c r="S27" t="n">
-        <v>6.437999973297119</v>
+        <v>6.438199977874756</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.584342792466194</v>
+        <v>1.736513516888491</v>
       </c>
       <c r="V27" t="n">
-        <v>8.110999994277954</v>
+        <v>8.111066662470499</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-19.36875888957238</v>
+        <v>-19.24613046220681</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.018999984264374</v>
+        <v>8.019049985408783</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-18.44369653714401</v>
+        <v>-18.3194991594635</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4840475259491932</v>
+        <v>0.4834501786691952</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8323,13 +8323,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>-4.33</v>
+        <v>-4.34</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="CC27" t="n">
         <v>2</v>
@@ -8360,13 +8360,13 @@
         <v>9</v>
       </c>
       <c r="CM27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN27" t="n">
         <v>0</v>
       </c>
       <c r="CO27" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
@@ -8379,82 +8379,82 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31.76000022888184</v>
+        <v>31.56999969482422</v>
       </c>
       <c r="D28" t="n">
-        <v>31.76000022888184</v>
+        <v>31.56999969482422</v>
       </c>
       <c r="E28" t="n">
         <v>33.04999923706055</v>
       </c>
       <c r="F28" t="n">
-        <v>31.72999954223633</v>
+        <v>31.40999984741211</v>
       </c>
       <c r="G28" t="n">
         <v>32.52000045776367</v>
       </c>
       <c r="H28" t="n">
-        <v>866400</v>
+        <v>1726500</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.009975111717826612</v>
+        <v>-0.01589782129428585</v>
       </c>
       <c r="J28" t="n">
-        <v>30.82777807447646</v>
+        <v>30.80666690402561</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>3.023968033483426</v>
+        <v>2.477816873784757</v>
       </c>
       <c r="M28" t="n">
-        <v>30.80500030517578</v>
+        <v>30.78600025177002</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.100145801802177</v>
+        <v>2.546610266493205</v>
       </c>
       <c r="P28" t="n">
-        <v>31.02192328526424</v>
+        <v>31.01461557241587</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.379210782099363</v>
+        <v>1.790717415508789</v>
       </c>
       <c r="S28" t="n">
-        <v>33.14220012664795</v>
+        <v>33.1384001159668</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.170513401295763</v>
+        <v>-4.732879124079645</v>
       </c>
       <c r="V28" t="n">
-        <v>34.75333324432373</v>
+        <v>34.75206657409668</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.613081785272476</v>
+        <v>-9.156482456914649</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.29034994125366</v>
+        <v>34.28939993858337</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-7.379188945889519</v>
+        <v>-7.930731504867222</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.494307929754804</v>
+        <v>0.4952397089673741</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8606,13 +8606,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>9.18</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>6.34</v>
+        <v>6.3</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8647,13 +8647,13 @@
         <v>7</v>
       </c>
       <c r="CM28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN28" t="n">
         <v>-1</v>
       </c>
       <c r="CO28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
@@ -8666,82 +8666,82 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.63999938964844</v>
+        <v>17.48999977111816</v>
       </c>
       <c r="D29" t="n">
-        <v>17.63999938964844</v>
+        <v>17.48999977111816</v>
       </c>
       <c r="E29" t="n">
         <v>17.84000015258789</v>
       </c>
       <c r="F29" t="n">
-        <v>17.61000061035156</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="G29" t="n">
         <v>17.64999961853027</v>
       </c>
       <c r="H29" t="n">
-        <v>780600</v>
+        <v>1491800</v>
       </c>
       <c r="I29" t="n">
-        <v>0.001134991456442469</v>
+        <v>-0.007378039836738792</v>
       </c>
       <c r="J29" t="n">
-        <v>17.6233336130778</v>
+        <v>17.60666698879666</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.09456653852520623</v>
+        <v>-0.6626309099429798</v>
       </c>
       <c r="M29" t="n">
-        <v>17.61500034332276</v>
+        <v>17.60000038146973</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1419190794121015</v>
+        <v>-0.62500345436002</v>
       </c>
       <c r="P29" t="n">
-        <v>17.80076936575083</v>
+        <v>17.79500014965351</v>
       </c>
       <c r="Q29" t="n">
         <v>-1</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.9031630757023124</v>
+        <v>-1.713966709583208</v>
       </c>
       <c r="S29" t="n">
-        <v>18.11420013427734</v>
+        <v>18.11120014190674</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-2.61783982242517</v>
+        <v>-3.429923836748983</v>
       </c>
       <c r="V29" t="n">
-        <v>17.04940010706584</v>
+        <v>17.04840010960897</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>3.464047291246558</v>
+        <v>2.590270398805924</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.35060009002686</v>
+        <v>16.3498500919342</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>7.885944812558035</v>
+        <v>6.973456470689138</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2316263282904076</v>
+        <v>0.2313890277501444</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>12.08</v>
+        <v>11.98</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC29" t="n">
         <v>2</v>
@@ -8942,13 +8942,13 @@
         <v>8</v>
       </c>
       <c r="CM29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN29" t="n">
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
@@ -8961,106 +8961,106 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.35000038146973</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="D30" t="n">
-        <v>22.35000038146973</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="E30" t="n">
         <v>22.79999923706055</v>
       </c>
       <c r="F30" t="n">
-        <v>22.29999923706055</v>
+        <v>22.02000045776367</v>
       </c>
       <c r="G30" t="n">
         <v>22.70000076293945</v>
       </c>
       <c r="H30" t="n">
-        <v>5892600</v>
+        <v>6690000</v>
       </c>
       <c r="I30" t="n">
-        <v>0.003141817444654471</v>
+        <v>-0.005834877204162536</v>
       </c>
       <c r="J30" t="n">
-        <v>21.97666676839193</v>
+        <v>21.95444446139865</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.698772689290398</v>
+        <v>0.8907315212436958</v>
       </c>
       <c r="M30" t="n">
-        <v>21.96700000762939</v>
+        <v>21.94699993133545</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.743526078696734</v>
+        <v>0.9249541524123628</v>
       </c>
       <c r="P30" t="n">
-        <v>23.21923079857459</v>
+        <v>23.21153846153846</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-3.743579727706688</v>
+        <v>-4.573323930109834</v>
       </c>
       <c r="S30" t="n">
-        <v>25.16239994049072</v>
+        <v>25.15839992523193</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-11.1769925192841</v>
+        <v>-11.95783641106868</v>
       </c>
       <c r="V30" t="n">
-        <v>28.73546660105387</v>
+        <v>28.73413326263428</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-22.22155049102268</v>
+        <v>-22.91398033107189</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.6293999671936</v>
+        <v>28.62839996337891</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-21.93339571531165</v>
+        <v>-22.62927845473628</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.401435860233374</v>
+        <v>0.4002724241039495</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AE30" t="n">
         <v>22</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AF30" t="n">
         <v>22.1</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AG30" t="n">
         <v>22.2</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
         <v>22.6</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>22.8</v>
       </c>
-      <c r="AI30" t="n">
-        <v>22.9</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -9184,13 +9184,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>5.16</v>
+        <v>5.12</v>
       </c>
       <c r="CA30" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CC30" t="n">
         <v>8</v>
@@ -9221,13 +9221,13 @@
         <v>2</v>
       </c>
       <c r="CM30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN30" t="n">
         <v>0</v>
       </c>
       <c r="CO30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -9240,82 +9240,82 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.42000007629395</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="D31" t="n">
-        <v>13.42000007629395</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="E31" t="n">
         <v>13.75</v>
       </c>
       <c r="F31" t="n">
-        <v>13.35999965667725</v>
+        <v>13.27000045776367</v>
       </c>
       <c r="G31" t="n">
         <v>13.64000034332275</v>
       </c>
       <c r="H31" t="n">
-        <v>3008300</v>
+        <v>4939200</v>
       </c>
       <c r="I31" t="n">
-        <v>0.001492571517391239</v>
+        <v>-0.003731286454023874</v>
       </c>
       <c r="J31" t="n">
-        <v>13.08444436391195</v>
+        <v>13.07666662004259</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>2.564539257834214</v>
+        <v>2.090240344647153</v>
       </c>
       <c r="M31" t="n">
-        <v>13.12199993133545</v>
+        <v>13.11499996185303</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.270996391692321</v>
+        <v>1.791844607702893</v>
       </c>
       <c r="P31" t="n">
-        <v>13.25692312534039</v>
+        <v>13.25423082938561</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.230126699926601</v>
+        <v>0.7225583537581659</v>
       </c>
       <c r="S31" t="n">
-        <v>13.53060005187988</v>
+        <v>13.5292000579834</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.8174062876876745</v>
+        <v>-1.324540074399513</v>
       </c>
       <c r="V31" t="n">
-        <v>15.02800001780192</v>
+        <v>15.02753335316976</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.70002621508627</v>
+        <v>-11.1630627081336</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.03676666259766</v>
+        <v>15.03641666412354</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-10.7520893459446</v>
+        <v>-11.2155463653621</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4760339732885214</v>
+        <v>0.4759782989003583</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9467,13 +9467,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>8.34</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
       </c>
       <c r="CB31" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC31" t="n">
         <v>9</v>
@@ -9523,10 +9523,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>32.72999954223633</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="D32" t="n">
-        <v>32.72999954223633</v>
+        <v>32.65000152587891</v>
       </c>
       <c r="E32" t="n">
         <v>32.97000122070312</v>
@@ -9538,67 +9538,67 @@
         <v>32.36000061035156</v>
       </c>
       <c r="H32" t="n">
-        <v>734200</v>
+        <v>1073400</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01488370673601014</v>
+        <v>0.01240314808926835</v>
       </c>
       <c r="J32" t="n">
-        <v>32.36000061035156</v>
+        <v>32.3511119418674</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.143383575111576</v>
+        <v>0.9238927692766411</v>
       </c>
       <c r="M32" t="n">
-        <v>32.37400054931641</v>
+        <v>32.36600074768067</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.099644736144415</v>
+        <v>0.8774663895371508</v>
       </c>
       <c r="P32" t="n">
-        <v>33.98576941856971</v>
+        <v>33.98269257178674</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.694987336809369</v>
+        <v>-3.921675844527581</v>
       </c>
       <c r="S32" t="n">
-        <v>33.86560009002685</v>
+        <v>33.8640001296997</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-3.353256829265368</v>
+        <v>-3.584923810451106</v>
       </c>
       <c r="V32" t="n">
-        <v>32.18697137196859</v>
+        <v>32.18643805185954</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.687105518541141</v>
+        <v>1.440244718202313</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.29801411628723</v>
+        <v>31.29761412620545</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.575323599218086</v>
+        <v>4.321055893334402</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2169592622181908</v>
+        <v>0.2151747297536945</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9748,13 +9748,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>14.55</v>
+        <v>14.51</v>
       </c>
       <c r="CA32" t="n">
         <v>0.66</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CC32" t="n">
         <v>2</v>
@@ -9782,7 +9782,7 @@
         <v>0</v>
       </c>
       <c r="CL32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM32" t="n">
         <v>7</v>
@@ -9791,7 +9791,7 @@
         <v>1</v>
       </c>
       <c r="CO32" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
@@ -9804,61 +9804,61 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>73.30999755859375</v>
+        <v>73.25</v>
       </c>
       <c r="D33" t="n">
-        <v>73.30999755859375</v>
+        <v>73.25</v>
       </c>
       <c r="E33" t="n">
         <v>74.69999694824219</v>
       </c>
       <c r="F33" t="n">
-        <v>72.91000366210938</v>
+        <v>72.80000305175781</v>
       </c>
       <c r="G33" t="n">
         <v>73.58000183105469</v>
       </c>
       <c r="H33" t="n">
-        <v>1722700</v>
+        <v>2088600</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01284885797825686</v>
+        <v>0.0120199334014337</v>
       </c>
       <c r="J33" t="n">
-        <v>71.43110995822482</v>
+        <v>71.42444356282552</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>2.630349159445737</v>
+        <v>2.555926719357232</v>
       </c>
       <c r="M33" t="n">
-        <v>71.54099884033204</v>
+        <v>71.53499908447266</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>2.472706206143183</v>
+        <v>2.397429143043909</v>
       </c>
       <c r="P33" t="n">
-        <v>75.60423044057993</v>
+        <v>75.60192284217247</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-3.034529772496389</v>
+        <v>-3.110929925793521</v>
       </c>
       <c r="S33" t="n">
-        <v>77.64039962768555</v>
+        <v>77.63919967651367</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-5.57751130836225</v>
+        <v>-5.653329368156057</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
-        <v>0.4851270556584271</v>
+        <v>0.4848645963593949</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10021,7 +10021,7 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>32.01</v>
+        <v>31.99</v>
       </c>
       <c r="CA33" t="n">
         <v>0.06</v>
@@ -10081,10 +10081,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.20000076293945</v>
+        <v>25.23999977111816</v>
       </c>
       <c r="D34" t="n">
-        <v>25.20000076293945</v>
+        <v>25.23999977111816</v>
       </c>
       <c r="E34" t="n">
         <v>25.29999923706055</v>
@@ -10096,67 +10096,67 @@
         <v>25.29999923706055</v>
       </c>
       <c r="H34" t="n">
-        <v>1413300</v>
+        <v>2094200</v>
       </c>
       <c r="I34" t="n">
-        <v>0.005586644053497958</v>
+        <v>0.007182773703583223</v>
       </c>
       <c r="J34" t="n">
-        <v>25.04777738783095</v>
+        <v>25.05222172207302</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6077320664086571</v>
+        <v>0.7495464918374553</v>
       </c>
       <c r="M34" t="n">
-        <v>25.1379997253418</v>
+        <v>25.14199962615967</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.246642685476495</v>
+        <v>0.3897865977872764</v>
       </c>
       <c r="P34" t="n">
-        <v>26.28038450387808</v>
+        <v>26.28192292726957</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-4.11098909446777</v>
+        <v>-3.964409906515355</v>
       </c>
       <c r="S34" t="n">
-        <v>25.73519992828369</v>
+        <v>25.73599990844727</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-2.079638653811427</v>
+        <v>-1.927261964149683</v>
       </c>
       <c r="V34" t="n">
-        <v>21.9814000193278</v>
+        <v>21.98166667938233</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>14.64238283631435</v>
+        <v>14.82295741838351</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.35835003376007</v>
+        <v>20.35855002880096</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>23.78213716313215</v>
+        <v>23.97739394707128</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.259056604623716</v>
+        <v>0.2595027974360374</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>37.61</v>
+        <v>37.67</v>
       </c>
       <c r="CA34" t="n">
         <v>0.38</v>
@@ -10364,82 +10364,82 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.65000152587891</v>
+        <v>48.36000061035156</v>
       </c>
       <c r="D35" t="n">
-        <v>48.65000152587891</v>
+        <v>48.36000061035156</v>
       </c>
       <c r="E35" t="n">
         <v>49.20000076293945</v>
       </c>
       <c r="F35" t="n">
-        <v>48.40999984741211</v>
+        <v>48.15000152587891</v>
       </c>
       <c r="G35" t="n">
         <v>49.16999816894531</v>
       </c>
       <c r="H35" t="n">
-        <v>769900</v>
+        <v>1300100</v>
       </c>
       <c r="I35" t="n">
-        <v>0.003713643504075215</v>
+        <v>-0.00226945755273833</v>
       </c>
       <c r="J35" t="n">
-        <v>48.39111158582899</v>
+        <v>48.35888926188151</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5349948194323475</v>
+        <v>0.002298126543056197</v>
       </c>
       <c r="M35" t="n">
-        <v>48.46000061035156</v>
+        <v>48.43100051879883</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3920778232238737</v>
+        <v>-0.1466001273702857</v>
       </c>
       <c r="P35" t="n">
-        <v>51.44076948899489</v>
+        <v>51.42961560762846</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-5.425206486681799</v>
+        <v>-5.968574645192533</v>
       </c>
       <c r="S35" t="n">
-        <v>52.38119995117187</v>
+        <v>52.37539993286133</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-7.123163327245412</v>
+        <v>-7.666575009750765</v>
       </c>
       <c r="V35" t="n">
-        <v>50.41494529724121</v>
+        <v>50.41301195780436</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-3.500834446921209</v>
+        <v>-4.072383830530043</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.88475425720215</v>
+        <v>48.88330425262451</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.4802166542315278</v>
+        <v>-1.070516100074913</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2449965816400458</v>
+        <v>0.2436273574431324</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10591,13 +10591,13 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.87</v>
+        <v>12.79</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CC35" t="n">
         <v>5</v>
@@ -10628,13 +10628,13 @@
         <v>4</v>
       </c>
       <c r="CM35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36">
@@ -10647,82 +10647,82 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.27000045776367</v>
+        <v>38.04000091552734</v>
       </c>
       <c r="D36" t="n">
-        <v>38.27000045776367</v>
+        <v>38.04000091552734</v>
       </c>
       <c r="E36" t="n">
         <v>39.04999923706055</v>
       </c>
       <c r="F36" t="n">
-        <v>38.09999847412109</v>
+        <v>37.93999862670898</v>
       </c>
       <c r="G36" t="n">
         <v>39.02999877929688</v>
       </c>
       <c r="H36" t="n">
-        <v>2877800</v>
+        <v>5149000</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.008549171746176754</v>
+        <v>-0.01450770934535639</v>
       </c>
       <c r="J36" t="n">
-        <v>38.3055551317003</v>
+        <v>38.27999962700738</v>
       </c>
       <c r="K36" t="n">
         <v>-1</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.09281858418286332</v>
+        <v>-0.6269558877182162</v>
       </c>
       <c r="M36" t="n">
-        <v>38.35499954223633</v>
+        <v>38.33199958801269</v>
       </c>
       <c r="N36" t="n">
         <v>-1</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.2216114860829439</v>
+        <v>-0.7617621716156532</v>
       </c>
       <c r="P36" t="n">
-        <v>40.97230764535757</v>
+        <v>40.96346150911771</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-6.595447859525411</v>
+        <v>-7.136751841490889</v>
       </c>
       <c r="S36" t="n">
-        <v>41.43699996948242</v>
+        <v>41.4323999786377</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-7.642926645392248</v>
+        <v>-8.187792801912162</v>
       </c>
       <c r="V36" t="n">
-        <v>40.04033332824707</v>
+        <v>40.0387999979655</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-4.421373958029696</v>
+        <v>-4.992155315693076</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.04344999313354</v>
+        <v>39.04229999542236</v>
       </c>
       <c r="Z36" t="n">
         <v>-1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-1.980996903464972</v>
+        <v>-2.567213202123172</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2545989933278944</v>
+        <v>0.2559028989653203</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10874,13 +10874,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>31.11</v>
+        <v>30.93</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CC36" t="n">
         <v>8</v>
@@ -10930,82 +10930,82 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.10000038146973</v>
+        <v>16.03000068664551</v>
       </c>
       <c r="D37" t="n">
-        <v>16.10000038146973</v>
+        <v>16.03000068664551</v>
       </c>
       <c r="E37" t="n">
         <v>16.39999961853027</v>
       </c>
       <c r="F37" t="n">
-        <v>16.07999992370605</v>
+        <v>15.96000003814697</v>
       </c>
       <c r="G37" t="n">
         <v>16.34000015258789</v>
       </c>
       <c r="H37" t="n">
-        <v>1015700</v>
+        <v>1784800</v>
       </c>
       <c r="I37" t="n">
-        <v>0.003115336248348477</v>
+        <v>-0.001246015661412692</v>
       </c>
       <c r="J37" t="n">
-        <v>15.75444433424208</v>
+        <v>15.74666659037272</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>2.193387719023426</v>
+        <v>1.79932746176269</v>
       </c>
       <c r="M37" t="n">
-        <v>15.77499990463257</v>
+        <v>15.76799993515015</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>2.060224905242099</v>
+        <v>1.661597872735315</v>
       </c>
       <c r="P37" t="n">
-        <v>16.08846147243793</v>
+        <v>16.08576917648315</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>0.07172164381015184</v>
+        <v>-0.346694579698297</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06759996414184</v>
+        <v>16.06619997024536</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>0.2016506348190754</v>
+        <v>-0.2253132891840881</v>
       </c>
       <c r="V37" t="n">
-        <v>15.85380003611247</v>
+        <v>15.85333337148031</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.552942164001397</v>
+        <v>1.11438592140516</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.69595001220703</v>
+        <v>15.69560001373291</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.574233282779681</v>
+        <v>2.130537683299857</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.270297717736284</v>
+        <v>0.2698510279465743</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11157,13 +11157,13 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>13.88</v>
+        <v>13.82</v>
       </c>
       <c r="CA37" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="CB37" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CC37" t="n">
         <v>9</v>
@@ -11217,10 +11217,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23.78000068664551</v>
+        <v>23.69000053405762</v>
       </c>
       <c r="D38" t="n">
-        <v>23.78000068664551</v>
+        <v>23.69000053405762</v>
       </c>
       <c r="E38" t="n">
         <v>24.04999923706055</v>
@@ -11232,67 +11232,67 @@
         <v>24.02000045776367</v>
       </c>
       <c r="H38" t="n">
-        <v>4624100</v>
+        <v>6982900</v>
       </c>
       <c r="I38" t="n">
-        <v>0.007200341884760819</v>
+        <v>0.003388391428968518</v>
       </c>
       <c r="J38" t="n">
-        <v>23.57444466484917</v>
+        <v>23.56444464789497</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8719442799975216</v>
+        <v>0.5328192029930446</v>
       </c>
       <c r="M38" t="n">
-        <v>23.57500019073486</v>
+        <v>23.56600017547607</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.8695673139006488</v>
+        <v>0.5261833050081383</v>
       </c>
       <c r="P38" t="n">
-        <v>23.11038472102238</v>
+        <v>23.10692317669208</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.897467842731351</v>
+        <v>2.523388133101533</v>
       </c>
       <c r="S38" t="n">
-        <v>21.33560009002685</v>
+        <v>21.3338000869751</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>11.45691045156619</v>
+        <v>11.04444795337258</v>
       </c>
       <c r="V38" t="n">
-        <v>20.61546669006348</v>
+        <v>20.61486668904622</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>15.35029036285322</v>
+        <v>14.91706879019196</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.67020004272461</v>
+        <v>19.66975004196167</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>20.89353761016267</v>
+        <v>20.43874723125361</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.2596753358598956</v>
+        <v>0.2595135062640872</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11442,10 +11442,10 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>28.65</v>
+        <v>28.54</v>
       </c>
       <c r="CA38" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="CB38" t="n">
         <v>0.89</v>
@@ -11498,10 +11498,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.28999996185303</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="D39" t="n">
-        <v>10.28999996185303</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="E39" t="n">
         <v>10.38000011444092</v>
@@ -11513,67 +11513,67 @@
         <v>10.3100004196167</v>
       </c>
       <c r="H39" t="n">
-        <v>3574100</v>
+        <v>5692600</v>
       </c>
       <c r="I39" t="n">
-        <v>0.008823544536357586</v>
+        <v>0.009803959150949337</v>
       </c>
       <c r="J39" t="n">
-        <v>10.23888884650336</v>
+        <v>10.23999998304579</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4991861530669665</v>
+        <v>0.5859395291837399</v>
       </c>
       <c r="M39" t="n">
-        <v>10.24200000762939</v>
+        <v>10.24300003051758</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.4686580178468725</v>
+        <v>0.5564791569604725</v>
       </c>
       <c r="P39" t="n">
-        <v>10.07038464913001</v>
+        <v>10.07076927331778</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>2.180803617486305</v>
+        <v>2.276200667454736</v>
       </c>
       <c r="S39" t="n">
-        <v>9.398800001144409</v>
+        <v>9.399000005722046</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>9.482061120569703</v>
+        <v>9.586128146231458</v>
       </c>
       <c r="V39" t="n">
-        <v>9.072844982147217</v>
+        <v>9.072911650339762</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>13.41536179776934</v>
+        <v>13.5247491399208</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.593540859222411</v>
+        <v>8.593590860366822</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>19.7410954392567</v>
+        <v>19.85676718957973</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.2634022232272986</v>
+        <v>0.2635893749154926</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11729,7 +11729,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.93</v>
+        <v>23.95</v>
       </c>
       <c r="CA39" t="n">
         <v>0.6</v>
@@ -11770,13 +11770,13 @@
         <v>10</v>
       </c>
       <c r="CM39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
       </c>
       <c r="CO39" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40">
@@ -11789,103 +11789,105 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.67000007629395</v>
+        <v>12.52999973297119</v>
       </c>
       <c r="D40" t="n">
-        <v>12.67000007629395</v>
+        <v>12.52999973297119</v>
       </c>
       <c r="E40" t="n">
         <v>13.03999996185303</v>
       </c>
       <c r="F40" t="n">
-        <v>12.56999969482422</v>
+        <v>12.47000026702881</v>
       </c>
       <c r="G40" t="n">
         <v>12.72999954223633</v>
       </c>
       <c r="H40" t="n">
-        <v>2335900</v>
+        <v>3408400</v>
       </c>
       <c r="I40" t="n">
-        <v>0.005555531167059646</v>
+        <v>-0.005555606855495165</v>
       </c>
       <c r="J40" t="n">
-        <v>12.5911111831665</v>
+        <v>12.57555558946398</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6265443294068496</v>
+        <v>-0.3622572073948923</v>
       </c>
       <c r="M40" t="n">
-        <v>12.65800008773804</v>
+        <v>12.64400005340576</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.09480161536365525</v>
+        <v>-0.9016159439501381</v>
       </c>
       <c r="P40" t="n">
-        <v>12.45346157367413</v>
+        <v>12.44807694508479</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.73878163383557</v>
+        <v>0.6581160146085693</v>
       </c>
       <c r="S40" t="n">
-        <v>11.5639999961853</v>
+        <v>11.56119998931885</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>9.56416534480705</v>
+        <v>8.379750757251824</v>
       </c>
       <c r="V40" t="n">
-        <v>15.22293333689372</v>
+        <v>15.22200000127157</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-16.77031097819092</v>
+        <v>-17.68493146810865</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.84304997444153</v>
+        <v>20.84234997272491</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-39.21235091874586</v>
+        <v>-39.88202026466103</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6864648487520625</v>
+        <v>0.6864211227353177</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
         <v>7</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AF40" t="n">
         <v>11.6</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AG40" t="n">
         <v>12.6</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
         <v>13.3</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AI40" t="n">
         <v>14</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>14.8</v>
       </c>
       <c r="AJ40" t="n">
         <v>1</v>
@@ -12012,10 +12014,10 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-14.91</v>
+        <v>-14.74</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="CB40" t="n">
         <v>0.13</v>
@@ -12053,13 +12055,13 @@
         <v>10</v>
       </c>
       <c r="CM40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN40" t="n">
         <v>-1</v>
       </c>
       <c r="CO40" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
@@ -12072,103 +12074,103 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22.68000030517578</v>
+        <v>22.59000015258789</v>
       </c>
       <c r="D41" t="n">
-        <v>22.68000030517578</v>
+        <v>22.59000015258789</v>
       </c>
       <c r="E41" t="n">
         <v>23.03000068664551</v>
       </c>
       <c r="F41" t="n">
-        <v>22.53000068664551</v>
+        <v>22.44000053405762</v>
       </c>
       <c r="G41" t="n">
         <v>23.03000068664551</v>
       </c>
       <c r="H41" t="n">
-        <v>506700</v>
+        <v>654800</v>
       </c>
       <c r="I41" t="n">
-        <v>0.006657772479305102</v>
+        <v>0.002663092060088079</v>
       </c>
       <c r="J41" t="n">
-        <v>22.6488889058431</v>
+        <v>22.63888888888889</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.137363909823661</v>
+        <v>-0.2159502462375401</v>
       </c>
       <c r="M41" t="n">
-        <v>22.72100009918213</v>
+        <v>22.71200008392334</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.1804488967359411</v>
+        <v>-0.5371606678612423</v>
       </c>
       <c r="P41" t="n">
-        <v>22.85461543156551</v>
+        <v>22.8511538872352</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.7640256599923186</v>
+        <v>-1.14284703492892</v>
       </c>
       <c r="S41" t="n">
-        <v>22.89120002746582</v>
+        <v>22.88940002441406</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.9226240740399526</v>
+        <v>-1.30802848264624</v>
       </c>
       <c r="V41" t="n">
-        <v>23.66260004679362</v>
+        <v>23.66200004577637</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-4.152543421579683</v>
+        <v>-4.530470336888646</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.51239998817444</v>
+        <v>23.5119499874115</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-3.540258261246453</v>
+        <v>-3.921196818286987</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.2992391673434082</v>
+        <v>0.2985942144812817</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AE41" t="n">
         <v>22.4</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AF41" t="n">
         <v>22.5</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AG41" t="n">
         <v>22.6</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>22.9</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>23</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>23.2</v>
       </c>
       <c r="AJ41" t="n">
         <v>2</v>
@@ -12295,7 +12297,7 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>9.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="CA41" t="n">
         <v>0.39</v>
@@ -12351,82 +12353,82 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>26.19000053405762</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="D42" t="n">
-        <v>26.19000053405762</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="E42" t="n">
         <v>26.6299991607666</v>
       </c>
       <c r="F42" t="n">
-        <v>26.14999961853027</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="G42" t="n">
         <v>26.57999992370605</v>
       </c>
       <c r="H42" t="n">
-        <v>322500</v>
+        <v>568300</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.004560962916023703</v>
+        <v>-0.004941055241558745</v>
       </c>
       <c r="J42" t="n">
-        <v>26.3044442070855</v>
+        <v>26.30333307054308</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4350735264615793</v>
+        <v>-0.468886452665628</v>
       </c>
       <c r="M42" t="n">
-        <v>26.32599983215332</v>
+        <v>26.32499980926514</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.5165968964627945</v>
+        <v>-0.5508053376635642</v>
       </c>
       <c r="P42" t="n">
-        <v>27.36499977111816</v>
+        <v>27.3646151469304</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.29380320441543</v>
+        <v>-4.329002382799827</v>
       </c>
       <c r="S42" t="n">
-        <v>27.69379985809326</v>
+        <v>27.69359985351563</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-5.430093854008163</v>
+        <v>-5.465521118041635</v>
       </c>
       <c r="V42" t="n">
-        <v>26.94446656545003</v>
+        <v>26.94439989725749</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.800077817683876</v>
+        <v>-2.836951630010172</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.0063999080658</v>
+        <v>26.00634990692139</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.705982476009219</v>
+        <v>0.6677230710034375</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.2971865144653714</v>
+        <v>0.2971997595583538</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12615,13 +12617,13 @@
         <v>6</v>
       </c>
       <c r="CM42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN42" t="n">
         <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -12634,10 +12636,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.3799991607666</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="D43" t="n">
-        <v>27.3799991607666</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="E43" t="n">
         <v>27.92000007629395</v>
@@ -12649,67 +12651,67 @@
         <v>27.79000091552734</v>
       </c>
       <c r="H43" t="n">
-        <v>2222900</v>
+        <v>3002000</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01439890266349764</v>
+        <v>-0.01403892323100453</v>
       </c>
       <c r="J43" t="n">
-        <v>28.1477779812283</v>
+        <v>28.14888911777073</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.727671153913914</v>
+        <v>-2.695984644179765</v>
       </c>
       <c r="M43" t="n">
-        <v>28.22200012207031</v>
+        <v>28.2230001449585</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-2.983491452277491</v>
+        <v>-2.951496123840894</v>
       </c>
       <c r="P43" t="n">
-        <v>29.13730768057016</v>
+        <v>29.13769230475793</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-6.031128678973317</v>
+        <v>-5.99804849618824</v>
       </c>
       <c r="S43" t="n">
-        <v>29.21340000152588</v>
+        <v>29.21360000610352</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-6.275889970573489</v>
+        <v>-6.242300216591171</v>
       </c>
       <c r="V43" t="n">
-        <v>27.9553332901001</v>
+        <v>27.95539995829264</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-2.058047827092942</v>
+        <v>-2.02250931658191</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.77829999923706</v>
+        <v>26.77835000038147</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.246965496490385</v>
+        <v>2.284119033690483</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2504916067567867</v>
+        <v>0.250364829764933</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12917,10 +12919,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13.14000034332275</v>
+        <v>13.10999965667725</v>
       </c>
       <c r="D44" t="n">
-        <v>13.14000034332275</v>
+        <v>13.10999965667725</v>
       </c>
       <c r="E44" t="n">
         <v>13.1899995803833</v>
@@ -12932,67 +12934,67 @@
         <v>13.14000034332275</v>
       </c>
       <c r="H44" t="n">
-        <v>6579100</v>
+        <v>9972500</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01154738836393965</v>
+        <v>0.009237866641528925</v>
       </c>
       <c r="J44" t="n">
-        <v>12.95111105177138</v>
+        <v>12.9477776421441</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.458479436986552</v>
+        <v>1.252894658965478</v>
       </c>
       <c r="M44" t="n">
-        <v>12.97299995422363</v>
+        <v>12.96999988555908</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.287291988656411</v>
+        <v>1.079412277204732</v>
       </c>
       <c r="P44" t="n">
-        <v>13.45115386522733</v>
+        <v>13.44999999266404</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.313210636218683</v>
+        <v>-2.527883540314065</v>
       </c>
       <c r="S44" t="n">
-        <v>13.70600002288818</v>
+        <v>13.70540000915527</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-4.12957594207095</v>
+        <v>-4.344275629170229</v>
       </c>
       <c r="V44" t="n">
-        <v>12.89993971506755</v>
+        <v>12.89973971048991</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.860943799410233</v>
+        <v>1.629954951853457</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.39466055393219</v>
+        <v>12.39451055049896</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>6.013394123601916</v>
+        <v>5.772628965566377</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2380189825229078</v>
+        <v>0.2368290232669848</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13144,7 +13146,7 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.699999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
@@ -13200,82 +13202,82 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40.66999816894531</v>
+        <v>40.45000076293945</v>
       </c>
       <c r="D45" t="n">
-        <v>40.66999816894531</v>
+        <v>40.45000076293945</v>
       </c>
       <c r="E45" t="n">
         <v>40.81999969482422</v>
       </c>
       <c r="F45" t="n">
-        <v>40.40000152587891</v>
+        <v>40.29000091552734</v>
       </c>
       <c r="G45" t="n">
         <v>40.59999847412109</v>
       </c>
       <c r="H45" t="n">
-        <v>8559600</v>
+        <v>14243500</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01522707875045137</v>
+        <v>0.009735381334970761</v>
       </c>
       <c r="J45" t="n">
-        <v>39.81888834635416</v>
+        <v>39.79444419013129</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>2.137452495378557</v>
+        <v>1.647357027217211</v>
       </c>
       <c r="M45" t="n">
-        <v>39.87699966430664</v>
+        <v>39.85499992370605</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>1.988611257903831</v>
+        <v>1.492913913868781</v>
       </c>
       <c r="P45" t="n">
-        <v>41.59192276000977</v>
+        <v>41.58346132131723</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.216595266307031</v>
+        <v>-2.725748464322096</v>
       </c>
       <c r="S45" t="n">
-        <v>42.68919975280762</v>
+        <v>42.6847998046875</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-4.730005705317782</v>
+        <v>-5.235585154372985</v>
       </c>
       <c r="V45" t="n">
-        <v>41.83173433939616</v>
+        <v>41.83026769002279</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-2.777164726246475</v>
+        <v>-3.299684662100669</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.55452880859375</v>
+        <v>40.55342882156372</v>
       </c>
       <c r="Z45" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.2847261791563275</v>
+        <v>-0.2550414641369877</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2458905696002045</v>
+        <v>0.242680952369193</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13447,13 +13449,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.66</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CC45" t="n">
         <v>10</v>
@@ -13481,16 +13483,16 @@
         <v>0</v>
       </c>
       <c r="CL45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN45" t="n">
         <v>0</v>
       </c>
       <c r="CO45" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
@@ -13503,82 +13505,82 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.84000015258789</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="D46" t="n">
-        <v>16.84000015258789</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="E46" t="n">
         <v>17.1299991607666</v>
       </c>
       <c r="F46" t="n">
-        <v>16.76000022888184</v>
+        <v>16.70999908447266</v>
       </c>
       <c r="G46" t="n">
         <v>16.80999946594238</v>
       </c>
       <c r="H46" t="n">
-        <v>2987900</v>
+        <v>4569100</v>
       </c>
       <c r="I46" t="n">
-        <v>0.01384705200389869</v>
+        <v>0.01023480253143383</v>
       </c>
       <c r="J46" t="n">
-        <v>16.47999996609158</v>
+        <v>16.47333335876465</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>2.184467155564499</v>
+        <v>1.861598507127259</v>
       </c>
       <c r="M46" t="n">
-        <v>16.51800003051758</v>
+        <v>16.51200008392334</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.949389281241116</v>
+        <v>1.623065657461465</v>
       </c>
       <c r="P46" t="n">
-        <v>17.15884626828707</v>
+        <v>17.15653859652006</v>
       </c>
       <c r="Q46" t="n">
         <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.858202531299969</v>
+        <v>-2.194719568613478</v>
       </c>
       <c r="S46" t="n">
-        <v>18.08560005187988</v>
+        <v>18.08440006256103</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-6.887246736181806</v>
+        <v>-7.212842955271379</v>
       </c>
       <c r="V46" t="n">
-        <v>18.50918928782145</v>
+        <v>18.50878929138183</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.018164487257385</v>
+        <v>-9.340365690700768</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.38392148971558</v>
+        <v>18.38362149238586</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-8.398215462307066</v>
+        <v>-8.723095209529548</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.1920257898172265</v>
+        <v>0.1893329902169105</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13734,13 +13736,13 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>28.07</v>
+        <v>27.97</v>
       </c>
       <c r="CA46" t="n">
         <v>0.24</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CC46" t="n">
         <v>4</v>
@@ -13794,103 +13796,103 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.05000019073486</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="D47" t="n">
-        <v>15.05000019073486</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="E47" t="n">
         <v>15.51000022888184</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>14.85000038146973</v>
       </c>
       <c r="G47" t="n">
         <v>15.13000011444092</v>
       </c>
       <c r="H47" t="n">
-        <v>3025800</v>
+        <v>5102600</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0006649088369148348</v>
+        <v>-0.007978715815388671</v>
       </c>
       <c r="J47" t="n">
-        <v>14.56444454193115</v>
+        <v>14.55000008477105</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>3.333842546523435</v>
+        <v>2.542955253382858</v>
       </c>
       <c r="M47" t="n">
-        <v>14.48000011444092</v>
+        <v>14.46700010299683</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>3.936464584178311</v>
+        <v>3.131264049713257</v>
       </c>
       <c r="P47" t="n">
-        <v>14.24192314881545</v>
+        <v>14.23692314441388</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>5.673932048893447</v>
+        <v>4.797925260614249</v>
       </c>
       <c r="S47" t="n">
-        <v>14.71280004501343</v>
+        <v>14.71020004272461</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>2.291882882182732</v>
+        <v>1.426221485499774</v>
       </c>
       <c r="V47" t="n">
-        <v>14.6771333694458</v>
+        <v>14.67626670201619</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>2.540460810046731</v>
+        <v>1.660731432771436</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.94340002536774</v>
+        <v>14.94275002479553</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.7133595111297516</v>
+        <v>-0.1522474006714766</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4684106806509712</v>
+        <v>0.4687775789995374</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AE47" t="n">
         <v>14.8</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AF47" t="n">
         <v>14.9</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AG47" t="n">
         <v>15</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>15.1</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>15.2</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>15.3</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14017,13 +14019,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>10.17</v>
+        <v>10.08</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14073,82 +14075,82 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.1299991607666</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="D48" t="n">
-        <v>16.1299991607666</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="E48" t="n">
         <v>16.54999923706055</v>
       </c>
       <c r="F48" t="n">
-        <v>16.11000061035156</v>
+        <v>15.96000003814697</v>
       </c>
       <c r="G48" t="n">
         <v>16.5</v>
       </c>
       <c r="H48" t="n">
-        <v>1819000</v>
+        <v>2875900</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.014058767787541</v>
+        <v>-0.02078240463956704</v>
       </c>
       <c r="J48" t="n">
-        <v>16.78111097547743</v>
+        <v>16.76888889736599</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-3.880028060492021</v>
+        <v>-4.465939539500168</v>
       </c>
       <c r="M48" t="n">
-        <v>16.84499988555908</v>
+        <v>16.83400001525879</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-4.244587293855901</v>
+        <v>-4.835449428283741</v>
       </c>
       <c r="P48" t="n">
-        <v>17.40500002640944</v>
+        <v>17.40076930706318</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-7.325486145982311</v>
+        <v>-7.9351023218211</v>
       </c>
       <c r="S48" t="n">
-        <v>18.48340007781982</v>
+        <v>18.48120010375976</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-12.73251083212398</v>
+        <v>-13.31731506708481</v>
       </c>
       <c r="V48" t="n">
-        <v>18.86833339055379</v>
+        <v>18.86760006586711</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-14.51285692862575</v>
+        <v>-15.09253746190515</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.57160003185272</v>
+        <v>19.57105003833771</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-17.58466791414562</v>
+        <v>-18.14439988461471</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.5026060309019564</v>
+        <v>0.5036564205925965</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14296,13 +14298,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>59.74</v>
+        <v>59.33</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14356,82 +14358,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.760000228881836</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="D49" t="n">
-        <v>6.760000228881836</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="E49" t="n">
         <v>6.829999923706055</v>
       </c>
       <c r="F49" t="n">
-        <v>6.71999979019165</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="G49" t="n">
         <v>6.739999771118164</v>
       </c>
       <c r="H49" t="n">
-        <v>7539100</v>
+        <v>9180600</v>
       </c>
       <c r="I49" t="n">
-        <v>0.01654137322359328</v>
+        <v>0.01353378563309016</v>
       </c>
       <c r="J49" t="n">
-        <v>6.688888920678033</v>
+        <v>6.686666647593181</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>1.063125865103987</v>
+        <v>0.797604043027632</v>
       </c>
       <c r="M49" t="n">
-        <v>6.71100001335144</v>
+        <v>6.708999967575073</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7301477489630523</v>
+        <v>0.4620629556254994</v>
       </c>
       <c r="P49" t="n">
-        <v>7.551538394047664</v>
+        <v>7.550769145672138</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-10.48181342479488</v>
+        <v>-10.73757333739545</v>
       </c>
       <c r="S49" t="n">
-        <v>8.19459997177124</v>
+        <v>8.194199962615967</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-17.50664764395228</v>
+        <v>-17.74670130253393</v>
       </c>
       <c r="V49" t="n">
-        <v>8.849644231796265</v>
+        <v>8.849510895411173</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-23.61274587069227</v>
+        <v>-23.83760130050662</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.725471150875091</v>
+        <v>8.725371148586273</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-22.52567096959727</v>
+        <v>-22.75400488596738</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4403643814619106</v>
+        <v>0.4388805074707386</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14579,13 +14581,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>37.56</v>
+        <v>37.44</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="CC49" t="n">
         <v>2</v>
@@ -14639,109 +14641,113 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.52000045776367</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="D50" t="n">
-        <v>14.52000045776367</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="E50" t="n">
         <v>14.8100004196167</v>
       </c>
       <c r="F50" t="n">
-        <v>14.48999977111816</v>
+        <v>14.38000011444092</v>
       </c>
       <c r="G50" t="n">
         <v>14.71000003814697</v>
       </c>
       <c r="H50" t="n">
-        <v>1276200</v>
+        <v>2076600</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0006891956391517073</v>
+        <v>-0.005513433662586498</v>
       </c>
       <c r="J50" t="n">
-        <v>14.73333337571886</v>
+        <v>14.72333335876465</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.44796097743073</v>
+        <v>-1.992300564289329</v>
       </c>
       <c r="M50" t="n">
-        <v>14.73600006103516</v>
+        <v>14.72700004577637</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-1.465795347291218</v>
+        <v>-2.016702245382044</v>
       </c>
       <c r="P50" t="n">
-        <v>15.46846151351929</v>
+        <v>15.46499996918898</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.13157976264588</v>
+        <v>-6.692529363564429</v>
       </c>
       <c r="S50" t="n">
-        <v>15.74380004882813</v>
+        <v>15.74200004577637</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-7.773216042308325</v>
+        <v>-8.334390400110561</v>
       </c>
       <c r="V50" t="n">
-        <v>15.84440003077189</v>
+        <v>15.84380002975464</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-8.358786514074772</v>
+        <v>-8.923362589301455</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.42880001544952</v>
+        <v>15.42835001468658</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-5.890280234210251</v>
+        <v>-6.470878017159659</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.3253063695119644</v>
+        <v>0.3248860328736564</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="AE50" t="n">
         <v>13.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG50" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>15.1</v>
+        <v>17.8</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AJ50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
@@ -14862,13 +14868,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CB50" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CC50" t="n">
         <v>5</v>
@@ -14922,82 +14928,82 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6.059999942779541</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="D51" t="n">
-        <v>6.059999942779541</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="E51" t="n">
         <v>6.340000152587891</v>
       </c>
       <c r="F51" t="n">
-        <v>6.03000020980835</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="G51" t="n">
         <v>6.320000171661377</v>
       </c>
       <c r="H51" t="n">
-        <v>4127800</v>
+        <v>7357600</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.01463417092557195</v>
+        <v>-0.0292683418511438</v>
       </c>
       <c r="J51" t="n">
-        <v>6.183333343929714</v>
+        <v>6.173333326975505</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.994610257770621</v>
+        <v>-3.293739800106881</v>
       </c>
       <c r="M51" t="n">
-        <v>6.207999992370605</v>
+        <v>6.198999977111816</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.384021420311706</v>
+        <v>-3.694147245776559</v>
       </c>
       <c r="P51" t="n">
-        <v>6.637307717249944</v>
+        <v>6.633846172919641</v>
       </c>
       <c r="Q51" t="n">
         <v>-1</v>
       </c>
       <c r="R51" t="n">
-        <v>-8.697920889971943</v>
+        <v>-10.00696074982732</v>
       </c>
       <c r="S51" t="n">
-        <v>7.170000009536743</v>
+        <v>7.168200006484986</v>
       </c>
       <c r="T51" t="n">
         <v>-1</v>
       </c>
       <c r="U51" t="n">
-        <v>-15.4811724585886</v>
+        <v>-16.71549643159144</v>
       </c>
       <c r="V51" t="n">
-        <v>7.956933358510335</v>
+        <v>7.956333357493083</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-23.84000632230921</v>
+        <v>-24.96543920486629</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.788800008296967</v>
+        <v>7.788350007534027</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-22.19597452336474</v>
+        <v>-23.34705317022737</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.437961347406114</v>
+        <v>0.4417745315781466</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15149,13 +15155,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>-4.49</v>
+        <v>-4.42</v>
       </c>
       <c r="CA51" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CB51" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="CC51" t="n">
         <v>7</v>
@@ -15190,13 +15196,13 @@
         <v>1</v>
       </c>
       <c r="CM51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -15209,82 +15215,82 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>29.95000076293945</v>
+        <v>29.89999961853027</v>
       </c>
       <c r="D52" t="n">
-        <v>29.95000076293945</v>
+        <v>29.89999961853027</v>
       </c>
       <c r="E52" t="n">
         <v>30.47999954223633</v>
       </c>
       <c r="F52" t="n">
-        <v>29.82999992370605</v>
+        <v>29.75</v>
       </c>
       <c r="G52" t="n">
         <v>30.45999908447266</v>
       </c>
       <c r="H52" t="n">
-        <v>525700</v>
+        <v>935600</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.00166664123535154</v>
+        <v>-0.003333346048990937</v>
       </c>
       <c r="J52" t="n">
-        <v>29.83555560641819</v>
+        <v>29.82999992370605</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.383586476588516</v>
+        <v>0.2346620683984301</v>
       </c>
       <c r="M52" t="n">
-        <v>29.84099998474121</v>
+        <v>29.83599987030029</v>
       </c>
       <c r="N52" t="n">
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.3652718684158697</v>
+        <v>0.2145051230332297</v>
       </c>
       <c r="P52" t="n">
-        <v>31.12653827667236</v>
+        <v>31.12461515573355</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.779853394794822</v>
+        <v>-3.934556398772642</v>
       </c>
       <c r="S52" t="n">
-        <v>31.6153999710083</v>
+        <v>31.61439994812012</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-5.267683501066061</v>
+        <v>-5.422846337122354</v>
       </c>
       <c r="V52" t="n">
-        <v>30.58926670074463</v>
+        <v>30.5889333597819</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-2.089837406235096</v>
+        <v>-2.252231985824757</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.85395005226135</v>
+        <v>29.85370004653931</v>
       </c>
       <c r="Z52" t="n">
         <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.3217353499619186</v>
+        <v>0.1550882199485853</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.3009137451443207</v>
+        <v>0.300849840749737</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15436,7 +15442,7 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>12.58</v>
+        <v>12.56</v>
       </c>
       <c r="CA52" t="n">
         <v>0.29</v>
@@ -15505,13 +15511,13 @@
         <v>10.5600004196167</v>
       </c>
       <c r="F53" t="n">
-        <v>10.02999973297119</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="G53" t="n">
         <v>10.55000019073486</v>
       </c>
       <c r="H53" t="n">
-        <v>4318800</v>
+        <v>6594900</v>
       </c>
       <c r="I53" t="n">
         <v>-0.03365379236858779</v>
@@ -15764,13 +15770,13 @@
         <v>9</v>
       </c>
       <c r="CM53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -15783,13 +15789,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>48.36999893188477</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="D54" t="n">
-        <v>48.36999893188477</v>
+        <v>48.11999893188477</v>
       </c>
       <c r="E54" t="n">
-        <v>48.43999862670898</v>
+        <v>48.54000091552734</v>
       </c>
       <c r="F54" t="n">
         <v>47.54999923706055</v>
@@ -15798,67 +15804,67 @@
         <v>47.63000106811523</v>
       </c>
       <c r="H54" t="n">
-        <v>5119900</v>
+        <v>7618200</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.01063613140223874</v>
+        <v>-0.01574965161334618</v>
       </c>
       <c r="J54" t="n">
-        <v>49.99888865152995</v>
+        <v>49.97111087375217</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.257851851463776</v>
+        <v>-3.704364200636005</v>
       </c>
       <c r="M54" t="n">
-        <v>49.93699989318848</v>
+        <v>49.91199989318848</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-3.137955753560307</v>
+        <v>-3.590320895052473</v>
       </c>
       <c r="P54" t="n">
-        <v>51.27846174973708</v>
+        <v>51.2688463651217</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-5.671899504409809</v>
+        <v>-6.141833991761317</v>
       </c>
       <c r="S54" t="n">
-        <v>51.84720008850098</v>
+        <v>51.84220008850097</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-6.706632471340352</v>
+        <v>-7.179867270798608</v>
       </c>
       <c r="V54" t="n">
-        <v>41.40293342590332</v>
+        <v>41.40126675923666</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>16.82746832045135</v>
+        <v>16.22832511797277</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.40955006599426</v>
+        <v>39.40830006599426</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>22.73674490291201</v>
+        <v>22.10625388890575</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3638213471516117</v>
+        <v>0.3649328984757468</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16010,13 +16016,13 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.79</v>
+        <v>5.76</v>
       </c>
       <c r="CA54" t="n">
         <v>0.52</v>
       </c>
       <c r="CB54" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CC54" t="n">
         <v>1</v>
@@ -16066,13 +16072,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>43.08000183105469</v>
+        <v>42.81000137329102</v>
       </c>
       <c r="D55" t="n">
-        <v>43.08000183105469</v>
+        <v>42.81000137329102</v>
       </c>
       <c r="E55" t="n">
-        <v>43.13999938964844</v>
+        <v>43.18999862670898</v>
       </c>
       <c r="F55" t="n">
         <v>42.15000152587891</v>
@@ -16081,67 +16087,67 @@
         <v>42.25</v>
       </c>
       <c r="H55" t="n">
-        <v>27380500</v>
+        <v>36330500</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.008287219314803473</v>
+        <v>-0.01450269966239404</v>
       </c>
       <c r="J55" t="n">
-        <v>44.66111119588216</v>
+        <v>44.63111114501953</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-3.540237406751441</v>
+        <v>-4.080359473487446</v>
       </c>
       <c r="M55" t="n">
-        <v>44.69500007629394</v>
+        <v>44.66800003051758</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-3.61337564041273</v>
+        <v>-4.159574317088651</v>
       </c>
       <c r="P55" t="n">
-        <v>46.28230769817646</v>
+        <v>46.27192306518555</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-6.919071296109862</v>
+        <v>-7.481689678247328</v>
       </c>
       <c r="S55" t="n">
-        <v>46.94919990539551</v>
+        <v>46.94379989624024</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-8.241243902212197</v>
+        <v>-8.805845568714387</v>
       </c>
       <c r="V55" t="n">
-        <v>38.26780011494954</v>
+        <v>38.26600011189779</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>12.57506755457633</v>
+        <v>11.87477459913661</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.44260005950927</v>
+        <v>36.44125005722046</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>18.2133046508943</v>
+        <v>17.47676412326765</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.3216406170833636</v>
+        <v>0.3227610763141934</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16293,13 +16299,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>5.16</v>
+        <v>5.13</v>
       </c>
       <c r="CA55" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CC55" t="n">
         <v>1</v>
@@ -16334,13 +16340,13 @@
         <v>3</v>
       </c>
       <c r="CM55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN55" t="n">
         <v>0</v>
       </c>
       <c r="CO55" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
@@ -16353,10 +16359,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.260000228881836</v>
+        <v>6.230000019073486</v>
       </c>
       <c r="D56" t="n">
-        <v>6.260000228881836</v>
+        <v>6.230000019073486</v>
       </c>
       <c r="E56" t="n">
         <v>6.340000152587891</v>
@@ -16368,67 +16374,67 @@
         <v>6.21999979019165</v>
       </c>
       <c r="H56" t="n">
-        <v>2450600</v>
+        <v>3441000</v>
       </c>
       <c r="I56" t="n">
-        <v>0.01623382856279409</v>
+        <v>0.0113636645122297</v>
       </c>
       <c r="J56" t="n">
-        <v>6.041111098395453</v>
+        <v>6.037777741750081</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>3.623325691602004</v>
+        <v>3.183659378420389</v>
       </c>
       <c r="M56" t="n">
-        <v>6.048000001907349</v>
+        <v>6.044999980926514</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>3.505294757070581</v>
+        <v>3.060381120441583</v>
       </c>
       <c r="P56" t="n">
-        <v>6.302692321630625</v>
+        <v>6.301538467407227</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-0.6773627930760799</v>
+        <v>-1.135253695645133</v>
       </c>
       <c r="S56" t="n">
-        <v>6.302000007629394</v>
+        <v>6.301400003433227</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.6664515819852799</v>
+        <v>-1.133081288615856</v>
       </c>
       <c r="V56" t="n">
-        <v>6.372684713999431</v>
+        <v>6.372484712600708</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-1.768241960410359</v>
+        <v>-2.235936215672329</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.849149792194367</v>
+        <v>6.848999791145324</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-8.60179118850569</v>
+        <v>-9.037812687220507</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3422870523300636</v>
+        <v>0.3403194703316538</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16580,13 +16586,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>6.26</v>
+        <v>6.23</v>
       </c>
       <c r="CA56" t="n">
         <v>0.2</v>
       </c>
       <c r="CB56" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CC56" t="n">
         <v>9</v>
@@ -16640,10 +16646,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>63.61999893188477</v>
+        <v>62.81000137329102</v>
       </c>
       <c r="D57" t="n">
-        <v>63.61999893188477</v>
+        <v>62.81000137329102</v>
       </c>
       <c r="E57" t="n">
         <v>64.15000152587891</v>
@@ -16655,67 +16661,67 @@
         <v>63.15999984741211</v>
       </c>
       <c r="H57" t="n">
-        <v>4925000</v>
+        <v>6262200</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.01745175394772558</v>
+        <v>-0.0299613687522623</v>
       </c>
       <c r="J57" t="n">
-        <v>67.18333307902019</v>
+        <v>67.09333335028754</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-5.303896046574934</v>
+        <v>-6.384139471255179</v>
       </c>
       <c r="M57" t="n">
-        <v>67.19399986267089</v>
+        <v>67.11300010681153</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-5.318928681267025</v>
+        <v>-6.411572611375162</v>
       </c>
       <c r="P57" t="n">
-        <v>65.79769251896785</v>
+        <v>65.76653876671425</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.309680786230169</v>
+        <v>-4.495504019012773</v>
       </c>
       <c r="S57" t="n">
-        <v>65.93859985351563</v>
+        <v>65.92239990234376</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-3.51630293452044</v>
+        <v>-4.721306465880172</v>
       </c>
       <c r="V57" t="n">
-        <v>51.50339988708496</v>
+        <v>51.49799990336101</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>23.52582367642524</v>
+        <v>21.96590448397538</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.11374996185302</v>
+        <v>48.10969997406006</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>32.22831099701409</v>
+        <v>30.55579520794583</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3925048950534091</v>
+        <v>0.3985977820828747</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16867,13 +16873,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>21.42</v>
+        <v>21.15</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CC57" t="n">
         <v>10</v>
@@ -16923,82 +16929,82 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.79000091552734</v>
+        <v>48.47999954223633</v>
       </c>
       <c r="D58" t="n">
-        <v>48.79000091552734</v>
+        <v>48.47999954223633</v>
       </c>
       <c r="E58" t="n">
         <v>49.4900016784668</v>
       </c>
       <c r="F58" t="n">
-        <v>48.68000030517578</v>
+        <v>48.25</v>
       </c>
       <c r="G58" t="n">
         <v>49.4900016784668</v>
       </c>
       <c r="H58" t="n">
-        <v>603200</v>
+        <v>768200</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.002045376873992533</v>
+        <v>-0.00838617002517128</v>
       </c>
       <c r="J58" t="n">
-        <v>48.78111097547743</v>
+        <v>48.7466663784451</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>0.01822414428892495</v>
+        <v>-0.5470463028969008</v>
       </c>
       <c r="M58" t="n">
-        <v>48.77299995422364</v>
+        <v>48.74199981689453</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>0.03485732130413243</v>
+        <v>-0.5375246720332424</v>
       </c>
       <c r="P58" t="n">
-        <v>50.06153884300819</v>
+        <v>50.04961571326623</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.539949743591294</v>
+        <v>-3.136120325123405</v>
       </c>
       <c r="S58" t="n">
-        <v>50.24800010681152</v>
+        <v>50.2418000793457</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-2.901606408583288</v>
+        <v>-3.50664294337982</v>
       </c>
       <c r="V58" t="n">
-        <v>49.23246671040853</v>
+        <v>49.23040003458659</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-0.8987276576731886</v>
+        <v>-1.524262430983841</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.54860000610351</v>
+        <v>49.54704999923706</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-1.53102023161648</v>
+        <v>-2.153610471293777</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.302861384522528</v>
+        <v>0.3032514827688724</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17150,13 +17156,13 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>8.56</v>
+        <v>8.51</v>
       </c>
       <c r="CA58" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="CB58" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CC58" t="n">
         <v>7</v>
@@ -17210,10 +17216,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18.44000053405762</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="D59" t="n">
-        <v>18.44000053405762</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="E59" t="n">
         <v>18.55999946594238</v>
@@ -17225,67 +17231,67 @@
         <v>18.29999923706055</v>
       </c>
       <c r="H59" t="n">
-        <v>5287100</v>
+        <v>8070700</v>
       </c>
       <c r="I59" t="n">
-        <v>0.02387564129434105</v>
+        <v>0.01887840912087535</v>
       </c>
       <c r="J59" t="n">
-        <v>18.68222236633301</v>
+        <v>18.6722223493788</v>
       </c>
       <c r="K59" t="n">
         <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.296536501524013</v>
+        <v>-1.72567550814214</v>
       </c>
       <c r="M59" t="n">
-        <v>18.77800006866455</v>
+        <v>18.76900005340576</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.799976213499773</v>
+        <v>-2.232402742521197</v>
       </c>
       <c r="P59" t="n">
-        <v>20.5469231238732</v>
+        <v>20.54346157954289</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-10.25419999439027</v>
+        <v>-10.67717429012746</v>
       </c>
       <c r="S59" t="n">
-        <v>21.85880004882813</v>
+        <v>21.85700004577637</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-15.64038056587555</v>
+        <v>-16.04520134035655</v>
       </c>
       <c r="V59" t="n">
-        <v>22.8682181930542</v>
+        <v>22.86761819203695</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-19.36406947674469</v>
+        <v>-19.75552404552724</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.56042826652527</v>
+        <v>21.55997826576233</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-14.47293946991038</v>
+        <v>-14.88859517725076</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3467884519065827</v>
+        <v>0.3430337533183794</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17437,13 +17443,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>24.92</v>
+        <v>24.8</v>
       </c>
       <c r="CA59" t="n">
         <v>0.1</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17497,82 +17503,82 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14.09000015258789</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="D60" t="n">
-        <v>14.09000015258789</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="E60" t="n">
         <v>14.44999980926514</v>
       </c>
       <c r="F60" t="n">
-        <v>14.0600004196167</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="G60" t="n">
         <v>14.44999980926514</v>
       </c>
       <c r="H60" t="n">
-        <v>2872500</v>
+        <v>4488500</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01122805946751648</v>
+        <v>-0.01052628901966834</v>
       </c>
       <c r="J60" t="n">
-        <v>14.56444443596734</v>
+        <v>14.56555557250977</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.257551535627363</v>
+        <v>-3.196274860388453</v>
       </c>
       <c r="M60" t="n">
-        <v>14.63500003814697</v>
+        <v>14.63600006103516</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-3.723948644608877</v>
+        <v>-3.662200583015852</v>
       </c>
       <c r="P60" t="n">
-        <v>15.49384623307448</v>
+        <v>15.49423085726225</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-9.060668728529279</v>
+        <v>-8.998384551234654</v>
       </c>
       <c r="S60" t="n">
-        <v>15.88120006561279</v>
+        <v>15.88140007019043</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-11.27874408498479</v>
+        <v>-11.21689322633721</v>
       </c>
       <c r="V60" t="n">
-        <v>15.63446671168009</v>
+        <v>15.63453337987264</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-9.878600834772149</v>
+        <v>-9.81502268803505</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.52775001525879</v>
+        <v>15.5278000164032</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-9.259228550550159</v>
+        <v>-9.195118648006659</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3426422841109389</v>
+        <v>0.3425285263585565</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17724,13 +17730,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>25.16</v>
+        <v>25.18</v>
       </c>
       <c r="CA60" t="n">
         <v>0.67</v>
       </c>
       <c r="CB60" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CC60" t="n">
         <v>8</v>
@@ -17765,13 +17771,13 @@
         <v>2</v>
       </c>
       <c r="CM60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN60" t="n">
         <v>0</v>
       </c>
       <c r="CO60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61">
@@ -17784,103 +17790,103 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35.2400016784668</v>
+        <v>34.43000030517578</v>
       </c>
       <c r="D61" t="n">
-        <v>35.2400016784668</v>
+        <v>34.43000030517578</v>
       </c>
       <c r="E61" t="n">
         <v>35.65000152587891</v>
       </c>
       <c r="F61" t="n">
-        <v>35.18000030517578</v>
+        <v>34.41999816894531</v>
       </c>
       <c r="G61" t="n">
         <v>35.43000030517578</v>
       </c>
       <c r="H61" t="n">
-        <v>2190400</v>
+        <v>3467100</v>
       </c>
       <c r="I61" t="n">
-        <v>0.006857190813337022</v>
+        <v>-0.01628570556640629</v>
       </c>
       <c r="J61" t="n">
-        <v>34.67888895670573</v>
+        <v>34.58888880411784</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>1.61802392937554</v>
+        <v>-0.4593628313469819</v>
       </c>
       <c r="M61" t="n">
-        <v>34.68600006103516</v>
+        <v>34.60499992370605</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>1.597190844884939</v>
+        <v>-0.5057061664964462</v>
       </c>
       <c r="P61" t="n">
-        <v>36.70153852609488</v>
+        <v>36.67038462712215</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-3.982222289098115</v>
+        <v>-6.109519561159258</v>
       </c>
       <c r="S61" t="n">
-        <v>37.90299987792969</v>
+        <v>37.88679985046387</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-7.025824362291472</v>
+        <v>-9.124020922674369</v>
       </c>
       <c r="V61" t="n">
-        <v>41.15866658528646</v>
+        <v>41.15326657613119</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-14.38011820561623</v>
+        <v>-16.33713877492021</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.72844997406006</v>
+        <v>40.72439996719361</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-13.47571120209301</v>
+        <v>-15.45608938888826</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.4077118120417437</v>
+        <v>0.4072586852104623</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AH61" t="n">
         <v>34.9</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AI61" t="n">
         <v>35.1</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>35.7</v>
       </c>
       <c r="AJ61" t="n">
         <v>1</v>
@@ -18007,13 +18013,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>17.45</v>
+        <v>17.04</v>
       </c>
       <c r="CA61" t="n">
         <v>0.09</v>
       </c>
       <c r="CB61" t="n">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18045,16 +18051,16 @@
         <v>0</v>
       </c>
       <c r="CL61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CN61" t="n">
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62">
@@ -18067,10 +18073,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11.98999977111816</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="D62" t="n">
-        <v>11.98999977111816</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="E62" t="n">
         <v>12.02000045776367</v>
@@ -18082,67 +18088,67 @@
         <v>11.89999961853027</v>
       </c>
       <c r="H62" t="n">
-        <v>718000</v>
+        <v>1027600</v>
       </c>
       <c r="I62" t="n">
-        <v>0.00756303827503868</v>
+        <v>-0.004201616694398003</v>
       </c>
       <c r="J62" t="n">
-        <v>12.15999995337592</v>
+        <v>12.14444446563721</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-1.398027819980071</v>
+        <v>-2.424516699801396</v>
       </c>
       <c r="M62" t="n">
-        <v>12.14699993133545</v>
+        <v>12.13299999237061</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-1.292501532104842</v>
+        <v>-2.332478456101809</v>
       </c>
       <c r="P62" t="n">
-        <v>12.55153850408701</v>
+        <v>12.54615391217745</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-4.473863764079569</v>
+        <v>-5.548740558905709</v>
       </c>
       <c r="S62" t="n">
-        <v>13.04580007553101</v>
+        <v>13.04300008773804</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-8.09302839457983</v>
+        <v>-9.14666639763248</v>
       </c>
       <c r="V62" t="n">
-        <v>11.95960000356038</v>
+        <v>11.95866667429606</v>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>0.2541871596769961</v>
+        <v>-0.9086823454984514</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.16685000419617</v>
+        <v>12.16615000724792</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-1.453541656361425</v>
+        <v>-2.598600424866155</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3513439883030107</v>
+        <v>0.3494670036239227</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18294,13 +18300,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6.59</v>
+        <v>6.51</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="CB62" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="CC62" t="n">
         <v>8</v>
@@ -18328,7 +18334,7 @@
         <v>0</v>
       </c>
       <c r="CL62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM62" t="n">
         <v>3</v>
@@ -18337,7 +18343,7 @@
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -18350,103 +18356,103 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>43.27999877929688</v>
+        <v>43.0099983215332</v>
       </c>
       <c r="D63" t="n">
-        <v>43.27999877929688</v>
+        <v>43.0099983215332</v>
       </c>
       <c r="E63" t="n">
         <v>44.88999938964844</v>
       </c>
       <c r="F63" t="n">
-        <v>43.11999893188477</v>
+        <v>42.77999877929688</v>
       </c>
       <c r="G63" t="n">
         <v>44.7400016784668</v>
       </c>
       <c r="H63" t="n">
-        <v>2325400</v>
+        <v>3368800</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.00961102920617718</v>
+        <v>-0.01578952927596788</v>
       </c>
       <c r="J63" t="n">
-        <v>43.53111139933268</v>
+        <v>43.50111134847005</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.5768578195310088</v>
+        <v>-1.128966621111679</v>
       </c>
       <c r="M63" t="n">
-        <v>43.57200012207031</v>
+        <v>43.54500007629395</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.6701582253634781</v>
+        <v>-1.228618105002597</v>
       </c>
       <c r="P63" t="n">
-        <v>45.94653877845177</v>
+        <v>45.93615414546086</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-5.803570998051906</v>
+        <v>-6.370049644691041</v>
       </c>
       <c r="S63" t="n">
-        <v>46.64020011901855</v>
+        <v>46.63480010986328</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-7.204517414477134</v>
+        <v>-7.772740056332799</v>
       </c>
       <c r="V63" t="n">
-        <v>45.520533396403</v>
+        <v>45.51873339335123</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-4.922030674805684</v>
+        <v>-5.511434270674308</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.38230005264282</v>
+        <v>43.380950050354</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-0.2358133921479614</v>
+        <v>-0.855102823682332</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.5159647628698472</v>
+        <v>0.5169112979880497</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
       <c r="AD63" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AE63" t="n">
         <v>42.7</v>
       </c>
-      <c r="AE63" t="n">
+      <c r="AF63" t="n">
         <v>42.8</v>
       </c>
-      <c r="AF63" t="n">
+      <c r="AG63" t="n">
         <v>43.2</v>
       </c>
-      <c r="AG63" t="n">
+      <c r="AH63" t="n">
         <v>43.3</v>
       </c>
-      <c r="AH63" t="n">
+      <c r="AI63" t="n">
         <v>43.7</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>44.1</v>
       </c>
       <c r="AJ63" t="n">
         <v>1</v>
@@ -18573,13 +18579,13 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>21.64</v>
+        <v>21.5</v>
       </c>
       <c r="CA63" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CC63" t="n">
         <v>10</v>
@@ -18629,82 +18635,82 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.54000091552734</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="D64" t="n">
-        <v>27.54000091552734</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="E64" t="n">
         <v>27.77000045776367</v>
       </c>
       <c r="F64" t="n">
-        <v>27.44000053405762</v>
+        <v>27.31999969482422</v>
       </c>
       <c r="G64" t="n">
         <v>27.70999908447266</v>
       </c>
       <c r="H64" t="n">
-        <v>1335000</v>
+        <v>2189300</v>
       </c>
       <c r="I64" t="n">
-        <v>0.008052753409979241</v>
+        <v>0.005856509853564118</v>
       </c>
       <c r="J64" t="n">
-        <v>27.24000019497342</v>
+        <v>27.23333337571886</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>1.101324223225547</v>
+        <v>0.9057509160351186</v>
       </c>
       <c r="M64" t="n">
-        <v>27.23000011444092</v>
+        <v>27.22399997711182</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1.138453175848579</v>
+        <v>0.9403451562582268</v>
       </c>
       <c r="P64" t="n">
-        <v>28.32500010270339</v>
+        <v>28.32269235757681</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.771400474244386</v>
+        <v>-2.975327361895544</v>
       </c>
       <c r="S64" t="n">
-        <v>29.47619998931885</v>
+        <v>29.47499996185303</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-6.568686175603078</v>
+        <v>-6.768449269545908</v>
       </c>
       <c r="V64" t="n">
-        <v>31.97493335723877</v>
+        <v>31.9745333480835</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-13.87002872582189</v>
+        <v>-14.05660485148742</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.00645002365112</v>
+        <v>31.00615001678467</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-11.17976777567132</v>
+        <v>-11.37242280205546</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2538414988515463</v>
+        <v>0.2529461232747711</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18874,7 +18880,7 @@
         <v>18881600000</v>
       </c>
       <c r="BZ64" t="n">
-        <v>6.67</v>
+        <v>6.65</v>
       </c>
       <c r="CA64" t="n">
         <v>0</v>
@@ -18934,82 +18940,82 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28.86000061035156</v>
+        <v>28.75</v>
       </c>
       <c r="D65" t="n">
-        <v>28.86000061035156</v>
+        <v>28.75</v>
       </c>
       <c r="E65" t="n">
         <v>29.18000030517578</v>
       </c>
       <c r="F65" t="n">
-        <v>28.71999931335449</v>
+        <v>28.64999961853027</v>
       </c>
       <c r="G65" t="n">
         <v>29.1299991607666</v>
       </c>
       <c r="H65" t="n">
-        <v>3277800</v>
+        <v>5651600</v>
       </c>
       <c r="I65" t="n">
-        <v>0.003128263856652325</v>
+        <v>-0.0006951844784651717</v>
       </c>
       <c r="J65" t="n">
-        <v>28.85444471571181</v>
+        <v>28.84222242567274</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.01925490056902766</v>
+        <v>-0.319747987210086</v>
       </c>
       <c r="M65" t="n">
-        <v>28.92100028991699</v>
+        <v>28.91000022888183</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-0.2109182910478283</v>
+        <v>-0.553442502992408</v>
       </c>
       <c r="P65" t="n">
-        <v>31.24023107381968</v>
+        <v>31.23600028111385</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-7.619119262734336</v>
+        <v>-7.958766355297259</v>
       </c>
       <c r="S65" t="n">
-        <v>31.40337371826172</v>
+        <v>31.40117370605469</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-8.099044168719782</v>
+        <v>-8.442912774128237</v>
       </c>
       <c r="V65" t="n">
-        <v>28.72001538594564</v>
+        <v>28.7192820485433</v>
       </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
       <c r="X65" t="n">
-        <v>0.4874134728856341</v>
+        <v>0.1069593292923655</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.52174619674683</v>
+        <v>27.52119619369507</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.862534535555466</v>
+        <v>4.464936035688894</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2726705893569471</v>
+        <v>0.2719032238632966</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19161,13 +19167,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>11.64</v>
+        <v>11.59</v>
       </c>
       <c r="CA65" t="n">
         <v>0.32</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CC65" t="n">
         <v>9</v>
@@ -19199,16 +19205,16 @@
         <v>0</v>
       </c>
       <c r="CL65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66">
@@ -19221,10 +19227,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>16.03000068664551</v>
+        <v>15.98999977111816</v>
       </c>
       <c r="D66" t="n">
-        <v>16.03000068664551</v>
+        <v>15.98999977111816</v>
       </c>
       <c r="E66" t="n">
         <v>16.21999931335449</v>
@@ -19236,67 +19242,67 @@
         <v>16.20000076293945</v>
       </c>
       <c r="H66" t="n">
-        <v>739100</v>
+        <v>1229600</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.006199533746060082</v>
+        <v>-0.00867944184330538</v>
       </c>
       <c r="J66" t="n">
-        <v>16.52555571662055</v>
+        <v>16.52111117045085</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.998719307675932</v>
+        <v>-3.214743813858072</v>
       </c>
       <c r="M66" t="n">
-        <v>16.60700016021729</v>
+        <v>16.60300006866455</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.474435286355947</v>
+        <v>-3.692105613510917</v>
       </c>
       <c r="P66" t="n">
-        <v>17.07769247201773</v>
+        <v>17.07615397526668</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-6.134855672620239</v>
+        <v>-6.360648924352132</v>
       </c>
       <c r="S66" t="n">
-        <v>17.70759998321533</v>
+        <v>17.70679996490479</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-9.473894249700612</v>
+        <v>-9.695711236301038</v>
       </c>
       <c r="V66" t="n">
-        <v>16.01764427185059</v>
+        <v>16.0173775990804</v>
       </c>
       <c r="W66" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>0.07714252224116133</v>
+        <v>-0.1709257822816911</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.73994419574738</v>
+        <v>15.73974419116974</v>
       </c>
       <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.842805077901739</v>
+        <v>1.589959639171405</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.2304873709985218</v>
+        <v>0.2306441753438772</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19306,30 +19312,30 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AE66" t="n">
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AF66" t="n">
         <v>13.5</v>
       </c>
-      <c r="AF66" t="n">
+      <c r="AG66" t="n">
         <v>16</v>
       </c>
-      <c r="AG66" t="n">
+      <c r="AH66" t="n">
         <v>23.3</v>
       </c>
-      <c r="AH66" t="inlineStr">
+      <c r="AI66" t="inlineStr">
         <is>
           <t>Foguete</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ66" t="n">
         <v>1</v>
       </c>
       <c r="AK66" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
@@ -19450,10 +19456,10 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>24.66</v>
+        <v>24.6</v>
       </c>
       <c r="CA66" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="CB66" t="n">
         <v>1.5</v>
@@ -19510,82 +19516,82 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.81999969482422</v>
+        <v>18.72999954223633</v>
       </c>
       <c r="D67" t="n">
-        <v>18.81999969482422</v>
+        <v>18.72999954223633</v>
       </c>
       <c r="E67" t="n">
         <v>19.43000030517578</v>
       </c>
       <c r="F67" t="n">
-        <v>18.81999969482422</v>
+        <v>18.6200008392334</v>
       </c>
       <c r="G67" t="n">
         <v>19.32999992370605</v>
       </c>
       <c r="H67" t="n">
-        <v>1371900</v>
+        <v>2207600</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.01259180366437107</v>
+        <v>-0.01731374254735518</v>
       </c>
       <c r="J67" t="n">
-        <v>19.01333321465386</v>
+        <v>19.00333319769965</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-1.016831281748317</v>
+        <v>-1.438345855538714</v>
       </c>
       <c r="M67" t="n">
-        <v>18.99299983978272</v>
+        <v>18.98399982452393</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.9108626673924931</v>
+        <v>-1.337970315188669</v>
       </c>
       <c r="P67" t="n">
-        <v>18.59730764535757</v>
+        <v>18.59384610102727</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>1.197442413242212</v>
+        <v>0.7322500168565901</v>
       </c>
       <c r="S67" t="n">
-        <v>18.7057999420166</v>
+        <v>18.70399993896485</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.6105045128335033</v>
+        <v>0.1390055782523811</v>
       </c>
       <c r="V67" t="n">
-        <v>21.58725456237793</v>
+        <v>21.58665456136068</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-12.8189291489454</v>
+        <v>-13.23343091910897</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.3729909324646</v>
+        <v>22.37254093170166</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-15.88071638863792</v>
+        <v>-16.28130394569482</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5156929774586597</v>
+        <v>0.5169101188107154</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19735,13 +19741,13 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.8</v>
+        <v>16.72</v>
       </c>
       <c r="CA67" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CC67" t="n">
         <v>10</v>
@@ -19776,13 +19782,13 @@
         <v>9</v>
       </c>
       <c r="CM67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN67" t="n">
         <v>-1</v>
       </c>
       <c r="CO67" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68">
@@ -19795,10 +19801,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>42.34000015258789</v>
+        <v>42.11999893188477</v>
       </c>
       <c r="D68" t="n">
-        <v>42.34000015258789</v>
+        <v>42.11999893188477</v>
       </c>
       <c r="E68" t="n">
         <v>42.86000061035156</v>
@@ -19810,67 +19816,67 @@
         <v>42.18000030517578</v>
       </c>
       <c r="H68" t="n">
-        <v>3088900</v>
+        <v>4511200</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01583492904461781</v>
+        <v>0.01055658885526323</v>
       </c>
       <c r="J68" t="n">
-        <v>41.81222237481011</v>
+        <v>41.78777779473199</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1.262257176972587</v>
+        <v>0.7950198710845551</v>
       </c>
       <c r="M68" t="n">
-        <v>41.89300003051758</v>
+        <v>41.87099990844727</v>
       </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>1.06700432469551</v>
+        <v>0.5946813402640148</v>
       </c>
       <c r="P68" t="n">
-        <v>43.44692303584172</v>
+        <v>43.43846145043006</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-2.547758980171437</v>
+        <v>-3.035242212825294</v>
       </c>
       <c r="S68" t="n">
-        <v>46.56599990844727</v>
+        <v>46.5615998840332</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-9.075290478392075</v>
+        <v>-9.539193161770067</v>
       </c>
       <c r="V68" t="n">
-        <v>49.63739995320638</v>
+        <v>49.63593327840169</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-14.70141427129104</v>
+        <v>-15.14212355867472</v>
       </c>
       <c r="Y68" t="n">
-        <v>50.03944997787475</v>
+        <v>50.03834997177124</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-15.38675950413368</v>
+        <v>-15.82456464762238</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2182366297595144</v>
+        <v>0.2145854400605174</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20022,7 +20028,7 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="CA68" t="n">
         <v>1.28</v>
@@ -20082,82 +20088,82 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39.2400016784668</v>
+        <v>39.13000106811523</v>
       </c>
       <c r="D69" t="n">
-        <v>39.2400016784668</v>
+        <v>39.13000106811523</v>
       </c>
       <c r="E69" t="n">
         <v>39.56000137329102</v>
       </c>
       <c r="F69" t="n">
-        <v>39.06000137329102</v>
+        <v>38.9900016784668</v>
       </c>
       <c r="G69" t="n">
         <v>39.20999908447266</v>
       </c>
       <c r="H69" t="n">
-        <v>380400</v>
+        <v>623300</v>
       </c>
       <c r="I69" t="n">
-        <v>0.006153889191456319</v>
+        <v>0.0033333607209034</v>
       </c>
       <c r="J69" t="n">
-        <v>38.70555538601346</v>
+        <v>38.6933330959744</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.380799957843946</v>
+        <v>1.128535427686557</v>
       </c>
       <c r="M69" t="n">
-        <v>38.69599990844726</v>
+        <v>38.68499984741211</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1.405834637447318</v>
+        <v>1.150319820236203</v>
       </c>
       <c r="P69" t="n">
-        <v>40.97653858478252</v>
+        <v>40.9723077920767</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-4.237880910127987</v>
+        <v>-4.496468037169565</v>
       </c>
       <c r="S69" t="n">
-        <v>42.01780021667481</v>
+        <v>42.01560020446777</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-6.611004202703687</v>
+        <v>-6.867923157850535</v>
       </c>
       <c r="V69" t="n">
-        <v>41.7448668162028</v>
+        <v>41.74413347880046</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-6.000414730665207</v>
+        <v>-6.262274942209056</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.06280014038086</v>
+        <v>40.0622501373291</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-2.053771725967628</v>
+        <v>-2.327001269320164</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2534269959587083</v>
+        <v>0.2525221527267005</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20309,13 +20315,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.619999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CC69" t="n">
         <v>6</v>
@@ -20365,82 +20371,82 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.64999961853027</v>
+        <v>22.53000068664551</v>
       </c>
       <c r="D70" t="n">
-        <v>22.64999961853027</v>
+        <v>22.53000068664551</v>
       </c>
       <c r="E70" t="n">
         <v>22.85000038146973</v>
       </c>
       <c r="F70" t="n">
-        <v>22.57999992370605</v>
+        <v>22.45999908447266</v>
       </c>
       <c r="G70" t="n">
         <v>22.85000038146973</v>
       </c>
       <c r="H70" t="n">
-        <v>709800</v>
+        <v>1250700</v>
       </c>
       <c r="I70" t="n">
-        <v>0.004434606867098179</v>
+        <v>-0.0008868537069469662</v>
       </c>
       <c r="J70" t="n">
-        <v>22.44555536905925</v>
+        <v>22.43222215440538</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.9108451366405032</v>
+        <v>0.4358842898715011</v>
       </c>
       <c r="M70" t="n">
-        <v>22.46099987030029</v>
+        <v>22.44899997711182</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.8414574120535581</v>
+        <v>0.3608210148170313</v>
       </c>
       <c r="P70" t="n">
-        <v>23.91884613037109</v>
+        <v>23.91423078683706</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-5.304798170132861</v>
+        <v>-5.788311204864121</v>
       </c>
       <c r="S70" t="n">
-        <v>25.39419994354248</v>
+        <v>25.39179996490478</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-10.80640591596993</v>
+        <v>-11.27056483673747</v>
       </c>
       <c r="V70" t="n">
-        <v>24.8618666712443</v>
+        <v>24.86106667836507</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-8.896625028048746</v>
+        <v>-9.376371584844884</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.33704999923706</v>
+        <v>24.33645000457764</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-6.932024960953252</v>
+        <v>-7.422813588639008</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3797765942229007</v>
+        <v>0.3788454616284155</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20592,13 +20598,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2265</v>
+        <v>2253</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CC70" t="n">
         <v>1</v>
@@ -20633,13 +20639,13 @@
         <v>2</v>
       </c>
       <c r="CM70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
@@ -20652,103 +20658,103 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>31.52000045776367</v>
+        <v>31</v>
       </c>
       <c r="D71" t="n">
-        <v>31.52000045776367</v>
+        <v>31</v>
       </c>
       <c r="E71" t="n">
         <v>31.84000015258789</v>
       </c>
       <c r="F71" t="n">
-        <v>31.42000007629395</v>
+        <v>30.55999946594238</v>
       </c>
       <c r="G71" t="n">
         <v>31.69000053405762</v>
       </c>
       <c r="H71" t="n">
-        <v>2877800</v>
+        <v>5462200</v>
       </c>
       <c r="I71" t="n">
-        <v>0.001270677131798292</v>
+        <v>-0.01524776204625788</v>
       </c>
       <c r="J71" t="n">
-        <v>31.5555551317003</v>
+        <v>31.49777730305989</v>
       </c>
       <c r="K71" t="n">
         <v>-1</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.112673263988668</v>
+        <v>-1.580356919380268</v>
       </c>
       <c r="M71" t="n">
-        <v>31.55999965667725</v>
+        <v>31.50799961090088</v>
       </c>
       <c r="N71" t="n">
         <v>-1</v>
       </c>
       <c r="O71" t="n">
-        <v>-0.1267401753761133</v>
+        <v>-1.61228772747961</v>
       </c>
       <c r="P71" t="n">
-        <v>32.42961524083064</v>
+        <v>32.40961522322435</v>
       </c>
       <c r="Q71" t="n">
         <v>-1</v>
       </c>
       <c r="R71" t="n">
-        <v>-2.804889223359383</v>
+        <v>-4.349373522380593</v>
       </c>
       <c r="S71" t="n">
-        <v>33.52539989471435</v>
+        <v>33.51499988555909</v>
       </c>
       <c r="T71" t="n">
         <v>-1</v>
       </c>
       <c r="U71" t="n">
-        <v>-5.981731592310866</v>
+        <v>-7.504102324770547</v>
       </c>
       <c r="V71" t="n">
-        <v>39.52213329315185</v>
+        <v>39.51866662343343</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-20.24721888374062</v>
+        <v>-21.55605781087287</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.45829998970031</v>
+        <v>40.4556999874115</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-22.09262261195382</v>
+        <v>-23.37297337669057</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4510199290758232</v>
+        <v>0.4523225331871994</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
       </c>
       <c r="AD71" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="AE71" t="n">
         <v>30.7</v>
       </c>
-      <c r="AE71" t="n">
+      <c r="AF71" t="n">
         <v>30.9</v>
       </c>
-      <c r="AF71" t="n">
+      <c r="AG71" t="n">
         <v>31.3</v>
       </c>
-      <c r="AG71" t="n">
+      <c r="AH71" t="n">
         <v>31.6</v>
       </c>
-      <c r="AH71" t="n">
+      <c r="AI71" t="n">
         <v>32</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>32.3</v>
       </c>
       <c r="AJ71" t="n">
         <v>3</v>
@@ -20875,13 +20881,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>20.47</v>
+        <v>20.13</v>
       </c>
       <c r="CA71" t="n">
         <v>0.18</v>
       </c>
       <c r="CB71" t="n">
-        <v>3.81</v>
+        <v>3.74</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20913,16 +20919,16 @@
         <v>0</v>
       </c>
       <c r="CL71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CN71" t="n">
         <v>0</v>
       </c>
       <c r="CO71" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72">
@@ -20935,10 +20941,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27.57999992370605</v>
+        <v>27.54000091552734</v>
       </c>
       <c r="D72" t="n">
-        <v>27.57999992370605</v>
+        <v>27.54000091552734</v>
       </c>
       <c r="E72" t="n">
         <v>28.03000068664551</v>
@@ -20950,67 +20956,67 @@
         <v>25.48999977111816</v>
       </c>
       <c r="H72" t="n">
-        <v>3142300</v>
+        <v>4620900</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.0104054864296631</v>
+        <v>-0.01184068581876407</v>
       </c>
       <c r="J72" t="n">
-        <v>28.61555586920844</v>
+        <v>28.61111153496636</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-3.618856646488179</v>
+        <v>-3.743687546462453</v>
       </c>
       <c r="M72" t="n">
-        <v>28.70900020599365</v>
+        <v>28.70500030517578</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-3.932565656019936</v>
+        <v>-4.058524219692748</v>
       </c>
       <c r="P72" t="n">
-        <v>29.22538485893836</v>
+        <v>29.22384643554688</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-5.62998551832271</v>
+        <v>-5.761888749768955</v>
       </c>
       <c r="S72" t="n">
-        <v>28.9484001159668</v>
+        <v>28.94760013580322</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-4.727032190998314</v>
+        <v>-4.862576564801036</v>
       </c>
       <c r="V72" t="n">
-        <v>25.11513332366943</v>
+        <v>25.11486666361491</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>9.814268426413808</v>
+        <v>9.65617012582369</v>
       </c>
       <c r="Y72" t="n">
-        <v>23.80230000495911</v>
+        <v>23.80210000991821</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>15.87115496384753</v>
+        <v>15.70408032926324</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2489278810262048</v>
+        <v>0.2493201797559128</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21162,7 +21168,7 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="CA72" t="n">
         <v>0.45</v>
@@ -21199,13 +21205,13 @@
         <v>7</v>
       </c>
       <c r="CM72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN72" t="n">
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -21218,13 +21224,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.14000034332275</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="D73" t="n">
-        <v>10.14000034332275</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="E73" t="n">
-        <v>10.15999984741211</v>
+        <v>10.25</v>
       </c>
       <c r="F73" t="n">
         <v>9.659999847412109</v>
@@ -21233,67 +21239,67 @@
         <v>9.770000457763672</v>
       </c>
       <c r="H73" t="n">
-        <v>11536100</v>
+        <v>17442100</v>
       </c>
       <c r="I73" t="n">
-        <v>0.04968949311518212</v>
+        <v>0.06004140091797572</v>
       </c>
       <c r="J73" t="n">
-        <v>9.651111178927952</v>
+        <v>9.662222226460775</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>5.065625660413416</v>
+        <v>5.979758394244942</v>
       </c>
       <c r="M73" t="n">
-        <v>9.675000095367432</v>
+        <v>9.685000038146972</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>4.806204065858073</v>
+        <v>5.730508319929544</v>
       </c>
       <c r="P73" t="n">
-        <v>8.819615400754488</v>
+        <v>8.823461532592773</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>14.97100363872229</v>
+        <v>16.05422354132643</v>
       </c>
       <c r="S73" t="n">
-        <v>7.86019998550415</v>
+        <v>7.862199974060059</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>29.00435564009862</v>
+        <v>30.24344082957996</v>
       </c>
       <c r="V73" t="n">
-        <v>6.610933329264323</v>
+        <v>6.611599992116292</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>53.38228111356786</v>
+        <v>54.87929976599304</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.051599997282028</v>
+        <v>6.052099994421005</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>67.55899841160951</v>
+        <v>69.19746502135922</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.5395710029102244</v>
+        <v>0.5465040612935747</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21445,7 +21451,7 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>-4.88</v>
+        <v>-4.92</v>
       </c>
       <c r="CA73" t="n">
         <v>-0.04</v>
@@ -21505,10 +21511,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>83.13999938964844</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="D74" t="n">
-        <v>83.13999938964844</v>
+        <v>83.27999877929688</v>
       </c>
       <c r="E74" t="n">
         <v>83.94000244140625</v>
@@ -21520,67 +21526,67 @@
         <v>83.68000030517578</v>
       </c>
       <c r="H74" t="n">
-        <v>4096100</v>
+        <v>6569800</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0008426591438712716</v>
+        <v>0.002527977431613593</v>
       </c>
       <c r="J74" t="n">
-        <v>82.65333218044705</v>
+        <v>82.66888766818576</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5888053105214245</v>
+        <v>0.7392274510381418</v>
       </c>
       <c r="M74" t="n">
-        <v>82.67499923706055</v>
+        <v>82.68899917602539</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5624434918403314</v>
+        <v>0.7147257908072941</v>
       </c>
       <c r="P74" t="n">
-        <v>82.8923081618089</v>
+        <v>82.89769275371845</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0.2988108707939901</v>
+        <v>0.4611781255652392</v>
       </c>
       <c r="S74" t="n">
-        <v>82.55660034179688</v>
+        <v>82.55940032958985</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>0.7066655427139642</v>
+        <v>0.8728242293794359</v>
       </c>
       <c r="V74" t="n">
-        <v>77.24420010884603</v>
+        <v>77.24513343811036</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>7.632675686322783</v>
+        <v>7.812615594769756</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.09040008544922</v>
+        <v>72.09110008239746</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>15.32742125317942</v>
+        <v>15.5204993183776</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3032521817572879</v>
+        <v>0.3034032235541304</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21728,7 +21734,7 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>23.69</v>
+        <v>23.73</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
@@ -21765,13 +21771,13 @@
         <v>9</v>
       </c>
       <c r="CM74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN74" t="n">
         <v>0</v>
       </c>
       <c r="CO74" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75">
@@ -21784,82 +21790,82 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.240000009536743</v>
+        <v>3.230000019073486</v>
       </c>
       <c r="D75" t="n">
-        <v>3.240000009536743</v>
+        <v>3.230000019073486</v>
       </c>
       <c r="E75" t="n">
         <v>3.359999895095825</v>
       </c>
       <c r="F75" t="n">
-        <v>3.220000028610229</v>
+        <v>3.210000038146973</v>
       </c>
       <c r="G75" t="n">
         <v>3.319999933242798</v>
       </c>
       <c r="H75" t="n">
-        <v>7403400</v>
+        <v>9792000</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>-0.003086416800562541</v>
       </c>
       <c r="J75" t="n">
-        <v>3.318888876173231</v>
+        <v>3.317777766121758</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-2.376966195007077</v>
+        <v>-2.645678922337162</v>
       </c>
       <c r="M75" t="n">
-        <v>3.335999989509582</v>
+        <v>3.334999990463257</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-2.877697250441299</v>
+        <v>-3.148424938231721</v>
       </c>
       <c r="P75" t="n">
-        <v>3.732692324198209</v>
+        <v>3.732307709180392</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-13.19938189031687</v>
+        <v>-13.45836756362222</v>
       </c>
       <c r="S75" t="n">
-        <v>3.749400005340576</v>
+        <v>3.749200005531311</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-13.58617365653846</v>
+        <v>-13.84828725306286</v>
       </c>
       <c r="V75" t="n">
-        <v>3.749194790522258</v>
+        <v>3.749128123919169</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-13.58144373487151</v>
+        <v>-13.84663547595726</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.747196098566056</v>
+        <v>3.747146098613739</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-13.53534951702692</v>
+        <v>-13.8010652889027</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.5224793185015366</v>
+        <v>0.5221732934030845</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -22011,10 +22017,10 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>12.96</v>
+        <v>12.92</v>
       </c>
       <c r="CA75" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CB75" t="n">
         <v>1.52</v>
@@ -22067,82 +22073,82 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>31.25</v>
+        <v>30.93000030517578</v>
       </c>
       <c r="D76" t="n">
-        <v>31.25</v>
+        <v>30.93000030517578</v>
       </c>
       <c r="E76" t="n">
         <v>32.27999877929688</v>
       </c>
       <c r="F76" t="n">
-        <v>31.14999961853027</v>
+        <v>30.81999969482422</v>
       </c>
       <c r="G76" t="n">
         <v>32.20000076293945</v>
       </c>
       <c r="H76" t="n">
-        <v>1905100</v>
+        <v>3270700</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.01945405782575782</v>
+        <v>-0.0294948386979782</v>
       </c>
       <c r="J76" t="n">
-        <v>32.66111056009928</v>
+        <v>32.62555503845215</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-4.320461049549174</v>
+        <v>-5.197014215629446</v>
       </c>
       <c r="M76" t="n">
-        <v>32.7339994430542</v>
+        <v>32.70199947357177</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-4.533510931457814</v>
+        <v>-5.418626374292618</v>
       </c>
       <c r="P76" t="n">
-        <v>32.93999972710242</v>
+        <v>32.92769204653226</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-5.130539590478272</v>
+        <v>-6.066904836614164</v>
       </c>
       <c r="S76" t="n">
-        <v>32.32679988861084</v>
+        <v>32.32039989471436</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-3.330982009729375</v>
+        <v>-4.301925700387015</v>
       </c>
       <c r="V76" t="n">
-        <v>28.38841395060221</v>
+        <v>28.38628061930338</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>10.08011949655639</v>
+        <v>8.961088351048721</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.72365769386291</v>
+        <v>26.72205769538879</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>16.9375852586847</v>
+        <v>15.74707553495447</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.2677780026566139</v>
+        <v>0.274846519380866</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22294,13 +22300,13 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>12.45</v>
+        <v>12.32</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="CB76" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CC76" t="n">
         <v>5</v>
@@ -22328,7 +22334,7 @@
         <v>0</v>
       </c>
       <c r="CL76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM76" t="n">
         <v>1</v>
@@ -22337,7 +22343,7 @@
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -22350,82 +22356,82 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>22.20999908447266</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="D77" t="n">
-        <v>22.20999908447266</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="E77" t="n">
         <v>22.72999954223633</v>
       </c>
       <c r="F77" t="n">
-        <v>22.15999984741211</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="G77" t="n">
         <v>22.51000022888184</v>
       </c>
       <c r="H77" t="n">
-        <v>953900</v>
+        <v>1403800</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.002694269064107635</v>
+        <v>-0.005837497325686614</v>
       </c>
       <c r="J77" t="n">
-        <v>22.48999998304579</v>
+        <v>22.48222223917643</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.245001773162363</v>
+        <v>-1.522193161722488</v>
       </c>
       <c r="M77" t="n">
-        <v>22.54099998474121</v>
+        <v>22.53400001525879</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-1.46843929059324</v>
+        <v>-1.748471755318884</v>
       </c>
       <c r="P77" t="n">
-        <v>24.50730771284837</v>
+        <v>24.50461541689359</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-9.37397389910484</v>
+        <v>-9.649676140662784</v>
       </c>
       <c r="S77" t="n">
-        <v>25.42440006256103</v>
+        <v>25.42300006866455</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-12.64297670811819</v>
+        <v>-12.91350615642965</v>
       </c>
       <c r="V77" t="n">
-        <v>29.1570666885376</v>
+        <v>29.15660002390544</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-23.82635975791081</v>
+        <v>-24.06522238019557</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.91800001144409</v>
+        <v>28.91765001296997</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-23.19662813582126</v>
+        <v>-23.43776420380516</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4672052330040793</v>
+        <v>0.4671081412589596</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22573,7 +22579,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>8.960000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
@@ -22633,10 +22639,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>34.2599983215332</v>
+        <v>33.95000076293945</v>
       </c>
       <c r="D78" t="n">
-        <v>34.2599983215332</v>
+        <v>33.95000076293945</v>
       </c>
       <c r="E78" t="n">
         <v>34.47000122070312</v>
@@ -22648,67 +22654,67 @@
         <v>34.11999893188477</v>
       </c>
       <c r="H78" t="n">
-        <v>1297600</v>
+        <v>1898800</v>
       </c>
       <c r="I78" t="n">
-        <v>0.01211225600868371</v>
+        <v>0.002954277498559144</v>
       </c>
       <c r="J78" t="n">
-        <v>34.72777811686198</v>
+        <v>34.6933339436849</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.346990278948035</v>
+        <v>-2.142582151234131</v>
       </c>
       <c r="M78" t="n">
-        <v>34.81400032043457</v>
+        <v>34.7830005645752</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-1.591319566272856</v>
+        <v>-2.394847448796909</v>
       </c>
       <c r="P78" t="n">
-        <v>37.19269224313589</v>
+        <v>37.18076926011305</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-7.885134806674113</v>
+        <v>-8.689353559555094</v>
       </c>
       <c r="S78" t="n">
-        <v>39.07680000305176</v>
+        <v>39.07060005187989</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-12.32649981867088</v>
+        <v>-13.10601649869991</v>
       </c>
       <c r="V78" t="n">
-        <v>36.99000007629395</v>
+        <v>36.98793342590332</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-7.38037780246002</v>
+        <v>-8.213307372388501</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.09760007858277</v>
+        <v>36.0960500907898</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-5.090648001665457</v>
+        <v>-5.94538549911289</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3146229996416562</v>
+        <v>0.3110255026246819</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22860,13 +22866,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>17.39</v>
+        <v>17.23</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
       </c>
       <c r="CB78" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CC78" t="n">
         <v>5</v>
@@ -22898,7 +22904,7 @@
         <v>0</v>
       </c>
       <c r="CL78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM78" t="n">
         <v>3</v>
@@ -22907,7 +22913,7 @@
         <v>0</v>
       </c>
       <c r="CO78" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
@@ -22920,82 +22926,82 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>43.72999954223633</v>
+        <v>43.56000137329102</v>
       </c>
       <c r="D79" t="n">
-        <v>43.72999954223633</v>
+        <v>43.56000137329102</v>
       </c>
       <c r="E79" t="n">
         <v>44.36000061035156</v>
       </c>
       <c r="F79" t="n">
-        <v>43.56000137329102</v>
+        <v>43.40000152587891</v>
       </c>
       <c r="G79" t="n">
         <v>44.18000030517578</v>
       </c>
       <c r="H79" t="n">
-        <v>1559000</v>
+        <v>2225700</v>
       </c>
       <c r="I79" t="n">
-        <v>0.006675896056521413</v>
+        <v>0.002762494253585102</v>
       </c>
       <c r="J79" t="n">
-        <v>42.83888922797309</v>
+        <v>42.82000054253472</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2.080143370480663</v>
+        <v>1.728166327371303</v>
       </c>
       <c r="M79" t="n">
-        <v>42.92700042724609</v>
+        <v>42.91000061035156</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>1.870615479763562</v>
+        <v>1.514800171740502</v>
       </c>
       <c r="P79" t="n">
-        <v>44.57653852609488</v>
+        <v>44.5700001349816</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-1.899068460335903</v>
+        <v>-2.266095487170227</v>
       </c>
       <c r="S79" t="n">
-        <v>46.78860015869141</v>
+        <v>46.7852001953125</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-6.537063742196437</v>
+        <v>-6.893630482625618</v>
       </c>
       <c r="V79" t="n">
-        <v>47.00799995422364</v>
+        <v>47.00686663309733</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-6.973282026845265</v>
+        <v>-7.332684577149401</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.48134994506836</v>
+        <v>44.48049995422363</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-1.689135792326225</v>
+        <v>-2.0694429736175</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.3374734906419627</v>
+        <v>0.3364294178148522</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23147,13 +23153,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>29.15</v>
+        <v>29.04</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB79" t="n">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="CC79" t="n">
         <v>6</v>
@@ -23188,13 +23194,13 @@
         <v>5</v>
       </c>
       <c r="CM79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
       </c>
       <c r="CO79" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80">
@@ -23207,10 +23213,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.619999885559082</v>
+        <v>9.640000343322754</v>
       </c>
       <c r="D80" t="n">
-        <v>9.619999885559082</v>
+        <v>9.640000343322754</v>
       </c>
       <c r="E80" t="n">
         <v>9.899999618530273</v>
@@ -23222,67 +23228,67 @@
         <v>9.779999732971191</v>
       </c>
       <c r="H80" t="n">
-        <v>908300</v>
+        <v>1275400</v>
       </c>
       <c r="I80" t="n">
-        <v>0.002083281593192376</v>
+        <v>0.004166662527455456</v>
       </c>
       <c r="J80" t="n">
-        <v>9.604444397820366</v>
+        <v>9.60666667090522</v>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0.1619613492920656</v>
+        <v>0.34698479253463</v>
       </c>
       <c r="M80" t="n">
-        <v>9.617999935150147</v>
+        <v>9.619999980926513</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.02079382847182323</v>
+        <v>0.2079039754251053</v>
       </c>
       <c r="P80" t="n">
-        <v>10.07884612450233</v>
+        <v>10.07961537287786</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-4.552567161708739</v>
+        <v>-4.361426634770348</v>
       </c>
       <c r="S80" t="n">
-        <v>10.68379999160767</v>
+        <v>10.68420000076294</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-9.957132358189218</v>
+        <v>-9.773306914561882</v>
       </c>
       <c r="V80" t="n">
-        <v>12.19373332977295</v>
+        <v>12.19386666615804</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-21.10701763445724</v>
+        <v>-20.9438596694115</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.40525000572205</v>
+        <v>12.40535000801086</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-22.45218854016033</v>
+        <v>-22.29158921676825</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4297884991227949</v>
+        <v>0.4301836213362589</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23434,10 +23440,10 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>22.37</v>
+        <v>22.42</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CB80" t="n">
         <v>0.88</v>
@@ -23475,13 +23481,13 @@
         <v>3</v>
       </c>
       <c r="CM80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
       </c>
       <c r="CO80" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.69000053405762</v>
+        <v>16.61000061035156</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69000053405762</v>
+        <v>16.61000061035156</v>
       </c>
       <c r="E2" t="n">
         <v>16.92000007629395</v>
@@ -912,67 +912,67 @@
         <v>16.79000091552734</v>
       </c>
       <c r="H2" t="n">
-        <v>21403900</v>
+        <v>37014900</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006027750485229966</v>
+        <v>0.001205573091001666</v>
       </c>
       <c r="J2" t="n">
-        <v>16.19000000423855</v>
+        <v>16.18111112382677</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>3.088329398938633</v>
+        <v>2.650556462054411</v>
       </c>
       <c r="M2" t="n">
-        <v>16.14800004959107</v>
+        <v>16.14000005722046</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.356455801350321</v>
+        <v>2.912023243276525</v>
       </c>
       <c r="P2" t="n">
-        <v>15.69423073988694</v>
+        <v>15.6911538197444</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>6.344814286691483</v>
+        <v>5.855826800008554</v>
       </c>
       <c r="S2" t="n">
-        <v>15.48440000534058</v>
+        <v>15.48280000686646</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>7.785904060223374</v>
+        <v>7.280340784517052</v>
       </c>
       <c r="V2" t="n">
-        <v>14.61933331807454</v>
+        <v>14.61879998524984</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>14.16389633460928</v>
+        <v>13.62082131988138</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.01634999752045</v>
+        <v>14.01594999790192</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.07522669603821</v>
+        <v>18.50784722289931</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.501217060401879</v>
+        <v>0.5010753432894378</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,13 +1124,13 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.86</v>
+        <v>16.78</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.57999992370605</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="D3" t="n">
-        <v>28.57999992370605</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="E3" t="n">
         <v>29.11000061035156</v>
@@ -1199,67 +1199,67 @@
         <v>29.10000038146973</v>
       </c>
       <c r="H3" t="n">
-        <v>1125000</v>
+        <v>1941200</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.003486763612470356</v>
+        <v>-0.004532812647556783</v>
       </c>
       <c r="J3" t="n">
-        <v>28.55444441901313</v>
+        <v>28.55111100938585</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08949746777740943</v>
+        <v>-0.003893972199319172</v>
       </c>
       <c r="M3" t="n">
-        <v>28.58600006103516</v>
+        <v>28.58299999237061</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.02098977582135255</v>
+        <v>-0.1154558839830245</v>
       </c>
       <c r="P3" t="n">
-        <v>29.95461544623742</v>
+        <v>29.95346157367413</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.588994056687278</v>
+        <v>-4.68547627846484</v>
       </c>
       <c r="S3" t="n">
-        <v>30.41219997406006</v>
+        <v>30.41159996032715</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.024556105499668</v>
+        <v>-6.121350819079286</v>
       </c>
       <c r="V3" t="n">
-        <v>29.26973332722982</v>
+        <v>29.26953332265218</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.356473138353128</v>
+        <v>-2.458303921896744</v>
       </c>
       <c r="Y3" t="n">
-        <v>27.97854997634888</v>
+        <v>27.97839997291565</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.149682338311321</v>
+        <v>2.043001975446169</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2640315631837619</v>
+        <v>0.2640041603649453</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.43</v>
+        <v>17.41</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.270000457763672</v>
+        <v>9.25</v>
       </c>
       <c r="D4" t="n">
-        <v>9.270000457763672</v>
+        <v>9.25</v>
       </c>
       <c r="E4" t="n">
         <v>9.390000343322754</v>
@@ -1486,70 +1486,70 @@
         <v>9.25</v>
       </c>
       <c r="H4" t="n">
-        <v>19179200</v>
+        <v>28327400</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01756320605008499</v>
+        <v>0.01536776603719625</v>
       </c>
       <c r="J4" t="n">
-        <v>8.664444287618002</v>
+        <v>8.66222201453315</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>6.988978750905527</v>
+        <v>6.785533601894509</v>
       </c>
       <c r="M4" t="n">
-        <v>8.656999874114991</v>
+        <v>8.654999828338623</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>7.080981778474939</v>
+        <v>6.874641056758877</v>
       </c>
       <c r="P4" t="n">
-        <v>8.968846101027269</v>
+        <v>8.968076852651743</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>3.357782632728073</v>
+        <v>3.14362992178079</v>
       </c>
       <c r="S4" t="n">
-        <v>8.904399948120117</v>
+        <v>8.903999938964844</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>4.105841064795608</v>
+        <v>3.885894692350826</v>
       </c>
       <c r="V4" t="n">
-        <v>8.628399947484334</v>
+        <v>8.628266611099242</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>7.43591528191041</v>
+        <v>7.205773962767578</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.900799953937531</v>
+        <v>8.900699951648711</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.147947439969307</v>
+        <v>3.924411004177109</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.521139125970367</v>
+        <v>0.5204761657154772</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>7.8</v>
@@ -1694,7 +1694,7 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>17.83</v>
+        <v>17.79</v>
       </c>
       <c r="CA4" t="n">
         <v>0.96</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.48999977111816</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="D5" t="n">
-        <v>12.48999977111816</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="E5" t="n">
         <v>12.68000030517578</v>
@@ -1769,88 +1769,88 @@
         <v>12.64000034332275</v>
       </c>
       <c r="H5" t="n">
-        <v>2011100</v>
+        <v>3057200</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0008000183105468794</v>
+        <v>-0.008000030517578138</v>
       </c>
       <c r="J5" t="n">
-        <v>12.50888888041178</v>
+        <v>12.49888886345757</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1510054927676149</v>
+        <v>-0.791184288520378</v>
       </c>
       <c r="M5" t="n">
-        <v>12.5289999961853</v>
+        <v>12.51999998092651</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3112796318861229</v>
+        <v>-0.9584693496729533</v>
       </c>
       <c r="P5" t="n">
-        <v>13.30653843512902</v>
+        <v>13.30307689079872</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.136371739288766</v>
+        <v>-6.788484195660553</v>
       </c>
       <c r="S5" t="n">
-        <v>12.95499994277954</v>
+        <v>12.95319993972778</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.589349083097017</v>
+        <v>-4.270761848590253</v>
       </c>
       <c r="V5" t="n">
-        <v>12.10253330866496</v>
+        <v>12.10193330764771</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>3.201531882385276</v>
+        <v>2.462964414902268</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.68839996814728</v>
+        <v>11.68794996738434</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.858079849725975</v>
+        <v>6.092168884474497</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2388315209808099</v>
+        <v>0.2391371490049974</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE5" t="n">
         <v>12.1</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>12.2</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>12.4</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>13.7</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>13.8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>13.9</v>
       </c>
       <c r="AJ5" t="n">
         <v>1</v>
@@ -1977,13 +1977,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-10.15</v>
+        <v>-10.08</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2033,82 +2033,82 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.75</v>
+        <v>52.56999969482422</v>
       </c>
       <c r="D6" t="n">
-        <v>52.75</v>
+        <v>52.56999969482422</v>
       </c>
       <c r="E6" t="n">
         <v>53.72000122070312</v>
       </c>
       <c r="F6" t="n">
-        <v>52.59999847412109</v>
+        <v>52.52999877929688</v>
       </c>
       <c r="G6" t="n">
         <v>53.47000122070312</v>
       </c>
       <c r="H6" t="n">
-        <v>4719500</v>
+        <v>7394800</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01420292179727778</v>
+        <v>-0.01756678482889651</v>
       </c>
       <c r="J6" t="n">
-        <v>54.12666659884982</v>
+        <v>54.10666656494141</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.543416554824525</v>
+        <v>-2.840069380864198</v>
       </c>
       <c r="M6" t="n">
-        <v>54.24899978637696</v>
+        <v>54.23099975585937</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.763184191929352</v>
+        <v>-3.062823972474694</v>
       </c>
       <c r="P6" t="n">
-        <v>58.25923054034893</v>
+        <v>58.25230745168832</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.456408004793971</v>
+        <v>-9.754648365778024</v>
       </c>
       <c r="S6" t="n">
-        <v>59.23539993286133</v>
+        <v>59.23179992675782</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-10.94852054719309</v>
+        <v>-11.24699948367456</v>
       </c>
       <c r="V6" t="n">
-        <v>58.20226669311523</v>
+        <v>58.20106669108073</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.367790986326286</v>
+        <v>-9.675195518571938</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.50854999542236</v>
+        <v>55.50764999389649</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-4.969594766301504</v>
+        <v>-5.292334118622001</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2921697279763685</v>
+        <v>0.2930457751124768</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.13</v>
+        <v>16.08</v>
       </c>
       <c r="CA6" t="n">
         <v>0.3</v>
@@ -2297,13 +2297,13 @@
         <v>2</v>
       </c>
       <c r="CM6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN6" t="n">
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -2316,82 +2316,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>58.02000045776367</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="D7" t="n">
-        <v>58.02000045776367</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="E7" t="n">
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>57.83000183105469</v>
+        <v>57.77000045776367</v>
       </c>
       <c r="G7" t="n">
         <v>59</v>
       </c>
       <c r="H7" t="n">
-        <v>512500</v>
+        <v>894400</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01343310486447513</v>
+        <v>-0.01292300830612847</v>
       </c>
       <c r="J7" t="n">
-        <v>59.53666644626193</v>
+        <v>59.53999964396159</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.547448621207589</v>
+        <v>-2.502520013118864</v>
       </c>
       <c r="M7" t="n">
-        <v>59.6689998626709</v>
+        <v>59.67199974060058</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.763578086950387</v>
+        <v>-2.718193642899542</v>
       </c>
       <c r="P7" t="n">
-        <v>64.02923085139348</v>
+        <v>64.0303846505972</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.385135997614482</v>
+        <v>-9.339917987640693</v>
       </c>
       <c r="S7" t="n">
-        <v>65.00019996643067</v>
+        <v>65.0007999420166</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-10.73873543815545</v>
+        <v>-10.69340794445061</v>
       </c>
       <c r="V7" t="n">
-        <v>58.48390683492025</v>
+        <v>58.48410682678222</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7932205665842783</v>
+        <v>-0.7422659133829527</v>
       </c>
       <c r="Y7" t="n">
-        <v>53.84469417572021</v>
+        <v>53.8448441696167</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.754350444293539</v>
+        <v>7.809763650159677</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.305993274806622</v>
+        <v>0.3059040647899649</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.74</v>
+        <v>17.75</v>
       </c>
       <c r="CA7" t="n">
         <v>0.27</v>
@@ -2584,13 +2584,13 @@
         <v>2</v>
       </c>
       <c r="CM7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.40999984741211</v>
+        <v>20.64999961853027</v>
       </c>
       <c r="D8" t="n">
-        <v>20.40999984741211</v>
+        <v>20.64999961853027</v>
       </c>
       <c r="E8" t="n">
         <v>21.01000022888184</v>
@@ -2618,67 +2618,67 @@
         <v>20.63999938964844</v>
       </c>
       <c r="H8" t="n">
-        <v>771200</v>
+        <v>2078200</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.004390251345750773</v>
+        <v>0.007317054562452352</v>
       </c>
       <c r="J8" t="n">
-        <v>19.91555553012424</v>
+        <v>19.94222217135959</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2.482704118094887</v>
+        <v>3.549140316905953</v>
       </c>
       <c r="M8" t="n">
-        <v>19.80900001525879</v>
+        <v>19.83299999237061</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.033973606392915</v>
+        <v>4.119395081298604</v>
       </c>
       <c r="P8" t="n">
-        <v>20.74038461538462</v>
+        <v>20.74961537581224</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.592953911411255</v>
+        <v>-0.4800848376114246</v>
       </c>
       <c r="S8" t="n">
-        <v>22.65980007171631</v>
+        <v>22.66460006713867</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.928596974305933</v>
+        <v>-8.888753574475645</v>
       </c>
       <c r="V8" t="n">
-        <v>25.12560002644857</v>
+        <v>25.12720002492269</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-18.76810971309167</v>
+        <v>-17.81814289674797</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.70290004730225</v>
+        <v>26.70410004615784</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.56635492303354</v>
+        <v>-22.67105207501131</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.446185318384313</v>
+        <v>0.4467912691557433</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2830,10 +2830,10 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="CB8" t="n">
         <v>0.53</v>
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="CL8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM8" t="n">
         <v>10</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -2886,82 +2886,82 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.6299991607666</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="D9" t="n">
-        <v>16.6299991607666</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="E9" t="n">
         <v>17.28000068664551</v>
       </c>
       <c r="F9" t="n">
-        <v>16.55999946594238</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="G9" t="n">
         <v>17.14999961853027</v>
       </c>
       <c r="H9" t="n">
-        <v>10749600</v>
+        <v>22367700</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01829996242725984</v>
+        <v>-0.02715472121128115</v>
       </c>
       <c r="J9" t="n">
-        <v>16.7344446182251</v>
+        <v>16.71777799394395</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.624134590906871</v>
+        <v>-1.422308944369055</v>
       </c>
       <c r="M9" t="n">
-        <v>16.75400018692017</v>
+        <v>16.73900022506714</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7401278785371624</v>
+        <v>-1.547288842513713</v>
       </c>
       <c r="P9" t="n">
-        <v>17.63500011884249</v>
+        <v>17.62923090274517</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-5.69889963880451</v>
+        <v>-6.518896750792975</v>
       </c>
       <c r="S9" t="n">
-        <v>17.91420011520386</v>
+        <v>17.91120012283325</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.168620123582016</v>
+        <v>-7.990534251093669</v>
       </c>
       <c r="V9" t="n">
-        <v>15.97820007960002</v>
+        <v>15.97720008214315</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>4.079302286361791</v>
+        <v>3.146981057432789</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.21960005283356</v>
+        <v>15.2188500547409</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.26699192512919</v>
+        <v>8.286759400080664</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3542295992318979</v>
+        <v>0.3581048060534285</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>16.97</v>
+        <v>16.82</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.59</v>
+        <v>4.55</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM9" t="n">
         <v>4</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -3173,103 +3173,103 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.19000053405762</v>
+        <v>21.06999969482422</v>
       </c>
       <c r="D10" t="n">
-        <v>21.19000053405762</v>
+        <v>21.06999969482422</v>
       </c>
       <c r="E10" t="n">
         <v>21.5</v>
       </c>
       <c r="F10" t="n">
-        <v>21.14999961853027</v>
+        <v>21.06999969482422</v>
       </c>
       <c r="G10" t="n">
         <v>21.44000053405762</v>
       </c>
       <c r="H10" t="n">
-        <v>8558200</v>
+        <v>13576200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.003789669417007202</v>
+        <v>-0.001894879884926648</v>
       </c>
       <c r="J10" t="n">
-        <v>20.86222245958116</v>
+        <v>20.84888903299968</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.571156069836273</v>
+        <v>1.060539300077662</v>
       </c>
       <c r="M10" t="n">
-        <v>20.85200023651123</v>
+        <v>20.84000015258789</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.620949039481393</v>
+        <v>1.103644628369962</v>
       </c>
       <c r="P10" t="n">
-        <v>21.68769242213322</v>
+        <v>21.68307700523963</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-2.294812552614825</v>
+        <v>-2.827446078189296</v>
       </c>
       <c r="S10" t="n">
-        <v>22.7053999710083</v>
+        <v>22.70299995422363</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.674180762662814</v>
+        <v>-7.192883155054634</v>
       </c>
       <c r="V10" t="n">
-        <v>22.94413333892822</v>
+        <v>22.94333333333333</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.645234531018221</v>
+        <v>-8.165045642201568</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.4513000202179</v>
+        <v>22.45070001602173</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-5.617935197625309</v>
+        <v>-6.149921027906413</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2850811782542741</v>
+        <v>0.2840311616931257</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE10" t="n">
         <v>20</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>20.7</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>21.1</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>21.2</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>21.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>21.4</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -3416,7 +3416,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.44</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3453,13 +3453,13 @@
         <v>5</v>
       </c>
       <c r="CM10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.67000007629395</v>
+        <v>15.64000034332275</v>
       </c>
       <c r="D11" t="n">
-        <v>15.67000007629395</v>
+        <v>15.64000034332275</v>
       </c>
       <c r="E11" t="n">
         <v>15.85000038146973</v>
@@ -3487,67 +3487,67 @@
         <v>15.69999980926514</v>
       </c>
       <c r="H11" t="n">
-        <v>2021000</v>
+        <v>3447900</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005776646535854635</v>
+        <v>0.003851118094384764</v>
       </c>
       <c r="J11" t="n">
-        <v>15.4666666454739</v>
+        <v>15.46333334181044</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.314655804517156</v>
+        <v>1.142489769877985</v>
       </c>
       <c r="M11" t="n">
-        <v>15.47399997711182</v>
+        <v>15.4710000038147</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.266641459687477</v>
+        <v>1.092368557083481</v>
       </c>
       <c r="P11" t="n">
-        <v>16.16884613037109</v>
+        <v>16.16769229448759</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.085229768747261</v>
+        <v>-3.263866862092315</v>
       </c>
       <c r="S11" t="n">
-        <v>16.52619997024536</v>
+        <v>16.52559997558594</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.180863692155265</v>
+        <v>-5.358956005055926</v>
       </c>
       <c r="V11" t="n">
-        <v>16.61673331578573</v>
+        <v>16.61653331756592</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.697469060253824</v>
+        <v>-5.876875492500208</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.06870000362396</v>
+        <v>16.06855000495911</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.481220803425911</v>
+        <v>-2.667008918067239</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2195445080725569</v>
+        <v>0.2188495607113607</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>7</v>
+        <v>6.98</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -3736,13 +3736,13 @@
         <v>9</v>
       </c>
       <c r="CG11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CH11" t="n">
         <v>1</v>
       </c>
       <c r="CI11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="n">
@@ -3758,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="CO11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.06999969482422</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>18.06999969482422</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
         <v>18.20000076293945</v>
@@ -3786,67 +3786,67 @@
         <v>18.10000038146973</v>
       </c>
       <c r="H12" t="n">
-        <v>13236800</v>
+        <v>23956100</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01289235091194563</v>
+        <v>0.00896860123562826</v>
       </c>
       <c r="J12" t="n">
-        <v>17.78888893127441</v>
+        <v>17.78111118740506</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.580260378463477</v>
+        <v>1.23101874954806</v>
       </c>
       <c r="M12" t="n">
-        <v>17.79400005340576</v>
+        <v>17.78700008392334</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.55108261543268</v>
+        <v>1.197503317432264</v>
       </c>
       <c r="P12" t="n">
-        <v>18.66076924250676</v>
+        <v>18.65807694655198</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-3.165837056367678</v>
+        <v>-3.527035226819534</v>
       </c>
       <c r="S12" t="n">
-        <v>19.06200004577637</v>
+        <v>19.06060005187988</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.204072755061979</v>
+        <v>-5.564358147136511</v>
       </c>
       <c r="V12" t="n">
-        <v>19.29780000050863</v>
+        <v>19.29733333587647</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.362384860720119</v>
+        <v>-6.722863274919652</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.68324999809265</v>
+        <v>18.68289999961853</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.282353462759634</v>
+        <v>-3.655214124319429</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2621234219128852</v>
+        <v>0.2601379900319095</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.07</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34.88000106811523</v>
+        <v>34.86000061035156</v>
       </c>
       <c r="D13" t="n">
-        <v>34.88000106811523</v>
+        <v>34.86000061035156</v>
       </c>
       <c r="E13" t="n">
         <v>35.38999938964844</v>
@@ -4085,67 +4085,67 @@
         <v>34.84999847412109</v>
       </c>
       <c r="H13" t="n">
-        <v>2061500</v>
+        <v>4489600</v>
       </c>
       <c r="I13" t="n">
-        <v>0.004608290374042534</v>
+        <v>0.004032240343498472</v>
       </c>
       <c r="J13" t="n">
-        <v>34.47666676839193</v>
+        <v>34.47444449530708</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.169876143865161</v>
+        <v>1.118382386399212</v>
       </c>
       <c r="M13" t="n">
-        <v>34.47700004577636</v>
+        <v>34.475</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.168898169225254</v>
+        <v>1.116753039453404</v>
       </c>
       <c r="P13" t="n">
-        <v>34.36230776860164</v>
+        <v>34.36153852022611</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5065731411283</v>
+        <v>1.450639615080222</v>
       </c>
       <c r="S13" t="n">
-        <v>34.69879997253418</v>
+        <v>34.6983999633789</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5222114186210525</v>
+        <v>0.4657293913933026</v>
       </c>
       <c r="V13" t="n">
-        <v>34.78513334910075</v>
+        <v>34.78500001271566</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2727248967609326</v>
+        <v>0.2156118948066403</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.29474997520447</v>
+        <v>34.29464997291565</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.706532613108159</v>
+        <v>1.648509717645174</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1590600858735742</v>
+        <v>0.1588906667511958</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4378,13 +4378,13 @@
         <v>4.03000020980835</v>
       </c>
       <c r="F14" t="n">
-        <v>3.890000104904175</v>
+        <v>3.869999885559082</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>7081900</v>
+        <v>10243000</v>
       </c>
       <c r="I14" t="n">
         <v>-0.01017810716884615</v>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.06000137329102</v>
+        <v>54.9900016784668</v>
       </c>
       <c r="D15" t="n">
-        <v>55.06000137329102</v>
+        <v>54.9900016784668</v>
       </c>
       <c r="E15" t="n">
         <v>56.47999954223633</v>
@@ -4671,67 +4671,67 @@
         <v>56.36000061035156</v>
       </c>
       <c r="H15" t="n">
-        <v>4154100</v>
+        <v>7080400</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00792790318394565</v>
+        <v>-0.009189158946544151</v>
       </c>
       <c r="J15" t="n">
-        <v>54.52333365546333</v>
+        <v>54.51555591159396</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9842899944800334</v>
+        <v>0.8702942837861284</v>
       </c>
       <c r="M15" t="n">
-        <v>54.61000022888184</v>
+        <v>54.60300025939942</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8240269960137889</v>
+        <v>0.7087548618736615</v>
       </c>
       <c r="P15" t="n">
-        <v>57.40423070467435</v>
+        <v>57.40153840871957</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-4.083722231979064</v>
+        <v>-4.201170904308817</v>
       </c>
       <c r="S15" t="n">
-        <v>57.83599983215332</v>
+        <v>57.83459983825684</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.799776033817292</v>
+        <v>-4.918505821334263</v>
       </c>
       <c r="V15" t="n">
-        <v>55.77366655985514</v>
+        <v>55.77319989522298</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.279573731804485</v>
+        <v>-1.404255481535075</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.22044994354248</v>
+        <v>53.22009994506836</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.456474779337589</v>
+        <v>3.325626474255508</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2874515428253042</v>
+        <v>0.2875962919134065</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4903,13 +4903,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ15" t="n">
-        <v>12.37</v>
+        <v>12.36</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CC15" t="n">
         <v>6</v>
@@ -4963,13 +4963,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.27000045776367</v>
+        <v>23.29000091552734</v>
       </c>
       <c r="D16" t="n">
-        <v>23.27000045776367</v>
+        <v>23.29000091552734</v>
       </c>
       <c r="E16" t="n">
-        <v>23.35000038146973</v>
+        <v>23.3700008392334</v>
       </c>
       <c r="F16" t="n">
         <v>22.94000053405762</v>
@@ -4978,67 +4978,67 @@
         <v>23.20000076293945</v>
       </c>
       <c r="H16" t="n">
-        <v>755300</v>
+        <v>1463300</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008232258868530629</v>
+        <v>0.009098829831692967</v>
       </c>
       <c r="J16" t="n">
-        <v>22.98555564880371</v>
+        <v>22.98777792188856</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.237493725650983</v>
+        <v>1.314711646622474</v>
       </c>
       <c r="M16" t="n">
-        <v>22.97200012207031</v>
+        <v>22.97400016784668</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.297232866575932</v>
+        <v>1.375471164673031</v>
       </c>
       <c r="P16" t="n">
-        <v>23.2342308484591</v>
+        <v>23.23500009683462</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.153952198968297</v>
+        <v>0.2367153796578428</v>
       </c>
       <c r="S16" t="n">
-        <v>23.27499996185303</v>
+        <v>23.2753999710083</v>
       </c>
       <c r="T16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.02148014649859904</v>
+        <v>0.06273122926879499</v>
       </c>
       <c r="V16" t="n">
-        <v>21.88586662292481</v>
+        <v>21.8859999593099</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>6.324327287040245</v>
+        <v>6.415064236624987</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.57379995346069</v>
+        <v>20.57389995574951</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>13.10501954136797</v>
+        <v>13.20168254740055</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2554684770309464</v>
+        <v>0.2557852296343822</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.69</v>
+        <v>11.7</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.97999954223633</v>
+        <v>19.90999984741211</v>
       </c>
       <c r="D17" t="n">
-        <v>19.97999954223633</v>
+        <v>19.90999984741211</v>
       </c>
       <c r="E17" t="n">
         <v>20.17000007629395</v>
@@ -5269,67 +5269,67 @@
         <v>19.92000007629395</v>
       </c>
       <c r="H17" t="n">
-        <v>2728100</v>
+        <v>4451500</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.004484312603706742</v>
+        <v>-0.007972090176631697</v>
       </c>
       <c r="J17" t="n">
-        <v>19.58666674296061</v>
+        <v>19.57888899909126</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.008166087867286</v>
+        <v>1.691162600371362</v>
       </c>
       <c r="M17" t="n">
-        <v>19.44700012207031</v>
+        <v>19.44000015258789</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.740779641180315</v>
+        <v>2.417693884439862</v>
       </c>
       <c r="P17" t="n">
-        <v>19.00307692014254</v>
+        <v>19.00038462418776</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>5.140865482990742</v>
+        <v>4.787351631115893</v>
       </c>
       <c r="S17" t="n">
-        <v>19.36239994049072</v>
+        <v>19.36099994659424</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>3.18968518181509</v>
+        <v>2.835596830392253</v>
       </c>
       <c r="V17" t="n">
-        <v>17.29399996439616</v>
+        <v>17.293533299764</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>15.53139576367492</v>
+        <v>15.12973955232052</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.61614995479584</v>
+        <v>17.61579995632172</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.41865046282122</v>
+        <v>13.02353510359365</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3935227894429228</v>
+        <v>0.3938628519222205</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5477,10 +5477,10 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>39.96</v>
+        <v>39.82</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CB17" t="n">
         <v>0.8100000000000001</v>
@@ -5514,13 +5514,13 @@
         <v>10</v>
       </c>
       <c r="CM17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN17" t="n">
         <v>0</v>
       </c>
       <c r="CO17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -5533,94 +5533,94 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.51000022888184</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="D18" t="n">
-        <v>11.51000022888184</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="E18" t="n">
         <v>11.93000030517578</v>
       </c>
       <c r="F18" t="n">
-        <v>11.32999992370605</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="G18" t="n">
         <v>11.84000015258789</v>
       </c>
       <c r="H18" t="n">
-        <v>2088100</v>
+        <v>3543600</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0145548006722751</v>
+        <v>-0.03082196925902769</v>
       </c>
       <c r="J18" t="n">
-        <v>12.05666669209798</v>
+        <v>12.03555552164713</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.534142621479577</v>
+        <v>-5.945349390278814</v>
       </c>
       <c r="M18" t="n">
-        <v>12.06599998474121</v>
+        <v>12.04699993133545</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-4.60798737412977</v>
+        <v>-6.034699432679752</v>
       </c>
       <c r="P18" t="n">
-        <v>10.36653837790856</v>
+        <v>10.35923066506019</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>11.03031512824022</v>
+        <v>9.274521060763021</v>
       </c>
       <c r="S18" t="n">
-        <v>10.16239995956421</v>
+        <v>10.15859994888306</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>13.26064979413993</v>
+        <v>11.43267528778765</v>
       </c>
       <c r="V18" t="n">
-        <v>9.022333326339721</v>
+        <v>9.021066656112671</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>27.5723231736478</v>
+        <v>25.48404890849345</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.789599990844726</v>
+        <v>8.788649988174438</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>30.95021662954727</v>
+        <v>28.80248627554672</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9910297819613113</v>
+        <v>0.9950899189018162</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="AG18" t="n">
         <v>12.2</v>
@@ -5756,13 +5756,13 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>-1</v>
+        <v>-0.99</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.69</v>
+        <v>4.77</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="CC18" t="n">
         <v>1</v>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.42000007629395</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="D19" t="n">
-        <v>11.42000007629395</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="E19" t="n">
         <v>11.72000026702881</v>
@@ -5831,67 +5831,67 @@
         <v>11.65999984741211</v>
       </c>
       <c r="H19" t="n">
-        <v>3194300</v>
+        <v>5341000</v>
       </c>
       <c r="I19" t="n">
-        <v>0.004397554198603659</v>
+        <v>0.0008795276149946574</v>
       </c>
       <c r="J19" t="n">
-        <v>11.20333321889242</v>
+        <v>11.19888877868652</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.933949951931801</v>
+        <v>1.617225952802403</v>
       </c>
       <c r="M19" t="n">
-        <v>11.18799991607666</v>
+        <v>11.18399991989136</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.073651787250301</v>
+        <v>1.752505328625433</v>
       </c>
       <c r="P19" t="n">
-        <v>11.43538453028752</v>
+        <v>11.43384607021625</v>
       </c>
       <c r="Q19" t="n">
         <v>-1</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1345337706207514</v>
+        <v>-0.470934761974761</v>
       </c>
       <c r="S19" t="n">
-        <v>11.84179992675781</v>
+        <v>11.84099992752075</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.561957245289753</v>
+        <v>-3.893250704346193</v>
       </c>
       <c r="V19" t="n">
-        <v>13.17979997634888</v>
+        <v>13.17953330993652</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.35225043788896</v>
+        <v>-13.65399785543903</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.02174997329712</v>
+        <v>14.02154997348785</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-18.55510119605556</v>
+        <v>-18.8392143810179</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5951170461259218</v>
+        <v>0.5947287198301298</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6043,7 +6043,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
@@ -6081,7 +6081,7 @@
         <v>1</v>
       </c>
       <c r="CL19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM19" t="n">
         <v>9</v>
@@ -6090,7 +6090,7 @@
         <v>-1</v>
       </c>
       <c r="CO19" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.21000003814697</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="D20" t="n">
-        <v>11.21000003814697</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="E20" t="n">
         <v>11.35000038146973</v>
@@ -6118,91 +6118,91 @@
         <v>11.35000038146973</v>
       </c>
       <c r="H20" t="n">
-        <v>5318400</v>
+        <v>11400100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0008928775939409661</v>
+        <v>-0.003571425226269853</v>
       </c>
       <c r="J20" t="n">
-        <v>11.31888898213704</v>
+        <v>11.31333340538873</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9620108843007099</v>
+        <v>-1.355334917501686</v>
       </c>
       <c r="M20" t="n">
-        <v>11.31500005722046</v>
+        <v>11.31000003814697</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9279718828324927</v>
+        <v>-1.326261628903044</v>
       </c>
       <c r="P20" t="n">
-        <v>11.97692317229051</v>
+        <v>11.97500008803148</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-6.403340182709602</v>
+        <v>-6.805847470798144</v>
       </c>
       <c r="S20" t="n">
-        <v>12.3654001045227</v>
+        <v>12.36440010070801</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.343814649015188</v>
+        <v>-9.740870915580706</v>
       </c>
       <c r="V20" t="n">
-        <v>11.69813336690267</v>
+        <v>11.69780003229777</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.172745458149445</v>
+        <v>-4.597447241368362</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.51175003051758</v>
+        <v>11.5115000295639</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-2.62123475206349</v>
+        <v>-3.053469845363931</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2211363442500854</v>
+        <v>0.2201825300178872</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AE20" t="n">
         <v>11</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
         <v>11.1</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AG20" t="n">
         <v>11.2</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AH20" t="n">
         <v>11.3</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>11.4</v>
       </c>
-      <c r="AI20" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
       <c r="CA20" t="n">
         <v>0.5600000000000001</v>
@@ -6388,7 +6388,7 @@
         <v>4.630000114440918</v>
       </c>
       <c r="E21" t="n">
-        <v>4.650000095367432</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="F21" t="n">
         <v>4.460000038146973</v>
@@ -6397,7 +6397,7 @@
         <v>4.480000019073486</v>
       </c>
       <c r="H21" t="n">
-        <v>8445100</v>
+        <v>10260900</v>
       </c>
       <c r="I21" t="n">
         <v>0.02660751207740697</v>
@@ -6684,7 +6684,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="H22" t="n">
-        <v>12527900</v>
+        <v>16588600</v>
       </c>
       <c r="I22" t="n">
         <v>-0.003937004178520276</v>
@@ -6744,7 +6744,7 @@
         <v>-19.81698368500952</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4591635564093937</v>
+        <v>0.4591635564093942</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.79000091552734</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="D23" t="n">
-        <v>43.79000091552734</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="E23" t="n">
         <v>44.29999923706055</v>
@@ -6967,67 +6967,67 @@
         <v>44.13999938964844</v>
       </c>
       <c r="H23" t="n">
-        <v>1365200</v>
+        <v>2321400</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004588225791221534</v>
+        <v>0.01353521795188306</v>
       </c>
       <c r="J23" t="n">
-        <v>43.89111158582899</v>
+        <v>43.93444485134549</v>
       </c>
       <c r="K23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2303670758119879</v>
+        <v>0.5589132960735974</v>
       </c>
       <c r="M23" t="n">
-        <v>44.02300033569336</v>
+        <v>44.0620002746582</v>
       </c>
       <c r="N23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5292674701617366</v>
+        <v>0.2678045249467365</v>
       </c>
       <c r="P23" t="n">
-        <v>47.86692311213567</v>
+        <v>47.88192308866061</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-8.517201297976689</v>
+        <v>-7.731357774895875</v>
       </c>
       <c r="S23" t="n">
-        <v>48.91079978942871</v>
+        <v>48.91859977722168</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.46966906275809</v>
+        <v>-9.686702999729699</v>
       </c>
       <c r="V23" t="n">
-        <v>48.78800003051758</v>
+        <v>48.79060002644857</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-10.24432055395572</v>
+        <v>-9.449770486063823</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.2945000076294</v>
+        <v>46.29645000457764</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-5.4099279432531</v>
+        <v>-4.571516172822295</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2742017392505117</v>
+        <v>0.2787313029401468</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7179,13 +7179,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.76</v>
+        <v>8.84</v>
       </c>
       <c r="CA23" t="n">
         <v>0.51</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7217,16 +7217,16 @@
         <v>0</v>
       </c>
       <c r="CL23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -7254,7 +7254,7 @@
         <v>14.98999977111816</v>
       </c>
       <c r="H24" t="n">
-        <v>15852600</v>
+        <v>20825800</v>
       </c>
       <c r="I24" t="n">
         <v>-0.009472218685912859</v>
@@ -7314,7 +7314,7 @@
         <v>8.479401840067279</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2282796465917406</v>
+        <v>0.2282796465917407</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7522,82 +7522,82 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.139999866485596</v>
+        <v>4.010000228881836</v>
       </c>
       <c r="D25" t="n">
-        <v>4.139999866485596</v>
+        <v>4.010000228881836</v>
       </c>
       <c r="E25" t="n">
         <v>4.369999885559082</v>
       </c>
       <c r="F25" t="n">
-        <v>4.079999923706055</v>
+        <v>4.010000228881836</v>
       </c>
       <c r="G25" t="n">
         <v>4.340000152587891</v>
       </c>
       <c r="H25" t="n">
-        <v>29719000</v>
+        <v>48802300</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.03271035898594565</v>
+        <v>-0.06308410460068736</v>
       </c>
       <c r="J25" t="n">
-        <v>4.307777775658502</v>
+        <v>4.293333371480306</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.894767044877537</v>
+        <v>-6.599374380768825</v>
       </c>
       <c r="M25" t="n">
-        <v>4.342000007629395</v>
+        <v>4.329000043869018</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.652237236040103</v>
+        <v>-7.368903020432363</v>
       </c>
       <c r="P25" t="n">
-        <v>4.796923068853525</v>
+        <v>4.791923082791842</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-13.69467871255512</v>
+        <v>-16.3175167965018</v>
       </c>
       <c r="S25" t="n">
-        <v>5.051399984359741</v>
+        <v>5.048799991607666</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-18.04252525430659</v>
+        <v>-20.57518151744113</v>
       </c>
       <c r="V25" t="n">
-        <v>5.588533331553141</v>
+        <v>5.587666667302449</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-25.91974278634168</v>
+        <v>-28.23479875155584</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.759449989795685</v>
+        <v>5.758799991607666</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-28.11813847119695</v>
+        <v>-30.36743358467679</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4347223835394273</v>
+        <v>0.4573001676432963</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7612,21 +7612,21 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>4.1</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>4.9</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>5</v>
       </c>
-      <c r="AI25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1</v>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="n">
         <v>-1</v>
       </c>
@@ -7749,13 +7749,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.72</v>
+        <v>-1.67</v>
       </c>
       <c r="CA25" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7809,13 +7809,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>51.25</v>
+        <v>50.75</v>
       </c>
       <c r="D26" t="n">
-        <v>51.25</v>
+        <v>50.75</v>
       </c>
       <c r="E26" t="n">
-        <v>51.43999862670898</v>
+        <v>51.61999893188477</v>
       </c>
       <c r="F26" t="n">
         <v>49.36000061035156</v>
@@ -7824,67 +7824,67 @@
         <v>50.59999847412109</v>
       </c>
       <c r="H26" t="n">
-        <v>10867600</v>
+        <v>13917000</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0377393613382927</v>
+        <v>-0.04712727000816297</v>
       </c>
       <c r="J26" t="n">
-        <v>52.41222212049696</v>
+        <v>52.35666656494141</v>
       </c>
       <c r="K26" t="n">
         <v>-1</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.217463930121083</v>
+        <v>-3.068695297758409</v>
       </c>
       <c r="M26" t="n">
-        <v>52.39599990844727</v>
+        <v>52.34599990844727</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.187189690910943</v>
+        <v>-3.048943398232261</v>
       </c>
       <c r="P26" t="n">
-        <v>53.94115359966572</v>
+        <v>53.92192283043494</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-4.989054590190291</v>
+        <v>-5.882436426478152</v>
       </c>
       <c r="S26" t="n">
-        <v>55.17839996337891</v>
+        <v>55.1683999633789</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.119452477756022</v>
+        <v>-8.008932588786084</v>
       </c>
       <c r="V26" t="n">
-        <v>48.71553326924642</v>
+        <v>48.71219993591308</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>5.202584392837919</v>
+        <v>4.183346403504448</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.28129993438721</v>
+        <v>44.27879993438721</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>15.73734302276244</v>
+        <v>14.614669040719</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.2942747187431597</v>
+        <v>0.3048942473632805</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8036,13 +8036,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.4</v>
+        <v>14.26</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8074,16 +8074,16 @@
         <v>0</v>
       </c>
       <c r="CL26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN26" t="n">
         <v>0</v>
       </c>
       <c r="CO26" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -8111,7 +8111,7 @@
         <v>6.840000152587891</v>
       </c>
       <c r="H27" t="n">
-        <v>9175100</v>
+        <v>12595900</v>
       </c>
       <c r="I27" t="n">
         <v>-0.02092673621646612</v>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31.56999969482422</v>
+        <v>31.47999954223633</v>
       </c>
       <c r="D28" t="n">
-        <v>31.56999969482422</v>
+        <v>31.47999954223633</v>
       </c>
       <c r="E28" t="n">
         <v>33.04999923706055</v>
@@ -8394,98 +8394,94 @@
         <v>32.52000045776367</v>
       </c>
       <c r="H28" t="n">
-        <v>1726500</v>
+        <v>2435400</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.01589782129428585</v>
+        <v>-0.01870331217492427</v>
       </c>
       <c r="J28" t="n">
-        <v>30.80666690402561</v>
+        <v>30.7966668870714</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>2.477816873784757</v>
+        <v>2.218852636457872</v>
       </c>
       <c r="M28" t="n">
-        <v>30.78600025177002</v>
+        <v>30.77700023651123</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.546610266493205</v>
+        <v>2.28417097287837</v>
       </c>
       <c r="P28" t="n">
-        <v>31.01461557241587</v>
+        <v>31.01115402808556</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.790717415508789</v>
+        <v>1.511860905679776</v>
       </c>
       <c r="S28" t="n">
-        <v>33.1384001159668</v>
+        <v>33.13660011291504</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.732879124079645</v>
+        <v>-4.999307608607227</v>
       </c>
       <c r="V28" t="n">
-        <v>34.75206657409668</v>
+        <v>34.75146657307943</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-9.156482456914649</v>
+        <v>-9.413896314169868</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.28939993858337</v>
+        <v>34.28894993782043</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-7.930731504867222</v>
+        <v>-8.191998882082579</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.4952397089673741</v>
+        <v>0.4958879051270886</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="AF28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AG28" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AI28" t="n">
         <v>41.8</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ28" t="n">
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -8606,13 +8602,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>6.3</v>
+        <v>6.28</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8666,82 +8662,82 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.48999977111816</v>
+        <v>17.45999908447266</v>
       </c>
       <c r="D29" t="n">
-        <v>17.48999977111816</v>
+        <v>17.45999908447266</v>
       </c>
       <c r="E29" t="n">
         <v>17.84000015258789</v>
       </c>
       <c r="F29" t="n">
-        <v>17.45000076293945</v>
+        <v>17.43000030517578</v>
       </c>
       <c r="G29" t="n">
         <v>17.64999961853027</v>
       </c>
       <c r="H29" t="n">
-        <v>1491800</v>
+        <v>3239100</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.007378039836738792</v>
+        <v>-0.009080689395001396</v>
       </c>
       <c r="J29" t="n">
-        <v>17.60666698879666</v>
+        <v>17.60333357916938</v>
       </c>
       <c r="K29" t="n">
         <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.6626309099429798</v>
+        <v>-0.8142463133592858</v>
       </c>
       <c r="M29" t="n">
-        <v>17.60000038146973</v>
+        <v>17.59700031280518</v>
       </c>
       <c r="N29" t="n">
         <v>-1</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.62500345436002</v>
+        <v>-0.778548763409547</v>
       </c>
       <c r="P29" t="n">
-        <v>17.79500014965351</v>
+        <v>17.79384627709022</v>
       </c>
       <c r="Q29" t="n">
         <v>-1</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.713966709583208</v>
+        <v>-1.876194654145088</v>
       </c>
       <c r="S29" t="n">
-        <v>18.11120014190674</v>
+        <v>18.11060012817383</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.429923836748983</v>
+        <v>-3.592377055959964</v>
       </c>
       <c r="V29" t="n">
-        <v>17.04840010960897</v>
+        <v>17.04820010503133</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>2.590270398805924</v>
+        <v>2.415498274916387</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.3498500919342</v>
+        <v>16.34970008850098</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>6.973456470689138</v>
+        <v>6.790944114947839</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2313890277501444</v>
+        <v>0.2316571046421608</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8901,13 +8897,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>11.98</v>
+        <v>11.96</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC29" t="n">
         <v>2</v>
@@ -8942,13 +8938,13 @@
         <v>8</v>
       </c>
       <c r="CM29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN29" t="n">
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
@@ -8961,10 +8957,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.14999961853027</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="D30" t="n">
-        <v>22.14999961853027</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="E30" t="n">
         <v>22.79999923706055</v>
@@ -8976,91 +8972,91 @@
         <v>22.70000076293945</v>
       </c>
       <c r="H30" t="n">
-        <v>6690000</v>
+        <v>8691100</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.005834877204162536</v>
+        <v>-0.003590660737905926</v>
       </c>
       <c r="J30" t="n">
-        <v>21.95444446139865</v>
+        <v>21.96000014411079</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8907315212436958</v>
+        <v>1.092898985672502</v>
       </c>
       <c r="M30" t="n">
-        <v>21.94699993133545</v>
+        <v>21.95200004577637</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9249541524123628</v>
+        <v>1.129740873933733</v>
       </c>
       <c r="P30" t="n">
-        <v>23.21153846153846</v>
+        <v>23.21346158247728</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-4.573323930109834</v>
+        <v>-4.365832368158464</v>
       </c>
       <c r="S30" t="n">
-        <v>25.15839992523193</v>
+        <v>25.15939994812012</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-11.95783641106868</v>
+        <v>-11.76259843749488</v>
       </c>
       <c r="V30" t="n">
-        <v>28.73413326263428</v>
+        <v>28.73446660359701</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-22.91398033107189</v>
+        <v>-22.74086354482586</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.62839996337891</v>
+        <v>28.62864996910095</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-22.62927845473628</v>
+        <v>-22.45529989398722</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4002724241039495</v>
+        <v>0.4004051514141092</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AF30" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AG30" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="AH30" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AI30" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -9184,7 +9180,7 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>5.12</v>
+        <v>5.13</v>
       </c>
       <c r="CA30" t="n">
         <v>0.49</v>
@@ -9221,13 +9217,13 @@
         <v>2</v>
       </c>
       <c r="CM30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN30" t="n">
         <v>0</v>
       </c>
       <c r="CO30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -9240,10 +9236,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.35000038146973</v>
+        <v>13.31999969482422</v>
       </c>
       <c r="D31" t="n">
-        <v>13.35000038146973</v>
+        <v>13.31999969482422</v>
       </c>
       <c r="E31" t="n">
         <v>13.75</v>
@@ -9255,67 +9251,67 @@
         <v>13.64000034332275</v>
       </c>
       <c r="H31" t="n">
-        <v>4939200</v>
+        <v>7009900</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.003731286454023874</v>
+        <v>-0.005970143730110733</v>
       </c>
       <c r="J31" t="n">
-        <v>13.07666662004259</v>
+        <v>13.07333321041531</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>2.090240344647153</v>
+        <v>1.886791076451671</v>
       </c>
       <c r="M31" t="n">
-        <v>13.11499996185303</v>
+        <v>13.11199989318848</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.791844607702893</v>
+        <v>1.586331630034524</v>
       </c>
       <c r="P31" t="n">
-        <v>13.25423082938561</v>
+        <v>13.25307695682232</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0.7225583537581659</v>
+        <v>0.5049600045327283</v>
       </c>
       <c r="S31" t="n">
-        <v>13.5292000579834</v>
+        <v>13.52860004425049</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.324540074399513</v>
+        <v>-1.541921179900079</v>
       </c>
       <c r="V31" t="n">
-        <v>15.02753335316976</v>
+        <v>15.02733334859212</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-11.1630627081336</v>
+        <v>-11.36152113061271</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.03641666412354</v>
+        <v>15.03626666069031</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-11.2155463653621</v>
+        <v>-11.414182819416</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4759782989003583</v>
+        <v>0.4761018502151838</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9467,7 +9463,7 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>8.289999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
@@ -9523,10 +9519,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>32.65000152587891</v>
+        <v>32.63000106811523</v>
       </c>
       <c r="D32" t="n">
-        <v>32.65000152587891</v>
+        <v>32.63000106811523</v>
       </c>
       <c r="E32" t="n">
         <v>32.97000122070312</v>
@@ -9538,67 +9534,67 @@
         <v>32.36000061035156</v>
       </c>
       <c r="H32" t="n">
-        <v>1073400</v>
+        <v>2148100</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01240314808926835</v>
+        <v>0.01178297885628643</v>
       </c>
       <c r="J32" t="n">
-        <v>32.3511119418674</v>
+        <v>32.34888966878255</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9238927692766411</v>
+        <v>0.8689986030771223</v>
       </c>
       <c r="M32" t="n">
-        <v>32.36600074768067</v>
+        <v>32.3640007019043</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8774663895371508</v>
+        <v>0.8219019912309157</v>
       </c>
       <c r="P32" t="n">
-        <v>33.98269257178674</v>
+        <v>33.98192332341121</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.921675844527581</v>
+        <v>-3.97835708835407</v>
       </c>
       <c r="S32" t="n">
-        <v>33.8640001296997</v>
+        <v>33.86360012054443</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-3.584923810451106</v>
+        <v>-3.642846738202524</v>
       </c>
       <c r="V32" t="n">
-        <v>32.18643805185954</v>
+        <v>32.18630471547445</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.440244718202313</v>
+        <v>1.378525296902027</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.29761412620545</v>
+        <v>31.29751412391663</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.321055893334402</v>
+        <v>4.257484920121371</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2151747297536945</v>
+        <v>0.2147638676446197</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9748,7 +9744,7 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>14.51</v>
+        <v>14.5</v>
       </c>
       <c r="CA32" t="n">
         <v>0.66</v>
@@ -9782,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="CL32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM32" t="n">
         <v>7</v>
@@ -9791,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="CO32" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
@@ -9804,10 +9800,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>73.25</v>
+        <v>73.5</v>
       </c>
       <c r="D33" t="n">
-        <v>73.25</v>
+        <v>73.5</v>
       </c>
       <c r="E33" t="n">
         <v>74.69999694824219</v>
@@ -9819,46 +9815,46 @@
         <v>73.58000183105469</v>
       </c>
       <c r="H33" t="n">
-        <v>2088600</v>
+        <v>3890800</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0120199334014337</v>
+        <v>0.01547392634819622</v>
       </c>
       <c r="J33" t="n">
-        <v>71.42444356282552</v>
+        <v>71.4522213406033</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>2.555926719357232</v>
+        <v>2.865941213549132</v>
       </c>
       <c r="M33" t="n">
-        <v>71.53499908447266</v>
+        <v>71.55999908447265</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>2.397429143043909</v>
+        <v>2.711013052469837</v>
       </c>
       <c r="P33" t="n">
-        <v>75.60192284217247</v>
+        <v>75.61153822678786</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-3.110929925793521</v>
+        <v>-2.792613768092574</v>
       </c>
       <c r="S33" t="n">
-        <v>77.63919967651367</v>
+        <v>77.64419967651367</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-5.653329368156057</v>
+        <v>-5.337423392577295</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
@@ -9871,7 +9867,7 @@
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
-        <v>0.4848645963593949</v>
+        <v>0.4860356431027495</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -9891,10 +9887,10 @@
         <v>74</v>
       </c>
       <c r="AH33" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AI33" t="n">
         <v>75.8</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>77.7</v>
       </c>
       <c r="AJ33" t="n">
         <v>1</v>
@@ -10021,13 +10017,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>31.99</v>
+        <v>32.1</v>
       </c>
       <c r="CA33" t="n">
         <v>0.06</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CC33" t="n">
         <v>8</v>
@@ -10062,13 +10058,13 @@
         <v>6</v>
       </c>
       <c r="CM33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
@@ -10081,10 +10077,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.23999977111816</v>
+        <v>25.13999938964844</v>
       </c>
       <c r="D34" t="n">
-        <v>25.23999977111816</v>
+        <v>25.13999938964844</v>
       </c>
       <c r="E34" t="n">
         <v>25.29999923706055</v>
@@ -10096,67 +10092,67 @@
         <v>25.29999923706055</v>
       </c>
       <c r="H34" t="n">
-        <v>2094200</v>
+        <v>4566800</v>
       </c>
       <c r="I34" t="n">
-        <v>0.007182773703583223</v>
+        <v>0.003192335411450253</v>
       </c>
       <c r="J34" t="n">
-        <v>25.05222172207302</v>
+        <v>25.04111056857639</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7495464918374553</v>
+        <v>0.3949058920579261</v>
       </c>
       <c r="M34" t="n">
-        <v>25.14199962615967</v>
+        <v>25.1319995880127</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3897865977872764</v>
+        <v>0.03183113865542343</v>
       </c>
       <c r="P34" t="n">
-        <v>26.28192292726957</v>
+        <v>26.2780767587515</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.964409906515355</v>
+        <v>-4.330900543260064</v>
       </c>
       <c r="S34" t="n">
-        <v>25.73599990844727</v>
+        <v>25.73399990081787</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-1.927261964149683</v>
+        <v>-2.308232351980987</v>
       </c>
       <c r="V34" t="n">
-        <v>21.98166667938233</v>
+        <v>21.98100001017253</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>14.82295741838351</v>
+        <v>14.37149983173635</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.35855002880096</v>
+        <v>20.35805002689361</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>23.97739394707128</v>
+        <v>23.48923082730281</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2595027974360374</v>
+        <v>0.2585410955648498</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10308,13 +10304,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>37.67</v>
+        <v>37.52</v>
       </c>
       <c r="CA34" t="n">
         <v>0.38</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CC34" t="n">
         <v>10</v>
@@ -10364,10 +10360,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.36000061035156</v>
+        <v>48.2400016784668</v>
       </c>
       <c r="D35" t="n">
-        <v>48.36000061035156</v>
+        <v>48.2400016784668</v>
       </c>
       <c r="E35" t="n">
         <v>49.20000076293945</v>
@@ -10379,67 +10375,67 @@
         <v>49.16999816894531</v>
       </c>
       <c r="H35" t="n">
-        <v>1300100</v>
+        <v>1747600</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.00226945755273833</v>
+        <v>-0.004745193654711266</v>
       </c>
       <c r="J35" t="n">
-        <v>48.35888926188151</v>
+        <v>48.34555604722765</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002298126543056197</v>
+        <v>-0.2183331362612429</v>
       </c>
       <c r="M35" t="n">
-        <v>48.43100051879883</v>
+        <v>48.41900062561035</v>
       </c>
       <c r="N35" t="n">
         <v>-1</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.1466001273702857</v>
+        <v>-0.3696874054209133</v>
       </c>
       <c r="P35" t="n">
-        <v>51.42961560762846</v>
+        <v>51.42500026409443</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-5.968574645192533</v>
+        <v>-6.193482876560017</v>
       </c>
       <c r="S35" t="n">
-        <v>52.37539993286133</v>
+        <v>52.37299995422363</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-7.666575009750765</v>
+        <v>-7.891467510681574</v>
       </c>
       <c r="V35" t="n">
-        <v>50.41301195780436</v>
+        <v>50.41221196492513</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-4.072383830530043</v>
+        <v>-4.308896994977469</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.88330425262451</v>
+        <v>48.88270425796509</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-1.070516100074913</v>
+        <v>-1.314785237957794</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2436273574431324</v>
+        <v>0.2434201343221602</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10591,7 +10587,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.79</v>
+        <v>12.76</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
@@ -10628,13 +10624,13 @@
         <v>4</v>
       </c>
       <c r="CM35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
@@ -10647,82 +10643,82 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.04000091552734</v>
+        <v>37.9900016784668</v>
       </c>
       <c r="D36" t="n">
-        <v>38.04000091552734</v>
+        <v>37.9900016784668</v>
       </c>
       <c r="E36" t="n">
         <v>39.04999923706055</v>
       </c>
       <c r="F36" t="n">
-        <v>37.93999862670898</v>
+        <v>37.83000183105469</v>
       </c>
       <c r="G36" t="n">
         <v>39.02999877929688</v>
       </c>
       <c r="H36" t="n">
-        <v>5149000</v>
+        <v>7858600</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.01450770934535639</v>
+        <v>-0.015803026418855</v>
       </c>
       <c r="J36" t="n">
-        <v>38.27999962700738</v>
+        <v>38.27444415622287</v>
       </c>
       <c r="K36" t="n">
         <v>-1</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.6269558877182162</v>
+        <v>-0.7431655351938716</v>
       </c>
       <c r="M36" t="n">
-        <v>38.33199958801269</v>
+        <v>38.32699966430664</v>
       </c>
       <c r="N36" t="n">
         <v>-1</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.7617621716156532</v>
+        <v>-0.8792704589232037</v>
       </c>
       <c r="P36" t="n">
-        <v>40.96346150911771</v>
+        <v>40.96153846153846</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-7.136751841490889</v>
+        <v>-7.25445599623129</v>
       </c>
       <c r="S36" t="n">
-        <v>41.4323999786377</v>
+        <v>41.43139999389648</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-8.187792801912162</v>
+        <v>-8.306256404409845</v>
       </c>
       <c r="V36" t="n">
-        <v>40.0387999979655</v>
+        <v>40.03846666971842</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-4.992155315693076</v>
+        <v>-5.11624235800445</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.04229999542236</v>
+        <v>39.04204999923706</v>
       </c>
       <c r="Z36" t="n">
         <v>-1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-2.567213202123172</v>
+        <v>-2.694654406699494</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2559028989653203</v>
+        <v>0.2563394707148283</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10874,7 +10870,7 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>30.93</v>
+        <v>30.89</v>
       </c>
       <c r="CA36" t="n">
         <v>0.96</v>
@@ -10911,13 +10907,13 @@
         <v>4</v>
       </c>
       <c r="CM36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN36" t="n">
         <v>0</v>
       </c>
       <c r="CO36" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37">
@@ -10930,113 +10926,111 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.03000068664551</v>
+        <v>15.97999954223633</v>
       </c>
       <c r="D37" t="n">
-        <v>16.03000068664551</v>
+        <v>15.97999954223633</v>
       </c>
       <c r="E37" t="n">
         <v>16.39999961853027</v>
       </c>
       <c r="F37" t="n">
-        <v>15.96000003814697</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="G37" t="n">
         <v>16.34000015258789</v>
       </c>
       <c r="H37" t="n">
-        <v>1784800</v>
+        <v>2433200</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.001246015661412692</v>
+        <v>-0.004361351909761169</v>
       </c>
       <c r="J37" t="n">
-        <v>15.74666659037272</v>
+        <v>15.74111090766059</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.79932746176269</v>
+        <v>1.517609754337473</v>
       </c>
       <c r="M37" t="n">
-        <v>15.76799993515015</v>
+        <v>15.76299982070923</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.661597872735315</v>
+        <v>1.376639751286474</v>
       </c>
       <c r="P37" t="n">
-        <v>16.08576917648315</v>
+        <v>16.08384605554434</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.346694579698297</v>
+        <v>-0.645657219979501</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06619997024536</v>
+        <v>16.06519994735718</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.2253132891840881</v>
+        <v>-0.5303413925754905</v>
       </c>
       <c r="V37" t="n">
-        <v>15.85333337148031</v>
+        <v>15.85300003051758</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.11438592140516</v>
+        <v>0.8011071183641713</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.69560001373291</v>
+        <v>15.69535000801086</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.130537683299857</v>
+        <v>1.813591503726769</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2698510279465743</v>
+        <v>0.2698942137864639</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AE37" t="n">
         <v>15.6</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AF37" t="n">
         <v>15.8</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AG37" t="n">
         <v>16</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AH37" t="n">
         <v>26</v>
       </c>
-      <c r="AH37" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>Foguete</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
       <c r="AJ37" t="n">
         <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -11157,7 +11151,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>13.82</v>
+        <v>13.78</v>
       </c>
       <c r="CA37" t="n">
         <v>0.37</v>
@@ -11217,10 +11211,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23.69000053405762</v>
+        <v>23.73999977111816</v>
       </c>
       <c r="D38" t="n">
-        <v>23.69000053405762</v>
+        <v>23.73999977111816</v>
       </c>
       <c r="E38" t="n">
         <v>24.04999923706055</v>
@@ -11232,67 +11226,67 @@
         <v>24.02000045776367</v>
       </c>
       <c r="H38" t="n">
-        <v>6982900</v>
+        <v>9698200</v>
       </c>
       <c r="I38" t="n">
-        <v>0.003388391428968518</v>
+        <v>0.005506105777464798</v>
       </c>
       <c r="J38" t="n">
-        <v>23.56444464789497</v>
+        <v>23.57000011867947</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5328192029930446</v>
+        <v>0.7212543554633565</v>
       </c>
       <c r="M38" t="n">
-        <v>23.56600017547607</v>
+        <v>23.57100009918213</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.5261833050081383</v>
+        <v>0.7169813381906487</v>
       </c>
       <c r="P38" t="n">
-        <v>23.10692317669208</v>
+        <v>23.10884622427134</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.523388133101533</v>
+        <v>2.731220506300851</v>
       </c>
       <c r="S38" t="n">
-        <v>21.3338000869751</v>
+        <v>21.33480007171631</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>11.04444795337258</v>
+        <v>11.27359849315131</v>
       </c>
       <c r="V38" t="n">
-        <v>20.61486668904622</v>
+        <v>20.61520001729329</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>14.91706879019196</v>
+        <v>15.15774647446349</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.66975004196167</v>
+        <v>19.67000003814697</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>20.43874723125361</v>
+        <v>20.69140683822087</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.2595135062640872</v>
+        <v>0.2595453689793789</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11442,10 +11436,10 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>28.54</v>
+        <v>28.6</v>
       </c>
       <c r="CA38" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="CB38" t="n">
         <v>0.89</v>
@@ -11498,10 +11492,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.30000019073486</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="D39" t="n">
-        <v>10.30000019073486</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="E39" t="n">
         <v>10.38000011444092</v>
@@ -11513,67 +11507,67 @@
         <v>10.3100004196167</v>
       </c>
       <c r="H39" t="n">
-        <v>5692600</v>
+        <v>11678700</v>
       </c>
       <c r="I39" t="n">
-        <v>0.009803959150949337</v>
+        <v>0.01176469488264886</v>
       </c>
       <c r="J39" t="n">
-        <v>10.23999998304579</v>
+        <v>10.24222215016683</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5859395291837399</v>
+        <v>0.7593815435464056</v>
       </c>
       <c r="M39" t="n">
-        <v>10.24300003051758</v>
+        <v>10.24499998092651</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.5564791569604725</v>
+        <v>0.7320616304278683</v>
       </c>
       <c r="P39" t="n">
-        <v>10.07076927331778</v>
+        <v>10.07153848501352</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>2.276200667454736</v>
+        <v>2.46696381273237</v>
       </c>
       <c r="S39" t="n">
-        <v>9.399000005722046</v>
+        <v>9.399399995803833</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>9.586128146231458</v>
+        <v>9.794238987928679</v>
       </c>
       <c r="V39" t="n">
-        <v>9.072911650339762</v>
+        <v>9.073044980367024</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>13.5247491399208</v>
+        <v>13.74350857022592</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.593590860366822</v>
+        <v>8.593690857887267</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>19.85676718957973</v>
+        <v>20.08809562136564</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.2635893749154926</v>
+        <v>0.2640550040678464</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11729,7 +11723,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.95</v>
+        <v>24</v>
       </c>
       <c r="CA39" t="n">
         <v>0.6</v>
@@ -11789,82 +11783,82 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.52999973297119</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="D40" t="n">
-        <v>12.52999973297119</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="E40" t="n">
         <v>13.03999996185303</v>
       </c>
       <c r="F40" t="n">
-        <v>12.47000026702881</v>
+        <v>12.31999969482422</v>
       </c>
       <c r="G40" t="n">
         <v>12.72999954223633</v>
       </c>
       <c r="H40" t="n">
-        <v>3408400</v>
+        <v>6307600</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.005555606855495165</v>
+        <v>-0.01587307594320275</v>
       </c>
       <c r="J40" t="n">
-        <v>12.57555558946398</v>
+        <v>12.56111113230387</v>
       </c>
       <c r="K40" t="n">
         <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3622572073948923</v>
+        <v>-1.282621513946034</v>
       </c>
       <c r="M40" t="n">
-        <v>12.64400005340576</v>
+        <v>12.63100004196167</v>
       </c>
       <c r="N40" t="n">
         <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.9016159439501381</v>
+        <v>-1.828837167793412</v>
       </c>
       <c r="P40" t="n">
-        <v>12.44807694508479</v>
+        <v>12.44307694068322</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R40" t="n">
-        <v>0.6581160146085693</v>
+        <v>-0.3461950959420758</v>
       </c>
       <c r="S40" t="n">
-        <v>11.56119998931885</v>
+        <v>11.55859998703003</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>8.379750757251824</v>
+        <v>7.279425124533978</v>
       </c>
       <c r="V40" t="n">
-        <v>15.22200000127157</v>
+        <v>15.22113333384196</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-17.68493146810865</v>
+        <v>-18.53432102220213</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.84234997272491</v>
+        <v>20.84169997215271</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-39.88202026466103</v>
+        <v>-40.50389538714056</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6864211227353177</v>
+        <v>0.6877320426116925</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12014,10 +12008,10 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-14.74</v>
+        <v>-14.59</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="CB40" t="n">
         <v>0.13</v>
@@ -12055,13 +12049,13 @@
         <v>10</v>
       </c>
       <c r="CM40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN40" t="n">
         <v>-1</v>
       </c>
       <c r="CO40" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41">
@@ -12074,10 +12068,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22.59000015258789</v>
+        <v>22.46999931335449</v>
       </c>
       <c r="D41" t="n">
-        <v>22.59000015258789</v>
+        <v>22.46999931335449</v>
       </c>
       <c r="E41" t="n">
         <v>23.03000068664551</v>
@@ -12089,88 +12083,88 @@
         <v>23.03000068664551</v>
       </c>
       <c r="H41" t="n">
-        <v>654800</v>
+        <v>1770100</v>
       </c>
       <c r="I41" t="n">
-        <v>0.002663092060088079</v>
+        <v>-0.00266317671825822</v>
       </c>
       <c r="J41" t="n">
-        <v>22.63888888888889</v>
+        <v>22.6255554623074</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.2159502462375401</v>
+        <v>-0.6875241105662723</v>
       </c>
       <c r="M41" t="n">
-        <v>22.71200008392334</v>
+        <v>22.7</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.5371606678612423</v>
+        <v>-1.013218883900912</v>
       </c>
       <c r="P41" t="n">
-        <v>22.8511538872352</v>
+        <v>22.84653847034161</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-1.14284703492892</v>
+        <v>-1.648123445378496</v>
       </c>
       <c r="S41" t="n">
-        <v>22.88940002441406</v>
+        <v>22.8870000076294</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.30802848264624</v>
+        <v>-1.821998051889267</v>
       </c>
       <c r="V41" t="n">
-        <v>23.66200004577637</v>
+        <v>23.66120004018148</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-4.530470336888646</v>
+        <v>-5.034405375906912</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.5119499874115</v>
+        <v>23.51134998321533</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-3.921196818286987</v>
+        <v>-4.42914026886698</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.2985942144812817</v>
+        <v>0.298431614380082</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE41" t="n">
         <v>22.3</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AF41" t="n">
         <v>22.4</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AG41" t="n">
         <v>22.5</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>22.6</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>22.9</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>23</v>
       </c>
       <c r="AJ41" t="n">
         <v>2</v>
@@ -12297,13 +12291,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>9.449999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CA41" t="n">
         <v>0.39</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="CC41" t="n">
         <v>4</v>
@@ -12353,82 +12347,82 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>26.18000030517578</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="D42" t="n">
-        <v>26.18000030517578</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="E42" t="n">
         <v>26.6299991607666</v>
       </c>
       <c r="F42" t="n">
-        <v>26.03000068664551</v>
+        <v>26.02000045776367</v>
       </c>
       <c r="G42" t="n">
         <v>26.57999992370605</v>
       </c>
       <c r="H42" t="n">
-        <v>568300</v>
+        <v>936000</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.004941055241558745</v>
+        <v>-0.006461424543698913</v>
       </c>
       <c r="J42" t="n">
-        <v>26.30333307054308</v>
+        <v>26.29888852437337</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.468886452665628</v>
+        <v>-0.604166729623109</v>
       </c>
       <c r="M42" t="n">
-        <v>26.32499980926514</v>
+        <v>26.3209997177124</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.5508053376635642</v>
+        <v>-0.6876650963305327</v>
       </c>
       <c r="P42" t="n">
-        <v>27.3646151469304</v>
+        <v>27.36307665017935</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.329002382799827</v>
+        <v>-4.469808991756393</v>
       </c>
       <c r="S42" t="n">
-        <v>27.69359985351563</v>
+        <v>27.69279983520508</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-5.465521118041635</v>
+        <v>-5.607235291473165</v>
       </c>
       <c r="V42" t="n">
-        <v>26.94439989725749</v>
+        <v>26.94413322448731</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.836951630010172</v>
+        <v>-2.984448704061697</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.00634990692139</v>
+        <v>26.00614990234375</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.6677230710034375</v>
+        <v>0.5146839797790446</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.2971997595583538</v>
+        <v>0.2972935567363804</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12580,13 +12574,13 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>10.91</v>
+        <v>10.89</v>
       </c>
       <c r="CA42" t="n">
         <v>0.04</v>
       </c>
       <c r="CB42" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CC42" t="n">
         <v>7</v>
@@ -12636,10 +12630,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.38999938964844</v>
+        <v>27.3799991607666</v>
       </c>
       <c r="D43" t="n">
-        <v>27.38999938964844</v>
+        <v>27.3799991607666</v>
       </c>
       <c r="E43" t="n">
         <v>27.92000007629395</v>
@@ -12651,67 +12645,67 @@
         <v>27.79000091552734</v>
       </c>
       <c r="H43" t="n">
-        <v>3002000</v>
+        <v>4262100</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01403892323100453</v>
+        <v>-0.01439890266349764</v>
       </c>
       <c r="J43" t="n">
-        <v>28.14888911777073</v>
+        <v>28.1477779812283</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.695984644179765</v>
+        <v>-2.727671153913914</v>
       </c>
       <c r="M43" t="n">
-        <v>28.2230001449585</v>
+        <v>28.22200012207031</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-2.951496123840894</v>
+        <v>-2.983491452277491</v>
       </c>
       <c r="P43" t="n">
-        <v>29.13769230475793</v>
+        <v>29.13730768057016</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-5.99804849618824</v>
+        <v>-6.031128678973317</v>
       </c>
       <c r="S43" t="n">
-        <v>29.21360000610352</v>
+        <v>29.21340000152588</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-6.242300216591171</v>
+        <v>-6.275889970573489</v>
       </c>
       <c r="V43" t="n">
-        <v>27.95539995829264</v>
+        <v>27.9553332901001</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-2.02250931658191</v>
+        <v>-2.058047827092942</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.77835000038147</v>
+        <v>26.77829999923706</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.284119033690483</v>
+        <v>2.246965496490385</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.250364829764933</v>
+        <v>0.2504916067567867</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12900,13 +12894,13 @@
         <v>5</v>
       </c>
       <c r="CM43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN43" t="n">
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
@@ -12919,10 +12913,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13.10999965667725</v>
+        <v>13.06999969482422</v>
       </c>
       <c r="D44" t="n">
-        <v>13.10999965667725</v>
+        <v>13.06999969482422</v>
       </c>
       <c r="E44" t="n">
         <v>13.1899995803833</v>
@@ -12934,67 +12928,67 @@
         <v>13.14000034332275</v>
       </c>
       <c r="H44" t="n">
-        <v>9972500</v>
+        <v>16997700</v>
       </c>
       <c r="I44" t="n">
-        <v>0.009237866641528925</v>
+        <v>0.006158577761019357</v>
       </c>
       <c r="J44" t="n">
-        <v>12.9477776421441</v>
+        <v>12.94333320193821</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.252894658965478</v>
+        <v>0.9786234419665973</v>
       </c>
       <c r="M44" t="n">
-        <v>12.96999988555908</v>
+        <v>12.96599988937378</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.079412277204732</v>
+        <v>0.8020963006152058</v>
       </c>
       <c r="P44" t="n">
-        <v>13.44999999266404</v>
+        <v>13.44846153259277</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.527883540314065</v>
+        <v>-2.814164555933334</v>
       </c>
       <c r="S44" t="n">
-        <v>13.70540000915527</v>
+        <v>13.70460000991821</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-4.344275629170229</v>
+        <v>-4.630564296912898</v>
       </c>
       <c r="V44" t="n">
-        <v>12.89973971048991</v>
+        <v>12.89947304407755</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>1.629954951853457</v>
+        <v>1.321966022673748</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.39451055049896</v>
+        <v>12.3943105506897</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>5.772628965566377</v>
+        <v>5.451607343313839</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2368290232669848</v>
+        <v>0.2355291736405792</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13146,7 +13140,7 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.68</v>
+        <v>8.66</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
@@ -13183,13 +13177,13 @@
         <v>7</v>
       </c>
       <c r="CM44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN44" t="n">
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45">
@@ -13202,10 +13196,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40.45000076293945</v>
+        <v>40.31999969482422</v>
       </c>
       <c r="D45" t="n">
-        <v>40.45000076293945</v>
+        <v>40.31999969482422</v>
       </c>
       <c r="E45" t="n">
         <v>40.81999969482422</v>
@@ -13217,67 +13211,67 @@
         <v>40.59999847412109</v>
       </c>
       <c r="H45" t="n">
-        <v>14243500</v>
+        <v>21543200</v>
       </c>
       <c r="I45" t="n">
-        <v>0.009735381334970761</v>
+        <v>0.006490222481783325</v>
       </c>
       <c r="J45" t="n">
-        <v>39.79444419013129</v>
+        <v>39.77999962700738</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.647357027217211</v>
+        <v>1.357466246556285</v>
       </c>
       <c r="M45" t="n">
-        <v>39.85499992370605</v>
+        <v>39.84199981689453</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>1.492913913868781</v>
+        <v>1.199738668055011</v>
       </c>
       <c r="P45" t="n">
-        <v>41.58346132131723</v>
+        <v>41.57846128023588</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.725748464322096</v>
+        <v>-3.026715146887513</v>
       </c>
       <c r="S45" t="n">
-        <v>42.6847998046875</v>
+        <v>42.6821997833252</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-5.235585154372985</v>
+        <v>-5.534391621080003</v>
       </c>
       <c r="V45" t="n">
-        <v>41.83026769002279</v>
+        <v>41.82940101623535</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-3.299684662100669</v>
+        <v>-3.608469843556414</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.55342882156372</v>
+        <v>40.55277881622315</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-0.2550414641369877</v>
+        <v>-0.5740152171909952</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.242680952369193</v>
+        <v>0.2412582975771645</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13449,7 +13443,7 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.609999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
@@ -13520,7 +13514,7 @@
         <v>16.80999946594238</v>
       </c>
       <c r="H46" t="n">
-        <v>4569100</v>
+        <v>6362700</v>
       </c>
       <c r="I46" t="n">
         <v>0.01023480253143383</v>
@@ -13774,7 +13768,7 @@
         <v>-1</v>
       </c>
       <c r="CL46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM46" t="n">
         <v>9</v>
@@ -13783,7 +13777,7 @@
         <v>1</v>
       </c>
       <c r="CO46" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -13796,10 +13790,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>14.92000007629395</v>
+        <v>14.86999988555908</v>
       </c>
       <c r="D47" t="n">
-        <v>14.92000007629395</v>
+        <v>14.86999988555908</v>
       </c>
       <c r="E47" t="n">
         <v>15.51000022888184</v>
@@ -13811,88 +13805,88 @@
         <v>15.13000011444092</v>
       </c>
       <c r="H47" t="n">
-        <v>5102600</v>
+        <v>9143800</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.007978715815388671</v>
+        <v>-0.01130319659076651</v>
       </c>
       <c r="J47" t="n">
-        <v>14.55000008477105</v>
+        <v>14.54444450802273</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>2.542955253382858</v>
+        <v>2.238348651657157</v>
       </c>
       <c r="M47" t="n">
-        <v>14.46700010299683</v>
+        <v>14.46200008392334</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>3.131264049713257</v>
+        <v>2.821185169880446</v>
       </c>
       <c r="P47" t="n">
-        <v>14.23692314441388</v>
+        <v>14.23500006015484</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>4.797925260614249</v>
+        <v>4.460834722310022</v>
       </c>
       <c r="S47" t="n">
-        <v>14.71020004272461</v>
+        <v>14.70920003890991</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1.426221485499774</v>
+        <v>1.093192330132224</v>
       </c>
       <c r="V47" t="n">
-        <v>14.67626670201619</v>
+        <v>14.67593336741129</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>1.660731432771436</v>
+        <v>1.322345320664391</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.94275002479553</v>
+        <v>14.94250002384186</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-0.1522474006714766</v>
+        <v>-0.4851941654147294</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4687775789995374</v>
+        <v>0.4692748523339494</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AE47" t="n">
         <v>14.7</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AF47" t="n">
         <v>14.8</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AG47" t="n">
         <v>14.9</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>15</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>15.1</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>15.2</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14019,13 +14013,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>10.08</v>
+        <v>10.05</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14075,10 +14069,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.02000045776367</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="D48" t="n">
-        <v>16.02000045776367</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="E48" t="n">
         <v>16.54999923706055</v>
@@ -14090,67 +14084,67 @@
         <v>16.5</v>
       </c>
       <c r="H48" t="n">
-        <v>2875900</v>
+        <v>8203400</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.02078240463956704</v>
+        <v>-0.004278709792952418</v>
       </c>
       <c r="J48" t="n">
-        <v>16.76888889736599</v>
+        <v>16.79888894822862</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-4.465939539500168</v>
+        <v>-3.02929577229534</v>
       </c>
       <c r="M48" t="n">
-        <v>16.83400001525879</v>
+        <v>16.86100006103516</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-4.835449428283741</v>
+        <v>-3.38650817532087</v>
       </c>
       <c r="P48" t="n">
-        <v>17.40076930706318</v>
+        <v>17.41115394005408</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-7.9351023218211</v>
+        <v>-6.4392804083338</v>
       </c>
       <c r="S48" t="n">
-        <v>18.48120010375976</v>
+        <v>18.48660011291504</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-13.31731506708481</v>
+        <v>-11.88211560790518</v>
       </c>
       <c r="V48" t="n">
-        <v>18.86760006586711</v>
+        <v>18.86940006891886</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-15.09253746190515</v>
+        <v>-13.66974648886815</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.57105003833771</v>
+        <v>19.57240004062653</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-18.14439988461471</v>
+        <v>-16.77054994934648</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.5036564205925965</v>
+        <v>0.5024253171545668</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14298,13 +14292,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>59.33</v>
+        <v>60.33</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14336,16 +14330,16 @@
         <v>0</v>
       </c>
       <c r="CL48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN48" t="n">
         <v>-1</v>
       </c>
       <c r="CO48" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
@@ -14358,103 +14352,103 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.739999771118164</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="D49" t="n">
-        <v>6.739999771118164</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="E49" t="n">
         <v>6.829999923706055</v>
       </c>
       <c r="F49" t="n">
-        <v>6.710000038146973</v>
+        <v>6.590000152587891</v>
       </c>
       <c r="G49" t="n">
         <v>6.739999771118164</v>
       </c>
       <c r="H49" t="n">
-        <v>9180600</v>
+        <v>13401600</v>
       </c>
       <c r="I49" t="n">
-        <v>0.01353378563309016</v>
+        <v>-0.007518825566588339</v>
       </c>
       <c r="J49" t="n">
-        <v>6.686666647593181</v>
+        <v>6.671111106872559</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.797604043027632</v>
+        <v>-1.065957396013562</v>
       </c>
       <c r="M49" t="n">
-        <v>6.708999967575073</v>
+        <v>6.694999980926513</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4620629556254994</v>
+        <v>-1.418970523742977</v>
       </c>
       <c r="P49" t="n">
-        <v>7.550769145672138</v>
+        <v>7.545384535422692</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-10.73757333739545</v>
+        <v>-12.52931015446469</v>
       </c>
       <c r="S49" t="n">
-        <v>8.194199962615967</v>
+        <v>8.191399965286255</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-17.74670130253393</v>
+        <v>-19.4276932807306</v>
       </c>
       <c r="V49" t="n">
-        <v>8.849510895411173</v>
+        <v>8.848577562967936</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-23.83760130050662</v>
+        <v>-25.41174151816061</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.725371148586273</v>
+        <v>8.724671149253846</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-22.75400488596738</v>
+        <v>-24.35245074885125</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4388805074707386</v>
+        <v>0.4332878365551336</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AF49" t="n">
         <v>6.5</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AG49" t="n">
         <v>6.6</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AH49" t="n">
         <v>6.7</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>7.2</v>
       </c>
       <c r="AJ49" t="n">
         <v>1</v>
@@ -14581,13 +14575,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>37.44</v>
+        <v>36.67</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="CC49" t="n">
         <v>2</v>
@@ -14622,13 +14616,13 @@
         <v>1</v>
       </c>
       <c r="CM49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN49" t="n">
         <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
@@ -14641,113 +14635,109 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.43000030517578</v>
+        <v>14.32999992370605</v>
       </c>
       <c r="D50" t="n">
-        <v>14.43000030517578</v>
+        <v>14.32999992370605</v>
       </c>
       <c r="E50" t="n">
         <v>14.8100004196167</v>
       </c>
       <c r="F50" t="n">
-        <v>14.38000011444092</v>
+        <v>14.28999996185303</v>
       </c>
       <c r="G50" t="n">
         <v>14.71000003814697</v>
       </c>
       <c r="H50" t="n">
-        <v>2076600</v>
+        <v>5347500</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.005513433662586498</v>
+        <v>-0.01240525860347641</v>
       </c>
       <c r="J50" t="n">
-        <v>14.72333335876465</v>
+        <v>14.71222220526801</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.992300564289329</v>
+        <v>-2.597991494616604</v>
       </c>
       <c r="M50" t="n">
-        <v>14.72700004577637</v>
+        <v>14.71700000762939</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-2.016702245382044</v>
+        <v>-2.629612582202326</v>
       </c>
       <c r="P50" t="n">
-        <v>15.46499996918898</v>
+        <v>15.46115380067092</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.692529363564429</v>
+        <v>-7.316102611409104</v>
       </c>
       <c r="S50" t="n">
-        <v>15.74200004577637</v>
+        <v>15.74000003814697</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-8.334390400110561</v>
+        <v>-8.958069320353781</v>
       </c>
       <c r="V50" t="n">
-        <v>15.84380002975464</v>
+        <v>15.84313336054484</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-8.923362589301455</v>
+        <v>-9.550720822732185</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.42835001468658</v>
+        <v>15.42785001277924</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-6.470878017159659</v>
+        <v>-7.116027756063274</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.3248860328736564</v>
+        <v>0.325584586178941</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>13.8</v>
+        <v>12.9</v>
       </c>
       <c r="AE50" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AF50" t="n">
         <v>13.9</v>
       </c>
-      <c r="AF50" t="n">
-        <v>14</v>
-      </c>
       <c r="AG50" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
+        <v>14.5</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>14.9</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
@@ -14868,13 +14858,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.69</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="CA50" t="n">
         <v>1.06</v>
       </c>
       <c r="CB50" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CC50" t="n">
         <v>5</v>
@@ -14906,7 +14896,7 @@
         <v>0</v>
       </c>
       <c r="CL50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM50" t="n">
         <v>3</v>
@@ -14915,7 +14905,7 @@
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -14937,13 +14927,13 @@
         <v>6.340000152587891</v>
       </c>
       <c r="F51" t="n">
-        <v>5.96999979019165</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="G51" t="n">
         <v>6.320000171661377</v>
       </c>
       <c r="H51" t="n">
-        <v>7357600</v>
+        <v>10598900</v>
       </c>
       <c r="I51" t="n">
         <v>-0.0292683418511438</v>
@@ -15215,10 +15205,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>29.89999961853027</v>
+        <v>29.78000068664551</v>
       </c>
       <c r="D52" t="n">
-        <v>29.89999961853027</v>
+        <v>29.78000068664551</v>
       </c>
       <c r="E52" t="n">
         <v>30.47999954223633</v>
@@ -15230,67 +15220,67 @@
         <v>30.45999908447266</v>
       </c>
       <c r="H52" t="n">
-        <v>935600</v>
+        <v>1870100</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.003333346048990937</v>
+        <v>-0.007333310445149732</v>
       </c>
       <c r="J52" t="n">
-        <v>29.82999992370605</v>
+        <v>29.81666670905219</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2346620683984301</v>
+        <v>-0.1229715674272644</v>
       </c>
       <c r="M52" t="n">
-        <v>29.83599987030029</v>
+        <v>29.82399997711182</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2145051230332297</v>
+        <v>-0.1475298098849145</v>
       </c>
       <c r="P52" t="n">
-        <v>31.12461515573355</v>
+        <v>31.11999981219952</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.934556398772642</v>
+        <v>-4.305909812469574</v>
       </c>
       <c r="S52" t="n">
-        <v>31.61439994812012</v>
+        <v>31.61199996948242</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-5.422846337122354</v>
+        <v>-5.795265356843886</v>
       </c>
       <c r="V52" t="n">
-        <v>30.5889333597819</v>
+        <v>30.58813336690267</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-2.252231985824757</v>
+        <v>-2.641981027621608</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.85370004653931</v>
+        <v>29.85310005187988</v>
       </c>
       <c r="Z52" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.1550882199485853</v>
+        <v>-0.2448635656174351</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.300849840749737</v>
+        <v>0.3010128488841567</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15442,13 +15432,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>12.56</v>
+        <v>12.51</v>
       </c>
       <c r="CA52" t="n">
         <v>0.29</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15502,10 +15492,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10.05000019073486</v>
+        <v>9.970000267028809</v>
       </c>
       <c r="D53" t="n">
-        <v>10.05000019073486</v>
+        <v>9.970000267028809</v>
       </c>
       <c r="E53" t="n">
         <v>10.5600004196167</v>
@@ -15517,67 +15507,67 @@
         <v>10.55000019073486</v>
       </c>
       <c r="H53" t="n">
-        <v>6594900</v>
+        <v>10713200</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.03365379236858779</v>
+        <v>-0.04134609300709113</v>
       </c>
       <c r="J53" t="n">
-        <v>10.07888878716363</v>
+        <v>10.06999990675184</v>
       </c>
       <c r="K53" t="n">
         <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.286624815878082</v>
+        <v>-0.9930450908543402</v>
       </c>
       <c r="M53" t="n">
-        <v>10.04999990463257</v>
+        <v>10.04199991226196</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O53" t="n">
-        <v>2.846789038281864e-06</v>
+        <v>-0.7169851211135493</v>
       </c>
       <c r="P53" t="n">
-        <v>10.17076917795035</v>
+        <v>10.1676922578078</v>
       </c>
       <c r="Q53" t="n">
         <v>-1</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.187412526058531</v>
+        <v>-1.944315246433499</v>
       </c>
       <c r="S53" t="n">
-        <v>10.04219995498657</v>
+        <v>10.04059995651245</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U53" t="n">
-        <v>0.07767457114233506</v>
+        <v>-0.7031421408025658</v>
       </c>
       <c r="V53" t="n">
-        <v>8.912533286412557</v>
+        <v>8.91199995358785</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>12.76255434643269</v>
+        <v>11.871637331136</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.904849956035614</v>
+        <v>8.904449956417084</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>12.85984873808097</v>
+        <v>11.96649221262482</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3279781158991983</v>
+        <v>0.3353736520913747</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15729,13 +15719,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>-5.95</v>
+        <v>-5.9</v>
       </c>
       <c r="CA53" t="n">
         <v>0.29</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="CC53" t="n">
         <v>3</v>
@@ -15770,13 +15760,13 @@
         <v>9</v>
       </c>
       <c r="CM53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -15789,10 +15779,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>48.11999893188477</v>
+        <v>48.09999847412109</v>
       </c>
       <c r="D54" t="n">
-        <v>48.11999893188477</v>
+        <v>48.09999847412109</v>
       </c>
       <c r="E54" t="n">
         <v>48.54000091552734</v>
@@ -15804,67 +15794,67 @@
         <v>47.63000106811523</v>
       </c>
       <c r="H54" t="n">
-        <v>7618200</v>
+        <v>10614200</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.01574965161334618</v>
+        <v>-0.01615874259336991</v>
       </c>
       <c r="J54" t="n">
-        <v>49.97111087375217</v>
+        <v>49.96888860066732</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.704364200636005</v>
+        <v>-3.740107452622566</v>
       </c>
       <c r="M54" t="n">
-        <v>49.91199989318848</v>
+        <v>49.90999984741211</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-3.590320895052473</v>
+        <v>-3.626530512571954</v>
       </c>
       <c r="P54" t="n">
-        <v>51.2688463651217</v>
+        <v>51.26807711674617</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-6.141833991761317</v>
+        <v>-6.179437226426144</v>
       </c>
       <c r="S54" t="n">
-        <v>51.84220008850097</v>
+        <v>51.8418000793457</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-7.179867270798608</v>
+        <v>-7.217730864857412</v>
       </c>
       <c r="V54" t="n">
-        <v>41.40126675923666</v>
+        <v>41.40113342285157</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>16.22832511797277</v>
+        <v>16.18039048073997</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.40830006599426</v>
+        <v>39.40820006370544</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>22.10625388890575</v>
+        <v>22.05581172538938</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3649328984757468</v>
+        <v>0.3650476727722735</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16050,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM54" t="n">
         <v>2</v>
@@ -16059,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="CO54" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -16072,10 +16062,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>42.81000137329102</v>
+        <v>42.81999969482422</v>
       </c>
       <c r="D55" t="n">
-        <v>42.81000137329102</v>
+        <v>42.81999969482422</v>
       </c>
       <c r="E55" t="n">
         <v>43.18999862670898</v>
@@ -16087,67 +16077,67 @@
         <v>42.25</v>
       </c>
       <c r="H55" t="n">
-        <v>36330500</v>
+        <v>53706300</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.01450269966239404</v>
+        <v>-0.01427253571558729</v>
       </c>
       <c r="J55" t="n">
-        <v>44.63111114501953</v>
+        <v>44.63222206963433</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.080359473487446</v>
+        <v>-4.060345397956476</v>
       </c>
       <c r="M55" t="n">
-        <v>44.66800003051758</v>
+        <v>44.6689998626709</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-4.159574317088651</v>
+        <v>-4.139336393317952</v>
       </c>
       <c r="P55" t="n">
-        <v>46.27192306518555</v>
+        <v>46.27230761601375</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-7.481689678247328</v>
+        <v>-7.460850990700899</v>
       </c>
       <c r="S55" t="n">
-        <v>46.94379989624024</v>
+        <v>46.9439998626709</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-8.805845568714387</v>
+        <v>-8.784935625236354</v>
       </c>
       <c r="V55" t="n">
-        <v>38.26600011189779</v>
+        <v>38.26606676737467</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>11.87477459913661</v>
+        <v>11.90070815256139</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.44125005722046</v>
+        <v>36.44130004882813</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>17.47676412326765</v>
+        <v>17.50403975008904</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.3227610763141934</v>
+        <v>0.3227017250435755</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16337,16 +16327,16 @@
         <v>0</v>
       </c>
       <c r="CL55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN55" t="n">
         <v>0</v>
       </c>
       <c r="CO55" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -16359,10 +16349,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.230000019073486</v>
+        <v>6.21999979019165</v>
       </c>
       <c r="D56" t="n">
-        <v>6.230000019073486</v>
+        <v>6.21999979019165</v>
       </c>
       <c r="E56" t="n">
         <v>6.340000152587891</v>
@@ -16374,67 +16364,67 @@
         <v>6.21999979019165</v>
       </c>
       <c r="H56" t="n">
-        <v>3441000</v>
+        <v>5262300</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0113636645122297</v>
+        <v>0.00974025069249751</v>
       </c>
       <c r="J56" t="n">
-        <v>6.037777741750081</v>
+        <v>6.036666605207655</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>3.183659378420389</v>
+        <v>3.036993708180592</v>
       </c>
       <c r="M56" t="n">
-        <v>6.044999980926514</v>
+        <v>6.04399995803833</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>3.060381120441583</v>
+        <v>2.911976065109766</v>
       </c>
       <c r="P56" t="n">
-        <v>6.301538467407227</v>
+        <v>6.301153843219463</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.135253695645133</v>
+        <v>-1.287923689010404</v>
       </c>
       <c r="S56" t="n">
-        <v>6.301400003433227</v>
+        <v>6.301199998855591</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-1.133081288615856</v>
+        <v>-1.288646744726206</v>
       </c>
       <c r="V56" t="n">
-        <v>6.372484712600708</v>
+        <v>6.372418044408162</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-2.235936215672329</v>
+        <v>-2.391843302720225</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.848999791145324</v>
+        <v>6.848949790000916</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-9.037812687220507</v>
+        <v>-9.183159741183927</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3403194703316538</v>
+        <v>0.3397913930933846</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16586,13 +16576,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="CA56" t="n">
         <v>0.2</v>
       </c>
       <c r="CB56" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CC56" t="n">
         <v>9</v>
@@ -16646,10 +16636,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.81000137329102</v>
+        <v>62.97999954223633</v>
       </c>
       <c r="D57" t="n">
-        <v>62.81000137329102</v>
+        <v>62.97999954223633</v>
       </c>
       <c r="E57" t="n">
         <v>64.15000152587891</v>
@@ -16661,67 +16651,67 @@
         <v>63.15999984741211</v>
       </c>
       <c r="H57" t="n">
-        <v>6262200</v>
+        <v>9292500</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0299613687522623</v>
+        <v>-0.02733591440561656</v>
       </c>
       <c r="J57" t="n">
-        <v>67.09333335028754</v>
+        <v>67.11222203572591</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.384139471255179</v>
+        <v>-6.157183249408535</v>
       </c>
       <c r="M57" t="n">
-        <v>67.11300010681153</v>
+        <v>67.12999992370605</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-6.411572611375162</v>
+        <v>-6.182035433019876</v>
       </c>
       <c r="P57" t="n">
-        <v>65.76653876671425</v>
+        <v>65.77307715782753</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.495504019012773</v>
+        <v>-4.246536328061705</v>
       </c>
       <c r="S57" t="n">
-        <v>65.92239990234376</v>
+        <v>65.92579986572265</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-4.721306465880172</v>
+        <v>-4.468357349453956</v>
       </c>
       <c r="V57" t="n">
-        <v>51.49799990336101</v>
+        <v>51.4991332244873</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>21.96590448397538</v>
+        <v>22.29331951608458</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.10969997406006</v>
+        <v>48.11054996490478</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>30.55579520794583</v>
+        <v>30.90683766487468</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3985977820828747</v>
+        <v>0.3970523775281813</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16873,7 +16863,7 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>21.15</v>
+        <v>21.21</v>
       </c>
       <c r="CA57" t="n">
         <v>0.44</v>
@@ -16929,10 +16919,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.47999954223633</v>
+        <v>48.54000091552734</v>
       </c>
       <c r="D58" t="n">
-        <v>48.47999954223633</v>
+        <v>48.54000091552734</v>
       </c>
       <c r="E58" t="n">
         <v>49.4900016784668</v>
@@ -16944,67 +16934,67 @@
         <v>49.4900016784668</v>
       </c>
       <c r="H58" t="n">
-        <v>768200</v>
+        <v>1039100</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.00838617002517128</v>
+        <v>-0.00715889708509998</v>
       </c>
       <c r="J58" t="n">
-        <v>48.7466663784451</v>
+        <v>48.75333319769965</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.5470463028969008</v>
+        <v>-0.4375747629546189</v>
       </c>
       <c r="M58" t="n">
-        <v>48.74199981689453</v>
+        <v>48.74799995422363</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.5375246720332424</v>
+        <v>-0.4266822000730406</v>
       </c>
       <c r="P58" t="n">
-        <v>50.04961571326623</v>
+        <v>50.05192345839281</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-3.136120325123405</v>
+        <v>-3.02070817342773</v>
       </c>
       <c r="S58" t="n">
-        <v>50.2418000793457</v>
+        <v>50.24300010681152</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.50664294337982</v>
+        <v>-3.389525282454819</v>
       </c>
       <c r="V58" t="n">
-        <v>49.23040003458659</v>
+        <v>49.23080004374186</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-1.524262430983841</v>
+        <v>-1.403184850948462</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.54704999923706</v>
+        <v>49.54735000610351</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.153610471293777</v>
+        <v>-2.033103870241455</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.3032514827688724</v>
+        <v>0.3030890660053491</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17156,7 +17146,7 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>8.51</v>
+        <v>8.52</v>
       </c>
       <c r="CA58" t="n">
         <v>-0.42</v>
@@ -17216,13 +17206,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18.35000038146973</v>
+        <v>18.5</v>
       </c>
       <c r="D59" t="n">
-        <v>18.35000038146973</v>
+        <v>18.5</v>
       </c>
       <c r="E59" t="n">
-        <v>18.55999946594238</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="F59" t="n">
         <v>18.03000068664551</v>
@@ -17231,67 +17221,67 @@
         <v>18.29999923706055</v>
       </c>
       <c r="H59" t="n">
-        <v>8070700</v>
+        <v>14427800</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01887840912087535</v>
+        <v>0.02720709410832622</v>
       </c>
       <c r="J59" t="n">
-        <v>18.6722223493788</v>
+        <v>18.68888897365994</v>
       </c>
       <c r="K59" t="n">
         <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.72567550814214</v>
+        <v>-1.010701994785021</v>
       </c>
       <c r="M59" t="n">
-        <v>18.76900005340576</v>
+        <v>18.78400001525879</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-2.232402742521197</v>
+        <v>-1.511925122594171</v>
       </c>
       <c r="P59" t="n">
-        <v>20.54346157954289</v>
+        <v>20.54923079564021</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-10.67717429012746</v>
+        <v>-9.972299284676797</v>
       </c>
       <c r="S59" t="n">
-        <v>21.85700004577637</v>
+        <v>21.86000003814697</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-16.04520134035655</v>
+        <v>-15.37053994640245</v>
       </c>
       <c r="V59" t="n">
-        <v>22.86761819203695</v>
+        <v>22.86861818949382</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-19.75552404552724</v>
+        <v>-19.10311394109866</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.55997826576233</v>
+        <v>21.56072826385498</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-14.88859517725076</v>
+        <v>-14.19584824036798</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3430337533183794</v>
+        <v>0.349602631572311</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17443,13 +17433,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="CA59" t="n">
         <v>0.1</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17484,13 +17474,13 @@
         <v>1</v>
       </c>
       <c r="CM59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
@@ -17503,10 +17493,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14.10000038146973</v>
+        <v>14.05000019073486</v>
       </c>
       <c r="D60" t="n">
-        <v>14.10000038146973</v>
+        <v>14.05000019073486</v>
       </c>
       <c r="E60" t="n">
         <v>14.44999980926514</v>
@@ -17518,67 +17508,67 @@
         <v>14.44999980926514</v>
       </c>
       <c r="H60" t="n">
-        <v>4488500</v>
+        <v>8620500</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01052628901966834</v>
+        <v>-0.01403507433439555</v>
       </c>
       <c r="J60" t="n">
-        <v>14.56555557250977</v>
+        <v>14.55999999576145</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.196274860388453</v>
+        <v>-3.502745914663807</v>
       </c>
       <c r="M60" t="n">
-        <v>14.63600006103516</v>
+        <v>14.63100004196167</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-3.662200583015852</v>
+        <v>-3.971019407836105</v>
       </c>
       <c r="P60" t="n">
-        <v>15.49423085726225</v>
+        <v>15.49230777300321</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-8.998384551234654</v>
+        <v>-9.309830422951601</v>
       </c>
       <c r="S60" t="n">
-        <v>15.88140007019043</v>
+        <v>15.88040006637573</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-11.21689322633721</v>
+        <v>-11.52615720000944</v>
       </c>
       <c r="V60" t="n">
-        <v>15.63453337987264</v>
+        <v>15.63420004526774</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-9.81502268803505</v>
+        <v>-10.13291278060878</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.5278000164032</v>
+        <v>15.52755001544952</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-9.195118648006659</v>
+        <v>-9.515666175568816</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3425285263585565</v>
+        <v>0.3432174744656972</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17730,13 +17720,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>25.18</v>
+        <v>25.09</v>
       </c>
       <c r="CA60" t="n">
         <v>0.67</v>
       </c>
       <c r="CB60" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CC60" t="n">
         <v>8</v>
@@ -17790,82 +17780,82 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34.43000030517578</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="D61" t="n">
-        <v>34.43000030517578</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="E61" t="n">
         <v>35.65000152587891</v>
       </c>
       <c r="F61" t="n">
-        <v>34.41999816894531</v>
+        <v>34.31000137329102</v>
       </c>
       <c r="G61" t="n">
         <v>35.43000030517578</v>
       </c>
       <c r="H61" t="n">
-        <v>3467100</v>
+        <v>6529900</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.01628570556640629</v>
+        <v>-0.01714281354631697</v>
       </c>
       <c r="J61" t="n">
-        <v>34.58888880411784</v>
+        <v>34.58555560641818</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.4593628313469819</v>
+        <v>-0.536507444468645</v>
       </c>
       <c r="M61" t="n">
-        <v>34.60499992370605</v>
+        <v>34.60200004577636</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.5057061664964462</v>
+        <v>-0.583777006040767</v>
       </c>
       <c r="P61" t="n">
-        <v>36.67038462712215</v>
+        <v>36.66923082791842</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-6.109519561159258</v>
+        <v>-6.188374424019324</v>
       </c>
       <c r="S61" t="n">
-        <v>37.88679985046387</v>
+        <v>37.88619987487793</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-9.124020922674369</v>
+        <v>-9.201763070755213</v>
       </c>
       <c r="V61" t="n">
-        <v>41.15326657613119</v>
+        <v>41.1530665842692</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-16.33713877492021</v>
+        <v>-16.40962780880991</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.72439996719361</v>
+        <v>40.72424997329712</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-15.45608938888826</v>
+        <v>-15.52944118446631</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.4072586852104623</v>
+        <v>0.4074539888588921</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -18013,7 +18003,7 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>17.04</v>
+        <v>17.03</v>
       </c>
       <c r="CA61" t="n">
         <v>0.09</v>
@@ -18073,10 +18063,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11.85000038146973</v>
+        <v>11.8100004196167</v>
       </c>
       <c r="D62" t="n">
-        <v>11.85000038146973</v>
+        <v>11.8100004196167</v>
       </c>
       <c r="E62" t="n">
         <v>12.02000045776367</v>
@@ -18088,67 +18078,67 @@
         <v>11.89999961853027</v>
       </c>
       <c r="H62" t="n">
-        <v>1027600</v>
+        <v>1573900</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.004201616694398003</v>
+        <v>-0.007562958134337272</v>
       </c>
       <c r="J62" t="n">
-        <v>12.14444446563721</v>
+        <v>12.14000002543131</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-2.424516699801396</v>
+        <v>-2.718283402992752</v>
       </c>
       <c r="M62" t="n">
-        <v>12.13299999237061</v>
+        <v>12.1289999961853</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-2.332478456101809</v>
+        <v>-2.630056696091458</v>
       </c>
       <c r="P62" t="n">
-        <v>12.54615391217745</v>
+        <v>12.54461545210618</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-5.548740558905709</v>
+        <v>-5.856018746004243</v>
       </c>
       <c r="S62" t="n">
-        <v>13.04300008773804</v>
+        <v>13.04220008850098</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-9.14666639763248</v>
+        <v>-9.447789947423678</v>
       </c>
       <c r="V62" t="n">
-        <v>11.95866667429606</v>
+        <v>11.95840000788371</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.9086823454984514</v>
+        <v>-1.240965247601467</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.16615000724792</v>
+        <v>12.16595000743866</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.598600424866155</v>
+        <v>-2.925785389585865</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3494670036239227</v>
+        <v>0.3495403267864516</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18300,7 +18290,7 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6.51</v>
+        <v>6.49</v>
       </c>
       <c r="CA62" t="n">
         <v>0.44</v>
@@ -18356,82 +18346,82 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>43.0099983215332</v>
+        <v>42.81999969482422</v>
       </c>
       <c r="D63" t="n">
-        <v>43.0099983215332</v>
+        <v>42.81999969482422</v>
       </c>
       <c r="E63" t="n">
         <v>44.88999938964844</v>
       </c>
       <c r="F63" t="n">
-        <v>42.77999877929688</v>
+        <v>42.72000122070312</v>
       </c>
       <c r="G63" t="n">
         <v>44.7400016784668</v>
       </c>
       <c r="H63" t="n">
-        <v>3368800</v>
+        <v>5486500</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.01578952927596788</v>
+        <v>-0.02013732386159439</v>
       </c>
       <c r="J63" t="n">
-        <v>43.50111134847005</v>
+        <v>43.48000038994683</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-1.128966621111679</v>
+        <v>-1.517940867533233</v>
       </c>
       <c r="M63" t="n">
-        <v>43.54500007629395</v>
+        <v>43.52600021362305</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-1.228618105002597</v>
+        <v>-1.622020207080416</v>
       </c>
       <c r="P63" t="n">
-        <v>45.93615414546086</v>
+        <v>45.92884650597205</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-6.370049644691041</v>
+        <v>-6.768832765577068</v>
       </c>
       <c r="S63" t="n">
-        <v>46.63480010986328</v>
+        <v>46.6310001373291</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-7.772740056332799</v>
+        <v>-8.17267575493003</v>
       </c>
       <c r="V63" t="n">
-        <v>45.51873339335123</v>
+        <v>45.51746673583985</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-5.511434270674308</v>
+        <v>-5.926224006863893</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.380950050354</v>
+        <v>43.38000005722046</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-0.855102823682332</v>
+        <v>-1.29091830718665</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.5169112979880497</v>
+        <v>0.5179475823039709</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18579,13 +18569,13 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>21.5</v>
+        <v>21.41</v>
       </c>
       <c r="CA63" t="n">
         <v>0.67</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CC63" t="n">
         <v>10</v>
@@ -18616,13 +18606,13 @@
         <v>4</v>
       </c>
       <c r="CM63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN63" t="n">
         <v>-1</v>
       </c>
       <c r="CO63" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -18635,10 +18625,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.47999954223633</v>
+        <v>27.46999931335449</v>
       </c>
       <c r="D64" t="n">
-        <v>27.47999954223633</v>
+        <v>27.46999931335449</v>
       </c>
       <c r="E64" t="n">
         <v>27.77000045776367</v>
@@ -18650,67 +18640,67 @@
         <v>27.70999908447266</v>
       </c>
       <c r="H64" t="n">
-        <v>2189300</v>
+        <v>3114100</v>
       </c>
       <c r="I64" t="n">
-        <v>0.005856509853564118</v>
+        <v>0.005490469260828412</v>
       </c>
       <c r="J64" t="n">
-        <v>27.23333337571886</v>
+        <v>27.23222223917643</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.9057509160351186</v>
+        <v>0.8731460550288519</v>
       </c>
       <c r="M64" t="n">
-        <v>27.22399997711182</v>
+        <v>27.22299995422363</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.9403451562582268</v>
+        <v>0.9073186626977127</v>
       </c>
       <c r="P64" t="n">
-        <v>28.32269235757681</v>
+        <v>28.32230773338905</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.975327361895544</v>
+        <v>-3.009318407446618</v>
       </c>
       <c r="S64" t="n">
-        <v>29.47499996185303</v>
+        <v>29.47479995727539</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-6.768449269545908</v>
+        <v>-6.801744699970541</v>
       </c>
       <c r="V64" t="n">
-        <v>31.9745333480835</v>
+        <v>31.97446667989095</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-14.05660485148742</v>
+        <v>-14.08770132628784</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.00615001678467</v>
+        <v>31.00610001564026</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-11.37242280205546</v>
+        <v>-11.40453233557934</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2529461232747711</v>
+        <v>0.2528121676196875</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18940,82 +18930,82 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28.75</v>
+        <v>28.55999946594238</v>
       </c>
       <c r="D65" t="n">
-        <v>28.75</v>
+        <v>28.55999946594238</v>
       </c>
       <c r="E65" t="n">
         <v>29.18000030517578</v>
       </c>
       <c r="F65" t="n">
-        <v>28.64999961853027</v>
+        <v>28.52000045776367</v>
       </c>
       <c r="G65" t="n">
         <v>29.1299991607666</v>
       </c>
       <c r="H65" t="n">
-        <v>5651600</v>
+        <v>11752700</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0006951844784651717</v>
+        <v>-0.007299304431002129</v>
       </c>
       <c r="J65" t="n">
-        <v>28.84222242567274</v>
+        <v>28.8211112552219</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.319747987210086</v>
+        <v>-0.9059740513378202</v>
       </c>
       <c r="M65" t="n">
-        <v>28.91000022888183</v>
+        <v>28.89100017547607</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-0.553442502992408</v>
+        <v>-1.145687956537613</v>
       </c>
       <c r="P65" t="n">
-        <v>31.23600028111385</v>
+        <v>31.22869256826548</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-7.958766355297259</v>
+        <v>-8.545644671128541</v>
       </c>
       <c r="S65" t="n">
-        <v>31.40117370605469</v>
+        <v>31.39737369537353</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-8.442912774128237</v>
+        <v>-9.036979516058201</v>
       </c>
       <c r="V65" t="n">
-        <v>28.7192820485433</v>
+        <v>28.71801537831624</v>
       </c>
       <c r="W65" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>0.1069593292923655</v>
+        <v>-0.5502327033823168</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.52119619369507</v>
+        <v>27.52024619102478</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.464936035688894</v>
+        <v>3.778139438507992</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2719032238632966</v>
+        <v>0.2716395135099759</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19167,13 +19157,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>11.59</v>
+        <v>11.52</v>
       </c>
       <c r="CA65" t="n">
         <v>0.32</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CC65" t="n">
         <v>9</v>
@@ -19205,16 +19195,16 @@
         <v>0</v>
       </c>
       <c r="CL65" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM65" t="n">
         <v>4</v>
       </c>
-      <c r="CM65" t="n">
-        <v>5</v>
-      </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
@@ -19227,82 +19217,82 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15.98999977111816</v>
+        <v>15.89000034332275</v>
       </c>
       <c r="D66" t="n">
-        <v>15.98999977111816</v>
+        <v>15.89000034332275</v>
       </c>
       <c r="E66" t="n">
         <v>16.21999931335449</v>
       </c>
       <c r="F66" t="n">
-        <v>15.96000003814697</v>
+        <v>15.89000034332275</v>
       </c>
       <c r="G66" t="n">
         <v>16.20000076293945</v>
       </c>
       <c r="H66" t="n">
-        <v>1229600</v>
+        <v>1781900</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.00867944184330538</v>
+        <v>-0.01487903471362872</v>
       </c>
       <c r="J66" t="n">
-        <v>16.52111117045085</v>
+        <v>16.51000012291802</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-3.214743813858072</v>
+        <v>-3.755298455356328</v>
       </c>
       <c r="M66" t="n">
-        <v>16.60300006866455</v>
+        <v>16.59300012588501</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.692105613510917</v>
+        <v>-4.236724987819282</v>
       </c>
       <c r="P66" t="n">
-        <v>17.07615397526668</v>
+        <v>17.07230784342839</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-6.360648924352132</v>
+        <v>-6.925293937695365</v>
       </c>
       <c r="S66" t="n">
-        <v>17.70679996490479</v>
+        <v>17.70479997634888</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-9.695711236301038</v>
+        <v>-10.25032553573291</v>
       </c>
       <c r="V66" t="n">
-        <v>16.0173775990804</v>
+        <v>16.01671093622844</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-0.1709257822816911</v>
+        <v>-0.7911149387048781</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.73974419116974</v>
+        <v>15.73924419403076</v>
       </c>
       <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.589959639171405</v>
+        <v>0.9578360144457702</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.2306441753438772</v>
+        <v>0.2320118482996528</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19456,13 +19446,13 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>24.6</v>
+        <v>24.45</v>
       </c>
       <c r="CA66" t="n">
         <v>0.8</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CC66" t="n">
         <v>3</v>
@@ -19494,16 +19484,16 @@
         <v>0</v>
       </c>
       <c r="CL66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN66" t="n">
         <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67">
@@ -19516,82 +19506,82 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.72999954223633</v>
+        <v>18.63999938964844</v>
       </c>
       <c r="D67" t="n">
-        <v>18.72999954223633</v>
+        <v>18.63999938964844</v>
       </c>
       <c r="E67" t="n">
         <v>19.43000030517578</v>
       </c>
       <c r="F67" t="n">
-        <v>18.6200008392334</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="G67" t="n">
         <v>19.32999992370605</v>
       </c>
       <c r="H67" t="n">
-        <v>2207600</v>
+        <v>3745800</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.01731374254735518</v>
+        <v>-0.0220356814303394</v>
       </c>
       <c r="J67" t="n">
-        <v>19.00333319769965</v>
+        <v>18.99333318074544</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-1.438345855538714</v>
+        <v>-1.860304285375236</v>
       </c>
       <c r="M67" t="n">
-        <v>18.98399982452393</v>
+        <v>18.97499980926514</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-1.337970315188669</v>
+        <v>-1.765483125080842</v>
       </c>
       <c r="P67" t="n">
-        <v>18.59384610102727</v>
+        <v>18.59038455669696</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>0.7322500168565901</v>
+        <v>0.2668843820855767</v>
       </c>
       <c r="S67" t="n">
-        <v>18.70399993896485</v>
+        <v>18.70219993591309</v>
       </c>
       <c r="T67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1390055782523811</v>
+        <v>-0.332584115653727</v>
       </c>
       <c r="V67" t="n">
-        <v>21.58665456136068</v>
+        <v>21.58605456034342</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-13.23343091910897</v>
+        <v>-13.64795573206462</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.37254093170166</v>
+        <v>22.37209093093872</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-16.28130394569482</v>
+        <v>-16.68190761789331</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5169101188107154</v>
+        <v>0.518485756344496</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19741,13 +19731,13 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.72</v>
+        <v>16.64</v>
       </c>
       <c r="CA67" t="n">
         <v>0.36</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CC67" t="n">
         <v>10</v>
@@ -19782,13 +19772,13 @@
         <v>9</v>
       </c>
       <c r="CM67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN67" t="n">
         <v>-1</v>
       </c>
       <c r="CO67" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68">
@@ -19801,82 +19791,82 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>42.11999893188477</v>
+        <v>42.09000015258789</v>
       </c>
       <c r="D68" t="n">
-        <v>42.11999893188477</v>
+        <v>42.09000015258789</v>
       </c>
       <c r="E68" t="n">
         <v>42.86000061035156</v>
       </c>
       <c r="F68" t="n">
-        <v>41.95000076293945</v>
+        <v>41.93999862670898</v>
       </c>
       <c r="G68" t="n">
         <v>42.18000030517578</v>
       </c>
       <c r="H68" t="n">
-        <v>4511200</v>
+        <v>7293800</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01055658885526323</v>
+        <v>0.009836848474331639</v>
       </c>
       <c r="J68" t="n">
-        <v>41.78777779473199</v>
+        <v>41.78444459703233</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.7950198710845551</v>
+        <v>0.7312662846241558</v>
       </c>
       <c r="M68" t="n">
-        <v>41.87099990844727</v>
+        <v>41.86800003051758</v>
       </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5946813402640148</v>
+        <v>0.5302381816864828</v>
       </c>
       <c r="P68" t="n">
-        <v>43.43846145043006</v>
+        <v>43.43730765122633</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.035242212825294</v>
+        <v>-3.101728839771693</v>
       </c>
       <c r="S68" t="n">
-        <v>46.5615998840332</v>
+        <v>46.56099990844726</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-9.539193161770067</v>
+        <v>-9.602456486438619</v>
       </c>
       <c r="V68" t="n">
-        <v>49.63593327840169</v>
+        <v>49.63573328653971</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-15.14212355867472</v>
+        <v>-15.20221951873144</v>
       </c>
       <c r="Y68" t="n">
-        <v>50.03834997177124</v>
+        <v>50.03819997787475</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-15.82456464762238</v>
+        <v>-15.88426407984559</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2145854400605174</v>
+        <v>0.2141674270170043</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20031,7 +20021,7 @@
         <v>4.68</v>
       </c>
       <c r="CA68" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CB68" t="n">
         <v>1.11</v>
@@ -20069,13 +20059,13 @@
         <v>3</v>
       </c>
       <c r="CM68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN68" t="n">
         <v>1</v>
       </c>
       <c r="CO68" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69">
@@ -20088,10 +20078,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39.13000106811523</v>
+        <v>39.36999893188477</v>
       </c>
       <c r="D69" t="n">
-        <v>39.13000106811523</v>
+        <v>39.36999893188477</v>
       </c>
       <c r="E69" t="n">
         <v>39.56000137329102</v>
@@ -20103,67 +20093,67 @@
         <v>39.20999908447266</v>
       </c>
       <c r="H69" t="n">
-        <v>623300</v>
+        <v>2323500</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0033333607209034</v>
+        <v>0.009487152099609375</v>
       </c>
       <c r="J69" t="n">
-        <v>38.6933330959744</v>
+        <v>38.71999952528212</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.128535427686557</v>
+        <v>1.678717496311514</v>
       </c>
       <c r="M69" t="n">
-        <v>38.68499984741211</v>
+        <v>38.70899963378906</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1.150319820236203</v>
+        <v>1.707611419435178</v>
       </c>
       <c r="P69" t="n">
-        <v>40.9723077920767</v>
+        <v>40.98153847914476</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-4.496468037169565</v>
+        <v>-3.932354926304429</v>
       </c>
       <c r="S69" t="n">
-        <v>42.01560020446777</v>
+        <v>42.02040016174316</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-6.867923157850535</v>
+        <v>-6.307415492609739</v>
       </c>
       <c r="V69" t="n">
-        <v>41.74413347880046</v>
+        <v>41.74573346455892</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-6.262274942209056</v>
+        <v>-5.690963687800792</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.0622501373291</v>
+        <v>40.06345012664795</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-2.327001269320164</v>
+        <v>-1.730882369269391</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2525221527267005</v>
+        <v>0.2548304774558118</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20315,13 +20305,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CC69" t="n">
         <v>6</v>
@@ -20352,13 +20342,13 @@
         <v>5</v>
       </c>
       <c r="CM69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN69" t="n">
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
@@ -20371,10 +20361,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.53000068664551</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="D70" t="n">
-        <v>22.53000068664551</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="E70" t="n">
         <v>22.85000038146973</v>
@@ -20386,67 +20376,67 @@
         <v>22.85000038146973</v>
       </c>
       <c r="H70" t="n">
-        <v>1250700</v>
+        <v>2627400</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0008868537069469662</v>
+        <v>0.002217345725094466</v>
       </c>
       <c r="J70" t="n">
-        <v>22.43222215440538</v>
+        <v>22.43999989827474</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4358842898715011</v>
+        <v>0.7130146342259545</v>
       </c>
       <c r="M70" t="n">
-        <v>22.44899997711182</v>
+        <v>22.45599994659424</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.3608210148170313</v>
+        <v>0.6412559459296155</v>
       </c>
       <c r="P70" t="n">
-        <v>23.91423078683706</v>
+        <v>23.91692308279184</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-5.788311204864121</v>
+        <v>-5.506237975359125</v>
       </c>
       <c r="S70" t="n">
-        <v>25.39179996490478</v>
+        <v>25.39319995880127</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-11.27056483673747</v>
+        <v>-10.99979357411952</v>
       </c>
       <c r="V70" t="n">
-        <v>24.86106667836507</v>
+        <v>24.86153334299723</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-9.376371584844884</v>
+        <v>-9.096514403704367</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.33645000457764</v>
+        <v>24.33680000305176</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-7.422813588639008</v>
+        <v>-7.136515981411856</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3788454616284155</v>
+        <v>0.3793126990294426</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20598,7 +20588,7 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2253</v>
+        <v>2260</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
@@ -20639,13 +20629,13 @@
         <v>2</v>
       </c>
       <c r="CM70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
@@ -20658,10 +20648,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>31</v>
+        <v>31.07999992370605</v>
       </c>
       <c r="D71" t="n">
-        <v>31</v>
+        <v>31.07999992370605</v>
       </c>
       <c r="E71" t="n">
         <v>31.84000015258789</v>
@@ -20673,67 +20663,67 @@
         <v>31.69000053405762</v>
       </c>
       <c r="H71" t="n">
-        <v>5462200</v>
+        <v>9812600</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.01524776204625788</v>
+        <v>-0.01270646837188161</v>
       </c>
       <c r="J71" t="n">
-        <v>31.49777730305989</v>
+        <v>31.50666618347168</v>
       </c>
       <c r="K71" t="n">
         <v>-1</v>
       </c>
       <c r="L71" t="n">
-        <v>-1.580356919380268</v>
+        <v>-1.354209478340343</v>
       </c>
       <c r="M71" t="n">
-        <v>31.50799961090088</v>
+        <v>31.51599960327149</v>
       </c>
       <c r="N71" t="n">
         <v>-1</v>
       </c>
       <c r="O71" t="n">
-        <v>-1.61228772747961</v>
+        <v>-1.383423293101488</v>
       </c>
       <c r="P71" t="n">
-        <v>32.40961522322435</v>
+        <v>32.41269214336689</v>
       </c>
       <c r="Q71" t="n">
         <v>-1</v>
       </c>
       <c r="R71" t="n">
-        <v>-4.349373522380593</v>
+        <v>-4.111636928417143</v>
       </c>
       <c r="S71" t="n">
-        <v>33.51499988555909</v>
+        <v>33.51659988403321</v>
       </c>
       <c r="T71" t="n">
         <v>-1</v>
       </c>
       <c r="U71" t="n">
-        <v>-7.504102324770547</v>
+        <v>-7.2698303788503</v>
       </c>
       <c r="V71" t="n">
-        <v>39.51866662343343</v>
+        <v>39.51919995625814</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-21.55605781087287</v>
+        <v>-21.35468339919083</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.4556999874115</v>
+        <v>40.45609998703003</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-23.37297337669057</v>
+        <v>-23.17598598562366</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4523225331871994</v>
+        <v>0.4517922926476912</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20881,13 +20871,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>20.13</v>
+        <v>20.18</v>
       </c>
       <c r="CA71" t="n">
         <v>0.18</v>
       </c>
       <c r="CB71" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20922,13 +20912,13 @@
         <v>4</v>
       </c>
       <c r="CM71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN71" t="n">
         <v>0</v>
       </c>
       <c r="CO71" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72">
@@ -20941,10 +20931,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27.54000091552734</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="D72" t="n">
-        <v>27.54000091552734</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="E72" t="n">
         <v>28.03000068664551</v>
@@ -20956,67 +20946,67 @@
         <v>25.48999977111816</v>
       </c>
       <c r="H72" t="n">
-        <v>4620900</v>
+        <v>6790800</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.01184068581876407</v>
+        <v>-0.01399358755842073</v>
       </c>
       <c r="J72" t="n">
-        <v>28.61111153496636</v>
+        <v>28.60444471571181</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-3.743687546462453</v>
+        <v>-3.931015562968945</v>
       </c>
       <c r="M72" t="n">
-        <v>28.70500030517578</v>
+        <v>28.69900016784668</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-4.058524219692748</v>
+        <v>-4.247536912369778</v>
       </c>
       <c r="P72" t="n">
-        <v>29.22384643554688</v>
+        <v>29.2215386904203</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-5.761888749768955</v>
+        <v>-5.959779074723731</v>
       </c>
       <c r="S72" t="n">
-        <v>28.94760013580322</v>
+        <v>28.9464001083374</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-4.862576564801036</v>
+        <v>-5.065916869153997</v>
       </c>
       <c r="V72" t="n">
-        <v>25.11486666361491</v>
+        <v>25.11446665445964</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>9.65617012582369</v>
+        <v>9.419005071153434</v>
       </c>
       <c r="Y72" t="n">
-        <v>23.80210000991821</v>
+        <v>23.80180000305176</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>15.70408032926324</v>
+        <v>15.45345116215148</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2493201797559128</v>
+        <v>0.2500372926212344</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21168,13 +21158,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
       <c r="CA72" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21205,13 +21195,13 @@
         <v>7</v>
       </c>
       <c r="CM72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN72" t="n">
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73">
@@ -21224,13 +21214,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.23999977111816</v>
+        <v>10.22999954223633</v>
       </c>
       <c r="D73" t="n">
-        <v>10.23999977111816</v>
+        <v>10.22999954223633</v>
       </c>
       <c r="E73" t="n">
-        <v>10.25</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="F73" t="n">
         <v>9.659999847412109</v>
@@ -21239,67 +21229,67 @@
         <v>9.770000457763672</v>
       </c>
       <c r="H73" t="n">
-        <v>17442100</v>
+        <v>24343800</v>
       </c>
       <c r="I73" t="n">
-        <v>0.06004140091797572</v>
+        <v>0.05900618052048112</v>
       </c>
       <c r="J73" t="n">
-        <v>9.662222226460775</v>
+        <v>9.661111089918348</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>5.979758394244942</v>
+        <v>5.888437127191628</v>
       </c>
       <c r="M73" t="n">
-        <v>9.685000038146972</v>
+        <v>9.684000015258789</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>5.730508319929544</v>
+        <v>5.638161153626848</v>
       </c>
       <c r="P73" t="n">
-        <v>8.823461532592773</v>
+        <v>8.82307690840501</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>16.05422354132643</v>
+        <v>15.94594095049834</v>
       </c>
       <c r="S73" t="n">
-        <v>7.862199974060059</v>
+        <v>7.861999969482422</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>30.24344082957996</v>
+        <v>30.1195571348978</v>
       </c>
       <c r="V73" t="n">
-        <v>6.611599992116292</v>
+        <v>6.611533323923747</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>54.87929976599304</v>
+        <v>54.72960720350918</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.052099994421005</v>
+        <v>6.052049993276596</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>69.19746502135922</v>
+        <v>69.03362585572064</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.5465040612935747</v>
+        <v>0.5457404774759926</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21511,10 +21501,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>83.27999877929688</v>
+        <v>83.44999694824219</v>
       </c>
       <c r="D74" t="n">
-        <v>83.27999877929688</v>
+        <v>83.44999694824219</v>
       </c>
       <c r="E74" t="n">
         <v>83.94000244140625</v>
@@ -21526,67 +21516,67 @@
         <v>83.68000030517578</v>
       </c>
       <c r="H74" t="n">
-        <v>6569800</v>
+        <v>10604000</v>
       </c>
       <c r="I74" t="n">
-        <v>0.002527977431613593</v>
+        <v>0.004574422232020758</v>
       </c>
       <c r="J74" t="n">
-        <v>82.66888766818576</v>
+        <v>82.68777635362413</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>0.7392274510381418</v>
+        <v>0.9218056504002839</v>
       </c>
       <c r="M74" t="n">
-        <v>82.68899917602539</v>
+        <v>82.70599899291992</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.7147257908072941</v>
+        <v>0.8995695165787931</v>
       </c>
       <c r="P74" t="n">
-        <v>82.89769275371845</v>
+        <v>82.90423114483173</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0.4611781255652392</v>
+        <v>0.6583087447696381</v>
       </c>
       <c r="S74" t="n">
-        <v>82.55940032958985</v>
+        <v>82.56280029296875</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>0.8728242293794359</v>
+        <v>1.074571904205383</v>
       </c>
       <c r="V74" t="n">
-        <v>77.24513343811036</v>
+        <v>77.24626675923665</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>7.812615594769756</v>
+        <v>8.031106808490179</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.09110008239746</v>
+        <v>72.09195007324219</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>15.5204993183776</v>
+        <v>15.75494471083212</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3034032235541304</v>
+        <v>0.3036921636418719</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21734,13 +21724,13 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>23.73</v>
+        <v>23.77</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
       </c>
       <c r="CB74" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CC74" t="n">
         <v>1</v>
@@ -21799,13 +21789,13 @@
         <v>3.359999895095825</v>
       </c>
       <c r="F75" t="n">
-        <v>3.210000038146973</v>
+        <v>3.200000047683716</v>
       </c>
       <c r="G75" t="n">
         <v>3.319999933242798</v>
       </c>
       <c r="H75" t="n">
-        <v>9792000</v>
+        <v>12476300</v>
       </c>
       <c r="I75" t="n">
         <v>-0.003086416800562541</v>
@@ -21865,7 +21855,7 @@
         <v>-13.8010652889027</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.5221732934030845</v>
+        <v>0.5221732934030836</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -22073,10 +22063,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>30.93000030517578</v>
+        <v>31.02000045776367</v>
       </c>
       <c r="D76" t="n">
-        <v>30.93000030517578</v>
+        <v>31.02000045776367</v>
       </c>
       <c r="E76" t="n">
         <v>32.27999877929688</v>
@@ -22088,67 +22078,67 @@
         <v>32.20000076293945</v>
       </c>
       <c r="H76" t="n">
-        <v>3270700</v>
+        <v>6392800</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0294948386979782</v>
+        <v>-0.0266708615966943</v>
       </c>
       <c r="J76" t="n">
-        <v>32.62555503845215</v>
+        <v>32.63555505540636</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-5.197014215629446</v>
+        <v>-4.950289936542859</v>
       </c>
       <c r="M76" t="n">
-        <v>32.70199947357177</v>
+        <v>32.71099948883057</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-5.418626374292618</v>
+        <v>-5.169511960783405</v>
       </c>
       <c r="P76" t="n">
-        <v>32.92769204653226</v>
+        <v>32.93115359086256</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-6.066904836614164</v>
+        <v>-5.803480670137173</v>
       </c>
       <c r="S76" t="n">
-        <v>32.32039989471436</v>
+        <v>32.32219989776611</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-4.301925700387015</v>
+        <v>-4.028808200312006</v>
       </c>
       <c r="V76" t="n">
-        <v>28.38628061930338</v>
+        <v>28.38688062032064</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>8.961088351048721</v>
+        <v>9.275833694661486</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.72205769538879</v>
+        <v>26.72250769615173</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>15.74707553495447</v>
+        <v>16.08192169116977</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.274846519380866</v>
+        <v>0.2725631395350822</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22300,7 +22290,7 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>12.32</v>
+        <v>12.36</v>
       </c>
       <c r="CA76" t="n">
         <v>0.49</v>
@@ -22356,10 +22346,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>22.13999938964844</v>
+        <v>22.18000030517578</v>
       </c>
       <c r="D77" t="n">
-        <v>22.13999938964844</v>
+        <v>22.18000030517578</v>
       </c>
       <c r="E77" t="n">
         <v>22.72999954223633</v>
@@ -22371,67 +22361,67 @@
         <v>22.51000022888184</v>
       </c>
       <c r="H77" t="n">
-        <v>1403800</v>
+        <v>2058800</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.005837497325686614</v>
+        <v>-0.00404131794961482</v>
       </c>
       <c r="J77" t="n">
-        <v>22.48222223917643</v>
+        <v>22.48666678534614</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.522193161722488</v>
+        <v>-1.363770287067186</v>
       </c>
       <c r="M77" t="n">
-        <v>22.53400001525879</v>
+        <v>22.53800010681152</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-1.748471755318884</v>
+        <v>-1.588427544321229</v>
       </c>
       <c r="P77" t="n">
-        <v>24.50461541689359</v>
+        <v>24.50615391364465</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-9.649676140662784</v>
+        <v>-9.492120292175665</v>
       </c>
       <c r="S77" t="n">
-        <v>25.42300006866455</v>
+        <v>25.4238000869751</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-12.91350615642965</v>
+        <v>-12.75891003981405</v>
       </c>
       <c r="V77" t="n">
-        <v>29.15660002390544</v>
+        <v>29.15686669667562</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-24.06522238019557</v>
+        <v>-23.92872479776889</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.91765001296997</v>
+        <v>28.91785001754761</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-23.43776420380516</v>
+        <v>-23.29996769567322</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4671081412589596</v>
+        <v>0.4671418730242133</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22579,7 +22569,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
@@ -22617,16 +22607,16 @@
         <v>1</v>
       </c>
       <c r="CL77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
       </c>
       <c r="CO77" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -22639,10 +22629,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.95000076293945</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="D78" t="n">
-        <v>33.95000076293945</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="E78" t="n">
         <v>34.47000122070312</v>
@@ -22654,67 +22644,67 @@
         <v>34.11999893188477</v>
       </c>
       <c r="H78" t="n">
-        <v>1898800</v>
+        <v>2802800</v>
       </c>
       <c r="I78" t="n">
-        <v>0.002954277498559144</v>
+        <v>0.002363421998847315</v>
       </c>
       <c r="J78" t="n">
-        <v>34.6933339436849</v>
+        <v>34.69111167060004</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.142582151234131</v>
+        <v>-2.193966491045855</v>
       </c>
       <c r="M78" t="n">
-        <v>34.7830005645752</v>
+        <v>34.78100051879883</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-2.394847448796909</v>
+        <v>-2.446738739338701</v>
       </c>
       <c r="P78" t="n">
-        <v>37.18076926011305</v>
+        <v>37.18000001173753</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-8.689353559555094</v>
+        <v>-8.741257949262355</v>
       </c>
       <c r="S78" t="n">
-        <v>39.07060005187989</v>
+        <v>39.07020004272461</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-13.10601649869991</v>
+        <v>-13.15631794034287</v>
       </c>
       <c r="V78" t="n">
-        <v>36.98793342590332</v>
+        <v>36.98780008951823</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-8.213307372388501</v>
+        <v>-8.267049613499406</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.0960500907898</v>
+        <v>36.09595008850098</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-5.94538549911289</v>
+        <v>-6.000534071037513</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3110255026246819</v>
+        <v>0.3108698010668322</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22866,7 +22856,7 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>17.23</v>
+        <v>17.22</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
@@ -22926,10 +22916,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>43.56000137329102</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="D79" t="n">
-        <v>43.56000137329102</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="E79" t="n">
         <v>44.36000061035156</v>
@@ -22941,67 +22931,67 @@
         <v>44.18000030517578</v>
       </c>
       <c r="H79" t="n">
-        <v>2225700</v>
+        <v>3915300</v>
       </c>
       <c r="I79" t="n">
-        <v>0.002762494253585102</v>
+        <v>0.0002302517621242117</v>
       </c>
       <c r="J79" t="n">
-        <v>42.82000054253472</v>
+        <v>42.80777825249566</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>1.728166327371303</v>
+        <v>1.500247236975802</v>
       </c>
       <c r="M79" t="n">
-        <v>42.91000061035156</v>
+        <v>42.8990005493164</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>1.514800171740502</v>
+        <v>1.284412705581852</v>
       </c>
       <c r="P79" t="n">
-        <v>44.5700001349816</v>
+        <v>44.56576934227576</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-2.266095487170227</v>
+        <v>-2.503644828314175</v>
       </c>
       <c r="S79" t="n">
-        <v>46.7852001953125</v>
+        <v>46.78300018310547</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-6.893630482625618</v>
+        <v>-7.124381521323741</v>
       </c>
       <c r="V79" t="n">
-        <v>47.00686663309733</v>
+        <v>47.00613329569499</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-7.332684577149401</v>
+        <v>-7.565252198868309</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.48049995422363</v>
+        <v>44.47994995117188</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-2.0694429736175</v>
+        <v>-2.315535852362816</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.3364294178148522</v>
+        <v>0.335956212917755</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23153,13 +23143,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>29.04</v>
+        <v>28.97</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB79" t="n">
-        <v>10.3</v>
+        <v>10.27</v>
       </c>
       <c r="CC79" t="n">
         <v>6</v>
@@ -23213,10 +23203,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.640000343322754</v>
+        <v>9.619999885559082</v>
       </c>
       <c r="D80" t="n">
-        <v>9.640000343322754</v>
+        <v>9.619999885559082</v>
       </c>
       <c r="E80" t="n">
         <v>9.899999618530273</v>
@@ -23228,67 +23218,67 @@
         <v>9.779999732971191</v>
       </c>
       <c r="H80" t="n">
-        <v>1275400</v>
+        <v>2015000</v>
       </c>
       <c r="I80" t="n">
-        <v>0.004166662527455456</v>
+        <v>0.002083281593192376</v>
       </c>
       <c r="J80" t="n">
-        <v>9.60666667090522</v>
+        <v>9.604444397820366</v>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0.34698479253463</v>
+        <v>0.1619613492920656</v>
       </c>
       <c r="M80" t="n">
-        <v>9.619999980926513</v>
+        <v>9.617999935150147</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.2079039754251053</v>
+        <v>0.02079382847182323</v>
       </c>
       <c r="P80" t="n">
-        <v>10.07961537287786</v>
+        <v>10.07884612450233</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-4.361426634770348</v>
+        <v>-4.552567161708739</v>
       </c>
       <c r="S80" t="n">
-        <v>10.68420000076294</v>
+        <v>10.68379999160767</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-9.773306914561882</v>
+        <v>-9.957132358189218</v>
       </c>
       <c r="V80" t="n">
-        <v>12.19386666615804</v>
+        <v>12.19373332977295</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-20.9438596694115</v>
+        <v>-21.10701763445724</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.40535000801086</v>
+        <v>12.40525000572205</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-22.29158921676825</v>
+        <v>-22.45218854016033</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4301836213362589</v>
+        <v>0.4297884991227949</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23440,10 +23430,10 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>22.42</v>
+        <v>22.37</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CB80" t="n">
         <v>0.88</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,82 +897,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.52000045776367</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52000045776367</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="E2" t="n">
         <v>16.64999961853027</v>
       </c>
       <c r="F2" t="n">
-        <v>16.46999931335449</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="G2" t="n">
         <v>16.60000038146973</v>
       </c>
       <c r="H2" t="n">
-        <v>11875500</v>
+        <v>17432600</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.005418431624367392</v>
+        <v>-0.01806147702500471</v>
       </c>
       <c r="J2" t="n">
-        <v>16.2733334435357</v>
+        <v>16.25</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.515774350005457</v>
+        <v>0.3692274827223558</v>
       </c>
       <c r="M2" t="n">
-        <v>16.21500005722046</v>
+        <v>16.19399995803833</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.880976869977865</v>
+        <v>0.7163116475523637</v>
       </c>
       <c r="P2" t="n">
-        <v>15.73769228275006</v>
+        <v>15.72961532152616</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4.970920519720008</v>
+        <v>3.689754215552616</v>
       </c>
       <c r="S2" t="n">
-        <v>15.51120000839233</v>
+        <v>15.50699998855591</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>6.503690551508109</v>
+        <v>5.178303204869316</v>
       </c>
       <c r="V2" t="n">
-        <v>14.64793332417806</v>
+        <v>14.64653331756592</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>12.7804181801917</v>
+        <v>11.3574052802067</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.03585000038147</v>
+        <v>14.03479999542236</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>17.69861075257066</v>
+        <v>16.21112856087801</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5013655659730855</v>
+        <v>0.5042658348469956</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,13 +1124,13 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.69</v>
+        <v>16.47</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1165,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="CM2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CN2" t="n">
         <v>-1</v>
       </c>
       <c r="CO2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.77000045776367</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="D3" t="n">
-        <v>28.77000045776367</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="E3" t="n">
         <v>28.89999961853027</v>
@@ -1199,67 +1199,67 @@
         <v>28.55999946594238</v>
       </c>
       <c r="H3" t="n">
-        <v>1023300</v>
+        <v>1705300</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007705822297099818</v>
+        <v>0.008756567659570225</v>
       </c>
       <c r="J3" t="n">
-        <v>28.55444441901313</v>
+        <v>28.55777761671278</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7548948793660036</v>
+        <v>0.8481809179927521</v>
       </c>
       <c r="M3" t="n">
-        <v>28.57299995422363</v>
+        <v>28.57599983215332</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6894638429834129</v>
+        <v>0.7838725021799031</v>
       </c>
       <c r="P3" t="n">
-        <v>29.77153851435735</v>
+        <v>29.77269231356107</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.364078937709858</v>
+        <v>-3.26706455115407</v>
       </c>
       <c r="S3" t="n">
-        <v>30.39699996948242</v>
+        <v>30.39759994506836</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.352500290660934</v>
+        <v>-5.255680418502926</v>
       </c>
       <c r="V3" t="n">
-        <v>29.30173332214355</v>
+        <v>29.30193331400553</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.81468058061278</v>
+        <v>-1.712972559066868</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.01109997749329</v>
+        <v>28.01124997138977</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.709284822374541</v>
+        <v>2.815830305596475</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2650480386455855</v>
+        <v>0.2654934644049385</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.54</v>
+        <v>17.56</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.979999542236328</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="D4" t="n">
-        <v>8.979999542236328</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="E4" t="n">
         <v>9.350000381469727</v>
@@ -1486,67 +1486,67 @@
         <v>9.279999732971191</v>
       </c>
       <c r="H4" t="n">
-        <v>9845800</v>
+        <v>15317600</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02918923867715373</v>
+        <v>-0.02810813285209035</v>
       </c>
       <c r="J4" t="n">
-        <v>8.715555297003853</v>
+        <v>8.716666433546278</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3.034164046017623</v>
+        <v>3.135755390615348</v>
       </c>
       <c r="M4" t="n">
-        <v>8.693999767303467</v>
+        <v>8.69499979019165</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.289622528038865</v>
+        <v>3.392754319089084</v>
       </c>
       <c r="P4" t="n">
-        <v>8.946153750786415</v>
+        <v>8.946538374974178</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.378327853430172</v>
+        <v>0.485790082402807</v>
       </c>
       <c r="S4" t="n">
-        <v>8.92739993095398</v>
+        <v>8.927599935531616</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5891929530340572</v>
+        <v>0.6989542098341432</v>
       </c>
       <c r="V4" t="n">
-        <v>8.632333275477091</v>
+        <v>8.632399943669638</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.027488926393686</v>
+        <v>4.142530811617033</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.89529994726181</v>
+        <v>8.895349948406219</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.9521836866286986</v>
+        <v>1.06403708972578</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5188877594338116</v>
+        <v>0.5184328855123049</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>17.27</v>
+        <v>17.29</v>
       </c>
       <c r="CA4" t="n">
         <v>0.99</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.47999954223633</v>
+        <v>12.43000030517578</v>
       </c>
       <c r="D5" t="n">
-        <v>12.47999954223633</v>
+        <v>12.43000030517578</v>
       </c>
       <c r="E5" t="n">
         <v>12.56999969482422</v>
@@ -1769,67 +1769,67 @@
         <v>12.39000034332275</v>
       </c>
       <c r="H5" t="n">
-        <v>567500</v>
+        <v>775200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006451606948963517</v>
+        <v>0.002419410287777479</v>
       </c>
       <c r="J5" t="n">
-        <v>12.47999996609158</v>
+        <v>12.47444449530708</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.396276061642537e-06</v>
+        <v>-0.3562819181889361</v>
       </c>
       <c r="M5" t="n">
-        <v>12.49699993133545</v>
+        <v>12.49200000762939</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1360357621231394</v>
+        <v>-0.4963152610930818</v>
       </c>
       <c r="P5" t="n">
-        <v>13.22115380947406</v>
+        <v>13.21923076189481</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.605821382295974</v>
+        <v>-5.970320595310538</v>
       </c>
       <c r="S5" t="n">
-        <v>12.96519992828369</v>
+        <v>12.96419994354248</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.742328608361025</v>
+        <v>-4.120575436147806</v>
       </c>
       <c r="V5" t="n">
-        <v>12.11339996973673</v>
+        <v>12.11306664148966</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>3.026396993540046</v>
+        <v>2.616460992632168</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.70074996471405</v>
+        <v>11.70049996852875</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.659825907503877</v>
+        <v>6.234779185583494</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2349948188828148</v>
+        <v>0.2337802553370897</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-10.15</v>
+        <v>-10.11</v>
       </c>
       <c r="CA5" t="n">
         <v>1.55</v>
@@ -2014,13 +2014,13 @@
         <v>7</v>
       </c>
       <c r="CM5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.52000045776367</v>
+        <v>52.5</v>
       </c>
       <c r="D6" t="n">
-        <v>52.52000045776367</v>
+        <v>52.5</v>
       </c>
       <c r="E6" t="n">
         <v>53.40999984741211</v>
@@ -2048,67 +2048,67 @@
         <v>52.81000137329102</v>
       </c>
       <c r="H6" t="n">
-        <v>2124800</v>
+        <v>3848100</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0009510982946699942</v>
+        <v>-0.001331552125367619</v>
       </c>
       <c r="J6" t="n">
-        <v>53.86777793036567</v>
+        <v>53.86555565728082</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.502010523516035</v>
+        <v>-2.535118482707489</v>
       </c>
       <c r="M6" t="n">
-        <v>53.94799995422363</v>
+        <v>53.94599990844726</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.646992469918547</v>
+        <v>-2.680458070851028</v>
       </c>
       <c r="P6" t="n">
-        <v>57.81346130371094</v>
+        <v>57.81269205533541</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.156104351094246</v>
+        <v>-9.189490865172596</v>
       </c>
       <c r="S6" t="n">
-        <v>59.10399993896485</v>
+        <v>59.10359992980957</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-11.1396851109913</v>
+        <v>-11.17292337125301</v>
       </c>
       <c r="V6" t="n">
-        <v>58.19593335469564</v>
+        <v>58.19580001831055</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.753143509767243</v>
+        <v>-9.787304266834445</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.55639999389648</v>
+        <v>55.55629999160767</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.465436091010929</v>
+        <v>-5.50126626875683</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2784504034481777</v>
+        <v>0.2783688080957503</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.79000091552734</v>
+        <v>57.72999954223633</v>
       </c>
       <c r="D7" t="n">
-        <v>57.79000091552734</v>
+        <v>57.72999954223633</v>
       </c>
       <c r="E7" t="n">
         <v>58.72000122070312</v>
@@ -2331,67 +2331,67 @@
         <v>58.09000015258789</v>
       </c>
       <c r="H7" t="n">
-        <v>356500</v>
+        <v>496300</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.004478868646861422</v>
+        <v>-0.005512484048749489</v>
       </c>
       <c r="J7" t="n">
-        <v>59.27555550469292</v>
+        <v>59.26888868543837</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.506184170721045</v>
+        <v>-2.596453514371575</v>
       </c>
       <c r="M7" t="n">
-        <v>59.36499977111816</v>
+        <v>59.35899963378906</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.653076495684714</v>
+        <v>-2.744318640143412</v>
       </c>
       <c r="P7" t="n">
-        <v>63.55730790358324</v>
+        <v>63.55500015845666</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.074183879538962</v>
+        <v>-9.16529085311512</v>
       </c>
       <c r="S7" t="n">
-        <v>64.87120002746582</v>
+        <v>64.87</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-10.91578251819045</v>
+        <v>-11.00662934756232</v>
       </c>
       <c r="V7" t="n">
-        <v>58.57337351481119</v>
+        <v>58.57297350565592</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.337421002540963</v>
+        <v>-1.439185878685493</v>
       </c>
       <c r="Y7" t="n">
-        <v>53.95154592514038</v>
+        <v>53.95124591827393</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.114633926732984</v>
+        <v>7.004015495187097</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2955176113685384</v>
+        <v>0.2954314390435147</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.67</v>
+        <v>17.65</v>
       </c>
       <c r="CA7" t="n">
         <v>0.27</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.28000068664551</v>
+        <v>20.27000045776367</v>
       </c>
       <c r="D8" t="n">
-        <v>20.28000068664551</v>
+        <v>20.27000045776367</v>
       </c>
       <c r="E8" t="n">
         <v>20.79000091552734</v>
@@ -2618,67 +2618,67 @@
         <v>20.64999961853027</v>
       </c>
       <c r="H8" t="n">
-        <v>416900</v>
+        <v>603700</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01791762415107978</v>
+        <v>-0.01840189674510262</v>
       </c>
       <c r="J8" t="n">
-        <v>20.07888899909126</v>
+        <v>20.07777786254883</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.001607646535397</v>
+        <v>0.9573897895015436</v>
       </c>
       <c r="M8" t="n">
-        <v>19.97600002288818</v>
+        <v>19.975</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.521829512459981</v>
+        <v>1.476848349254921</v>
       </c>
       <c r="P8" t="n">
-        <v>20.68846152378963</v>
+        <v>20.68807689960186</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.974341285234916</v>
+        <v>-2.020856959625076</v>
       </c>
       <c r="S8" t="n">
-        <v>22.50940006256103</v>
+        <v>22.5092000579834</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.904303845145993</v>
+        <v>-9.947930599273093</v>
       </c>
       <c r="V8" t="n">
-        <v>25.09913336435954</v>
+        <v>25.09906669616699</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.2003947218239</v>
+        <v>-19.24002313257645</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.61510004043579</v>
+        <v>26.61505003929138</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.80265091683102</v>
+        <v>-23.84008135307134</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4404686262036913</v>
+        <v>0.4406177277886826</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.55999946594238</v>
+        <v>16.63999938964844</v>
       </c>
       <c r="D9" t="n">
-        <v>16.55999946594238</v>
+        <v>16.63999938964844</v>
       </c>
       <c r="E9" t="n">
-        <v>16.65999984741211</v>
+        <v>16.68000030517578</v>
       </c>
       <c r="F9" t="n">
         <v>16.11000061035156</v>
@@ -2901,67 +2901,67 @@
         <v>16.54999923706055</v>
       </c>
       <c r="H9" t="n">
-        <v>11729200</v>
+        <v>14272600</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004854364437391068</v>
+        <v>0.009708728874782357</v>
       </c>
       <c r="J9" t="n">
-        <v>16.70222229427761</v>
+        <v>16.7111111746894</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8515203894990614</v>
+        <v>-0.42553594609955</v>
       </c>
       <c r="M9" t="n">
-        <v>16.7020001411438</v>
+        <v>16.71000013351441</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8502016165813026</v>
+        <v>-0.4189152801116455</v>
       </c>
       <c r="P9" t="n">
-        <v>17.52576934374296</v>
+        <v>17.5288462638855</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-5.510570513957916</v>
+        <v>-5.070766557342354</v>
       </c>
       <c r="S9" t="n">
-        <v>17.8954001045227</v>
+        <v>17.89700010299683</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.462256394272098</v>
+        <v>-7.023527440992231</v>
       </c>
       <c r="V9" t="n">
-        <v>16.00360007603963</v>
+        <v>16.00413340886434</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>3.476713909739498</v>
+        <v>3.973135967686372</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.23710005283356</v>
+        <v>15.23750005245209</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.682094417715744</v>
+        <v>9.204261410129762</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.350390818933815</v>
+        <v>0.3519167610154328</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>16.9</v>
+        <v>16.98</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM9" t="n">
         <v>4</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.92000007629395</v>
+        <v>20.86000061035156</v>
       </c>
       <c r="D10" t="n">
-        <v>20.92000007629395</v>
+        <v>20.86000061035156</v>
       </c>
       <c r="E10" t="n">
         <v>21.18000030517578</v>
@@ -3188,67 +3188,67 @@
         <v>21.05999946594238</v>
       </c>
       <c r="H10" t="n">
-        <v>8130100</v>
+        <v>10257200</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.007119108718692591</v>
+        <v>-0.009966734101293895</v>
       </c>
       <c r="J10" t="n">
-        <v>20.87333340115017</v>
+        <v>20.86666679382324</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2235707840569472</v>
+        <v>-0.03194656596353448</v>
       </c>
       <c r="M10" t="n">
-        <v>20.8560001373291</v>
+        <v>20.85000019073486</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.306865834979998</v>
+        <v>0.04796364280678714</v>
       </c>
       <c r="P10" t="n">
-        <v>21.55384621253381</v>
+        <v>21.55153854076679</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-2.940756512734473</v>
+        <v>-3.208763630063423</v>
       </c>
       <c r="S10" t="n">
-        <v>22.64339996337891</v>
+        <v>22.64219997406006</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.611047324484005</v>
+        <v>-7.871140462279574</v>
       </c>
       <c r="V10" t="n">
-        <v>22.94699999491374</v>
+        <v>22.94659999847412</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-8.833398348669022</v>
+        <v>-9.093283485402241</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.46075001716614</v>
+        <v>22.46045001983643</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-6.859743951981298</v>
+        <v>-7.125633760994958</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2687655433823159</v>
+        <v>0.2689692672101995</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3453,13 +3453,13 @@
         <v>4</v>
       </c>
       <c r="CM10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.63000011444092</v>
+        <v>15.65999984741211</v>
       </c>
       <c r="D11" t="n">
-        <v>15.63000011444092</v>
+        <v>15.65999984741211</v>
       </c>
       <c r="E11" t="n">
         <v>15.80000019073486</v>
@@ -3487,67 +3487,67 @@
         <v>15.71000003814697</v>
       </c>
       <c r="H11" t="n">
-        <v>1339600</v>
+        <v>1814100</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0006394008096108905</v>
+        <v>0.00127874064260447</v>
       </c>
       <c r="J11" t="n">
-        <v>15.49333339267307</v>
+        <v>15.49666669633653</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8821001801489656</v>
+        <v>1.053988927271614</v>
       </c>
       <c r="M11" t="n">
-        <v>15.48000001907349</v>
+        <v>15.4829999923706</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.968992862936763</v>
+        <v>1.143188368718743</v>
       </c>
       <c r="P11" t="n">
-        <v>16.0742307809683</v>
+        <v>16.07538461685181</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.763620061081528</v>
+        <v>-2.583980286258594</v>
       </c>
       <c r="S11" t="n">
-        <v>16.50979997634888</v>
+        <v>16.5103999710083</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.328955306353295</v>
+        <v>-5.150693654238935</v>
       </c>
       <c r="V11" t="n">
-        <v>16.62139998753866</v>
+        <v>16.62159998575846</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.96459909418585</v>
+        <v>-5.785244135163059</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.07875000476837</v>
+        <v>16.07890000343323</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.790950106161046</v>
+        <v>-2.605278694013096</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.215531037506938</v>
+        <v>0.2159119508959055</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.98</v>
+        <v>6.99</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -3752,13 +3752,13 @@
         <v>6</v>
       </c>
       <c r="CM11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN11" t="n">
         <v>1</v>
       </c>
       <c r="CO11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.02000045776367</v>
+        <v>18.04000091552734</v>
       </c>
       <c r="D12" t="n">
-        <v>18.02000045776367</v>
+        <v>18.04000091552734</v>
       </c>
       <c r="E12" t="n">
         <v>18.21999931335449</v>
@@ -3786,67 +3786,67 @@
         <v>18.09000015258789</v>
       </c>
       <c r="H12" t="n">
-        <v>16545000</v>
+        <v>21986900</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001111136542426117</v>
+        <v>0.002222273084852455</v>
       </c>
       <c r="J12" t="n">
-        <v>17.81777784559462</v>
+        <v>17.82000011867947</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.134948554872969</v>
+        <v>1.234572364661559</v>
       </c>
       <c r="M12" t="n">
-        <v>17.80500011444092</v>
+        <v>17.80700016021729</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.207527896326016</v>
+        <v>1.308478425415005</v>
       </c>
       <c r="P12" t="n">
-        <v>18.54230770697961</v>
+        <v>18.54307695535513</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.816840586780524</v>
+        <v>-2.71301273806395</v>
       </c>
       <c r="S12" t="n">
-        <v>19.04100006103516</v>
+        <v>19.04140007019043</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.362111233646926</v>
+        <v>-5.259062626549142</v>
       </c>
       <c r="V12" t="n">
-        <v>19.30040000915527</v>
+        <v>19.30053334554037</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.634057070238099</v>
+        <v>-6.531075631152359</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.69405000209808</v>
+        <v>18.6941500043869</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.605690282516426</v>
+        <v>-3.499218144211162</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2575095423128116</v>
+        <v>0.2577441355023115</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.039999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34.68000030517578</v>
+        <v>34.63999938964844</v>
       </c>
       <c r="D13" t="n">
-        <v>34.68000030517578</v>
+        <v>34.63999938964844</v>
       </c>
       <c r="E13" t="n">
         <v>35.02000045776367</v>
@@ -4085,67 +4085,67 @@
         <v>34.90999984741211</v>
       </c>
       <c r="H13" t="n">
-        <v>1116300</v>
+        <v>1529200</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.005163519851526632</v>
+        <v>-0.006310993024991385</v>
       </c>
       <c r="J13" t="n">
-        <v>34.53666687011719</v>
+        <v>34.53222232394748</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4150181475173357</v>
+        <v>0.3121057911937992</v>
       </c>
       <c r="M13" t="n">
-        <v>34.49500007629395</v>
+        <v>34.49099998474121</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5363102724240059</v>
+        <v>0.4319950276105263</v>
       </c>
       <c r="P13" t="n">
-        <v>34.33846165583684</v>
+        <v>34.33692315908579</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.994624199424172</v>
+        <v>0.8826540140433532</v>
       </c>
       <c r="S13" t="n">
-        <v>34.69439994812011</v>
+        <v>34.69359992980957</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04150422824970521</v>
+        <v>-0.1544969108699496</v>
       </c>
       <c r="V13" t="n">
-        <v>34.80413335164388</v>
+        <v>34.8038666788737</v>
       </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3566617942010401</v>
+        <v>-0.4708307003276959</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.29574997901916</v>
+        <v>34.29554997444153</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.120402167591284</v>
+        <v>1.004356003806931</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1576651200049876</v>
+        <v>0.1579666238746522</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4313,13 +4313,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.33</v>
+        <v>5.32</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3.990000009536743</v>
       </c>
       <c r="E14" t="n">
         <v>4.159999847412109</v>
@@ -4384,67 +4384,67 @@
         <v>4.079999923706055</v>
       </c>
       <c r="H14" t="n">
-        <v>18819700</v>
+        <v>23361300</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02827760723120476</v>
+        <v>0.0257069156647316</v>
       </c>
       <c r="J14" t="n">
-        <v>4.032222244474623</v>
+        <v>4.03111113442315</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7991187618385138</v>
+        <v>-1.019845980810199</v>
       </c>
       <c r="M14" t="n">
-        <v>4.069000029563904</v>
+        <v>4.068000030517578</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.695749055359413</v>
+        <v>-1.91740463116248</v>
       </c>
       <c r="P14" t="n">
-        <v>4.043461561203003</v>
+        <v>4.043076946185185</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.074860253897711</v>
+        <v>-1.312785716297648</v>
       </c>
       <c r="S14" t="n">
-        <v>4.097000026702881</v>
+        <v>4.096800026893615</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.36758667490035</v>
+        <v>-2.606913118916691</v>
       </c>
       <c r="V14" t="n">
-        <v>5.313333339691162</v>
+        <v>5.313266673088074</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-24.71769143261582</v>
+        <v>-24.90495480405178</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.513450000286102</v>
+        <v>5.513400000333786</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-27.45014465003885</v>
+        <v>-27.63086281976303</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.4914278531239124</v>
+        <v>0.4901335864716942</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4596,10 +4596,10 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>5.63</v>
+        <v>5.62</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CB14" t="n">
         <v>3.17</v>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54.84999847412109</v>
+        <v>54.79000091552734</v>
       </c>
       <c r="D15" t="n">
-        <v>54.84999847412109</v>
+        <v>54.79000091552734</v>
       </c>
       <c r="E15" t="n">
         <v>55.5</v>
@@ -4671,67 +4671,67 @@
         <v>54.9900016784668</v>
       </c>
       <c r="H15" t="n">
-        <v>5861900</v>
+        <v>7718800</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.002545975633249098</v>
+        <v>-0.00363703867675591</v>
       </c>
       <c r="J15" t="n">
-        <v>54.55444463094076</v>
+        <v>54.54777823554145</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5417594206663626</v>
+        <v>0.4440559960846753</v>
       </c>
       <c r="M15" t="n">
-        <v>54.54900016784668</v>
+        <v>54.54300041198731</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5517943598383966</v>
+        <v>0.4528546315280286</v>
       </c>
       <c r="P15" t="n">
-        <v>57.04461537874662</v>
+        <v>57.04230778033916</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.847193797441546</v>
+        <v>-3.948484821976516</v>
       </c>
       <c r="S15" t="n">
-        <v>57.81359977722168</v>
+        <v>57.81239982604981</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.126131765744564</v>
+        <v>-5.227942309290875</v>
       </c>
       <c r="V15" t="n">
-        <v>55.83373321533203</v>
+        <v>55.83333323160807</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.761900350487047</v>
+        <v>-1.868654897877534</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.29289993286133</v>
+        <v>53.29259994506836</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.921774839090016</v>
+        <v>2.809772786470237</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2874306125045282</v>
+        <v>0.287380920636897</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>3510880000</v>
       </c>
       <c r="BZ15" t="n">
-        <v>12.33</v>
+        <v>12.31</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -4963,13 +4963,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.54000091552734</v>
+        <v>23.59000015258789</v>
       </c>
       <c r="D16" t="n">
-        <v>23.54000091552734</v>
+        <v>23.59000015258789</v>
       </c>
       <c r="E16" t="n">
-        <v>23.57999992370605</v>
+        <v>23.68000030517578</v>
       </c>
       <c r="F16" t="n">
         <v>23.10000038146973</v>
@@ -4978,67 +4978,67 @@
         <v>23.29000091552734</v>
       </c>
       <c r="H16" t="n">
-        <v>421400</v>
+        <v>614800</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01073422027361648</v>
+        <v>0.01288103157009912</v>
       </c>
       <c r="J16" t="n">
-        <v>23.04888916015625</v>
+        <v>23.05444463094075</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.130739368646278</v>
+        <v>2.323003352370423</v>
       </c>
       <c r="M16" t="n">
-        <v>23.04300022125244</v>
+        <v>23.0480001449585</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.156840209620452</v>
+        <v>2.351614041220624</v>
       </c>
       <c r="P16" t="n">
-        <v>23.17192319723276</v>
+        <v>23.17384624481201</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.588464259792381</v>
+        <v>1.795791269949607</v>
       </c>
       <c r="S16" t="n">
-        <v>23.29719997406006</v>
+        <v>23.29819995880127</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.042189369270242</v>
+        <v>1.25245810535843</v>
       </c>
       <c r="V16" t="n">
-        <v>21.92799996693929</v>
+        <v>21.92833329518636</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>7.351335967796691</v>
+        <v>7.577716167631834</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.61274995803833</v>
+        <v>20.61299995422363</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.20116657626014</v>
+        <v>14.44234320562479</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2494700987598228</v>
+        <v>0.250528476642837</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5194,13 +5194,13 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.83</v>
+        <v>11.85</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CC16" t="n">
         <v>2</v>
@@ -5254,13 +5254,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.06999969482422</v>
+        <v>20.22999954223633</v>
       </c>
       <c r="D17" t="n">
-        <v>20.06999969482422</v>
+        <v>20.22999954223633</v>
       </c>
       <c r="E17" t="n">
-        <v>20.20999908447266</v>
+        <v>20.29999923706055</v>
       </c>
       <c r="F17" t="n">
         <v>19.72999954223633</v>
@@ -5269,79 +5269,79 @@
         <v>20.07999992370605</v>
       </c>
       <c r="H17" t="n">
-        <v>3426100</v>
+        <v>4126000</v>
       </c>
       <c r="I17" t="n">
-        <v>0.008036155130001443</v>
+        <v>0.01607231026000289</v>
       </c>
       <c r="J17" t="n">
-        <v>19.73222223917643</v>
+        <v>19.75</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.711806463324544</v>
+        <v>2.430377429044699</v>
       </c>
       <c r="M17" t="n">
-        <v>19.62800006866455</v>
+        <v>19.64400005340576</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25188314965061</v>
+        <v>2.983096554863678</v>
       </c>
       <c r="P17" t="n">
-        <v>18.98769231942984</v>
+        <v>18.99384615971492</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>5.700046941917595</v>
+        <v>6.508178344327296</v>
       </c>
       <c r="S17" t="n">
-        <v>19.38959995269775</v>
+        <v>19.392799949646</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>3.509096339204244</v>
+        <v>4.317064038014857</v>
       </c>
       <c r="V17" t="n">
-        <v>17.32846663157145</v>
+        <v>17.32953329722087</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>15.82097897951256</v>
+        <v>16.73712843427012</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.61634995937347</v>
+        <v>17.61714995861054</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.92825268065923</v>
+        <v>14.83128423022101</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3947955578644083</v>
+        <v>0.3971524367721794</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AE17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AG17" t="n">
         <v>20.6</v>
@@ -5477,10 +5477,10 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>40.14</v>
+        <v>40.46</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CB17" t="n">
         <v>0.82</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.14000034332275</v>
+        <v>11.26000022888184</v>
       </c>
       <c r="D18" t="n">
-        <v>11.14000034332275</v>
+        <v>11.26000022888184</v>
       </c>
       <c r="E18" t="n">
         <v>11.46000003814697</v>
@@ -5548,88 +5548,88 @@
         <v>11.31999969482422</v>
       </c>
       <c r="H18" t="n">
-        <v>2086400</v>
+        <v>2881900</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01590100321148991</v>
+        <v>-0.005300306321546655</v>
       </c>
       <c r="J18" t="n">
-        <v>11.91666666666667</v>
+        <v>11.92999998728434</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-6.51747963645241</v>
+        <v>-5.616091861832598</v>
       </c>
       <c r="M18" t="n">
-        <v>11.9460000038147</v>
+        <v>11.95799999237061</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.747025449812197</v>
+        <v>-5.837094530306951</v>
       </c>
       <c r="P18" t="n">
-        <v>10.44230761894813</v>
+        <v>10.44692299916194</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>6.681403668942133</v>
+        <v>7.782935030583856</v>
       </c>
       <c r="S18" t="n">
-        <v>10.147799949646</v>
+        <v>10.15019994735718</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>9.777492644712316</v>
+        <v>10.93377753424077</v>
       </c>
       <c r="V18" t="n">
-        <v>9.05333332379659</v>
+        <v>9.054133323033652</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>23.04860480549614</v>
+        <v>24.36309282343429</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.802399988174438</v>
+        <v>8.802999987602234</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>26.55639778115922</v>
+        <v>27.91094223264722</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9927914036153899</v>
+        <v>0.9912433733942698</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>12.2</v>
+        <v>16.8</v>
       </c>
       <c r="AI18" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -5756,13 +5756,13 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.57</v>
       </c>
       <c r="CC18" t="n">
         <v>1</v>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.36999988555908</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="D19" t="n">
-        <v>11.36999988555908</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="E19" t="n">
         <v>11.64999961853027</v>
@@ -5831,67 +5831,67 @@
         <v>11.47999954223633</v>
       </c>
       <c r="H19" t="n">
-        <v>2088600</v>
+        <v>3635000</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0008787547259464512</v>
+        <v>0.01669592077966642</v>
       </c>
       <c r="J19" t="n">
-        <v>11.2411110136244</v>
+        <v>11.26333321465386</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.146584815134942</v>
+        <v>2.722697396285643</v>
       </c>
       <c r="M19" t="n">
-        <v>11.21599988937378</v>
+        <v>11.23599987030029</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.373038495936542</v>
+        <v>2.972586582229985</v>
       </c>
       <c r="P19" t="n">
-        <v>11.3719230064979</v>
+        <v>11.37961530685425</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.01691113224839216</v>
+        <v>1.673030087891434</v>
       </c>
       <c r="S19" t="n">
-        <v>11.8381999206543</v>
+        <v>11.8421999168396</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.954993480709335</v>
+        <v>-2.298561280225573</v>
       </c>
       <c r="V19" t="n">
-        <v>13.14666664759318</v>
+        <v>13.14799997965495</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.51419952797967</v>
+        <v>-12.00182755759436</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.99304997444153</v>
+        <v>13.99404997348785</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-18.74537783880911</v>
+        <v>-17.32200673326215</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5929336170592157</v>
+        <v>0.5959985013222042</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6043,13 +6043,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>5.98</v>
+        <v>6.09</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CC19" t="n">
         <v>6</v>
@@ -6081,16 +6081,16 @@
         <v>1</v>
       </c>
       <c r="CL19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN19" t="n">
         <v>-1</v>
       </c>
       <c r="CO19" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.10999965667725</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="D20" t="n">
-        <v>11.10999965667725</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="E20" t="n">
         <v>11.23999977111816</v>
@@ -6118,67 +6118,67 @@
         <v>11.22000026702881</v>
       </c>
       <c r="H20" t="n">
-        <v>5141100</v>
+        <v>6666700</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.004480303890546877</v>
+        <v>-0.001792070283405334</v>
       </c>
       <c r="J20" t="n">
-        <v>11.29555553860135</v>
+        <v>11.29888894822862</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.642733562682966</v>
+        <v>-1.406232113917538</v>
       </c>
       <c r="M20" t="n">
-        <v>11.29300003051758</v>
+        <v>11.29600009918213</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.620476165286484</v>
+        <v>-1.381017656601026</v>
       </c>
       <c r="P20" t="n">
-        <v>11.87423086166382</v>
+        <v>11.87538473422711</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-6.436048059785559</v>
+        <v>-6.192510031147344</v>
       </c>
       <c r="S20" t="n">
-        <v>12.34760009765625</v>
+        <v>12.34820011138916</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-10.0230039132375</v>
+        <v>-9.784420054482617</v>
       </c>
       <c r="V20" t="n">
-        <v>11.70033336639404</v>
+        <v>11.70053337097168</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-5.045443503450647</v>
+        <v>-4.790662185021197</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.51415002822876</v>
+        <v>11.51430003166199</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.510032182668073</v>
+        <v>-3.25073766803006</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2202834542651116</v>
+        <v>0.220661177121628</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6326,7 +6326,7 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="CA20" t="n">
         <v>0.5600000000000001</v>
@@ -6382,13 +6382,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.710000038146973</v>
+        <v>4.730000019073486</v>
       </c>
       <c r="D21" t="n">
-        <v>4.710000038146973</v>
+        <v>4.730000019073486</v>
       </c>
       <c r="E21" t="n">
-        <v>4.710000038146973</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="F21" t="n">
         <v>4.570000171661377</v>
@@ -6397,67 +6397,67 @@
         <v>4.650000095367432</v>
       </c>
       <c r="H21" t="n">
-        <v>2939200</v>
+        <v>3975700</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01727860080532961</v>
+        <v>0.02159825100666191</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4566666815016</v>
+        <v>4.458888901604547</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>5.684368492193719</v>
+        <v>6.080239347775172</v>
       </c>
       <c r="M21" t="n">
-        <v>4.482999992370606</v>
+        <v>4.484999990463256</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>5.063574529616041</v>
+        <v>5.462653938265087</v>
       </c>
       <c r="P21" t="n">
-        <v>4.654230778033916</v>
+        <v>4.655000008069551</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.198248706881156</v>
+        <v>1.61117101769969</v>
       </c>
       <c r="S21" t="n">
-        <v>4.794000005722046</v>
+        <v>4.794400005340576</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.752189559341089</v>
+        <v>-1.343233484802138</v>
       </c>
       <c r="V21" t="n">
-        <v>5.337266670862833</v>
+        <v>5.337400004069011</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-11.75258182507968</v>
+        <v>-11.38007240477513</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.311200013160706</v>
+        <v>5.311300013065338</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-11.31947532617884</v>
+        <v>-10.94458969672028</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5093269506669602</v>
+        <v>0.5108959898705311</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6609,13 +6609,13 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>11.49</v>
+        <v>11.54</v>
       </c>
       <c r="CA21" t="n">
         <v>0.01</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CC21" t="n">
         <v>3</v>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.559999942779541</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="D22" t="n">
-        <v>2.559999942779541</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="E22" t="n">
         <v>2.589999914169312</v>
@@ -6684,67 +6684,67 @@
         <v>2.539999961853027</v>
       </c>
       <c r="H22" t="n">
-        <v>8198800</v>
+        <v>11203500</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01185769633558187</v>
+        <v>0.003952565445193956</v>
       </c>
       <c r="J22" t="n">
-        <v>2.516666650772095</v>
+        <v>2.514444430669149</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.721852673422281</v>
+        <v>1.016349014206591</v>
       </c>
       <c r="M22" t="n">
-        <v>2.518999981880188</v>
+        <v>2.516999983787537</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.627628471388504</v>
+        <v>0.9137853879077448</v>
       </c>
       <c r="P22" t="n">
-        <v>2.685384612817031</v>
+        <v>2.684615382781395</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-4.669151280566788</v>
+        <v>-5.386820840553305</v>
       </c>
       <c r="S22" t="n">
-        <v>2.888200001716614</v>
+        <v>2.887800002098083</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-11.36348101731202</v>
+        <v>-12.04377172907984</v>
       </c>
       <c r="V22" t="n">
-        <v>3.289381685256958</v>
+        <v>3.289248352050781</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-22.17382512180065</v>
+        <v>-22.77871142598923</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.154581613540649</v>
+        <v>3.154481613636017</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-18.84819426477794</v>
+        <v>-19.47963966969224</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.433064689954993</v>
+        <v>0.4305354580137679</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>7.76</v>
+        <v>7.7</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB22" t="n">
         <v>0.39</v>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.43000030517578</v>
+        <v>43.13999938964844</v>
       </c>
       <c r="D23" t="n">
-        <v>43.43000030517578</v>
+        <v>43.13999938964844</v>
       </c>
       <c r="E23" t="n">
         <v>44.34999847412109</v>
@@ -6967,67 +6967,67 @@
         <v>44.18000030517578</v>
       </c>
       <c r="H23" t="n">
-        <v>1064700</v>
+        <v>1558400</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.01697600712583369</v>
+        <v>-0.02354008393715434</v>
       </c>
       <c r="J23" t="n">
-        <v>43.81333372328017</v>
+        <v>43.78111139933268</v>
       </c>
       <c r="K23" t="n">
         <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8749241053544882</v>
+        <v>-1.46435754870767</v>
       </c>
       <c r="M23" t="n">
-        <v>43.88400039672852</v>
+        <v>43.85500030517578</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.034545819543336</v>
+        <v>-1.630374895797131</v>
       </c>
       <c r="P23" t="n">
-        <v>47.42076932466947</v>
+        <v>47.40961544330303</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-8.415656422970752</v>
+        <v>-9.005801911134697</v>
       </c>
       <c r="S23" t="n">
-        <v>48.81179977416992</v>
+        <v>48.80599975585938</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-11.02561162238083</v>
+        <v>-11.60922918197308</v>
       </c>
       <c r="V23" t="n">
-        <v>48.81933336893717</v>
+        <v>48.81740002950033</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-11.03934177681853</v>
+        <v>-11.62987098129159</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.31704999923706</v>
+        <v>46.31559999465942</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.23323310553854</v>
+        <v>-6.856438447039784</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2621938045917734</v>
+        <v>0.2647540094084426</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7179,13 +7179,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.69</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="CA23" t="n">
         <v>0.52</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7220,13 +7220,13 @@
         <v>2</v>
       </c>
       <c r="CM23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.56999969482422</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="D24" t="n">
-        <v>14.56999969482422</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="E24" t="n">
         <v>14.77000045776367</v>
@@ -7254,67 +7254,67 @@
         <v>14.76000022888184</v>
       </c>
       <c r="H24" t="n">
-        <v>10803500</v>
+        <v>14129300</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.00478146494924514</v>
+        <v>-0.006830626989386412</v>
       </c>
       <c r="J24" t="n">
-        <v>14.79555543263753</v>
+        <v>14.79222212897407</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.524483070880602</v>
+        <v>-1.705099916171509</v>
       </c>
       <c r="M24" t="n">
-        <v>14.80099992752075</v>
+        <v>14.79799995422363</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.560706937556399</v>
+        <v>-1.743478802329412</v>
       </c>
       <c r="P24" t="n">
-        <v>15.38692294634306</v>
+        <v>15.38576911045955</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-5.309204799215503</v>
+        <v>-5.497087227388258</v>
       </c>
       <c r="S24" t="n">
-        <v>15.60419990539551</v>
+        <v>15.60359991073608</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.627704187599457</v>
+        <v>-6.816375419567414</v>
       </c>
       <c r="V24" t="n">
-        <v>14.15673327763875</v>
+        <v>14.15653327941894</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>2.919221610526769</v>
+        <v>2.708761211981005</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.51089994907379</v>
+        <v>13.51074995040894</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>7.838854182493081</v>
+        <v>7.618007995277408</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2229920078960107</v>
+        <v>0.2230619291838968</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7466,7 +7466,7 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>16.01</v>
+        <v>15.98</v>
       </c>
       <c r="CA24" t="n">
         <v>0.42</v>
@@ -7537,7 +7537,7 @@
         <v>4.079999923706055</v>
       </c>
       <c r="H25" t="n">
-        <v>47250900</v>
+        <v>53419900</v>
       </c>
       <c r="I25" t="n">
         <v>-0.01496263784873919</v>
@@ -7809,13 +7809,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>52.72999954223633</v>
+        <v>52.70999908447266</v>
       </c>
       <c r="D26" t="n">
-        <v>52.72999954223633</v>
+        <v>52.70999908447266</v>
       </c>
       <c r="E26" t="n">
-        <v>52.93000030517578</v>
+        <v>53.20999908447266</v>
       </c>
       <c r="F26" t="n">
         <v>49.90000152587891</v>
@@ -7824,67 +7824,67 @@
         <v>49.95000076293945</v>
       </c>
       <c r="H26" t="n">
-        <v>4051700</v>
+        <v>5748800</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03901476930514924</v>
+        <v>0.03862067161522464</v>
       </c>
       <c r="J26" t="n">
-        <v>52.47111087375217</v>
+        <v>52.46888860066732</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4933927720856889</v>
+        <v>0.4595303812138868</v>
       </c>
       <c r="M26" t="n">
-        <v>52.3939998626709</v>
+        <v>52.39199981689453</v>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6412941948431425</v>
+        <v>0.6069614992546635</v>
       </c>
       <c r="P26" t="n">
-        <v>53.71807670593262</v>
+        <v>53.71730745755709</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.839375540388932</v>
+        <v>-1.875202650245128</v>
       </c>
       <c r="S26" t="n">
-        <v>55.15659996032715</v>
+        <v>55.15619995117188</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.399474260262993</v>
+        <v>-4.435042422909428</v>
       </c>
       <c r="V26" t="n">
-        <v>48.8257999420166</v>
+        <v>48.82566660563151</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>7.996181536925528</v>
+        <v>7.9555134601954</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.41594993591308</v>
+        <v>44.41584993362427</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.71861261172941</v>
+        <v>18.67384990548035</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3247590458179646</v>
+        <v>0.3243198166071996</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8096,13 +8096,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.619999885559082</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="D27" t="n">
-        <v>6.619999885559082</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="E27" t="n">
-        <v>6.710000038146973</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="F27" t="n">
         <v>6.400000095367432</v>
@@ -8111,67 +8111,67 @@
         <v>6.579999923706055</v>
       </c>
       <c r="H27" t="n">
-        <v>8343400</v>
+        <v>11185700</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01068697599783808</v>
+        <v>0.02900756867947263</v>
       </c>
       <c r="J27" t="n">
-        <v>6.425555600060357</v>
+        <v>6.438888920678033</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>3.026108520435158</v>
+        <v>4.676441139916783</v>
       </c>
       <c r="M27" t="n">
-        <v>6.425000047683715</v>
+        <v>6.437000036239624</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.035016909387669</v>
+        <v>4.707157576086436</v>
       </c>
       <c r="P27" t="n">
-        <v>6.442307673967802</v>
+        <v>6.446923054181612</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>2.758207471358471</v>
+        <v>4.545993716280764</v>
       </c>
       <c r="S27" t="n">
-        <v>6.44999997138977</v>
+        <v>6.452399969100952</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2.635657595711307</v>
+        <v>4.457253167727679</v>
       </c>
       <c r="V27" t="n">
-        <v>8.099866660435994</v>
+        <v>8.100666659673054</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-18.27026094275551</v>
+        <v>-16.79697419631642</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.01559998512268</v>
+        <v>8.016199984550475</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-17.41104972995029</v>
+        <v>-15.92026416371743</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4814933556084933</v>
+        <v>0.4878009303381183</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8323,13 +8323,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>-4.38</v>
+        <v>-4.46</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.21</v>
+        <v>4.14</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="CC27" t="n">
         <v>2</v>
@@ -8360,13 +8360,13 @@
         <v>10</v>
       </c>
       <c r="CM27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN27" t="n">
         <v>0</v>
       </c>
       <c r="CO27" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28">
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32.22999954223633</v>
+        <v>32.2599983215332</v>
       </c>
       <c r="D28" t="n">
-        <v>32.22999954223633</v>
+        <v>32.2599983215332</v>
       </c>
       <c r="E28" t="n">
         <v>32.58000183105469</v>
@@ -8394,67 +8394,67 @@
         <v>31.6299991607666</v>
       </c>
       <c r="H28" t="n">
-        <v>2111600</v>
+        <v>2882200</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0238246509182356</v>
+        <v>0.02477759817786396</v>
       </c>
       <c r="J28" t="n">
-        <v>31.00333340962728</v>
+        <v>31.00666660732693</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>3.956562078025266</v>
+        <v>4.042136260819819</v>
       </c>
       <c r="M28" t="n">
-        <v>30.94000015258789</v>
+        <v>30.94300003051758</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>4.169358058456692</v>
+        <v>4.256207509668533</v>
       </c>
       <c r="P28" t="n">
-        <v>30.9211540222168</v>
+        <v>30.92230782142052</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>4.232848227718565</v>
+        <v>4.325972394550813</v>
       </c>
       <c r="S28" t="n">
-        <v>33.05140007019043</v>
+        <v>33.05200004577637</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.48522158277627</v>
+        <v>-2.396229345111513</v>
       </c>
       <c r="V28" t="n">
-        <v>34.75833323160807</v>
+        <v>34.75853322347005</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-7.274036049210091</v>
+        <v>-7.18826334204966</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.28609993934631</v>
+        <v>34.2862499332428</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-5.996892037144272</v>
+        <v>-5.909808204906689</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.5017979948708511</v>
+        <v>0.5022573103900642</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
         <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>6.43</v>
+        <v>6.44</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8677,7 +8677,7 @@
         <v>17.51000022888184</v>
       </c>
       <c r="H29" t="n">
-        <v>837800</v>
+        <v>1210100</v>
       </c>
       <c r="I29" t="n">
         <v>-0.001718143234242908</v>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.48999977111816</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="D30" t="n">
-        <v>22.48999977111816</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="E30" t="n">
         <v>22.79999923706055</v>
@@ -8972,67 +8972,67 @@
         <v>22.29000091552734</v>
       </c>
       <c r="H30" t="n">
-        <v>12946500</v>
+        <v>13616300</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01306301793749642</v>
+        <v>0.01441440017238316</v>
       </c>
       <c r="J30" t="n">
-        <v>22.03222232394748</v>
+        <v>22.03555573357476</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>2.077763379652851</v>
+        <v>2.198468375593455</v>
       </c>
       <c r="M30" t="n">
-        <v>22.01300010681152</v>
+        <v>22.01600017547607</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.166899840967339</v>
+        <v>2.289245449993282</v>
       </c>
       <c r="P30" t="n">
-        <v>23.01038463299091</v>
+        <v>23.0115385055542</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.261521787543912</v>
+        <v>-2.136050345664141</v>
       </c>
       <c r="S30" t="n">
-        <v>25.06939994812012</v>
+        <v>25.06999996185303</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-10.28903835887534</v>
+        <v>-10.17151778208808</v>
       </c>
       <c r="V30" t="n">
-        <v>28.69219993591308</v>
+        <v>28.69239994049072</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.6163284051002</v>
+        <v>-21.51231509225047</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.61684996604919</v>
+        <v>28.61699996948242</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-21.40993925676613</v>
+        <v>-21.30551601572729</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4042742801815137</v>
+        <v>0.4048745552321386</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9180,7 +9180,7 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>5.19</v>
+        <v>5.2</v>
       </c>
       <c r="CA30" t="n">
         <v>0.48</v>
@@ -9236,10 +9236,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.52999973297119</v>
+        <v>13.43000030517578</v>
       </c>
       <c r="D31" t="n">
-        <v>13.52999973297119</v>
+        <v>13.43000030517578</v>
       </c>
       <c r="E31" t="n">
         <v>13.65999984741211</v>
@@ -9251,67 +9251,67 @@
         <v>13.40999984741211</v>
       </c>
       <c r="H31" t="n">
-        <v>2364700</v>
+        <v>4647700</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01576576899086368</v>
+        <v>0.00825830426965446</v>
       </c>
       <c r="J31" t="n">
-        <v>13.13444434271918</v>
+        <v>13.12333329518636</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>3.011588308806339</v>
+        <v>2.336807296526603</v>
       </c>
       <c r="M31" t="n">
-        <v>13.1189998626709</v>
+        <v>13.10899991989136</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>3.13285978049105</v>
+        <v>2.448702320894399</v>
       </c>
       <c r="P31" t="n">
-        <v>13.20038465353159</v>
+        <v>13.1965385216933</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>2.497011171196588</v>
+        <v>1.769113795247897</v>
       </c>
       <c r="S31" t="n">
-        <v>13.51940004348755</v>
+        <v>13.51740005493164</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>0.07840354934055407</v>
+        <v>-0.6465721914028291</v>
       </c>
       <c r="V31" t="n">
-        <v>15.0185333442688</v>
+        <v>15.01786668141683</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-9.911311425530403</v>
+        <v>-10.5731819966539</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.03481666088104</v>
+        <v>15.03431666374207</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-10.00888113138899</v>
+        <v>-10.67102944848421</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4690599537919887</v>
+        <v>0.467038326795581</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9463,13 +9463,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>8.4</v>
+        <v>8.34</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
       </c>
       <c r="CB31" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CC31" t="n">
         <v>9</v>
@@ -9500,13 +9500,13 @@
         <v>9</v>
       </c>
       <c r="CM31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN31" t="n">
         <v>0</v>
       </c>
       <c r="CO31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>32.4900016784668</v>
+        <v>32.43000030517578</v>
       </c>
       <c r="D32" t="n">
-        <v>32.4900016784668</v>
+        <v>32.43000030517578</v>
       </c>
       <c r="E32" t="n">
         <v>32.93999862670898</v>
@@ -9534,67 +9534,67 @@
         <v>32.79000091552734</v>
       </c>
       <c r="H32" t="n">
-        <v>775400</v>
+        <v>969900</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.004290511341271119</v>
+        <v>-0.006129352019387024</v>
       </c>
       <c r="J32" t="n">
-        <v>32.34000100029839</v>
+        <v>32.33333418104384</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.4638239750426092</v>
+        <v>0.2989673863842214</v>
       </c>
       <c r="M32" t="n">
-        <v>32.36300086975098</v>
+        <v>32.35700073242187</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3924259348722057</v>
+        <v>0.2256067345598003</v>
       </c>
       <c r="P32" t="n">
-        <v>33.79230807377742</v>
+        <v>33.79000032865084</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.853854529460813</v>
+        <v>-4.024859456192143</v>
       </c>
       <c r="S32" t="n">
-        <v>33.87380016326905</v>
+        <v>33.87260013580322</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-4.085158671694493</v>
+        <v>-4.258899006405536</v>
       </c>
       <c r="V32" t="n">
-        <v>32.21119045257569</v>
+        <v>32.21079044342041</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0.8655725602616368</v>
+        <v>0.6805479118571311</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.31664270401001</v>
+        <v>31.31634269714355</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.746758506481093</v>
+        <v>3.556154748982891</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2030240573030265</v>
+        <v>0.2030314712825135</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9744,13 +9744,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
       <c r="CA32" t="n">
         <v>0.67</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CC32" t="n">
         <v>2</v>
@@ -9781,13 +9781,13 @@
         <v>7</v>
       </c>
       <c r="CM32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN32" t="n">
         <v>1</v>
       </c>
       <c r="CO32" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>74.05000305175781</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="D33" t="n">
-        <v>74.05000305175781</v>
+        <v>73.87000274658203</v>
       </c>
       <c r="E33" t="n">
         <v>74.55999755859375</v>
@@ -9815,46 +9815,46 @@
         <v>73.44999694824219</v>
       </c>
       <c r="H33" t="n">
-        <v>1415400</v>
+        <v>1829000</v>
       </c>
       <c r="I33" t="n">
-        <v>0.007483034717793435</v>
+        <v>0.00503405097390508</v>
       </c>
       <c r="J33" t="n">
-        <v>71.76333279079861</v>
+        <v>71.7433327568902</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>3.186404772511334</v>
+        <v>2.964275435737392</v>
       </c>
       <c r="M33" t="n">
-        <v>71.71199951171874</v>
+        <v>71.69399948120117</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>3.260268233989216</v>
+        <v>3.035126065119891</v>
       </c>
       <c r="P33" t="n">
-        <v>75.19846138587364</v>
+        <v>75.19153829721304</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.527236479244737</v>
+        <v>-1.757558869732546</v>
       </c>
       <c r="S33" t="n">
-        <v>77.58599975585938</v>
+        <v>77.58239974975587</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-4.557519030789472</v>
+        <v>-4.785102052976282</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
@@ -9867,28 +9867,30 @@
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
-        <v>0.4871847421422195</v>
+        <v>0.4866955403539115</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AF33" t="n">
         <v>71.8</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AG33" t="n">
         <v>74</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
         <v>74.7</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AI33" t="n">
         <v>75.8</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>77.7</v>
       </c>
       <c r="AJ33" t="n">
         <v>1</v>
@@ -10015,13 +10017,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>32.34</v>
+        <v>32.26</v>
       </c>
       <c r="CA33" t="n">
         <v>0.05</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC33" t="n">
         <v>8</v>
@@ -10075,10 +10077,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.15999984741211</v>
+        <v>25.28000068664551</v>
       </c>
       <c r="D34" t="n">
-        <v>25.15999984741211</v>
+        <v>25.28000068664551</v>
       </c>
       <c r="E34" t="n">
         <v>25.53000068664551</v>
@@ -10090,67 +10092,67 @@
         <v>25.28000068664551</v>
       </c>
       <c r="H34" t="n">
-        <v>827200</v>
+        <v>1530000</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0007955631761831228</v>
+        <v>0.005568866364201952</v>
       </c>
       <c r="J34" t="n">
-        <v>25.05222172207302</v>
+        <v>25.06555514865451</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4302138410507655</v>
+        <v>0.8555387531582547</v>
       </c>
       <c r="M34" t="n">
-        <v>25.05299949645996</v>
+        <v>25.0649995803833</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.4270959689568022</v>
+        <v>0.8577742264574942</v>
       </c>
       <c r="P34" t="n">
-        <v>26.19615364074707</v>
+        <v>26.20076905764066</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.955366148575588</v>
+        <v>-3.514279939529642</v>
       </c>
       <c r="S34" t="n">
-        <v>25.82719989776611</v>
+        <v>25.82959991455078</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-2.583323213492119</v>
+        <v>-2.127788388993445</v>
       </c>
       <c r="V34" t="n">
-        <v>22.03760000864665</v>
+        <v>22.03840001424154</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>14.16851126048373</v>
+        <v>14.70887482897671</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.41440002441406</v>
+        <v>20.41500002861023</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>23.24633502489747</v>
+        <v>23.83051996677596</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2558273495481895</v>
+        <v>0.2567173629156684</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10302,13 +10304,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>37.55</v>
+        <v>37.73</v>
       </c>
       <c r="CA34" t="n">
         <v>0.38</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CC34" t="n">
         <v>10</v>
@@ -10339,13 +10341,13 @@
         <v>8</v>
       </c>
       <c r="CM34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35">
@@ -10358,10 +10360,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.59000015258789</v>
+        <v>48.61000061035156</v>
       </c>
       <c r="D35" t="n">
-        <v>48.59000015258789</v>
+        <v>48.61000061035156</v>
       </c>
       <c r="E35" t="n">
         <v>49.13000106811523</v>
@@ -10373,67 +10375,67 @@
         <v>48.56000137329102</v>
       </c>
       <c r="H35" t="n">
-        <v>946300</v>
+        <v>1442700</v>
       </c>
       <c r="I35" t="n">
-        <v>0.007255357834643705</v>
+        <v>0.007669961007690462</v>
       </c>
       <c r="J35" t="n">
-        <v>48.36000061035156</v>
+        <v>48.36222288343642</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.475598716570521</v>
+        <v>0.5123373413011737</v>
       </c>
       <c r="M35" t="n">
-        <v>48.37000045776367</v>
+        <v>48.37200050354004</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.4548267371142976</v>
+        <v>0.492020392652788</v>
       </c>
       <c r="P35" t="n">
-        <v>51.08346176147461</v>
+        <v>51.08423100985014</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-4.881152378688638</v>
+        <v>-4.843432798315959</v>
       </c>
       <c r="S35" t="n">
-        <v>52.28779998779297</v>
+        <v>52.28819999694824</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-7.072012660827875</v>
+        <v>-7.034473144631784</v>
       </c>
       <c r="V35" t="n">
-        <v>50.43966044108073</v>
+        <v>50.43979377746582</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-3.667075218822</v>
+        <v>-3.627677732361641</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.90592699050903</v>
+        <v>48.90602699279785</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.6459888552617565</v>
+        <v>-0.6052963216371675</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2439562673615679</v>
+        <v>0.2441527515813177</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10585,7 +10587,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.85</v>
+        <v>12.86</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
@@ -10656,7 +10658,7 @@
         <v>38.15000152587891</v>
       </c>
       <c r="H36" t="n">
-        <v>5516200</v>
+        <v>6590300</v>
       </c>
       <c r="I36" t="n">
         <v>0.01526712268312891</v>
@@ -10924,10 +10926,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15.73999977111816</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="D37" t="n">
-        <v>15.73999977111816</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="E37" t="n">
         <v>16.11000061035156</v>
@@ -10939,67 +10941,67 @@
         <v>16.05999946594238</v>
       </c>
       <c r="H37" t="n">
-        <v>1404700</v>
+        <v>1874500</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01501875957404297</v>
+        <v>-0.01752188616971684</v>
       </c>
       <c r="J37" t="n">
-        <v>15.75666639539931</v>
+        <v>15.75222195519341</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.1057750660127429</v>
+        <v>-0.3315224104689484</v>
       </c>
       <c r="M37" t="n">
-        <v>15.74099979400635</v>
+        <v>15.73699979782105</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.006352982029540552</v>
+        <v>-0.2351146281455246</v>
       </c>
       <c r="P37" t="n">
-        <v>16.04769218884982</v>
+        <v>16.04615372877855</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.917362410187808</v>
+        <v>-2.157239207378318</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06899993896484</v>
+        <v>16.06819993972778</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-2.047421551411577</v>
+        <v>-2.291483376132825</v>
       </c>
       <c r="V37" t="n">
-        <v>15.85553336461385</v>
+        <v>15.8552666982015</v>
       </c>
       <c r="W37" t="n">
         <v>-1</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.7286641883238918</v>
+        <v>-0.9792764252522635</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.70130000591278</v>
+        <v>15.70110000610352</v>
       </c>
       <c r="Z37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.2464749109360967</v>
+        <v>-0.007007132226097492</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2599046324962219</v>
+        <v>0.2609479690542923</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11147,7 +11149,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
       <c r="CA37" t="n">
         <v>0.37</v>
@@ -11207,10 +11209,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23.54000091552734</v>
+        <v>23.59000015258789</v>
       </c>
       <c r="D38" t="n">
-        <v>23.54000091552734</v>
+        <v>23.59000015258789</v>
       </c>
       <c r="E38" t="n">
         <v>24.04000091552734</v>
@@ -11222,67 +11224,67 @@
         <v>23.80999946594238</v>
       </c>
       <c r="H38" t="n">
-        <v>4307100</v>
+        <v>7061500</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0084245517067838</v>
+        <v>-0.006318433865899253</v>
       </c>
       <c r="J38" t="n">
-        <v>23.59222242567274</v>
+        <v>23.59777789645725</v>
       </c>
       <c r="K38" t="n">
         <v>-1</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.2213505332527475</v>
+        <v>-0.03295964519831213</v>
       </c>
       <c r="M38" t="n">
-        <v>23.56700019836426</v>
+        <v>23.57200012207031</v>
       </c>
       <c r="N38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.1145639352045694</v>
+        <v>0.07636191423876411</v>
       </c>
       <c r="P38" t="n">
-        <v>23.18961546971248</v>
+        <v>23.19153851729173</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.510958412710625</v>
+        <v>1.718133684831072</v>
       </c>
       <c r="S38" t="n">
-        <v>21.44960010528564</v>
+        <v>21.45060009002686</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>9.745640011846097</v>
+        <v>9.973614041481836</v>
       </c>
       <c r="V38" t="n">
-        <v>20.65433335622152</v>
+        <v>20.65466668446859</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>13.9712452081471</v>
+        <v>14.21147827249397</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.70670003890991</v>
+        <v>19.70695003509521</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>19.4517644712142</v>
+        <v>19.70396286882307</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.2557235605281427</v>
+        <v>0.2549780755147054</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11432,7 +11434,7 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>28.36</v>
+        <v>28.42</v>
       </c>
       <c r="CA38" t="n">
         <v>0.18</v>
@@ -11488,10 +11490,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.23999977111816</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="D39" t="n">
-        <v>10.23999977111816</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="E39" t="n">
         <v>10.4399995803833</v>
@@ -11503,67 +11505,67 @@
         <v>10.30000019073486</v>
       </c>
       <c r="H39" t="n">
-        <v>3490000</v>
+        <v>5332600</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.007751930820906638</v>
+        <v>-0.003875965410453319</v>
       </c>
       <c r="J39" t="n">
-        <v>10.25111103057861</v>
+        <v>10.25555547078451</v>
       </c>
       <c r="K39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.1083907824947444</v>
+        <v>0.2383514209086104</v>
       </c>
       <c r="M39" t="n">
-        <v>10.24199991226196</v>
+        <v>10.24599990844727</v>
       </c>
       <c r="N39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.01952881430319993</v>
+        <v>0.3318351047016421</v>
       </c>
       <c r="P39" t="n">
-        <v>10.10192309893095</v>
+        <v>10.10346155900222</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.366835510773488</v>
+        <v>1.747303861533268</v>
       </c>
       <c r="S39" t="n">
-        <v>9.443199987411498</v>
+        <v>9.44399998664856</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>8.437815409700741</v>
+        <v>8.852178605511698</v>
       </c>
       <c r="V39" t="n">
-        <v>9.090210371017456</v>
+        <v>9.09047703742981</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>12.64865556650494</v>
+        <v>13.08537154478859</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.611027512550354</v>
+        <v>8.611227512359619</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>18.91728084939485</v>
+        <v>19.37902834661374</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.2581919418932079</v>
+        <v>0.2570934611462297</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11719,10 +11721,10 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.81</v>
+        <v>23.91</v>
       </c>
       <c r="CA39" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="CB39" t="n">
         <v>0.72</v>
@@ -11760,13 +11762,13 @@
         <v>10</v>
       </c>
       <c r="CM39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
       </c>
       <c r="CO39" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
@@ -11779,13 +11781,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.65999984741211</v>
+        <v>12.67000007629395</v>
       </c>
       <c r="D40" t="n">
-        <v>12.65999984741211</v>
+        <v>12.67000007629395</v>
       </c>
       <c r="E40" t="n">
-        <v>12.68000030517578</v>
+        <v>12.78999996185303</v>
       </c>
       <c r="F40" t="n">
         <v>12.3100004196167</v>
@@ -11794,67 +11796,67 @@
         <v>12.5</v>
       </c>
       <c r="H40" t="n">
-        <v>2530700</v>
+        <v>3733900</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02096776103874221</v>
+        <v>0.02177423113466781</v>
       </c>
       <c r="J40" t="n">
-        <v>12.58444446987576</v>
+        <v>12.58555560641819</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6003870708572975</v>
+        <v>0.670963384665318</v>
       </c>
       <c r="M40" t="n">
-        <v>12.5710000038147</v>
+        <v>12.57200002670288</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7079774367226518</v>
+        <v>0.7795104150724842</v>
       </c>
       <c r="P40" t="n">
-        <v>12.45384616118211</v>
+        <v>12.45423078536987</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.655341519092858</v>
+        <v>1.732497932971813</v>
       </c>
       <c r="S40" t="n">
-        <v>11.63419998168945</v>
+        <v>11.63439998626709</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>8.817107040768732</v>
+        <v>8.901190360046487</v>
       </c>
       <c r="V40" t="n">
-        <v>15.08806667327881</v>
+        <v>15.08813334147135</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-16.09263054336074</v>
+        <v>-16.02672252723874</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.72414998054504</v>
+        <v>20.72419998168945</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-38.91184989832257</v>
+        <v>-38.86374341355358</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6906209013789741</v>
+        <v>0.6908385029892367</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12002,7 +12004,7 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-14.89</v>
+        <v>-14.91</v>
       </c>
       <c r="CA40" t="n">
         <v>0.78</v>
@@ -12062,10 +12064,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22.52000045776367</v>
+        <v>22.59000015258789</v>
       </c>
       <c r="D41" t="n">
-        <v>22.52000045776367</v>
+        <v>22.59000015258789</v>
       </c>
       <c r="E41" t="n">
         <v>22.71999931335449</v>
@@ -12077,67 +12079,67 @@
         <v>22.51000022888184</v>
       </c>
       <c r="H41" t="n">
-        <v>485900</v>
+        <v>679900</v>
       </c>
       <c r="I41" t="n">
-        <v>0.002225240139614115</v>
+        <v>0.005340491450842144</v>
       </c>
       <c r="J41" t="n">
-        <v>22.56888877020942</v>
+        <v>22.57666651407878</v>
       </c>
       <c r="K41" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.2166181638073343</v>
+        <v>0.05905937663914449</v>
       </c>
       <c r="M41" t="n">
-        <v>22.61499996185303</v>
+        <v>22.62199993133545</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.4200729792155644</v>
+        <v>-0.1414542429700593</v>
       </c>
       <c r="P41" t="n">
-        <v>22.80923080444336</v>
+        <v>22.81192310039814</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-1.268040773314214</v>
+        <v>-0.9728375237525342</v>
       </c>
       <c r="S41" t="n">
-        <v>22.90020000457764</v>
+        <v>22.90159999847412</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.660245529462475</v>
+        <v>-1.360602953099314</v>
       </c>
       <c r="V41" t="n">
-        <v>23.66800004323323</v>
+        <v>23.6684667078654</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-4.850429201337525</v>
+        <v>-4.556554375020486</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.50284998893738</v>
+        <v>23.5031999874115</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-4.181831274234087</v>
+        <v>-3.885427666499563</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.297078971767285</v>
+        <v>0.297542770098788</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12285,13 +12287,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>9.42</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="CA41" t="n">
         <v>0.39</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CC41" t="n">
         <v>4</v>
@@ -12322,13 +12324,13 @@
         <v>8</v>
       </c>
       <c r="CM41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN41" t="n">
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42">
@@ -12341,10 +12343,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>26.31999969482422</v>
+        <v>26.23999977111816</v>
       </c>
       <c r="D42" t="n">
-        <v>26.31999969482422</v>
+        <v>26.23999977111816</v>
       </c>
       <c r="E42" t="n">
         <v>26.55999946594238</v>
@@ -12356,67 +12358,67 @@
         <v>26.13999938964844</v>
       </c>
       <c r="H42" t="n">
-        <v>763500</v>
+        <v>944200</v>
       </c>
       <c r="I42" t="n">
-        <v>0.006886010305228396</v>
+        <v>0.003825569388089756</v>
       </c>
       <c r="J42" t="n">
-        <v>26.28999964396159</v>
+        <v>26.2811107635498</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1141120246059782</v>
+        <v>-0.1564279105305507</v>
       </c>
       <c r="M42" t="n">
-        <v>26.30099964141846</v>
+        <v>26.29299964904785</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.07224080325768566</v>
+        <v>-0.2015741019933622</v>
       </c>
       <c r="P42" t="n">
-        <v>27.21923050513634</v>
+        <v>27.2161535849938</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-3.303659925810315</v>
+        <v>-3.586670727835179</v>
       </c>
       <c r="S42" t="n">
-        <v>27.67799983978271</v>
+        <v>27.67639984130859</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-4.90642442669064</v>
+        <v>-5.189981639326231</v>
       </c>
       <c r="V42" t="n">
-        <v>26.96553321838379</v>
+        <v>26.96499988555908</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.393920855677639</v>
+        <v>-2.688670934611002</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.02934989929199</v>
+        <v>26.02894989967346</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.116623337335563</v>
+        <v>0.8108274527331127</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.297205258887672</v>
+        <v>0.2963959231765822</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12568,10 +12570,10 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>10.97</v>
+        <v>10.93</v>
       </c>
       <c r="CA42" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="CB42" t="n">
         <v>1.6</v>
@@ -12624,82 +12626,82 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.21999931335449</v>
+        <v>27.09000015258789</v>
       </c>
       <c r="D43" t="n">
-        <v>27.21999931335449</v>
+        <v>27.09000015258789</v>
       </c>
       <c r="E43" t="n">
         <v>27.53000068664551</v>
       </c>
       <c r="F43" t="n">
-        <v>27.1200008392334</v>
+        <v>27.05999946594238</v>
       </c>
       <c r="G43" t="n">
         <v>27.3799991607666</v>
       </c>
       <c r="H43" t="n">
-        <v>548800</v>
+        <v>908900</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.005843676125504627</v>
+        <v>-0.01059163685418429</v>
       </c>
       <c r="J43" t="n">
-        <v>28.00111113654243</v>
+        <v>27.98666678534614</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.789574382884244</v>
+        <v>-3.20390648745546</v>
       </c>
       <c r="M43" t="n">
-        <v>28.05500011444092</v>
+        <v>28.04200019836426</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-2.97629940360122</v>
+        <v>-3.394907777769354</v>
       </c>
       <c r="P43" t="n">
-        <v>28.99846150324895</v>
+        <v>28.99346153552716</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-6.132953604091026</v>
+        <v>-6.565140145845843</v>
       </c>
       <c r="S43" t="n">
-        <v>29.19360000610352</v>
+        <v>29.19100002288818</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-6.760388209526753</v>
+        <v>-7.197423413562169</v>
       </c>
       <c r="V43" t="n">
-        <v>27.97579995473226</v>
+        <v>27.97493329366048</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-2.701622983438297</v>
+        <v>-3.163307421623517</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.80619999885559</v>
+        <v>26.80555000305176</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.543670175245161</v>
+        <v>1.061161399425679</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2438030358937209</v>
+        <v>0.2443716355759988</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12851,13 +12853,13 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>7.65</v>
+        <v>7.61</v>
       </c>
       <c r="CA43" t="n">
         <v>0.84</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="CC43" t="n">
         <v>7</v>
@@ -12885,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="CL43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM43" t="n">
         <v>2</v>
@@ -12894,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44">
@@ -12907,10 +12909,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12.97999954223633</v>
+        <v>13.03999996185303</v>
       </c>
       <c r="D44" t="n">
-        <v>12.97999954223633</v>
+        <v>13.03999996185303</v>
       </c>
       <c r="E44" t="n">
         <v>13.10000038146973</v>
@@ -12922,67 +12924,67 @@
         <v>13.06999969482422</v>
       </c>
       <c r="H44" t="n">
-        <v>10577600</v>
+        <v>17422000</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.006886010305228285</v>
+        <v>-0.002295312446187081</v>
       </c>
       <c r="J44" t="n">
-        <v>12.94555536905924</v>
+        <v>12.95222208234999</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2660694902237091</v>
+        <v>0.6777051763392278</v>
       </c>
       <c r="M44" t="n">
-        <v>12.94699983596802</v>
+        <v>12.95299987792969</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.2548830361195608</v>
+        <v>0.6716597293540976</v>
       </c>
       <c r="P44" t="n">
-        <v>13.38076921609732</v>
+        <v>13.38307692454412</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.995116853064449</v>
+        <v>-2.563513343197602</v>
       </c>
       <c r="S44" t="n">
-        <v>13.69659999847412</v>
+        <v>13.69780000686645</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-5.231958707399103</v>
+        <v>-4.802231341410187</v>
       </c>
       <c r="V44" t="n">
-        <v>12.91424167633057</v>
+        <v>12.91464167912801</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.5091887511001364</v>
+        <v>0.9706679119685894</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.40592623710632</v>
+        <v>12.40622623920441</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.627411884917892</v>
+        <v>5.108513341840062</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2328987614475061</v>
+        <v>0.2328406045197276</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13134,13 +13136,13 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
       </c>
       <c r="CB44" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CC44" t="n">
         <v>2</v>
@@ -13168,16 +13170,16 @@
         <v>0</v>
       </c>
       <c r="CL44" t="n">
+        <v>7</v>
+      </c>
+      <c r="CM44" t="n">
         <v>6</v>
       </c>
-      <c r="CM44" t="n">
-        <v>5</v>
-      </c>
       <c r="CN44" t="n">
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -13190,10 +13192,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40.20999908447266</v>
+        <v>40.22000122070312</v>
       </c>
       <c r="D45" t="n">
-        <v>40.20999908447266</v>
+        <v>40.22000122070312</v>
       </c>
       <c r="E45" t="n">
         <v>40.45000076293945</v>
@@ -13205,67 +13207,67 @@
         <v>40.31999969482422</v>
       </c>
       <c r="H45" t="n">
-        <v>9322500</v>
+        <v>12330200</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.002728189761511457</v>
+        <v>-0.002480120904711502</v>
       </c>
       <c r="J45" t="n">
-        <v>39.83666610717773</v>
+        <v>39.83777745564779</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.9371591897035156</v>
+        <v>0.9594505252730871</v>
       </c>
       <c r="M45" t="n">
-        <v>39.82299957275391</v>
+        <v>39.82399978637695</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9717990002529239</v>
+        <v>0.9943788581016365</v>
       </c>
       <c r="P45" t="n">
-        <v>41.34153820918156</v>
+        <v>41.34192290672889</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.737051338011424</v>
+        <v>-2.713762706579762</v>
       </c>
       <c r="S45" t="n">
-        <v>42.62639976501465</v>
+        <v>42.62659980773926</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-5.668789045903042</v>
+        <v>-5.645767192060191</v>
       </c>
       <c r="V45" t="n">
-        <v>41.85565539042155</v>
+        <v>41.85572207132975</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-3.931741817440255</v>
+        <v>-3.907998165314317</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.57528512954712</v>
+        <v>40.57533514022827</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-0.900267352178037</v>
+        <v>-0.8757387173688416</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2342033922937639</v>
+        <v>0.2342230921467793</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13474,13 +13476,13 @@
         <v>5</v>
       </c>
       <c r="CM45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN45" t="n">
         <v>0</v>
       </c>
       <c r="CO45" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
@@ -13493,10 +13495,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.75</v>
+        <v>16.71999931335449</v>
       </c>
       <c r="D46" t="n">
-        <v>16.75</v>
+        <v>16.71999931335449</v>
       </c>
       <c r="E46" t="n">
         <v>16.94000053405762</v>
@@ -13508,67 +13510,67 @@
         <v>16.82999992370605</v>
       </c>
       <c r="H46" t="n">
-        <v>2064400</v>
+        <v>2995900</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.001787883517155309</v>
+        <v>-0.003575767034310617</v>
       </c>
       <c r="J46" t="n">
-        <v>16.50888888041179</v>
+        <v>16.5055554707845</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.460492715983445</v>
+        <v>1.299222210058682</v>
       </c>
       <c r="M46" t="n">
-        <v>16.50100002288819</v>
+        <v>16.49799995422363</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.508999313777543</v>
+        <v>1.345613769831687</v>
       </c>
       <c r="P46" t="n">
-        <v>17.07923089540922</v>
+        <v>17.07807702284593</v>
       </c>
       <c r="Q46" t="n">
         <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.927668156870652</v>
+        <v>-2.096709770148145</v>
       </c>
       <c r="S46" t="n">
-        <v>18.03560005187988</v>
+        <v>18.03500003814697</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-7.128124643382086</v>
+        <v>-7.291381879739609</v>
       </c>
       <c r="V46" t="n">
-        <v>18.50388830820719</v>
+        <v>18.50368830362956</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.478485164814128</v>
+        <v>-9.639640276069649</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.37539130210876</v>
+        <v>18.37524129867554</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-8.845478582664159</v>
+        <v>-9.008001355826288</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.1770329386397447</v>
+        <v>0.1768228070376764</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13724,7 +13726,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>27.92</v>
+        <v>27.87</v>
       </c>
       <c r="CA46" t="n">
         <v>0.24</v>
@@ -13784,10 +13786,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.07999992370605</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="D47" t="n">
-        <v>15.07999992370605</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="E47" t="n">
         <v>15.22000026702881</v>
@@ -13799,88 +13801,88 @@
         <v>15</v>
       </c>
       <c r="H47" t="n">
-        <v>2300400</v>
+        <v>3815300</v>
       </c>
       <c r="I47" t="n">
-        <v>0.01412239675609639</v>
+        <v>0.01882984096342266</v>
       </c>
       <c r="J47" t="n">
-        <v>14.71444447835287</v>
+        <v>14.72222222222222</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>2.484330590196429</v>
+        <v>2.905657786243372</v>
       </c>
       <c r="M47" t="n">
-        <v>14.59800004959106</v>
+        <v>14.60500001907349</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>3.301821293859309</v>
+        <v>3.731596020164613</v>
       </c>
       <c r="P47" t="n">
-        <v>14.23230776420006</v>
+        <v>14.23500006015484</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>5.956111781381479</v>
+        <v>6.427815627037504</v>
       </c>
       <c r="S47" t="n">
-        <v>14.70680004119873</v>
+        <v>14.70820003509522</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>2.537600847647785</v>
+        <v>3.003763767020307</v>
       </c>
       <c r="V47" t="n">
-        <v>14.68106669743856</v>
+        <v>14.68153336207072</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>2.717331338989827</v>
+        <v>3.190853740589667</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.92770001888275</v>
+        <v>14.92805001735687</v>
       </c>
       <c r="Z47" t="n">
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.020250304002976</v>
+        <v>1.486795669329484</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4709200403827994</v>
+        <v>0.4724164629054139</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="AE47" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="AF47" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AG47" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="AH47" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="AI47" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14007,13 +14009,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>10.19</v>
+        <v>10.24</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14063,82 +14065,82 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.07999992370605</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="D48" t="n">
-        <v>16.07999992370605</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="E48" t="n">
         <v>16.46999931335449</v>
       </c>
       <c r="F48" t="n">
-        <v>16.04999923706055</v>
+        <v>16.01000022888184</v>
       </c>
       <c r="G48" t="n">
         <v>16.25</v>
       </c>
       <c r="H48" t="n">
-        <v>1777800</v>
+        <v>2523600</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.01289140454382176</v>
+        <v>-0.01657461280473671</v>
       </c>
       <c r="J48" t="n">
-        <v>16.65000004238552</v>
+        <v>16.64333343505859</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-3.423424127498101</v>
+        <v>-3.745241178560378</v>
       </c>
       <c r="M48" t="n">
-        <v>16.72700004577637</v>
+        <v>16.72100009918213</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-3.867998566985616</v>
+        <v>-4.192330825072739</v>
       </c>
       <c r="P48" t="n">
-        <v>17.27692317962646</v>
+        <v>17.27461550785945</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-6.927872766904832</v>
+        <v>-7.262766858833794</v>
       </c>
       <c r="S48" t="n">
-        <v>18.47160011291504</v>
+        <v>18.47040012359619</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-12.94744458839175</v>
+        <v>-13.26663011865185</v>
       </c>
       <c r="V48" t="n">
-        <v>18.87353340148926</v>
+        <v>18.87313340504964</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-14.80132743751508</v>
+        <v>-15.11743114433025</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.54230003833771</v>
+        <v>19.542000041008</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-17.71695300880336</v>
+        <v>-18.02271812431464</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.4802221106838468</v>
+        <v>0.4805501578311729</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14286,10 +14288,10 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>59.56</v>
+        <v>59.33</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CB48" t="n">
         <v>1.97</v>
@@ -14346,82 +14348,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.559999942779541</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="D49" t="n">
-        <v>6.559999942779541</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="E49" t="n">
         <v>6.710000038146973</v>
       </c>
       <c r="F49" t="n">
-        <v>6.519999980926514</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="G49" t="n">
         <v>6.650000095367432</v>
       </c>
       <c r="H49" t="n">
-        <v>8001000</v>
+        <v>11332600</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.006060600368335001</v>
+        <v>-0.01212120073667011</v>
       </c>
       <c r="J49" t="n">
-        <v>6.645555549197727</v>
+        <v>6.641111108991835</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.287410898679715</v>
+        <v>-1.82365760906094</v>
       </c>
       <c r="M49" t="n">
-        <v>6.659999990463257</v>
+        <v>6.655999994277954</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.501502219623282</v>
+        <v>-2.043269433118343</v>
       </c>
       <c r="P49" t="n">
-        <v>7.4380768262423</v>
+        <v>7.43653836617103</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-11.80516017749122</v>
+        <v>-12.3247987183643</v>
       </c>
       <c r="S49" t="n">
-        <v>8.125799961090088</v>
+        <v>8.124999961853028</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-19.2694876296277</v>
+        <v>-19.75384601184011</v>
       </c>
       <c r="V49" t="n">
-        <v>8.840247408548992</v>
+        <v>8.839980742136637</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-25.79393268523604</v>
+        <v>-26.24418343075915</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.722137818336487</v>
+        <v>8.721937818527222</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-24.78908176630159</v>
+        <v>-25.24597037281476</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4311984892819773</v>
+        <v>0.4309502561948493</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14569,10 +14571,10 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>36.44</v>
+        <v>36.22</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="CB49" t="n">
         <v>0.45</v>
@@ -14629,10 +14631,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.34000015258789</v>
+        <v>14.27000045776367</v>
       </c>
       <c r="D50" t="n">
-        <v>14.34000015258789</v>
+        <v>14.27000045776367</v>
       </c>
       <c r="E50" t="n">
         <v>14.56999969482422</v>
@@ -14644,67 +14646,67 @@
         <v>14.48999977111816</v>
       </c>
       <c r="H50" t="n">
-        <v>3217100</v>
+        <v>4264400</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0006978526821408426</v>
+        <v>-0.004186982991055466</v>
       </c>
       <c r="J50" t="n">
-        <v>14.67111110687256</v>
+        <v>14.6633333630032</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.256890782659003</v>
+        <v>-2.682424899593022</v>
       </c>
       <c r="M50" t="n">
-        <v>14.675</v>
+        <v>14.66800003051758</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-2.282792827339762</v>
+        <v>-2.7133867734241</v>
       </c>
       <c r="P50" t="n">
-        <v>15.34153839258047</v>
+        <v>15.33884609662569</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.528277766960774</v>
+        <v>-6.968227154304336</v>
       </c>
       <c r="S50" t="n">
-        <v>15.72180004119873</v>
+        <v>15.72040004730225</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-8.789069222289141</v>
+        <v>-9.226225701473002</v>
       </c>
       <c r="V50" t="n">
-        <v>15.84373336156209</v>
+        <v>15.84326669692993</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.49102824857148</v>
+        <v>-9.930188447002056</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.43530001163483</v>
+        <v>15.43495001316071</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-7.096071072290918</v>
+        <v>-7.547478640382585</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.3003152155557279</v>
+        <v>0.2996307971375527</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14852,13 +14854,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="CB50" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CC50" t="n">
         <v>5</v>
@@ -14893,13 +14895,13 @@
         <v>4</v>
       </c>
       <c r="CM50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN50" t="n">
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -14912,10 +14914,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="E51" t="n">
         <v>6.070000171661377</v>
@@ -14927,67 +14929,67 @@
         <v>5.980000019073486</v>
       </c>
       <c r="H51" t="n">
-        <v>3832500</v>
+        <v>5041900</v>
       </c>
       <c r="I51" t="n">
-        <v>0.005025160948521012</v>
+        <v>0.006700241222102443</v>
       </c>
       <c r="J51" t="n">
-        <v>6.148888905843099</v>
+        <v>6.150000042385525</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.421395281700636</v>
+        <v>-2.276419716078316</v>
       </c>
       <c r="M51" t="n">
-        <v>6.155999994277954</v>
+        <v>6.157000017166138</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.534112969833608</v>
+        <v>-2.387522947449349</v>
       </c>
       <c r="P51" t="n">
-        <v>6.569615400754488</v>
+        <v>6.570000024942251</v>
       </c>
       <c r="Q51" t="n">
         <v>-1</v>
       </c>
       <c r="R51" t="n">
-        <v>-8.670452773979289</v>
+        <v>-8.523588948773824</v>
       </c>
       <c r="S51" t="n">
-        <v>7.135200004577637</v>
+        <v>7.135400009155274</v>
       </c>
       <c r="T51" t="n">
         <v>-1</v>
       </c>
       <c r="U51" t="n">
-        <v>-15.90985541889984</v>
+        <v>-15.77206293731903</v>
       </c>
       <c r="V51" t="n">
-        <v>7.953600025177002</v>
+        <v>7.953666693369548</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-24.56246252002753</v>
+        <v>-24.43736378981055</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.785650007724762</v>
+        <v>7.785700008869171</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-22.93514357764704</v>
+        <v>-22.80719495953513</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.443106022216424</v>
+        <v>0.4435863687856374</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15139,10 +15141,10 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>-4.44</v>
+        <v>-4.45</v>
       </c>
       <c r="CA51" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CB51" t="n">
         <v>0.65</v>
@@ -15199,10 +15201,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30.14999961853027</v>
+        <v>30.07999992370605</v>
       </c>
       <c r="D52" t="n">
-        <v>30.14999961853027</v>
+        <v>30.07999992370605</v>
       </c>
       <c r="E52" t="n">
         <v>30.29999923706055</v>
@@ -15214,67 +15216,67 @@
         <v>29.86000061035156</v>
       </c>
       <c r="H52" t="n">
-        <v>1200400</v>
+        <v>1485700</v>
       </c>
       <c r="I52" t="n">
-        <v>0.01242440978353265</v>
+        <v>0.01007384923248433</v>
       </c>
       <c r="J52" t="n">
-        <v>29.89222229851617</v>
+        <v>29.88444455464681</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.8623558243339525</v>
+        <v>0.6543717709112936</v>
       </c>
       <c r="M52" t="n">
-        <v>29.85</v>
+        <v>29.84300003051758</v>
       </c>
       <c r="N52" t="n">
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>1.005023847672603</v>
+        <v>0.7941557247800759</v>
       </c>
       <c r="P52" t="n">
-        <v>30.95538440117469</v>
+        <v>30.95269210521991</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.601759914226277</v>
+        <v>-2.819438705193228</v>
       </c>
       <c r="S52" t="n">
-        <v>31.60199996948242</v>
+        <v>31.60059997558594</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-4.594647023461561</v>
+        <v>-4.81193411851253</v>
       </c>
       <c r="V52" t="n">
-        <v>30.60846669514974</v>
+        <v>30.60800003051758</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-1.49784398279616</v>
+        <v>-1.725039552682572</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.87335004806518</v>
+        <v>29.87300004959106</v>
       </c>
       <c r="Z52" t="n">
         <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.9260748125669526</v>
+        <v>0.6929329955858428</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.2985904900142977</v>
+        <v>0.2975333908875565</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15426,13 +15428,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>12.67</v>
+        <v>12.64</v>
       </c>
       <c r="CA52" t="n">
         <v>0.29</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15464,16 +15466,16 @@
         <v>0</v>
       </c>
       <c r="CL52" t="n">
+        <v>6</v>
+      </c>
+      <c r="CM52" t="n">
         <v>7</v>
       </c>
-      <c r="CM52" t="n">
-        <v>8</v>
-      </c>
       <c r="CN52" t="n">
         <v>0</v>
       </c>
       <c r="CO52" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
@@ -15486,10 +15488,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10.27999973297119</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="D53" t="n">
-        <v>10.27999973297119</v>
+        <v>10.23999977111816</v>
       </c>
       <c r="E53" t="n">
         <v>10.32999992370605</v>
@@ -15501,67 +15503,67 @@
         <v>10.02000045776367</v>
       </c>
       <c r="H53" t="n">
-        <v>6512500</v>
+        <v>7993600</v>
       </c>
       <c r="I53" t="n">
-        <v>0.03109322544028048</v>
+        <v>0.02708119326558633</v>
       </c>
       <c r="J53" t="n">
-        <v>10.10777770148383</v>
+        <v>10.10333326127794</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1.703856540711968</v>
+        <v>1.352687338979619</v>
       </c>
       <c r="M53" t="n">
-        <v>10.09099988937378</v>
+        <v>10.08699989318848</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>1.872954570105938</v>
+        <v>1.516802612767002</v>
       </c>
       <c r="P53" t="n">
-        <v>10.17153838964609</v>
+        <v>10.16999992957482</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>1.066321918771971</v>
+        <v>0.6882973650745245</v>
       </c>
       <c r="S53" t="n">
-        <v>10.07359994888306</v>
+        <v>10.072799949646</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>2.04891781622735</v>
+        <v>1.65991404880472</v>
       </c>
       <c r="V53" t="n">
-        <v>8.925466616948446</v>
+        <v>8.925199950536092</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>15.1760482017897</v>
+        <v>14.73132061879576</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.909999954700471</v>
+        <v>8.909799954891206</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>15.37597963227797</v>
+        <v>14.92962606300403</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3472383607795378</v>
+        <v>0.3442832587239385</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15713,7 +15715,7 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>-6.08</v>
+        <v>-6.06</v>
       </c>
       <c r="CA53" t="n">
         <v>0.28</v>
@@ -15734,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="CG53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CH53" t="n">
         <v>8</v>
@@ -15773,10 +15775,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47.7400016784668</v>
+        <v>47.59000015258789</v>
       </c>
       <c r="D54" t="n">
-        <v>47.7400016784668</v>
+        <v>47.59000015258789</v>
       </c>
       <c r="E54" t="n">
         <v>48.58000183105469</v>
@@ -15788,67 +15790,67 @@
         <v>48.38000106811523</v>
       </c>
       <c r="H54" t="n">
-        <v>2742700</v>
+        <v>3705200</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.007484341103419889</v>
+        <v>-0.01060287604390664</v>
       </c>
       <c r="J54" t="n">
-        <v>49.66777759128146</v>
+        <v>49.6511107550727</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.881341196053562</v>
+        <v>-4.151187297001674</v>
       </c>
       <c r="M54" t="n">
-        <v>49.74599990844727</v>
+        <v>49.73099975585937</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-4.032481473228636</v>
+        <v>-4.305160993710419</v>
       </c>
       <c r="P54" t="n">
-        <v>51.11423096290002</v>
+        <v>51.10846167344313</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-6.601349997581534</v>
+        <v>-6.884303314266052</v>
       </c>
       <c r="S54" t="n">
-        <v>51.79420013427735</v>
+        <v>51.79120010375976</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-7.827514365121909</v>
+        <v>-8.111802666775601</v>
       </c>
       <c r="V54" t="n">
-        <v>41.50946676890055</v>
+        <v>41.50846675872803</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>15.00991314644939</v>
+        <v>14.65130819986526</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.46885006904602</v>
+        <v>39.46810006141663</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>20.9561504704378</v>
+        <v>20.57839135537994</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3448245861522921</v>
+        <v>0.3452993455497884</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16000,7 +16002,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.72</v>
+        <v>5.7</v>
       </c>
       <c r="CA54" t="n">
         <v>0.53</v>
@@ -16056,10 +16058,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>42.52999877929688</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="D55" t="n">
-        <v>42.52999877929688</v>
+        <v>42.43999862670898</v>
       </c>
       <c r="E55" t="n">
         <v>43.18000030517578</v>
@@ -16071,67 +16073,67 @@
         <v>43.09999847412109</v>
       </c>
       <c r="H55" t="n">
-        <v>24316600</v>
+        <v>28946300</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.006772557627140685</v>
+        <v>-0.00887438278429431</v>
       </c>
       <c r="J55" t="n">
-        <v>44.3055551317003</v>
+        <v>44.29555511474609</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.007525347838446</v>
+        <v>-4.189035408248875</v>
       </c>
       <c r="M55" t="n">
-        <v>44.42199974060058</v>
+        <v>44.4129997253418</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-4.259153060087178</v>
+        <v>-4.442395494189128</v>
       </c>
       <c r="P55" t="n">
-        <v>46.09961524376502</v>
+        <v>46.09615369943472</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-7.743267369136965</v>
+        <v>-7.931583829239475</v>
       </c>
       <c r="S55" t="n">
-        <v>46.8773998260498</v>
+        <v>46.87559982299805</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-9.273980773005833</v>
+        <v>-9.462494801213987</v>
       </c>
       <c r="V55" t="n">
-        <v>38.35326675415039</v>
+        <v>38.35266675313314</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>10.89015976636332</v>
+        <v>10.65722991281159</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.49130004882812</v>
+        <v>36.49085004806518</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.54832445648282</v>
+        <v>16.30312412785034</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.3069416624846102</v>
+        <v>0.307181262088923</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16283,7 +16285,7 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="CA55" t="n">
         <v>0.59</v>
@@ -16343,10 +16345,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.269999980926514</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="D56" t="n">
-        <v>6.269999980926514</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="E56" t="n">
         <v>6.300000190734863</v>
@@ -16358,67 +16360,67 @@
         <v>6.21999979019165</v>
       </c>
       <c r="H56" t="n">
-        <v>2821300</v>
+        <v>3874100</v>
       </c>
       <c r="I56" t="n">
-        <v>0.008038616144924848</v>
+        <v>0.006430938913094986</v>
       </c>
       <c r="J56" t="n">
-        <v>6.061111026340061</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>3.446380600498387</v>
+        <v>3.3003347853261</v>
       </c>
       <c r="M56" t="n">
-        <v>6.059999942779541</v>
+        <v>6.058999967575073</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>3.46534719686238</v>
+        <v>3.317383435920476</v>
       </c>
       <c r="P56" t="n">
-        <v>6.269230769230769</v>
+        <v>6.268846163382897</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01226963441064862</v>
+        <v>-0.1411094525294241</v>
       </c>
       <c r="S56" t="n">
-        <v>6.308000001907349</v>
+        <v>6.307800006866455</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.6024099709788371</v>
+        <v>-0.757788419616762</v>
       </c>
       <c r="V56" t="n">
-        <v>6.363187745412191</v>
+        <v>6.363121080398559</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-1.464482398038067</v>
+        <v>-1.620601748949658</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.838890697956085</v>
+        <v>6.838840699195861</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-8.318464823536276</v>
+        <v>-8.464014527814458</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3201748658649307</v>
+        <v>0.3197188400441768</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16570,7 +16572,7 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>6.27</v>
+        <v>6.26</v>
       </c>
       <c r="CA56" t="n">
         <v>0.2</v>
@@ -16630,10 +16632,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.88000106811523</v>
+        <v>62.56000137329102</v>
       </c>
       <c r="D57" t="n">
-        <v>62.88000106811523</v>
+        <v>62.56000137329102</v>
       </c>
       <c r="E57" t="n">
         <v>63.95999908447266</v>
@@ -16645,67 +16647,67 @@
         <v>63.79999923706055</v>
       </c>
       <c r="H57" t="n">
-        <v>3748500</v>
+        <v>4777900</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.001587781436137248</v>
+        <v>-0.006668754715751457</v>
       </c>
       <c r="J57" t="n">
-        <v>66.4544440375434</v>
+        <v>66.41888851589627</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-5.37878695879057</v>
+        <v>-5.809924298389446</v>
       </c>
       <c r="M57" t="n">
-        <v>66.68899993896484</v>
+        <v>66.65699996948243</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-5.711584930551787</v>
+        <v>-6.146389123523622</v>
       </c>
       <c r="P57" t="n">
-        <v>65.82115408090445</v>
+        <v>65.80884640033429</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.468400856621383</v>
+        <v>-4.936790727616782</v>
       </c>
       <c r="S57" t="n">
-        <v>65.98739990234375</v>
+        <v>65.98099990844726</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-4.70907906483242</v>
+        <v>-5.184823721833697</v>
       </c>
       <c r="V57" t="n">
-        <v>51.69033322652181</v>
+        <v>51.68819989522298</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>21.64750571941006</v>
+        <v>21.03343026088399</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.22669996261597</v>
+        <v>48.22509996414185</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>30.38420857503854</v>
+        <v>29.72498018626814</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3904330820348221</v>
+        <v>0.3907938931024932</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16857,13 +16859,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>21.17</v>
+        <v>21.06</v>
       </c>
       <c r="CA57" t="n">
         <v>0.44</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CC57" t="n">
         <v>10</v>
@@ -16913,10 +16915,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.43999862670898</v>
+        <v>48.54999923706055</v>
       </c>
       <c r="D58" t="n">
-        <v>48.43999862670898</v>
+        <v>48.54999923706055</v>
       </c>
       <c r="E58" t="n">
         <v>48.88999938964844</v>
@@ -16928,67 +16930,67 @@
         <v>48.59000015258789</v>
       </c>
       <c r="H58" t="n">
-        <v>373900</v>
+        <v>498000</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.002060203686283235</v>
+        <v>0.0002059810742609525</v>
       </c>
       <c r="J58" t="n">
-        <v>48.81111102634006</v>
+        <v>48.82333331637912</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.7603031191623746</v>
+        <v>-0.5598431339117025</v>
       </c>
       <c r="M58" t="n">
-        <v>48.72199974060059</v>
+        <v>48.73299980163574</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.5787962632753111</v>
+        <v>-0.3755167244374167</v>
       </c>
       <c r="P58" t="n">
-        <v>49.78384648836576</v>
+        <v>49.78807728107159</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.699365268954915</v>
+        <v>-2.486695834871559</v>
       </c>
       <c r="S58" t="n">
-        <v>50.26500007629394</v>
+        <v>50.26720008850098</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.630759866338227</v>
+        <v>-3.416145813606306</v>
       </c>
       <c r="V58" t="n">
-        <v>49.24466669718424</v>
+        <v>49.24540003458659</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-1.634020746700006</v>
+        <v>-1.412113206589121</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.52534999847412</v>
+        <v>49.52590000152588</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.191506716860305</v>
+        <v>-1.970485674031693</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.2968778385810996</v>
+        <v>0.2969743641285346</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17140,7 +17142,7 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>8.5</v>
+        <v>8.52</v>
       </c>
       <c r="CA58" t="n">
         <v>-0.42</v>
@@ -17200,10 +17202,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>19.1200008392334</v>
+        <v>19.05999946594238</v>
       </c>
       <c r="D59" t="n">
-        <v>19.1200008392334</v>
+        <v>19.05999946594238</v>
       </c>
       <c r="E59" t="n">
         <v>19.43000030517578</v>
@@ -17215,67 +17217,67 @@
         <v>18.54999923706055</v>
       </c>
       <c r="H59" t="n">
-        <v>10014600</v>
+        <v>12750700</v>
       </c>
       <c r="I59" t="n">
-        <v>0.03351355887748109</v>
+        <v>0.03027024140229106</v>
       </c>
       <c r="J59" t="n">
-        <v>18.63666682773166</v>
+        <v>18.6300000084771</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>2.593457381459043</v>
+        <v>2.308102293449374</v>
       </c>
       <c r="M59" t="n">
-        <v>18.73200016021729</v>
+        <v>18.72600002288818</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>2.071325409446355</v>
+        <v>1.783613385912439</v>
       </c>
       <c r="P59" t="n">
-        <v>20.38615388136644</v>
+        <v>20.38384613623986</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-6.210848056485731</v>
+        <v>-6.494587240549507</v>
       </c>
       <c r="S59" t="n">
-        <v>21.77520004272461</v>
+        <v>21.77400001525879</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-12.19368455068843</v>
+        <v>-12.46440960510006</v>
       </c>
       <c r="V59" t="n">
-        <v>22.86843780517578</v>
+        <v>22.86803779602051</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-16.3913118940464</v>
+        <v>-16.65223034894931</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.57005375862122</v>
+        <v>21.56975375175476</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-11.35858513291174</v>
+        <v>-11.63552590677213</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3653622529964105</v>
+        <v>0.3623025691995039</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17427,13 +17429,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>25.84</v>
+        <v>25.76</v>
       </c>
       <c r="CA59" t="n">
         <v>0.09</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.56</v>
+        <v>4.55</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17487,10 +17489,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.84000015258789</v>
+        <v>13.85000038146973</v>
       </c>
       <c r="D60" t="n">
-        <v>13.84000015258789</v>
+        <v>13.85000038146973</v>
       </c>
       <c r="E60" t="n">
         <v>14.13000011444092</v>
@@ -17502,67 +17504,67 @@
         <v>14.13000011444092</v>
       </c>
       <c r="H60" t="n">
-        <v>4389400</v>
+        <v>6041800</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01494662172926198</v>
+        <v>-0.01423486167616028</v>
       </c>
       <c r="J60" t="n">
-        <v>14.43444442749023</v>
+        <v>14.43555556403266</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.11823453191057</v>
+        <v>-4.056339778303319</v>
       </c>
       <c r="M60" t="n">
-        <v>14.48800001144409</v>
+        <v>14.48900003433227</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-4.472666057042689</v>
+        <v>-4.41023984642427</v>
       </c>
       <c r="P60" t="n">
-        <v>15.39115395912757</v>
+        <v>15.39153858331534</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-10.07821642651938</v>
+        <v>-10.01549126165113</v>
       </c>
       <c r="S60" t="n">
-        <v>15.82920007705689</v>
+        <v>15.82940008163452</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-12.56664843950122</v>
+        <v>-12.50457812650348</v>
       </c>
       <c r="V60" t="n">
-        <v>15.62613337834676</v>
+        <v>15.62620004653931</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-11.43042352520763</v>
+        <v>-11.36680485197647</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.51200001239777</v>
+        <v>15.51205001354218</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-10.77875102161908</v>
+        <v>-10.71457112774561</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3146983527109977</v>
+        <v>0.3145387847172256</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17714,7 +17716,7 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>24.71</v>
+        <v>24.73</v>
       </c>
       <c r="CA60" t="n">
         <v>0.68</v>
@@ -17774,10 +17776,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34.84999847412109</v>
+        <v>34.54999923706055</v>
       </c>
       <c r="D61" t="n">
-        <v>34.84999847412109</v>
+        <v>34.54999923706055</v>
       </c>
       <c r="E61" t="n">
         <v>35.15000152587891</v>
@@ -17789,88 +17791,88 @@
         <v>34.58000183105469</v>
       </c>
       <c r="H61" t="n">
-        <v>5594300</v>
+        <v>6754800</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01308130605470059</v>
+        <v>0.004360398387447617</v>
       </c>
       <c r="J61" t="n">
-        <v>34.58666653103299</v>
+        <v>34.5533332824707</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.7613683812281508</v>
+        <v>-0.00964898345088938</v>
       </c>
       <c r="M61" t="n">
-        <v>34.61199989318848</v>
+        <v>34.58199996948242</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6876186919769867</v>
+        <v>-0.09253580605551306</v>
       </c>
       <c r="P61" t="n">
-        <v>36.49269236051119</v>
+        <v>36.48115392831656</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-4.501432424228749</v>
+        <v>-5.293568002400975</v>
       </c>
       <c r="S61" t="n">
-        <v>37.84239982604981</v>
+        <v>37.83639984130859</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-7.907535900693103</v>
+        <v>-8.685817408716712</v>
       </c>
       <c r="V61" t="n">
-        <v>41.11473325093587</v>
+        <v>41.11273325602213</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-15.23720156124855</v>
+        <v>-15.96277722060789</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.71899995803833</v>
+        <v>40.71749996185303</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-14.41342245626207</v>
+        <v>-15.14705158855682</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.4052991788375858</v>
+        <v>0.4024717959552113</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="AE61" t="n">
         <v>34</v>
       </c>
-      <c r="AE61" t="n">
+      <c r="AF61" t="n">
         <v>34.4</v>
       </c>
-      <c r="AF61" t="n">
+      <c r="AG61" t="n">
         <v>34.7</v>
       </c>
-      <c r="AG61" t="n">
+      <c r="AH61" t="n">
         <v>34.9</v>
       </c>
-      <c r="AH61" t="n">
+      <c r="AI61" t="n">
         <v>35.1</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>35.2</v>
       </c>
       <c r="AJ61" t="n">
         <v>1</v>
@@ -17997,13 +17999,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>17.25</v>
+        <v>17.1</v>
       </c>
       <c r="CA61" t="n">
         <v>0.09</v>
       </c>
       <c r="CB61" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18038,13 +18040,13 @@
         <v>4</v>
       </c>
       <c r="CM61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CN61" t="n">
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62">
@@ -18057,10 +18059,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11.64999961853027</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="D62" t="n">
-        <v>11.64999961853027</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="E62" t="n">
         <v>12.01000022888184</v>
@@ -18072,67 +18074,67 @@
         <v>11.93000030517578</v>
       </c>
       <c r="H62" t="n">
-        <v>1147200</v>
+        <v>1406300</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.01354790816270091</v>
+        <v>-0.01693486501552077</v>
       </c>
       <c r="J62" t="n">
-        <v>12.08333333333333</v>
+        <v>12.07888889312744</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-3.586210053542569</v>
+        <v>-3.881890466903628</v>
       </c>
       <c r="M62" t="n">
-        <v>12.09099998474121</v>
+        <v>12.08699998855591</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-3.647344030828537</v>
+        <v>-3.946391431540419</v>
       </c>
       <c r="P62" t="n">
-        <v>12.48884619199313</v>
+        <v>12.48730773192186</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-6.716765989164439</v>
+        <v>-7.025598264083046</v>
       </c>
       <c r="S62" t="n">
-        <v>13.01260007858276</v>
+        <v>13.0118000793457</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-10.47139274106467</v>
+        <v>-10.77330126593019</v>
       </c>
       <c r="V62" t="n">
-        <v>11.95493333816528</v>
+        <v>11.95466667175293</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.550693600787635</v>
+        <v>-2.883116899361821</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.15770000457764</v>
+        <v>12.15750000476837</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-4.17595750722754</v>
+        <v>-4.503395828717964</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3496527611284067</v>
+        <v>0.3505023527482612</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18284,10 +18286,10 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6.4</v>
+        <v>6.38</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="CB62" t="n">
         <v>0.8100000000000001</v>
@@ -18299,7 +18301,7 @@
         <v>5</v>
       </c>
       <c r="CE62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CF62" t="n">
         <v>9</v>
@@ -18340,10 +18342,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>43.15000152587891</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="D63" t="n">
-        <v>43.15000152587891</v>
+        <v>43.09999847412109</v>
       </c>
       <c r="E63" t="n">
         <v>43.59999847412109</v>
@@ -18355,67 +18357,67 @@
         <v>42.81999969482422</v>
       </c>
       <c r="H63" t="n">
-        <v>3112800</v>
+        <v>4759600</v>
       </c>
       <c r="I63" t="n">
-        <v>0.007706721938500527</v>
+        <v>0.006538972005894594</v>
       </c>
       <c r="J63" t="n">
-        <v>43.49888949924045</v>
+        <v>43.49333360460069</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.8020617937100074</v>
+        <v>-0.9043572839355603</v>
       </c>
       <c r="M63" t="n">
-        <v>43.44700050354004</v>
+        <v>43.44200019836425</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.6835891412962639</v>
+        <v>-0.7872605374557288</v>
       </c>
       <c r="P63" t="n">
-        <v>45.58923119765062</v>
+        <v>45.58730800335224</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-5.350451428313219</v>
+        <v>-5.456144787159277</v>
       </c>
       <c r="S63" t="n">
-        <v>46.59820014953613</v>
+        <v>46.59720008850098</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-7.399853669437386</v>
+        <v>-7.505175434871042</v>
       </c>
       <c r="V63" t="n">
-        <v>45.5644667561849</v>
+        <v>45.56413340250651</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-5.299009079214681</v>
+        <v>-5.408058366034601</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.41750005722046</v>
+        <v>43.41725004196167</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-0.616107631690015</v>
+        <v>-0.7307039656679387</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.4985857184332205</v>
+        <v>0.4983370009202606</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18563,7 +18565,7 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>21.58</v>
+        <v>21.55</v>
       </c>
       <c r="CA63" t="n">
         <v>0.67</v>
@@ -18619,10 +18621,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.42000007629395</v>
+        <v>27.46999931335449</v>
       </c>
       <c r="D64" t="n">
-        <v>27.42000007629395</v>
+        <v>27.46999931335449</v>
       </c>
       <c r="E64" t="n">
         <v>27.69000053405762</v>
@@ -18634,67 +18636,67 @@
         <v>27.61000061035156</v>
       </c>
       <c r="H64" t="n">
-        <v>654500</v>
+        <v>840600</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.001820139727351178</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>27.28777779473199</v>
+        <v>27.29333326551649</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.4845476335837222</v>
+        <v>0.6472864494759407</v>
       </c>
       <c r="M64" t="n">
-        <v>27.25100002288819</v>
+        <v>27.25599994659424</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6201609235030521</v>
+        <v>0.7851459024786046</v>
       </c>
       <c r="P64" t="n">
-        <v>28.16153849088229</v>
+        <v>28.16346153846154</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.633160169244393</v>
+        <v>-2.462276251660395</v>
       </c>
       <c r="S64" t="n">
-        <v>29.41399997711182</v>
+        <v>29.41499996185303</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-6.779084457637458</v>
+        <v>-6.612274863236165</v>
       </c>
       <c r="V64" t="n">
-        <v>31.97053334554036</v>
+        <v>31.97086667378743</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-14.23352316354516</v>
+        <v>-14.07802736897074</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.01020001411438</v>
+        <v>31.01045001029968</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-11.57748075209558</v>
+        <v>-11.41696007561734</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2523108220269846</v>
+        <v>0.2525704801172893</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18864,7 +18866,7 @@
         <v>18881600000</v>
       </c>
       <c r="BZ64" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="CA64" t="n">
         <v>0</v>
@@ -18905,13 +18907,13 @@
         <v>5</v>
       </c>
       <c r="CM64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
@@ -18924,10 +18926,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28.47999954223633</v>
+        <v>28.43000030517578</v>
       </c>
       <c r="D65" t="n">
-        <v>28.47999954223633</v>
+        <v>28.43000030517578</v>
       </c>
       <c r="E65" t="n">
         <v>28.93000030517578</v>
@@ -18939,67 +18941,67 @@
         <v>28.54999923706055</v>
       </c>
       <c r="H65" t="n">
-        <v>5280100</v>
+        <v>10226700</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.002801117829202115</v>
+        <v>-0.004551791428484608</v>
       </c>
       <c r="J65" t="n">
-        <v>28.76000001695421</v>
+        <v>28.7544445461697</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.9735760589458214</v>
+        <v>-1.128327276407575</v>
       </c>
       <c r="M65" t="n">
-        <v>28.78700008392334</v>
+        <v>28.78200016021729</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-1.066455486129174</v>
+        <v>-1.222986078389515</v>
       </c>
       <c r="P65" t="n">
-        <v>30.96992331284743</v>
+        <v>30.96800026526818</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-8.039812515706792</v>
+        <v>-8.195556504624761</v>
       </c>
       <c r="S65" t="n">
-        <v>31.38542987823486</v>
+        <v>31.38442989349365</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-9.257258375209924</v>
+        <v>-9.413679325525548</v>
       </c>
       <c r="V65" t="n">
-        <v>28.74110298156738</v>
+        <v>28.74076965332031</v>
       </c>
       <c r="W65" t="n">
         <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>-0.9084670115079078</v>
+        <v>-1.081284015331268</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.55454038619995</v>
+        <v>27.55429039001465</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.358644866019515</v>
+        <v>3.178125448944526</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2706322023899235</v>
+        <v>0.2705254230837683</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19151,13 +19153,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>11.48</v>
+        <v>11.46</v>
       </c>
       <c r="CA65" t="n">
         <v>0.32</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CC65" t="n">
         <v>9</v>
@@ -19192,13 +19194,13 @@
         <v>3</v>
       </c>
       <c r="CM65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
@@ -19211,10 +19213,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15.88000011444092</v>
+        <v>15.84000015258789</v>
       </c>
       <c r="D66" t="n">
-        <v>15.88000011444092</v>
+        <v>15.84000015258789</v>
       </c>
       <c r="E66" t="n">
         <v>15.97999954223633</v>
@@ -19226,67 +19228,67 @@
         <v>15.89999961853027</v>
       </c>
       <c r="H66" t="n">
-        <v>930900</v>
+        <v>1534800</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0006293410110616016</v>
+        <v>-0.003146645038045848</v>
       </c>
       <c r="J66" t="n">
-        <v>16.36444452073839</v>
+        <v>16.3600000805325</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.960347390243169</v>
+        <v>-3.178483651496911</v>
       </c>
       <c r="M66" t="n">
-        <v>16.44700012207031</v>
+        <v>16.44300012588501</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.447437243394531</v>
+        <v>-3.667213821569345</v>
       </c>
       <c r="P66" t="n">
-        <v>16.99653860238882</v>
+        <v>16.99500014231755</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-6.569211026243756</v>
+        <v>-6.796116387511584</v>
       </c>
       <c r="S66" t="n">
-        <v>17.66059997558594</v>
+        <v>17.65979997634888</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-10.08232938635452</v>
+        <v>-10.30475897914008</v>
       </c>
       <c r="V66" t="n">
-        <v>16.02936279296875</v>
+        <v>16.0290961265564</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-0.9318067128242344</v>
+        <v>-1.179704535274568</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.74184419631958</v>
+        <v>15.74164419651031</v>
       </c>
       <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.8776348971465425</v>
+        <v>0.6248137414983627</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.2266463417968481</v>
+        <v>0.2262049738155777</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19440,7 +19442,7 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>24.43</v>
+        <v>24.37</v>
       </c>
       <c r="CA66" t="n">
         <v>0.8</v>
@@ -19500,10 +19502,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.79000091552734</v>
+        <v>18.76000022888184</v>
       </c>
       <c r="D67" t="n">
-        <v>18.79000091552734</v>
+        <v>18.76000022888184</v>
       </c>
       <c r="E67" t="n">
         <v>19.03000068664551</v>
@@ -19515,67 +19517,67 @@
         <v>18.60000038146973</v>
       </c>
       <c r="H67" t="n">
-        <v>1268100</v>
+        <v>1731600</v>
       </c>
       <c r="I67" t="n">
-        <v>0.008047292424387509</v>
+        <v>0.006437813474395204</v>
       </c>
       <c r="J67" t="n">
-        <v>19.00222227308485</v>
+        <v>18.99888886345757</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-1.116823887793929</v>
+        <v>-1.257382135832243</v>
       </c>
       <c r="M67" t="n">
-        <v>18.97299995422363</v>
+        <v>18.96999988555908</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.9645234761914904</v>
+        <v>-1.107009266969526</v>
       </c>
       <c r="P67" t="n">
-        <v>18.58923075749324</v>
+        <v>18.58807688492995</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>1.080034782790428</v>
+        <v>0.9249119476758241</v>
       </c>
       <c r="S67" t="n">
-        <v>18.70739994049072</v>
+        <v>18.70679992675781</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.4415417177126589</v>
+        <v>0.2843901807487959</v>
       </c>
       <c r="V67" t="n">
-        <v>21.54592123667399</v>
+        <v>21.54572123209635</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-12.79091430286911</v>
+        <v>-12.92934672831778</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.34989093780517</v>
+        <v>22.34974093437195</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-15.92799728725397</v>
+        <v>-16.0616658422622</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5184976014943958</v>
+        <v>0.5183049706570604</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19725,7 +19727,7 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.78</v>
+        <v>16.75</v>
       </c>
       <c r="CA67" t="n">
         <v>0.35</v>
@@ -19785,10 +19787,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.79999923706055</v>
+        <v>41.84999847412109</v>
       </c>
       <c r="D68" t="n">
-        <v>41.79999923706055</v>
+        <v>41.84999847412109</v>
       </c>
       <c r="E68" t="n">
         <v>42.4900016784668</v>
@@ -19800,67 +19802,67 @@
         <v>42.31999969482422</v>
       </c>
       <c r="H68" t="n">
-        <v>1444500</v>
+        <v>2165000</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.006890019350819898</v>
+        <v>-0.005702106856657729</v>
       </c>
       <c r="J68" t="n">
-        <v>41.79555553860135</v>
+        <v>41.80111100938585</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.01063198802344938</v>
+        <v>0.116952548759452</v>
       </c>
       <c r="M68" t="n">
-        <v>41.78600006103515</v>
+        <v>41.79099998474121</v>
       </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.03350207247629691</v>
+        <v>0.1411751080410208</v>
       </c>
       <c r="P68" t="n">
-        <v>43.20653842045711</v>
+        <v>43.20846146803636</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.255385029249654</v>
+        <v>-3.143974461854413</v>
       </c>
       <c r="S68" t="n">
-        <v>46.3339998626709</v>
+        <v>46.33499984741211</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-9.785472091873473</v>
+        <v>-9.679510927076237</v>
       </c>
       <c r="V68" t="n">
-        <v>49.59573328653971</v>
+        <v>49.59606661478679</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-15.71855789375924</v>
+        <v>-15.6183114294718</v>
       </c>
       <c r="Y68" t="n">
-        <v>49.97649997711181</v>
+        <v>49.97674997329712</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-16.36069101236768</v>
+        <v>-16.26106440198332</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2065438285100927</v>
+        <v>0.2064714631628539</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20012,7 +20014,7 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="CA68" t="n">
         <v>1.29</v>
@@ -20072,10 +20074,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39.63999938964844</v>
+        <v>39.56000137329102</v>
       </c>
       <c r="D69" t="n">
-        <v>39.63999938964844</v>
+        <v>39.56000137329102</v>
       </c>
       <c r="E69" t="n">
         <v>40.0099983215332</v>
@@ -20087,67 +20089,67 @@
         <v>39.54000091552734</v>
       </c>
       <c r="H69" t="n">
-        <v>659900</v>
+        <v>1061500</v>
       </c>
       <c r="I69" t="n">
-        <v>0.006858025529307366</v>
+        <v>0.004826071794794329</v>
       </c>
       <c r="J69" t="n">
-        <v>38.86999935574002</v>
+        <v>38.86111068725586</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.980962301700448</v>
+        <v>1.798432092329134</v>
       </c>
       <c r="M69" t="n">
-        <v>38.81199951171875</v>
+        <v>38.803999710083</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>2.133360528564578</v>
+        <v>1.948257058180443</v>
       </c>
       <c r="P69" t="n">
-        <v>40.74230766296387</v>
+        <v>40.73923081618089</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-2.705561703657412</v>
+        <v>-2.894579547195349</v>
       </c>
       <c r="S69" t="n">
-        <v>41.96060012817383</v>
+        <v>41.95900016784668</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-5.530427904836516</v>
+        <v>-5.717483221618867</v>
       </c>
       <c r="V69" t="n">
-        <v>41.76820012410482</v>
+        <v>41.76766680399577</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-5.095265604294434</v>
+        <v>-5.285584758815283</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.09350011825561</v>
+        <v>40.09310012817383</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-1.131107853566229</v>
+        <v>-1.329652117642559</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.255382446220216</v>
+        <v>0.2546719441678306</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20299,13 +20301,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.710000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CC69" t="n">
         <v>6</v>
@@ -20333,7 +20335,7 @@
         <v>0</v>
       </c>
       <c r="CL69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM69" t="n">
         <v>9</v>
@@ -20342,7 +20344,7 @@
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
@@ -20355,10 +20357,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.65999984741211</v>
+        <v>22.57999992370605</v>
       </c>
       <c r="D70" t="n">
-        <v>22.65999984741211</v>
+        <v>22.57999992370605</v>
       </c>
       <c r="E70" t="n">
         <v>22.80999946594238</v>
@@ -20370,67 +20372,67 @@
         <v>22.70000076293945</v>
       </c>
       <c r="H70" t="n">
-        <v>1245200</v>
+        <v>1760200</v>
       </c>
       <c r="I70" t="n">
-        <v>0.002654843580957467</v>
+        <v>-0.0008849759923044154</v>
       </c>
       <c r="J70" t="n">
-        <v>22.49222204420302</v>
+        <v>22.48333316379123</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.7459369860361713</v>
+        <v>0.4299485276965104</v>
       </c>
       <c r="M70" t="n">
-        <v>22.46199989318848</v>
+        <v>22.45399990081787</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.8814885369297665</v>
+        <v>0.5611473387580961</v>
       </c>
       <c r="P70" t="n">
-        <v>23.75576921609732</v>
+        <v>23.75269229595478</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-4.612645285098558</v>
+        <v>-4.937092425722361</v>
       </c>
       <c r="S70" t="n">
-        <v>25.31679996490479</v>
+        <v>25.31519996643067</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-10.49421775728229</v>
+        <v>-10.80457609006302</v>
       </c>
       <c r="V70" t="n">
-        <v>24.85793333689372</v>
+        <v>24.85740000406901</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-8.84197998157584</v>
+        <v>-9.161859566930405</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.34110000610352</v>
+        <v>24.34070000648499</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-6.906426407474899</v>
+        <v>-7.233563875771183</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3793974747796879</v>
+        <v>0.3788475264031167</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20582,13 +20584,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2266</v>
+        <v>2258</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CC70" t="n">
         <v>1</v>
@@ -20623,13 +20625,13 @@
         <v>2</v>
       </c>
       <c r="CM70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
@@ -20642,13 +20644,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>31.5</v>
+        <v>31.78000068664551</v>
       </c>
       <c r="D71" t="n">
-        <v>31.5</v>
+        <v>31.78000068664551</v>
       </c>
       <c r="E71" t="n">
-        <v>31.94000053405762</v>
+        <v>31.95999908447266</v>
       </c>
       <c r="F71" t="n">
         <v>30.75</v>
@@ -20657,88 +20659,88 @@
         <v>31.48999977111816</v>
       </c>
       <c r="H71" t="n">
-        <v>3686000</v>
+        <v>5903100</v>
       </c>
       <c r="I71" t="n">
-        <v>0.01351351600144612</v>
+        <v>0.02252254712541135</v>
       </c>
       <c r="J71" t="n">
-        <v>31.54666625128852</v>
+        <v>31.57777743869358</v>
       </c>
       <c r="K71" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.1479276793205199</v>
+        <v>0.6403973438109625</v>
       </c>
       <c r="M71" t="n">
-        <v>31.50599956512451</v>
+        <v>31.53399963378906</v>
       </c>
       <c r="N71" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>-0.01904261158929527</v>
+        <v>0.7801137049321614</v>
       </c>
       <c r="P71" t="n">
-        <v>32.28307679983286</v>
+        <v>32.29384605701153</v>
       </c>
       <c r="Q71" t="n">
         <v>-1</v>
       </c>
       <c r="R71" t="n">
-        <v>-2.425657271418782</v>
+        <v>-1.591155694056627</v>
       </c>
       <c r="S71" t="n">
-        <v>33.44419990539551</v>
+        <v>33.44979991912842</v>
       </c>
       <c r="T71" t="n">
         <v>-1</v>
       </c>
       <c r="U71" t="n">
-        <v>-5.813264813914272</v>
+        <v>-4.991955815939057</v>
       </c>
       <c r="V71" t="n">
-        <v>39.44886662801107</v>
+        <v>39.45073329925537</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-20.14979721208744</v>
+        <v>-19.44382770891269</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.39934999465942</v>
+        <v>40.40074999809265</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-22.02844846720521</v>
+        <v>-21.33809226772803</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4530314292179153</v>
+        <v>0.4566111323443067</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="AE71" t="n">
-        <v>30.9</v>
+        <v>31.3</v>
       </c>
       <c r="AF71" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="AG71" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="AH71" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="AI71" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="AJ71" t="n">
         <v>3</v>
@@ -20865,13 +20867,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>20.45</v>
+        <v>20.64</v>
       </c>
       <c r="CA71" t="n">
         <v>0.18</v>
       </c>
       <c r="CB71" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20903,16 +20905,16 @@
         <v>0</v>
       </c>
       <c r="CL71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CN71" t="n">
         <v>0</v>
       </c>
       <c r="CO71" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72">
@@ -20925,82 +20927,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27.27000045776367</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="D72" t="n">
-        <v>27.27000045776367</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="E72" t="n">
         <v>27.68000030517578</v>
       </c>
       <c r="F72" t="n">
-        <v>27.13999938964844</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="G72" t="n">
         <v>27.60000038146973</v>
       </c>
       <c r="H72" t="n">
-        <v>1681700</v>
+        <v>2432000</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.007641888208545722</v>
+        <v>-0.01382820840963073</v>
       </c>
       <c r="J72" t="n">
-        <v>28.39777819315593</v>
+        <v>28.37888929578993</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-3.971359053941961</v>
+        <v>-4.506479802611342</v>
       </c>
       <c r="M72" t="n">
-        <v>28.47100028991699</v>
+        <v>28.4540002822876</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-4.218326788394069</v>
+        <v>-4.758557276253092</v>
       </c>
       <c r="P72" t="n">
-        <v>29.12153867574839</v>
+        <v>29.11500021127554</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-6.35796837042345</v>
+        <v>-6.920830551893495</v>
       </c>
       <c r="S72" t="n">
-        <v>28.97300010681152</v>
+        <v>28.96960010528564</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-5.877885074964939</v>
+        <v>-6.453660792765997</v>
       </c>
       <c r="V72" t="n">
-        <v>25.15573332468669</v>
+        <v>25.15459999084473</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>8.404712777751309</v>
+        <v>7.7337758951963</v>
       </c>
       <c r="Y72" t="n">
-        <v>23.85095000267029</v>
+        <v>23.85010000228882</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>14.33507032093311</v>
+        <v>13.62635954930598</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2488014590169091</v>
+        <v>0.2503996654798288</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21152,13 +21154,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>10.14</v>
+        <v>10.07</v>
       </c>
       <c r="CA72" t="n">
         <v>0.46</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21208,13 +21210,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.5</v>
+        <v>10.64000034332275</v>
       </c>
       <c r="D73" t="n">
-        <v>10.5</v>
+        <v>10.64000034332275</v>
       </c>
       <c r="E73" t="n">
-        <v>10.52000045776367</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="F73" t="n">
         <v>10.21000003814697</v>
@@ -21223,67 +21225,67 @@
         <v>10.25</v>
       </c>
       <c r="H73" t="n">
-        <v>7949100</v>
+        <v>11485000</v>
       </c>
       <c r="I73" t="n">
-        <v>0.02639300780502762</v>
+        <v>0.04007828146948267</v>
       </c>
       <c r="J73" t="n">
-        <v>9.814444435967339</v>
+        <v>9.830000029669868</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>6.985169344077</v>
+        <v>8.240084549420786</v>
       </c>
       <c r="M73" t="n">
-        <v>9.744999980926513</v>
+        <v>9.759000015258788</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>7.74756306363486</v>
+        <v>9.027567647161268</v>
       </c>
       <c r="P73" t="n">
-        <v>8.947307678369375</v>
+        <v>8.952692306958712</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>17.35373787786852</v>
+        <v>18.84693429095668</v>
       </c>
       <c r="S73" t="n">
-        <v>7.942199974060059</v>
+        <v>7.944999980926513</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>32.20518287494581</v>
+        <v>33.92070948856013</v>
       </c>
       <c r="V73" t="n">
-        <v>6.649599990844727</v>
+        <v>6.650533326466879</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>57.90423505859849</v>
+        <v>59.98717427637183</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.082349992990494</v>
+        <v>6.083049994707108</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>72.63064460447944</v>
+        <v>74.91226198339108</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.545575146965782</v>
+        <v>0.5496962221770312</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21435,13 +21437,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>-5.05</v>
+        <v>-5.12</v>
       </c>
       <c r="CA73" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21495,10 +21497,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>83.83000183105469</v>
+        <v>83.98000335693359</v>
       </c>
       <c r="D74" t="n">
-        <v>83.83000183105469</v>
+        <v>83.98000335693359</v>
       </c>
       <c r="E74" t="n">
         <v>84.05000305175781</v>
@@ -21510,67 +21512,67 @@
         <v>83.15000152587891</v>
       </c>
       <c r="H74" t="n">
-        <v>6308500</v>
+        <v>8243700</v>
       </c>
       <c r="I74" t="n">
-        <v>0.004553683603466085</v>
+        <v>0.006351185477216026</v>
       </c>
       <c r="J74" t="n">
-        <v>82.72444322374132</v>
+        <v>82.74111005995009</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>1.33643523513747</v>
+        <v>1.497312878792495</v>
       </c>
       <c r="M74" t="n">
-        <v>82.80199890136718</v>
+        <v>82.81699905395507</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>1.241519460070099</v>
+        <v>1.404306261110508</v>
       </c>
       <c r="P74" t="n">
-        <v>82.71576954768254</v>
+        <v>82.72153883713942</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>1.347061496816315</v>
+        <v>1.521326292384158</v>
       </c>
       <c r="S74" t="n">
-        <v>82.66260040283203</v>
+        <v>82.66560043334961</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>1.412248613682211</v>
+        <v>1.590024044697699</v>
       </c>
       <c r="V74" t="n">
-        <v>77.40313344319661</v>
+        <v>77.40413345336914</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>8.303111388345187</v>
+        <v>8.49550225573674</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.24030008316041</v>
+        <v>72.2410500907898</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>16.04326357248328</v>
+        <v>16.24969909959881</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3020705310076185</v>
+        <v>0.3024310435980251</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21718,7 +21720,7 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>23.88</v>
+        <v>23.93</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
@@ -21774,10 +21776,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.210000038146973</v>
+        <v>3.220000028610229</v>
       </c>
       <c r="D75" t="n">
-        <v>3.210000038146973</v>
+        <v>3.220000028610229</v>
       </c>
       <c r="E75" t="n">
         <v>3.289999961853027</v>
@@ -21789,67 +21791,67 @@
         <v>3.240000009536743</v>
       </c>
       <c r="H75" t="n">
-        <v>7375900</v>
+        <v>8988700</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.006191944522728088</v>
+        <v>-0.003095972261364044</v>
       </c>
       <c r="J75" t="n">
-        <v>3.295555538601346</v>
+        <v>3.296666648652819</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-2.596087350137124</v>
+        <v>-2.325579993777016</v>
       </c>
       <c r="M75" t="n">
-        <v>3.30699999332428</v>
+        <v>3.307999992370605</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-2.933170709800955</v>
+        <v>-2.660216564792452</v>
       </c>
       <c r="P75" t="n">
-        <v>3.68000001173753</v>
+        <v>3.680384626755348</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-12.77173837205084</v>
+        <v>-12.50914360412913</v>
       </c>
       <c r="S75" t="n">
-        <v>3.741200008392334</v>
+        <v>3.741400008201599</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-14.19865201148731</v>
+        <v>-13.93595922511354</v>
       </c>
       <c r="V75" t="n">
-        <v>3.750928123792013</v>
+        <v>3.750994790395101</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-14.42117971320088</v>
+        <v>-14.15610501898192</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.742646098136902</v>
+        <v>3.742696098089218</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-14.23180407720307</v>
+        <v>-13.96576306972516</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.5147259207426625</v>
+        <v>0.5149241600282439</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21999,10 +22001,10 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>12.84</v>
+        <v>12.88</v>
       </c>
       <c r="CA75" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CB75" t="n">
         <v>1.51</v>
@@ -22036,13 +22038,13 @@
         <v>1</v>
       </c>
       <c r="CM75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN75" t="n">
         <v>-1</v>
       </c>
       <c r="CO75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -22055,10 +22057,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>31.26000022888184</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="D76" t="n">
-        <v>31.26000022888184</v>
+        <v>31.14999961853027</v>
       </c>
       <c r="E76" t="n">
         <v>31.67000007629395</v>
@@ -22070,67 +22072,67 @@
         <v>31.06999969482422</v>
       </c>
       <c r="H76" t="n">
-        <v>2348100</v>
+        <v>3213500</v>
       </c>
       <c r="I76" t="n">
-        <v>0.007736936414457718</v>
+        <v>0.004190817499941879</v>
       </c>
       <c r="J76" t="n">
-        <v>32.42888853285048</v>
+        <v>32.41666624281142</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-3.604466131438821</v>
+        <v>-3.90745493319207</v>
       </c>
       <c r="M76" t="n">
-        <v>32.4979995727539</v>
+        <v>32.48699951171875</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-3.809463228961326</v>
+        <v>-4.115492083860168</v>
       </c>
       <c r="P76" t="n">
-        <v>32.85038434542142</v>
+        <v>32.84615355271559</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-4.841295309719111</v>
+        <v>-5.16393474037415</v>
       </c>
       <c r="S76" t="n">
-        <v>32.35079990386963</v>
+        <v>32.34859989166259</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-3.371785792713326</v>
+        <v>-3.705261671746244</v>
       </c>
       <c r="V76" t="n">
-        <v>28.45000972747803</v>
+        <v>28.44927639007568</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>9.876940388845709</v>
+        <v>9.493117474849784</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.77774359703064</v>
+        <v>26.77719359397888</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>16.73873907862883</v>
+        <v>16.33033726706394</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.272849707146244</v>
+        <v>0.2719496680043538</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22282,10 +22284,10 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>12.45</v>
+        <v>12.41</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="CB76" t="n">
         <v>1.72</v>
@@ -22316,7 +22318,7 @@
         <v>0</v>
       </c>
       <c r="CL76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM76" t="n">
         <v>2</v>
@@ -22325,7 +22327,7 @@
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77">
@@ -22338,10 +22340,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>22.30999946594238</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="D77" t="n">
-        <v>22.30999946594238</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="E77" t="n">
         <v>22.45000076293945</v>
@@ -22353,67 +22355,67 @@
         <v>22.29000091552734</v>
       </c>
       <c r="H77" t="n">
-        <v>1580800</v>
+        <v>1817900</v>
       </c>
       <c r="I77" t="n">
-        <v>0.005861098240664386</v>
+        <v>0.00541023129998619</v>
       </c>
       <c r="J77" t="n">
-        <v>22.41666666666667</v>
+        <v>22.41555553012424</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.4758388136399332</v>
+        <v>-0.5155183100789003</v>
       </c>
       <c r="M77" t="n">
-        <v>22.46900005340576</v>
+        <v>22.46800003051758</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.7076442524609703</v>
+        <v>-0.7477336355209296</v>
       </c>
       <c r="P77" t="n">
-        <v>24.30615388430082</v>
+        <v>24.30576926011306</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-8.212547439057149</v>
+        <v>-8.252238394873908</v>
       </c>
       <c r="S77" t="n">
-        <v>25.36400009155274</v>
+        <v>25.3638000869751</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-12.04069001177563</v>
+        <v>-12.07942358561595</v>
       </c>
       <c r="V77" t="n">
-        <v>29.11993335723877</v>
+        <v>29.11986668904622</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-23.38581550909882</v>
+        <v>-23.4199817080586</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.89150001525879</v>
+        <v>28.89145001411438</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-22.78005830725454</v>
+        <v>-22.81453777444089</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4662706986102572</v>
+        <v>0.4661725698232022</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22561,7 +22563,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>9</v>
+        <v>8.99</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
@@ -22621,10 +22623,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.83000183105469</v>
+        <v>33.7599983215332</v>
       </c>
       <c r="D78" t="n">
-        <v>33.83000183105469</v>
+        <v>33.7599983215332</v>
       </c>
       <c r="E78" t="n">
         <v>34.06999969482422</v>
@@ -22636,67 +22638,67 @@
         <v>33.72000122070312</v>
       </c>
       <c r="H78" t="n">
-        <v>1237900</v>
+        <v>1895600</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.002947199328667272</v>
+        <v>-0.005010373772871612</v>
       </c>
       <c r="J78" t="n">
-        <v>34.50333404541016</v>
+        <v>34.49555587768555</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.951498986936422</v>
+        <v>-2.132325563213088</v>
       </c>
       <c r="M78" t="n">
-        <v>34.60500068664551</v>
+        <v>34.59800033569336</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-2.239557405614804</v>
+        <v>-2.422111122114825</v>
       </c>
       <c r="P78" t="n">
-        <v>36.90384630056528</v>
+        <v>36.90115385789137</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-8.329333599743249</v>
+        <v>-8.51235044967687</v>
       </c>
       <c r="S78" t="n">
-        <v>38.93500007629395</v>
+        <v>38.93360000610352</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-13.11159171757007</v>
+        <v>-13.28826947356336</v>
       </c>
       <c r="V78" t="n">
-        <v>36.99640009562174</v>
+        <v>36.99593340555827</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-8.55866586041645</v>
+        <v>-8.74673183279895</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.10040010452271</v>
+        <v>36.1000500869751</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-6.289122189489473</v>
+        <v>-6.482128860774582</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3109036868064529</v>
+        <v>0.3107537227300767</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22848,7 +22850,7 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
@@ -22908,10 +22910,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>43.7599983215332</v>
+        <v>43.84999847412109</v>
       </c>
       <c r="D79" t="n">
-        <v>43.7599983215332</v>
+        <v>43.84999847412109</v>
       </c>
       <c r="E79" t="n">
         <v>44.02000045776367</v>
@@ -22923,67 +22925,67 @@
         <v>43.88999938964844</v>
       </c>
       <c r="H79" t="n">
-        <v>1545600</v>
+        <v>2643100</v>
       </c>
       <c r="I79" t="n">
-        <v>0.007134581200241685</v>
+        <v>0.009205931050818794</v>
       </c>
       <c r="J79" t="n">
-        <v>42.87777794731988</v>
+        <v>42.88777796427409</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2.057523538876551</v>
+        <v>2.243577437489408</v>
       </c>
       <c r="M79" t="n">
-        <v>42.90300025939941</v>
+        <v>42.9120002746582</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>1.997524781372452</v>
+        <v>2.185864544787548</v>
       </c>
       <c r="P79" t="n">
-        <v>44.38423083378719</v>
+        <v>44.38769237811749</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-1.406428590802096</v>
+        <v>-1.211358093175997</v>
       </c>
       <c r="S79" t="n">
-        <v>46.73880012512207</v>
+        <v>46.74060012817383</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-6.37329541112409</v>
+        <v>-6.184348609401721</v>
       </c>
       <c r="V79" t="n">
-        <v>47.04166661580404</v>
+        <v>47.04226661682129</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-6.976088498463898</v>
+        <v>-6.785957336415223</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.50374994277954</v>
+        <v>44.50419994354248</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-1.67121112760748</v>
+        <v>-1.469976924090985</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.3379411789090649</v>
+        <v>0.3386639090577136</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23135,13 +23137,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>29.17</v>
+        <v>29.23</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB79" t="n">
-        <v>10.35</v>
+        <v>10.37</v>
       </c>
       <c r="CC79" t="n">
         <v>6</v>
@@ -23195,10 +23197,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.699999809265137</v>
+        <v>9.670000076293945</v>
       </c>
       <c r="D80" t="n">
-        <v>9.699999809265137</v>
+        <v>9.670000076293945</v>
       </c>
       <c r="E80" t="n">
         <v>9.869999885559082</v>
@@ -23210,67 +23212,67 @@
         <v>9.630000114440918</v>
       </c>
       <c r="H80" t="n">
-        <v>1405200</v>
+        <v>1698700</v>
       </c>
       <c r="I80" t="n">
-        <v>0.008316000484173136</v>
+        <v>0.005197525086244603</v>
       </c>
       <c r="J80" t="n">
-        <v>9.619999885559082</v>
+        <v>9.616666581895617</v>
       </c>
       <c r="K80" t="n">
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0.8316000484173121</v>
+        <v>0.5545944007119337</v>
       </c>
       <c r="M80" t="n">
-        <v>9.613999938964843</v>
+        <v>9.610999965667725</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.8945274687567044</v>
+        <v>0.6138810824781988</v>
       </c>
       <c r="P80" t="n">
-        <v>9.998461503248949</v>
+        <v>9.99730766736544</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-2.985076192840555</v>
+        <v>-3.273957368941807</v>
       </c>
       <c r="S80" t="n">
-        <v>10.66979999542236</v>
+        <v>10.66920000076294</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-9.089206794628735</v>
+        <v>-9.365275038405347</v>
       </c>
       <c r="V80" t="n">
-        <v>12.17953332901001</v>
+        <v>12.1793333307902</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-20.35819807511801</v>
+        <v>-20.60320697646469</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.38575000286102</v>
+        <v>12.38560000419617</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-21.68419508689822</v>
+        <v>-21.92546123709948</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4282644440034701</v>
+        <v>0.4274251382950149</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23422,13 +23424,13 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>22.56</v>
+        <v>22.49</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CB80" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="CC80" t="n">
         <v>5</v>
@@ -23463,13 +23465,13 @@
         <v>3</v>
       </c>
       <c r="CM80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
       </c>
       <c r="CO80" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -423,7 +423,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -897,82 +897,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.30999946594238</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30999946594238</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="E2" t="n">
         <v>16.64999961853027</v>
       </c>
       <c r="F2" t="n">
-        <v>16.28000068664551</v>
+        <v>16.25</v>
       </c>
       <c r="G2" t="n">
         <v>16.60000038146973</v>
       </c>
       <c r="H2" t="n">
-        <v>17432600</v>
+        <v>24767400</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01806147702500471</v>
+        <v>-0.01926548362826619</v>
       </c>
       <c r="J2" t="n">
-        <v>16.25</v>
+        <v>16.24777793884277</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3692274827223558</v>
+        <v>0.2598692377720765</v>
       </c>
       <c r="M2" t="n">
-        <v>16.19399995803833</v>
+        <v>16.19200010299683</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7163116475523637</v>
+        <v>0.6052421683988271</v>
       </c>
       <c r="P2" t="n">
-        <v>15.72961532152616</v>
+        <v>15.7288461465102</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3.689754215552616</v>
+        <v>3.567679178689481</v>
       </c>
       <c r="S2" t="n">
-        <v>15.50699998855591</v>
+        <v>15.50660001754761</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>5.178303204869316</v>
+        <v>5.05204814139285</v>
       </c>
       <c r="V2" t="n">
-        <v>14.64653331756592</v>
+        <v>14.64639999389648</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>11.3574052802067</v>
+        <v>11.22187651788691</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.03479999542236</v>
+        <v>14.03470000267029</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.21112856087801</v>
+        <v>16.06946291996234</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5042658348469956</v>
+        <v>0.5046799249320054</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.47</v>
+        <v>16.45</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.06</v>
@@ -1165,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="CM2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN2" t="n">
         <v>-1</v>
       </c>
       <c r="CO2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.79999923706055</v>
+        <v>28.6299991607666</v>
       </c>
       <c r="D3" t="n">
-        <v>28.79999923706055</v>
+        <v>28.6299991607666</v>
       </c>
       <c r="E3" t="n">
         <v>28.89999961853027</v>
@@ -1199,67 +1199,67 @@
         <v>28.55999946594238</v>
       </c>
       <c r="H3" t="n">
-        <v>1705300</v>
+        <v>3638900</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008756567659570225</v>
+        <v>0.00280209897877004</v>
       </c>
       <c r="J3" t="n">
-        <v>28.55777761671278</v>
+        <v>28.53888871934679</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8481809179927521</v>
+        <v>0.3192501372979191</v>
       </c>
       <c r="M3" t="n">
-        <v>28.57599983215332</v>
+        <v>28.55899982452393</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7838725021799031</v>
+        <v>0.2486058219087461</v>
       </c>
       <c r="P3" t="n">
-        <v>29.77269231356107</v>
+        <v>29.76615384908823</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.26706455115407</v>
+        <v>-3.8169348115374</v>
       </c>
       <c r="S3" t="n">
-        <v>30.39759994506836</v>
+        <v>30.39419994354248</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-5.255680418502926</v>
+        <v>-5.804399477705944</v>
       </c>
       <c r="V3" t="n">
-        <v>29.30193331400553</v>
+        <v>29.30079998016357</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.712972559066868</v>
+        <v>-2.289360085223272</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.01124997138977</v>
+        <v>28.0103999710083</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.815830305596475</v>
+        <v>2.212032639303996</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2654934644049385</v>
+        <v>0.2634252605277249</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,13 +1411,13 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.56</v>
+        <v>17.46</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="CC3" t="n">
         <v>9</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.989999771118164</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="D4" t="n">
-        <v>8.989999771118164</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="E4" t="n">
         <v>9.350000381469727</v>
@@ -1486,67 +1486,67 @@
         <v>9.279999732971191</v>
       </c>
       <c r="H4" t="n">
-        <v>15317600</v>
+        <v>19606800</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02810813285209035</v>
+        <v>-0.02918923867715373</v>
       </c>
       <c r="J4" t="n">
-        <v>8.716666433546278</v>
+        <v>8.715555297003853</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3.135755390615348</v>
+        <v>3.034164046017623</v>
       </c>
       <c r="M4" t="n">
-        <v>8.69499979019165</v>
+        <v>8.693999767303467</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.392754319089084</v>
+        <v>3.289622528038865</v>
       </c>
       <c r="P4" t="n">
-        <v>8.946538374974178</v>
+        <v>8.946153750786415</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.485790082402807</v>
+        <v>0.378327853430172</v>
       </c>
       <c r="S4" t="n">
-        <v>8.927599935531616</v>
+        <v>8.92739993095398</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6989542098341432</v>
+        <v>0.5891929530340572</v>
       </c>
       <c r="V4" t="n">
-        <v>8.632399943669638</v>
+        <v>8.632333275477091</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.142530811617033</v>
+        <v>4.027488926393686</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.895349948406219</v>
+        <v>8.89529994726181</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.06403708972578</v>
+        <v>0.9521836866286986</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5184328855123049</v>
+        <v>0.5188877594338116</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>17.29</v>
+        <v>17.27</v>
       </c>
       <c r="CA4" t="n">
         <v>0.99</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.43000030517578</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="D5" t="n">
-        <v>12.43000030517578</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="E5" t="n">
         <v>12.56999969482422</v>
@@ -1769,88 +1769,88 @@
         <v>12.39000034332275</v>
       </c>
       <c r="H5" t="n">
-        <v>775200</v>
+        <v>1296100</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002419410287777479</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>12.47444449530708</v>
+        <v>12.4711110856798</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3562819181889361</v>
+        <v>-0.5702095559968025</v>
       </c>
       <c r="M5" t="n">
-        <v>12.49200000762939</v>
+        <v>12.48899993896484</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4963152610930818</v>
+        <v>-0.7126296810755434</v>
       </c>
       <c r="P5" t="n">
-        <v>13.21923076189481</v>
+        <v>13.21807688933152</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-5.970320595310538</v>
+        <v>-6.189079377057724</v>
       </c>
       <c r="S5" t="n">
-        <v>12.96419994354248</v>
+        <v>12.96359992980957</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.120575436147806</v>
+        <v>-4.347560201879632</v>
       </c>
       <c r="V5" t="n">
-        <v>12.11306664148966</v>
+        <v>12.11286663691203</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>2.616460992632168</v>
+        <v>2.370479179084281</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.70049996852875</v>
+        <v>11.70034996509552</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.234779185583494</v>
+        <v>5.979732704764806</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2337802553370897</v>
+        <v>0.2333295883325575</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE5" t="n">
         <v>12.1</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>12.2</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>12.4</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>13.7</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>13.8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>13.9</v>
       </c>
       <c r="AJ5" t="n">
         <v>1</v>
@@ -1977,13 +1977,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-10.11</v>
+        <v>-10.08</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2014,13 +2014,13 @@
         <v>7</v>
       </c>
       <c r="CM5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.5</v>
+        <v>52.70000076293945</v>
       </c>
       <c r="D6" t="n">
-        <v>52.5</v>
+        <v>52.70000076293945</v>
       </c>
       <c r="E6" t="n">
         <v>53.40999984741211</v>
@@ -2048,67 +2048,67 @@
         <v>52.81000137329102</v>
       </c>
       <c r="H6" t="n">
-        <v>3848100</v>
+        <v>6782400</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001331552125367619</v>
+        <v>0.002472913617460604</v>
       </c>
       <c r="J6" t="n">
-        <v>53.86555565728082</v>
+        <v>53.88777796427409</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.535118482707489</v>
+        <v>-2.20416808078836</v>
       </c>
       <c r="M6" t="n">
-        <v>53.94599990844726</v>
+        <v>53.96599998474121</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.680458070851028</v>
+        <v>-2.345920064781002</v>
       </c>
       <c r="P6" t="n">
-        <v>57.81269205533541</v>
+        <v>57.82038439237154</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.189490865172596</v>
+        <v>-8.85567206659325</v>
       </c>
       <c r="S6" t="n">
-        <v>59.10359992980957</v>
+        <v>59.10759994506836</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-11.17292337125301</v>
+        <v>-10.84056735188674</v>
       </c>
       <c r="V6" t="n">
-        <v>58.19580001831055</v>
+        <v>58.19713335673014</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.787304266834445</v>
+        <v>-9.445710255340229</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.55629999160767</v>
+        <v>55.55729999542236</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.50126626875683</v>
+        <v>-5.142977129411141</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2783688080957503</v>
+        <v>0.2793795736192248</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>16.06</v>
+        <v>16.12</v>
       </c>
       <c r="CA6" t="n">
         <v>0.3</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CC6" t="n">
         <v>4</v>
@@ -2297,13 +2297,13 @@
         <v>2</v>
       </c>
       <c r="CM6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN6" t="n">
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.72999954223633</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="D7" t="n">
-        <v>57.72999954223633</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="E7" t="n">
         <v>58.72000122070312</v>
@@ -2331,67 +2331,67 @@
         <v>58.09000015258789</v>
       </c>
       <c r="H7" t="n">
-        <v>496300</v>
+        <v>1766200</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.005512484048749489</v>
+        <v>-0.002583939933730073</v>
       </c>
       <c r="J7" t="n">
-        <v>59.26888868543837</v>
+        <v>59.28777779473199</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.596453514371575</v>
+        <v>-2.340745969022289</v>
       </c>
       <c r="M7" t="n">
-        <v>59.35899963378906</v>
+        <v>59.37599983215332</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.744318640143412</v>
+        <v>-2.485850024331092</v>
       </c>
       <c r="P7" t="n">
-        <v>63.55500015845666</v>
+        <v>63.56153869628906</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.16529085311512</v>
+        <v>-8.907174506051874</v>
       </c>
       <c r="S7" t="n">
-        <v>64.87</v>
+        <v>64.87340003967284</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-11.00662934756232</v>
+        <v>-10.74924161448207</v>
       </c>
       <c r="V7" t="n">
-        <v>58.57297350565592</v>
+        <v>58.57410685221354</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.439185878685493</v>
+        <v>-1.150858907734516</v>
       </c>
       <c r="Y7" t="n">
-        <v>53.95124591827393</v>
+        <v>53.95209592819214</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.004015495187097</v>
+        <v>7.317427673136663</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2954314390435147</v>
+        <v>0.2957543431410397</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.65</v>
+        <v>17.71</v>
       </c>
       <c r="CA7" t="n">
         <v>0.27</v>
@@ -2581,16 +2581,16 @@
         <v>-1</v>
       </c>
       <c r="CL7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -2603,82 +2603,82 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.27000045776367</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="D8" t="n">
-        <v>20.27000045776367</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="E8" t="n">
         <v>20.79000091552734</v>
       </c>
       <c r="F8" t="n">
-        <v>20.21999931335449</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="G8" t="n">
         <v>20.64999961853027</v>
       </c>
       <c r="H8" t="n">
-        <v>603700</v>
+        <v>1292700</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01840189674510262</v>
+        <v>-0.03874088386629648</v>
       </c>
       <c r="J8" t="n">
-        <v>20.07777786254883</v>
+        <v>20.03111118740506</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9573897895015436</v>
+        <v>-0.9041475744451278</v>
       </c>
       <c r="M8" t="n">
-        <v>19.975</v>
+        <v>19.9329999923706</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.476848349254921</v>
+        <v>-0.4163929711164689</v>
       </c>
       <c r="P8" t="n">
-        <v>20.68807689960186</v>
+        <v>20.67192305051363</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-2.020856959625076</v>
+        <v>-3.976033903742134</v>
       </c>
       <c r="S8" t="n">
-        <v>22.5092000579834</v>
+        <v>22.50080005645752</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.947930599273093</v>
+        <v>-11.78091298236766</v>
       </c>
       <c r="V8" t="n">
-        <v>25.09906669616699</v>
+        <v>25.09626669565836</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.24002313257645</v>
+        <v>-20.9045687066126</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.61505003929138</v>
+        <v>26.61295003890991</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-23.84008135307134</v>
+        <v>-25.41225098139176</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4406177277886826</v>
+        <v>0.4507982432002295</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2697,13 +2697,13 @@
         <v>18.3</v>
       </c>
       <c r="AG8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AH8" t="n">
         <v>23</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>23.1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>23.3</v>
       </c>
       <c r="AJ8" t="n">
         <v>1</v>
@@ -2830,13 +2830,13 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>5.03</v>
+        <v>4.93</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="CC8" t="n">
         <v>10</v>
@@ -2864,16 +2864,16 @@
         <v>1</v>
       </c>
       <c r="CL8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CN8" t="n">
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.63999938964844</v>
+        <v>16.5</v>
       </c>
       <c r="D9" t="n">
-        <v>16.63999938964844</v>
+        <v>16.5</v>
       </c>
       <c r="E9" t="n">
         <v>16.68000030517578</v>
@@ -2901,67 +2901,67 @@
         <v>16.54999923706055</v>
       </c>
       <c r="H9" t="n">
-        <v>14272600</v>
+        <v>21619500</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009708728874782357</v>
+        <v>0.001213620043642116</v>
       </c>
       <c r="J9" t="n">
-        <v>16.7111111746894</v>
+        <v>16.69555568695068</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.42553594609955</v>
+        <v>-1.171303852458956</v>
       </c>
       <c r="M9" t="n">
-        <v>16.71000013351441</v>
+        <v>16.69600019454956</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4189152801116455</v>
+        <v>-1.173935027944876</v>
       </c>
       <c r="P9" t="n">
-        <v>17.5288462638855</v>
+        <v>17.52346167197594</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-5.070766557342354</v>
+        <v>-5.840522216068162</v>
       </c>
       <c r="S9" t="n">
-        <v>17.89700010299683</v>
+        <v>17.89420011520386</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.023527440992231</v>
+        <v>-7.791351981244874</v>
       </c>
       <c r="V9" t="n">
-        <v>16.00413340886434</v>
+        <v>16.00320007960002</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>3.973135967686372</v>
+        <v>3.104378611333341</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.23750005245209</v>
+        <v>15.23680005550385</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.204261410129762</v>
+        <v>8.290454294173538</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3519167610154328</v>
+        <v>0.3496137460537244</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>16.98</v>
+        <v>16.84</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM9" t="n">
         <v>4</v>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -3173,82 +3173,82 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.86000061035156</v>
+        <v>20.61000061035156</v>
       </c>
       <c r="D10" t="n">
-        <v>20.86000061035156</v>
+        <v>20.61000061035156</v>
       </c>
       <c r="E10" t="n">
         <v>21.18000030517578</v>
       </c>
       <c r="F10" t="n">
-        <v>20.81999969482422</v>
+        <v>20.61000061035156</v>
       </c>
       <c r="G10" t="n">
         <v>21.05999946594238</v>
       </c>
       <c r="H10" t="n">
-        <v>10257200</v>
+        <v>19220300</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.009966734101293895</v>
+        <v>-0.02183194547390777</v>
       </c>
       <c r="J10" t="n">
-        <v>20.86666679382324</v>
+        <v>20.83888901604546</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.03194656596353448</v>
+        <v>-1.098371441575711</v>
       </c>
       <c r="M10" t="n">
-        <v>20.85000019073486</v>
+        <v>20.82500019073486</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04796364280678714</v>
+        <v>-1.032410940764138</v>
       </c>
       <c r="P10" t="n">
-        <v>21.55153854076679</v>
+        <v>21.54192315615141</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-3.208763630063423</v>
+        <v>-4.326087968305316</v>
       </c>
       <c r="S10" t="n">
-        <v>22.64219997406006</v>
+        <v>22.63719997406006</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.871140462279574</v>
+        <v>-8.95516833367847</v>
       </c>
       <c r="V10" t="n">
-        <v>22.94659999847412</v>
+        <v>22.94493333180746</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.093283485402241</v>
+        <v>-10.17624539452938</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.46045001983643</v>
+        <v>22.45920001983643</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-7.125633760994958</v>
+        <v>-8.233594285867767</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2689692672101995</v>
+        <v>0.2725203153637994</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3260,16 +3260,16 @@
         <v>20</v>
       </c>
       <c r="AF10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AG10" t="n">
         <v>20.7</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>21.1</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>21.2</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>21.3</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -3416,13 +3416,13 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.31</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="CC10" t="n">
         <v>1</v>
@@ -3453,13 +3453,13 @@
         <v>4</v>
       </c>
       <c r="CM10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.65999984741211</v>
+        <v>15.59000015258789</v>
       </c>
       <c r="D11" t="n">
-        <v>15.65999984741211</v>
+        <v>15.59000015258789</v>
       </c>
       <c r="E11" t="n">
         <v>15.80000019073486</v>
@@ -3487,88 +3487,90 @@
         <v>15.71000003814697</v>
       </c>
       <c r="H11" t="n">
-        <v>1814100</v>
+        <v>2934500</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00127874064260447</v>
+        <v>-0.003196943071437364</v>
       </c>
       <c r="J11" t="n">
-        <v>15.49666669633653</v>
+        <v>15.48888895246718</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.053988927271614</v>
+        <v>0.6527982764354991</v>
       </c>
       <c r="M11" t="n">
-        <v>15.4829999923706</v>
+        <v>15.47600002288818</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.143188368718743</v>
+        <v>0.736625287743006</v>
       </c>
       <c r="P11" t="n">
-        <v>16.07538461685181</v>
+        <v>16.07269232089703</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.583980286258594</v>
+        <v>-3.003181786050638</v>
       </c>
       <c r="S11" t="n">
-        <v>16.5103999710083</v>
+        <v>16.50899997711182</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.150693654238935</v>
+        <v>-5.566659554170653</v>
       </c>
       <c r="V11" t="n">
-        <v>16.62159998575846</v>
+        <v>16.6211333211263</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.785244135163059</v>
+        <v>-6.203747654365952</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.07890000343323</v>
+        <v>16.07855000495911</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-2.605278694013096</v>
+        <v>-3.038519345466669</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2159119508959055</v>
+        <v>0.2152455710926054</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
         <v>10.2</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>15.5</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>15.6</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>15.9</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>16</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>16.1</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -3715,13 +3717,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.99</v>
+        <v>6.96</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -3771,10 +3773,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.04000091552734</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="D12" t="n">
-        <v>18.04000091552734</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="E12" t="n">
         <v>18.21999931335449</v>
@@ -3786,67 +3788,67 @@
         <v>18.09000015258789</v>
       </c>
       <c r="H12" t="n">
-        <v>21986900</v>
+        <v>31045500</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002222273084852455</v>
+        <v>-0.005555576748318192</v>
       </c>
       <c r="J12" t="n">
-        <v>17.82000011867947</v>
+        <v>17.80444441901313</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.234572364661559</v>
+        <v>0.5366929586137559</v>
       </c>
       <c r="M12" t="n">
-        <v>17.80700016021729</v>
+        <v>17.79300003051758</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.308478425415005</v>
+        <v>0.6013577689494451</v>
       </c>
       <c r="P12" t="n">
-        <v>18.54307695535513</v>
+        <v>18.53769229008601</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.71301273806395</v>
+        <v>-3.43997872861866</v>
       </c>
       <c r="S12" t="n">
-        <v>19.04140007019043</v>
+        <v>19.03860004425049</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.259062626549142</v>
+        <v>-5.980483980302227</v>
       </c>
       <c r="V12" t="n">
-        <v>19.30053334554037</v>
+        <v>19.29960000356039</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.531075631152359</v>
+        <v>-7.251965764948053</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.6941500043869</v>
+        <v>18.69344999790192</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-3.499218144211162</v>
+        <v>-4.24453688035486</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2577441355023115</v>
+        <v>0.256946470153103</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4014,13 +4016,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.050000000000001</v>
+        <v>7.99</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4070,106 +4072,106 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34.63999938964844</v>
+        <v>34.58000183105469</v>
       </c>
       <c r="D13" t="n">
-        <v>34.63999938964844</v>
+        <v>34.58000183105469</v>
       </c>
       <c r="E13" t="n">
         <v>35.02000045776367</v>
       </c>
       <c r="F13" t="n">
-        <v>34.61000061035156</v>
+        <v>34.58000183105469</v>
       </c>
       <c r="G13" t="n">
         <v>34.90999984741211</v>
       </c>
       <c r="H13" t="n">
-        <v>1529200</v>
+        <v>2537100</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.006310993024991385</v>
+        <v>-0.00803209335612376</v>
       </c>
       <c r="J13" t="n">
-        <v>34.53222232394748</v>
+        <v>34.52555592854818</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3121057911937992</v>
+        <v>0.1576973955732551</v>
       </c>
       <c r="M13" t="n">
-        <v>34.49099998474121</v>
+        <v>34.48500022888184</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4319950276105263</v>
+        <v>0.2754867378347428</v>
       </c>
       <c r="P13" t="n">
-        <v>34.33692315908579</v>
+        <v>34.33461556067834</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8826540140433532</v>
+        <v>0.7146906012175618</v>
       </c>
       <c r="S13" t="n">
-        <v>34.69359992980957</v>
+        <v>34.6923999786377</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1544969108699496</v>
+        <v>-0.3239849294145647</v>
       </c>
       <c r="V13" t="n">
-        <v>34.8038666788737</v>
+        <v>34.80346669514974</v>
       </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4708307003276959</v>
+        <v>-0.6420764519018216</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.29554997444153</v>
+        <v>34.29524998664856</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.004356003806931</v>
+        <v>0.8302952872977662</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1579666238746522</v>
+        <v>0.1585486144210809</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="AE13" t="n">
         <v>34.3</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>34.4</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>34.6</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>34.7</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>34.8</v>
       </c>
-      <c r="AI13" t="n">
-        <v>35</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -4313,13 +4315,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4350,13 +4352,13 @@
         <v>9</v>
       </c>
       <c r="CM13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN13" t="n">
         <v>1</v>
       </c>
       <c r="CO13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -4369,10 +4371,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.990000009536743</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="D14" t="n">
-        <v>3.990000009536743</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="E14" t="n">
         <v>4.159999847412109</v>
@@ -4384,67 +4386,67 @@
         <v>4.079999923706055</v>
       </c>
       <c r="H14" t="n">
-        <v>23361300</v>
+        <v>28203600</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0257069156647316</v>
+        <v>0.02056553253178528</v>
       </c>
       <c r="J14" t="n">
-        <v>4.03111113442315</v>
+        <v>4.028888914320204</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.019845980810199</v>
+        <v>-1.461665659250639</v>
       </c>
       <c r="M14" t="n">
-        <v>4.068000030517578</v>
+        <v>4.066000032424927</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.91740463116248</v>
+        <v>-2.361042868891556</v>
       </c>
       <c r="P14" t="n">
-        <v>4.043076946185185</v>
+        <v>4.04230771614955</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.312785716297648</v>
+        <v>-1.788772469014227</v>
       </c>
       <c r="S14" t="n">
-        <v>4.096800026893615</v>
+        <v>4.096400027275085</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.606913118916691</v>
+        <v>-3.085636115204716</v>
       </c>
       <c r="V14" t="n">
-        <v>5.313266673088074</v>
+        <v>5.313133339881897</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-24.90495480405178</v>
+        <v>-25.27949564505986</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.513400000333786</v>
+        <v>5.513300000429154</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-27.63086281976303</v>
+        <v>-27.99230899277736</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.4901335864716942</v>
+        <v>0.4878762079148878</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4596,13 +4598,13 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>5.62</v>
+        <v>5.59</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CC14" t="n">
         <v>8</v>
@@ -4640,7 +4642,7 @@
         <v>3</v>
       </c>
       <c r="CN14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
         <v>38</v>
@@ -4656,82 +4658,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54.79000091552734</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="D15" t="n">
-        <v>54.79000091552734</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="E15" t="n">
         <v>55.5</v>
       </c>
       <c r="F15" t="n">
-        <v>54.40999984741211</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="G15" t="n">
         <v>54.9900016784668</v>
       </c>
       <c r="H15" t="n">
-        <v>7718800</v>
+        <v>11581300</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00363703867675591</v>
+        <v>-0.01254777996627054</v>
       </c>
       <c r="J15" t="n">
-        <v>54.54777823554145</v>
+        <v>54.49333360460069</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4440559960846753</v>
+        <v>-0.3547853558436428</v>
       </c>
       <c r="M15" t="n">
-        <v>54.54300041198731</v>
+        <v>54.49400024414062</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4528546315280286</v>
+        <v>-0.3560043421494551</v>
       </c>
       <c r="P15" t="n">
-        <v>57.04230778033916</v>
+        <v>57.0234615619366</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.948484821976516</v>
+        <v>-4.77603823106729</v>
       </c>
       <c r="S15" t="n">
-        <v>57.81239982604981</v>
+        <v>57.80259979248047</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.227942309290875</v>
+        <v>-6.059589997672695</v>
       </c>
       <c r="V15" t="n">
-        <v>55.83333323160807</v>
+        <v>55.83006655375163</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.868654897877534</v>
+        <v>-2.74057942456145</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.29259994506836</v>
+        <v>53.29014993667602</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.809772786470237</v>
+        <v>1.895001799740691</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.287380920636897</v>
+        <v>0.2882761737164767</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4903,13 +4905,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ15" t="n">
-        <v>12.31</v>
+        <v>12.2</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CC15" t="n">
         <v>6</v>
@@ -4944,13 +4946,13 @@
         <v>6</v>
       </c>
       <c r="CM15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN15" t="n">
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -4963,10 +4965,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.59000015258789</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="D16" t="n">
-        <v>23.59000015258789</v>
+        <v>23.35000038146973</v>
       </c>
       <c r="E16" t="n">
         <v>23.68000030517578</v>
@@ -4978,88 +4980,88 @@
         <v>23.29000091552734</v>
       </c>
       <c r="H16" t="n">
-        <v>614800</v>
+        <v>1186600</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01288103157009912</v>
+        <v>0.002576189934899498</v>
       </c>
       <c r="J16" t="n">
-        <v>23.05444463094075</v>
+        <v>23.0277779897054</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.323003352370423</v>
+        <v>1.399276959802088</v>
       </c>
       <c r="M16" t="n">
-        <v>23.0480001449585</v>
+        <v>23.02400016784668</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.351614041220624</v>
+        <v>1.415914746553514</v>
       </c>
       <c r="P16" t="n">
-        <v>23.17384624481201</v>
+        <v>23.16461548438439</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.795791269949607</v>
+        <v>0.8002934355215418</v>
       </c>
       <c r="S16" t="n">
-        <v>23.29819995880127</v>
+        <v>23.29339996337891</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.25245810535843</v>
+        <v>0.2429890792233226</v>
       </c>
       <c r="V16" t="n">
-        <v>21.92833329518636</v>
+        <v>21.92673329671224</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>7.577716167631834</v>
+        <v>6.491012890510674</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.61299995422363</v>
+        <v>20.61179995536804</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.44234320562479</v>
+        <v>13.28462546711531</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.250528476642837</v>
+        <v>0.2468411354695097</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="AE16" t="n">
         <v>23</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AF16" t="n">
         <v>23.1</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
         <v>23.4</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>23.9</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>25.7</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>27.5</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
@@ -5194,13 +5196,13 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.85</v>
+        <v>11.73</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="CC16" t="n">
         <v>2</v>
@@ -5254,13 +5256,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.22999954223633</v>
+        <v>20.23999977111816</v>
       </c>
       <c r="D17" t="n">
-        <v>20.22999954223633</v>
+        <v>20.23999977111816</v>
       </c>
       <c r="E17" t="n">
-        <v>20.29999923706055</v>
+        <v>20.45999908447266</v>
       </c>
       <c r="F17" t="n">
         <v>19.72999954223633</v>
@@ -5269,67 +5271,67 @@
         <v>20.07999992370605</v>
       </c>
       <c r="H17" t="n">
-        <v>4126000</v>
+        <v>6083300</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01607231026000289</v>
+        <v>0.0165745819304437</v>
       </c>
       <c r="J17" t="n">
-        <v>19.75</v>
+        <v>19.75111113654243</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.430377429044699</v>
+        <v>2.475246233976285</v>
       </c>
       <c r="M17" t="n">
-        <v>19.64400005340576</v>
+        <v>19.64500007629395</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.983096554863678</v>
+        <v>3.028758933639387</v>
       </c>
       <c r="P17" t="n">
-        <v>18.99384615971492</v>
+        <v>18.99423078390268</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>6.508178344327296</v>
+        <v>6.558670374118286</v>
       </c>
       <c r="S17" t="n">
-        <v>19.392799949646</v>
+        <v>19.39299995422363</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>4.317064038014857</v>
+        <v>4.367554369586133</v>
       </c>
       <c r="V17" t="n">
-        <v>17.32953329722087</v>
+        <v>17.32959996541341</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>16.73712843427012</v>
+        <v>16.79438539558534</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.61714995861054</v>
+        <v>17.61719995975495</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>14.83128423022101</v>
+        <v>14.8877223245169</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3971524367721794</v>
+        <v>0.3973446148921655</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5477,7 +5479,7 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>40.46</v>
+        <v>40.48</v>
       </c>
       <c r="CA17" t="n">
         <v>1.13</v>
@@ -5514,13 +5516,13 @@
         <v>10</v>
       </c>
       <c r="CM17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN17" t="n">
         <v>0</v>
       </c>
       <c r="CO17" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -5533,10 +5535,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.26000022888184</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="D18" t="n">
-        <v>11.26000022888184</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="E18" t="n">
         <v>11.46000003814697</v>
@@ -5548,88 +5550,88 @@
         <v>11.31999969482422</v>
       </c>
       <c r="H18" t="n">
-        <v>2881900</v>
+        <v>3547200</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.005300306321546655</v>
+        <v>-0.01678441568069766</v>
       </c>
       <c r="J18" t="n">
-        <v>11.92999998728434</v>
+        <v>11.91555553012424</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.616091861832598</v>
+        <v>-6.592688135247456</v>
       </c>
       <c r="M18" t="n">
-        <v>11.95799999237061</v>
+        <v>11.94499998092651</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.837094530306951</v>
+        <v>-6.822937361129916</v>
       </c>
       <c r="P18" t="n">
-        <v>10.44692299916194</v>
+        <v>10.44192299476037</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>7.782935030583856</v>
+        <v>6.589563244488783</v>
       </c>
       <c r="S18" t="n">
-        <v>10.15019994735718</v>
+        <v>10.14759994506836</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>10.93377753424077</v>
+        <v>9.681108584202674</v>
       </c>
       <c r="V18" t="n">
-        <v>9.054133323033652</v>
+        <v>9.053266655604045</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>24.36309282343429</v>
+        <v>22.93905103912253</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.802999987602234</v>
+        <v>8.802349987030029</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>27.91094223264722</v>
+        <v>26.44350805001624</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9912433733942698</v>
+        <v>0.9929632130160336</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AE18" t="n">
         <v>10.3</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
         <v>11</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AG18" t="n">
         <v>11.2</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="n">
         <v>12.2</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>16.8</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>17</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -5756,13 +5758,13 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0.57</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="CC18" t="n">
         <v>1</v>
@@ -5816,10 +5818,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.56999969482422</v>
+        <v>11.4399995803833</v>
       </c>
       <c r="D19" t="n">
-        <v>11.56999969482422</v>
+        <v>11.4399995803833</v>
       </c>
       <c r="E19" t="n">
         <v>11.64999961853027</v>
@@ -5831,67 +5833,67 @@
         <v>11.47999954223633</v>
       </c>
       <c r="H19" t="n">
-        <v>3635000</v>
+        <v>5665000</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01669592077966642</v>
+        <v>0.005272360750352201</v>
       </c>
       <c r="J19" t="n">
-        <v>11.26333321465386</v>
+        <v>11.24888875749376</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.722697396285643</v>
+        <v>1.698930685595285</v>
       </c>
       <c r="M19" t="n">
-        <v>11.23599987030029</v>
+        <v>11.2229998588562</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.972586582229985</v>
+        <v>1.93352690239822</v>
       </c>
       <c r="P19" t="n">
-        <v>11.37961530685425</v>
+        <v>11.37461530245267</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.673030087891434</v>
+        <v>0.5748262793250453</v>
       </c>
       <c r="S19" t="n">
-        <v>11.8421999168396</v>
+        <v>11.83959991455078</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.298561280225573</v>
+        <v>-3.375116870937293</v>
       </c>
       <c r="V19" t="n">
-        <v>13.14799997965495</v>
+        <v>13.14713331222534</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-12.00182755759436</v>
+        <v>-12.9848362475689</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.99404997348785</v>
+        <v>13.99339997291565</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-17.32200673326215</v>
+        <v>-18.24717650802862</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5959985013222042</v>
+        <v>0.5935110786783261</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6043,13 +6045,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.09</v>
+        <v>6.02</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CC19" t="n">
         <v>6</v>
@@ -6103,106 +6105,106 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.14000034332275</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="D20" t="n">
-        <v>11.14000034332275</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="E20" t="n">
         <v>11.23999977111816</v>
       </c>
       <c r="F20" t="n">
-        <v>11.05000019073486</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="G20" t="n">
         <v>11.22000026702881</v>
       </c>
       <c r="H20" t="n">
-        <v>6666700</v>
+        <v>9733300</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.001792070283405334</v>
+        <v>-0.009856600195451981</v>
       </c>
       <c r="J20" t="n">
-        <v>11.29888894822862</v>
+        <v>11.28888893127441</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.406232113917538</v>
+        <v>-2.116140410220002</v>
       </c>
       <c r="M20" t="n">
-        <v>11.29600009918213</v>
+        <v>11.28700008392334</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.381017656601026</v>
+        <v>-2.099759824809855</v>
       </c>
       <c r="P20" t="n">
-        <v>11.87538473422711</v>
+        <v>11.8719231898968</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-6.192510031147344</v>
+        <v>-6.923250647893421</v>
       </c>
       <c r="S20" t="n">
-        <v>12.34820011138916</v>
+        <v>12.3464001083374</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.784420054482617</v>
+        <v>-10.50022602723763</v>
       </c>
       <c r="V20" t="n">
-        <v>11.70053337097168</v>
+        <v>11.69993336995443</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.790662185021197</v>
+        <v>-5.555016072900045</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.51430003166199</v>
+        <v>11.51385003089905</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.25073766803006</v>
+        <v>-4.028624994414364</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.220661177121628</v>
+        <v>0.22035403881122</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AE20" t="n">
         <v>10.9</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
         <v>11</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AG20" t="n">
         <v>11.1</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AH20" t="n">
         <v>11.2</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>11.3</v>
       </c>
-      <c r="AI20" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -6326,7 +6328,7 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.59</v>
+        <v>6.54</v>
       </c>
       <c r="CA20" t="n">
         <v>0.5600000000000001</v>
@@ -6382,13 +6384,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.730000019073486</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="D21" t="n">
-        <v>4.730000019073486</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="E21" t="n">
-        <v>4.739999771118164</v>
+        <v>4.75</v>
       </c>
       <c r="F21" t="n">
         <v>4.570000171661377</v>
@@ -6397,67 +6399,67 @@
         <v>4.650000095367432</v>
       </c>
       <c r="H21" t="n">
-        <v>3975700</v>
+        <v>6098100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02159825100666191</v>
+        <v>0.01511872421037097</v>
       </c>
       <c r="J21" t="n">
-        <v>4.458888901604547</v>
+        <v>4.455555544959174</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>6.080239347775172</v>
+        <v>5.486280259316178</v>
       </c>
       <c r="M21" t="n">
-        <v>4.484999990463256</v>
+        <v>4.481999969482422</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>5.462653938265087</v>
+        <v>4.86389650305798</v>
       </c>
       <c r="P21" t="n">
-        <v>4.655000008069551</v>
+        <v>4.653846153846154</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.61117101769969</v>
+        <v>0.9917314387549965</v>
       </c>
       <c r="S21" t="n">
-        <v>4.794400005340576</v>
+        <v>4.793800001144409</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.343233484802138</v>
+        <v>-1.956698065352741</v>
       </c>
       <c r="V21" t="n">
-        <v>5.337400004069011</v>
+        <v>5.337200002670288</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-11.38007240477513</v>
+        <v>-11.93884795560125</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.311300013065338</v>
+        <v>5.311150012016296</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-10.94458969672028</v>
+        <v>-11.50692790390881</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5108959898705311</v>
+        <v>0.5086561672834405</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6609,13 +6611,13 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>11.54</v>
+        <v>11.46</v>
       </c>
       <c r="CA21" t="n">
         <v>0.01</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC21" t="n">
         <v>3</v>
@@ -6669,10 +6671,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.539999961853027</v>
+        <v>2.529999971389771</v>
       </c>
       <c r="D22" t="n">
-        <v>2.539999961853027</v>
+        <v>2.529999971389771</v>
       </c>
       <c r="E22" t="n">
         <v>2.589999914169312</v>
@@ -6684,67 +6686,67 @@
         <v>2.539999961853027</v>
       </c>
       <c r="H22" t="n">
-        <v>11203500</v>
+        <v>15381900</v>
       </c>
       <c r="I22" t="n">
-        <v>0.003952565445193956</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2.514444430669149</v>
+        <v>2.513333320617676</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.016349014206591</v>
+        <v>0.6631293444197341</v>
       </c>
       <c r="M22" t="n">
-        <v>2.516999983787537</v>
+        <v>2.515999984741211</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9137853879077448</v>
+        <v>0.55643826444615</v>
       </c>
       <c r="P22" t="n">
-        <v>2.684615382781395</v>
+        <v>2.684230767763578</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-5.386820840553305</v>
+        <v>-5.74580986948108</v>
       </c>
       <c r="S22" t="n">
-        <v>2.887800002098083</v>
+        <v>2.887600002288818</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-12.04377172907984</v>
+        <v>-12.38398776200308</v>
       </c>
       <c r="V22" t="n">
-        <v>3.289248352050781</v>
+        <v>3.289181685447693</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-22.77871142598923</v>
+        <v>-23.08117296824209</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.154481613636017</v>
+        <v>3.154431613683701</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-19.47963966969224</v>
+        <v>-19.79537738542785</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4305354580137679</v>
+        <v>0.4297235762236731</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6892,13 +6894,13 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>7.7</v>
+        <v>7.67</v>
       </c>
       <c r="CA22" t="n">
         <v>1.02</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="CC22" t="n">
         <v>6</v>
@@ -6952,82 +6954,82 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.13999938964844</v>
+        <v>43.02999877929688</v>
       </c>
       <c r="D23" t="n">
-        <v>43.13999938964844</v>
+        <v>43.02999877929688</v>
       </c>
       <c r="E23" t="n">
         <v>44.34999847412109</v>
       </c>
       <c r="F23" t="n">
-        <v>42.95999908447266</v>
+        <v>42.93999862670898</v>
       </c>
       <c r="G23" t="n">
         <v>44.18000030517578</v>
       </c>
       <c r="H23" t="n">
-        <v>1558400</v>
+        <v>2616800</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.02354008393715434</v>
+        <v>-0.02602991213071992</v>
       </c>
       <c r="J23" t="n">
-        <v>43.78111139933268</v>
+        <v>43.76888910929362</v>
       </c>
       <c r="K23" t="n">
         <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.46435754870767</v>
+        <v>-1.688163316532178</v>
       </c>
       <c r="M23" t="n">
-        <v>43.85500030517578</v>
+        <v>43.84400024414062</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.630374895797131</v>
+        <v>-1.856585759308158</v>
       </c>
       <c r="P23" t="n">
-        <v>47.40961544330303</v>
+        <v>47.40538465059721</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-9.005801911134697</v>
+        <v>-9.229723381740792</v>
       </c>
       <c r="S23" t="n">
-        <v>48.80599975585938</v>
+        <v>48.80379974365234</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-11.60922918197308</v>
+        <v>-11.83063817711537</v>
       </c>
       <c r="V23" t="n">
-        <v>48.81740002950033</v>
+        <v>48.81666669209798</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-11.62987098129159</v>
+        <v>-11.8538775891837</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.31559999465942</v>
+        <v>46.31504999160767</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.856438447039784</v>
+        <v>-7.092837453281482</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2647540094084426</v>
+        <v>0.2660747462059046</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7179,13 +7181,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.630000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="CA23" t="n">
         <v>0.52</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7220,13 +7222,13 @@
         <v>2</v>
       </c>
       <c r="CM23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -7239,82 +7241,82 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.53999996185303</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="D24" t="n">
-        <v>14.53999996185303</v>
+        <v>14.44999980926514</v>
       </c>
       <c r="E24" t="n">
         <v>14.77000045776367</v>
       </c>
       <c r="F24" t="n">
-        <v>14.47999954223633</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="G24" t="n">
         <v>14.76000022888184</v>
       </c>
       <c r="H24" t="n">
-        <v>14129300</v>
+        <v>19352700</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.006830626989386412</v>
+        <v>-0.01297817825149683</v>
       </c>
       <c r="J24" t="n">
-        <v>14.79222212897407</v>
+        <v>14.78222211201986</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.705099916171509</v>
+        <v>-2.247444939178535</v>
       </c>
       <c r="M24" t="n">
-        <v>14.79799995422363</v>
+        <v>14.78899993896484</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.743478802329412</v>
+        <v>-2.292245122041942</v>
       </c>
       <c r="P24" t="n">
-        <v>15.38576911045955</v>
+        <v>15.38230756612924</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-5.497087227388258</v>
+        <v>-6.060909605766713</v>
       </c>
       <c r="S24" t="n">
-        <v>15.60359991073608</v>
+        <v>15.60179990768433</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.816375419567414</v>
+        <v>-7.3824821830454</v>
       </c>
       <c r="V24" t="n">
-        <v>14.15653327941894</v>
+        <v>14.15593327840169</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>2.708761211981005</v>
+        <v>2.077337644082531</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.51074995040894</v>
+        <v>13.510299949646</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>7.618007995277408</v>
+        <v>6.955432989063754</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2230619291838968</v>
+        <v>0.2242174499179031</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7466,13 +7468,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>15.98</v>
+        <v>15.88</v>
       </c>
       <c r="CA24" t="n">
         <v>0.42</v>
       </c>
       <c r="CB24" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CC24" t="n">
         <v>3</v>
@@ -7522,10 +7524,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.950000047683716</v>
+        <v>3.940000057220459</v>
       </c>
       <c r="D25" t="n">
-        <v>3.950000047683716</v>
+        <v>3.940000057220459</v>
       </c>
       <c r="E25" t="n">
         <v>4.099999904632568</v>
@@ -7537,67 +7539,67 @@
         <v>4.079999923706055</v>
       </c>
       <c r="H25" t="n">
-        <v>53419900</v>
+        <v>65594600</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.01496263784873919</v>
+        <v>-0.01745640091419542</v>
       </c>
       <c r="J25" t="n">
-        <v>4.242222282621595</v>
+        <v>4.241111172570123</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.888423459915755</v>
+        <v>-7.099816606957504</v>
       </c>
       <c r="M25" t="n">
-        <v>4.259000039100647</v>
+        <v>4.258000040054322</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.255223962904234</v>
+        <v>-7.468294500762987</v>
       </c>
       <c r="P25" t="n">
-        <v>4.740000000366797</v>
+        <v>4.73961538534898</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-16.66666566712972</v>
+        <v>-16.87089063387461</v>
       </c>
       <c r="S25" t="n">
-        <v>5.018799996376037</v>
+        <v>5.018599996566772</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-21.29592630636961</v>
+        <v>-21.49204838170375</v>
       </c>
       <c r="V25" t="n">
-        <v>5.57600000222524</v>
+        <v>5.575933335622151</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-29.16068783882046</v>
+        <v>-29.33918287635263</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.748699992895126</v>
+        <v>5.74864999294281</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-31.28881220857657</v>
+        <v>-31.46216829938674</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4572610517775189</v>
+        <v>0.4575263326845292</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7749,13 +7751,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.65</v>
+        <v>-1.64</v>
       </c>
       <c r="CA25" t="n">
         <v>3.03</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7809,10 +7811,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>52.70999908447266</v>
+        <v>52.93999862670898</v>
       </c>
       <c r="D26" t="n">
-        <v>52.70999908447266</v>
+        <v>52.93999862670898</v>
       </c>
       <c r="E26" t="n">
         <v>53.20999908447266</v>
@@ -7824,67 +7826,67 @@
         <v>49.95000076293945</v>
       </c>
       <c r="H26" t="n">
-        <v>5748800</v>
+        <v>8535100</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03862067161522464</v>
+        <v>0.04315268229968439</v>
       </c>
       <c r="J26" t="n">
-        <v>52.46888860066732</v>
+        <v>52.49444410536024</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4595303812138868</v>
+        <v>0.8487651006542307</v>
       </c>
       <c r="M26" t="n">
-        <v>52.39199981689453</v>
+        <v>52.41499977111816</v>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6069614992546635</v>
+        <v>1.001619494196982</v>
       </c>
       <c r="P26" t="n">
-        <v>53.71730745755709</v>
+        <v>53.72615359379695</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.875202650245128</v>
+        <v>-1.463263074873713</v>
       </c>
       <c r="S26" t="n">
-        <v>55.15619995117188</v>
+        <v>55.1607999420166</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.435042422909428</v>
+        <v>-4.026049871724229</v>
       </c>
       <c r="V26" t="n">
-        <v>48.82566660563151</v>
+        <v>48.82719993591309</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>7.9555134601954</v>
+        <v>8.423171298362488</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.41584993362427</v>
+        <v>44.41699993133545</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.67384990548035</v>
+        <v>19.18859605229822</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3243198166071996</v>
+        <v>0.3295745335926139</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8036,13 +8038,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.81</v>
+        <v>14.87</v>
       </c>
       <c r="CA26" t="n">
         <v>0.34</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8077,13 +8079,13 @@
         <v>7</v>
       </c>
       <c r="CM26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CN26" t="n">
         <v>0</v>
       </c>
       <c r="CO26" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
@@ -8096,13 +8098,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.739999771118164</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="D27" t="n">
-        <v>6.739999771118164</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="E27" t="n">
-        <v>6.769999980926514</v>
+        <v>6.880000114440918</v>
       </c>
       <c r="F27" t="n">
         <v>6.400000095367432</v>
@@ -8111,67 +8113,67 @@
         <v>6.579999923706055</v>
       </c>
       <c r="H27" t="n">
-        <v>11185700</v>
+        <v>15153000</v>
       </c>
       <c r="I27" t="n">
-        <v>0.02900756867947263</v>
+        <v>0.03816793781985406</v>
       </c>
       <c r="J27" t="n">
-        <v>6.438888920678033</v>
+        <v>6.445555633968777</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>4.676441139916783</v>
+        <v>5.499053563328587</v>
       </c>
       <c r="M27" t="n">
-        <v>6.437000036239624</v>
+        <v>6.443000078201294</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>4.707157576086436</v>
+        <v>5.540898776975242</v>
       </c>
       <c r="P27" t="n">
-        <v>6.446923054181612</v>
+        <v>6.449230762628408</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>4.545993716280764</v>
+        <v>5.438934363134766</v>
       </c>
       <c r="S27" t="n">
-        <v>6.452399969100952</v>
+        <v>6.453599977493286</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>4.457253167727679</v>
+        <v>5.367550118532857</v>
       </c>
       <c r="V27" t="n">
-        <v>8.100666659673054</v>
+        <v>8.101066662470499</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-16.79697419631642</v>
+        <v>-16.06043408781015</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.016199984550475</v>
+        <v>8.01649998664856</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-15.92026416371743</v>
+        <v>-15.1749491416425</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4878009303381183</v>
+        <v>0.4930733214683481</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8323,10 +8325,10 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>-4.46</v>
+        <v>-4.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CB27" t="n">
         <v>0.7</v>
@@ -8363,7 +8365,7 @@
         <v>10</v>
       </c>
       <c r="CN27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO27" t="n">
         <v>75</v>
@@ -8379,10 +8381,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32.2599983215332</v>
+        <v>32.18000030517578</v>
       </c>
       <c r="D28" t="n">
-        <v>32.2599983215332</v>
+        <v>32.18000030517578</v>
       </c>
       <c r="E28" t="n">
         <v>32.58000183105469</v>
@@ -8394,67 +8396,67 @@
         <v>31.6299991607666</v>
       </c>
       <c r="H28" t="n">
-        <v>2882200</v>
+        <v>4232800</v>
       </c>
       <c r="I28" t="n">
-        <v>0.02477759817786396</v>
+        <v>0.02223636509270821</v>
       </c>
       <c r="J28" t="n">
-        <v>31.00666660732693</v>
+        <v>30.99777793884277</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>4.042136260819819</v>
+        <v>3.813893914155652</v>
       </c>
       <c r="M28" t="n">
-        <v>30.94300003051758</v>
+        <v>30.93500022888184</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>4.256207509668533</v>
+        <v>4.024567858679295</v>
       </c>
       <c r="P28" t="n">
-        <v>30.92230782142052</v>
+        <v>30.91923097463755</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>4.325972394550813</v>
+        <v>4.077621890312924</v>
       </c>
       <c r="S28" t="n">
-        <v>33.05200004577637</v>
+        <v>33.05040008544922</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.396229345111513</v>
+        <v>-2.633552931350566</v>
       </c>
       <c r="V28" t="n">
-        <v>34.75853322347005</v>
+        <v>34.757999903361</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-7.18826334204966</v>
+        <v>-7.416996390335846</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.2862499332428</v>
+        <v>34.28584994316101</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-5.909808204906689</v>
+        <v>-6.142037142075527</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.5022573103900642</v>
+        <v>0.5010653469554753</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8602,13 +8604,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8662,10 +8664,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.43000030517578</v>
+        <v>17.44000053405762</v>
       </c>
       <c r="D29" t="n">
-        <v>17.43000030517578</v>
+        <v>17.44000053405762</v>
       </c>
       <c r="E29" t="n">
         <v>17.54999923706055</v>
@@ -8677,67 +8679,67 @@
         <v>17.51000022888184</v>
       </c>
       <c r="H29" t="n">
-        <v>1210100</v>
+        <v>2071900</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.001718143234242908</v>
+        <v>-0.001145392409145352</v>
       </c>
       <c r="J29" t="n">
-        <v>17.60777812533908</v>
+        <v>17.60888926188151</v>
       </c>
       <c r="K29" t="n">
         <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.009655045047768</v>
+        <v>-0.9591106248222758</v>
       </c>
       <c r="M29" t="n">
-        <v>17.58600025177002</v>
+        <v>17.5870002746582</v>
       </c>
       <c r="N29" t="n">
         <v>-1</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.8870689432552333</v>
+        <v>-0.8358431699827867</v>
       </c>
       <c r="P29" t="n">
-        <v>17.73230780087984</v>
+        <v>17.73269242506761</v>
       </c>
       <c r="Q29" t="n">
         <v>-1</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.704840109357133</v>
+        <v>-1.650577836652884</v>
       </c>
       <c r="S29" t="n">
-        <v>18.09220012664795</v>
+        <v>18.09240013122558</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.660139821783287</v>
+        <v>-3.605931730649679</v>
       </c>
       <c r="V29" t="n">
-        <v>17.06633344014486</v>
+        <v>17.0664001083374</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>2.130902143136837</v>
+        <v>2.18909918523299</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.37035008907318</v>
+        <v>16.37040009021759</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>6.472984452604294</v>
+        <v>6.533746505555385</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2316385288261404</v>
+        <v>0.2316949922849287</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8897,7 +8899,7 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>11.94</v>
+        <v>11.95</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
@@ -8938,13 +8940,13 @@
         <v>7</v>
       </c>
       <c r="CM29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN29" t="n">
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
@@ -8957,10 +8959,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.52000045776367</v>
+        <v>22.5</v>
       </c>
       <c r="D30" t="n">
-        <v>22.52000045776367</v>
+        <v>22.5</v>
       </c>
       <c r="E30" t="n">
         <v>22.79999923706055</v>
@@ -8972,67 +8974,67 @@
         <v>22.29000091552734</v>
       </c>
       <c r="H30" t="n">
-        <v>13616300</v>
+        <v>15444000</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01441440017238316</v>
+        <v>0.01351347868245867</v>
       </c>
       <c r="J30" t="n">
-        <v>22.03555573357476</v>
+        <v>22.03333346048991</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>2.198468375593455</v>
+        <v>2.118002436385373</v>
       </c>
       <c r="M30" t="n">
-        <v>22.01600017547607</v>
+        <v>22.01400012969971</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.289245449993282</v>
+        <v>2.207685415812357</v>
       </c>
       <c r="P30" t="n">
-        <v>23.0115385055542</v>
+        <v>23.01076925717867</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.136050345664141</v>
+        <v>-2.21969657541687</v>
       </c>
       <c r="S30" t="n">
-        <v>25.06999996185303</v>
+        <v>25.06959995269775</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-10.17151778208808</v>
+        <v>-10.24986420822897</v>
       </c>
       <c r="V30" t="n">
-        <v>28.69239994049072</v>
+        <v>28.69226660410563</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.51231509225047</v>
+        <v>-21.5816571396962</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.61699996948242</v>
+        <v>28.6168999671936</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-21.30551601572729</v>
+        <v>-21.37513138811686</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4048745552321386</v>
+        <v>0.4044702567543937</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9236,10 +9238,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.43000030517578</v>
+        <v>13.36999988555908</v>
       </c>
       <c r="D31" t="n">
-        <v>13.43000030517578</v>
+        <v>13.36999988555908</v>
       </c>
       <c r="E31" t="n">
         <v>13.65999984741211</v>
@@ -9251,67 +9253,67 @@
         <v>13.40999984741211</v>
       </c>
       <c r="H31" t="n">
-        <v>4647700</v>
+        <v>7432100</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00825830426965446</v>
+        <v>0.003753768159190818</v>
       </c>
       <c r="J31" t="n">
-        <v>13.12333329518636</v>
+        <v>13.11666658189562</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>2.336807296526603</v>
+        <v>1.931384792635736</v>
       </c>
       <c r="M31" t="n">
-        <v>13.10899991989136</v>
+        <v>13.10299987792969</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.448702320894399</v>
+        <v>2.037701366990946</v>
       </c>
       <c r="P31" t="n">
-        <v>13.1965385216933</v>
+        <v>13.19423081324651</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.769113795247897</v>
+        <v>1.332166117149542</v>
       </c>
       <c r="S31" t="n">
-        <v>13.51740005493164</v>
+        <v>13.51620004653931</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.6465721914028291</v>
+        <v>-1.081666152297429</v>
       </c>
       <c r="V31" t="n">
-        <v>15.01786668141683</v>
+        <v>15.01746667861939</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.5731819966539</v>
+        <v>-10.97033759632594</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.03431666374207</v>
+        <v>15.03401666164398</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-10.67102944848421</v>
+        <v>-11.06834463161316</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.467038326795581</v>
+        <v>0.4663087289052153</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9463,13 +9465,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>8.34</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
       </c>
       <c r="CB31" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC31" t="n">
         <v>9</v>
@@ -9519,10 +9521,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>32.43000030517578</v>
+        <v>32.31999969482422</v>
       </c>
       <c r="D32" t="n">
-        <v>32.43000030517578</v>
+        <v>32.31999969482422</v>
       </c>
       <c r="E32" t="n">
         <v>32.93999862670898</v>
@@ -9534,73 +9536,73 @@
         <v>32.79000091552734</v>
       </c>
       <c r="H32" t="n">
-        <v>969900</v>
+        <v>1512500</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.006129352019387024</v>
+        <v>-0.009500501475433243</v>
       </c>
       <c r="J32" t="n">
-        <v>32.33333418104384</v>
+        <v>32.32111189100478</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2989673863842214</v>
+        <v>-0.003441082671622654</v>
       </c>
       <c r="M32" t="n">
-        <v>32.35700073242187</v>
+        <v>32.34600067138672</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2256067345598003</v>
+        <v>-0.08038389916160631</v>
       </c>
       <c r="P32" t="n">
-        <v>33.79000032865084</v>
+        <v>33.78576953594501</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-4.024859456192143</v>
+        <v>-4.338423724702642</v>
       </c>
       <c r="S32" t="n">
-        <v>33.87260013580322</v>
+        <v>33.87040012359619</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-4.258899006405536</v>
+        <v>-4.577449404537352</v>
       </c>
       <c r="V32" t="n">
-        <v>32.21079044342041</v>
+        <v>32.21005710601807</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0.6805479118571311</v>
+        <v>0.3413300027512446</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.31634269714355</v>
+        <v>31.3157926940918</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.556154748982891</v>
+        <v>3.206711101143163</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2030314712825135</v>
+        <v>0.2034080435176699</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>29</v>
+        <v>27.9</v>
       </c>
       <c r="AE32" t="n">
         <v>29.1</v>
@@ -9744,13 +9746,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>14.41</v>
+        <v>14.36</v>
       </c>
       <c r="CA32" t="n">
         <v>0.67</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CC32" t="n">
         <v>2</v>
@@ -9781,13 +9783,13 @@
         <v>7</v>
       </c>
       <c r="CM32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN32" t="n">
         <v>1</v>
       </c>
       <c r="CO32" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
@@ -9800,10 +9802,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>73.87000274658203</v>
+        <v>73.59999847412109</v>
       </c>
       <c r="D33" t="n">
-        <v>73.87000274658203</v>
+        <v>73.59999847412109</v>
       </c>
       <c r="E33" t="n">
         <v>74.55999755859375</v>
@@ -9815,46 +9817,46 @@
         <v>73.44999694824219</v>
       </c>
       <c r="H33" t="n">
-        <v>1829000</v>
+        <v>2637000</v>
       </c>
       <c r="I33" t="n">
-        <v>0.00503405097390508</v>
+        <v>0.001360523457429874</v>
       </c>
       <c r="J33" t="n">
-        <v>71.7433327568902</v>
+        <v>71.7133322821723</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>2.964275435737392</v>
+        <v>2.630844407738964</v>
       </c>
       <c r="M33" t="n">
-        <v>71.69399948120117</v>
+        <v>71.66699905395508</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>3.035126065119891</v>
+        <v>2.697195983761981</v>
       </c>
       <c r="P33" t="n">
-        <v>75.19153829721304</v>
+        <v>75.18115351750301</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.757558869732546</v>
+        <v>-2.103126873430855</v>
       </c>
       <c r="S33" t="n">
-        <v>77.58239974975587</v>
+        <v>77.57699966430664</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-4.785102052976282</v>
+        <v>-5.126521014469414</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
@@ -9867,21 +9869,19 @@
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
-        <v>0.4866955403539115</v>
+        <v>0.4861551492415598</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AD33" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="AE33" t="n">
-        <v>69.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>71.8</v>
+        <v>73</v>
       </c>
       <c r="AG33" t="n">
         <v>74</v>
@@ -10017,13 +10017,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>32.26</v>
+        <v>32.14</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC33" t="n">
         <v>8</v>
@@ -10055,7 +10055,7 @@
         <v>0</v>
       </c>
       <c r="CL33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM33" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
@@ -10077,10 +10077,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.28000068664551</v>
+        <v>25</v>
       </c>
       <c r="D34" t="n">
-        <v>25.28000068664551</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
         <v>25.53000068664551</v>
@@ -10092,67 +10092,67 @@
         <v>25.28000068664551</v>
       </c>
       <c r="H34" t="n">
-        <v>1530000</v>
+        <v>3921600</v>
       </c>
       <c r="I34" t="n">
-        <v>0.005568866364201952</v>
+        <v>-0.005568790495121601</v>
       </c>
       <c r="J34" t="n">
-        <v>25.06555514865451</v>
+        <v>25.03444396124946</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8555387531582547</v>
+        <v>-0.1375862843319935</v>
       </c>
       <c r="M34" t="n">
-        <v>25.0649995803833</v>
+        <v>25.03699951171875</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8577742264574942</v>
+        <v>-0.1477793363435296</v>
       </c>
       <c r="P34" t="n">
-        <v>26.20076905764066</v>
+        <v>26.18999980046199</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.514279939529642</v>
+        <v>-4.543718249440379</v>
       </c>
       <c r="S34" t="n">
-        <v>25.82959991455078</v>
+        <v>25.82399990081787</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-2.127788388993445</v>
+        <v>-3.190829863625324</v>
       </c>
       <c r="V34" t="n">
-        <v>22.03840001424154</v>
+        <v>22.03653334299723</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>14.70887482897671</v>
+        <v>13.44797119799469</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.41500002861023</v>
+        <v>20.413600025177</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>23.83051996677596</v>
+        <v>22.46737454033775</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2567173629156684</v>
+        <v>0.255802334319678</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10304,13 +10304,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>37.73</v>
+        <v>37.31</v>
       </c>
       <c r="CA34" t="n">
         <v>0.38</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CC34" t="n">
         <v>10</v>
@@ -10341,13 +10341,13 @@
         <v>8</v>
       </c>
       <c r="CM34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
@@ -10360,10 +10360,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.61000061035156</v>
+        <v>48.40000152587891</v>
       </c>
       <c r="D35" t="n">
-        <v>48.61000061035156</v>
+        <v>48.40000152587891</v>
       </c>
       <c r="E35" t="n">
         <v>49.13000106811523</v>
@@ -10375,67 +10375,67 @@
         <v>48.56000137329102</v>
       </c>
       <c r="H35" t="n">
-        <v>1442700</v>
+        <v>2176000</v>
       </c>
       <c r="I35" t="n">
-        <v>0.007669961007690462</v>
+        <v>0.00331674630690415</v>
       </c>
       <c r="J35" t="n">
-        <v>48.36222288343642</v>
+        <v>48.33888965182834</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5123373413011737</v>
+        <v>0.1264238266347021</v>
       </c>
       <c r="M35" t="n">
-        <v>48.37200050354004</v>
+        <v>48.35100059509277</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.492020392652788</v>
+        <v>0.1013441918120487</v>
       </c>
       <c r="P35" t="n">
-        <v>51.08423100985014</v>
+        <v>51.0761541219858</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-4.843432798315959</v>
+        <v>-5.239534264297597</v>
       </c>
       <c r="S35" t="n">
-        <v>52.28819999694824</v>
+        <v>52.28400001525879</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-7.034473144631784</v>
+        <v>-7.428655971705228</v>
       </c>
       <c r="V35" t="n">
-        <v>50.43979377746582</v>
+        <v>50.43839378356934</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-3.627677732361641</v>
+        <v>-4.041350457029131</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.90602699279785</v>
+        <v>48.90497699737548</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.6052963216371675</v>
+        <v>-1.032564582381213</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2441527515813177</v>
+        <v>0.2423790558343404</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10587,13 +10587,13 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.86</v>
+        <v>12.8</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CC35" t="n">
         <v>5</v>
@@ -10621,16 +10621,16 @@
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.56999969482422</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="D36" t="n">
-        <v>38.56999969482422</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="E36" t="n">
         <v>38.95000076293945</v>
@@ -10658,67 +10658,67 @@
         <v>38.15000152587891</v>
       </c>
       <c r="H36" t="n">
-        <v>6590300</v>
+        <v>8916600</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01526712268312891</v>
+        <v>0.005527746122519606</v>
       </c>
       <c r="J36" t="n">
-        <v>38.27222188313802</v>
+        <v>38.23111089070638</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.7780520623951298</v>
+        <v>-0.08137385245190985</v>
       </c>
       <c r="M36" t="n">
-        <v>38.303999710083</v>
+        <v>38.26699981689453</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6944444098645732</v>
+        <v>-0.1750831114946724</v>
       </c>
       <c r="P36" t="n">
-        <v>40.71192301236666</v>
+        <v>40.69769228421725</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-5.261169601081756</v>
+        <v>-6.137182186731532</v>
       </c>
       <c r="S36" t="n">
-        <v>41.39199996948242</v>
+        <v>41.38459999084473</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-6.817743227529019</v>
+        <v>-7.695131108213644</v>
       </c>
       <c r="V36" t="n">
-        <v>40.05639999389648</v>
+        <v>40.05393333435059</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-3.710768564570837</v>
+        <v>-4.62859054549129</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.05920000076294</v>
+        <v>39.05735000610352</v>
       </c>
       <c r="Z36" t="n">
         <v>-1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-1.252458590880428</v>
+        <v>-2.195103464597796</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2601062743999914</v>
+        <v>0.2549849013720991</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10870,13 +10870,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>31.36</v>
+        <v>31.06</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CC36" t="n">
         <v>8</v>
@@ -10904,16 +10904,16 @@
         <v>0</v>
       </c>
       <c r="CL36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN36" t="n">
         <v>0</v>
       </c>
       <c r="CO36" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
@@ -10926,10 +10926,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15.69999980926514</v>
+        <v>15.73999977111816</v>
       </c>
       <c r="D37" t="n">
-        <v>15.69999980926514</v>
+        <v>15.73999977111816</v>
       </c>
       <c r="E37" t="n">
         <v>16.11000061035156</v>
@@ -10941,67 +10941,67 @@
         <v>16.05999946594238</v>
       </c>
       <c r="H37" t="n">
-        <v>1874500</v>
+        <v>2716700</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01752188616971684</v>
+        <v>-0.01501875957404297</v>
       </c>
       <c r="J37" t="n">
-        <v>15.75222195519341</v>
+        <v>15.75666639539931</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.3315224104689484</v>
+        <v>-0.1057750660127429</v>
       </c>
       <c r="M37" t="n">
-        <v>15.73699979782105</v>
+        <v>15.74099979400635</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.2351146281455246</v>
+        <v>-0.006352982029540552</v>
       </c>
       <c r="P37" t="n">
-        <v>16.04615372877855</v>
+        <v>16.04769218884982</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-2.157239207378318</v>
+        <v>-1.917362410187808</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06819993972778</v>
+        <v>16.06899993896484</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-2.291483376132825</v>
+        <v>-2.047421551411577</v>
       </c>
       <c r="V37" t="n">
-        <v>15.8552666982015</v>
+        <v>15.85553336461385</v>
       </c>
       <c r="W37" t="n">
         <v>-1</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.9792764252522635</v>
+        <v>-0.7286641883238918</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.70110000610352</v>
+        <v>15.70130000591278</v>
       </c>
       <c r="Z37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0.007007132226097492</v>
+        <v>0.2464749109360967</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2609479690542923</v>
+        <v>0.259904632496222</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11149,7 +11149,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>13.53</v>
+        <v>13.57</v>
       </c>
       <c r="CA37" t="n">
         <v>0.37</v>
@@ -11190,13 +11190,13 @@
         <v>8</v>
       </c>
       <c r="CM37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38">
@@ -11209,82 +11209,82 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23.59000015258789</v>
+        <v>23.5</v>
       </c>
       <c r="D38" t="n">
-        <v>23.59000015258789</v>
+        <v>23.5</v>
       </c>
       <c r="E38" t="n">
         <v>24.04000091552734</v>
       </c>
       <c r="F38" t="n">
-        <v>23.53000068664551</v>
+        <v>23.3700008392334</v>
       </c>
       <c r="G38" t="n">
         <v>23.80999946594238</v>
       </c>
       <c r="H38" t="n">
-        <v>7061500</v>
+        <v>10533000</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.006318433865899253</v>
+        <v>-0.01010951025408791</v>
       </c>
       <c r="J38" t="n">
-        <v>23.59777789645725</v>
+        <v>23.58777787950304</v>
       </c>
       <c r="K38" t="n">
         <v>-1</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.03295964519831213</v>
+        <v>-0.3721328899714312</v>
       </c>
       <c r="M38" t="n">
-        <v>23.57200012207031</v>
+        <v>23.56300010681152</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.07636191423876411</v>
+        <v>-0.2673687837963814</v>
       </c>
       <c r="P38" t="n">
-        <v>23.19153851729173</v>
+        <v>23.18807697296143</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.718133684831072</v>
+        <v>1.345187129585147</v>
       </c>
       <c r="S38" t="n">
-        <v>21.45060009002686</v>
+        <v>21.4488000869751</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>9.973614041481836</v>
+        <v>9.563238524799832</v>
       </c>
       <c r="V38" t="n">
-        <v>20.65466668446859</v>
+        <v>20.65406668345133</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>14.21147827249397</v>
+        <v>13.77904584199351</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.70695003509521</v>
+        <v>19.70650003433228</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>19.70396286882307</v>
+        <v>19.24999344916024</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.2549780755147054</v>
+        <v>0.2564230585106856</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11434,13 +11434,13 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>28.42</v>
+        <v>28.31</v>
       </c>
       <c r="CA38" t="n">
         <v>0.18</v>
       </c>
       <c r="CB38" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="CC38" t="n">
         <v>1</v>
@@ -11471,13 +11471,13 @@
         <v>10</v>
       </c>
       <c r="CM38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN38" t="n">
         <v>0</v>
       </c>
       <c r="CO38" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
@@ -11490,82 +11490,82 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.27999973297119</v>
+        <v>10.22000026702881</v>
       </c>
       <c r="D39" t="n">
-        <v>10.27999973297119</v>
+        <v>10.22000026702881</v>
       </c>
       <c r="E39" t="n">
         <v>10.4399995803833</v>
       </c>
       <c r="F39" t="n">
-        <v>10.22000026702881</v>
+        <v>10.21000003814697</v>
       </c>
       <c r="G39" t="n">
         <v>10.30000019073486</v>
       </c>
       <c r="H39" t="n">
-        <v>5332600</v>
+        <v>8381700</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.003875965410453319</v>
+        <v>-0.009689867320980872</v>
       </c>
       <c r="J39" t="n">
-        <v>10.25555547078451</v>
+        <v>10.24888886345757</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2383514209086104</v>
+        <v>-0.2818705209280465</v>
       </c>
       <c r="M39" t="n">
-        <v>10.24599990844727</v>
+        <v>10.23999996185303</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3318351047016421</v>
+        <v>-0.195309520495339</v>
       </c>
       <c r="P39" t="n">
-        <v>10.10346155900222</v>
+        <v>10.1011538872352</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.747303861533268</v>
+        <v>1.176562411783405</v>
       </c>
       <c r="S39" t="n">
-        <v>9.44399998664856</v>
+        <v>9.442799997329711</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>8.852178605511698</v>
+        <v>8.230612423421849</v>
       </c>
       <c r="V39" t="n">
-        <v>9.09047703742981</v>
+        <v>9.090077040990193</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>13.08537154478859</v>
+        <v>12.43029317511187</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.611227512359619</v>
+        <v>8.610927515029907</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>19.37902834661374</v>
+        <v>18.68640456199814</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.2570934611462297</v>
+        <v>0.2589222474586371</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11721,10 +11721,10 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.91</v>
+        <v>23.77</v>
       </c>
       <c r="CA39" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="CB39" t="n">
         <v>0.72</v>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.67000007629395</v>
+        <v>12.47999954223633</v>
       </c>
       <c r="D40" t="n">
-        <v>12.67000007629395</v>
+        <v>12.47999954223633</v>
       </c>
       <c r="E40" t="n">
         <v>12.78999996185303</v>
@@ -11796,88 +11796,90 @@
         <v>12.5</v>
       </c>
       <c r="H40" t="n">
-        <v>3733900</v>
+        <v>6368600</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02177423113466781</v>
+        <v>0.006451606948963517</v>
       </c>
       <c r="J40" t="n">
-        <v>12.58555560641819</v>
+        <v>12.56444443596734</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.670963384665318</v>
+        <v>-0.6720941316694921</v>
       </c>
       <c r="M40" t="n">
-        <v>12.57200002670288</v>
+        <v>12.55299997329712</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7795104150724842</v>
+        <v>-0.5815377297544678</v>
       </c>
       <c r="P40" t="n">
-        <v>12.45423078536987</v>
+        <v>12.4469230725215</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.732497932971813</v>
+        <v>0.2657401312927377</v>
       </c>
       <c r="S40" t="n">
-        <v>11.63439998626709</v>
+        <v>11.63059997558594</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>8.901190360046487</v>
+        <v>7.303144880172862</v>
       </c>
       <c r="V40" t="n">
-        <v>15.08813334147135</v>
+        <v>15.0868666712443</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-16.02672252723874</v>
+        <v>-17.27904929375883</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.72419998168945</v>
+        <v>20.72324997901917</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-38.86374341355358</v>
+        <v>-39.77778796824122</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6908385029892367</v>
+        <v>0.6880514360676916</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
         <v>7</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AF40" t="n">
         <v>11.6</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AG40" t="n">
         <v>12.6</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
         <v>13.3</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AI40" t="n">
         <v>14</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>14.8</v>
       </c>
       <c r="AJ40" t="n">
         <v>1</v>
@@ -12004,10 +12006,10 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-14.91</v>
+        <v>-14.68</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="CB40" t="n">
         <v>0.13</v>
@@ -12045,13 +12047,13 @@
         <v>10</v>
       </c>
       <c r="CM40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CN40" t="n">
         <v>-1</v>
       </c>
       <c r="CO40" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41">
@@ -12064,10 +12066,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22.59000015258789</v>
+        <v>22.40999984741211</v>
       </c>
       <c r="D41" t="n">
-        <v>22.59000015258789</v>
+        <v>22.40999984741211</v>
       </c>
       <c r="E41" t="n">
         <v>22.71999931335449</v>
@@ -12079,88 +12081,88 @@
         <v>22.51000022888184</v>
       </c>
       <c r="H41" t="n">
-        <v>679900</v>
+        <v>1006000</v>
       </c>
       <c r="I41" t="n">
-        <v>0.005340491450842144</v>
+        <v>-0.002670203283305139</v>
       </c>
       <c r="J41" t="n">
-        <v>22.57666651407878</v>
+        <v>22.55666648017036</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.05905937663914449</v>
+        <v>-0.6502141302092774</v>
       </c>
       <c r="M41" t="n">
-        <v>22.62199993133545</v>
+        <v>22.60399990081787</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.1414542429700593</v>
+        <v>-0.8582554161077616</v>
       </c>
       <c r="P41" t="n">
-        <v>22.81192310039814</v>
+        <v>22.80500001173753</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.9728375237525342</v>
+        <v>-1.732077018733249</v>
       </c>
       <c r="S41" t="n">
-        <v>22.90159999847412</v>
+        <v>22.8979999923706</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-1.360602953099314</v>
+        <v>-2.131191130758545</v>
       </c>
       <c r="V41" t="n">
-        <v>23.6684667078654</v>
+        <v>23.66726670583089</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-4.556554375020486</v>
+        <v>-5.312260490599993</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.5031999874115</v>
+        <v>23.50229998588562</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-3.885427666499563</v>
+        <v>-4.647630823917217</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.297542770098788</v>
+        <v>0.2969039390115799</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE41" t="n">
         <v>22.3</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AF41" t="n">
         <v>22.4</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AG41" t="n">
         <v>22.5</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>22.6</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>22.9</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>23</v>
       </c>
       <c r="AJ41" t="n">
         <v>2</v>
@@ -12287,13 +12289,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>9.449999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="CA41" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="CC41" t="n">
         <v>4</v>
@@ -12308,7 +12310,7 @@
         <v>7</v>
       </c>
       <c r="CG41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CH41" t="n">
         <v>6</v>
@@ -12324,13 +12326,13 @@
         <v>8</v>
       </c>
       <c r="CM41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN41" t="n">
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
@@ -12343,10 +12345,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>26.23999977111816</v>
+        <v>26.19000053405762</v>
       </c>
       <c r="D42" t="n">
-        <v>26.23999977111816</v>
+        <v>26.19000053405762</v>
       </c>
       <c r="E42" t="n">
         <v>26.55999946594238</v>
@@ -12358,67 +12360,67 @@
         <v>26.13999938964844</v>
       </c>
       <c r="H42" t="n">
-        <v>944200</v>
+        <v>1767600</v>
       </c>
       <c r="I42" t="n">
-        <v>0.003825569388089756</v>
+        <v>0.001912821177378454</v>
       </c>
       <c r="J42" t="n">
-        <v>26.2811107635498</v>
+        <v>26.2755552927653</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.1564279105305507</v>
+        <v>-0.3256059015857986</v>
       </c>
       <c r="M42" t="n">
-        <v>26.29299964904785</v>
+        <v>26.2879997253418</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.2015741019933622</v>
+        <v>-0.3727905976418178</v>
       </c>
       <c r="P42" t="n">
-        <v>27.2161535849938</v>
+        <v>27.21423053741455</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-3.586670727835179</v>
+        <v>-3.763582446135326</v>
       </c>
       <c r="S42" t="n">
-        <v>27.67639984130859</v>
+        <v>27.67539985656738</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-5.189981639326231</v>
+        <v>-5.367219011136629</v>
       </c>
       <c r="V42" t="n">
-        <v>26.96499988555908</v>
+        <v>26.96466655731201</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-2.688670934611002</v>
+        <v>-2.872893019492309</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.02894989967346</v>
+        <v>26.02869990348816</v>
       </c>
       <c r="Z42" t="n">
         <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.8108274527331127</v>
+        <v>0.6197029861942533</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.2963959231765822</v>
+        <v>0.2960239653753747</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12570,7 +12572,7 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>10.93</v>
+        <v>10.91</v>
       </c>
       <c r="CA42" t="n">
         <v>0.04</v>
@@ -12635,13 +12637,13 @@
         <v>27.53000068664551</v>
       </c>
       <c r="F43" t="n">
-        <v>27.05999946594238</v>
+        <v>26.96999931335449</v>
       </c>
       <c r="G43" t="n">
         <v>27.3799991607666</v>
       </c>
       <c r="H43" t="n">
-        <v>908900</v>
+        <v>1825200</v>
       </c>
       <c r="I43" t="n">
         <v>-0.01059163685418429</v>
@@ -12887,7 +12889,7 @@
         <v>0</v>
       </c>
       <c r="CL43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM43" t="n">
         <v>2</v>
@@ -12896,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -12909,10 +12911,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13.03999996185303</v>
+        <v>12.97000026702881</v>
       </c>
       <c r="D44" t="n">
-        <v>13.03999996185303</v>
+        <v>12.97000026702881</v>
       </c>
       <c r="E44" t="n">
         <v>13.10000038146973</v>
@@ -12924,67 +12926,67 @@
         <v>13.06999969482422</v>
       </c>
       <c r="H44" t="n">
-        <v>17422000</v>
+        <v>25860600</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.002295312446187081</v>
+        <v>-0.007651065809512581</v>
       </c>
       <c r="J44" t="n">
-        <v>12.95222208234999</v>
+        <v>12.94444433848063</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6777051763392278</v>
+        <v>0.1974277758080833</v>
       </c>
       <c r="M44" t="n">
-        <v>12.95299987792969</v>
+        <v>12.94599990844727</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6716597293540976</v>
+        <v>0.1853882183784199</v>
       </c>
       <c r="P44" t="n">
-        <v>13.38307692454412</v>
+        <v>13.38038462858934</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.563513343197602</v>
+        <v>-3.067059527449427</v>
       </c>
       <c r="S44" t="n">
-        <v>13.69780000686645</v>
+        <v>13.69640001296997</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-4.802231341410187</v>
+        <v>-5.303581563427535</v>
       </c>
       <c r="V44" t="n">
-        <v>12.91464167912801</v>
+        <v>12.91417501449585</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.9706679119685894</v>
+        <v>0.4322788909883602</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.40622623920441</v>
+        <v>12.40587624073029</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>5.108513341840062</v>
+        <v>4.547232419153283</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2328406045197276</v>
+        <v>0.2329823289900352</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13136,13 +13138,13 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
       </c>
       <c r="CB44" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CC44" t="n">
         <v>2</v>
@@ -13170,16 +13172,16 @@
         <v>0</v>
       </c>
       <c r="CL44" t="n">
+        <v>6</v>
+      </c>
+      <c r="CM44" t="n">
         <v>7</v>
       </c>
-      <c r="CM44" t="n">
-        <v>6</v>
-      </c>
       <c r="CN44" t="n">
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
@@ -13192,10 +13194,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40.22000122070312</v>
+        <v>40</v>
       </c>
       <c r="D45" t="n">
-        <v>40.22000122070312</v>
+        <v>40</v>
       </c>
       <c r="E45" t="n">
         <v>40.45000076293945</v>
@@ -13207,67 +13209,67 @@
         <v>40.31999969482422</v>
       </c>
       <c r="H45" t="n">
-        <v>12330200</v>
+        <v>20146300</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.002480120904711502</v>
+        <v>-0.007936500427734305</v>
       </c>
       <c r="J45" t="n">
-        <v>39.83777745564779</v>
+        <v>39.81333287556966</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.9594505252730871</v>
+        <v>0.4688558102225077</v>
       </c>
       <c r="M45" t="n">
-        <v>39.82399978637695</v>
+        <v>39.80199966430664</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9943788581016365</v>
+        <v>0.4974632866773257</v>
       </c>
       <c r="P45" t="n">
-        <v>41.34192290672889</v>
+        <v>41.33346132131723</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.713762706579762</v>
+        <v>-3.226106110376761</v>
       </c>
       <c r="S45" t="n">
-        <v>42.62659980773926</v>
+        <v>42.62219978332519</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-5.645767192060191</v>
+        <v>-6.152192511544323</v>
       </c>
       <c r="V45" t="n">
-        <v>41.85572207132975</v>
+        <v>41.85425539652506</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-3.907998165314317</v>
+        <v>-4.430267314417475</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.57533514022827</v>
+        <v>40.57423513412476</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-0.8757387173688416</v>
+        <v>-1.415270385816338</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2342230921467793</v>
+        <v>0.2342993814961832</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13439,13 +13441,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.550000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CC45" t="n">
         <v>10</v>
@@ -13476,13 +13478,13 @@
         <v>5</v>
       </c>
       <c r="CM45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN45" t="n">
         <v>0</v>
       </c>
       <c r="CO45" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -13495,10 +13497,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.71999931335449</v>
+        <v>16.67000007629395</v>
       </c>
       <c r="D46" t="n">
-        <v>16.71999931335449</v>
+        <v>16.67000007629395</v>
       </c>
       <c r="E46" t="n">
         <v>16.94000053405762</v>
@@ -13510,67 +13512,67 @@
         <v>16.82999992370605</v>
       </c>
       <c r="H46" t="n">
-        <v>2995900</v>
+        <v>4951500</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.003575767034310617</v>
+        <v>-0.006555459228264948</v>
       </c>
       <c r="J46" t="n">
-        <v>16.5055554707845</v>
+        <v>16.5</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.299222210058682</v>
+        <v>1.030303492690578</v>
       </c>
       <c r="M46" t="n">
-        <v>16.49799995422363</v>
+        <v>16.49300003051758</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.345613769831687</v>
+        <v>1.073182837863686</v>
       </c>
       <c r="P46" t="n">
-        <v>17.07807702284593</v>
+        <v>17.07615397526668</v>
       </c>
       <c r="Q46" t="n">
         <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>-2.096709770148145</v>
+        <v>-2.378485808695629</v>
       </c>
       <c r="S46" t="n">
-        <v>18.03500003814697</v>
+        <v>18.03400005340576</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-7.291381879739609</v>
+        <v>-7.563491034005085</v>
       </c>
       <c r="V46" t="n">
-        <v>18.50368830362956</v>
+        <v>18.50335497538249</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.639640276069649</v>
+        <v>-9.908229623912531</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.37524129867554</v>
+        <v>18.37499130249023</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-9.008001355826288</v>
+        <v>-9.278868208036771</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.1768228070376764</v>
+        <v>0.1768098196360958</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13726,13 +13728,13 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>27.87</v>
+        <v>27.78</v>
       </c>
       <c r="CA46" t="n">
         <v>0.24</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CC46" t="n">
         <v>4</v>
@@ -13786,10 +13788,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.14999961853027</v>
+        <v>15</v>
       </c>
       <c r="D47" t="n">
-        <v>15.14999961853027</v>
+        <v>15</v>
       </c>
       <c r="E47" t="n">
         <v>15.22000026702881</v>
@@ -13801,88 +13803,88 @@
         <v>15</v>
       </c>
       <c r="H47" t="n">
-        <v>3815300</v>
+        <v>6368300</v>
       </c>
       <c r="I47" t="n">
-        <v>0.01882984096342266</v>
+        <v>0.008742442195118327</v>
       </c>
       <c r="J47" t="n">
-        <v>14.72222222222222</v>
+        <v>14.70555559794108</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>2.905657786243372</v>
+        <v>2.002266423039092</v>
       </c>
       <c r="M47" t="n">
-        <v>14.60500001907349</v>
+        <v>14.59000005722046</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>3.731596020164613</v>
+        <v>2.810143530990841</v>
       </c>
       <c r="P47" t="n">
-        <v>14.23500006015484</v>
+        <v>14.22923084405752</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>6.427815627037504</v>
+        <v>5.416801262060967</v>
       </c>
       <c r="S47" t="n">
-        <v>14.70820003509522</v>
+        <v>14.70520004272461</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>3.003763767020307</v>
+        <v>2.004732723246719</v>
       </c>
       <c r="V47" t="n">
-        <v>14.68153336207072</v>
+        <v>14.68053336461385</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>3.190853740589667</v>
+        <v>2.17612417377284</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.92805001735687</v>
+        <v>14.92730001926422</v>
       </c>
       <c r="Z47" t="n">
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.486795669329484</v>
+        <v>0.4870269951160419</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4724164629054139</v>
+        <v>0.4696895287284134</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AF47" t="n">
         <v>14.9</v>
       </c>
-      <c r="AE47" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF47" t="n">
+      <c r="AG47" t="n">
         <v>15.1</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>15.2</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>15.3</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>15.4</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14009,13 +14011,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>10.24</v>
+        <v>10.14</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14065,82 +14067,82 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.02000045776367</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="D48" t="n">
-        <v>16.02000045776367</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="E48" t="n">
         <v>16.46999931335449</v>
       </c>
       <c r="F48" t="n">
-        <v>16.01000022888184</v>
+        <v>15.97000026702881</v>
       </c>
       <c r="G48" t="n">
         <v>16.25</v>
       </c>
       <c r="H48" t="n">
-        <v>2523600</v>
+        <v>6336300</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.01657461280473671</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>16.64333343505859</v>
+        <v>16.67333348592122</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-3.745241178560378</v>
+        <v>-2.299075771006204</v>
       </c>
       <c r="M48" t="n">
-        <v>16.72100009918213</v>
+        <v>16.7480001449585</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-4.192330825072739</v>
+        <v>-2.734650259535732</v>
       </c>
       <c r="P48" t="n">
-        <v>17.27461550785945</v>
+        <v>17.28500014085036</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-7.262766858833794</v>
+        <v>-5.756431687677537</v>
       </c>
       <c r="S48" t="n">
-        <v>18.47040012359619</v>
+        <v>18.47580013275147</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-13.26663011865185</v>
+        <v>-11.83060653134813</v>
       </c>
       <c r="V48" t="n">
-        <v>18.87313340504964</v>
+        <v>18.8749334081014</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-15.11743114433025</v>
+        <v>-13.69505489997948</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.542000041008</v>
+        <v>19.54335004329682</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-18.02271812431464</v>
+        <v>-16.64683445039833</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.4805501578311729</v>
+        <v>0.4809417467636123</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14288,13 +14290,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>59.33</v>
+        <v>60.33</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14326,16 +14328,16 @@
         <v>0</v>
       </c>
       <c r="CL48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN48" t="n">
         <v>0</v>
       </c>
       <c r="CO48" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49">
@@ -14348,103 +14350,105 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.519999980926514</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="D49" t="n">
-        <v>6.519999980926514</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="E49" t="n">
         <v>6.710000038146973</v>
       </c>
       <c r="F49" t="n">
-        <v>6.489999771118164</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="G49" t="n">
         <v>6.650000095367432</v>
       </c>
       <c r="H49" t="n">
-        <v>11332600</v>
+        <v>17456400</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.01212120073667011</v>
+        <v>-0.03787878842612158</v>
       </c>
       <c r="J49" t="n">
-        <v>6.641111108991835</v>
+        <v>6.622222211625841</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.82365760906094</v>
+        <v>-4.110739541711009</v>
       </c>
       <c r="M49" t="n">
-        <v>6.655999994277954</v>
+        <v>6.638999986648559</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-2.043269433118343</v>
+        <v>-4.353066464786687</v>
       </c>
       <c r="P49" t="n">
-        <v>7.43653836617103</v>
+        <v>7.429999901698186</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-12.3247987183643</v>
+        <v>-14.53566637085385</v>
       </c>
       <c r="S49" t="n">
-        <v>8.124999961853028</v>
+        <v>8.121599960327149</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-19.75384601184011</v>
+        <v>-21.81343656851597</v>
       </c>
       <c r="V49" t="n">
-        <v>8.839980742136637</v>
+        <v>8.838847408294678</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-26.24418343075915</v>
+        <v>-28.15805487632346</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.721937818527222</v>
+        <v>8.721087818145753</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-25.24597037281476</v>
+        <v>-27.18798345981244</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4309502561948493</v>
+        <v>0.437827437763735</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AE49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF49" t="n">
         <v>6.3</v>
       </c>
-      <c r="AE49" t="n">
+      <c r="AG49" t="n">
         <v>6.4</v>
       </c>
-      <c r="AF49" t="n">
+      <c r="AH49" t="n">
         <v>6.5</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AI49" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>6.8</v>
       </c>
       <c r="AJ49" t="n">
         <v>1</v>
@@ -14571,13 +14575,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>36.22</v>
+        <v>35.28</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="CC49" t="n">
         <v>2</v>
@@ -14612,13 +14616,13 @@
         <v>1</v>
       </c>
       <c r="CM49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN49" t="n">
         <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -14631,82 +14635,82 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.27000045776367</v>
+        <v>14.13000011444092</v>
       </c>
       <c r="D50" t="n">
-        <v>14.27000045776367</v>
+        <v>14.13000011444092</v>
       </c>
       <c r="E50" t="n">
         <v>14.56999969482422</v>
       </c>
       <c r="F50" t="n">
-        <v>14.26000022888184</v>
+        <v>14.13000011444092</v>
       </c>
       <c r="G50" t="n">
         <v>14.48999977111816</v>
       </c>
       <c r="H50" t="n">
-        <v>4264400</v>
+        <v>9344200</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.004186982991055466</v>
+        <v>-0.01395672088834266</v>
       </c>
       <c r="J50" t="n">
-        <v>14.6633333630032</v>
+        <v>14.64777776930067</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.682424899593022</v>
+        <v>-3.534854658601738</v>
       </c>
       <c r="M50" t="n">
-        <v>14.66800003051758</v>
+        <v>14.6539999961853</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-2.7133867734241</v>
+        <v>-3.575814670948482</v>
       </c>
       <c r="P50" t="n">
-        <v>15.33884609662569</v>
+        <v>15.33346146803636</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.968227154304336</v>
+        <v>-7.848595414050095</v>
       </c>
       <c r="S50" t="n">
-        <v>15.72040004730225</v>
+        <v>15.71760004043579</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-9.226225701473002</v>
+        <v>-10.10077824801842</v>
       </c>
       <c r="V50" t="n">
-        <v>15.84326669692993</v>
+        <v>15.84233336130778</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.930188447002056</v>
+        <v>-10.80859244540925</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.43495001316071</v>
+        <v>15.43425001144409</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-7.547478640382585</v>
+        <v>-8.450361345942351</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.2996307971375527</v>
+        <v>0.300266581684417</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14854,13 +14858,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.6</v>
+        <v>8.51</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CB50" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CC50" t="n">
         <v>5</v>
@@ -14892,7 +14896,7 @@
         <v>0</v>
       </c>
       <c r="CL50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM50" t="n">
         <v>2</v>
@@ -14901,7 +14905,7 @@
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -14914,10 +14918,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6.010000228881836</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="D51" t="n">
-        <v>6.010000228881836</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="E51" t="n">
         <v>6.070000171661377</v>
@@ -14929,67 +14933,67 @@
         <v>5.980000019073486</v>
       </c>
       <c r="H51" t="n">
-        <v>5041900</v>
+        <v>6832900</v>
       </c>
       <c r="I51" t="n">
-        <v>0.006700241222102443</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>6.150000042385525</v>
+        <v>6.145555549197727</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.276419716078316</v>
+        <v>-2.856629601680107</v>
       </c>
       <c r="M51" t="n">
-        <v>6.157000017166138</v>
+        <v>6.152999973297119</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.387522947449349</v>
+        <v>-2.974161935635549</v>
       </c>
       <c r="P51" t="n">
-        <v>6.570000024942251</v>
+        <v>6.568461546531091</v>
       </c>
       <c r="Q51" t="n">
         <v>-1</v>
       </c>
       <c r="R51" t="n">
-        <v>-8.523588948773824</v>
+        <v>-9.111140441333596</v>
       </c>
       <c r="S51" t="n">
-        <v>7.135400009155274</v>
+        <v>7.13460000038147</v>
       </c>
       <c r="T51" t="n">
         <v>-1</v>
       </c>
       <c r="U51" t="n">
-        <v>-15.77206293731903</v>
+        <v>-16.32327264496329</v>
       </c>
       <c r="V51" t="n">
-        <v>7.953666693369548</v>
+        <v>7.95340002377828</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-24.43736378981055</v>
+        <v>-24.9377653287507</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.785700008869171</v>
+        <v>7.78550000667572</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-22.80719495953513</v>
+        <v>-23.31899319154016</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4435863687856374</v>
+        <v>0.4419819391446058</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15141,13 +15145,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>-4.45</v>
+        <v>-4.42</v>
       </c>
       <c r="CA51" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CB51" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="CC51" t="n">
         <v>7</v>
@@ -15182,13 +15186,13 @@
         <v>1</v>
       </c>
       <c r="CM51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -15201,10 +15205,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30.07999992370605</v>
+        <v>29.92000007629395</v>
       </c>
       <c r="D52" t="n">
-        <v>30.07999992370605</v>
+        <v>29.92000007629395</v>
       </c>
       <c r="E52" t="n">
         <v>30.29999923706055</v>
@@ -15216,67 +15220,67 @@
         <v>29.86000061035156</v>
       </c>
       <c r="H52" t="n">
-        <v>1485700</v>
+        <v>2342600</v>
       </c>
       <c r="I52" t="n">
-        <v>0.01007384923248433</v>
+        <v>0.004701121102096417</v>
       </c>
       <c r="J52" t="n">
-        <v>29.88444455464681</v>
+        <v>29.86666679382324</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.6543717709112936</v>
+        <v>0.1785712575121809</v>
       </c>
       <c r="M52" t="n">
-        <v>29.84300003051758</v>
+        <v>29.82700004577637</v>
       </c>
       <c r="N52" t="n">
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.7941557247800759</v>
+        <v>0.3117981371738683</v>
       </c>
       <c r="P52" t="n">
-        <v>30.95269210521991</v>
+        <v>30.94653826493483</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.819438705193228</v>
+        <v>-3.317134148745958</v>
       </c>
       <c r="S52" t="n">
-        <v>31.60059997558594</v>
+        <v>31.5973999786377</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-4.81193411851253</v>
+        <v>-5.30866433148868</v>
       </c>
       <c r="V52" t="n">
-        <v>30.60800003051758</v>
+        <v>30.60693336486817</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-1.725039552682572</v>
+        <v>-2.244371497089314</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.87300004959106</v>
+        <v>29.872200050354</v>
       </c>
       <c r="Z52" t="n">
         <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.6929329955858428</v>
+        <v>0.1600150837881651</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.2975333908875565</v>
+        <v>0.2956929192910936</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15428,13 +15432,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>12.64</v>
+        <v>12.57</v>
       </c>
       <c r="CA52" t="n">
         <v>0.29</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15488,10 +15492,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10.23999977111816</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="D53" t="n">
-        <v>10.23999977111816</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="E53" t="n">
         <v>10.32999992370605</v>
@@ -15503,67 +15507,67 @@
         <v>10.02000045776367</v>
       </c>
       <c r="H53" t="n">
-        <v>7993600</v>
+        <v>11601200</v>
       </c>
       <c r="I53" t="n">
-        <v>0.02708119326558633</v>
+        <v>0.01303912848135358</v>
       </c>
       <c r="J53" t="n">
-        <v>10.10333326127794</v>
+        <v>10.08777777353922</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1.352687338979619</v>
+        <v>0.1211625414921653</v>
       </c>
       <c r="M53" t="n">
-        <v>10.08699989318848</v>
+        <v>10.07299995422363</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>1.516802612767002</v>
+        <v>0.2680475267427397</v>
       </c>
       <c r="P53" t="n">
-        <v>10.16999992957482</v>
+        <v>10.16461533766526</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R53" t="n">
-        <v>0.6882973650745245</v>
+        <v>-0.6356852084318929</v>
       </c>
       <c r="S53" t="n">
-        <v>10.072799949646</v>
+        <v>10.06999996185303</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>1.65991404880472</v>
+        <v>0.2979187659418754</v>
       </c>
       <c r="V53" t="n">
-        <v>8.925199950536092</v>
+        <v>8.924266621271769</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>14.73132061879576</v>
+        <v>13.17457008058783</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.909799954891206</v>
+        <v>8.909099957942963</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>14.92962606300403</v>
+        <v>13.36723607489675</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3442832587239385</v>
+        <v>0.3369098074460121</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15715,13 +15719,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>-6.06</v>
+        <v>-5.98</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="CC53" t="n">
         <v>3</v>
@@ -15756,13 +15760,13 @@
         <v>9</v>
       </c>
       <c r="CM53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54">
@@ -15775,82 +15779,82 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47.59000015258789</v>
+        <v>47.54000091552734</v>
       </c>
       <c r="D54" t="n">
-        <v>47.59000015258789</v>
+        <v>47.54000091552734</v>
       </c>
       <c r="E54" t="n">
         <v>48.58000183105469</v>
       </c>
       <c r="F54" t="n">
-        <v>47.54000091552734</v>
+        <v>47.43000030517578</v>
       </c>
       <c r="G54" t="n">
         <v>48.38000106811523</v>
       </c>
       <c r="H54" t="n">
-        <v>3705200</v>
+        <v>5785100</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.01060287604390664</v>
+        <v>-0.01164236125485618</v>
       </c>
       <c r="J54" t="n">
-        <v>49.6511107550727</v>
+        <v>49.64555528428819</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-4.151187297001674</v>
+        <v>-4.241173971574479</v>
       </c>
       <c r="M54" t="n">
-        <v>49.73099975585937</v>
+        <v>49.72599983215332</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-4.305160993710419</v>
+        <v>-4.396088412509884</v>
       </c>
       <c r="P54" t="n">
-        <v>51.10846167344313</v>
+        <v>51.10653862586388</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-6.884303314266052</v>
+        <v>-6.97863288383924</v>
       </c>
       <c r="S54" t="n">
-        <v>51.79120010375976</v>
+        <v>51.79020011901856</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-8.111802666775601</v>
+        <v>-8.206570342890879</v>
       </c>
       <c r="V54" t="n">
-        <v>41.50846675872803</v>
+        <v>41.50813343048096</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>14.65130819986526</v>
+        <v>14.53177241792559</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.46810006141663</v>
+        <v>39.46785006523132</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>20.57839135537994</v>
+        <v>20.45247166226334</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3452993455497884</v>
+        <v>0.3455099940920633</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16002,7 +16006,7 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.7</v>
+        <v>5.69</v>
       </c>
       <c r="CA54" t="n">
         <v>0.53</v>
@@ -16058,10 +16062,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>42.43999862670898</v>
+        <v>42.5099983215332</v>
       </c>
       <c r="D55" t="n">
-        <v>42.43999862670898</v>
+        <v>42.5099983215332</v>
       </c>
       <c r="E55" t="n">
         <v>43.18000030517578</v>
@@ -16073,67 +16077,67 @@
         <v>43.09999847412109</v>
       </c>
       <c r="H55" t="n">
-        <v>28946300</v>
+        <v>37455200</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.00887438278429431</v>
+        <v>-0.007239639782820606</v>
       </c>
       <c r="J55" t="n">
-        <v>44.29555511474609</v>
+        <v>44.30333285861545</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.189035408248875</v>
+        <v>-4.047854690312547</v>
       </c>
       <c r="M55" t="n">
-        <v>44.4129997253418</v>
+        <v>44.41999969482422</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-4.442395494189128</v>
+        <v>-4.299868046855409</v>
       </c>
       <c r="P55" t="n">
-        <v>46.09615369943472</v>
+        <v>46.0988459953895</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-7.931583829239475</v>
+        <v>-7.785113914164415</v>
       </c>
       <c r="S55" t="n">
-        <v>46.87559982299805</v>
+        <v>46.87699981689453</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-9.462494801213987</v>
+        <v>-9.315872415937882</v>
       </c>
       <c r="V55" t="n">
-        <v>38.35266675313314</v>
+        <v>38.3531334177653</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>10.65722991281159</v>
+        <v>10.8383971095369</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.49085004806518</v>
+        <v>36.4912000465393</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.30312412785034</v>
+        <v>16.49383486242651</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.307181262088923</v>
+        <v>0.3069844776918418</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16285,7 +16289,7 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="CA55" t="n">
         <v>0.59</v>
@@ -16323,16 +16327,16 @@
         <v>0</v>
       </c>
       <c r="CL55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN55" t="n">
         <v>0</v>
       </c>
       <c r="CO55" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -16345,10 +16349,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.260000228881836</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="D56" t="n">
-        <v>6.260000228881836</v>
+        <v>6.179999828338623</v>
       </c>
       <c r="E56" t="n">
         <v>6.300000190734863</v>
@@ -16360,67 +16364,67 @@
         <v>6.21999979019165</v>
       </c>
       <c r="H56" t="n">
-        <v>3874100</v>
+        <v>5998900</v>
       </c>
       <c r="I56" t="n">
-        <v>0.006430938913094986</v>
+        <v>-0.006430862251169733</v>
       </c>
       <c r="J56" t="n">
-        <v>6.059999942779541</v>
+        <v>6.051111009385851</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>3.3003347853261</v>
+        <v>2.130002552470998</v>
       </c>
       <c r="M56" t="n">
-        <v>6.058999967575073</v>
+        <v>6.050999927520752</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>3.317383435920476</v>
+        <v>2.131877414692447</v>
       </c>
       <c r="P56" t="n">
-        <v>6.268846163382897</v>
+        <v>6.265769224900466</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-0.1411094525294241</v>
+        <v>-1.368856615736679</v>
       </c>
       <c r="S56" t="n">
-        <v>6.307800006866455</v>
+        <v>6.306199998855591</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.757788419616762</v>
+        <v>-2.001207867493412</v>
       </c>
       <c r="V56" t="n">
-        <v>6.363121080398559</v>
+        <v>6.362587744394938</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-1.620601748949658</v>
+        <v>-2.869711560632923</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.838840699195861</v>
+        <v>6.838440697193146</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-8.464014527814458</v>
+        <v>-9.628523489642628</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3197188400441768</v>
+        <v>0.318510396282177</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16572,13 +16576,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>6.26</v>
+        <v>6.18</v>
       </c>
       <c r="CA56" t="n">
         <v>0.2</v>
       </c>
       <c r="CB56" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CC56" t="n">
         <v>9</v>
@@ -16613,13 +16617,13 @@
         <v>8</v>
       </c>
       <c r="CM56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
@@ -16632,10 +16636,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.56000137329102</v>
+        <v>62.97000122070312</v>
       </c>
       <c r="D57" t="n">
-        <v>62.56000137329102</v>
+        <v>62.97000122070312</v>
       </c>
       <c r="E57" t="n">
         <v>63.95999908447266</v>
@@ -16647,67 +16651,67 @@
         <v>63.79999923706055</v>
       </c>
       <c r="H57" t="n">
-        <v>4777900</v>
+        <v>6686300</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.006668754715751457</v>
+        <v>-0.0001587539156220341</v>
       </c>
       <c r="J57" t="n">
-        <v>66.41888851589627</v>
+        <v>66.46444405449762</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-5.809924298389446</v>
+        <v>-5.257612372307245</v>
       </c>
       <c r="M57" t="n">
-        <v>66.65699996948243</v>
+        <v>66.69799995422363</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-6.146389123523622</v>
+        <v>-5.589371099701818</v>
       </c>
       <c r="P57" t="n">
-        <v>65.80884640033429</v>
+        <v>65.82461562523476</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.936790727616782</v>
+        <v>-4.336697415422925</v>
       </c>
       <c r="S57" t="n">
-        <v>65.98099990844726</v>
+        <v>65.98919990539551</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-5.184823721833697</v>
+        <v>-4.575292152383748</v>
       </c>
       <c r="V57" t="n">
-        <v>51.68819989522298</v>
+        <v>51.69093322753906</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>21.03343026088399</v>
+        <v>21.82020576706281</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.22509996414185</v>
+        <v>48.22714996337891</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>29.72498018626814</v>
+        <v>30.56960916935615</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3907938931024932</v>
+        <v>0.3904316314652815</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16859,13 +16863,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>21.06</v>
+        <v>21.2</v>
       </c>
       <c r="CA57" t="n">
         <v>0.44</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CC57" t="n">
         <v>10</v>
@@ -16893,7 +16897,7 @@
         <v>0</v>
       </c>
       <c r="CL57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM57" t="n">
         <v>1</v>
@@ -16902,7 +16906,7 @@
         <v>0</v>
       </c>
       <c r="CO57" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
@@ -16915,10 +16919,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.54999923706055</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="D58" t="n">
-        <v>48.54999923706055</v>
+        <v>48.27999877929688</v>
       </c>
       <c r="E58" t="n">
         <v>48.88999938964844</v>
@@ -16930,67 +16934,67 @@
         <v>48.59000015258789</v>
       </c>
       <c r="H58" t="n">
-        <v>498000</v>
+        <v>775600</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0002059810742609525</v>
+        <v>-0.005356450995601336</v>
       </c>
       <c r="J58" t="n">
-        <v>48.82333331637912</v>
+        <v>48.79333326551649</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.5598431339117025</v>
+        <v>-1.052058656100067</v>
       </c>
       <c r="M58" t="n">
-        <v>48.73299980163574</v>
+        <v>48.70599975585937</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.3755167244374167</v>
+        <v>-0.8746375779120524</v>
       </c>
       <c r="P58" t="n">
-        <v>49.78807728107159</v>
+        <v>49.77769264808068</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.486695834871559</v>
+        <v>-3.008765149827718</v>
       </c>
       <c r="S58" t="n">
-        <v>50.26720008850098</v>
+        <v>50.2618000793457</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.416145813606306</v>
+        <v>-3.942957269577019</v>
       </c>
       <c r="V58" t="n">
-        <v>49.24540003458659</v>
+        <v>49.24360003153483</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-1.412113206589121</v>
+        <v>-1.956805050038751</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.52590000152588</v>
+        <v>49.52454999923706</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-1.970485674031693</v>
+        <v>-2.512998543064717</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.2969743641285346</v>
+        <v>0.2969967837119589</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17142,13 +17146,13 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>8.52</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="CA58" t="n">
         <v>-0.42</v>
       </c>
       <c r="CB58" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CC58" t="n">
         <v>7</v>
@@ -17202,10 +17206,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>19.05999946594238</v>
+        <v>18.95000076293945</v>
       </c>
       <c r="D59" t="n">
-        <v>19.05999946594238</v>
+        <v>18.95000076293945</v>
       </c>
       <c r="E59" t="n">
         <v>19.43000030517578</v>
@@ -17217,67 +17221,67 @@
         <v>18.54999923706055</v>
       </c>
       <c r="H59" t="n">
-        <v>12750700</v>
+        <v>22727300</v>
       </c>
       <c r="I59" t="n">
-        <v>0.03027024140229106</v>
+        <v>0.02432436556429485</v>
       </c>
       <c r="J59" t="n">
-        <v>18.6300000084771</v>
+        <v>18.61777793036567</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>2.308102293449374</v>
+        <v>1.784438689817689</v>
       </c>
       <c r="M59" t="n">
-        <v>18.72600002288818</v>
+        <v>18.71500015258789</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1.783613385912439</v>
+        <v>1.255680515284777</v>
       </c>
       <c r="P59" t="n">
-        <v>20.38384613623986</v>
+        <v>20.37961541689359</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-6.494587240549507</v>
+        <v>-7.014924593567487</v>
       </c>
       <c r="S59" t="n">
-        <v>21.77400001525879</v>
+        <v>21.77180004119873</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-12.46440960510006</v>
+        <v>-12.9607991664428</v>
       </c>
       <c r="V59" t="n">
-        <v>22.86803779602051</v>
+        <v>22.86730447133382</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-16.65223034894931</v>
+        <v>-17.13058796809678</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.56975375175476</v>
+        <v>21.56920375823974</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-11.63552590677213</v>
+        <v>-12.14325305958371</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3623025691995039</v>
+        <v>0.357268068706676</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17429,13 +17433,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>25.76</v>
+        <v>25.61</v>
       </c>
       <c r="CA59" t="n">
         <v>0.09</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17467,7 +17471,7 @@
         <v>0</v>
       </c>
       <c r="CL59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM59" t="n">
         <v>9</v>
@@ -17476,7 +17480,7 @@
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60">
@@ -17504,7 +17508,7 @@
         <v>14.13000011444092</v>
       </c>
       <c r="H60" t="n">
-        <v>6041800</v>
+        <v>9655600</v>
       </c>
       <c r="I60" t="n">
         <v>-0.01423486167616028</v>
@@ -17754,7 +17758,7 @@
         <v>0</v>
       </c>
       <c r="CL60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM60" t="n">
         <v>1</v>
@@ -17763,7 +17767,7 @@
         <v>0</v>
       </c>
       <c r="CO60" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -17776,10 +17780,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34.54999923706055</v>
+        <v>34.47000122070312</v>
       </c>
       <c r="D61" t="n">
-        <v>34.54999923706055</v>
+        <v>34.47000122070312</v>
       </c>
       <c r="E61" t="n">
         <v>35.15000152587891</v>
@@ -17791,67 +17795,67 @@
         <v>34.58000183105469</v>
       </c>
       <c r="H61" t="n">
-        <v>6754800</v>
+        <v>8731900</v>
       </c>
       <c r="I61" t="n">
-        <v>0.004360398387447617</v>
+        <v>0.002034874759280436</v>
       </c>
       <c r="J61" t="n">
-        <v>34.5533332824707</v>
+        <v>34.54444461398654</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.00964898345088938</v>
+        <v>-0.2155003333105432</v>
       </c>
       <c r="M61" t="n">
-        <v>34.58199996948242</v>
+        <v>34.57400016784668</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.09253580605551306</v>
+        <v>-0.3008010257380324</v>
       </c>
       <c r="P61" t="n">
-        <v>36.48115392831656</v>
+        <v>36.47807708153358</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-5.293568002400975</v>
+        <v>-5.504884087892361</v>
       </c>
       <c r="S61" t="n">
-        <v>37.83639984130859</v>
+        <v>37.83479988098144</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-8.685817408716712</v>
+        <v>-8.893396214234276</v>
       </c>
       <c r="V61" t="n">
-        <v>41.11273325602213</v>
+        <v>41.11219993591308</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-15.96277722060789</v>
+        <v>-16.15627167985176</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.71749996185303</v>
+        <v>40.71709997177124</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-15.14705158855682</v>
+        <v>-15.34269079919534</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.4024717959552113</v>
+        <v>0.4019829740118173</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -17999,13 +18003,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>17.1</v>
+        <v>17.06</v>
       </c>
       <c r="CA61" t="n">
         <v>0.09</v>
       </c>
       <c r="CB61" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18059,10 +18063,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11.60999965667725</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="D62" t="n">
-        <v>11.60999965667725</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="E62" t="n">
         <v>12.01000022888184</v>
@@ -18074,67 +18078,67 @@
         <v>11.93000030517578</v>
       </c>
       <c r="H62" t="n">
-        <v>1406300</v>
+        <v>1990600</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.01693486501552077</v>
+        <v>-0.01947506246728048</v>
       </c>
       <c r="J62" t="n">
-        <v>12.07888889312744</v>
+        <v>12.07555558946398</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-3.881890466903628</v>
+        <v>-4.103791846979677</v>
       </c>
       <c r="M62" t="n">
-        <v>12.08699998855591</v>
+        <v>12.08400001525879</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-3.946391431540419</v>
+        <v>-4.170805121783518</v>
       </c>
       <c r="P62" t="n">
-        <v>12.48730773192186</v>
+        <v>12.48615389603835</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-7.025598264083046</v>
+        <v>-7.257270572484312</v>
       </c>
       <c r="S62" t="n">
-        <v>13.0118000793457</v>
+        <v>13.01120008468628</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-10.77330126593019</v>
+        <v>-10.99975522369145</v>
       </c>
       <c r="V62" t="n">
-        <v>11.95466667175293</v>
+        <v>11.95446667353312</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.883116899361821</v>
+        <v>-3.132442124382896</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.15750000476837</v>
+        <v>12.15735000610352</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-4.503395828717964</v>
+        <v>-4.748979688070227</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3505023527482612</v>
+        <v>0.351318234325385</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18286,7 +18290,7 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6.38</v>
+        <v>6.36</v>
       </c>
       <c r="CA62" t="n">
         <v>0.45</v>
@@ -18342,10 +18346,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>43.09999847412109</v>
+        <v>42.81999969482422</v>
       </c>
       <c r="D63" t="n">
-        <v>43.09999847412109</v>
+        <v>42.81999969482422</v>
       </c>
       <c r="E63" t="n">
         <v>43.59999847412109</v>
@@ -18357,67 +18361,67 @@
         <v>42.81999969482422</v>
       </c>
       <c r="H63" t="n">
-        <v>4759600</v>
+        <v>6729400</v>
       </c>
       <c r="I63" t="n">
-        <v>0.006538972005894594</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>43.49333360460069</v>
+        <v>43.46222262912326</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.9043572839355603</v>
+        <v>-1.477657826612622</v>
       </c>
       <c r="M63" t="n">
-        <v>43.44200019836425</v>
+        <v>43.41400032043457</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.7872605374557288</v>
+        <v>-1.368223663394498</v>
       </c>
       <c r="P63" t="n">
-        <v>45.58730800335224</v>
+        <v>45.57653881953313</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-5.456144787159277</v>
+        <v>-6.048153712645496</v>
       </c>
       <c r="S63" t="n">
-        <v>46.59720008850098</v>
+        <v>46.59160011291504</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-7.505175434871042</v>
+        <v>-8.095022297904176</v>
       </c>
       <c r="V63" t="n">
-        <v>45.56413340250651</v>
+        <v>45.56226674397787</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-5.408058366034601</v>
+        <v>-6.018723924696092</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.41725004196167</v>
+        <v>43.41585004806519</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-0.7307039656679387</v>
+        <v>-1.37242585963723</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.4983370009202606</v>
+        <v>0.4973677062603452</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18565,13 +18569,13 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>21.55</v>
+        <v>21.41</v>
       </c>
       <c r="CA63" t="n">
         <v>0.67</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CC63" t="n">
         <v>10</v>
@@ -18621,10 +18625,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.46999931335449</v>
+        <v>27.21999931335449</v>
       </c>
       <c r="D64" t="n">
-        <v>27.46999931335449</v>
+        <v>27.21999931335449</v>
       </c>
       <c r="E64" t="n">
         <v>27.69000053405762</v>
@@ -18636,67 +18640,67 @@
         <v>27.61000061035156</v>
       </c>
       <c r="H64" t="n">
-        <v>840600</v>
+        <v>1230200</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>-0.009100837504515846</v>
       </c>
       <c r="J64" t="n">
-        <v>27.29333326551649</v>
+        <v>27.26555548773872</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.6472864494759407</v>
+        <v>-0.1670832431956519</v>
       </c>
       <c r="M64" t="n">
-        <v>27.25599994659424</v>
+        <v>27.23099994659424</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.7851459024786046</v>
+        <v>-0.04039746341052722</v>
       </c>
       <c r="P64" t="n">
-        <v>28.16346153846154</v>
+        <v>28.15384615384615</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.462276251660395</v>
+        <v>-3.31694232961519</v>
       </c>
       <c r="S64" t="n">
-        <v>29.41499996185303</v>
+        <v>29.40999996185303</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-6.612274863236165</v>
+        <v>-7.446449001493134</v>
       </c>
       <c r="V64" t="n">
-        <v>31.97086667378743</v>
+        <v>31.96920000712077</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-14.07802736897074</v>
+        <v>-14.85555063219739</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.01045001029968</v>
+        <v>31.00920001029968</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-11.41696007561734</v>
+        <v>-12.21960158819515</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2525704801172893</v>
+        <v>0.2523746076945932</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18866,13 +18870,13 @@
         <v>18881600000</v>
       </c>
       <c r="BZ64" t="n">
-        <v>6.65</v>
+        <v>6.59</v>
       </c>
       <c r="CA64" t="n">
         <v>0</v>
       </c>
       <c r="CB64" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="CC64" t="n">
         <v>4</v>
@@ -18907,13 +18911,13 @@
         <v>5</v>
       </c>
       <c r="CM64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -18926,82 +18930,82 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28.43000030517578</v>
+        <v>28.15999984741211</v>
       </c>
       <c r="D65" t="n">
-        <v>28.43000030517578</v>
+        <v>28.15999984741211</v>
       </c>
       <c r="E65" t="n">
         <v>28.93000030517578</v>
       </c>
       <c r="F65" t="n">
-        <v>28.36000061035156</v>
+        <v>28.15999984741211</v>
       </c>
       <c r="G65" t="n">
         <v>28.54999923706055</v>
       </c>
       <c r="H65" t="n">
-        <v>10226700</v>
+        <v>15272300</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.004551791428484608</v>
+        <v>-0.01400558914601069</v>
       </c>
       <c r="J65" t="n">
-        <v>28.7544445461697</v>
+        <v>28.72444449530708</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-1.128327276407575</v>
+        <v>-1.96503242382001</v>
       </c>
       <c r="M65" t="n">
-        <v>28.78200016021729</v>
+        <v>28.75500011444092</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-1.222986078389515</v>
+        <v>-2.069206275989532</v>
       </c>
       <c r="P65" t="n">
-        <v>30.96800026526818</v>
+        <v>30.95761563227727</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-8.195556504624761</v>
+        <v>-9.036922669032322</v>
       </c>
       <c r="S65" t="n">
-        <v>31.38442989349365</v>
+        <v>31.37902988433838</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-9.413679325525548</v>
+        <v>-10.25853905870087</v>
       </c>
       <c r="V65" t="n">
-        <v>28.74076965332031</v>
+        <v>28.73896965026855</v>
       </c>
       <c r="W65" t="n">
         <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>-1.081284015331268</v>
+        <v>-2.014580932796367</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.55429039001465</v>
+        <v>27.55294038772583</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.178125448944526</v>
+        <v>2.203247461591105</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2705254230837683</v>
+        <v>0.271591111150805</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19153,13 +19157,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>11.46</v>
+        <v>11.35</v>
       </c>
       <c r="CA65" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CC65" t="n">
         <v>9</v>
@@ -19194,13 +19198,13 @@
         <v>3</v>
       </c>
       <c r="CM65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
@@ -19213,10 +19217,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15.84000015258789</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="D66" t="n">
-        <v>15.84000015258789</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="E66" t="n">
         <v>15.97999954223633</v>
@@ -19228,67 +19232,67 @@
         <v>15.89999961853027</v>
       </c>
       <c r="H66" t="n">
-        <v>1534800</v>
+        <v>2345100</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.003146645038045848</v>
+        <v>0.0006292809937993304</v>
       </c>
       <c r="J66" t="n">
-        <v>16.3600000805325</v>
+        <v>16.36666668785943</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-3.178483651496911</v>
+        <v>-2.851326285488067</v>
       </c>
       <c r="M66" t="n">
-        <v>16.44300012588501</v>
+        <v>16.44900007247925</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.667213821569345</v>
+        <v>-3.337591656209572</v>
       </c>
       <c r="P66" t="n">
-        <v>16.99500014231755</v>
+        <v>16.99730781408457</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-6.796116387511584</v>
+        <v>-6.45577645328648</v>
       </c>
       <c r="S66" t="n">
-        <v>17.65979997634888</v>
+        <v>17.66099996566772</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-10.30475897914008</v>
+        <v>-9.971124797920641</v>
       </c>
       <c r="V66" t="n">
-        <v>16.0290961265564</v>
+        <v>16.02949612299601</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-1.179704535274568</v>
+        <v>-0.807863849693701</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.74164419651031</v>
+        <v>15.74194419384003</v>
       </c>
       <c r="Z66" t="n">
         <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.6248137414983627</v>
+        <v>1.004040052130887</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.2262049738155777</v>
+        <v>0.2269546641884164</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19442,7 +19446,7 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>24.37</v>
+        <v>24.46</v>
       </c>
       <c r="CA66" t="n">
         <v>0.8</v>
@@ -19502,10 +19506,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.76000022888184</v>
+        <v>18.72999954223633</v>
       </c>
       <c r="D67" t="n">
-        <v>18.76000022888184</v>
+        <v>18.72999954223633</v>
       </c>
       <c r="E67" t="n">
         <v>19.03000068664551</v>
@@ -19517,67 +19521,67 @@
         <v>18.60000038146973</v>
       </c>
       <c r="H67" t="n">
-        <v>1731600</v>
+        <v>3843800</v>
       </c>
       <c r="I67" t="n">
-        <v>0.006437813474395204</v>
+        <v>0.004828334524403122</v>
       </c>
       <c r="J67" t="n">
-        <v>18.99888886345757</v>
+        <v>18.9955554538303</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-1.257382135832243</v>
+        <v>-1.397989715222675</v>
       </c>
       <c r="M67" t="n">
-        <v>18.96999988555908</v>
+        <v>18.96699981689453</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-1.107009266969526</v>
+        <v>-1.249540132578585</v>
       </c>
       <c r="P67" t="n">
-        <v>18.58807688492995</v>
+        <v>18.58692301236666</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>0.9249119476758241</v>
+        <v>0.7697698525703914</v>
       </c>
       <c r="S67" t="n">
-        <v>18.70679992675781</v>
+        <v>18.7061999130249</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.2843901807487959</v>
+        <v>0.1272285623059831</v>
       </c>
       <c r="V67" t="n">
-        <v>21.54572123209635</v>
+        <v>21.54552122751872</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-12.92934672831778</v>
+        <v>-13.06778172387077</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.34974093437195</v>
+        <v>22.34959093093872</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-16.0616658422622</v>
+        <v>-16.19533619155312</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5183049706570604</v>
+        <v>0.5181542642476571</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19727,10 +19731,10 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.75</v>
+        <v>16.72</v>
       </c>
       <c r="CA67" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="CB67" t="n">
         <v>1.95</v>
@@ -19787,10 +19791,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.84999847412109</v>
+        <v>41.68999862670898</v>
       </c>
       <c r="D68" t="n">
-        <v>41.84999847412109</v>
+        <v>41.68999862670898</v>
       </c>
       <c r="E68" t="n">
         <v>42.4900016784668</v>
@@ -19802,67 +19806,67 @@
         <v>42.31999969482422</v>
       </c>
       <c r="H68" t="n">
-        <v>2165000</v>
+        <v>4890800</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.005702106856657729</v>
+        <v>-0.009503481217124965</v>
       </c>
       <c r="J68" t="n">
-        <v>41.80111100938585</v>
+        <v>41.78333324856229</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.116952548759452</v>
+        <v>-0.223377635522923</v>
       </c>
       <c r="M68" t="n">
-        <v>41.79099998474121</v>
+        <v>41.775</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.1411751080410208</v>
+        <v>-0.2034742628151148</v>
       </c>
       <c r="P68" t="n">
-        <v>43.20846146803636</v>
+        <v>43.20230762775127</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.143974461854413</v>
+        <v>-3.500528291388881</v>
       </c>
       <c r="S68" t="n">
-        <v>46.33499984741211</v>
+        <v>46.33179985046387</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-9.679510927076237</v>
+        <v>-10.01860760586966</v>
       </c>
       <c r="V68" t="n">
-        <v>49.59606661478679</v>
+        <v>49.59499994913737</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-15.6183114294718</v>
+        <v>-15.9391094475964</v>
       </c>
       <c r="Y68" t="n">
-        <v>49.97674997329712</v>
+        <v>49.97594997406006</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-16.26106440198332</v>
+        <v>-16.57987762444112</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2064714631628539</v>
+        <v>0.2069047121913891</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20014,10 +20018,10 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="CA68" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CB68" t="n">
         <v>1.1</v>
@@ -20055,13 +20059,13 @@
         <v>3</v>
       </c>
       <c r="CM68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN68" t="n">
         <v>1</v>
       </c>
       <c r="CO68" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69">
@@ -20074,82 +20078,82 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39.56000137329102</v>
+        <v>39.22000122070312</v>
       </c>
       <c r="D69" t="n">
-        <v>39.56000137329102</v>
+        <v>39.22000122070312</v>
       </c>
       <c r="E69" t="n">
         <v>40.0099983215332</v>
       </c>
       <c r="F69" t="n">
-        <v>39.36000061035156</v>
+        <v>39.22000122070312</v>
       </c>
       <c r="G69" t="n">
         <v>39.54000091552734</v>
       </c>
       <c r="H69" t="n">
-        <v>1061500</v>
+        <v>1688400</v>
       </c>
       <c r="I69" t="n">
-        <v>0.004826071794794329</v>
+        <v>-0.003809949587277317</v>
       </c>
       <c r="J69" t="n">
-        <v>38.86111068725586</v>
+        <v>38.82333289252387</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1.798432092329134</v>
+        <v>1.021726623207144</v>
       </c>
       <c r="M69" t="n">
-        <v>38.803999710083</v>
+        <v>38.76999969482422</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1.948257058180443</v>
+        <v>1.160695200982884</v>
       </c>
       <c r="P69" t="n">
-        <v>40.73923081618089</v>
+        <v>40.7261538872352</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-2.894579547195349</v>
+        <v>-3.698244304390716</v>
       </c>
       <c r="S69" t="n">
-        <v>41.95900016784668</v>
+        <v>41.95220016479492</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-5.717483221618867</v>
+        <v>-6.512647568802795</v>
       </c>
       <c r="V69" t="n">
-        <v>41.76766680399577</v>
+        <v>41.76540013631185</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-5.285584758815283</v>
+        <v>-6.094515812852683</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.09310012817383</v>
+        <v>40.09140012741089</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-1.329652117642559</v>
+        <v>-2.173530742100415</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2546719441678306</v>
+        <v>0.2531629223664019</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20301,13 +20305,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.69</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CC69" t="n">
         <v>6</v>
@@ -20338,13 +20342,13 @@
         <v>5</v>
       </c>
       <c r="CM69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN69" t="n">
         <v>0</v>
       </c>
       <c r="CO69" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70">
@@ -20357,10 +20361,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.57999992370605</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="D70" t="n">
-        <v>22.57999992370605</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="E70" t="n">
         <v>22.80999946594238</v>
@@ -20372,67 +20376,67 @@
         <v>22.70000076293945</v>
       </c>
       <c r="H70" t="n">
-        <v>1760200</v>
+        <v>2905400</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0008849759923044154</v>
+        <v>-0.01150443471209039</v>
       </c>
       <c r="J70" t="n">
-        <v>22.48333316379123</v>
+        <v>22.45666652255588</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4299485276965104</v>
+        <v>-0.5195177559002759</v>
       </c>
       <c r="M70" t="n">
-        <v>22.45399990081787</v>
+        <v>22.42999992370606</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.5611473387580961</v>
+        <v>-0.4012473090695179</v>
       </c>
       <c r="P70" t="n">
-        <v>23.75269229595478</v>
+        <v>23.74346153552716</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-4.937092425722361</v>
+        <v>-5.91093838966689</v>
       </c>
       <c r="S70" t="n">
-        <v>25.31519996643067</v>
+        <v>25.3103999710083</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-10.80457609006302</v>
+        <v>-11.73588652025588</v>
       </c>
       <c r="V70" t="n">
-        <v>24.85740000406901</v>
+        <v>24.85580000559489</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-9.161859566930405</v>
+        <v>-10.12158068716641</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.34070000648499</v>
+        <v>24.33950000762939</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-7.233563875771183</v>
+        <v>-8.21504079547544</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3788475264031167</v>
+        <v>0.3788634555597079</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20584,13 +20588,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2258</v>
+        <v>2234</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CC70" t="n">
         <v>1</v>
@@ -20625,13 +20629,13 @@
         <v>2</v>
       </c>
       <c r="CM70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
@@ -20644,10 +20648,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>31.78000068664551</v>
+        <v>31.75</v>
       </c>
       <c r="D71" t="n">
-        <v>31.78000068664551</v>
+        <v>31.75</v>
       </c>
       <c r="E71" t="n">
         <v>31.95999908447266</v>
@@ -20659,67 +20663,67 @@
         <v>31.48999977111816</v>
       </c>
       <c r="H71" t="n">
-        <v>5903100</v>
+        <v>8129700</v>
       </c>
       <c r="I71" t="n">
-        <v>0.02252254712541135</v>
+        <v>0.02155727406494967</v>
       </c>
       <c r="J71" t="n">
-        <v>31.57777743869358</v>
+        <v>31.5744440290663</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>0.6403973438109625</v>
+        <v>0.5560065310163186</v>
       </c>
       <c r="M71" t="n">
-        <v>31.53399963378906</v>
+        <v>31.53099956512451</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.7801137049321614</v>
+        <v>0.694555954127504</v>
       </c>
       <c r="P71" t="n">
-        <v>32.29384605701153</v>
+        <v>32.29269218444824</v>
       </c>
       <c r="Q71" t="n">
         <v>-1</v>
       </c>
       <c r="R71" t="n">
-        <v>-1.591155694056627</v>
+        <v>-1.680541781244228</v>
       </c>
       <c r="S71" t="n">
-        <v>33.44979991912842</v>
+        <v>33.44919990539551</v>
       </c>
       <c r="T71" t="n">
         <v>-1</v>
       </c>
       <c r="U71" t="n">
-        <v>-4.991955815939057</v>
+        <v>-5.07994185272402</v>
       </c>
       <c r="V71" t="n">
-        <v>39.45073329925537</v>
+        <v>39.45053329467773</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-19.44382770891269</v>
+        <v>-19.51946564868519</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.40074999809265</v>
+        <v>40.40059999465942</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-21.33809226772803</v>
+        <v>-21.41205822637028</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4566111323443067</v>
+        <v>0.4561574442394895</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20867,13 +20871,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>20.64</v>
+        <v>20.62</v>
       </c>
       <c r="CA71" t="n">
         <v>0.18</v>
       </c>
       <c r="CB71" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20905,16 +20909,16 @@
         <v>0</v>
       </c>
       <c r="CL71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN71" t="n">
         <v>0</v>
       </c>
       <c r="CO71" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -20927,82 +20931,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27.10000038146973</v>
+        <v>26.90999984741211</v>
       </c>
       <c r="D72" t="n">
-        <v>27.10000038146973</v>
+        <v>26.90999984741211</v>
       </c>
       <c r="E72" t="n">
         <v>27.68000030517578</v>
       </c>
       <c r="F72" t="n">
-        <v>27.02000045776367</v>
+        <v>26.89999961853027</v>
       </c>
       <c r="G72" t="n">
         <v>27.60000038146973</v>
       </c>
       <c r="H72" t="n">
-        <v>2432000</v>
+        <v>4196600</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.01382820840963073</v>
+        <v>-0.02074234731875224</v>
       </c>
       <c r="J72" t="n">
-        <v>28.37888929578993</v>
+        <v>28.35777812533908</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-4.506479802611342</v>
+        <v>-5.105400964518139</v>
       </c>
       <c r="M72" t="n">
-        <v>28.4540002822876</v>
+        <v>28.43500022888184</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-4.758557276253092</v>
+        <v>-5.363110143114269</v>
       </c>
       <c r="P72" t="n">
-        <v>29.11500021127554</v>
+        <v>29.10769249842717</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-6.920830551893495</v>
+        <v>-7.550212546507465</v>
       </c>
       <c r="S72" t="n">
-        <v>28.96960010528564</v>
+        <v>28.96580009460449</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-6.453660792765997</v>
+        <v>-7.097336308605268</v>
       </c>
       <c r="V72" t="n">
-        <v>25.15459999084473</v>
+        <v>25.15333332061768</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>7.7337758951963</v>
+        <v>6.983831941488762</v>
       </c>
       <c r="Y72" t="n">
-        <v>23.85010000228882</v>
+        <v>23.84914999961853</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>13.62635954930598</v>
+        <v>12.83420938625712</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2503996654798288</v>
+        <v>0.2536780272098306</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21154,13 +21158,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="CA72" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21210,13 +21214,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.64000034332275</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="D73" t="n">
-        <v>10.64000034332275</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="E73" t="n">
-        <v>10.64999961853027</v>
+        <v>10.71000003814697</v>
       </c>
       <c r="F73" t="n">
         <v>10.21000003814697</v>
@@ -21225,67 +21229,67 @@
         <v>10.25</v>
       </c>
       <c r="H73" t="n">
-        <v>11485000</v>
+        <v>17431400</v>
       </c>
       <c r="I73" t="n">
-        <v>0.04007828146948267</v>
+        <v>0.04105572777006516</v>
       </c>
       <c r="J73" t="n">
-        <v>9.830000029669868</v>
+        <v>9.831111060248482</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>8.240084549420786</v>
+        <v>8.329562683844753</v>
       </c>
       <c r="M73" t="n">
-        <v>9.759000015258788</v>
+        <v>9.75999994277954</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>9.027567647161268</v>
+        <v>9.118849190251851</v>
       </c>
       <c r="P73" t="n">
-        <v>8.952692306958712</v>
+        <v>8.953076894466694</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>18.84693429095668</v>
+        <v>18.95351446285841</v>
       </c>
       <c r="S73" t="n">
-        <v>7.944999980926513</v>
+        <v>7.945199966430664</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>33.92070948856013</v>
+        <v>34.04319165694611</v>
       </c>
       <c r="V73" t="n">
-        <v>6.650533326466879</v>
+        <v>6.650599988301595</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>59.98717427637183</v>
+        <v>60.13592213129074</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.083049994707108</v>
+        <v>6.083099991083145</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>74.91226198339108</v>
+        <v>75.07520234981301</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.5496962221770312</v>
+        <v>0.5500988168791906</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21497,10 +21501,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>83.98000335693359</v>
+        <v>83.95999908447266</v>
       </c>
       <c r="D74" t="n">
-        <v>83.98000335693359</v>
+        <v>83.95999908447266</v>
       </c>
       <c r="E74" t="n">
         <v>84.05000305175781</v>
@@ -21512,67 +21516,67 @@
         <v>83.15000152587891</v>
       </c>
       <c r="H74" t="n">
-        <v>8243700</v>
+        <v>12765800</v>
       </c>
       <c r="I74" t="n">
-        <v>0.006351185477216026</v>
+        <v>0.006111469800853087</v>
       </c>
       <c r="J74" t="n">
-        <v>82.74111005995009</v>
+        <v>82.73888736300998</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>1.497312878792495</v>
+        <v>1.475861907720792</v>
       </c>
       <c r="M74" t="n">
-        <v>82.81699905395507</v>
+        <v>82.81499862670898</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>1.404306261110508</v>
+        <v>1.382600346254662</v>
       </c>
       <c r="P74" t="n">
-        <v>82.72153883713942</v>
+        <v>82.72076944204477</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>1.521326292384158</v>
+        <v>1.498087663819552</v>
       </c>
       <c r="S74" t="n">
-        <v>82.66560043334961</v>
+        <v>82.6652003479004</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>1.590024044697699</v>
+        <v>1.566316577136497</v>
       </c>
       <c r="V74" t="n">
-        <v>77.40413345336914</v>
+        <v>77.40400009155273</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>8.49550225573674</v>
+        <v>8.469845208471849</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.2410500907898</v>
+        <v>72.24095006942748</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>16.24969909959881</v>
+        <v>16.22216901048855</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3024310435980251</v>
+        <v>0.3023778035060607</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21720,7 +21724,7 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>23.93</v>
+        <v>23.92</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
@@ -21757,13 +21761,13 @@
         <v>9</v>
       </c>
       <c r="CM74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN74" t="n">
         <v>0</v>
       </c>
       <c r="CO74" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75">
@@ -21776,10 +21780,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.220000028610229</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="D75" t="n">
-        <v>3.220000028610229</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="E75" t="n">
         <v>3.289999961853027</v>
@@ -21791,67 +21795,67 @@
         <v>3.240000009536743</v>
       </c>
       <c r="H75" t="n">
-        <v>8988700</v>
+        <v>10678100</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.003095972261364044</v>
+        <v>-0.01238388904545618</v>
       </c>
       <c r="J75" t="n">
-        <v>3.296666648652819</v>
+        <v>3.2933333184984</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-2.325579993777016</v>
+        <v>-3.13764964807922</v>
       </c>
       <c r="M75" t="n">
-        <v>3.307999992370605</v>
+        <v>3.304999995231628</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-2.660216564792452</v>
+        <v>-3.479574528807513</v>
       </c>
       <c r="P75" t="n">
-        <v>3.680384626755348</v>
+        <v>3.679230781701895</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-12.50914360412913</v>
+        <v>-13.297092612797</v>
       </c>
       <c r="S75" t="n">
-        <v>3.741400008201599</v>
+        <v>3.740800008773804</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-13.93595922511354</v>
+        <v>-14.72412185258445</v>
       </c>
       <c r="V75" t="n">
-        <v>3.750994790395101</v>
+        <v>3.750794790585836</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-14.15610501898192</v>
+        <v>-14.95135737025449</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.742696098089218</v>
+        <v>3.742546098232269</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-13.96576306972516</v>
+        <v>-14.76390741780833</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.5149241600282439</v>
+        <v>0.5147986261844677</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21861,26 +21865,28 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AE75" t="n">
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AF75" t="n">
         <v>2.9</v>
       </c>
-      <c r="AF75" t="n">
+      <c r="AG75" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG75" t="n">
+      <c r="AH75" t="n">
         <v>3.3</v>
       </c>
-      <c r="AH75" t="n">
+      <c r="AI75" t="n">
         <v>3.4</v>
       </c>
-      <c r="AI75" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AJ75" t="n">
         <v>1</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
@@ -22001,13 +22007,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>12.88</v>
+        <v>12.76</v>
       </c>
       <c r="CA75" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="CB75" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CC75" t="n">
         <v>6</v>
@@ -22038,13 +22044,13 @@
         <v>1</v>
       </c>
       <c r="CM75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN75" t="n">
         <v>-1</v>
       </c>
       <c r="CO75" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -22057,82 +22063,82 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>31.14999961853027</v>
+        <v>30.90999984741211</v>
       </c>
       <c r="D76" t="n">
-        <v>31.14999961853027</v>
+        <v>30.90999984741211</v>
       </c>
       <c r="E76" t="n">
         <v>31.67000007629395</v>
       </c>
       <c r="F76" t="n">
-        <v>30.86000061035156</v>
+        <v>30.82999992370605</v>
       </c>
       <c r="G76" t="n">
         <v>31.06999969482422</v>
       </c>
       <c r="H76" t="n">
-        <v>3213500</v>
+        <v>5419400</v>
       </c>
       <c r="I76" t="n">
-        <v>0.004190817499941879</v>
+        <v>-0.003546118914515728</v>
       </c>
       <c r="J76" t="n">
-        <v>32.41666624281142</v>
+        <v>32.38999960157606</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-3.90745493319207</v>
+        <v>-4.569310813118813</v>
       </c>
       <c r="M76" t="n">
-        <v>32.48699951171875</v>
+        <v>32.46299953460694</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-4.115492083860168</v>
+        <v>-4.783906938541719</v>
       </c>
       <c r="P76" t="n">
-        <v>32.84615355271559</v>
+        <v>32.83692279228797</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-5.16393474037415</v>
+        <v>-5.868159318900663</v>
       </c>
       <c r="S76" t="n">
-        <v>32.34859989166259</v>
+        <v>32.34379989624023</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-3.705261671746244</v>
+        <v>-4.432998143161266</v>
       </c>
       <c r="V76" t="n">
-        <v>28.44927639007568</v>
+        <v>28.44767639160156</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>9.493117474849784</v>
+        <v>8.655622420316497</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.77719359397888</v>
+        <v>26.77599359512329</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>16.33033726706394</v>
+        <v>15.43922632638269</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.2719496680043538</v>
+        <v>0.2713302107391853</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22284,13 +22290,13 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>12.41</v>
+        <v>12.31</v>
       </c>
       <c r="CA76" t="n">
         <v>0.49</v>
       </c>
       <c r="CB76" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CC76" t="n">
         <v>5</v>
@@ -22321,13 +22327,13 @@
         <v>7</v>
       </c>
       <c r="CM76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN76" t="n">
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -22340,10 +22346,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>22.29999923706055</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="D77" t="n">
-        <v>22.29999923706055</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="E77" t="n">
         <v>22.45000076293945</v>
@@ -22355,67 +22361,67 @@
         <v>22.29000091552734</v>
       </c>
       <c r="H77" t="n">
-        <v>1817900</v>
+        <v>2532400</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00541023129998619</v>
+        <v>-0.001352600822034589</v>
       </c>
       <c r="J77" t="n">
-        <v>22.41555553012424</v>
+        <v>22.3988889058431</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.5155183100789003</v>
+        <v>-1.111168006409004</v>
       </c>
       <c r="M77" t="n">
-        <v>22.46800003051758</v>
+        <v>22.45300006866455</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.7477336355209296</v>
+        <v>-1.349487592783404</v>
       </c>
       <c r="P77" t="n">
-        <v>24.30576926011306</v>
+        <v>24.30000004401574</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-8.252238394873908</v>
+        <v>-8.847738360457072</v>
       </c>
       <c r="S77" t="n">
-        <v>25.3638000869751</v>
+        <v>25.36080009460449</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-12.07942358561595</v>
+        <v>-12.66048572638415</v>
       </c>
       <c r="V77" t="n">
-        <v>29.11986668904622</v>
+        <v>29.11886669158936</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-23.4199817080586</v>
+        <v>-23.93248043225514</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.89145001411438</v>
+        <v>28.89070001602173</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-22.81453777444089</v>
+        <v>-23.33173095062878</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4661725698232022</v>
+        <v>0.4651389052265448</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22563,13 +22569,13 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>8.99</v>
+        <v>8.93</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
       </c>
       <c r="CB77" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CC77" t="n">
         <v>8</v>
@@ -22601,7 +22607,7 @@
         <v>1</v>
       </c>
       <c r="CL77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM77" t="n">
         <v>4</v>
@@ -22610,7 +22616,7 @@
         <v>0</v>
       </c>
       <c r="CO77" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -22623,10 +22629,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.7599983215332</v>
+        <v>33.59999847412109</v>
       </c>
       <c r="D78" t="n">
-        <v>33.7599983215332</v>
+        <v>33.59999847412109</v>
       </c>
       <c r="E78" t="n">
         <v>34.06999969482422</v>
@@ -22638,67 +22644,67 @@
         <v>33.72000122070312</v>
       </c>
       <c r="H78" t="n">
-        <v>1895600</v>
+        <v>3144000</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.005010373772871612</v>
+        <v>-0.009725960155807845</v>
       </c>
       <c r="J78" t="n">
-        <v>34.49555587768555</v>
+        <v>34.47777811686198</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.132325563213088</v>
+        <v>-2.545928684167699</v>
       </c>
       <c r="M78" t="n">
-        <v>34.59800033569336</v>
+        <v>34.58200035095215</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-2.422111122114825</v>
+        <v>-2.839632950278478</v>
       </c>
       <c r="P78" t="n">
-        <v>36.90115385789137</v>
+        <v>36.89500001760629</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-8.51235044967687</v>
+        <v>-8.930753603233024</v>
       </c>
       <c r="S78" t="n">
-        <v>38.93360000610352</v>
+        <v>38.93040000915527</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-13.28826947356336</v>
+        <v>-13.69213142885926</v>
       </c>
       <c r="V78" t="n">
-        <v>36.99593340555827</v>
+        <v>36.99486673990885</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-8.74673183279895</v>
+        <v>-9.176592768005525</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.1000500869751</v>
+        <v>36.09925008773804</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-6.482128860774582</v>
+        <v>-6.923278482357924</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3107537227300767</v>
+        <v>0.3108429047434015</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22850,13 +22856,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>17.14</v>
+        <v>17.06</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
       </c>
       <c r="CB78" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CC78" t="n">
         <v>5</v>
@@ -22910,10 +22916,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>43.84999847412109</v>
+        <v>43.72000122070312</v>
       </c>
       <c r="D79" t="n">
-        <v>43.84999847412109</v>
+        <v>43.72000122070312</v>
       </c>
       <c r="E79" t="n">
         <v>44.02000045776367</v>
@@ -22925,67 +22931,67 @@
         <v>43.88999938964844</v>
       </c>
       <c r="H79" t="n">
-        <v>2643100</v>
+        <v>4254400</v>
       </c>
       <c r="I79" t="n">
-        <v>0.009205931050818794</v>
+        <v>0.006214049551731327</v>
       </c>
       <c r="J79" t="n">
-        <v>42.88777796427409</v>
+        <v>42.87333382500542</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2.243577437489408</v>
+        <v>1.974811194187774</v>
       </c>
       <c r="M79" t="n">
-        <v>42.9120002746582</v>
+        <v>42.8990005493164</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2.185864544787548</v>
+        <v>1.913799064952348</v>
       </c>
       <c r="P79" t="n">
-        <v>44.38769237811749</v>
+        <v>44.38269248375526</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-1.211358093175997</v>
+        <v>-1.493129925127203</v>
       </c>
       <c r="S79" t="n">
-        <v>46.74060012817383</v>
+        <v>46.73800018310547</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-6.184348609401721</v>
+        <v>-6.457270209633981</v>
       </c>
       <c r="V79" t="n">
-        <v>47.04226661682129</v>
+        <v>47.04139996846517</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-6.785957336415223</v>
+        <v>-7.060586525886964</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.50419994354248</v>
+        <v>44.50354995727539</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-1.469976924090985</v>
+        <v>-1.760643223573158</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.3386639090577136</v>
+        <v>0.3376537524214701</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23137,13 +23143,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>29.23</v>
+        <v>29.15</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB79" t="n">
-        <v>10.37</v>
+        <v>10.34</v>
       </c>
       <c r="CC79" t="n">
         <v>6</v>
@@ -23197,10 +23203,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.670000076293945</v>
+        <v>9.579999923706055</v>
       </c>
       <c r="D80" t="n">
-        <v>9.670000076293945</v>
+        <v>9.579999923706055</v>
       </c>
       <c r="E80" t="n">
         <v>9.869999885559082</v>
@@ -23212,67 +23218,67 @@
         <v>9.630000114440918</v>
       </c>
       <c r="H80" t="n">
-        <v>1698700</v>
+        <v>2162800</v>
       </c>
       <c r="I80" t="n">
-        <v>0.005197525086244603</v>
+        <v>-0.004158000242086568</v>
       </c>
       <c r="J80" t="n">
-        <v>9.616666581895617</v>
+        <v>9.606666564941406</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5545944007119337</v>
+        <v>-0.2775847486230955</v>
       </c>
       <c r="M80" t="n">
-        <v>9.610999965667725</v>
+        <v>9.601999950408935</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O80" t="n">
-        <v>0.6138810824781988</v>
+        <v>-0.2291192128358968</v>
       </c>
       <c r="P80" t="n">
-        <v>9.99730766736544</v>
+        <v>9.993846123035137</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-3.273957368941807</v>
+        <v>-4.141010320092833</v>
       </c>
       <c r="S80" t="n">
-        <v>10.66920000076294</v>
+        <v>10.66739999771118</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-9.365275038405347</v>
+        <v>-10.19367488083733</v>
       </c>
       <c r="V80" t="n">
-        <v>12.1793333307902</v>
+        <v>12.17873332977295</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-20.60320697646469</v>
+        <v>-21.33828975230007</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.38560000419617</v>
+        <v>12.38515000343323</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-21.92546123709948</v>
+        <v>-22.64930242225222</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4274251382950149</v>
+        <v>0.4260492430839058</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23424,10 +23430,10 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>22.49</v>
+        <v>22.28</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CB80" t="n">
         <v>0.88</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.15999984741211</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="D2" t="n">
-        <v>16.15999984741211</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="E2" t="n">
-        <v>16.29999923706055</v>
+        <v>16.30999946594238</v>
       </c>
       <c r="F2" t="n">
         <v>16.02000045776367</v>
@@ -912,67 +912,67 @@
         <v>16.29000091552734</v>
       </c>
       <c r="H2" t="n">
-        <v>19309600</v>
+        <v>31110700</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.007980421166908558</v>
+        <v>0.001227658028918555</v>
       </c>
       <c r="J2" t="n">
-        <v>16.28666676415337</v>
+        <v>16.30333338843452</v>
       </c>
       <c r="K2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7777338271576584</v>
+        <v>0.04088781937437921</v>
       </c>
       <c r="M2" t="n">
-        <v>16.23900012969971</v>
+        <v>16.25400009155273</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4864848922755642</v>
+        <v>0.3445267261857157</v>
       </c>
       <c r="P2" t="n">
-        <v>15.77346152525682</v>
+        <v>15.77923074135414</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.450561162724864</v>
+        <v>3.363717365493687</v>
       </c>
       <c r="S2" t="n">
-        <v>15.52940000534058</v>
+        <v>15.53239999771118</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>4.060683876097395</v>
+        <v>5.006305969108361</v>
       </c>
       <c r="V2" t="n">
-        <v>14.67166666030884</v>
+        <v>14.67266665776571</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>10.14426800691738</v>
+        <v>11.15906771663824</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.05365000247955</v>
+        <v>14.0544000005722</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.98792018131178</v>
+        <v>16.04906267986072</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5051930036959787</v>
+        <v>0.5044523871443013</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,13 +1124,13 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.32</v>
+        <v>16.47</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1165,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="CM2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN2" t="n">
         <v>-1</v>
       </c>
       <c r="CO2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.18000030517578</v>
+        <v>28.29000091552734</v>
       </c>
       <c r="D3" t="n">
-        <v>28.18000030517578</v>
+        <v>28.29000091552734</v>
       </c>
       <c r="E3" t="n">
         <v>28.84000015258789</v>
@@ -1199,67 +1199,67 @@
         <v>28.65999984741211</v>
       </c>
       <c r="H3" t="n">
-        <v>1936200</v>
+        <v>3068700</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01571773904232177</v>
+        <v>-0.0118755939645705</v>
       </c>
       <c r="J3" t="n">
-        <v>28.48777770996094</v>
+        <v>28.5</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.080384043707066</v>
+        <v>-0.7368388928865132</v>
       </c>
       <c r="M3" t="n">
-        <v>28.50299987792969</v>
+        <v>28.51399993896484</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.133212553546026</v>
+        <v>-0.7855755906466202</v>
       </c>
       <c r="P3" t="n">
-        <v>29.5861538373507</v>
+        <v>29.59038463005653</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.7527419072625</v>
+        <v>-4.394615787482241</v>
       </c>
       <c r="S3" t="n">
-        <v>30.36679996490479</v>
+        <v>30.36899997711182</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.201284502339103</v>
+        <v>-6.84579361569808</v>
       </c>
       <c r="V3" t="n">
-        <v>29.32819998423258</v>
+        <v>29.32893332163493</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.915002215185714</v>
+        <v>-3.542346374190158</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.03964997291565</v>
+        <v>28.04019997596741</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5005423833596315</v>
+        <v>0.8908671827377642</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2622571336787886</v>
+        <v>0.2612142280108507</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.18</v>
+        <v>17.25</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.800000190734863</v>
+        <v>8.810000419616699</v>
       </c>
       <c r="D4" t="n">
-        <v>8.800000190734863</v>
+        <v>8.810000419616699</v>
       </c>
       <c r="E4" t="n">
         <v>9.090000152587891</v>
@@ -1486,67 +1486,67 @@
         <v>8.989999771118164</v>
       </c>
       <c r="H4" t="n">
-        <v>9675000</v>
+        <v>14670100</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02004447223575678</v>
+        <v>-0.01893086094493202</v>
       </c>
       <c r="J4" t="n">
-        <v>8.772221989101833</v>
+        <v>8.77333312564426</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3166609516669796</v>
+        <v>0.4179402907346712</v>
       </c>
       <c r="M4" t="n">
-        <v>8.723999786376954</v>
+        <v>8.724999809265137</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8711646746781059</v>
+        <v>0.97421905111447</v>
       </c>
       <c r="P4" t="n">
-        <v>8.916538385244516</v>
+        <v>8.91692300943228</v>
       </c>
       <c r="Q4" t="n">
         <v>-1</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.306989208979414</v>
+        <v>-1.199097375882669</v>
       </c>
       <c r="S4" t="n">
-        <v>8.944399938583373</v>
+        <v>8.944599943161011</v>
       </c>
       <c r="T4" t="n">
         <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.614415151827171</v>
+        <v>-1.504813232560788</v>
       </c>
       <c r="V4" t="n">
-        <v>8.634866609573365</v>
+        <v>8.63493327776591</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.912404541124202</v>
+        <v>2.027429005173318</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.890049946308135</v>
+        <v>8.890099947452546</v>
       </c>
       <c r="Z4" t="n">
         <v>-1</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.012927442670532</v>
+        <v>-0.9009969326475256</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5208652360944828</v>
+        <v>0.5205818032248681</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>16.92</v>
+        <v>16.94</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1735,13 +1735,13 @@
         <v>9</v>
       </c>
       <c r="CM4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN4" t="n">
         <v>-1</v>
       </c>
       <c r="CO4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.26000022888184</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="D5" t="n">
-        <v>12.26000022888184</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="E5" t="n">
         <v>12.52999973297119</v>
@@ -1769,67 +1769,67 @@
         <v>12.42000007629395</v>
       </c>
       <c r="H5" t="n">
-        <v>607600</v>
+        <v>1333200</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01129027370607538</v>
+        <v>-0.009677410423445276</v>
       </c>
       <c r="J5" t="n">
-        <v>12.45333332485623</v>
+        <v>12.45555549197727</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.552460621836154</v>
+        <v>-1.409457483603632</v>
       </c>
       <c r="M5" t="n">
-        <v>12.45</v>
+        <v>12.45199995040894</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.526102579262356</v>
+        <v>-1.381305959867886</v>
       </c>
       <c r="P5" t="n">
-        <v>13.14576919262226</v>
+        <v>13.146538404318</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.73805351943603</v>
+        <v>-6.591382801287031</v>
       </c>
       <c r="S5" t="n">
-        <v>12.97319993972778</v>
+        <v>12.97359992980957</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.497484923992562</v>
+        <v>-5.346243144469766</v>
       </c>
       <c r="V5" t="n">
-        <v>12.12173330307007</v>
+        <v>12.12186663309733</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.140653092711993</v>
+        <v>1.304527633080021</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.71294996738434</v>
+        <v>11.71304996490479</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.670473817618993</v>
+        <v>4.840325703084413</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2221809829305574</v>
+        <v>0.2218271475697592</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1977,10 +1977,10 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.970000000000001</v>
+        <v>-9.98</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CB5" t="n">
         <v>1.08</v>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>51.86000061035156</v>
+        <v>52.13999938964844</v>
       </c>
       <c r="D6" t="n">
-        <v>51.86000061035156</v>
+        <v>52.13999938964844</v>
       </c>
       <c r="E6" t="n">
         <v>52.70000076293945</v>
@@ -2048,67 +2048,67 @@
         <v>52.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4939500</v>
+        <v>8314400</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01593928160203384</v>
+        <v>-0.01062621186307133</v>
       </c>
       <c r="J6" t="n">
-        <v>53.61555565728082</v>
+        <v>53.64666663275825</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.27433899622535</v>
+        <v>-2.808501138428225</v>
       </c>
       <c r="M6" t="n">
-        <v>53.68500022888183</v>
+        <v>53.71300010681152</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.399459086801763</v>
+        <v>-2.928528873894731</v>
       </c>
       <c r="P6" t="n">
-        <v>57.38884588388296</v>
+        <v>57.39961506770207</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.634006727924318</v>
+        <v>-9.163154965150881</v>
       </c>
       <c r="S6" t="n">
-        <v>58.98959999084472</v>
+        <v>58.99519996643066</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-12.08619719679348</v>
+        <v>-11.61992938524313</v>
       </c>
       <c r="V6" t="n">
-        <v>58.17866668701172</v>
+        <v>58.18053334554036</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.8607956085573</v>
+        <v>-10.38239701244496</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.59520000457763</v>
+        <v>55.59659999847412</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-6.718564541396596</v>
+        <v>-6.217287763857052</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2799592615723571</v>
+        <v>0.2790698658524022</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>15.86</v>
+        <v>15.94</v>
       </c>
       <c r="CA6" t="n">
         <v>0.3</v>
@@ -2294,7 +2294,7 @@
         <v>-1</v>
       </c>
       <c r="CL6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM6" t="n">
         <v>3</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.06999969482422</v>
+        <v>57.27000045776367</v>
       </c>
       <c r="D7" t="n">
-        <v>57.06999969482422</v>
+        <v>57.27000045776367</v>
       </c>
       <c r="E7" t="n">
         <v>57.88999938964844</v>
@@ -2331,67 +2331,67 @@
         <v>57.79999923706055</v>
       </c>
       <c r="H7" t="n">
-        <v>849500</v>
+        <v>1674500</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0143350916957008</v>
+        <v>-0.0108808471763796</v>
       </c>
       <c r="J7" t="n">
-        <v>58.98444451226128</v>
+        <v>59.00666681925455</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.245677454907799</v>
+        <v>-2.943169738447569</v>
       </c>
       <c r="M7" t="n">
-        <v>59.06599998474121</v>
+        <v>59.08600006103516</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.379271138104202</v>
+        <v>-3.07348543038212</v>
       </c>
       <c r="P7" t="n">
-        <v>63.09615413959209</v>
+        <v>63.10384647662823</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.550747627875682</v>
+        <v>-9.244834260658322</v>
       </c>
       <c r="S7" t="n">
-        <v>64.75480003356934</v>
+        <v>64.75880004882812</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-11.86753774972862</v>
+        <v>-11.56414199370263</v>
       </c>
       <c r="V7" t="n">
-        <v>58.65186904907227</v>
+        <v>58.65320238749186</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.697048499723932</v>
+        <v>-2.358271796636228</v>
       </c>
       <c r="Y7" t="n">
-        <v>54.04898151397705</v>
+        <v>54.04998151779175</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.589408155759475</v>
+        <v>5.957483887227568</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2963616101477217</v>
+        <v>0.2958874366049735</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,13 +2543,13 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.45</v>
+        <v>17.51</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CC7" t="n">
         <v>4</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.18000030517578</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="D8" t="n">
-        <v>19.18000030517578</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="E8" t="n">
         <v>19.85000038146973</v>
@@ -2618,67 +2618,67 @@
         <v>19.85000038146973</v>
       </c>
       <c r="H8" t="n">
-        <v>1714500</v>
+        <v>2255000</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03375315180947802</v>
+        <v>-0.02770786568460792</v>
       </c>
       <c r="J8" t="n">
-        <v>20.01333342658149</v>
+        <v>20.02666664123535</v>
       </c>
       <c r="K8" t="n">
         <v>-1</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.163889661174007</v>
+        <v>-3.628499026785518</v>
       </c>
       <c r="M8" t="n">
-        <v>19.94600009918213</v>
+        <v>19.95799999237061</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.840367944436925</v>
+        <v>-3.296927325190875</v>
       </c>
       <c r="P8" t="n">
-        <v>20.58538458897517</v>
+        <v>20.5899999325092</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-6.827097534782363</v>
+        <v>-6.265180668659906</v>
       </c>
       <c r="S8" t="n">
-        <v>22.32440006256104</v>
+        <v>22.32680004119873</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-14.08503587363383</v>
+        <v>-13.55680526789756</v>
       </c>
       <c r="V8" t="n">
-        <v>25.05860003153483</v>
+        <v>25.05940002441406</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-23.45941001876068</v>
+        <v>-22.98299552959143</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.5318500328064</v>
+        <v>26.53245002746582</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-27.70952541394632</v>
+        <v>-27.25888782573188</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4505408417532444</v>
+        <v>0.4475446931563276</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2830,13 +2830,13 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>4.76</v>
+        <v>4.79</v>
       </c>
       <c r="CA8" t="n">
         <v>0.55</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="CC8" t="n">
         <v>10</v>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.30999946594238</v>
+        <v>16.48999977111816</v>
       </c>
       <c r="D9" t="n">
-        <v>16.30999946594238</v>
+        <v>16.48999977111816</v>
       </c>
       <c r="E9" t="n">
         <v>16.63999938964844</v>
@@ -2901,67 +2901,67 @@
         <v>16.53000068664551</v>
       </c>
       <c r="H9" t="n">
-        <v>9857500</v>
+        <v>14396800</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01151518388227979</v>
+        <v>-0.0006060744776870131</v>
       </c>
       <c r="J9" t="n">
-        <v>16.65000014834934</v>
+        <v>16.67000018225776</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.04204612238795</v>
+        <v>-1.079786497730056</v>
       </c>
       <c r="M9" t="n">
-        <v>16.65700006484985</v>
+        <v>16.67500009536743</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.083211848211028</v>
+        <v>-1.109447215539519</v>
       </c>
       <c r="P9" t="n">
-        <v>17.41730781701895</v>
+        <v>17.42423090567956</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-6.357517262194691</v>
+        <v>-5.361677881902231</v>
       </c>
       <c r="S9" t="n">
-        <v>17.86840009689331</v>
+        <v>17.87200010299683</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-8.721545423766726</v>
+        <v>-7.732768150817789</v>
       </c>
       <c r="V9" t="n">
-        <v>16.02820007324219</v>
+        <v>16.02940007527669</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.758147461427284</v>
+        <v>2.873468087878637</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.25395005226135</v>
+        <v>15.25485005378723</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.923120962523896</v>
+        <v>8.096767342687114</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3475282140639439</v>
+        <v>0.3475380179168544</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>16.64</v>
+        <v>16.83</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.51</v>
+        <v>4.56</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3131,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="CF9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CG9" t="n">
         <v>1</v>
@@ -3140,7 +3140,7 @@
         <v>4</v>
       </c>
       <c r="CI9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
@@ -3151,16 +3151,16 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.54000091552734</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="D10" t="n">
-        <v>20.54000091552734</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="E10" t="n">
         <v>20.70000076293945</v>
@@ -3188,67 +3188,67 @@
         <v>20.67000007629395</v>
       </c>
       <c r="H10" t="n">
-        <v>12790800</v>
+        <v>21808600</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.003396394602194319</v>
+        <v>-0.00582245685005589</v>
       </c>
       <c r="J10" t="n">
-        <v>20.85222244262695</v>
+        <v>20.84666675991482</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.497305757017792</v>
+        <v>-1.710906558368734</v>
       </c>
       <c r="M10" t="n">
-        <v>20.80900020599365</v>
+        <v>20.80400009155273</v>
       </c>
       <c r="N10" t="n">
         <v>-1</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.292706462604713</v>
+        <v>-1.509326663395211</v>
       </c>
       <c r="P10" t="n">
-        <v>21.43192320603591</v>
+        <v>21.43000008509709</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-4.161653072074141</v>
+        <v>-4.386375689436536</v>
       </c>
       <c r="S10" t="n">
-        <v>22.57459999084473</v>
+        <v>22.57359996795654</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-9.012780187212748</v>
+        <v>-9.230252152054041</v>
       </c>
       <c r="V10" t="n">
-        <v>22.9425333404541</v>
+        <v>22.94219999949138</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.47195786652916</v>
+        <v>-10.68860104274035</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.46725002288818</v>
+        <v>22.46700001716614</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-8.578037389522452</v>
+        <v>-8.799573795065777</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2553375389441337</v>
+        <v>0.255252530966667</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3418,7 +3418,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.18</v>
+        <v>8.16</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3455,13 +3455,13 @@
         <v>4</v>
       </c>
       <c r="CM10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.48999977111816</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="D11" t="n">
-        <v>15.48999977111816</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="E11" t="n">
         <v>15.64000034332275</v>
@@ -3489,67 +3489,67 @@
         <v>15.64000034332275</v>
       </c>
       <c r="H11" t="n">
-        <v>1650600</v>
+        <v>3743000</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.006414392590825435</v>
+        <v>-0.004490038110268935</v>
       </c>
       <c r="J11" t="n">
-        <v>15.50555557674832</v>
+        <v>15.5088889863756</v>
       </c>
       <c r="K11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1003240777356003</v>
+        <v>0.07164582451932054</v>
       </c>
       <c r="M11" t="n">
-        <v>15.48900003433227</v>
+        <v>15.49200010299683</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006454495342975062</v>
+        <v>0.1807407344480279</v>
       </c>
       <c r="P11" t="n">
-        <v>15.99230769964365</v>
+        <v>15.99346157220694</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.140934616563667</v>
+        <v>-2.96034171405417</v>
       </c>
       <c r="S11" t="n">
-        <v>16.4923999786377</v>
+        <v>16.49299999237061</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.07795232239045</v>
+        <v>-5.899469684454182</v>
       </c>
       <c r="V11" t="n">
-        <v>16.62406665166219</v>
+        <v>16.62426665623983</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.82183790709618</v>
+        <v>-6.642495704083746</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.08745000362396</v>
+        <v>16.08760000705719</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.713765900569787</v>
+        <v>-3.528180393871853</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2150984601708135</v>
+        <v>0.2150519241780177</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3559,28 +3559,26 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AE11" t="n">
+        <v>10.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.2</v>
+        <v>15.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -3721,7 +3719,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.92</v>
+        <v>6.93</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3755,16 +3753,16 @@
         <v>0</v>
       </c>
       <c r="CL11" t="n">
+        <v>6</v>
+      </c>
+      <c r="CM11" t="n">
         <v>7</v>
       </c>
-      <c r="CM11" t="n">
-        <v>8</v>
-      </c>
       <c r="CN11" t="n">
         <v>1</v>
       </c>
       <c r="CO11" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -3777,10 +3775,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.76000022888184</v>
+        <v>17.80999946594238</v>
       </c>
       <c r="D12" t="n">
-        <v>17.76000022888184</v>
+        <v>17.80999946594238</v>
       </c>
       <c r="E12" t="n">
         <v>17.95000076293945</v>
@@ -3792,67 +3790,67 @@
         <v>17.94000053405762</v>
       </c>
       <c r="H12" t="n">
-        <v>11525300</v>
+        <v>16009200</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.007821195119105395</v>
+        <v>-0.0050279415925083</v>
       </c>
       <c r="J12" t="n">
-        <v>17.81555557250977</v>
+        <v>17.82111104329427</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3118361557786847</v>
+        <v>-0.06235064314953529</v>
       </c>
       <c r="M12" t="n">
-        <v>17.8</v>
+        <v>17.80499992370606</v>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2247178152705886</v>
+        <v>0.02807942857483632</v>
       </c>
       <c r="P12" t="n">
-        <v>18.43576922783485</v>
+        <v>18.4376922754141</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-3.665531883165013</v>
+        <v>-3.404400074019676</v>
       </c>
       <c r="S12" t="n">
-        <v>19.01680004119873</v>
+        <v>19.01780002593994</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.608892187929177</v>
+        <v>-6.350895257864421</v>
       </c>
       <c r="V12" t="n">
-        <v>19.30013333638509</v>
+        <v>19.30046666463216</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.979909157413736</v>
+        <v>-7.722441247604851</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.70244999885559</v>
+        <v>18.70269999504089</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-5.039178129236675</v>
+        <v>-4.773110456432578</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2564854823578505</v>
+        <v>0.2563581820186041</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4020,13 +4018,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.93</v>
+        <v>7.95</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4076,10 +4074,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34.95000076293945</v>
+        <v>34.91999816894531</v>
       </c>
       <c r="D13" t="n">
-        <v>34.95000076293945</v>
+        <v>34.91999816894531</v>
       </c>
       <c r="E13" t="n">
         <v>35.02000045776367</v>
@@ -4091,67 +4089,67 @@
         <v>34.70000076293945</v>
       </c>
       <c r="H13" t="n">
-        <v>1295000</v>
+        <v>2267200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01069979503449558</v>
+        <v>0.009832166567015355</v>
       </c>
       <c r="J13" t="n">
-        <v>34.61777835422092</v>
+        <v>34.61444473266602</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9596872604565295</v>
+        <v>0.8827338951675942</v>
       </c>
       <c r="M13" t="n">
-        <v>34.56800041198731</v>
+        <v>34.56500015258789</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.105069273314632</v>
+        <v>1.027044741184072</v>
       </c>
       <c r="P13" t="n">
-        <v>34.34423094529372</v>
+        <v>34.34307699937087</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.763818262842036</v>
+        <v>1.679876178785658</v>
       </c>
       <c r="S13" t="n">
-        <v>34.69300003051758</v>
+        <v>34.6923999786377</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7407855538460275</v>
+        <v>0.6560462534957621</v>
       </c>
       <c r="V13" t="n">
-        <v>34.82340003967285</v>
+        <v>34.82320002237956</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.363550724864222</v>
+        <v>0.2779702798810692</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.29764998435974</v>
+        <v>34.29749997138977</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.90202762835702</v>
+        <v>1.814995839565036</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1525363446463286</v>
+        <v>0.1520248499846494</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4319,13 +4317,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>7.39</v>
+        <v>7.38</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4375,82 +4373,82 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.789999961853027</v>
+        <v>3.740000009536743</v>
       </c>
       <c r="D14" t="n">
-        <v>3.789999961853027</v>
+        <v>3.740000009536743</v>
       </c>
       <c r="E14" t="n">
         <v>3.990000009536743</v>
       </c>
       <c r="F14" t="n">
-        <v>3.769999980926514</v>
+        <v>3.730000019073486</v>
       </c>
       <c r="G14" t="n">
         <v>3.980000019073486</v>
       </c>
       <c r="H14" t="n">
-        <v>11562400</v>
+        <v>18142600</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.04534006686650183</v>
+        <v>-0.05793451320301424</v>
       </c>
       <c r="J14" t="n">
-        <v>3.966666698455811</v>
+        <v>3.961111148198446</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.453783240007487</v>
+        <v>-5.582048329097411</v>
       </c>
       <c r="M14" t="n">
-        <v>4.005000019073487</v>
+        <v>4.000000023841858</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.368291041112086</v>
+        <v>-6.500000318884856</v>
       </c>
       <c r="P14" t="n">
-        <v>4.032692331534165</v>
+        <v>4.030769256445078</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-6.018122626994709</v>
+        <v>-7.213740812461629</v>
       </c>
       <c r="S14" t="n">
-        <v>4.085000023841858</v>
+        <v>4.084000024795532</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.221543702988511</v>
+        <v>-8.423114916019419</v>
       </c>
       <c r="V14" t="n">
-        <v>5.293133339881897</v>
+        <v>5.292800006866455</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-28.39779921475412</v>
+        <v>-29.33796847255202</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.507050000429153</v>
+        <v>5.506800000667572</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-31.17912563790631</v>
+        <v>-32.08396874621641</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5033702978809484</v>
+        <v>0.5138393751949578</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4602,13 +4600,13 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>5.34</v>
+        <v>5.27</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="CC14" t="n">
         <v>8</v>
@@ -4640,16 +4638,16 @@
         <v>1</v>
       </c>
       <c r="CL14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN14" t="n">
         <v>-1</v>
       </c>
       <c r="CO14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -4662,10 +4660,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53.7599983215332</v>
+        <v>53.86000061035156</v>
       </c>
       <c r="D15" t="n">
-        <v>53.7599983215332</v>
+        <v>53.86000061035156</v>
       </c>
       <c r="E15" t="n">
         <v>54.4900016784668</v>
@@ -4677,67 +4675,67 @@
         <v>54.4900016784668</v>
       </c>
       <c r="H15" t="n">
-        <v>4330900</v>
+        <v>6434400</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.009944768381484392</v>
+        <v>-0.008103105578106118</v>
       </c>
       <c r="J15" t="n">
-        <v>54.4466667175293</v>
+        <v>54.45777808295356</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.261176188357952</v>
+        <v>-1.097689795003066</v>
       </c>
       <c r="M15" t="n">
-        <v>54.42000007629395</v>
+        <v>54.43000030517578</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.212792638433397</v>
+        <v>-1.047216041940785</v>
       </c>
       <c r="P15" t="n">
-        <v>56.70538462125338</v>
+        <v>56.70923086313101</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-5.194191555868991</v>
+        <v>-5.024279485743917</v>
       </c>
       <c r="S15" t="n">
-        <v>57.75579978942871</v>
+        <v>57.75779983520508</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.918441926981815</v>
+        <v>-6.748524417437542</v>
       </c>
       <c r="V15" t="n">
-        <v>55.87926653544108</v>
+        <v>55.87993321736653</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.792584164582308</v>
+        <v>-3.614772764952431</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.35514993667603</v>
+        <v>53.35564994812012</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.758780333927774</v>
+        <v>0.9452619595522613</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2809099550686923</v>
+        <v>0.2807252609611026</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4909,7 +4907,7 @@
         <v>3510880000</v>
       </c>
       <c r="BZ15" t="n">
-        <v>12.08</v>
+        <v>12.1</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -4947,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM15" t="n">
         <v>6</v>
@@ -4956,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -4969,94 +4967,94 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.25</v>
+        <v>23.14999961853027</v>
       </c>
       <c r="D16" t="n">
-        <v>23.25</v>
+        <v>23.14999961853027</v>
       </c>
       <c r="E16" t="n">
         <v>23.5</v>
       </c>
       <c r="F16" t="n">
-        <v>23.07999992370605</v>
+        <v>23.01000022888184</v>
       </c>
       <c r="G16" t="n">
         <v>23.36000061035156</v>
       </c>
       <c r="H16" t="n">
-        <v>419700</v>
+        <v>1267100</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.004282671513319736</v>
+        <v>-0.008565343026639582</v>
       </c>
       <c r="J16" t="n">
-        <v>23.09333356221517</v>
+        <v>23.08222240871853</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6784054686724236</v>
+        <v>0.2936338131207863</v>
       </c>
       <c r="M16" t="n">
-        <v>23.05000019073486</v>
+        <v>23.04000015258789</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8676781241222213</v>
+        <v>0.4774282344352685</v>
       </c>
       <c r="P16" t="n">
-        <v>23.11346164116492</v>
+        <v>23.10961547264686</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5907308950724254</v>
+        <v>0.1747504017590203</v>
       </c>
       <c r="S16" t="n">
-        <v>23.30919998168945</v>
+        <v>23.30719997406006</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2539768921110866</v>
+        <v>-0.6744712179272593</v>
       </c>
       <c r="V16" t="n">
-        <v>21.96686663309733</v>
+        <v>21.96619996388753</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.841221637724969</v>
+        <v>5.389187281318157</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.64799995422363</v>
+        <v>20.64749995231628</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.60170501523136</v>
+        <v>12.12010980502873</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2468584196235508</v>
+        <v>0.2474091929860133</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AE16" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AG16" t="n">
         <v>23.4</v>
@@ -5200,13 +5198,13 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.68</v>
+        <v>11.63</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CC16" t="n">
         <v>2</v>
@@ -5260,10 +5258,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.19000053405762</v>
+        <v>20.29999923706055</v>
       </c>
       <c r="D17" t="n">
-        <v>20.19000053405762</v>
+        <v>20.29999923706055</v>
       </c>
       <c r="E17" t="n">
         <v>20.54000091552734</v>
@@ -5275,67 +5273,67 @@
         <v>20.25</v>
       </c>
       <c r="H17" t="n">
-        <v>2819900</v>
+        <v>4296000</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.00247031806452358</v>
+        <v>0.002964400524747113</v>
       </c>
       <c r="J17" t="n">
-        <v>19.86444452073839</v>
+        <v>19.87666659884983</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.638888079550123</v>
+        <v>2.129796946109749</v>
       </c>
       <c r="M17" t="n">
-        <v>19.79500007629395</v>
+        <v>19.80599994659424</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.995455702153372</v>
+        <v>2.494190102990763</v>
       </c>
       <c r="P17" t="n">
-        <v>18.98615389603835</v>
+        <v>18.99038461538462</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>6.340655641006168</v>
+        <v>6.896198514141607</v>
       </c>
       <c r="S17" t="n">
-        <v>19.43639995574951</v>
+        <v>19.43859992980957</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>3.877264205428034</v>
+        <v>4.431385544027789</v>
       </c>
       <c r="V17" t="n">
-        <v>17.36273330052694</v>
+        <v>17.36346662521362</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>16.28353776213838</v>
+        <v>16.91213324638044</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.61789996623993</v>
+        <v>17.61844995975494</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>14.59935958738807</v>
+        <v>15.22012029112067</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3970819907106662</v>
+        <v>0.397263260297812</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5483,13 +5481,13 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>40.38</v>
+        <v>40.6</v>
       </c>
       <c r="CA17" t="n">
         <v>1.13</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="CC17" t="n">
         <v>10</v>
@@ -5539,82 +5537,82 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.68000030517578</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="D18" t="n">
-        <v>10.68000030517578</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="E18" t="n">
         <v>11.13000011444092</v>
       </c>
       <c r="F18" t="n">
-        <v>10.52999973297119</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="G18" t="n">
         <v>11.03999996185303</v>
       </c>
       <c r="H18" t="n">
-        <v>1627300</v>
+        <v>2465300</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.04043124929363406</v>
+        <v>-0.05840076958860307</v>
       </c>
       <c r="J18" t="n">
-        <v>11.72333335876465</v>
+        <v>11.70111105177138</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.899627961264498</v>
+        <v>-10.4358595019931</v>
       </c>
       <c r="M18" t="n">
-        <v>11.79200000762939</v>
+        <v>11.77199993133545</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-9.430119587297758</v>
+        <v>-10.97519874817526</v>
       </c>
       <c r="P18" t="n">
-        <v>10.52269224020151</v>
+        <v>10.51499990316538</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.494941231610697</v>
+        <v>-0.332861257740119</v>
       </c>
       <c r="S18" t="n">
-        <v>10.11739995956421</v>
+        <v>10.11339994430542</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>5.560720618539292</v>
+        <v>3.624889749735742</v>
       </c>
       <c r="V18" t="n">
-        <v>9.082733322779337</v>
+        <v>9.081399984359741</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>17.58575227999403</v>
+        <v>15.40070429983589</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.811949987411499</v>
+        <v>8.810949983596801</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.19905719429781</v>
+        <v>18.94290129607782</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9843874651815713</v>
+        <v>0.9931628293645351</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5762,13 +5760,13 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>-0.93</v>
+        <v>-0.91</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="CC18" t="n">
         <v>1</v>
@@ -5822,13 +5820,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.4399995803833</v>
+        <v>11.47000026702881</v>
       </c>
       <c r="D19" t="n">
-        <v>11.4399995803833</v>
+        <v>11.47000026702881</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5</v>
+        <v>11.51000022888184</v>
       </c>
       <c r="F19" t="n">
         <v>11.19999980926514</v>
@@ -5837,67 +5835,67 @@
         <v>11.44999980926514</v>
       </c>
       <c r="H19" t="n">
-        <v>2318300</v>
+        <v>3496200</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.002622437740028571</v>
       </c>
       <c r="J19" t="n">
-        <v>11.29111088646783</v>
+        <v>11.29444429609511</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.318636362821607</v>
+        <v>1.55435687078822</v>
       </c>
       <c r="M19" t="n">
-        <v>11.26799983978271</v>
+        <v>11.27099990844727</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.526444293984862</v>
+        <v>1.765596310868554</v>
       </c>
       <c r="P19" t="n">
-        <v>11.33499989142785</v>
+        <v>11.33615376399114</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9263316273594357</v>
+        <v>1.180704724232221</v>
       </c>
       <c r="S19" t="n">
-        <v>11.8361999130249</v>
+        <v>11.83679992675781</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.347360939769285</v>
+        <v>-3.09880763380845</v>
       </c>
       <c r="V19" t="n">
-        <v>13.11279997507731</v>
+        <v>13.11299997965495</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-12.75700382735493</v>
+        <v>-12.52954865534418</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.96814997196197</v>
+        <v>13.9682999753952</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-18.09939323857051</v>
+        <v>-17.88549582101676</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5935522911927497</v>
+        <v>0.5937577282851618</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6049,13 +6047,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.02</v>
+        <v>6.04</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CC19" t="n">
         <v>6</v>
@@ -6109,13 +6107,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.02000045776367</v>
+        <v>11.11999988555908</v>
       </c>
       <c r="D20" t="n">
-        <v>11.02000045776367</v>
+        <v>11.11999988555908</v>
       </c>
       <c r="E20" t="n">
-        <v>11.09000015258789</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="F20" t="n">
         <v>10.93000030517578</v>
@@ -6124,88 +6122,88 @@
         <v>11.06999969482422</v>
       </c>
       <c r="H20" t="n">
-        <v>3432300</v>
+        <v>5119800</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.002714907914331599</v>
+        <v>0.006334813901895719</v>
       </c>
       <c r="J20" t="n">
-        <v>11.23555564880371</v>
+        <v>11.24666669633653</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.918509398001958</v>
+        <v>-1.126260910876932</v>
       </c>
       <c r="M20" t="n">
-        <v>11.26200008392334</v>
+        <v>11.27200002670288</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.148815701973984</v>
+        <v>-1.348475344071295</v>
       </c>
       <c r="P20" t="n">
-        <v>11.77961551226102</v>
+        <v>11.78346164409931</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-6.448555589159032</v>
+        <v>-5.630448662532554</v>
       </c>
       <c r="S20" t="n">
-        <v>12.3284001159668</v>
+        <v>12.3304001045227</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-10.61289093390623</v>
+        <v>-9.816390455323958</v>
       </c>
       <c r="V20" t="n">
-        <v>11.70120004018148</v>
+        <v>11.70186670303345</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-5.821621543761258</v>
+        <v>-4.972427324979948</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5156000328064</v>
+        <v>11.51610002994537</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-4.303723415461012</v>
+        <v>-3.439533725447944</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2199444548321578</v>
+        <v>0.2230158705171651</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="AE20" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="AJ20" t="n">
         <v>2</v>
@@ -6332,13 +6330,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
       <c r="CA20" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="CB20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CC20" t="n">
         <v>5</v>
@@ -6366,16 +6364,16 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN20" t="n">
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
@@ -6388,10 +6386,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.690000057220459</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="D21" t="n">
-        <v>4.690000057220459</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="E21" t="n">
         <v>4.75</v>
@@ -6403,67 +6401,67 @@
         <v>4.699999809265137</v>
       </c>
       <c r="H21" t="n">
-        <v>7165600</v>
+        <v>11676600</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.00212760690435887</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4.50111108356052</v>
+        <v>4.502222167121039</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>4.19649660169066</v>
+        <v>4.392889439984408</v>
       </c>
       <c r="M21" t="n">
-        <v>4.478999996185303</v>
+        <v>4.479999971389771</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.710874329423119</v>
+        <v>4.910710698221688</v>
       </c>
       <c r="P21" t="n">
-        <v>4.644230769230769</v>
+        <v>4.644615375078642</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9855084784529485</v>
+        <v>1.1924439316045</v>
       </c>
       <c r="S21" t="n">
-        <v>4.789200000762939</v>
+        <v>4.789399995803833</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.071325973579663</v>
+        <v>-1.866626020316172</v>
       </c>
       <c r="V21" t="n">
-        <v>5.331266670227051</v>
+        <v>5.331333335240682</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-12.02840999471672</v>
+        <v>-11.84194433693282</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.30975001335144</v>
+        <v>5.309800012111664</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-11.67192343467416</v>
+        <v>-11.48442881945783</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5078073974414539</v>
+        <v>0.5078294498137349</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6615,13 +6613,13 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>11.44</v>
+        <v>11.46</v>
       </c>
       <c r="CA21" t="n">
         <v>0.01</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CC21" t="n">
         <v>3</v>
@@ -6675,10 +6673,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.5</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="E22" t="n">
         <v>2.539999961853027</v>
@@ -6690,79 +6688,79 @@
         <v>2.529999971389771</v>
       </c>
       <c r="H22" t="n">
-        <v>13755000</v>
+        <v>18511300</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01185769633558176</v>
+        <v>-0.003952565445193956</v>
       </c>
       <c r="J22" t="n">
-        <v>2.513333320617676</v>
+        <v>2.515555540720622</v>
       </c>
       <c r="K22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5305034755357873</v>
+        <v>0.1766782777779136</v>
       </c>
       <c r="M22" t="n">
-        <v>2.511999988555908</v>
+        <v>2.513999986648559</v>
       </c>
       <c r="N22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4777065529688412</v>
+        <v>0.2386632581471465</v>
       </c>
       <c r="P22" t="n">
-        <v>2.662307693408086</v>
+        <v>2.663076923443721</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-6.096503939419254</v>
+        <v>-5.372617713655421</v>
       </c>
       <c r="S22" t="n">
-        <v>2.879200000762939</v>
+        <v>2.87960000038147</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-13.17032511331126</v>
+        <v>-12.4878462080608</v>
       </c>
       <c r="V22" t="n">
-        <v>3.286818051338196</v>
+        <v>3.286951384544373</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-23.93859468484574</v>
+        <v>-23.33321409084885</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.152977068424225</v>
+        <v>3.153077068328857</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-20.70985783447406</v>
+        <v>-20.07807210807812</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4284856272484651</v>
+        <v>0.4286005588144843</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
         <v>2.6</v>
@@ -6898,10 +6896,10 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>7.58</v>
+        <v>7.64</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="CB22" t="n">
         <v>0.38</v>
@@ -6939,13 +6937,13 @@
         <v>2</v>
       </c>
       <c r="CM22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN22" t="n">
         <v>0</v>
       </c>
       <c r="CO22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6958,10 +6956,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42.54000091552734</v>
+        <v>42.88999938964844</v>
       </c>
       <c r="D23" t="n">
-        <v>42.54000091552734</v>
+        <v>42.88999938964844</v>
       </c>
       <c r="E23" t="n">
         <v>43.29000091552734</v>
@@ -6973,67 +6971,67 @@
         <v>42.91999816894531</v>
       </c>
       <c r="H23" t="n">
-        <v>666300</v>
+        <v>1435000</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.01138735481455055</v>
+        <v>-0.003253529947014444</v>
       </c>
       <c r="J23" t="n">
-        <v>43.52666685316298</v>
+        <v>43.56555557250977</v>
       </c>
       <c r="K23" t="n">
         <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.266807934005488</v>
+        <v>-1.550665827586989</v>
       </c>
       <c r="M23" t="n">
-        <v>43.64600028991699</v>
+        <v>43.6810001373291</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.534022286218865</v>
+        <v>-1.810857684562689</v>
       </c>
       <c r="P23" t="n">
-        <v>46.97961543156551</v>
+        <v>46.99307691133939</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-9.45008696911383</v>
+        <v>-8.731238283103115</v>
       </c>
       <c r="S23" t="n">
-        <v>48.68039978027344</v>
+        <v>48.68739974975586</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-12.61369851616203</v>
+        <v>-11.9073936786622</v>
       </c>
       <c r="V23" t="n">
-        <v>48.83706670125326</v>
+        <v>48.83940002441406</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-12.89402949658383</v>
+        <v>-12.18155962561295</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.32805000305176</v>
+        <v>46.32979999542236</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-8.176577877279282</v>
+        <v>-7.424596277371792</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2614234056529194</v>
+        <v>0.2619138703895837</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7185,13 +7183,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.51</v>
+        <v>8.58</v>
       </c>
       <c r="CA23" t="n">
         <v>0.53</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7245,10 +7243,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.32999992370605</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="D24" t="n">
-        <v>14.32999992370605</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="E24" t="n">
         <v>14.48999977111816</v>
@@ -7260,67 +7258,67 @@
         <v>14.48999977111816</v>
       </c>
       <c r="H24" t="n">
-        <v>9487700</v>
+        <v>13910200</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.008304490459725811</v>
+        <v>-0.001384048744175859</v>
       </c>
       <c r="J24" t="n">
-        <v>14.72444428337945</v>
+        <v>14.73555543687609</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.678840383257325</v>
+        <v>-2.073590866725287</v>
       </c>
       <c r="M24" t="n">
-        <v>14.73699989318848</v>
+        <v>14.74699993133545</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.761755936976968</v>
+        <v>-2.149587222049716</v>
       </c>
       <c r="P24" t="n">
-        <v>15.29076913686899</v>
+        <v>15.29461530538706</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-6.283328226088612</v>
+        <v>-5.653067978157916</v>
       </c>
       <c r="S24" t="n">
-        <v>15.60039991378784</v>
+        <v>15.60239992141724</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.143380920376215</v>
+        <v>-7.514226158452169</v>
       </c>
       <c r="V24" t="n">
-        <v>14.16999994277954</v>
+        <v>14.17066661198934</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.129145953229476</v>
+        <v>1.830074055704815</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.52449995040894</v>
+        <v>13.52499995231628</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>5.955857711935316</v>
+        <v>6.691315017006766</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2243935974775127</v>
+        <v>0.2244712133405255</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7472,13 +7470,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>15.75</v>
+        <v>15.86</v>
       </c>
       <c r="CA24" t="n">
         <v>0.42</v>
       </c>
       <c r="CB24" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CC24" t="n">
         <v>3</v>
@@ -7528,82 +7526,82 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.869999885559082</v>
+        <v>3.839999914169312</v>
       </c>
       <c r="D25" t="n">
-        <v>3.869999885559082</v>
+        <v>3.839999914169312</v>
       </c>
       <c r="E25" t="n">
         <v>3.970000028610229</v>
       </c>
       <c r="F25" t="n">
-        <v>3.779999971389771</v>
+        <v>3.75</v>
       </c>
       <c r="G25" t="n">
         <v>3.930000066757202</v>
       </c>
       <c r="H25" t="n">
-        <v>48679800</v>
+        <v>68209700</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.01776654077278361</v>
+        <v>-0.02538074659869272</v>
       </c>
       <c r="J25" t="n">
-        <v>4.181111176808675</v>
+        <v>4.177777846654256</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-7.440875836433877</v>
+        <v>-8.085109952781512</v>
       </c>
       <c r="M25" t="n">
-        <v>4.204000043869018</v>
+        <v>4.201000046730042</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.944818145209863</v>
+        <v>-8.593195156989443</v>
       </c>
       <c r="P25" t="n">
-        <v>4.689615378013024</v>
+        <v>4.688461532959571</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-17.47724336406477</v>
+        <v>-18.09680239084038</v>
       </c>
       <c r="S25" t="n">
-        <v>4.991599998474121</v>
+        <v>4.990999999046326</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-22.46975144758996</v>
+        <v>-23.06151242430267</v>
       </c>
       <c r="V25" t="n">
-        <v>5.562600002288819</v>
+        <v>5.562400002479553</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-30.42821910677183</v>
+        <v>-30.96505263092274</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.738999991416931</v>
+        <v>5.738849991559983</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-32.56665113526864</v>
+        <v>-33.08764090685893</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4571853977147681</v>
+        <v>0.4586683344742613</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7755,13 +7753,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.61</v>
+        <v>-1.6</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7815,10 +7813,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>51.75</v>
+        <v>52.38000106811523</v>
       </c>
       <c r="D26" t="n">
-        <v>51.75</v>
+        <v>52.38000106811523</v>
       </c>
       <c r="E26" t="n">
         <v>53.47999954223633</v>
@@ -7830,67 +7828,67 @@
         <v>53.20000076293945</v>
       </c>
       <c r="H26" t="n">
-        <v>2106300</v>
+        <v>3076300</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.02247825193763064</v>
+        <v>-0.01057796700265168</v>
       </c>
       <c r="J26" t="n">
-        <v>52.2999996609158</v>
+        <v>52.36999977959527</v>
       </c>
       <c r="K26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.05162459747934</v>
+        <v>0.01909736215783379</v>
       </c>
       <c r="M26" t="n">
-        <v>52.41999969482422</v>
+        <v>52.48299980163574</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.278137540489863</v>
+        <v>-0.1962516127313623</v>
       </c>
       <c r="P26" t="n">
-        <v>53.49269206707294</v>
+        <v>53.51692287738506</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-3.257813356799903</v>
+        <v>-2.124415508482578</v>
       </c>
       <c r="S26" t="n">
-        <v>55.10439994812012</v>
+        <v>55.11699996948242</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.087354097455431</v>
+        <v>-4.965798034876042</v>
       </c>
       <c r="V26" t="n">
-        <v>48.93386660257976</v>
+        <v>48.93806660970052</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>5.754978285880602</v>
+        <v>7.033245685542576</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.54974992752075</v>
+        <v>44.55289993286133</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>16.16226821518312</v>
+        <v>17.5681070077344</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3344669362254687</v>
+        <v>0.3303156873427982</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8042,13 +8040,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.54</v>
+        <v>14.71</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8083,13 +8081,13 @@
         <v>7</v>
       </c>
       <c r="CM26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN26" t="n">
         <v>0</v>
       </c>
       <c r="CO26" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
@@ -8102,10 +8100,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.699999809265137</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="D27" t="n">
-        <v>6.699999809265137</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="E27" t="n">
         <v>6.909999847412109</v>
@@ -8117,67 +8115,67 @@
         <v>6.789999961853027</v>
       </c>
       <c r="H27" t="n">
-        <v>5342800</v>
+        <v>7163400</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.01470593803893994</v>
+        <v>-0.01029414260263606</v>
       </c>
       <c r="J27" t="n">
-        <v>6.506666713290745</v>
+        <v>6.510000069936116</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>2.971307806184126</v>
+        <v>3.379415465037452</v>
       </c>
       <c r="M27" t="n">
-        <v>6.471000051498413</v>
+        <v>6.474000072479248</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.538861937015396</v>
+        <v>3.954277783877168</v>
       </c>
       <c r="P27" t="n">
-        <v>6.451538452735314</v>
+        <v>6.452692306958712</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>3.851195468337945</v>
+        <v>4.297550525006756</v>
       </c>
       <c r="S27" t="n">
-        <v>6.460799970626831</v>
+        <v>6.461399974822998</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>3.702325404374008</v>
+        <v>4.156994541385682</v>
       </c>
       <c r="V27" t="n">
-        <v>8.090133326848347</v>
+        <v>8.09033332824707</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-17.18307302760808</v>
+        <v>-16.81430484976478</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.012949986457825</v>
+        <v>8.013099987506866</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-16.38535345174525</v>
+        <v>-16.01252911399891</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4952362322623685</v>
+        <v>0.4942025340029884</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8329,10 +8327,10 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>-4.44</v>
+        <v>-4.46</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="CB27" t="n">
         <v>0.6899999999999999</v>
@@ -8385,10 +8383,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31.65999984741211</v>
+        <v>31.8700008392334</v>
       </c>
       <c r="D28" t="n">
-        <v>31.65999984741211</v>
+        <v>31.8700008392334</v>
       </c>
       <c r="E28" t="n">
         <v>32.36000061035156</v>
@@ -8400,67 +8398,67 @@
         <v>32.16999816894531</v>
       </c>
       <c r="H28" t="n">
-        <v>1275200</v>
+        <v>1924100</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.01615911910603796</v>
+        <v>-0.009633295929227237</v>
       </c>
       <c r="J28" t="n">
-        <v>31.23888905843099</v>
+        <v>31.26222250196669</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.348033818339223</v>
+        <v>1.944130290891741</v>
       </c>
       <c r="M28" t="n">
-        <v>31.06400012969971</v>
+        <v>31.08500022888184</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.918618707262296</v>
+        <v>2.52533570716271</v>
       </c>
       <c r="P28" t="n">
-        <v>30.82423092768742</v>
+        <v>30.83230788891132</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.711402343453014</v>
+        <v>3.365602581749255</v>
       </c>
       <c r="S28" t="n">
-        <v>32.95760009765625</v>
+        <v>32.96180011749268</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.937180639364622</v>
+        <v>-3.312316907351997</v>
       </c>
       <c r="V28" t="n">
-        <v>34.75966657002767</v>
+        <v>34.76106657663981</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.917423636302424</v>
+        <v>-8.316964990220619</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.28414994239807</v>
+        <v>34.28519994735718</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-7.654120342475706</v>
+        <v>-7.044436409389969</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.4928368525211526</v>
+        <v>0.4916767335811524</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8608,13 +8606,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>9.15</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8668,13 +8666,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.5</v>
+        <v>17.6200008392334</v>
       </c>
       <c r="D29" t="n">
-        <v>17.5</v>
+        <v>17.6200008392334</v>
       </c>
       <c r="E29" t="n">
-        <v>17.65999984741211</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="F29" t="n">
         <v>17.36000061035156</v>
@@ -8683,67 +8681,67 @@
         <v>17.44000053405762</v>
       </c>
       <c r="H29" t="n">
-        <v>1920200</v>
+        <v>3325400</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00344033624455542</v>
+        <v>0.01032111809998337</v>
       </c>
       <c r="J29" t="n">
-        <v>17.59555583530002</v>
+        <v>17.60888926188151</v>
       </c>
       <c r="K29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.54306801214156</v>
+        <v>0.06310209114631893</v>
       </c>
       <c r="M29" t="n">
-        <v>17.59800033569336</v>
+        <v>17.6100004196167</v>
       </c>
       <c r="N29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.5568833607451962</v>
+        <v>0.05678829857129656</v>
       </c>
       <c r="P29" t="n">
-        <v>17.68538475036621</v>
+        <v>17.6900001672598</v>
       </c>
       <c r="Q29" t="n">
         <v>-1</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.048237021602666</v>
+        <v>-0.3956999851020818</v>
       </c>
       <c r="S29" t="n">
-        <v>18.07560012817383</v>
+        <v>18.07800014495849</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.184403970503087</v>
+        <v>-2.533462230626326</v>
       </c>
       <c r="V29" t="n">
-        <v>17.08460010528565</v>
+        <v>17.08540011088053</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>2.431428843253043</v>
+        <v>3.128991565216038</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.39090009212494</v>
+        <v>16.39150009632111</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>6.766558893296735</v>
+        <v>7.494742614728811</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1962450874531068</v>
+        <v>0.1990234637997804</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8903,13 +8901,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>11.99</v>
+        <v>12.07</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="CC29" t="n">
         <v>2</v>
@@ -8963,10 +8961,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.36000061035156</v>
+        <v>22.56999969482422</v>
       </c>
       <c r="D30" t="n">
-        <v>22.36000061035156</v>
+        <v>22.56999969482422</v>
       </c>
       <c r="E30" t="n">
         <v>22.68000030517578</v>
@@ -8978,67 +8976,67 @@
         <v>22.59000015258789</v>
       </c>
       <c r="H30" t="n">
-        <v>3707800</v>
+        <v>5092700</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.00622219509548616</v>
+        <v>0.00311109754774308</v>
       </c>
       <c r="J30" t="n">
-        <v>22.10222244262695</v>
+        <v>22.12555567423503</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.166299761907433</v>
+        <v>2.008736083888468</v>
       </c>
       <c r="M30" t="n">
-        <v>22.06600017547607</v>
+        <v>22.08700008392334</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.33236849695233</v>
+        <v>2.186804948909494</v>
       </c>
       <c r="P30" t="n">
-        <v>22.82884619786189</v>
+        <v>22.83692308572622</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.053741934422605</v>
+        <v>-1.168823794256415</v>
       </c>
       <c r="S30" t="n">
-        <v>24.96879997253418</v>
+        <v>24.97299995422363</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-10.44823685981028</v>
+        <v>-9.622393239915889</v>
       </c>
       <c r="V30" t="n">
-        <v>28.64953327178955</v>
+        <v>28.65093326568604</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.95335121787526</v>
+        <v>-21.22420765310526</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.6031499671936</v>
+        <v>28.60419996261597</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-21.82678958087701</v>
+        <v>-21.09550442130211</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.403874106536195</v>
+        <v>0.404870864272684</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9186,13 +9184,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>5.16</v>
+        <v>5.21</v>
       </c>
       <c r="CA30" t="n">
         <v>0.48</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="CC30" t="n">
         <v>8</v>
@@ -9242,10 +9240,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.35999965667725</v>
+        <v>13.39000034332275</v>
       </c>
       <c r="D31" t="n">
-        <v>13.35999965667725</v>
+        <v>13.39000034332275</v>
       </c>
       <c r="E31" t="n">
         <v>13.47999954223633</v>
@@ -9257,67 +9255,67 @@
         <v>13.43000030517578</v>
       </c>
       <c r="H31" t="n">
-        <v>1409700</v>
+        <v>2853400</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0007479602817825892</v>
+        <v>0.001495920563565178</v>
       </c>
       <c r="J31" t="n">
-        <v>13.19666650560167</v>
+        <v>13.19999991522895</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.237684918431817</v>
+        <v>1.439397191772694</v>
       </c>
       <c r="M31" t="n">
-        <v>13.14099988937378</v>
+        <v>13.14399995803833</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.666538080413174</v>
+        <v>1.871579321894168</v>
       </c>
       <c r="P31" t="n">
-        <v>13.15307694215041</v>
+        <v>13.1542308147137</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.573188657201046</v>
+        <v>1.792347511078609</v>
       </c>
       <c r="S31" t="n">
-        <v>13.50480003356934</v>
+        <v>13.50540004730225</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-1.072214150021874</v>
+        <v>-0.8544708307440559</v>
       </c>
       <c r="V31" t="n">
-        <v>15.00673334121704</v>
+        <v>15.00693334579468</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.97329876594079</v>
+        <v>-10.7745730937429</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.03249999523163</v>
+        <v>15.03264999866486</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-11.1258961522362</v>
+        <v>-10.92721280338461</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4623172214935999</v>
+        <v>0.4624166862767599</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9469,7 +9467,7 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
@@ -9525,13 +9523,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>32.33000183105469</v>
+        <v>32.77999877929688</v>
       </c>
       <c r="D32" t="n">
-        <v>32.33000183105469</v>
+        <v>32.77999877929688</v>
       </c>
       <c r="E32" t="n">
-        <v>32.5</v>
+        <v>32.81000137329102</v>
       </c>
       <c r="F32" t="n">
         <v>31.95000076293945</v>
@@ -9540,67 +9538,67 @@
         <v>32.31999969482422</v>
       </c>
       <c r="H32" t="n">
-        <v>982500</v>
+        <v>1534200</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0003094720397558426</v>
+        <v>0.01423264507475608</v>
       </c>
       <c r="J32" t="n">
-        <v>32.32111189100478</v>
+        <v>32.37111155192057</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.02750505638509842</v>
+        <v>1.26312384028112</v>
       </c>
       <c r="M32" t="n">
-        <v>32.32200088500976</v>
+        <v>32.36700057983398</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.02475386989001031</v>
+        <v>1.275985392728068</v>
       </c>
       <c r="P32" t="n">
-        <v>33.61653885474572</v>
+        <v>33.63384642967811</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.827095434333833</v>
+        <v>-2.538655970159299</v>
       </c>
       <c r="S32" t="n">
-        <v>33.87940017700195</v>
+        <v>33.8884001159668</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-4.573275612473893</v>
+        <v>-3.270739642110424</v>
       </c>
       <c r="V32" t="n">
-        <v>32.23482855478922</v>
+        <v>32.23782853444418</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>0.2952498292450906</v>
+        <v>1.681782767326969</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.33279984474182</v>
+        <v>31.33504982948303</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.182613718704152</v>
+        <v>4.611286586990823</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.1974310706391261</v>
+        <v>0.205061088293506</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9750,13 +9748,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>14.37</v>
+        <v>14.57</v>
       </c>
       <c r="CA32" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CC32" t="n">
         <v>2</v>
@@ -9784,16 +9782,16 @@
         <v>0</v>
       </c>
       <c r="CL32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN32" t="n">
         <v>1</v>
       </c>
       <c r="CO32" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
@@ -9806,13 +9804,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>73.48000335693359</v>
+        <v>73.88999938964844</v>
       </c>
       <c r="D33" t="n">
-        <v>73.48000335693359</v>
+        <v>73.88999938964844</v>
       </c>
       <c r="E33" t="n">
-        <v>73.93000030517578</v>
+        <v>74.09999847412109</v>
       </c>
       <c r="F33" t="n">
         <v>71.73000335693359</v>
@@ -9821,46 +9819,46 @@
         <v>73.70999908447266</v>
       </c>
       <c r="H33" t="n">
-        <v>1723300</v>
+        <v>2382900</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.001630368473848454</v>
+        <v>0.003940229912223536</v>
       </c>
       <c r="J33" t="n">
-        <v>72.04444376627605</v>
+        <v>72.08999888102214</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.992602781853293</v>
+        <v>2.496879645673225</v>
       </c>
       <c r="M33" t="n">
-        <v>71.88999938964844</v>
+        <v>71.93099899291992</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>2.211717875621659</v>
+        <v>2.723443889499345</v>
       </c>
       <c r="P33" t="n">
-        <v>74.94230739886945</v>
+        <v>74.95807647705078</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.951239683818317</v>
+        <v>-1.424899273835218</v>
       </c>
       <c r="S33" t="n">
-        <v>77.51659973144531</v>
+        <v>77.5247996520996</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-5.207396078383757</v>
+        <v>-4.688564535171583</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
@@ -9873,7 +9871,7 @@
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
-        <v>0.4854662947368249</v>
+        <v>0.4860382929229833</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10021,13 +10019,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>32.09</v>
+        <v>32.27</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CC33" t="n">
         <v>8</v>
@@ -10081,10 +10079,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>24.72999954223633</v>
+        <v>25.01000022888184</v>
       </c>
       <c r="D34" t="n">
-        <v>24.72999954223633</v>
+        <v>25.01000022888184</v>
       </c>
       <c r="E34" t="n">
         <v>25.15999984741211</v>
@@ -10096,67 +10094,67 @@
         <v>24.95999908447266</v>
       </c>
       <c r="H34" t="n">
-        <v>1786900</v>
+        <v>3433400</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.01080001831054689</v>
+        <v>0.0004000091552733842</v>
       </c>
       <c r="J34" t="n">
-        <v>25.00555504692925</v>
+        <v>25.03666623433431</v>
       </c>
       <c r="K34" t="n">
         <v>-1</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.10197715737873</v>
+        <v>-0.1065078121938777</v>
       </c>
       <c r="M34" t="n">
-        <v>25.00399951934815</v>
+        <v>25.0319995880127</v>
       </c>
       <c r="N34" t="n">
         <v>-1</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.095824597580061</v>
+        <v>-0.08788494524182723</v>
       </c>
       <c r="P34" t="n">
-        <v>26.10153821798471</v>
+        <v>26.11230747516339</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-5.254627770570841</v>
+        <v>-4.221408802458405</v>
       </c>
       <c r="S34" t="n">
-        <v>25.89539989471436</v>
+        <v>25.90099990844726</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-4.500414580258724</v>
+        <v>-3.440020395794995</v>
       </c>
       <c r="V34" t="n">
-        <v>22.09006666819255</v>
+        <v>22.09193333943685</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>11.95076915655044</v>
+        <v>13.20874386415006</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.46675002098084</v>
+        <v>20.46815002441406</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>20.83012455267767</v>
+        <v>22.18984226249237</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2558747568135373</v>
+        <v>0.2550142273367397</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10308,13 +10306,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>36.91</v>
+        <v>37.33</v>
       </c>
       <c r="CA34" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CC34" t="n">
         <v>10</v>
@@ -10342,16 +10340,16 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
+        <v>8</v>
+      </c>
+      <c r="CM34" t="n">
         <v>7</v>
       </c>
-      <c r="CM34" t="n">
-        <v>6</v>
-      </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35">
@@ -10364,10 +10362,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47.79999923706055</v>
+        <v>48.06000137329102</v>
       </c>
       <c r="D35" t="n">
-        <v>47.79999923706055</v>
+        <v>48.06000137329102</v>
       </c>
       <c r="E35" t="n">
         <v>48.52999877929688</v>
@@ -10379,67 +10377,67 @@
         <v>48.25</v>
       </c>
       <c r="H35" t="n">
-        <v>465200</v>
+        <v>939700</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0123967411136866</v>
+        <v>-0.007024796319605398</v>
       </c>
       <c r="J35" t="n">
-        <v>48.28666729397244</v>
+        <v>48.31555642022027</v>
       </c>
       <c r="K35" t="n">
         <v>-1</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.007872533320695</v>
+        <v>-0.5289291190327714</v>
       </c>
       <c r="M35" t="n">
-        <v>48.28500061035156</v>
+        <v>48.31100082397461</v>
       </c>
       <c r="N35" t="n">
         <v>-1</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.004455560029621</v>
+        <v>-0.5195492670460966</v>
       </c>
       <c r="P35" t="n">
-        <v>50.76346177321214</v>
+        <v>50.77346185537485</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-5.837786535108632</v>
+        <v>-5.344249501467836</v>
       </c>
       <c r="S35" t="n">
-        <v>52.20779998779297</v>
+        <v>52.21300003051758</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-8.442801174849421</v>
+        <v>-7.953955250223521</v>
       </c>
       <c r="V35" t="n">
-        <v>50.45257560729981</v>
+        <v>50.45430895487468</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-5.257563837544634</v>
+        <v>-4.745496729972224</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.92561336517334</v>
+        <v>48.92691337585449</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-2.300664316073834</v>
+        <v>-1.771850997229056</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2423818028623775</v>
+        <v>0.2417258199610943</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10591,7 +10589,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.65</v>
+        <v>12.71</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
@@ -10625,7 +10623,7 @@
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM35" t="n">
         <v>6</v>
@@ -10634,7 +10632,7 @@
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
@@ -10647,13 +10645,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37.9900016784668</v>
+        <v>38.29999923706055</v>
       </c>
       <c r="D36" t="n">
-        <v>37.9900016784668</v>
+        <v>38.29999923706055</v>
       </c>
       <c r="E36" t="n">
-        <v>38.31000137329102</v>
+        <v>38.33000183105469</v>
       </c>
       <c r="F36" t="n">
         <v>37.65000152587891</v>
@@ -10662,67 +10660,67 @@
         <v>38.29000091552734</v>
       </c>
       <c r="H36" t="n">
-        <v>2028600</v>
+        <v>4234100</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.005497358122473983</v>
+        <v>0.002617761050363931</v>
       </c>
       <c r="J36" t="n">
-        <v>38.16222212049696</v>
+        <v>38.19666629367404</v>
       </c>
       <c r="K36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.4512851518089843</v>
+        <v>0.2705286963842141</v>
       </c>
       <c r="M36" t="n">
-        <v>38.20699996948242</v>
+        <v>38.23799972534179</v>
       </c>
       <c r="N36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.5679542785064352</v>
+        <v>0.1621410956746866</v>
       </c>
       <c r="P36" t="n">
-        <v>40.4761538872352</v>
+        <v>40.48807687025804</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-6.142263950509512</v>
+        <v>-5.404251825072049</v>
       </c>
       <c r="S36" t="n">
-        <v>41.33319999694825</v>
+        <v>41.33939994812012</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-8.088409120823664</v>
+        <v>-7.352309696981428</v>
       </c>
       <c r="V36" t="n">
-        <v>40.065</v>
+        <v>40.06706665039062</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-5.179079799159368</v>
+        <v>-4.41027397575372</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.06930002212525</v>
+        <v>39.07085000991821</v>
       </c>
       <c r="Z36" t="n">
         <v>-1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-2.762522858221764</v>
+        <v>-1.972956238889048</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2523347057464668</v>
+        <v>0.2535022477522542</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10874,13 +10872,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>30.89</v>
+        <v>31.14</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CC36" t="n">
         <v>8</v>
@@ -10895,7 +10893,7 @@
         <v>2</v>
       </c>
       <c r="CG36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CH36" t="n">
         <v>5</v>
@@ -10930,82 +10928,82 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15.40999984741211</v>
+        <v>15.44999980926514</v>
       </c>
       <c r="D37" t="n">
-        <v>15.40999984741211</v>
+        <v>15.44999980926514</v>
       </c>
       <c r="E37" t="n">
         <v>15.76000022888184</v>
       </c>
       <c r="F37" t="n">
-        <v>15.3100004196167</v>
+        <v>15.22999954223633</v>
       </c>
       <c r="G37" t="n">
         <v>15.69999980926514</v>
       </c>
       <c r="H37" t="n">
-        <v>799200</v>
+        <v>1358100</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.02096568796090981</v>
+        <v>-0.01842439428653342</v>
       </c>
       <c r="J37" t="n">
-        <v>15.73333305782742</v>
+        <v>15.73777749803331</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-2.055084000490601</v>
+        <v>-1.828578964241536</v>
       </c>
       <c r="M37" t="n">
-        <v>15.72199974060059</v>
+        <v>15.72599973678589</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.984479699377973</v>
+        <v>-1.755054890883279</v>
       </c>
       <c r="P37" t="n">
-        <v>16.00576910605798</v>
+        <v>16.00730756612925</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-3.722215750446977</v>
+        <v>-3.48158336161009</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06739994049072</v>
+        <v>16.06819993972778</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-4.091515089643908</v>
+        <v>-3.847351494140792</v>
       </c>
       <c r="V37" t="n">
-        <v>15.85440003077189</v>
+        <v>15.85466669718424</v>
       </c>
       <c r="W37" t="n">
         <v>-1</v>
       </c>
       <c r="X37" t="n">
-        <v>-2.803008518122689</v>
+        <v>-2.552351907788612</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.70660000324249</v>
+        <v>15.70680000305176</v>
       </c>
       <c r="Z37" t="n">
         <v>-1</v>
       </c>
       <c r="AA37" t="n">
-        <v>-1.888379125776123</v>
+        <v>-1.634961887441908</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2474401427533524</v>
+        <v>0.2459641246792642</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11153,7 +11151,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>13.28</v>
+        <v>13.32</v>
       </c>
       <c r="CA37" t="n">
         <v>0.38</v>
@@ -11182,16 +11180,12 @@
       <c r="CI37" t="n">
         <v>28</v>
       </c>
-      <c r="CJ37" t="inlineStr">
-        <is>
-          <t>melhor</t>
-        </is>
-      </c>
+      <c r="CJ37" t="inlineStr"/>
       <c r="CK37" t="n">
         <v>0</v>
       </c>
       <c r="CL37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM37" t="n">
         <v>5</v>
@@ -11200,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -11213,82 +11207,82 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23.13999938964844</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="D38" t="n">
-        <v>23.13999938964844</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="E38" t="n">
         <v>23.47999954223633</v>
       </c>
       <c r="F38" t="n">
-        <v>22.95999908447266</v>
+        <v>22.84000015258789</v>
       </c>
       <c r="G38" t="n">
         <v>23.47999954223633</v>
       </c>
       <c r="H38" t="n">
-        <v>7777100</v>
+        <v>11935400</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.01531917490857715</v>
+        <v>-0.02297876236286567</v>
       </c>
       <c r="J38" t="n">
-        <v>23.57444445292155</v>
+        <v>23.55444441901313</v>
       </c>
       <c r="K38" t="n">
         <v>-1</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.842864480394035</v>
+        <v>-2.523707729912059</v>
       </c>
       <c r="M38" t="n">
-        <v>23.54300003051758</v>
+        <v>23.525</v>
       </c>
       <c r="N38" t="n">
         <v>-1</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.711764177661098</v>
+        <v>-2.40170421053068</v>
       </c>
       <c r="P38" t="n">
-        <v>23.24269236051119</v>
+        <v>23.23576927185059</v>
       </c>
       <c r="Q38" t="n">
         <v>-1</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.4418290672608475</v>
+        <v>-1.186834763900056</v>
       </c>
       <c r="S38" t="n">
-        <v>21.55840007781983</v>
+        <v>21.55480007171631</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>7.336348273153287</v>
+        <v>6.519192978274092</v>
       </c>
       <c r="V38" t="n">
-        <v>20.68833334604899</v>
+        <v>20.68713334401449</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>11.85047631721218</v>
+        <v>10.98685691565762</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.74025003433228</v>
+        <v>19.7393500328064</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>17.2224229652781</v>
+        <v>16.31588196325415</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.26101211887946</v>
+        <v>0.2663485207639401</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11438,13 +11432,13 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>27.88</v>
+        <v>27.66</v>
       </c>
       <c r="CA38" t="n">
         <v>0.18</v>
       </c>
       <c r="CB38" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="CC38" t="n">
         <v>1</v>
@@ -11475,13 +11469,13 @@
         <v>10</v>
       </c>
       <c r="CM38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN38" t="n">
         <v>0</v>
       </c>
       <c r="CO38" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
@@ -11494,82 +11488,82 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9.970000267028809</v>
+        <v>9.930000305175781</v>
       </c>
       <c r="D39" t="n">
-        <v>9.970000267028809</v>
+        <v>9.930000305175781</v>
       </c>
       <c r="E39" t="n">
         <v>10.28999996185303</v>
       </c>
       <c r="F39" t="n">
-        <v>9.970000267028809</v>
+        <v>9.909999847412109</v>
       </c>
       <c r="G39" t="n">
         <v>10.28999996185303</v>
       </c>
       <c r="H39" t="n">
-        <v>4241500</v>
+        <v>6786200</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.02446183889119224</v>
+        <v>-0.02837572938120259</v>
       </c>
       <c r="J39" t="n">
-        <v>10.22888893551297</v>
+        <v>10.22444449530708</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.530955904559097</v>
+        <v>-2.879806235599805</v>
       </c>
       <c r="M39" t="n">
-        <v>10.2210000038147</v>
+        <v>10.21700000762939</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.455725826163886</v>
+        <v>-2.809040836246457</v>
       </c>
       <c r="P39" t="n">
-        <v>10.11730773632343</v>
+        <v>10.11576927625216</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.455994748145827</v>
+        <v>-1.836429499360867</v>
       </c>
       <c r="S39" t="n">
-        <v>9.482400007247925</v>
+        <v>9.481600008010865</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>5.142160839114396</v>
+        <v>4.729162765631004</v>
       </c>
       <c r="V39" t="n">
-        <v>9.104792416890461</v>
+        <v>9.104525750478109</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>9.502774039452945</v>
+        <v>9.066639793449143</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.626539161205292</v>
+        <v>8.626339161396027</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>15.57358148752448</v>
+        <v>15.11256535812787</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.2702097742809853</v>
+        <v>0.2737197776891691</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11725,7 +11719,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.19</v>
+        <v>23.09</v>
       </c>
       <c r="CA39" t="n">
         <v>0.62</v>
@@ -11785,96 +11779,94 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.05000019073486</v>
+        <v>11.89000034332275</v>
       </c>
       <c r="D40" t="n">
-        <v>12.05000019073486</v>
+        <v>11.89000034332275</v>
       </c>
       <c r="E40" t="n">
         <v>12.52999973297119</v>
       </c>
       <c r="F40" t="n">
-        <v>11.88000011444092</v>
+        <v>11.84000015258789</v>
       </c>
       <c r="G40" t="n">
         <v>12.5</v>
       </c>
       <c r="H40" t="n">
-        <v>4635000</v>
+        <v>6420800</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.03445507750590926</v>
+        <v>-0.04727557857008147</v>
       </c>
       <c r="J40" t="n">
-        <v>12.47777779897054</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="K40" t="n">
         <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.428315643439097</v>
+        <v>-4.574636381052436</v>
       </c>
       <c r="M40" t="n">
-        <v>12.51300001144409</v>
+        <v>12.49700002670288</v>
       </c>
       <c r="N40" t="n">
         <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.700150405864141</v>
+        <v>-4.8571631758272</v>
       </c>
       <c r="P40" t="n">
-        <v>12.42384617145245</v>
+        <v>12.41769233116737</v>
       </c>
       <c r="Q40" t="n">
         <v>-1</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.009100205833286</v>
+        <v>-4.249517331977628</v>
       </c>
       <c r="S40" t="n">
-        <v>11.69919998168945</v>
+        <v>11.69599998474121</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>2.998497415160448</v>
+        <v>1.658689798517768</v>
       </c>
       <c r="V40" t="n">
-        <v>14.94786666234334</v>
+        <v>14.94679999669393</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-19.38648863458745</v>
+        <v>-20.45119794235092</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.60534997463226</v>
+        <v>20.6045499753952</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-41.52004112732904</v>
+        <v>-42.29429733956274</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6895829146076271</v>
+        <v>0.6960072680027475</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AD40" t="n">
+        <v>7</v>
       </c>
       <c r="AE40" t="n">
-        <v>7</v>
+        <v>11.6</v>
       </c>
       <c r="AF40" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="AG40" t="n">
         <v>12.6</v>
@@ -12010,13 +12002,13 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-14.18</v>
+        <v>-13.99</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="CC40" t="n">
         <v>9</v>
@@ -12048,16 +12040,16 @@
         <v>0</v>
       </c>
       <c r="CL40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CM40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN40" t="n">
         <v>-1</v>
       </c>
       <c r="CO40" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41">
@@ -12070,10 +12062,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21.89999961853027</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="D41" t="n">
-        <v>21.89999961853027</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="E41" t="n">
         <v>22.46999931335449</v>
@@ -12085,88 +12077,88 @@
         <v>22.35000038146973</v>
       </c>
       <c r="H41" t="n">
-        <v>1059100</v>
+        <v>1721400</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.02275770782482756</v>
+        <v>-0.01651043883998482</v>
       </c>
       <c r="J41" t="n">
-        <v>22.45666652255588</v>
+        <v>22.47222222222222</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.478849224868178</v>
+        <v>-1.923358101485241</v>
       </c>
       <c r="M41" t="n">
-        <v>22.49099979400635</v>
+        <v>22.50499992370606</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-2.627718558041034</v>
+        <v>-2.066203109331702</v>
       </c>
       <c r="P41" t="n">
-        <v>22.76269230475793</v>
+        <v>22.76807697002704</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-3.789941342076354</v>
+        <v>-3.197793364183422</v>
       </c>
       <c r="S41" t="n">
-        <v>22.89599998474121</v>
+        <v>22.89880001068115</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-4.350106424155789</v>
+        <v>-3.750410915651573</v>
       </c>
       <c r="V41" t="n">
-        <v>23.66700003306071</v>
+        <v>23.66793337504069</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-7.466093767955771</v>
+        <v>-6.878219714908029</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.49584998130798</v>
+        <v>23.49654998779297</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-6.792052060458685</v>
+        <v>-6.198991226466593</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3031314220471597</v>
+        <v>0.2999613122900693</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>16.8</v>
+        <v>19.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>19.5</v>
+        <v>20.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>20.3</v>
+        <v>22</v>
       </c>
       <c r="AG41" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AI41" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AJ41" t="n">
         <v>2</v>
@@ -12293,13 +12285,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>9.16</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="CA41" t="n">
         <v>0.4</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CC41" t="n">
         <v>4</v>
@@ -12327,7 +12319,7 @@
         <v>0</v>
       </c>
       <c r="CL41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM41" t="n">
         <v>4</v>
@@ -12336,7 +12328,7 @@
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -12349,10 +12341,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>25.8700008392334</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="D42" t="n">
-        <v>25.8700008392334</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="E42" t="n">
         <v>26.29999923706055</v>
@@ -12364,67 +12356,67 @@
         <v>26.29999923706055</v>
       </c>
       <c r="H42" t="n">
-        <v>360500</v>
+        <v>732700</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.01221839206944997</v>
+        <v>-0.01298205978063083</v>
       </c>
       <c r="J42" t="n">
-        <v>26.22777769300673</v>
+        <v>26.22555541992188</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.364114253068138</v>
+        <v>-1.432019388870077</v>
       </c>
       <c r="M42" t="n">
-        <v>26.23499984741211</v>
+        <v>26.23299980163574</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.391267430156721</v>
+        <v>-1.459990939130545</v>
       </c>
       <c r="P42" t="n">
-        <v>27.07269213749812</v>
+        <v>27.0719228891226</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.442451796653383</v>
+        <v>-4.513615499931238</v>
       </c>
       <c r="S42" t="n">
-        <v>27.65419986724854</v>
+        <v>27.65379985809326</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-6.451819385771501</v>
+        <v>-6.522790668478887</v>
       </c>
       <c r="V42" t="n">
-        <v>26.98219989776611</v>
+        <v>26.98206656138102</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-4.121973236973882</v>
+        <v>-4.195624443131432</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.04959990501404</v>
+        <v>26.04949990272522</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.6894503809483459</v>
+        <v>-0.7658477974643277</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.283898702174971</v>
+        <v>0.2840751862217111</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12576,7 +12568,7 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
       <c r="CA42" t="n">
         <v>0.04</v>
@@ -12613,13 +12605,13 @@
         <v>6</v>
       </c>
       <c r="CM42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN42" t="n">
         <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -12632,10 +12624,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>26.70999908447266</v>
+        <v>26.81999969482422</v>
       </c>
       <c r="D43" t="n">
-        <v>26.70999908447266</v>
+        <v>26.81999969482422</v>
       </c>
       <c r="E43" t="n">
         <v>27.23999977111816</v>
@@ -12647,67 +12639,67 @@
         <v>27.07999992370605</v>
       </c>
       <c r="H43" t="n">
-        <v>1079700</v>
+        <v>2387400</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01402735570228242</v>
+        <v>-0.009966794250382383</v>
       </c>
       <c r="J43" t="n">
-        <v>27.80555555555556</v>
+        <v>27.81777784559462</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-3.940063232665778</v>
+        <v>-3.586836289759265</v>
       </c>
       <c r="M43" t="n">
-        <v>27.85900001525879</v>
+        <v>27.87000007629394</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-4.124343767388666</v>
+        <v>-3.767493285236299</v>
       </c>
       <c r="P43" t="n">
-        <v>28.84884614210862</v>
+        <v>28.85307693481445</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-7.413977831557163</v>
+        <v>-7.046309981370133</v>
       </c>
       <c r="S43" t="n">
-        <v>29.16080001831055</v>
+        <v>29.16300003051758</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-8.404436545976075</v>
+        <v>-8.034154007617637</v>
       </c>
       <c r="V43" t="n">
-        <v>27.99146662394206</v>
+        <v>27.9921999613444</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-4.578065010617618</v>
+        <v>-4.187596073688107</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.83</v>
+        <v>26.83055000305176</v>
       </c>
       <c r="Z43" t="n">
         <v>-1</v>
       </c>
       <c r="AA43" t="n">
-        <v>-0.4472639415853226</v>
+        <v>-0.03932199759729026</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2427613953533033</v>
+        <v>0.2418278398031297</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12859,7 +12851,7 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="CA43" t="n">
         <v>0.85</v>
@@ -12893,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="CL43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM43" t="n">
         <v>3</v>
@@ -12902,7 +12894,7 @@
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -12915,10 +12907,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12.90999984741211</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="D44" t="n">
-        <v>12.90999984741211</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="E44" t="n">
         <v>13.02000045776367</v>
@@ -12930,67 +12922,67 @@
         <v>12.94999980926514</v>
       </c>
       <c r="H44" t="n">
-        <v>10776800</v>
+        <v>18619500</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.004626092396406989</v>
+        <v>-0.0007710276542751693</v>
       </c>
       <c r="J44" t="n">
-        <v>12.95222208234999</v>
+        <v>12.95777765909831</v>
       </c>
       <c r="K44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.325984488757461</v>
+        <v>0.01715092747486304</v>
       </c>
       <c r="M44" t="n">
-        <v>12.94099988937378</v>
+        <v>12.94599990844727</v>
       </c>
       <c r="N44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.2395490474204029</v>
+        <v>0.1081425135077533</v>
       </c>
       <c r="P44" t="n">
-        <v>13.32269232089703</v>
+        <v>13.32461540515606</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-3.097665723598527</v>
+        <v>-2.736404435868368</v>
       </c>
       <c r="S44" t="n">
-        <v>13.68680000305176</v>
+        <v>13.68780000686646</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-5.675542533436921</v>
+        <v>-5.317143502640185</v>
       </c>
       <c r="V44" t="n">
-        <v>12.92834625879924</v>
+        <v>12.92867959340413</v>
       </c>
       <c r="W44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.1419084159711416</v>
+        <v>0.2422555568537553</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.41694584846497</v>
+        <v>12.41719584941864</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.970815407945882</v>
+        <v>4.371391055684656</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2281066192057976</v>
+        <v>0.2284187248162591</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13142,7 +13134,7 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
@@ -13198,10 +13190,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39.84999847412109</v>
+        <v>39.97999954223633</v>
       </c>
       <c r="D45" t="n">
-        <v>39.84999847412109</v>
+        <v>39.97999954223633</v>
       </c>
       <c r="E45" t="n">
         <v>40.15999984741211</v>
@@ -13213,67 +13205,67 @@
         <v>39.86999893188477</v>
       </c>
       <c r="H45" t="n">
-        <v>26041600</v>
+        <v>45062300</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.003750038146972612</v>
+        <v>-0.0005000114440918413</v>
       </c>
       <c r="J45" t="n">
-        <v>39.83888838026259</v>
+        <v>39.8533329433865</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.02788755989489317</v>
+        <v>0.3178318837969185</v>
       </c>
       <c r="M45" t="n">
-        <v>39.8169994354248</v>
+        <v>39.82999954223633</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.08287675908328274</v>
+        <v>0.3766005566757196</v>
       </c>
       <c r="P45" t="n">
-        <v>41.13423054034893</v>
+        <v>41.13923058143029</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-3.122051997467467</v>
+        <v>-2.817823821229227</v>
       </c>
       <c r="S45" t="n">
-        <v>42.56499977111817</v>
+        <v>42.56759979248047</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-6.378483053203952</v>
+        <v>-6.078802335247572</v>
       </c>
       <c r="V45" t="n">
-        <v>41.8772683207194</v>
+        <v>41.87813499450684</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-4.840979194422016</v>
+        <v>-4.532521451873365</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.59372785568237</v>
+        <v>40.59437786102295</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-1.832128806216973</v>
+        <v>-1.513456668531731</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2294630930540686</v>
+        <v>0.2298607165344155</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13445,13 +13437,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.470000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CC45" t="n">
         <v>10</v>
@@ -13501,10 +13493,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.68000030517578</v>
+        <v>16.69000053405762</v>
       </c>
       <c r="D46" t="n">
-        <v>16.68000030517578</v>
+        <v>16.69000053405762</v>
       </c>
       <c r="E46" t="n">
         <v>16.79999923706055</v>
@@ -13516,67 +13508,67 @@
         <v>16.79999923706055</v>
       </c>
       <c r="H46" t="n">
-        <v>1196700</v>
+        <v>2529900</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0005998937514137825</v>
+        <v>0.001199787502827565</v>
       </c>
       <c r="J46" t="n">
-        <v>16.54222234090169</v>
+        <v>16.54333347744412</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8328866668260467</v>
+        <v>0.8865628974563725</v>
       </c>
       <c r="M46" t="n">
-        <v>16.51800003051758</v>
+        <v>16.51900005340576</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9807499355787834</v>
+        <v>1.035174526902431</v>
       </c>
       <c r="P46" t="n">
-        <v>16.99846164996807</v>
+        <v>16.99884627415584</v>
       </c>
       <c r="Q46" t="n">
         <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.873471560839104</v>
+        <v>-1.816862951268486</v>
       </c>
       <c r="S46" t="n">
-        <v>17.98200004577637</v>
+        <v>17.982200050354</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-7.240572446258006</v>
+        <v>-7.185992329514468</v>
       </c>
       <c r="V46" t="n">
-        <v>18.50036356608073</v>
+        <v>18.50043023427327</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.83960804014939</v>
+        <v>-9.785878908165692</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.36462892532349</v>
+        <v>18.3646789264679</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-9.173224392379229</v>
+        <v>-9.119018084202205</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.172635343645703</v>
+        <v>0.1727996003822144</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13732,7 +13724,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>27.8</v>
+        <v>27.82</v>
       </c>
       <c r="CA46" t="n">
         <v>0.24</v>
@@ -13792,10 +13784,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.01000022888184</v>
+        <v>15.03999996185303</v>
       </c>
       <c r="D47" t="n">
-        <v>15.01000022888184</v>
+        <v>15.03999996185303</v>
       </c>
       <c r="E47" t="n">
         <v>15.10000038146973</v>
@@ -13807,67 +13799,67 @@
         <v>15.02000045776367</v>
       </c>
       <c r="H47" t="n">
-        <v>2962300</v>
+        <v>4116000</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0006666819254557144</v>
+        <v>0.002666664123535112</v>
       </c>
       <c r="J47" t="n">
-        <v>14.84333335028754</v>
+        <v>14.84666665395101</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1.122839962299055</v>
+        <v>1.302200099242934</v>
       </c>
       <c r="M47" t="n">
-        <v>14.73600006103516</v>
+        <v>14.73900003433227</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>1.859393096578422</v>
+        <v>2.0422004669219</v>
       </c>
       <c r="P47" t="n">
-        <v>14.24423085726225</v>
+        <v>14.24538469314575</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>5.375996635361837</v>
+        <v>5.578054126468126</v>
       </c>
       <c r="S47" t="n">
-        <v>14.70300004959106</v>
+        <v>14.70360004425049</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>2.088010462186658</v>
+        <v>2.287874510937078</v>
       </c>
       <c r="V47" t="n">
-        <v>14.68566670099894</v>
+        <v>14.68586669921875</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>2.208503941198886</v>
+        <v>2.411388240730231</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.91870002269745</v>
+        <v>14.9188500213623</v>
       </c>
       <c r="Z47" t="n">
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.6119849989977834</v>
+        <v>0.812059510734728</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4695993294616521</v>
+        <v>0.4696917828807515</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -14015,7 +14007,7 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>10.14</v>
+        <v>10.16</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
@@ -14049,16 +14041,16 @@
         <v>1</v>
       </c>
       <c r="CL47" t="n">
+        <v>10</v>
+      </c>
+      <c r="CM47" t="n">
         <v>9</v>
       </c>
-      <c r="CM47" t="n">
-        <v>10</v>
-      </c>
       <c r="CN47" t="n">
         <v>0</v>
       </c>
       <c r="CO47" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
@@ -14071,82 +14063,82 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.85999965667725</v>
+        <v>15.82999992370605</v>
       </c>
       <c r="D48" t="n">
-        <v>15.85999965667725</v>
+        <v>15.82999992370605</v>
       </c>
       <c r="E48" t="n">
         <v>16.36000061035156</v>
       </c>
       <c r="F48" t="n">
-        <v>15.78999996185303</v>
+        <v>15.68000030517578</v>
       </c>
       <c r="G48" t="n">
         <v>16.25</v>
       </c>
       <c r="H48" t="n">
-        <v>2789600</v>
+        <v>6152100</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0263966381021028</v>
+        <v>-0.02823824223256022</v>
       </c>
       <c r="J48" t="n">
-        <v>16.56777795155843</v>
+        <v>16.56444464789497</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-4.272017025762995</v>
+        <v>-4.433862648587169</v>
       </c>
       <c r="M48" t="n">
-        <v>16.59200010299683</v>
+        <v>16.58900012969971</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-4.411767368464327</v>
+        <v>-4.575322201817297</v>
       </c>
       <c r="P48" t="n">
-        <v>17.17615395325881</v>
+        <v>17.1750001173753</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-7.662683393285782</v>
+        <v>-7.831151001324073</v>
       </c>
       <c r="S48" t="n">
-        <v>18.46060010910034</v>
+        <v>18.46000011444092</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-14.08730180521652</v>
+        <v>-14.24702152995904</v>
       </c>
       <c r="V48" t="n">
-        <v>18.87620007197062</v>
+        <v>18.87600007375081</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-15.97885381482129</v>
+        <v>-16.13689414146889</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.51145004272461</v>
+        <v>19.51130004405975</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-18.71439784358266</v>
+        <v>-18.86752862208418</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.3931173530522613</v>
+        <v>0.393952949741052</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14294,13 +14286,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>58.74</v>
+        <v>58.63</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14354,82 +14346,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.079999923706055</v>
+        <v>6.090000152587891</v>
       </c>
       <c r="D49" t="n">
-        <v>6.079999923706055</v>
+        <v>6.090000152587891</v>
       </c>
       <c r="E49" t="n">
         <v>6.429999828338623</v>
       </c>
       <c r="F49" t="n">
-        <v>6.070000171661377</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="G49" t="n">
         <v>6.380000114440918</v>
       </c>
       <c r="H49" t="n">
-        <v>9075400</v>
+        <v>14455100</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.04251968267425299</v>
+        <v>-0.04094484345661142</v>
       </c>
       <c r="J49" t="n">
-        <v>6.563333299424913</v>
+        <v>6.56444443596734</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-7.364144919490968</v>
+        <v>-7.227485707395352</v>
       </c>
       <c r="M49" t="n">
-        <v>6.567999982833863</v>
+        <v>6.569000005722046</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-7.429964378855754</v>
+        <v>-7.291822997669567</v>
       </c>
       <c r="P49" t="n">
-        <v>7.319615290715144</v>
+        <v>7.319999914902907</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-16.93552622337309</v>
+        <v>-16.80327563680486</v>
       </c>
       <c r="S49" t="n">
-        <v>8.062399959564209</v>
+        <v>8.062599964141846</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-24.58821251489125</v>
+        <v>-24.46605090575037</v>
       </c>
       <c r="V49" t="n">
-        <v>8.826047407786051</v>
+        <v>8.826114075978596</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-31.11299268183766</v>
+        <v>-31.00021028322522</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.717964012622833</v>
+        <v>8.718014013767242</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-30.25894675749111</v>
+        <v>-30.14463910047937</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4385694345076454</v>
+        <v>0.4377025514603108</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14581,7 +14573,7 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>33.78</v>
+        <v>33.83</v>
       </c>
       <c r="CA49" t="n">
         <v>0.73</v>
@@ -14641,13 +14633,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13.9399995803833</v>
+        <v>14.09000015258789</v>
       </c>
       <c r="D50" t="n">
-        <v>13.9399995803833</v>
+        <v>14.09000015258789</v>
       </c>
       <c r="E50" t="n">
-        <v>14.13000011444092</v>
+        <v>14.14000034332275</v>
       </c>
       <c r="F50" t="n">
         <v>13.76000022888184</v>
@@ -14656,67 +14648,67 @@
         <v>14.09000015258789</v>
       </c>
       <c r="H50" t="n">
-        <v>6931300</v>
+        <v>8880600</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.01344660527379871</v>
+        <v>-0.002830853611398565</v>
       </c>
       <c r="J50" t="n">
-        <v>14.55888885921902</v>
+        <v>14.57555558946398</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-4.250937587478218</v>
+        <v>-3.331299681139234</v>
       </c>
       <c r="M50" t="n">
-        <v>14.57699995040894</v>
+        <v>14.59200000762939</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-4.369900337468035</v>
+        <v>-3.440240232860707</v>
       </c>
       <c r="P50" t="n">
-        <v>15.22307685705332</v>
+        <v>15.22884610983042</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-8.428501601340379</v>
+        <v>-7.478215677203445</v>
       </c>
       <c r="S50" t="n">
-        <v>15.69260004043579</v>
+        <v>15.69560005187988</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-11.16832427728031</v>
+        <v>-10.22961781636177</v>
       </c>
       <c r="V50" t="n">
-        <v>15.83906668980916</v>
+        <v>15.84006669362386</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-11.98976648445909</v>
+        <v>-11.04835336167131</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.43975000858307</v>
+        <v>15.44050001144409</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-9.713566782921005</v>
+        <v>-8.746477496552874</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.2993393226087039</v>
+        <v>0.2990976192368708</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14864,13 +14856,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.4</v>
+        <v>8.49</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="CB50" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CC50" t="n">
         <v>5</v>
@@ -14939,7 +14931,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="H51" t="n">
-        <v>3078900</v>
+        <v>4605100</v>
       </c>
       <c r="I51" t="n">
         <v>-0.02680064539951565</v>
@@ -15211,10 +15203,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>29.45999908447266</v>
+        <v>29.54000091552734</v>
       </c>
       <c r="D52" t="n">
-        <v>29.45999908447266</v>
+        <v>29.54000091552734</v>
       </c>
       <c r="E52" t="n">
         <v>30.04000091552734</v>
@@ -15226,67 +15218,67 @@
         <v>29.85000038146973</v>
       </c>
       <c r="H52" t="n">
-        <v>1041500</v>
+        <v>1495600</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.01537436466070585</v>
+        <v>-0.01270050667772826</v>
       </c>
       <c r="J52" t="n">
-        <v>29.83444446987576</v>
+        <v>29.84333356221517</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.255077451772851</v>
+        <v>-1.01641676877504</v>
       </c>
       <c r="M52" t="n">
-        <v>29.82600002288818</v>
+        <v>29.83400020599365</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.227120425583928</v>
+        <v>-0.9854504539664296</v>
       </c>
       <c r="P52" t="n">
-        <v>30.78461522322435</v>
+        <v>30.78769221672645</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-4.30285104798835</v>
+        <v>-4.052565201757</v>
       </c>
       <c r="S52" t="n">
-        <v>31.56959995269775</v>
+        <v>31.57119998931885</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-6.682380744089294</v>
+        <v>-6.433708805742891</v>
       </c>
       <c r="V52" t="n">
-        <v>30.62160002390544</v>
+        <v>30.6221333694458</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-3.793403801649655</v>
+        <v>-3.533824508119312</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.88980004310608</v>
+        <v>29.89020005226135</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-1.437951936826533</v>
+        <v>-1.171618577733522</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.29476040954813</v>
+        <v>0.2940585786386757</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15438,13 +15430,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>12.38</v>
+        <v>12.41</v>
       </c>
       <c r="CA52" t="n">
         <v>0.3</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15498,10 +15490,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.899999618530273</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="D53" t="n">
-        <v>9.899999618530273</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="E53" t="n">
         <v>10.05000019073486</v>
@@ -15513,67 +15505,67 @@
         <v>9.970000267028809</v>
       </c>
       <c r="H53" t="n">
-        <v>8418200</v>
+        <v>11707100</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.01980205498867016</v>
+        <v>-0.02178220383361951</v>
       </c>
       <c r="J53" t="n">
-        <v>10.10444439782037</v>
+        <v>10.10222223069933</v>
       </c>
       <c r="K53" t="n">
         <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.023315397076097</v>
+        <v>-2.199734980914453</v>
       </c>
       <c r="M53" t="n">
-        <v>10.06899995803833</v>
+        <v>10.06700000762939</v>
       </c>
       <c r="N53" t="n">
         <v>-1</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.678422288333995</v>
+        <v>-1.857553323202108</v>
       </c>
       <c r="P53" t="n">
-        <v>10.15461532886212</v>
+        <v>10.15384611716637</v>
       </c>
       <c r="Q53" t="n">
         <v>-1</v>
       </c>
       <c r="R53" t="n">
-        <v>-2.507389025443029</v>
+        <v>-2.696968218402313</v>
       </c>
       <c r="S53" t="n">
-        <v>10.08079996109009</v>
+        <v>10.0803999710083</v>
       </c>
       <c r="T53" t="n">
         <v>-1</v>
       </c>
       <c r="U53" t="n">
-        <v>-1.793511856773953</v>
+        <v>-1.988014931389057</v>
       </c>
       <c r="V53" t="n">
-        <v>8.935866619745891</v>
+        <v>8.935733289718629</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>10.7894739235913</v>
+        <v>10.56731209523402</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.91419995546341</v>
+        <v>8.914099957942963</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>11.05875645590246</v>
+        <v>10.83564421596242</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3391591988508472</v>
+        <v>0.3401634791776192</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15725,7 +15717,7 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>-5.86</v>
+        <v>-5.85</v>
       </c>
       <c r="CA53" t="n">
         <v>0.29</v>
@@ -15763,16 +15755,16 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54">
@@ -15785,82 +15777,82 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47.15000152587891</v>
+        <v>47.13000106811523</v>
       </c>
       <c r="D54" t="n">
-        <v>47.15000152587891</v>
+        <v>47.13000106811523</v>
       </c>
       <c r="E54" t="n">
         <v>47.52000045776367</v>
       </c>
       <c r="F54" t="n">
-        <v>46.90000152587891</v>
+        <v>46.88999938964844</v>
       </c>
       <c r="G54" t="n">
         <v>47.15999984741211</v>
       </c>
       <c r="H54" t="n">
-        <v>3722500</v>
+        <v>5897000</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.008203605009209358</v>
+        <v>-0.008624312989405025</v>
       </c>
       <c r="J54" t="n">
-        <v>49.12999979654948</v>
+        <v>49.12777752346463</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-4.030120657174582</v>
+        <v>-4.066490600750682</v>
       </c>
       <c r="M54" t="n">
-        <v>49.39599990844727</v>
+        <v>49.3939998626709</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-4.546923610679392</v>
+        <v>-4.583550230494007</v>
       </c>
       <c r="P54" t="n">
-        <v>50.89307711674617</v>
+        <v>50.89230786837064</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-7.354783406554168</v>
+        <v>-7.392682623052485</v>
       </c>
       <c r="S54" t="n">
-        <v>51.71860015869141</v>
+        <v>51.71820014953613</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-8.833569777206627</v>
+        <v>-8.871536650840021</v>
       </c>
       <c r="V54" t="n">
-        <v>41.6115334447225</v>
+        <v>41.6114001083374</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>13.30993506527177</v>
+        <v>13.26223329522649</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.53970007896423</v>
+        <v>39.53960007667541</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>19.24724120748574</v>
+        <v>19.19695944501329</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3424169244017109</v>
+        <v>0.3424777314594623</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16012,13 +16004,13 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="CA54" t="n">
         <v>0.53</v>
       </c>
       <c r="CB54" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CC54" t="n">
         <v>1</v>
@@ -16068,82 +16060,82 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>42.06000137329102</v>
+        <v>42</v>
       </c>
       <c r="D55" t="n">
-        <v>42.06000137329102</v>
+        <v>42</v>
       </c>
       <c r="E55" t="n">
         <v>42.34999847412109</v>
       </c>
       <c r="F55" t="n">
-        <v>41.86000061035156</v>
+        <v>41.81999969482422</v>
       </c>
       <c r="G55" t="n">
         <v>42.20000076293945</v>
       </c>
       <c r="H55" t="n">
-        <v>24010400</v>
+        <v>31048500</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.01058567315948922</v>
+        <v>-0.01199713812444136</v>
       </c>
       <c r="J55" t="n">
-        <v>43.81666649712457</v>
+        <v>43.80999967787001</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.009125440769963</v>
+        <v>-4.131476126863122</v>
       </c>
       <c r="M55" t="n">
-        <v>44.07899971008301</v>
+        <v>44.07299957275391</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-4.580408698181397</v>
+        <v>-4.703559078913802</v>
       </c>
       <c r="P55" t="n">
-        <v>45.88307688786433</v>
+        <v>45.88076914273775</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-8.332212601863429</v>
+        <v>-8.458378565242564</v>
       </c>
       <c r="S55" t="n">
-        <v>46.79059982299805</v>
+        <v>46.78939979553223</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-10.11014705432756</v>
+        <v>-10.23607871967093</v>
       </c>
       <c r="V55" t="n">
-        <v>38.43533342997233</v>
+        <v>38.43493342081706</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>9.430561985165777</v>
+        <v>9.27558931909593</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.54885004997254</v>
+        <v>36.54855004310608</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>15.07886381044325</v>
+        <v>14.91563947260391</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.3035306022894734</v>
+        <v>0.3038467717598101</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16295,7 +16287,7 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>5.04</v>
+        <v>5.03</v>
       </c>
       <c r="CA55" t="n">
         <v>0.6</v>
@@ -16333,7 +16325,7 @@
         <v>0</v>
       </c>
       <c r="CL55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM55" t="n">
         <v>2</v>
@@ -16342,7 +16334,7 @@
         <v>0</v>
       </c>
       <c r="CO55" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
@@ -16355,10 +16347,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.110000133514404</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="D56" t="n">
-        <v>6.110000133514404</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="E56" t="n">
         <v>6.21999979019165</v>
@@ -16370,67 +16362,67 @@
         <v>6.199999809265137</v>
       </c>
       <c r="H56" t="n">
-        <v>1744800</v>
+        <v>2973700</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.01132681177485351</v>
+        <v>-0.01618121479130386</v>
       </c>
       <c r="J56" t="n">
-        <v>6.067777686648899</v>
+        <v>6.064444330003527</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.6958469648353874</v>
+        <v>0.2565048478649151</v>
       </c>
       <c r="M56" t="n">
-        <v>6.056999921798706</v>
+        <v>6.053999900817871</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.8750241439653037</v>
+        <v>0.4294685053541394</v>
       </c>
       <c r="P56" t="n">
-        <v>6.236153841018677</v>
+        <v>6.234999986795279</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.022940913908968</v>
+        <v>-2.485967336286912</v>
       </c>
       <c r="S56" t="n">
-        <v>6.30920000076294</v>
+        <v>6.308599996566772</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-3.157292005713039</v>
+        <v>-3.623626049917968</v>
       </c>
       <c r="V56" t="n">
-        <v>6.351866537729899</v>
+        <v>6.351666536331177</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-3.807800475321947</v>
+        <v>-4.277091863548002</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.828263425827027</v>
+        <v>6.828113424777984</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-10.51897455502206</v>
+        <v>-10.95637190731428</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3181290473688206</v>
+        <v>0.3194606021941033</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16582,13 +16574,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>6.11</v>
+        <v>6.08</v>
       </c>
       <c r="CA56" t="n">
         <v>0.2</v>
       </c>
       <c r="CB56" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CC56" t="n">
         <v>9</v>
@@ -16603,7 +16595,7 @@
         <v>10</v>
       </c>
       <c r="CG56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CH56" t="n">
         <v>9</v>
@@ -16623,13 +16615,13 @@
         <v>8</v>
       </c>
       <c r="CM56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57">
@@ -16642,10 +16634,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>61.75</v>
+        <v>62.09999847412109</v>
       </c>
       <c r="D57" t="n">
-        <v>61.75</v>
+        <v>62.09999847412109</v>
       </c>
       <c r="E57" t="n">
         <v>62.45999908447266</v>
@@ -16657,67 +16649,67 @@
         <v>62.27999877929688</v>
       </c>
       <c r="H57" t="n">
-        <v>2896800</v>
+        <v>4724900</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.01937432423460106</v>
+        <v>-0.01381614625562355</v>
       </c>
       <c r="J57" t="n">
-        <v>65.67888853285048</v>
+        <v>65.71777725219727</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-5.981965621853321</v>
+        <v>-5.505023038427874</v>
       </c>
       <c r="M57" t="n">
-        <v>65.99299964904785</v>
+        <v>66.02799949645996</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-6.429469294640653</v>
+        <v>-5.948992930717913</v>
       </c>
       <c r="P57" t="n">
-        <v>65.78807713435246</v>
+        <v>65.80153861412636</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-6.138007539125819</v>
+        <v>-5.625309404559443</v>
       </c>
       <c r="S57" t="n">
-        <v>65.97039993286133</v>
+        <v>65.97739990234375</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-6.397414502801962</v>
+        <v>-5.876863037891428</v>
       </c>
       <c r="V57" t="n">
-        <v>51.8617999013265</v>
+        <v>51.8641332244873</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>19.06644219345844</v>
+        <v>19.73592271431424</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.33819995880127</v>
+        <v>48.33994995117187</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>27.745758122209</v>
+        <v>28.46516915480514</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3853282150607522</v>
+        <v>0.3832914719159162</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16869,13 +16861,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>20.79</v>
+        <v>20.91</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CC57" t="n">
         <v>10</v>
@@ -16925,10 +16917,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.27999877929688</v>
+        <v>48.33000183105469</v>
       </c>
       <c r="D58" t="n">
-        <v>48.27999877929688</v>
+        <v>48.33000183105469</v>
       </c>
       <c r="E58" t="n">
         <v>48.59999847412109</v>
@@ -16940,67 +16932,67 @@
         <v>48.29000091552734</v>
       </c>
       <c r="H58" t="n">
-        <v>316500</v>
+        <v>867800</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>0.001035688753564301</v>
       </c>
       <c r="J58" t="n">
-        <v>48.7466663784451</v>
+        <v>48.75222227308485</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.9573323343287649</v>
+        <v>-0.8660537352843219</v>
       </c>
       <c r="M58" t="n">
-        <v>48.74199981689453</v>
+        <v>48.74700012207031</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.9478499842706992</v>
+        <v>-0.8554337497105318</v>
       </c>
       <c r="P58" t="n">
-        <v>49.55692335275504</v>
+        <v>49.55884654705341</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.5766825038124</v>
+        <v>-2.479566821298</v>
       </c>
       <c r="S58" t="n">
-        <v>50.26740005493164</v>
+        <v>50.2684001159668</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.953658381899515</v>
+        <v>-3.856097032012793</v>
       </c>
       <c r="V58" t="n">
-        <v>49.25660001118978</v>
+        <v>49.25693336486816</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-1.982680963913566</v>
+        <v>-1.881829562850119</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.49840000152588</v>
+        <v>49.49865001678467</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.461496174000464</v>
+        <v>-2.360969815002424</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.2835672076124666</v>
+        <v>0.2836920607937705</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17152,7 +17144,7 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>8.470000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="CA58" t="n">
         <v>-0.42</v>
@@ -17190,16 +17182,16 @@
         <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN58" t="n">
         <v>0</v>
       </c>
       <c r="CO58" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
@@ -17212,10 +17204,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18.79999923706055</v>
+        <v>18.8700008392334</v>
       </c>
       <c r="D59" t="n">
-        <v>18.79999923706055</v>
+        <v>18.8700008392334</v>
       </c>
       <c r="E59" t="n">
         <v>19.01000022888184</v>
@@ -17227,67 +17219,67 @@
         <v>18.8700008392334</v>
       </c>
       <c r="H59" t="n">
-        <v>7751100</v>
+        <v>11191100</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.007915647484946997</v>
+        <v>-0.004221631687873595</v>
       </c>
       <c r="J59" t="n">
-        <v>18.58222219679091</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1.171964461318558</v>
+        <v>1.506189802836173</v>
       </c>
       <c r="M59" t="n">
-        <v>18.63600006103515</v>
+        <v>18.64300022125244</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8800127467711681</v>
+        <v>1.217618491052647</v>
       </c>
       <c r="P59" t="n">
-        <v>20.22923080737774</v>
+        <v>20.23192317669208</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-7.065180005736773</v>
+        <v>-6.731551546358518</v>
       </c>
       <c r="S59" t="n">
-        <v>21.67940002441406</v>
+        <v>21.68080005645752</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-13.28173650613441</v>
+        <v>-12.96446261164121</v>
       </c>
       <c r="V59" t="n">
-        <v>22.86466395060221</v>
+        <v>22.86513062795003</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-17.77705861902515</v>
+        <v>-17.47258676857521</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.5766841506958</v>
+        <v>21.57703415870667</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-12.8689139361838</v>
+        <v>-12.54590088499693</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3571903717253896</v>
+        <v>0.3573533398179006</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17439,13 +17431,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>25.41</v>
+        <v>25.5</v>
       </c>
       <c r="CA59" t="n">
         <v>0.09</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17499,82 +17491,82 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.67000007629395</v>
+        <v>13.6899995803833</v>
       </c>
       <c r="D60" t="n">
-        <v>13.67000007629395</v>
+        <v>13.6899995803833</v>
       </c>
       <c r="E60" t="n">
         <v>13.90999984741211</v>
       </c>
       <c r="F60" t="n">
-        <v>13.64999961853027</v>
+        <v>13.5600004196167</v>
       </c>
       <c r="G60" t="n">
         <v>13.85999965667725</v>
       </c>
       <c r="H60" t="n">
-        <v>2531900</v>
+        <v>5243500</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01299641156808984</v>
+        <v>-0.01155240409238512</v>
       </c>
       <c r="J60" t="n">
-        <v>14.29888894822862</v>
+        <v>14.30111111534966</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.398165998852568</v>
+        <v>-4.273175210214569</v>
       </c>
       <c r="M60" t="n">
-        <v>14.35900001525879</v>
+        <v>14.36099996566772</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-4.798383858434914</v>
+        <v>-4.672379269469802</v>
       </c>
       <c r="P60" t="n">
-        <v>15.29307706539447</v>
+        <v>15.29384627709022</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-10.61314856493638</v>
+        <v>-10.4868760130631</v>
       </c>
       <c r="S60" t="n">
-        <v>15.77660009384155</v>
+        <v>15.77700008392334</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-13.35268692251334</v>
+        <v>-13.2281200002444</v>
       </c>
       <c r="V60" t="n">
-        <v>15.61420004526774</v>
+        <v>15.614333375295</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-12.45148623264265</v>
+        <v>-12.32414954042407</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.5037000131607</v>
+        <v>15.50380001068115</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-11.8274988248623</v>
+        <v>-11.69907009280471</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3139433943409303</v>
+        <v>0.3137305064227877</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17726,7 +17718,7 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>24.41</v>
+        <v>24.45</v>
       </c>
       <c r="CA60" t="n">
         <v>0.6899999999999999</v>
@@ -17786,10 +17778,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>33.75</v>
+        <v>33.88000106811523</v>
       </c>
       <c r="D61" t="n">
-        <v>33.75</v>
+        <v>33.88000106811523</v>
       </c>
       <c r="E61" t="n">
         <v>34.43000030517578</v>
@@ -17801,88 +17793,88 @@
         <v>34.29999923706055</v>
       </c>
       <c r="H61" t="n">
-        <v>3991200</v>
+        <v>7287700</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.02088776313331497</v>
+        <v>-0.01711633686376346</v>
       </c>
       <c r="J61" t="n">
-        <v>34.43111122979058</v>
+        <v>34.4455557929145</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.978185441779375</v>
+        <v>-1.641880096809465</v>
       </c>
       <c r="M61" t="n">
-        <v>34.46500015258789</v>
+        <v>34.47800025939942</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.074568836275496</v>
+        <v>-1.734436993981848</v>
       </c>
       <c r="P61" t="n">
-        <v>36.29000018193172</v>
+        <v>36.29500022301307</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-6.999173792223752</v>
+        <v>-6.653806695299563</v>
       </c>
       <c r="S61" t="n">
-        <v>37.76639991760254</v>
+        <v>37.76899993896485</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-10.63484983044555</v>
+        <v>-10.29680128447743</v>
       </c>
       <c r="V61" t="n">
-        <v>41.06526659647623</v>
+        <v>41.06613327026367</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-17.81375649733137</v>
+        <v>-17.49892582984426</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.70449996948242</v>
+        <v>40.705149974823</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-17.08533448315653</v>
+        <v>-16.7672859845235</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3755671994405315</v>
+        <v>0.3743705106673904</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="AE61" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="AF61" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="AG61" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="AH61" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="AI61" t="n">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="AJ61" t="n">
         <v>2</v>
@@ -18009,13 +18001,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>16.71</v>
+        <v>16.77</v>
       </c>
       <c r="CA61" t="n">
         <v>0.09</v>
       </c>
       <c r="CB61" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18027,16 +18019,16 @@
         <v>7</v>
       </c>
       <c r="CF61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CG61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CH61" t="n">
         <v>7</v>
       </c>
       <c r="CI61" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CJ61" t="inlineStr">
         <is>
@@ -18050,7 +18042,7 @@
         <v>3</v>
       </c>
       <c r="CM61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN61" t="n">
         <v>0</v>
@@ -18069,10 +18061,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11.3100004196167</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="D62" t="n">
-        <v>11.3100004196167</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="E62" t="n">
         <v>11.63000011444092</v>
@@ -18084,67 +18076,67 @@
         <v>11.53999996185303</v>
       </c>
       <c r="H62" t="n">
-        <v>1526300</v>
+        <v>2023100</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.02331601950502815</v>
+        <v>-0.01727114081026082</v>
       </c>
       <c r="J62" t="n">
-        <v>11.94444455040826</v>
+        <v>11.95222229427761</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-5.311625233924103</v>
+        <v>-4.787579796860542</v>
       </c>
       <c r="M62" t="n">
-        <v>11.99900007247925</v>
+        <v>12.00600004196167</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-5.742142251026646</v>
+        <v>-5.214059014932914</v>
       </c>
       <c r="P62" t="n">
-        <v>12.39807697442862</v>
+        <v>12.40076927038339</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-8.776171958410217</v>
+        <v>-8.231498656945153</v>
       </c>
       <c r="S62" t="n">
-        <v>12.96440010070801</v>
+        <v>12.96580009460449</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-12.76109706766115</v>
+        <v>-12.23063728109984</v>
       </c>
       <c r="V62" t="n">
-        <v>11.94766667683919</v>
+        <v>11.94813334147135</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-5.337161426327896</v>
+        <v>-4.754995703458343</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.14750000953674</v>
+        <v>12.14785000801086</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-6.894419339473484</v>
+        <v>-6.320870714271172</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3547592802304533</v>
+        <v>0.3525714617987601</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18296,13 +18288,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6.21</v>
+        <v>6.25</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="CB62" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="CC62" t="n">
         <v>8</v>
@@ -18333,13 +18325,13 @@
         <v>2</v>
       </c>
       <c r="CM62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN62" t="n">
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
@@ -18352,10 +18344,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>41.52000045776367</v>
+        <v>41.77000045776367</v>
       </c>
       <c r="D63" t="n">
-        <v>41.52000045776367</v>
+        <v>41.77000045776367</v>
       </c>
       <c r="E63" t="n">
         <v>42.90000152587891</v>
@@ -18367,88 +18359,88 @@
         <v>42.90000152587891</v>
       </c>
       <c r="H63" t="n">
-        <v>4267500</v>
+        <v>5693100</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.030359627424698</v>
+        <v>-0.02452123410891716</v>
       </c>
       <c r="J63" t="n">
-        <v>43.3011114332411</v>
+        <v>43.32888921101888</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-4.11331468529032</v>
+        <v>-3.597804563286088</v>
       </c>
       <c r="M63" t="n">
-        <v>43.2680004119873</v>
+        <v>43.29300041198731</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-4.039936991725068</v>
+        <v>-3.517889588918248</v>
       </c>
       <c r="P63" t="n">
-        <v>45.23115422175481</v>
+        <v>45.24076960637019</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-8.204861953768544</v>
+        <v>-7.671773002106081</v>
       </c>
       <c r="S63" t="n">
-        <v>46.52960014343262</v>
+        <v>46.53460014343262</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-10.76647912345325</v>
+        <v>-10.23883233332428</v>
       </c>
       <c r="V63" t="n">
-        <v>45.59506675720215</v>
+        <v>45.59673342386881</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-8.937515808757496</v>
+        <v>-8.392559463704776</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.44645004272461</v>
+        <v>43.44770004272461</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-4.434078234393126</v>
+        <v>-3.861423236008264</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.4971242300325304</v>
+        <v>0.495020262662431</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>40.4</v>
+        <v>40.9</v>
       </c>
       <c r="AE63" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="AF63" t="n">
-        <v>41</v>
+        <v>41.7</v>
       </c>
       <c r="AG63" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="AH63" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="AI63" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="AJ63" t="n">
         <v>3</v>
@@ -18575,13 +18567,13 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>20.76</v>
+        <v>20.89</v>
       </c>
       <c r="CA63" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CC63" t="n">
         <v>10</v>
@@ -18631,10 +18623,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.23999977111816</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="D64" t="n">
-        <v>27.23999977111816</v>
+        <v>27.47999954223633</v>
       </c>
       <c r="E64" t="n">
         <v>27.55999946594238</v>
@@ -18646,67 +18638,67 @@
         <v>27.53000068664551</v>
       </c>
       <c r="H64" t="n">
-        <v>558300</v>
+        <v>1446800</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0007347706931741804</v>
+        <v>0.0095518087964932</v>
       </c>
       <c r="J64" t="n">
-        <v>27.30888875325521</v>
+        <v>27.33555539449056</v>
       </c>
       <c r="K64" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.2522584597252481</v>
+        <v>0.528411241920045</v>
       </c>
       <c r="M64" t="n">
-        <v>27.26299991607666</v>
+        <v>27.28699989318848</v>
       </c>
       <c r="N64" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.08436395491800507</v>
+        <v>0.7072952314410711</v>
       </c>
       <c r="P64" t="n">
-        <v>28.04346150618333</v>
+        <v>28.05269226661095</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.865059061585569</v>
+        <v>-2.041489347731019</v>
       </c>
       <c r="S64" t="n">
-        <v>29.35279994964599</v>
+        <v>29.35759994506836</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-7.197951071626172</v>
+        <v>-6.395619554545498</v>
       </c>
       <c r="V64" t="n">
-        <v>31.96280000050863</v>
+        <v>31.96439999898275</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-14.77592773259948</v>
+        <v>-14.0293590897659</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.01120000839233</v>
+        <v>31.01240000724793</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-12.16076848446238</v>
+        <v>-11.39028409341437</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2521078072508575</v>
+        <v>0.2550969023070511</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18876,13 +18868,13 @@
         <v>18881600000</v>
       </c>
       <c r="BZ64" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="CA64" t="n">
         <v>0</v>
       </c>
       <c r="CB64" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CC64" t="n">
         <v>4</v>
@@ -18914,7 +18906,7 @@
         <v>0</v>
       </c>
       <c r="CL64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM64" t="n">
         <v>8</v>
@@ -18923,7 +18915,7 @@
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -18936,10 +18928,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27.57999992370605</v>
+        <v>27.95999908447266</v>
       </c>
       <c r="D65" t="n">
-        <v>27.57999992370605</v>
+        <v>27.95999908447266</v>
       </c>
       <c r="E65" t="n">
         <v>28.45000076293945</v>
@@ -18951,67 +18943,67 @@
         <v>28.1200008392334</v>
       </c>
       <c r="H65" t="n">
-        <v>8057000</v>
+        <v>12108900</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.02059658831139366</v>
+        <v>-0.007102299858777639</v>
       </c>
       <c r="J65" t="n">
-        <v>28.54888894822862</v>
+        <v>28.59111107720269</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-3.3937889011358</v>
+        <v>-2.20737134358257</v>
       </c>
       <c r="M65" t="n">
-        <v>28.61000003814697</v>
+        <v>28.64799995422363</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-3.600140206457784</v>
+        <v>-2.4015668488213</v>
       </c>
       <c r="P65" t="n">
-        <v>30.68853869804969</v>
+        <v>30.70315405038687</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-10.12931506752125</v>
+        <v>-8.934440290441909</v>
       </c>
       <c r="S65" t="n">
-        <v>31.33359100341797</v>
+        <v>31.3411909866333</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-11.97944748593438</v>
+        <v>-10.78833252891598</v>
       </c>
       <c r="V65" t="n">
-        <v>28.75619946797689</v>
+        <v>28.75873279571533</v>
       </c>
       <c r="W65" t="n">
         <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>-4.090246854702261</v>
+        <v>-2.77736059135984</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.5826376247406</v>
+        <v>27.58453762054443</v>
       </c>
       <c r="Z65" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>-0.009562903557048778</v>
+        <v>1.361130170434995</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2710103445130063</v>
+        <v>0.2678909562761259</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19163,13 +19155,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>11.12</v>
+        <v>11.27</v>
       </c>
       <c r="CA65" t="n">
         <v>0.33</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CC65" t="n">
         <v>9</v>
@@ -19204,13 +19196,13 @@
         <v>3</v>
       </c>
       <c r="CM65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66">
@@ -19223,10 +19215,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15.53999996185303</v>
+        <v>15.5600004196167</v>
       </c>
       <c r="D66" t="n">
-        <v>15.53999996185303</v>
+        <v>15.5600004196167</v>
       </c>
       <c r="E66" t="n">
         <v>15.80000019073486</v>
@@ -19238,67 +19230,67 @@
         <v>15.5</v>
       </c>
       <c r="H66" t="n">
-        <v>1911700</v>
+        <v>2860900</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.02264148838454649</v>
+        <v>-0.02138359792897926</v>
       </c>
       <c r="J66" t="n">
-        <v>16.1733332739936</v>
+        <v>16.17555554707845</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-3.91591084788291</v>
+        <v>-3.805465139482821</v>
       </c>
       <c r="M66" t="n">
-        <v>16.28400001525879</v>
+        <v>16.28600006103516</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-4.568902313366518</v>
+        <v>-4.457814311050128</v>
       </c>
       <c r="P66" t="n">
-        <v>16.91500010857215</v>
+        <v>16.91576935694768</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-8.128880507794404</v>
+        <v>-8.014822788856096</v>
       </c>
       <c r="S66" t="n">
-        <v>17.6053999710083</v>
+        <v>17.60579998016357</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-11.73162786733883</v>
+        <v>-11.62003182389823</v>
       </c>
       <c r="V66" t="n">
-        <v>16.03988131205241</v>
+        <v>16.0400146484375</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-3.116490331033614</v>
+        <v>-2.992604678622029</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.74266642093658</v>
+        <v>15.7427664232254</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-1.287370599519445</v>
+        <v>-1.160952266553785</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.1920717489775118</v>
+        <v>0.191125888383533</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19452,7 +19444,7 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>23.91</v>
+        <v>23.94</v>
       </c>
       <c r="CA66" t="n">
         <v>0.82</v>
@@ -19490,16 +19482,16 @@
         <v>0</v>
       </c>
       <c r="CL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM66" t="n">
         <v>3</v>
       </c>
-      <c r="CM66" t="n">
-        <v>2</v>
-      </c>
       <c r="CN66" t="n">
         <v>1</v>
       </c>
       <c r="CO66" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
@@ -19512,10 +19504,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.60000038146973</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="D67" t="n">
-        <v>18.60000038146973</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="E67" t="n">
         <v>18.85000038146973</v>
@@ -19527,67 +19519,67 @@
         <v>18.79999923706055</v>
       </c>
       <c r="H67" t="n">
-        <v>1669700</v>
+        <v>2775700</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.006940692148627803</v>
+        <v>-0.004271218668513765</v>
       </c>
       <c r="J67" t="n">
-        <v>19.00111113654243</v>
+        <v>19.00666660732693</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-2.110985784938098</v>
+        <v>-1.87653624996592</v>
       </c>
       <c r="M67" t="n">
-        <v>18.95599994659424</v>
+        <v>18.96099987030029</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-1.878031051527168</v>
+        <v>-1.640210188794715</v>
       </c>
       <c r="P67" t="n">
-        <v>18.58346146803636</v>
+        <v>18.58538451561561</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>0.088998023655688</v>
+        <v>0.3476662151400468</v>
       </c>
       <c r="S67" t="n">
-        <v>18.70339992523193</v>
+        <v>18.70439990997314</v>
       </c>
       <c r="T67" t="n">
         <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>-0.552838222866188</v>
+        <v>-0.2908422173644012</v>
       </c>
       <c r="V67" t="n">
-        <v>21.50272122701009</v>
+        <v>21.50305455525716</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-13.49931859737914</v>
+        <v>-13.26813792615041</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.3252409362793</v>
+        <v>22.3254909324646</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-16.68622777887214</v>
+        <v>-16.4632048856297</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.514377204332084</v>
+        <v>0.5140985241549075</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19737,13 +19729,13 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.61</v>
+        <v>16.65</v>
       </c>
       <c r="CA67" t="n">
         <v>0.36</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CC67" t="n">
         <v>10</v>
@@ -19797,10 +19789,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.68999862670898</v>
+        <v>41.41999816894531</v>
       </c>
       <c r="D68" t="n">
-        <v>41.68999862670898</v>
+        <v>41.41999816894531</v>
       </c>
       <c r="E68" t="n">
         <v>41.79000091552734</v>
@@ -19812,67 +19804,67 @@
         <v>41.65000152587891</v>
       </c>
       <c r="H68" t="n">
-        <v>1459800</v>
+        <v>2474600</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>-0.006476384424505488</v>
       </c>
       <c r="J68" t="n">
-        <v>41.7522218492296</v>
+        <v>41.72222179836697</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.1490297276760683</v>
+        <v>-0.7243708901271655</v>
       </c>
       <c r="M68" t="n">
-        <v>41.77399978637695</v>
+        <v>41.74699974060059</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.2010847898155159</v>
+        <v>-0.7832935868137408</v>
       </c>
       <c r="P68" t="n">
-        <v>42.98461532592773</v>
+        <v>42.97423069293682</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.011814086045467</v>
+        <v>-3.616661657300964</v>
       </c>
       <c r="S68" t="n">
-        <v>46.10339981079102</v>
+        <v>46.09799980163574</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-9.572832377210123</v>
+        <v>-10.14794926638973</v>
       </c>
       <c r="V68" t="n">
-        <v>49.55539993286133</v>
+        <v>49.55359992980957</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-15.87193588752901</v>
+        <v>-16.41374546427533</v>
       </c>
       <c r="Y68" t="n">
-        <v>49.91149995803833</v>
+        <v>49.91014995574951</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-16.47215839684509</v>
+        <v>-17.01087212587338</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2055537954926911</v>
+        <v>0.2051817229684479</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20024,13 +20016,13 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="CA68" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CB68" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CC68" t="n">
         <v>3</v>
@@ -20065,13 +20057,13 @@
         <v>4</v>
       </c>
       <c r="CM68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN68" t="n">
         <v>1</v>
       </c>
       <c r="CO68" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
@@ -20084,10 +20076,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39.02000045776367</v>
+        <v>39.11000061035156</v>
       </c>
       <c r="D69" t="n">
-        <v>39.02000045776367</v>
+        <v>39.11000061035156</v>
       </c>
       <c r="E69" t="n">
         <v>39.52999877929688</v>
@@ -20099,67 +20091,67 @@
         <v>39.52999877929688</v>
       </c>
       <c r="H69" t="n">
-        <v>514800</v>
+        <v>1216700</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.00509945835580139</v>
+        <v>-0.002804706958894676</v>
       </c>
       <c r="J69" t="n">
-        <v>38.87555525037978</v>
+        <v>38.88555526733398</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0.3715579274780517</v>
+        <v>0.5771946458641022</v>
       </c>
       <c r="M69" t="n">
-        <v>38.84299964904785</v>
+        <v>38.85199966430664</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.4556826463327897</v>
+        <v>0.6640609190624208</v>
       </c>
       <c r="P69" t="n">
-        <v>40.48769231942984</v>
+        <v>40.49115386376014</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-3.625032145785771</v>
+        <v>-3.410999987937412</v>
       </c>
       <c r="S69" t="n">
-        <v>41.88620018005371</v>
+        <v>41.88800018310547</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-6.842825823228842</v>
+        <v>-6.63196992124333</v>
       </c>
       <c r="V69" t="n">
-        <v>41.78106681823731</v>
+        <v>41.78166681925456</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-6.608415176389028</v>
+        <v>-6.394350470651386</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.11860012054444</v>
+        <v>40.11905012130737</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-2.738379852437022</v>
+        <v>-2.515138090021483</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2518811787914079</v>
+        <v>0.2519639921334049</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20311,7 +20303,7 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
@@ -20367,10 +20359,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.09000015258789</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="D70" t="n">
-        <v>22.09000015258789</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="E70" t="n">
         <v>22.40999984741211</v>
@@ -20382,67 +20374,67 @@
         <v>22.38999938964844</v>
       </c>
       <c r="H70" t="n">
-        <v>1790300</v>
+        <v>3514700</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.01119068927002853</v>
+        <v>-0.008952585567296167</v>
       </c>
       <c r="J70" t="n">
-        <v>22.45888879564073</v>
+        <v>22.46444426642524</v>
       </c>
       <c r="K70" t="n">
         <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>-1.642506209498853</v>
+        <v>-1.44425952820791</v>
       </c>
       <c r="M70" t="n">
-        <v>22.41999988555908</v>
+        <v>22.42499980926514</v>
       </c>
       <c r="N70" t="n">
         <v>-1</v>
       </c>
       <c r="O70" t="n">
-        <v>-1.471898905689771</v>
+        <v>-1.27090489204352</v>
       </c>
       <c r="P70" t="n">
-        <v>23.60653847914476</v>
+        <v>23.60846152672401</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-6.424229998382247</v>
+        <v>-6.220067052710395</v>
       </c>
       <c r="S70" t="n">
-        <v>25.21859996795654</v>
+        <v>25.21959995269775</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-12.40592189631438</v>
+        <v>-12.21113962483726</v>
       </c>
       <c r="V70" t="n">
-        <v>24.84546667734782</v>
+        <v>24.84580000559489</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-11.09041967511985</v>
+        <v>-10.89037428996912</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.33810000419617</v>
+        <v>24.33835000038147</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-9.236957080547285</v>
+        <v>-9.032455407612174</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3779965891411004</v>
+        <v>0.3778257593024321</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20594,13 +20586,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2209</v>
+        <v>2214</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CC70" t="n">
         <v>1</v>
@@ -20654,13 +20646,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>31.52000045776367</v>
+        <v>33.66999816894531</v>
       </c>
       <c r="D71" t="n">
-        <v>31.52000045776367</v>
+        <v>33.66999816894531</v>
       </c>
       <c r="E71" t="n">
-        <v>32.27999877929688</v>
+        <v>33.70000076293945</v>
       </c>
       <c r="F71" t="n">
         <v>31.39999961853027</v>
@@ -20669,94 +20661,98 @@
         <v>31.80999946594238</v>
       </c>
       <c r="H71" t="n">
-        <v>4840500</v>
+        <v>11207400</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.007244080070435532</v>
+        <v>0.06047238327386806</v>
       </c>
       <c r="J71" t="n">
-        <v>31.58111084832085</v>
+        <v>31.81999948289659</v>
       </c>
       <c r="K71" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.1935029798371756</v>
+        <v>5.813949453528762</v>
       </c>
       <c r="M71" t="n">
-        <v>31.56899967193603</v>
+        <v>31.7839994430542</v>
       </c>
       <c r="N71" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>-0.155213071942602</v>
+        <v>5.933799266735336</v>
       </c>
       <c r="P71" t="n">
-        <v>32.20461522615873</v>
+        <v>32.28730744581956</v>
       </c>
       <c r="Q71" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>-2.125828126146863</v>
+        <v>4.282459060564288</v>
       </c>
       <c r="S71" t="n">
-        <v>33.38599990844727</v>
+        <v>33.4289998626709</v>
       </c>
       <c r="T71" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>-5.589167482779103</v>
+        <v>0.7209258645620695</v>
       </c>
       <c r="V71" t="n">
-        <v>39.38513328552246</v>
+        <v>39.39946660359701</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-19.96980122103567</v>
+        <v>-14.54199492672476</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.34344999313355</v>
+        <v>40.35419998168945</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-21.87083538188138</v>
+        <v>-16.56383180877597</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4536311534921005</v>
+        <v>0.4896238748957832</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>30.7</v>
+        <v>32</v>
       </c>
       <c r="AE71" t="n">
-        <v>30.9</v>
+        <v>32.3</v>
       </c>
       <c r="AF71" t="n">
-        <v>31.3</v>
+        <v>32.6</v>
       </c>
       <c r="AG71" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>32.3</v>
+        <v>48.4</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AJ71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
@@ -20877,13 +20873,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>20.47</v>
+        <v>21.86</v>
       </c>
       <c r="CA71" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="CB71" t="n">
-        <v>3.81</v>
+        <v>4.07</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20898,7 +20894,7 @@
         <v>4</v>
       </c>
       <c r="CG71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CH71" t="n">
         <v>5</v>
@@ -20915,16 +20911,16 @@
         <v>0</v>
       </c>
       <c r="CL71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CM71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CN71" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO71" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72">
@@ -20937,82 +20933,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>26.23999977111816</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="D72" t="n">
-        <v>26.23999977111816</v>
+        <v>26.07999992370605</v>
       </c>
       <c r="E72" t="n">
         <v>27.06999969482422</v>
       </c>
       <c r="F72" t="n">
-        <v>26.22999954223633</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="G72" t="n">
         <v>27.06999969482422</v>
       </c>
       <c r="H72" t="n">
-        <v>1018400</v>
+        <v>2230900</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.02489781048283346</v>
+        <v>-0.03084354992242311</v>
       </c>
       <c r="J72" t="n">
-        <v>28.02000024583604</v>
+        <v>28.00222248501248</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-6.35260692041714</v>
+        <v>-6.864535707246977</v>
       </c>
       <c r="M72" t="n">
-        <v>28.14600028991699</v>
+        <v>28.13000030517578</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-6.771834360712457</v>
+        <v>-7.287594593778003</v>
       </c>
       <c r="P72" t="n">
-        <v>28.99153863466703</v>
+        <v>28.98538479438195</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-9.49083419897789</v>
+        <v>-10.0236201495556</v>
       </c>
       <c r="S72" t="n">
-        <v>28.96200008392334</v>
+        <v>28.9588000869751</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-9.398523254325049</v>
+        <v>-9.941020189451331</v>
       </c>
       <c r="V72" t="n">
-        <v>25.18779998779297</v>
+        <v>25.18673332214355</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>4.177418368555949</v>
+        <v>3.546575850617212</v>
       </c>
       <c r="Y72" t="n">
-        <v>23.89869999885559</v>
+        <v>23.89789999961853</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>9.796766235714447</v>
+        <v>9.13092750460231</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2521329253622841</v>
+        <v>0.2567394842341222</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21164,13 +21160,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>9.75</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="CA72" t="n">
         <v>0.48</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21220,13 +21216,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.76000022888184</v>
+        <v>11.06999969482422</v>
       </c>
       <c r="D73" t="n">
-        <v>10.76000022888184</v>
+        <v>11.06999969482422</v>
       </c>
       <c r="E73" t="n">
-        <v>10.80000019073486</v>
+        <v>11.09000015258789</v>
       </c>
       <c r="F73" t="n">
         <v>10.60000038146973</v>
@@ -21235,67 +21231,67 @@
         <v>10.63000011444092</v>
       </c>
       <c r="H73" t="n">
-        <v>9314100</v>
+        <v>20347600</v>
       </c>
       <c r="I73" t="n">
-        <v>0.01032869617761945</v>
+        <v>0.03943662829463146</v>
       </c>
       <c r="J73" t="n">
-        <v>10.02333333757189</v>
+        <v>10.0577777226766</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>7.349520029914565</v>
+        <v>10.06407180649294</v>
       </c>
       <c r="M73" t="n">
-        <v>9.923999977111816</v>
+        <v>9.954999923706055</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>8.424025127953714</v>
+        <v>11.20039959481056</v>
       </c>
       <c r="P73" t="n">
-        <v>9.08807690326984</v>
+        <v>9.099999959652241</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>18.39688795998686</v>
+        <v>21.64834883413848</v>
       </c>
       <c r="S73" t="n">
-        <v>8.027999973297119</v>
+        <v>8.034199962615967</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>34.03089517528583</v>
+        <v>37.78596184230128</v>
       </c>
       <c r="V73" t="n">
-        <v>6.689933322270711</v>
+        <v>6.691999985376994</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>60.83867671837503</v>
+        <v>65.42139448615958</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.114799991846085</v>
+        <v>6.116349989175797</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>75.96651146775031</v>
+        <v>80.99029183115707</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.5464497105806644</v>
+        <v>0.550736551076428</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21447,13 +21443,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>-5.17</v>
+        <v>-5.32</v>
       </c>
       <c r="CA73" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21507,88 +21503,88 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>83.43000030517578</v>
+        <v>82.83999633789062</v>
       </c>
       <c r="D74" t="n">
-        <v>83.43000030517578</v>
+        <v>82.83999633789062</v>
       </c>
       <c r="E74" t="n">
         <v>84.27999877929688</v>
       </c>
       <c r="F74" t="n">
-        <v>82.88999938964844</v>
+        <v>82.55000305175781</v>
       </c>
       <c r="G74" t="n">
         <v>84.01000213623047</v>
       </c>
       <c r="H74" t="n">
-        <v>5574000</v>
+        <v>10296000</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.006312515305814115</v>
+        <v>-0.01333971842299797</v>
       </c>
       <c r="J74" t="n">
-        <v>82.91666497124567</v>
+        <v>82.85110897488065</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>0.6190979028258465</v>
+        <v>-0.0134127800189008</v>
       </c>
       <c r="M74" t="n">
-        <v>82.80799865722656</v>
+        <v>82.74899826049804</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.7511371582881956</v>
+        <v>0.1099687963667152</v>
       </c>
       <c r="P74" t="n">
-        <v>82.57500017606296</v>
+        <v>82.55230771578275</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>1.035422497474815</v>
+        <v>0.3484925256097686</v>
       </c>
       <c r="S74" t="n">
-        <v>82.75460037231446</v>
+        <v>82.74280029296875</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>0.8161478997212096</v>
+        <v>0.117467676435568</v>
       </c>
       <c r="V74" t="n">
-        <v>77.5593334197998</v>
+        <v>77.5554000600179</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>7.569259077563557</v>
+        <v>6.813963017124694</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.38115007400512</v>
+        <v>72.3782000541687</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>15.26481717943679</v>
+        <v>14.45434713199857</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3025434754003673</v>
+        <v>0.3041426250477751</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AE74" t="n">
         <v>82.7</v>
@@ -21730,13 +21726,13 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>23.77</v>
+        <v>23.6</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
       </c>
       <c r="CB74" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CC74" t="n">
         <v>1</v>
@@ -21767,13 +21763,13 @@
         <v>9</v>
       </c>
       <c r="CM74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN74" t="n">
         <v>0</v>
       </c>
       <c r="CO74" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75">
@@ -21786,10 +21782,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.099999904632568</v>
+        <v>3.130000114440918</v>
       </c>
       <c r="D75" t="n">
-        <v>3.099999904632568</v>
+        <v>3.130000114440918</v>
       </c>
       <c r="E75" t="n">
         <v>3.210000038146973</v>
@@ -21801,67 +21797,67 @@
         <v>3.190000057220459</v>
       </c>
       <c r="H75" t="n">
-        <v>7048900</v>
+        <v>9981800</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.02821321347132211</v>
+        <v>-0.01880875915463798</v>
       </c>
       <c r="J75" t="n">
-        <v>3.266666650772095</v>
+        <v>3.270000007417467</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-5.102043273994111</v>
+        <v>-4.281342283149296</v>
       </c>
       <c r="M75" t="n">
-        <v>3.273999977111816</v>
+        <v>3.276999998092651</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-5.314602128761874</v>
+        <v>-4.485806644409314</v>
       </c>
       <c r="P75" t="n">
-        <v>3.622307704045222</v>
+        <v>3.62346155826862</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-14.41920019189329</v>
+        <v>-13.61850914912122</v>
       </c>
       <c r="S75" t="n">
-        <v>3.732000007629395</v>
+        <v>3.732600011825562</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-16.93462223217623</v>
+        <v>-16.14423981877234</v>
       </c>
       <c r="V75" t="n">
-        <v>3.751794789632161</v>
+        <v>3.751994791030884</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-17.37288208834836</v>
+        <v>-16.57770629311212</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.737346098423004</v>
+        <v>3.737496099472046</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-17.05344319219908</v>
+        <v>-16.25409014117612</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.5108969114355215</v>
+        <v>0.5087492418935832</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -22013,13 +22009,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>12.4</v>
+        <v>12.52</v>
       </c>
       <c r="CA75" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CB75" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CC75" t="n">
         <v>6</v>
@@ -22034,7 +22030,7 @@
         <v>6</v>
       </c>
       <c r="CG75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CH75" t="n">
         <v>9</v>
@@ -22069,82 +22065,82 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>29.8799991607666</v>
+        <v>29.8700008392334</v>
       </c>
       <c r="D76" t="n">
-        <v>29.8799991607666</v>
+        <v>29.8700008392334</v>
       </c>
       <c r="E76" t="n">
         <v>30.95000076293945</v>
       </c>
       <c r="F76" t="n">
-        <v>29.82999992370605</v>
+        <v>29.70000076293945</v>
       </c>
       <c r="G76" t="n">
         <v>30.89999961853027</v>
       </c>
       <c r="H76" t="n">
-        <v>2236000</v>
+        <v>4349200</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.03332257171563013</v>
+        <v>-0.03364603731196014</v>
       </c>
       <c r="J76" t="n">
-        <v>32.01444413926866</v>
+        <v>32.01333321465386</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-6.667131152478661</v>
+        <v>-6.695124062993132</v>
       </c>
       <c r="M76" t="n">
-        <v>32.13899955749512</v>
+        <v>32.1379997253418</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-7.028844792406417</v>
+        <v>-7.057062995491951</v>
       </c>
       <c r="P76" t="n">
-        <v>32.70884587214543</v>
+        <v>32.70846132131723</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-8.648567798559506</v>
+        <v>-8.678061784073925</v>
       </c>
       <c r="S76" t="n">
-        <v>32.33039989471435</v>
+        <v>32.33019992828369</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-7.579246597405572</v>
+        <v>-7.609600604102718</v>
       </c>
       <c r="V76" t="n">
-        <v>28.50067186991374</v>
+        <v>28.50060521443685</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>4.83963078887599</v>
+        <v>4.804794896435703</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.82549651145935</v>
+        <v>26.82544651985168</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>11.38656519554979</v>
+        <v>11.34950099387403</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.2700595553905888</v>
+        <v>0.2703625413687186</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22352,10 +22348,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>21.93000030517578</v>
+        <v>21.88999938964844</v>
       </c>
       <c r="D77" t="n">
-        <v>21.93000030517578</v>
+        <v>21.88999938964844</v>
       </c>
       <c r="E77" t="n">
         <v>22.14999961853027</v>
@@ -22367,67 +22363,67 @@
         <v>22.13999938964844</v>
       </c>
       <c r="H77" t="n">
-        <v>2256300</v>
+        <v>3124100</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.009932249080963684</v>
+        <v>-0.01173815951962021</v>
       </c>
       <c r="J77" t="n">
-        <v>22.3022223578559</v>
+        <v>22.2977778116862</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.668990859778636</v>
+        <v>-1.828785027286648</v>
       </c>
       <c r="M77" t="n">
-        <v>22.35200004577637</v>
+        <v>22.34799995422363</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-1.887973066107467</v>
+        <v>-2.049402924258708</v>
       </c>
       <c r="P77" t="n">
-        <v>24.10038463885968</v>
+        <v>24.09884614210862</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-9.005600392718828</v>
+        <v>-9.165778060222571</v>
       </c>
       <c r="S77" t="n">
-        <v>25.29780010223389</v>
+        <v>25.29700008392334</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-13.31261921371857</v>
+        <v>-13.46800285793614</v>
       </c>
       <c r="V77" t="n">
-        <v>29.07313335418701</v>
+        <v>29.07286668141683</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-24.5695328466634</v>
+        <v>-24.70642943635011</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.85835001945496</v>
+        <v>28.85815001487732</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-24.00812835663995</v>
+        <v>-24.14621388286004</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.459791216265062</v>
+        <v>0.4599148009378761</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22577,7 +22573,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
@@ -22618,13 +22614,13 @@
         <v>2</v>
       </c>
       <c r="CM77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
       </c>
       <c r="CO77" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
@@ -22637,10 +22633,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.27000045776367</v>
+        <v>33.31000137329102</v>
       </c>
       <c r="D78" t="n">
-        <v>33.27000045776367</v>
+        <v>33.31000137329102</v>
       </c>
       <c r="E78" t="n">
         <v>33.79000091552734</v>
@@ -22652,67 +22648,67 @@
         <v>33.79000091552734</v>
       </c>
       <c r="H78" t="n">
-        <v>1635500</v>
+        <v>2998500</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.009821369980465566</v>
+        <v>-0.008630866488087308</v>
       </c>
       <c r="J78" t="n">
-        <v>34.2533336215549</v>
+        <v>34.25777816772461</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.870766316223419</v>
+        <v>-2.766603221590493</v>
       </c>
       <c r="M78" t="n">
-        <v>34.35700035095215</v>
+        <v>34.36100044250488</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-3.163838175873675</v>
+        <v>-3.058697522420709</v>
       </c>
       <c r="P78" t="n">
-        <v>36.65730769817646</v>
+        <v>36.65884619492751</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-9.240469235500598</v>
+        <v>-9.135161548264634</v>
       </c>
       <c r="S78" t="n">
-        <v>38.77599998474121</v>
+        <v>38.77680000305176</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-14.19950363406285</v>
+        <v>-14.09811699090823</v>
       </c>
       <c r="V78" t="n">
-        <v>36.99666674296061</v>
+        <v>36.99693341573079</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-10.07297849584251</v>
+        <v>-9.965507143551863</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.10100009918213</v>
+        <v>36.10120010375977</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-7.84188702152491</v>
+        <v>-7.731595410807576</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3074542274940524</v>
+        <v>0.3073916839930121</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22864,13 +22860,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>16.89</v>
+        <v>16.91</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
       </c>
       <c r="CB78" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CC78" t="n">
         <v>5</v>
@@ -22905,13 +22901,13 @@
         <v>1</v>
       </c>
       <c r="CM78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
       </c>
       <c r="CO78" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
@@ -22924,13 +22920,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>43.68000030517578</v>
+        <v>44.13000106811523</v>
       </c>
       <c r="D79" t="n">
-        <v>43.68000030517578</v>
+        <v>44.13000106811523</v>
       </c>
       <c r="E79" t="n">
-        <v>43.77999877929688</v>
+        <v>44.27999877929688</v>
       </c>
       <c r="F79" t="n">
         <v>43.09999847412109</v>
@@ -22939,67 +22935,67 @@
         <v>43.59999847412109</v>
       </c>
       <c r="H79" t="n">
-        <v>2044500</v>
+        <v>3489000</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.000914933998409917</v>
+        <v>0.00937785535143032</v>
       </c>
       <c r="J79" t="n">
-        <v>43.02222273084853</v>
+        <v>43.07222281561958</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>1.528925128862774</v>
+        <v>2.455824620483876</v>
       </c>
       <c r="M79" t="n">
-        <v>42.95400047302246</v>
+        <v>42.99900054931641</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>1.690179783392444</v>
+        <v>2.630294900695799</v>
       </c>
       <c r="P79" t="n">
-        <v>44.24769254831168</v>
+        <v>44.26500026996319</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-1.282987225867342</v>
+        <v>-0.3049795572678673</v>
       </c>
       <c r="S79" t="n">
-        <v>46.68760017395019</v>
+        <v>46.69660018920899</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-6.441967155237363</v>
+        <v>-5.496329734272307</v>
       </c>
       <c r="V79" t="n">
-        <v>47.06493329366048</v>
+        <v>47.06793329874674</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-7.192048838918977</v>
+        <v>-6.241897667322769</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.53144996643066</v>
+        <v>44.53369997024536</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-1.912018723613838</v>
+        <v>-0.906502047662445</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.3239796612147916</v>
+        <v>0.326269377809694</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23151,13 +23147,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>29.12</v>
+        <v>29.42</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB79" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
       <c r="CC79" t="n">
         <v>6</v>
@@ -23189,7 +23185,7 @@
         <v>0</v>
       </c>
       <c r="CL79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM79" t="n">
         <v>10</v>
@@ -23198,7 +23194,7 @@
         <v>0</v>
       </c>
       <c r="CO79" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80">
@@ -23211,10 +23207,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.430000305175781</v>
+        <v>9.560000419616699</v>
       </c>
       <c r="D80" t="n">
-        <v>9.430000305175781</v>
+        <v>9.560000419616699</v>
       </c>
       <c r="E80" t="n">
         <v>9.659999847412109</v>
@@ -23226,67 +23222,67 @@
         <v>9.560000419616699</v>
       </c>
       <c r="H80" t="n">
-        <v>1405000</v>
+        <v>2064000</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.01565758034706177</v>
+        <v>-0.002087630923656492</v>
       </c>
       <c r="J80" t="n">
-        <v>9.592222107781303</v>
+        <v>9.606666564941406</v>
       </c>
       <c r="K80" t="n">
         <v>-1</v>
       </c>
       <c r="L80" t="n">
-        <v>-1.691180633462671</v>
+        <v>-0.4857683464835824</v>
       </c>
       <c r="M80" t="n">
-        <v>9.588999938964843</v>
+        <v>9.601999950408935</v>
       </c>
       <c r="N80" t="n">
         <v>-1</v>
       </c>
       <c r="O80" t="n">
-        <v>-1.658146154980852</v>
+        <v>-0.4374039888476246</v>
       </c>
       <c r="P80" t="n">
-        <v>9.927692303290733</v>
+        <v>9.932692307692308</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-5.013169051885121</v>
+        <v>-3.752173897373025</v>
       </c>
       <c r="S80" t="n">
-        <v>10.64840000152588</v>
+        <v>10.6510000038147</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-11.44209173373939</v>
+        <v>-10.2431657478852</v>
       </c>
       <c r="V80" t="n">
-        <v>12.16179999669393</v>
+        <v>12.16266666412353</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-22.46213300877142</v>
+        <v>-21.39881258263842</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.36455000400543</v>
+        <v>12.36520000457764</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-23.73357459736924</v>
+        <v>-22.68624513895808</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4267959612445061</v>
+        <v>0.4262666889768775</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23438,13 +23434,13 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>21.93</v>
+        <v>22.23</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CB80" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="CC80" t="n">
         <v>5</v>
@@ -23479,13 +23475,13 @@
         <v>3</v>
       </c>
       <c r="CM80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
       </c>
       <c r="CO80" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.30999946594238</v>
+        <v>16.31999969482422</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30999946594238</v>
+        <v>16.31999969482422</v>
       </c>
       <c r="E2" t="n">
-        <v>16.30999946594238</v>
+        <v>16.45999908447266</v>
       </c>
       <c r="F2" t="n">
         <v>16.02000045776367</v>
@@ -912,67 +912,67 @@
         <v>16.29000091552734</v>
       </c>
       <c r="H2" t="n">
-        <v>31110700</v>
+        <v>86399400</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001227658028918555</v>
+        <v>0.001841545586917626</v>
       </c>
       <c r="J2" t="n">
-        <v>16.30333338843452</v>
+        <v>16.30444452497694</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04088781937437921</v>
+        <v>0.09540447589886165</v>
       </c>
       <c r="M2" t="n">
-        <v>16.25400009155273</v>
+        <v>16.25500011444092</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3445267261857157</v>
+        <v>0.3998743766575262</v>
       </c>
       <c r="P2" t="n">
-        <v>15.77923074135414</v>
+        <v>15.7796153655419</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3.363717365493687</v>
+        <v>3.424572252010417</v>
       </c>
       <c r="S2" t="n">
-        <v>15.53239999771118</v>
+        <v>15.53260000228882</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>5.006305969108361</v>
+        <v>5.069336057191793</v>
       </c>
       <c r="V2" t="n">
-        <v>14.67266665776571</v>
+        <v>14.67273332595825</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>11.15906771663824</v>
+        <v>11.2267178328097</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.0544000005722</v>
+        <v>14.05445000171661</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.04906267986072</v>
+        <v>16.11980328530031</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5044523871443013</v>
+        <v>0.5044531766715817</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.47</v>
+        <v>16.48</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.06</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.29000091552734</v>
+        <v>28.20999908447266</v>
       </c>
       <c r="D3" t="n">
-        <v>28.29000091552734</v>
+        <v>28.20999908447266</v>
       </c>
       <c r="E3" t="n">
         <v>28.84000015258789</v>
@@ -1199,67 +1199,67 @@
         <v>28.65999984741211</v>
       </c>
       <c r="H3" t="n">
-        <v>3068700</v>
+        <v>7452700</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0118755939645705</v>
+        <v>-0.01466992974521275</v>
       </c>
       <c r="J3" t="n">
-        <v>28.5</v>
+        <v>28.49111090766059</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7368388928865132</v>
+        <v>-0.9866650131650376</v>
       </c>
       <c r="M3" t="n">
-        <v>28.51399993896484</v>
+        <v>28.50599975585937</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7855755906466202</v>
+        <v>-1.038380249497741</v>
       </c>
       <c r="P3" t="n">
-        <v>29.59038463005653</v>
+        <v>29.58730763655442</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.394615787482241</v>
+        <v>-4.655065506467833</v>
       </c>
       <c r="S3" t="n">
-        <v>30.36899997711182</v>
+        <v>30.36739994049072</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.84579361569808</v>
+        <v>-7.104331817165132</v>
       </c>
       <c r="V3" t="n">
-        <v>29.32893332163493</v>
+        <v>29.32839997609456</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.542346374190158</v>
+        <v>-3.813371655233527</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.04019997596741</v>
+        <v>28.03979996681213</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8908671827377642</v>
+        <v>0.6069911977331177</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2612142280108507</v>
+        <v>0.2619261844269395</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.810000419616699</v>
+        <v>8.75</v>
       </c>
       <c r="D4" t="n">
-        <v>8.810000419616699</v>
+        <v>8.75</v>
       </c>
       <c r="E4" t="n">
         <v>9.090000152587891</v>
@@ -1486,67 +1486,67 @@
         <v>8.989999771118164</v>
       </c>
       <c r="H4" t="n">
-        <v>14670100</v>
+        <v>21906200</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01893086094493202</v>
+        <v>-0.0256124224900629</v>
       </c>
       <c r="J4" t="n">
-        <v>8.77333312564426</v>
+        <v>8.766666412353516</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4179402907346712</v>
+        <v>-0.1901111730455514</v>
       </c>
       <c r="M4" t="n">
-        <v>8.724999809265137</v>
+        <v>8.718999767303467</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.97421905111447</v>
+        <v>0.3555480390398074</v>
       </c>
       <c r="P4" t="n">
-        <v>8.91692300943228</v>
+        <v>8.914615300985483</v>
       </c>
       <c r="Q4" t="n">
         <v>-1</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.199097375882669</v>
+        <v>-1.846577731372048</v>
       </c>
       <c r="S4" t="n">
-        <v>8.944599943161011</v>
+        <v>8.943399934768676</v>
       </c>
       <c r="T4" t="n">
         <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.504813232560788</v>
+        <v>-2.16248782542764</v>
       </c>
       <c r="V4" t="n">
-        <v>8.63493327776591</v>
+        <v>8.634533274968465</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>2.027429005173318</v>
+        <v>1.33726654764622</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.890099947452546</v>
+        <v>8.889799945354461</v>
       </c>
       <c r="Z4" t="n">
         <v>-1</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.9009969326475256</v>
+        <v>-1.572588204614397</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5205818032248681</v>
+        <v>0.5225791514169914</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>16.94</v>
+        <v>16.83</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1712,7 +1712,7 @@
         <v>2</v>
       </c>
       <c r="CF4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CG4" t="n">
         <v>4</v>
@@ -1721,7 +1721,7 @@
         <v>10</v>
       </c>
       <c r="CI4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM4" t="n">
         <v>8</v>
@@ -1741,7 +1741,7 @@
         <v>-1</v>
       </c>
       <c r="CO4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.27999973297119</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="D5" t="n">
-        <v>12.27999973297119</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="E5" t="n">
         <v>12.52999973297119</v>
@@ -1769,67 +1769,67 @@
         <v>12.42000007629395</v>
       </c>
       <c r="H5" t="n">
-        <v>1333200</v>
+        <v>3330300</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.009677410423445276</v>
+        <v>-0.002419333378555932</v>
       </c>
       <c r="J5" t="n">
-        <v>12.45555549197727</v>
+        <v>12.46555550893148</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.409457483603632</v>
+        <v>-0.7665572810127196</v>
       </c>
       <c r="M5" t="n">
-        <v>12.45199995040894</v>
+        <v>12.46099996566772</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.381305959867886</v>
+        <v>-0.7302791137096863</v>
       </c>
       <c r="P5" t="n">
-        <v>13.146538404318</v>
+        <v>13.14999994864831</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.591382801287031</v>
+        <v>-5.931559438290343</v>
       </c>
       <c r="S5" t="n">
-        <v>12.97359992980957</v>
+        <v>12.97539993286133</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.346243144469766</v>
+        <v>-4.665752504237027</v>
       </c>
       <c r="V5" t="n">
-        <v>12.12186663309733</v>
+        <v>12.12246663411458</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.304527633080021</v>
+        <v>2.041937989318933</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.71304996490479</v>
+        <v>11.71349996566772</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.840325703084413</v>
+        <v>5.604643546468259</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2218271475697592</v>
+        <v>0.2214523217477525</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1977,13 +1977,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.98</v>
+        <v>-10.06</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2014,13 +2014,13 @@
         <v>7</v>
       </c>
       <c r="CM5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.13999938964844</v>
+        <v>52.43000030517578</v>
       </c>
       <c r="D6" t="n">
-        <v>52.13999938964844</v>
+        <v>52.43000030517578</v>
       </c>
       <c r="E6" t="n">
         <v>52.70000076293945</v>
@@ -2048,67 +2048,67 @@
         <v>52.5</v>
       </c>
       <c r="H6" t="n">
-        <v>8314400</v>
+        <v>30308700</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01062621186307133</v>
+        <v>-0.005123348270490879</v>
       </c>
       <c r="J6" t="n">
-        <v>53.64666663275825</v>
+        <v>53.67888895670573</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.808501138428225</v>
+        <v>-2.326591842348352</v>
       </c>
       <c r="M6" t="n">
-        <v>53.71300010681152</v>
+        <v>53.74200019836426</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.928528873894731</v>
+        <v>-2.441293380123227</v>
       </c>
       <c r="P6" t="n">
-        <v>57.39961506770207</v>
+        <v>57.41076894906851</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.163154965150881</v>
+        <v>-8.675669626218346</v>
       </c>
       <c r="S6" t="n">
-        <v>58.99519996643066</v>
+        <v>59.00099998474121</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-11.61992938524313</v>
+        <v>-11.13709883097713</v>
       </c>
       <c r="V6" t="n">
-        <v>58.18053334554036</v>
+        <v>58.18246668497721</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.38239701244496</v>
+        <v>-9.886941388971271</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.59659999847412</v>
+        <v>55.59805000305176</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-6.217287763857052</v>
+        <v>-5.698130955495896</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2790698658524022</v>
+        <v>0.2790429846021751</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2260,13 +2260,13 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>15.94</v>
+        <v>16.03</v>
       </c>
       <c r="CA6" t="n">
         <v>0.3</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CC6" t="n">
         <v>4</v>
@@ -2297,13 +2297,13 @@
         <v>3</v>
       </c>
       <c r="CM6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN6" t="n">
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.27000045776367</v>
+        <v>56.93000030517578</v>
       </c>
       <c r="D7" t="n">
-        <v>57.27000045776367</v>
+        <v>56.93000030517578</v>
       </c>
       <c r="E7" t="n">
         <v>57.88999938964844</v>
@@ -2331,67 +2331,67 @@
         <v>57.79999923706055</v>
       </c>
       <c r="H7" t="n">
-        <v>1674500</v>
+        <v>5218300</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0108808471763796</v>
+        <v>-0.01675304309395531</v>
       </c>
       <c r="J7" t="n">
-        <v>59.00666681925455</v>
+        <v>58.96888902452257</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.943169738447569</v>
+        <v>-3.457566783221746</v>
       </c>
       <c r="M7" t="n">
-        <v>59.08600006103516</v>
+        <v>59.05200004577637</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.07348543038212</v>
+        <v>-3.593442625068819</v>
       </c>
       <c r="P7" t="n">
-        <v>63.10384647662823</v>
+        <v>63.09076954768254</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.244834260658322</v>
+        <v>-9.764929619142769</v>
       </c>
       <c r="S7" t="n">
-        <v>64.75880004882812</v>
+        <v>64.75200004577637</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-11.56414199370263</v>
+        <v>-12.07993534573578</v>
       </c>
       <c r="V7" t="n">
-        <v>58.65320238749186</v>
+        <v>58.65093571980794</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.358271796636228</v>
+        <v>-2.93419941815345</v>
       </c>
       <c r="Y7" t="n">
-        <v>54.04998151779175</v>
+        <v>54.04828151702881</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.957483887227568</v>
+        <v>5.33174914587994</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2958874366049735</v>
+        <v>0.2968940071656754</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,13 +2543,13 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.51</v>
+        <v>17.41</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CC7" t="n">
         <v>4</v>
@@ -2581,7 +2581,7 @@
         <v>-1</v>
       </c>
       <c r="CL7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM7" t="n">
         <v>3</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.29999923706055</v>
+        <v>19.30999946594238</v>
       </c>
       <c r="D8" t="n">
-        <v>19.29999923706055</v>
+        <v>19.30999946594238</v>
       </c>
       <c r="E8" t="n">
         <v>19.85000038146973</v>
@@ -2618,67 +2618,67 @@
         <v>19.85000038146973</v>
       </c>
       <c r="H8" t="n">
-        <v>2255000</v>
+        <v>3138000</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02770786568460792</v>
+        <v>-0.027204075826187</v>
       </c>
       <c r="J8" t="n">
-        <v>20.02666664123535</v>
+        <v>20.02777777777778</v>
       </c>
       <c r="K8" t="n">
         <v>-1</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.628499026785518</v>
+        <v>-3.583913900981171</v>
       </c>
       <c r="M8" t="n">
-        <v>19.95799999237061</v>
+        <v>19.95900001525879</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.296927325190875</v>
+        <v>-3.25166866486417</v>
       </c>
       <c r="P8" t="n">
-        <v>20.5899999325092</v>
+        <v>20.59038455669696</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-6.265180668659906</v>
+        <v>-6.218364145793187</v>
       </c>
       <c r="S8" t="n">
-        <v>22.32680004119873</v>
+        <v>22.32700004577637</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-13.55680526789756</v>
+        <v>-13.51278977761597</v>
       </c>
       <c r="V8" t="n">
-        <v>25.05940002441406</v>
+        <v>25.05946669260661</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-22.98299552959143</v>
+        <v>-22.94329443315932</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.53245002746582</v>
+        <v>26.53250002861023</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-27.25888782573188</v>
+        <v>-27.2213344195977</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4475446931563276</v>
+        <v>0.447325079454448</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.48999977111816</v>
+        <v>16.5</v>
       </c>
       <c r="D9" t="n">
-        <v>16.48999977111816</v>
+        <v>16.5</v>
       </c>
       <c r="E9" t="n">
         <v>16.63999938964844</v>
@@ -2901,67 +2901,67 @@
         <v>16.53000068664551</v>
       </c>
       <c r="H9" t="n">
-        <v>14396800</v>
+        <v>48006400</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0006060744776870131</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>16.67000018225776</v>
+        <v>16.67111131880019</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.079786497730056</v>
+        <v>-1.026394194892227</v>
       </c>
       <c r="M9" t="n">
-        <v>16.67500009536743</v>
+        <v>16.67600011825562</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.109447215539519</v>
+        <v>-1.055409672628532</v>
       </c>
       <c r="P9" t="n">
-        <v>17.42423090567956</v>
+        <v>17.42461552986732</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-5.361677881902231</v>
+        <v>-5.306375502417516</v>
       </c>
       <c r="S9" t="n">
-        <v>17.87200010299683</v>
+        <v>17.87220010757446</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.732768150817789</v>
+        <v>-7.677846595914673</v>
       </c>
       <c r="V9" t="n">
-        <v>16.02940007527669</v>
+        <v>16.02946674346924</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>2.873468087878637</v>
+        <v>2.93542676160744</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.25485005378723</v>
+        <v>15.25490005493164</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.096767342687114</v>
+        <v>8.161967240590609</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3475380179168544</v>
+        <v>0.3476228942049198</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>16.83</v>
+        <v>16.84</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
@@ -3154,13 +3154,13 @@
         <v>5</v>
       </c>
       <c r="CM9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.48999977111816</v>
+        <v>20.29999923706055</v>
       </c>
       <c r="D10" t="n">
-        <v>20.48999977111816</v>
+        <v>20.29999923706055</v>
       </c>
       <c r="E10" t="n">
         <v>20.70000076293945</v>
@@ -3188,67 +3188,67 @@
         <v>20.67000007629395</v>
       </c>
       <c r="H10" t="n">
-        <v>21808600</v>
+        <v>60390500</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.00582245685005589</v>
+        <v>-0.0150413083023061</v>
       </c>
       <c r="J10" t="n">
-        <v>20.84666675991482</v>
+        <v>20.82555558946397</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.710906558368734</v>
+        <v>-2.523612636146503</v>
       </c>
       <c r="M10" t="n">
-        <v>20.80400009155273</v>
+        <v>20.78500003814697</v>
       </c>
       <c r="N10" t="n">
         <v>-1</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.509326663395211</v>
+        <v>-2.33341736923886</v>
       </c>
       <c r="P10" t="n">
-        <v>21.43000008509709</v>
+        <v>21.42269237224872</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-4.386375689436536</v>
+        <v>-5.240672440605686</v>
       </c>
       <c r="S10" t="n">
-        <v>22.57359996795654</v>
+        <v>22.56979995727539</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-9.230252152054041</v>
+        <v>-10.05680477678833</v>
       </c>
       <c r="V10" t="n">
-        <v>22.94219999949138</v>
+        <v>22.94093332926432</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.68860104274035</v>
+        <v>-11.51188600001247</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.46700001716614</v>
+        <v>22.46605001449585</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-8.799573795065777</v>
+        <v>-9.641440199935875</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.255252530966667</v>
+        <v>0.2566918088563193</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>8.16</v>
+        <v>8.09</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="CC10" t="n">
         <v>1</v>
@@ -3455,13 +3455,13 @@
         <v>4</v>
       </c>
       <c r="CM10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.52000045776367</v>
+        <v>15.5</v>
       </c>
       <c r="D11" t="n">
-        <v>15.52000045776367</v>
+        <v>15.5</v>
       </c>
       <c r="E11" t="n">
         <v>15.64000034332275</v>
@@ -3489,67 +3489,67 @@
         <v>15.64000034332275</v>
       </c>
       <c r="H11" t="n">
-        <v>3743000</v>
+        <v>24262100</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.004490038110268935</v>
+        <v>-0.005772941097306639</v>
       </c>
       <c r="J11" t="n">
-        <v>15.5088889863756</v>
+        <v>15.50666671329074</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07164582451932054</v>
+        <v>-0.04299256193486586</v>
       </c>
       <c r="M11" t="n">
-        <v>15.49200010299683</v>
+        <v>15.49000005722046</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1807407344480279</v>
+        <v>0.06455740957133801</v>
       </c>
       <c r="P11" t="n">
-        <v>15.99346157220694</v>
+        <v>15.99269232383141</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.96034171405417</v>
+        <v>-3.080734086888103</v>
       </c>
       <c r="S11" t="n">
-        <v>16.49299999237061</v>
+        <v>16.49259998321533</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.899469684454182</v>
+        <v>-6.018456666780918</v>
       </c>
       <c r="V11" t="n">
-        <v>16.62426665623983</v>
+        <v>16.62413331985474</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.642495704083746</v>
+        <v>-6.76205669327824</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.08760000705719</v>
+        <v>16.08750000476837</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.528180393871853</v>
+        <v>-3.651903680461453</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2150519241780177</v>
+        <v>0.2150668792441424</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3559,11 +3559,13 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
         <v>10.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>15.5</v>
       </c>
       <c r="AG11" t="n">
         <v>15.6</v>
@@ -3578,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -3719,7 +3721,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.93</v>
+        <v>6.92</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3775,10 +3777,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.80999946594238</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="D12" t="n">
-        <v>17.80999946594238</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="E12" t="n">
         <v>17.95000076293945</v>
@@ -3790,67 +3792,67 @@
         <v>17.94000053405762</v>
       </c>
       <c r="H12" t="n">
-        <v>16009200</v>
+        <v>59352800</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0050279415925083</v>
+        <v>-0.01117312066218035</v>
       </c>
       <c r="J12" t="n">
-        <v>17.82111104329427</v>
+        <v>17.80888896518283</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.06235064314953529</v>
+        <v>-0.6114261392513746</v>
       </c>
       <c r="M12" t="n">
-        <v>17.80499992370606</v>
+        <v>17.79400005340576</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02807942857483632</v>
+        <v>-0.5282639664166785</v>
       </c>
       <c r="P12" t="n">
-        <v>18.4376922754141</v>
+        <v>18.43346155606783</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-3.404400074019676</v>
+        <v>-3.978963966683419</v>
       </c>
       <c r="S12" t="n">
-        <v>19.01780002593994</v>
+        <v>19.01560005187988</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.350895257864421</v>
+        <v>-6.918526290788122</v>
       </c>
       <c r="V12" t="n">
-        <v>19.30046666463216</v>
+        <v>19.29973333994548</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.722441247604851</v>
+        <v>-8.288884353106519</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.70269999504089</v>
+        <v>18.70215000152588</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-4.773110456432578</v>
+        <v>-5.358470756061001</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2563581820186041</v>
+        <v>0.2569750378927478</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4018,13 +4020,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.95</v>
+        <v>7.9</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4052,16 +4054,16 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM12" t="n">
         <v>6</v>
       </c>
-      <c r="CM12" t="n">
-        <v>7</v>
-      </c>
       <c r="CN12" t="n">
         <v>0</v>
       </c>
       <c r="CO12" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -4074,13 +4076,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34.91999816894531</v>
+        <v>35.40000152587891</v>
       </c>
       <c r="D13" t="n">
-        <v>34.91999816894531</v>
+        <v>35.40000152587891</v>
       </c>
       <c r="E13" t="n">
-        <v>35.02000045776367</v>
+        <v>35.40000152587891</v>
       </c>
       <c r="F13" t="n">
         <v>34.52000045776367</v>
@@ -4089,88 +4091,88 @@
         <v>34.70000076293945</v>
       </c>
       <c r="H13" t="n">
-        <v>2267200</v>
+        <v>9480700</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009832166567015355</v>
+        <v>0.0237131188954367</v>
       </c>
       <c r="J13" t="n">
-        <v>34.61444473266602</v>
+        <v>34.66777843899197</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8827338951675942</v>
+        <v>2.112114245149835</v>
       </c>
       <c r="M13" t="n">
-        <v>34.56500015258789</v>
+        <v>34.61300048828125</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.027044741184072</v>
+        <v>2.273715154697744</v>
       </c>
       <c r="P13" t="n">
-        <v>34.34307699937087</v>
+        <v>34.36153866694524</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.679876178785658</v>
+        <v>3.022166349997126</v>
       </c>
       <c r="S13" t="n">
-        <v>34.6923999786377</v>
+        <v>34.70200004577637</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6560462534957621</v>
+        <v>2.011415708552209</v>
       </c>
       <c r="V13" t="n">
-        <v>34.82320002237956</v>
+        <v>34.82640004475911</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2779702798810692</v>
+        <v>1.647030644518522</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.29749997138977</v>
+        <v>34.29989998817444</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.814995839565036</v>
+        <v>3.20730246468284</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1520248499846494</v>
+        <v>0.1646851945483669</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="AG13" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>35.5</v>
+        <v>36.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>36.4</v>
+        <v>38.6</v>
       </c>
       <c r="AJ13" t="n">
         <v>2</v>
@@ -4317,13 +4319,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>7.38</v>
+        <v>7.48</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.36</v>
+        <v>5.44</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4354,13 +4356,13 @@
         <v>9</v>
       </c>
       <c r="CM13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN13" t="n">
         <v>1</v>
       </c>
       <c r="CO13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -4373,82 +4375,82 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.740000009536743</v>
+        <v>3.690000057220459</v>
       </c>
       <c r="D14" t="n">
-        <v>3.740000009536743</v>
+        <v>3.690000057220459</v>
       </c>
       <c r="E14" t="n">
         <v>3.990000009536743</v>
       </c>
       <c r="F14" t="n">
-        <v>3.730000019073486</v>
+        <v>3.690000057220459</v>
       </c>
       <c r="G14" t="n">
         <v>3.980000019073486</v>
       </c>
       <c r="H14" t="n">
-        <v>18142600</v>
+        <v>25828300</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.05793451320301424</v>
+        <v>-0.07052895953952665</v>
       </c>
       <c r="J14" t="n">
-        <v>3.961111148198446</v>
+        <v>3.955555597941081</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.582048329097411</v>
+        <v>-6.713482699089019</v>
       </c>
       <c r="M14" t="n">
-        <v>4.000000023841858</v>
+        <v>3.995000028610229</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.500000318884856</v>
+        <v>-7.634542408147943</v>
       </c>
       <c r="P14" t="n">
-        <v>4.030769256445078</v>
+        <v>4.028846181355989</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-7.213740812461629</v>
+        <v>-8.410500398441249</v>
       </c>
       <c r="S14" t="n">
-        <v>4.084000024795532</v>
+        <v>4.083000025749207</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.423114916019419</v>
+        <v>-9.625274701207829</v>
       </c>
       <c r="V14" t="n">
-        <v>5.292800006866455</v>
+        <v>5.292466673851013</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-29.33796847255202</v>
+        <v>-30.27825615885333</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.506800000667572</v>
+        <v>5.506550000905991</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-32.08396874621641</v>
+        <v>-32.9888940150667</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5138393751949578</v>
+        <v>0.5266355167779001</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4600,13 +4602,13 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>5.27</v>
+        <v>5.2</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="CC14" t="n">
         <v>8</v>
@@ -4660,10 +4662,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53.86000061035156</v>
+        <v>53.75</v>
       </c>
       <c r="D15" t="n">
-        <v>53.86000061035156</v>
+        <v>53.75</v>
       </c>
       <c r="E15" t="n">
         <v>54.4900016784668</v>
@@ -4675,67 +4677,67 @@
         <v>54.4900016784668</v>
       </c>
       <c r="H15" t="n">
-        <v>6434400</v>
+        <v>14559100</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.008103105578106118</v>
+        <v>-0.01012889953569585</v>
       </c>
       <c r="J15" t="n">
-        <v>54.45777808295356</v>
+        <v>54.4455557929145</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.097689795003066</v>
+        <v>-1.277525378857491</v>
       </c>
       <c r="M15" t="n">
-        <v>54.43000030517578</v>
+        <v>54.41900024414063</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.047216041940785</v>
+        <v>-1.229350486299422</v>
       </c>
       <c r="P15" t="n">
-        <v>56.70923086313101</v>
+        <v>56.70500007042518</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-5.024279485743917</v>
+        <v>-5.211180789622071</v>
       </c>
       <c r="S15" t="n">
-        <v>57.75779983520508</v>
+        <v>57.75559982299805</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.748524417437542</v>
+        <v>-6.935431084213303</v>
       </c>
       <c r="V15" t="n">
-        <v>55.87993321736653</v>
+        <v>55.87919987996419</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.614772764952431</v>
+        <v>-3.810362146448033</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.35564994812012</v>
+        <v>53.35509994506836</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.9452619595522613</v>
+        <v>0.7401355359435331</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2807252609611026</v>
+        <v>0.2809339909101137</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4907,7 +4909,7 @@
         <v>3510880000</v>
       </c>
       <c r="BZ15" t="n">
-        <v>12.1</v>
+        <v>12.08</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -4948,13 +4950,13 @@
         <v>5</v>
       </c>
       <c r="CM15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN15" t="n">
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -4967,10 +4969,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.14999961853027</v>
+        <v>23.25</v>
       </c>
       <c r="D16" t="n">
-        <v>23.14999961853027</v>
+        <v>23.25</v>
       </c>
       <c r="E16" t="n">
         <v>23.5</v>
@@ -4982,67 +4984,67 @@
         <v>23.36000061035156</v>
       </c>
       <c r="H16" t="n">
-        <v>1267100</v>
+        <v>2752400</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.008565343026639582</v>
+        <v>-0.004282671513319736</v>
       </c>
       <c r="J16" t="n">
-        <v>23.08222240871853</v>
+        <v>23.09333356221517</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2936338131207863</v>
+        <v>0.6784054686724236</v>
       </c>
       <c r="M16" t="n">
-        <v>23.04000015258789</v>
+        <v>23.05000019073486</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4774282344352685</v>
+        <v>0.8676781241222213</v>
       </c>
       <c r="P16" t="n">
-        <v>23.10961547264686</v>
+        <v>23.11346164116492</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1747504017590203</v>
+        <v>0.5907308950724254</v>
       </c>
       <c r="S16" t="n">
-        <v>23.30719997406006</v>
+        <v>23.30919998168945</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6744712179272593</v>
+        <v>-0.2539768921110866</v>
       </c>
       <c r="V16" t="n">
-        <v>21.96619996388753</v>
+        <v>21.96686663309733</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.389187281318157</v>
+        <v>5.841221637724969</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.64749995231628</v>
+        <v>20.64799995422363</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.12010980502873</v>
+        <v>12.60170501523136</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2474091929860133</v>
+        <v>0.2468584196235508</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5198,13 +5200,13 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.63</v>
+        <v>11.68</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CC16" t="n">
         <v>2</v>
@@ -5258,10 +5260,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.29999923706055</v>
+        <v>20.25</v>
       </c>
       <c r="D17" t="n">
-        <v>20.29999923706055</v>
+        <v>20.25</v>
       </c>
       <c r="E17" t="n">
         <v>20.54000091552734</v>
@@ -5273,67 +5275,67 @@
         <v>20.25</v>
       </c>
       <c r="H17" t="n">
-        <v>4296000</v>
+        <v>6488600</v>
       </c>
       <c r="I17" t="n">
-        <v>0.002964400524747113</v>
+        <v>0.0004940824602235327</v>
       </c>
       <c r="J17" t="n">
-        <v>19.87666659884983</v>
+        <v>19.87111112806532</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.129796946109749</v>
+        <v>1.906732187711168</v>
       </c>
       <c r="M17" t="n">
-        <v>19.80599994659424</v>
+        <v>19.80100002288818</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.494190102990763</v>
+        <v>2.267562126118954</v>
       </c>
       <c r="P17" t="n">
-        <v>18.99038461538462</v>
+        <v>18.98846156780536</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>6.896198514141607</v>
+        <v>6.643710590717658</v>
       </c>
       <c r="S17" t="n">
-        <v>19.43859992980957</v>
+        <v>19.43759994506836</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>4.431385544027789</v>
+        <v>4.179528631248321</v>
       </c>
       <c r="V17" t="n">
-        <v>17.36346662521362</v>
+        <v>17.36313329696655</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>16.91213324638044</v>
+        <v>16.62641559941143</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.61844995975494</v>
+        <v>17.61819996356964</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>15.22012029112067</v>
+        <v>14.9379621179934</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.397263260297812</v>
+        <v>0.3971034306301939</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5481,13 +5483,13 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="CA17" t="n">
         <v>1.13</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="CC17" t="n">
         <v>10</v>
@@ -5537,82 +5539,82 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.47999954223633</v>
+        <v>10.46000003814697</v>
       </c>
       <c r="D18" t="n">
-        <v>10.47999954223633</v>
+        <v>10.46000003814697</v>
       </c>
       <c r="E18" t="n">
         <v>11.13000011444092</v>
       </c>
       <c r="F18" t="n">
-        <v>10.43000030517578</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="G18" t="n">
         <v>11.03999996185303</v>
       </c>
       <c r="H18" t="n">
-        <v>2465300</v>
+        <v>4861500</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05840076958860307</v>
+        <v>-0.06019767020708611</v>
       </c>
       <c r="J18" t="n">
-        <v>11.70111105177138</v>
+        <v>11.69888888465034</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.4358595019931</v>
+        <v>-10.5897992426346</v>
       </c>
       <c r="M18" t="n">
-        <v>11.77199993133545</v>
+        <v>11.76999998092651</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.97519874817526</v>
+        <v>-11.12999103570449</v>
       </c>
       <c r="P18" t="n">
-        <v>10.51499990316538</v>
+        <v>10.51423069146963</v>
       </c>
       <c r="Q18" t="n">
         <v>-1</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.332861257740119</v>
+        <v>-0.5157833693591927</v>
       </c>
       <c r="S18" t="n">
-        <v>10.11339994430542</v>
+        <v>10.11299995422363</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>3.624889749735742</v>
+        <v>3.431227978780107</v>
       </c>
       <c r="V18" t="n">
-        <v>9.081399984359741</v>
+        <v>9.081266654332479</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>15.40070429983589</v>
+        <v>15.18217046469756</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.810949983596801</v>
+        <v>8.810849986076356</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>18.94290129607782</v>
+        <v>18.71726399469679</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9931628293645351</v>
+        <v>0.9941861405460924</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5763,7 +5765,7 @@
         <v>-0.91</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.15</v>
+        <v>5.16</v>
       </c>
       <c r="CB18" t="n">
         <v>-0.53</v>
@@ -5820,13 +5822,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.47000026702881</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="D19" t="n">
-        <v>11.47000026702881</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="E19" t="n">
-        <v>11.51000022888184</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="F19" t="n">
         <v>11.19999980926514</v>
@@ -5835,67 +5837,67 @@
         <v>11.44999980926514</v>
       </c>
       <c r="H19" t="n">
-        <v>3496200</v>
+        <v>5693800</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002622437740028571</v>
+        <v>0.01223779269737202</v>
       </c>
       <c r="J19" t="n">
-        <v>11.29444429609511</v>
+        <v>11.30666648017036</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.55435687078822</v>
+        <v>2.417453844730191</v>
       </c>
       <c r="M19" t="n">
-        <v>11.27099990844727</v>
+        <v>11.28199987411499</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.765596310868554</v>
+        <v>2.641376111648292</v>
       </c>
       <c r="P19" t="n">
-        <v>11.33615376399114</v>
+        <v>11.34038452001718</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.180704724232221</v>
+        <v>2.11293896839142</v>
       </c>
       <c r="S19" t="n">
-        <v>11.83679992675781</v>
+        <v>11.83899991989136</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.09880763380845</v>
+        <v>-2.187684753254726</v>
       </c>
       <c r="V19" t="n">
-        <v>13.11299997965495</v>
+        <v>13.11373331069946</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-12.52954865534418</v>
+        <v>-11.69562740567584</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.9682999753952</v>
+        <v>13.96884997367859</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-17.88549582101676</v>
+        <v>-17.10126498941451</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5937577282851618</v>
+        <v>0.5953410912444945</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6047,7 +6049,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.04</v>
+        <v>6.09</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
@@ -6088,13 +6090,13 @@
         <v>8</v>
       </c>
       <c r="CM19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN19" t="n">
         <v>-1</v>
       </c>
       <c r="CO19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -6107,106 +6109,106 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.11999988555908</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="D20" t="n">
-        <v>11.11999988555908</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="E20" t="n">
         <v>11.13000011444092</v>
       </c>
       <c r="F20" t="n">
-        <v>10.93000030517578</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="G20" t="n">
         <v>11.06999969482422</v>
       </c>
       <c r="H20" t="n">
-        <v>5119800</v>
+        <v>24553000</v>
       </c>
       <c r="I20" t="n">
-        <v>0.006334813901895719</v>
+        <v>-0.02624433998618247</v>
       </c>
       <c r="J20" t="n">
-        <v>11.24666669633653</v>
+        <v>11.20666673448351</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.126260910876932</v>
+        <v>-3.985721322712799</v>
       </c>
       <c r="M20" t="n">
-        <v>11.27200002670288</v>
+        <v>11.23600006103516</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.348475344071295</v>
+        <v>-4.23638153762583</v>
       </c>
       <c r="P20" t="n">
-        <v>11.78346164409931</v>
+        <v>11.76961550345788</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-5.630448662532554</v>
+        <v>-8.578150019254396</v>
       </c>
       <c r="S20" t="n">
-        <v>12.3304001045227</v>
+        <v>12.32320011138916</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.816390455323958</v>
+        <v>-12.68501581064652</v>
       </c>
       <c r="V20" t="n">
-        <v>11.70186670303345</v>
+        <v>11.69946670532227</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.972427324979948</v>
+        <v>-8.029994016847384</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.51610002994537</v>
+        <v>11.51430003166199</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-3.439533725447944</v>
+        <v>-6.550982697219805</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2230158705171651</v>
+        <v>0.2264450918034724</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AH20" t="n">
         <v>10.9</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AI20" t="n">
         <v>11</v>
       </c>
-      <c r="AF20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>11.4</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -6330,13 +6332,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.58</v>
+        <v>6.37</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="CB20" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="CC20" t="n">
         <v>5</v>
@@ -6364,16 +6366,16 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CM20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CN20" t="n">
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6386,10 +6388,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.699999809265137</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="D21" t="n">
-        <v>4.699999809265137</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="E21" t="n">
         <v>4.75</v>
@@ -6401,67 +6403,67 @@
         <v>4.699999809265137</v>
       </c>
       <c r="H21" t="n">
-        <v>11676600</v>
+        <v>14187700</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.00851063052687262</v>
       </c>
       <c r="J21" t="n">
-        <v>4.502222167121039</v>
+        <v>4.497777726915148</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>4.392889439984408</v>
+        <v>3.606717146696876</v>
       </c>
       <c r="M21" t="n">
-        <v>4.479999971389771</v>
+        <v>4.475999975204468</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.910710698221688</v>
+        <v>4.110810393810066</v>
       </c>
       <c r="P21" t="n">
-        <v>4.644615375078642</v>
+        <v>4.643076915007371</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1924439316045</v>
+        <v>0.3644766760171481</v>
       </c>
       <c r="S21" t="n">
-        <v>4.789399995803833</v>
+        <v>4.788599996566773</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.866626020316172</v>
+        <v>-2.685547952363202</v>
       </c>
       <c r="V21" t="n">
-        <v>5.331333335240682</v>
+        <v>5.331066668828329</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-11.84194433693282</v>
+        <v>-12.587852733864</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.309800012111664</v>
+        <v>5.309600012302399</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-11.48442881945783</v>
+        <v>-12.23444634972802</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5078294498137349</v>
+        <v>0.5081903944610863</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6613,13 +6615,13 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>11.46</v>
+        <v>11.37</v>
       </c>
       <c r="CA21" t="n">
         <v>0.01</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CC21" t="n">
         <v>3</v>
@@ -6673,10 +6675,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.519999980926514</v>
+        <v>2.5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.519999980926514</v>
+        <v>2.5</v>
       </c>
       <c r="E22" t="n">
         <v>2.539999961853027</v>
@@ -6688,79 +6690,79 @@
         <v>2.529999971389771</v>
       </c>
       <c r="H22" t="n">
-        <v>18511300</v>
+        <v>33862900</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.003952565445193956</v>
+        <v>-0.01185769633558176</v>
       </c>
       <c r="J22" t="n">
-        <v>2.515555540720622</v>
+        <v>2.513333320617676</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1766782777779136</v>
+        <v>-0.5305034755357873</v>
       </c>
       <c r="M22" t="n">
-        <v>2.513999986648559</v>
+        <v>2.511999988555908</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2386632581471465</v>
+        <v>-0.4777065529688412</v>
       </c>
       <c r="P22" t="n">
-        <v>2.663076923443721</v>
+        <v>2.662307693408086</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-5.372617713655421</v>
+        <v>-6.096503939419254</v>
       </c>
       <c r="S22" t="n">
-        <v>2.87960000038147</v>
+        <v>2.879200000762939</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-12.4878462080608</v>
+        <v>-13.17032511331126</v>
       </c>
       <c r="V22" t="n">
-        <v>3.286951384544373</v>
+        <v>3.286818051338196</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-23.33321409084885</v>
+        <v>-23.93859468484574</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.153077068328857</v>
+        <v>3.152977068424225</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-20.07807210807812</v>
+        <v>-20.70985783447406</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4286005588144843</v>
+        <v>0.4284856272484651</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.3</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.5</v>
       </c>
       <c r="AG22" t="n">
         <v>2.6</v>
@@ -6896,10 +6898,10 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>7.64</v>
+        <v>7.58</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CB22" t="n">
         <v>0.38</v>
@@ -6937,13 +6939,13 @@
         <v>2</v>
       </c>
       <c r="CM22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CN22" t="n">
         <v>0</v>
       </c>
       <c r="CO22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -6956,13 +6958,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42.88999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="D23" t="n">
-        <v>42.88999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="E23" t="n">
-        <v>43.29000091552734</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="F23" t="n">
         <v>42.38999938964844</v>
@@ -6971,67 +6973,67 @@
         <v>42.91999816894531</v>
       </c>
       <c r="H23" t="n">
-        <v>1435000</v>
+        <v>6242500</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.003253529947014444</v>
+        <v>0.008366270522061292</v>
       </c>
       <c r="J23" t="n">
-        <v>43.56555557250977</v>
+        <v>43.62111112806532</v>
       </c>
       <c r="K23" t="n">
         <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.550665827586989</v>
+        <v>-0.5298162574042976</v>
       </c>
       <c r="M23" t="n">
-        <v>43.6810001373291</v>
+        <v>43.7310001373291</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.810857684562689</v>
+        <v>-0.7797689204678997</v>
       </c>
       <c r="P23" t="n">
-        <v>46.99307691133939</v>
+        <v>47.01230768057016</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-8.731238283103115</v>
+        <v>-7.705021237276544</v>
       </c>
       <c r="S23" t="n">
-        <v>48.68739974975586</v>
+        <v>48.69739974975586</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-11.9073936786622</v>
+        <v>-10.89873460878993</v>
       </c>
       <c r="V23" t="n">
-        <v>48.83940002441406</v>
+        <v>48.8427333577474</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-12.18155962561295</v>
+        <v>-11.16385917258263</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.32979999542236</v>
+        <v>46.33229999542236</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-7.424596277371792</v>
+        <v>-6.350430706148027</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2619138703895837</v>
+        <v>0.2662585949720707</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7183,13 +7185,13 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.58</v>
+        <v>8.68</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="CB23" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CC23" t="n">
         <v>3</v>
@@ -7221,16 +7223,16 @@
         <v>0</v>
       </c>
       <c r="CL23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CN23" t="n">
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -7243,13 +7245,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.43000030517578</v>
+        <v>14.5600004196167</v>
       </c>
       <c r="D24" t="n">
-        <v>14.43000030517578</v>
+        <v>14.5600004196167</v>
       </c>
       <c r="E24" t="n">
-        <v>14.48999977111816</v>
+        <v>14.5600004196167</v>
       </c>
       <c r="F24" t="n">
         <v>14.14000034332275</v>
@@ -7258,67 +7260,67 @@
         <v>14.48999977111816</v>
       </c>
       <c r="H24" t="n">
-        <v>13910200</v>
+        <v>49357700</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.001384048744175859</v>
+        <v>0.007612499086749658</v>
       </c>
       <c r="J24" t="n">
-        <v>14.73555543687609</v>
+        <v>14.74999989403619</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.073590866725287</v>
+        <v>-1.288132039216549</v>
       </c>
       <c r="M24" t="n">
-        <v>14.74699993133545</v>
+        <v>14.75999994277954</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.149587222049716</v>
+        <v>-1.355010324784446</v>
       </c>
       <c r="P24" t="n">
-        <v>15.29461530538706</v>
+        <v>15.29961530978863</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-5.653067978157916</v>
+        <v>-4.834205796656401</v>
       </c>
       <c r="S24" t="n">
-        <v>15.60239992141724</v>
+        <v>15.60499992370606</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.514226158452169</v>
+        <v>-6.696568466507094</v>
       </c>
       <c r="V24" t="n">
-        <v>14.17066661198934</v>
+        <v>14.17153327941895</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.830074055704815</v>
+        <v>2.741179324342538</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.52499995231628</v>
+        <v>13.52564995288849</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>6.691315017006766</v>
+        <v>7.647325417491804</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2244712133405255</v>
+        <v>0.2272344143601079</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7470,13 +7472,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>15.86</v>
+        <v>16</v>
       </c>
       <c r="CA24" t="n">
         <v>0.42</v>
       </c>
       <c r="CB24" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CC24" t="n">
         <v>3</v>
@@ -7504,16 +7506,16 @@
         <v>0</v>
       </c>
       <c r="CL24" t="n">
+        <v>6</v>
+      </c>
+      <c r="CM24" t="n">
         <v>5</v>
       </c>
-      <c r="CM24" t="n">
-        <v>4</v>
-      </c>
       <c r="CN24" t="n">
         <v>0</v>
       </c>
       <c r="CO24" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -7526,10 +7528,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.839999914169312</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="D25" t="n">
-        <v>3.839999914169312</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="E25" t="n">
         <v>3.970000028610229</v>
@@ -7541,67 +7543,67 @@
         <v>3.930000066757202</v>
       </c>
       <c r="H25" t="n">
-        <v>68209700</v>
+        <v>97231400</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.02538074659869272</v>
+        <v>-0.0355330210332383</v>
       </c>
       <c r="J25" t="n">
-        <v>4.177777846654256</v>
+        <v>4.173333406448364</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-8.085109952781512</v>
+        <v>-8.945689638772436</v>
       </c>
       <c r="M25" t="n">
-        <v>4.201000046730042</v>
+        <v>4.197000050544739</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.593195156989443</v>
+        <v>-9.459139705679235</v>
       </c>
       <c r="P25" t="n">
-        <v>4.688461532959571</v>
+        <v>4.686923072888301</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-18.09680239084038</v>
+        <v>-18.92335561687496</v>
       </c>
       <c r="S25" t="n">
-        <v>4.990999999046326</v>
+        <v>4.990199999809265</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-23.06151242430267</v>
+        <v>-23.85074841766808</v>
       </c>
       <c r="V25" t="n">
-        <v>5.562400002479553</v>
+        <v>5.5621333360672</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-30.96505263092274</v>
+        <v>-31.68089071731714</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.738849991559983</v>
+        <v>5.738649991750717</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-33.08764090685893</v>
+        <v>-33.78233630246196</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4586683344742613</v>
+        <v>0.4622798086409993</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7616,21 +7618,21 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>3.8</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>4.9</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>5</v>
       </c>
-      <c r="AI25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1</v>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="n">
         <v>-1</v>
       </c>
@@ -7753,13 +7755,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.6</v>
+        <v>-1.58</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7813,10 +7815,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>52.38000106811523</v>
+        <v>52.70999908447266</v>
       </c>
       <c r="D26" t="n">
-        <v>52.38000106811523</v>
+        <v>52.70999908447266</v>
       </c>
       <c r="E26" t="n">
         <v>53.47999954223633</v>
@@ -7828,67 +7830,67 @@
         <v>53.20000076293945</v>
       </c>
       <c r="H26" t="n">
-        <v>3076300</v>
+        <v>4421800</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.01057796700265168</v>
+        <v>-0.004344532455659911</v>
       </c>
       <c r="J26" t="n">
-        <v>52.36999977959527</v>
+        <v>52.40666622585721</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01909736215783379</v>
+        <v>0.5788058666204285</v>
       </c>
       <c r="M26" t="n">
-        <v>52.48299980163574</v>
+        <v>52.51599960327148</v>
       </c>
       <c r="N26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1962516127313623</v>
+        <v>0.369410241958128</v>
       </c>
       <c r="P26" t="n">
-        <v>53.51692287738506</v>
+        <v>53.52961510878343</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.124415508482578</v>
+        <v>-1.531144998231621</v>
       </c>
       <c r="S26" t="n">
-        <v>55.11699996948242</v>
+        <v>55.12359992980957</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.965798034876042</v>
+        <v>-4.378525438124908</v>
       </c>
       <c r="V26" t="n">
-        <v>48.93806660970052</v>
+        <v>48.94026659647623</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>7.033245685542576</v>
+        <v>7.702721603620866</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.55289993286133</v>
+        <v>44.55454992294312</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>17.5681070077344</v>
+        <v>18.30441374816792</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3303156873427982</v>
+        <v>0.3295639782051385</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8040,13 +8042,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.71</v>
+        <v>14.81</v>
       </c>
       <c r="CA26" t="n">
         <v>0.34</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8081,13 +8083,13 @@
         <v>7</v>
       </c>
       <c r="CM26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN26" t="n">
         <v>0</v>
       </c>
       <c r="CO26" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
@@ -8100,10 +8102,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.730000019073486</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="D27" t="n">
-        <v>6.730000019073486</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="E27" t="n">
         <v>6.909999847412109</v>
@@ -8115,67 +8117,67 @@
         <v>6.789999961853027</v>
       </c>
       <c r="H27" t="n">
-        <v>7163400</v>
+        <v>11725800</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.01029414260263606</v>
+        <v>-0.01323531618580209</v>
       </c>
       <c r="J27" t="n">
-        <v>6.510000069936116</v>
+        <v>6.507777849833171</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>3.379415465037452</v>
+        <v>3.107392307790374</v>
       </c>
       <c r="M27" t="n">
-        <v>6.474000072479248</v>
+        <v>6.472000074386597</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.954277783877168</v>
+        <v>3.677378878629462</v>
       </c>
       <c r="P27" t="n">
-        <v>6.452692306958712</v>
+        <v>6.451923076923077</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>4.297550525006756</v>
+        <v>4.000000591249655</v>
       </c>
       <c r="S27" t="n">
-        <v>6.461399974822998</v>
+        <v>6.460999975204468</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>4.156994541385682</v>
+        <v>3.853893575268511</v>
       </c>
       <c r="V27" t="n">
-        <v>8.09033332824707</v>
+        <v>8.090199995040894</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-16.81430484976478</v>
+        <v>-17.0601463219692</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.013099987506866</v>
+        <v>8.012999987602234</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-16.01252911399891</v>
+        <v>-16.26107514627819</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.4942025340029884</v>
+        <v>0.4948551912512092</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8327,10 +8329,10 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>-4.46</v>
+        <v>-4.44</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CB27" t="n">
         <v>0.6899999999999999</v>
@@ -8383,10 +8385,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31.8700008392334</v>
+        <v>31.72999954223633</v>
       </c>
       <c r="D28" t="n">
-        <v>31.8700008392334</v>
+        <v>31.72999954223633</v>
       </c>
       <c r="E28" t="n">
         <v>32.36000061035156</v>
@@ -8398,67 +8400,67 @@
         <v>32.16999816894531</v>
       </c>
       <c r="H28" t="n">
-        <v>1924100</v>
+        <v>2905100</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.009633295929227237</v>
+        <v>-0.01398386447084887</v>
       </c>
       <c r="J28" t="n">
-        <v>31.26222250196669</v>
+        <v>31.24666680230035</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.944130290891741</v>
+        <v>1.546829756255471</v>
       </c>
       <c r="M28" t="n">
-        <v>31.08500022888184</v>
+        <v>31.07100009918213</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.52533570716271</v>
+        <v>2.120946995431749</v>
       </c>
       <c r="P28" t="n">
-        <v>30.83230788891132</v>
+        <v>30.8269232236422</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>3.365602581749255</v>
+        <v>2.929505199213408</v>
       </c>
       <c r="S28" t="n">
-        <v>32.96180011749268</v>
+        <v>32.95900009155273</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.312316907351997</v>
+        <v>-3.728876925581828</v>
       </c>
       <c r="V28" t="n">
-        <v>34.76106657663981</v>
+        <v>34.76013323465983</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-8.316964990220619</v>
+        <v>-8.717267197935003</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.28519994735718</v>
+        <v>34.28449994087219</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-7.044436409389969</v>
+        <v>-7.450890061227127</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.4916767335811524</v>
+        <v>0.4923697338877574</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8606,13 +8608,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>9.210000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8647,13 +8649,13 @@
         <v>8</v>
       </c>
       <c r="CM28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN28" t="n">
         <v>-1</v>
       </c>
       <c r="CO28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
@@ -8666,13 +8668,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.6200008392334</v>
+        <v>17.70999908447266</v>
       </c>
       <c r="D29" t="n">
-        <v>17.6200008392334</v>
+        <v>17.70999908447266</v>
       </c>
       <c r="E29" t="n">
-        <v>17.70000076293945</v>
+        <v>17.70999908447266</v>
       </c>
       <c r="F29" t="n">
         <v>17.36000061035156</v>
@@ -8681,67 +8683,67 @@
         <v>17.44000053405762</v>
       </c>
       <c r="H29" t="n">
-        <v>3325400</v>
+        <v>7987900</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01032111809998337</v>
+        <v>0.01548156778365772</v>
       </c>
       <c r="J29" t="n">
-        <v>17.60888926188151</v>
+        <v>17.6188890669081</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06310209114631893</v>
+        <v>0.5171155639755031</v>
       </c>
       <c r="M29" t="n">
-        <v>17.6100004196167</v>
+        <v>17.61900024414063</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.05678829857129656</v>
+        <v>0.5164812933258975</v>
       </c>
       <c r="P29" t="n">
-        <v>17.6900001672598</v>
+        <v>17.69346163823054</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.3956999851020818</v>
+        <v>0.09346642607446902</v>
       </c>
       <c r="S29" t="n">
-        <v>18.07800014495849</v>
+        <v>18.07980010986328</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-2.533462230626326</v>
+        <v>-2.045382267190463</v>
       </c>
       <c r="V29" t="n">
-        <v>17.08540011088053</v>
+        <v>17.08600009918213</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>3.128991565216038</v>
+        <v>3.652106880886629</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.39150009632111</v>
+        <v>16.3919500875473</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>7.494742614728811</v>
+        <v>8.040830955962075</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1990234637997804</v>
+        <v>0.2023757187569098</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8901,13 +8903,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>12.07</v>
+        <v>12.13</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="CC29" t="n">
         <v>2</v>
@@ -8942,13 +8944,13 @@
         <v>8</v>
       </c>
       <c r="CM29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN29" t="n">
         <v>1</v>
       </c>
       <c r="CO29" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
@@ -8961,10 +8963,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.56999969482422</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="D30" t="n">
-        <v>22.56999969482422</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="E30" t="n">
         <v>22.68000030517578</v>
@@ -8976,67 +8978,67 @@
         <v>22.59000015258789</v>
       </c>
       <c r="H30" t="n">
-        <v>5092700</v>
+        <v>7473400</v>
       </c>
       <c r="I30" t="n">
-        <v>0.00311109754774308</v>
+        <v>0.0008889092339410265</v>
       </c>
       <c r="J30" t="n">
-        <v>22.12555567423503</v>
+        <v>22.12000020345052</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>2.008736083888468</v>
+        <v>1.808319397080095</v>
       </c>
       <c r="M30" t="n">
-        <v>22.08700008392334</v>
+        <v>22.08200016021728</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.186804948909494</v>
+        <v>1.983517318940542</v>
       </c>
       <c r="P30" t="n">
-        <v>22.83692308572622</v>
+        <v>22.83500003814697</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.168823794256415</v>
+        <v>-1.379459513278208</v>
       </c>
       <c r="S30" t="n">
-        <v>24.97299995422363</v>
+        <v>24.97199996948242</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-9.622393239915889</v>
+        <v>-9.818995333634749</v>
       </c>
       <c r="V30" t="n">
-        <v>28.65093326568604</v>
+        <v>28.65059993743897</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.22420765310526</v>
+        <v>-21.39780490831599</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.60419996261597</v>
+        <v>28.60394996643067</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-21.09550442130211</v>
+        <v>-21.26961316813608</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.404870864272684</v>
+        <v>0.4044697099148438</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9184,7 +9186,7 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="CA30" t="n">
         <v>0.48</v>
@@ -9240,13 +9242,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.39000034332275</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="D31" t="n">
-        <v>13.39000034332275</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="E31" t="n">
-        <v>13.47999954223633</v>
+        <v>13.52999973297119</v>
       </c>
       <c r="F31" t="n">
         <v>13.19999980926514</v>
@@ -9255,67 +9257,67 @@
         <v>13.43000030517578</v>
       </c>
       <c r="H31" t="n">
-        <v>2853400</v>
+        <v>4667100</v>
       </c>
       <c r="I31" t="n">
-        <v>0.001495920563565178</v>
+        <v>0.002243809515929396</v>
       </c>
       <c r="J31" t="n">
-        <v>13.19999991522895</v>
+        <v>13.20111094580756</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.439397191772694</v>
+        <v>1.506605569328036</v>
       </c>
       <c r="M31" t="n">
-        <v>13.14399995803833</v>
+        <v>13.14499988555908</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.871579321894168</v>
+        <v>1.939899088560132</v>
       </c>
       <c r="P31" t="n">
-        <v>13.1542308147137</v>
+        <v>13.15461540222168</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.792347511078609</v>
+        <v>1.865384952775973</v>
       </c>
       <c r="S31" t="n">
-        <v>13.50540004730225</v>
+        <v>13.5056000328064</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.8544708307440559</v>
+        <v>-0.7819009449384702</v>
       </c>
       <c r="V31" t="n">
-        <v>15.00693334579468</v>
+        <v>15.00700000762939</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.7745730937429</v>
+        <v>-10.70833869715559</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.03264999866486</v>
+        <v>15.03269999504089</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-10.92721280338461</v>
+        <v>-10.86099221729448</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4624166862767599</v>
+        <v>0.4624701540710189</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9473,7 +9475,7 @@
         <v>0.11</v>
       </c>
       <c r="CB31" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CC31" t="n">
         <v>9</v>
@@ -9523,13 +9525,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>32.77999877929688</v>
+        <v>33.09999847412109</v>
       </c>
       <c r="D32" t="n">
-        <v>32.77999877929688</v>
+        <v>33.09999847412109</v>
       </c>
       <c r="E32" t="n">
-        <v>32.81000137329102</v>
+        <v>33.09999847412109</v>
       </c>
       <c r="F32" t="n">
         <v>31.95000076293945</v>
@@ -9538,86 +9540,88 @@
         <v>32.31999969482422</v>
       </c>
       <c r="H32" t="n">
-        <v>1534200</v>
+        <v>7482300</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01423264507475608</v>
+        <v>0.02413362582493428</v>
       </c>
       <c r="J32" t="n">
-        <v>32.37111155192057</v>
+        <v>32.40666707356771</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.26312384028112</v>
+        <v>2.139471482764404</v>
       </c>
       <c r="M32" t="n">
-        <v>32.36700057983398</v>
+        <v>32.3990005493164</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.275985392728068</v>
+        <v>2.163640584337344</v>
       </c>
       <c r="P32" t="n">
-        <v>33.63384642967811</v>
+        <v>33.64615411024828</v>
       </c>
       <c r="Q32" t="n">
         <v>-1</v>
       </c>
       <c r="R32" t="n">
-        <v>-2.538655970159299</v>
+        <v>-1.623233473690915</v>
       </c>
       <c r="S32" t="n">
-        <v>33.8884001159668</v>
+        <v>33.89480010986328</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-3.270739642110424</v>
+        <v>-2.344907281252573</v>
       </c>
       <c r="V32" t="n">
-        <v>32.23782853444418</v>
+        <v>32.239961865743</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.681782767326969</v>
+        <v>2.667610501400558</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.33504982948303</v>
+        <v>31.33664982795715</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.611286586990823</v>
+        <v>5.627112840220591</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.205061088293506</v>
+        <v>0.2149774723630686</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>27.9</v>
+        <v>29.1</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>29.4</v>
+        <v>32.9</v>
       </c>
       <c r="AG32" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="AH32" t="n">
         <v>39.4</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
       <c r="AI32" t="inlineStr">
         <is>
           <t>Foguete</t>
@@ -9627,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -9748,13 +9752,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>14.57</v>
+        <v>14.71</v>
       </c>
       <c r="CA32" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CC32" t="n">
         <v>2</v>
@@ -9804,10 +9808,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>73.88999938964844</v>
+        <v>73.37999725341797</v>
       </c>
       <c r="D33" t="n">
-        <v>73.88999938964844</v>
+        <v>73.37999725341797</v>
       </c>
       <c r="E33" t="n">
         <v>74.09999847412109</v>
@@ -9819,46 +9823,46 @@
         <v>73.70999908447266</v>
       </c>
       <c r="H33" t="n">
-        <v>2382900</v>
+        <v>6032100</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003940229912223536</v>
+        <v>-0.002989147082394061</v>
       </c>
       <c r="J33" t="n">
-        <v>72.08999888102214</v>
+        <v>72.03333197699652</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>2.496879645673225</v>
+        <v>1.869502964060441</v>
       </c>
       <c r="M33" t="n">
-        <v>71.93099899291992</v>
+        <v>71.87999877929687</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>2.723443889499345</v>
+        <v>2.08680926487875</v>
       </c>
       <c r="P33" t="n">
-        <v>74.95807647705078</v>
+        <v>74.93846101027269</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.424899273835218</v>
+        <v>-2.07965807656643</v>
       </c>
       <c r="S33" t="n">
-        <v>77.5247996520996</v>
+        <v>77.514599609375</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-4.688564535171583</v>
+        <v>-5.333965958403749</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
@@ -9871,7 +9875,7 @@
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
-        <v>0.4860382929229833</v>
+        <v>0.4854081453201791</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10019,13 +10023,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>32.27</v>
+        <v>32.04</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CC33" t="n">
         <v>8</v>
@@ -10060,13 +10064,13 @@
         <v>7</v>
       </c>
       <c r="CM33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
@@ -10079,13 +10083,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.01000022888184</v>
+        <v>25.6299991607666</v>
       </c>
       <c r="D34" t="n">
-        <v>25.01000022888184</v>
+        <v>25.6299991607666</v>
       </c>
       <c r="E34" t="n">
-        <v>25.15999984741211</v>
+        <v>25.6299991607666</v>
       </c>
       <c r="F34" t="n">
         <v>24.67000007629395</v>
@@ -10094,67 +10098,67 @@
         <v>24.95999908447266</v>
       </c>
       <c r="H34" t="n">
-        <v>3433400</v>
+        <v>14286500</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0004000091552733842</v>
+        <v>0.02519996643066413</v>
       </c>
       <c r="J34" t="n">
-        <v>25.03666623433431</v>
+        <v>25.10555500454373</v>
       </c>
       <c r="K34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.1065078121938777</v>
+        <v>2.088956631820954</v>
       </c>
       <c r="M34" t="n">
-        <v>25.0319995880127</v>
+        <v>25.09399948120117</v>
       </c>
       <c r="N34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.08788494524182723</v>
+        <v>2.13596752469436</v>
       </c>
       <c r="P34" t="n">
-        <v>26.11230747516339</v>
+        <v>26.13615358792818</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-4.221408802458405</v>
+        <v>-1.936606415549098</v>
       </c>
       <c r="S34" t="n">
-        <v>25.90099990844726</v>
+        <v>25.91339988708496</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-3.440020395794995</v>
+        <v>-1.093645478992525</v>
       </c>
       <c r="V34" t="n">
-        <v>22.09193333943685</v>
+        <v>22.09606666564941</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>13.20874386415006</v>
+        <v>15.99349127874893</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.46815002441406</v>
+        <v>20.47125001907349</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>22.18984226249237</v>
+        <v>25.19997135927997</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2550142273367397</v>
+        <v>0.2675038065951823</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10306,13 +10310,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>37.33</v>
+        <v>38.25</v>
       </c>
       <c r="CA34" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="CC34" t="n">
         <v>10</v>
@@ -10340,16 +10344,16 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
@@ -10362,10 +10366,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.06000137329102</v>
+        <v>48</v>
       </c>
       <c r="D35" t="n">
-        <v>48.06000137329102</v>
+        <v>48</v>
       </c>
       <c r="E35" t="n">
         <v>48.52999877929688</v>
@@ -10377,67 +10381,67 @@
         <v>48.25</v>
       </c>
       <c r="H35" t="n">
-        <v>939700</v>
+        <v>3589300</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.007024796319605398</v>
+        <v>-0.008264494075791107</v>
       </c>
       <c r="J35" t="n">
-        <v>48.31555642022027</v>
+        <v>48.30888960096571</v>
       </c>
       <c r="K35" t="n">
         <v>-1</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5289291190327714</v>
+        <v>-0.6394053010060049</v>
       </c>
       <c r="M35" t="n">
-        <v>48.31100082397461</v>
+        <v>48.30500068664551</v>
       </c>
       <c r="N35" t="n">
         <v>-1</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.5195492670460966</v>
+        <v>-0.6314060290031783</v>
       </c>
       <c r="P35" t="n">
-        <v>50.77346185537485</v>
+        <v>50.77115411024828</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-5.344249501467836</v>
+        <v>-5.458127077889118</v>
       </c>
       <c r="S35" t="n">
-        <v>52.21300003051758</v>
+        <v>52.21180000305176</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-7.953955250223521</v>
+        <v>-8.066758860651383</v>
       </c>
       <c r="V35" t="n">
-        <v>50.45430895487468</v>
+        <v>50.4539089457194</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-4.745496729972224</v>
+        <v>-4.863664673354496</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.92691337585449</v>
+        <v>48.92661336898804</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-1.771850997229056</v>
+        <v>-1.893884136226291</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2417258199610943</v>
+        <v>0.2417883923043981</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10589,7 +10593,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.71</v>
+        <v>12.7</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
@@ -10623,7 +10627,7 @@
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM35" t="n">
         <v>6</v>
@@ -10632,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
@@ -10645,13 +10649,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.29999923706055</v>
+        <v>38.54999923706055</v>
       </c>
       <c r="D36" t="n">
-        <v>38.29999923706055</v>
+        <v>38.54999923706055</v>
       </c>
       <c r="E36" t="n">
-        <v>38.33000183105469</v>
+        <v>38.54999923706055</v>
       </c>
       <c r="F36" t="n">
         <v>37.65000152587891</v>
@@ -10660,67 +10664,67 @@
         <v>38.29000091552734</v>
       </c>
       <c r="H36" t="n">
-        <v>4234100</v>
+        <v>17971100</v>
       </c>
       <c r="I36" t="n">
-        <v>0.002617761050363931</v>
+        <v>0.009162263537456639</v>
       </c>
       <c r="J36" t="n">
-        <v>38.19666629367404</v>
+        <v>38.22444407145182</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2705286963842141</v>
+        <v>0.8516936570749746</v>
       </c>
       <c r="M36" t="n">
-        <v>38.23799972534179</v>
+        <v>38.2629997253418</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1621410956746866</v>
+        <v>0.7500706002636426</v>
       </c>
       <c r="P36" t="n">
-        <v>40.48807687025804</v>
+        <v>40.49769225487342</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-5.404251825072049</v>
+        <v>-4.809392608238046</v>
       </c>
       <c r="S36" t="n">
-        <v>41.33939994812012</v>
+        <v>41.34439994812012</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-7.352309696981428</v>
+        <v>-6.758837265907959</v>
       </c>
       <c r="V36" t="n">
-        <v>40.06706665039062</v>
+        <v>40.06873331705729</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-4.41027397575372</v>
+        <v>-3.790322164614624</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.07085000991821</v>
+        <v>39.07210000991822</v>
       </c>
       <c r="Z36" t="n">
         <v>-1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-1.972956238889048</v>
+        <v>-1.336249581479207</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2535022477522542</v>
+        <v>0.2560186862837769</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10872,13 +10876,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>31.14</v>
+        <v>31.34</v>
       </c>
       <c r="CA36" t="n">
         <v>0.95</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CC36" t="n">
         <v>8</v>
@@ -10906,16 +10910,16 @@
         <v>0</v>
       </c>
       <c r="CL36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN36" t="n">
         <v>0</v>
       </c>
       <c r="CO36" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
@@ -10928,10 +10932,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15.44999980926514</v>
+        <v>15.39000034332275</v>
       </c>
       <c r="D37" t="n">
-        <v>15.44999980926514</v>
+        <v>15.39000034332275</v>
       </c>
       <c r="E37" t="n">
         <v>15.76000022888184</v>
@@ -10943,67 +10947,67 @@
         <v>15.69999980926514</v>
       </c>
       <c r="H37" t="n">
-        <v>1358100</v>
+        <v>2171800</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.01842439428653342</v>
+        <v>-0.02223630450348768</v>
       </c>
       <c r="J37" t="n">
-        <v>15.73777749803331</v>
+        <v>15.73111089070638</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.828578964241536</v>
+        <v>-2.168381812025418</v>
       </c>
       <c r="M37" t="n">
-        <v>15.72599973678589</v>
+        <v>15.71999979019165</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.755054890883279</v>
+        <v>-2.099233150593276</v>
       </c>
       <c r="P37" t="n">
-        <v>16.00730756612925</v>
+        <v>16.00499989436223</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-3.48158336161009</v>
+        <v>-3.842546423609216</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06819993972778</v>
+        <v>16.06699995040893</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-3.847351494140792</v>
+        <v>-4.213603094390685</v>
       </c>
       <c r="V37" t="n">
-        <v>15.85466669718424</v>
+        <v>15.85426670074463</v>
       </c>
       <c r="W37" t="n">
         <v>-1</v>
       </c>
       <c r="X37" t="n">
-        <v>-2.552351907788612</v>
+        <v>-2.928336997131947</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.70680000305176</v>
+        <v>15.70650000572205</v>
       </c>
       <c r="Z37" t="n">
         <v>-1</v>
       </c>
       <c r="AA37" t="n">
-        <v>-1.634961887441908</v>
+        <v>-2.015087144074027</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2459641246792642</v>
+        <v>0.2482567976356146</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11151,7 +11155,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>13.32</v>
+        <v>13.27</v>
       </c>
       <c r="CA37" t="n">
         <v>0.38</v>
@@ -11180,7 +11184,11 @@
       <c r="CI37" t="n">
         <v>28</v>
       </c>
-      <c r="CJ37" t="inlineStr"/>
+      <c r="CJ37" t="inlineStr">
+        <is>
+          <t>melhor</t>
+        </is>
+      </c>
       <c r="CK37" t="n">
         <v>0</v>
       </c>
@@ -11207,82 +11215,82 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>22.95999908447266</v>
+        <v>22.77000045776367</v>
       </c>
       <c r="D38" t="n">
-        <v>22.95999908447266</v>
+        <v>22.77000045776367</v>
       </c>
       <c r="E38" t="n">
         <v>23.47999954223633</v>
       </c>
       <c r="F38" t="n">
-        <v>22.84000015258789</v>
+        <v>22.73999977111816</v>
       </c>
       <c r="G38" t="n">
         <v>23.47999954223633</v>
       </c>
       <c r="H38" t="n">
-        <v>11935400</v>
+        <v>25828200</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.02297876236286567</v>
+        <v>-0.03106381030792882</v>
       </c>
       <c r="J38" t="n">
-        <v>23.55444441901313</v>
+        <v>23.53333346048991</v>
       </c>
       <c r="K38" t="n">
         <v>-1</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.523707729912059</v>
+        <v>-3.243624639950805</v>
       </c>
       <c r="M38" t="n">
-        <v>23.525</v>
+        <v>23.5060001373291</v>
       </c>
       <c r="N38" t="n">
         <v>-1</v>
       </c>
       <c r="O38" t="n">
-        <v>-2.40170421053068</v>
+        <v>-3.13111407838637</v>
       </c>
       <c r="P38" t="n">
-        <v>23.23576927185059</v>
+        <v>23.22846163236178</v>
       </c>
       <c r="Q38" t="n">
         <v>-1</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.186834763900056</v>
+        <v>-1.973704422850718</v>
       </c>
       <c r="S38" t="n">
-        <v>21.55480007171631</v>
+        <v>21.55100009918213</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>6.519192978274092</v>
+        <v>5.656351691204364</v>
       </c>
       <c r="V38" t="n">
-        <v>20.68713334401449</v>
+        <v>20.68586668650309</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>10.98685691565762</v>
+        <v>10.07515809149255</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.7393500328064</v>
+        <v>19.73840003967285</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>16.31588196325415</v>
+        <v>15.35889642522955</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.2663485207639401</v>
+        <v>0.273827224236368</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11432,7 +11440,7 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>27.66</v>
+        <v>27.43</v>
       </c>
       <c r="CA38" t="n">
         <v>0.18</v>
@@ -11469,13 +11477,13 @@
         <v>10</v>
       </c>
       <c r="CM38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN38" t="n">
         <v>0</v>
       </c>
       <c r="CO38" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
@@ -11488,82 +11496,82 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9.930000305175781</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="D39" t="n">
-        <v>9.930000305175781</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="E39" t="n">
         <v>10.28999996185303</v>
       </c>
       <c r="F39" t="n">
-        <v>9.909999847412109</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="G39" t="n">
         <v>10.28999996185303</v>
       </c>
       <c r="H39" t="n">
-        <v>6786200</v>
+        <v>12566100</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.02837572938120259</v>
+        <v>-0.0410958968023637</v>
       </c>
       <c r="J39" t="n">
-        <v>10.22444449530708</v>
+        <v>10.21000003814697</v>
       </c>
       <c r="K39" t="n">
         <v>-1</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.879806235599805</v>
+        <v>-4.015669401373683</v>
       </c>
       <c r="M39" t="n">
-        <v>10.21700000762939</v>
+        <v>10.2039999961853</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.809040836246457</v>
+        <v>-3.959229768732576</v>
       </c>
       <c r="P39" t="n">
-        <v>10.11576927625216</v>
+        <v>10.11076927185059</v>
       </c>
       <c r="Q39" t="n">
         <v>-1</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.836429499360867</v>
+        <v>-3.07364427730475</v>
       </c>
       <c r="S39" t="n">
-        <v>9.481600008010865</v>
+        <v>9.479000005722046</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>4.729162765631004</v>
+        <v>3.386435117829348</v>
       </c>
       <c r="V39" t="n">
-        <v>9.104525750478109</v>
+        <v>9.103659083048502</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>9.066639793449143</v>
+        <v>7.64902443439458</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.626339161396027</v>
+        <v>8.625689160823821</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>15.11256535812787</v>
+        <v>13.61411254238712</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.2737197776891691</v>
+        <v>0.2879318490193298</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11719,13 +11727,13 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.09</v>
+        <v>22.79</v>
       </c>
       <c r="CA39" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="CB39" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CC39" t="n">
         <v>1</v>
@@ -11740,7 +11748,7 @@
         <v>3</v>
       </c>
       <c r="CG39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CH39" t="n">
         <v>10</v>
@@ -11760,13 +11768,13 @@
         <v>10</v>
       </c>
       <c r="CM39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
       </c>
       <c r="CO39" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40">
@@ -11779,10 +11787,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11.89000034332275</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="D40" t="n">
-        <v>11.89000034332275</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="E40" t="n">
         <v>12.52999973297119</v>
@@ -11794,67 +11802,67 @@
         <v>12.5</v>
       </c>
       <c r="H40" t="n">
-        <v>6420800</v>
+        <v>11148400</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.04727557857008147</v>
+        <v>-0.02644230254890867</v>
       </c>
       <c r="J40" t="n">
-        <v>12.46000003814697</v>
+        <v>12.48888884650336</v>
       </c>
       <c r="K40" t="n">
         <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>-4.574636381052436</v>
+        <v>-2.71352585596895</v>
       </c>
       <c r="M40" t="n">
-        <v>12.49700002670288</v>
+        <v>12.52299995422363</v>
       </c>
       <c r="N40" t="n">
         <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>-4.8571631758272</v>
+        <v>-2.97852221557788</v>
       </c>
       <c r="P40" t="n">
-        <v>12.41769233116737</v>
+        <v>12.42769230329073</v>
       </c>
       <c r="Q40" t="n">
         <v>-1</v>
       </c>
       <c r="R40" t="n">
-        <v>-4.249517331977628</v>
+        <v>-2.23446701111943</v>
       </c>
       <c r="S40" t="n">
-        <v>11.69599998474121</v>
+        <v>11.70119997024536</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1.658689798517768</v>
+        <v>3.835501054816179</v>
       </c>
       <c r="V40" t="n">
-        <v>14.94679999669393</v>
+        <v>14.94853332519531</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-20.45119794235092</v>
+        <v>-18.72112565015454</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.6045499753952</v>
+        <v>20.60584997177124</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-42.29429733956274</v>
+        <v>-41.0361638312662</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6960072680027475</v>
+        <v>0.6865591043647564</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12002,13 +12010,13 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-13.99</v>
+        <v>-14.29</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="CC40" t="n">
         <v>9</v>
@@ -12040,16 +12048,16 @@
         <v>0</v>
       </c>
       <c r="CL40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CM40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CN40" t="n">
         <v>-1</v>
       </c>
       <c r="CO40" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
@@ -12062,10 +12070,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>22.04000091552734</v>
+        <v>21.90999984741211</v>
       </c>
       <c r="D41" t="n">
-        <v>22.04000091552734</v>
+        <v>21.90999984741211</v>
       </c>
       <c r="E41" t="n">
         <v>22.46999931335449</v>
@@ -12077,88 +12085,88 @@
         <v>22.35000038146973</v>
       </c>
       <c r="H41" t="n">
-        <v>1721400</v>
+        <v>2766100</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.01651043883998482</v>
+        <v>-0.02231146824651764</v>
       </c>
       <c r="J41" t="n">
-        <v>22.47222222222222</v>
+        <v>22.45777765909831</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.923358101485241</v>
+        <v>-2.439145226216442</v>
       </c>
       <c r="M41" t="n">
-        <v>22.50499992370606</v>
+        <v>22.49199981689453</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-2.066203109331702</v>
+        <v>-2.587586582875839</v>
       </c>
       <c r="P41" t="n">
-        <v>22.76807697002704</v>
+        <v>22.76307692894569</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-3.197793364183422</v>
+        <v>-3.747635190956097</v>
       </c>
       <c r="S41" t="n">
-        <v>22.89880001068115</v>
+        <v>22.89619998931885</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-3.750410915651573</v>
+        <v>-4.307265582790177</v>
       </c>
       <c r="V41" t="n">
-        <v>23.66793337504069</v>
+        <v>23.66706670125325</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-6.878219714908029</v>
+        <v>-7.424100654383597</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.49654998779297</v>
+        <v>23.49589998245239</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-6.198991226466593</v>
+        <v>-6.749688823261472</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.2999613122900693</v>
+        <v>0.3028701873188357</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
       <c r="AD41" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AE41" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AF41" t="n">
         <v>20.3</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AG41" t="n">
         <v>22</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>22.3</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>22.4</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>22.5</v>
       </c>
       <c r="AJ41" t="n">
         <v>2</v>
@@ -12285,13 +12293,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>9.220000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="CA41" t="n">
         <v>0.4</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CC41" t="n">
         <v>4</v>
@@ -12341,10 +12349,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>25.85000038146973</v>
+        <v>25.94000053405762</v>
       </c>
       <c r="D42" t="n">
-        <v>25.85000038146973</v>
+        <v>25.94000053405762</v>
       </c>
       <c r="E42" t="n">
         <v>26.29999923706055</v>
@@ -12356,67 +12364,67 @@
         <v>26.29999923706055</v>
       </c>
       <c r="H42" t="n">
-        <v>732700</v>
+        <v>2116200</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.01298205978063083</v>
+        <v>-0.009545627907677878</v>
       </c>
       <c r="J42" t="n">
-        <v>26.22555541992188</v>
+        <v>26.23555543687608</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.432019388870077</v>
+        <v>-1.126543341266719</v>
       </c>
       <c r="M42" t="n">
-        <v>26.23299980163574</v>
+        <v>26.24199981689453</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.459990939130545</v>
+        <v>-1.150824193827206</v>
       </c>
       <c r="P42" t="n">
-        <v>27.0719228891226</v>
+        <v>27.0753844334529</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.513615499931238</v>
+        <v>-4.193417464434828</v>
       </c>
       <c r="S42" t="n">
-        <v>27.65379985809326</v>
+        <v>27.65559986114502</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-6.522790668478887</v>
+        <v>-6.20344283147425</v>
       </c>
       <c r="V42" t="n">
-        <v>26.98206656138102</v>
+        <v>26.98266656239828</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-4.195624443131432</v>
+        <v>-3.864206771148656</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.04949990272522</v>
+        <v>26.04994990348816</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.7658477974643277</v>
+        <v>-0.4220713277295748</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.2840751862217111</v>
+        <v>0.283416302608669</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12568,7 +12576,7 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>10.77</v>
+        <v>10.81</v>
       </c>
       <c r="CA42" t="n">
         <v>0.04</v>
@@ -12624,10 +12632,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>26.81999969482422</v>
+        <v>27.03000068664551</v>
       </c>
       <c r="D43" t="n">
-        <v>26.81999969482422</v>
+        <v>27.03000068664551</v>
       </c>
       <c r="E43" t="n">
         <v>27.23999977111816</v>
@@ -12639,67 +12647,67 @@
         <v>27.07999992370605</v>
       </c>
       <c r="H43" t="n">
-        <v>2387400</v>
+        <v>4753800</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.009966794250382383</v>
+        <v>-0.002214819697468728</v>
       </c>
       <c r="J43" t="n">
-        <v>27.81777784559462</v>
+        <v>27.84111128913032</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-3.586836289759265</v>
+        <v>-2.913355699280159</v>
       </c>
       <c r="M43" t="n">
-        <v>27.87000007629394</v>
+        <v>27.89100017547607</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-3.767493285236299</v>
+        <v>-3.08701546525256</v>
       </c>
       <c r="P43" t="n">
-        <v>28.85307693481445</v>
+        <v>28.86115389603835</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-7.046309981370133</v>
+        <v>-6.344698538349834</v>
       </c>
       <c r="S43" t="n">
-        <v>29.16300003051758</v>
+        <v>29.167200050354</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-8.034154007617637</v>
+        <v>-7.327406676056852</v>
       </c>
       <c r="V43" t="n">
-        <v>27.9921999613444</v>
+        <v>27.99359996795654</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-4.187596073688107</v>
+        <v>-3.442212800118733</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.83055000305176</v>
+        <v>26.83160000801086</v>
       </c>
       <c r="Z43" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>-0.03932199759729026</v>
+        <v>0.7394291752091198</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2418278398031297</v>
+        <v>0.2416324509419899</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12851,13 +12859,13 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>7.53</v>
+        <v>7.59</v>
       </c>
       <c r="CA43" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="CC43" t="n">
         <v>7</v>
@@ -12885,7 +12893,7 @@
         <v>0</v>
       </c>
       <c r="CL43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM43" t="n">
         <v>3</v>
@@ -12894,7 +12902,7 @@
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
@@ -12907,10 +12915,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12.96000003814697</v>
+        <v>12.92000007629395</v>
       </c>
       <c r="D44" t="n">
-        <v>12.96000003814697</v>
+        <v>12.92000007629395</v>
       </c>
       <c r="E44" t="n">
         <v>13.02000045776367</v>
@@ -12922,67 +12930,67 @@
         <v>12.94999980926514</v>
       </c>
       <c r="H44" t="n">
-        <v>18619500</v>
+        <v>48529700</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0007710276542751693</v>
+        <v>-0.00385506474213182</v>
       </c>
       <c r="J44" t="n">
-        <v>12.95777765909831</v>
+        <v>12.95333321889242</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.01715092747486304</v>
+        <v>-0.2573325493538166</v>
       </c>
       <c r="M44" t="n">
-        <v>12.94599990844727</v>
+        <v>12.94199991226196</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1081425135077533</v>
+        <v>-0.1699879162197623</v>
       </c>
       <c r="P44" t="n">
-        <v>13.32461540515606</v>
+        <v>13.32307694508479</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.736404435868368</v>
+        <v>-3.025403744587325</v>
       </c>
       <c r="S44" t="n">
-        <v>13.68780000686646</v>
+        <v>13.6870000076294</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-5.317143502640185</v>
+        <v>-5.603857170365379</v>
       </c>
       <c r="V44" t="n">
-        <v>12.92867959340413</v>
+        <v>12.92841292699178</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X44" t="n">
-        <v>0.2422555568537553</v>
+        <v>-0.06507257112952626</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.41719584941864</v>
+        <v>12.41699584960937</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.371391055684656</v>
+        <v>4.050933355996849</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2284187248162591</v>
+        <v>0.2281253009182956</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13134,7 +13142,7 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.58</v>
+        <v>8.56</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
@@ -13190,10 +13198,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39.97999954223633</v>
+        <v>40.04000091552734</v>
       </c>
       <c r="D45" t="n">
-        <v>39.97999954223633</v>
+        <v>40.04000091552734</v>
       </c>
       <c r="E45" t="n">
         <v>40.15999984741211</v>
@@ -13205,67 +13213,67 @@
         <v>39.86999893188477</v>
       </c>
       <c r="H45" t="n">
-        <v>45062300</v>
+        <v>80299300</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0005000114440918413</v>
+        <v>0.001000022888183683</v>
       </c>
       <c r="J45" t="n">
-        <v>39.8533329433865</v>
+        <v>39.85999976264106</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3178318837969185</v>
+        <v>0.4515834268895072</v>
       </c>
       <c r="M45" t="n">
-        <v>39.82999954223633</v>
+        <v>39.83599967956543</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3766005566757196</v>
+        <v>0.5121027151392342</v>
       </c>
       <c r="P45" t="n">
-        <v>41.13923058143029</v>
+        <v>41.14153832655687</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.817823821229227</v>
+        <v>-2.677433697996856</v>
       </c>
       <c r="S45" t="n">
-        <v>42.56759979248047</v>
+        <v>42.56879981994629</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-6.078802335247572</v>
+        <v>-5.940498475679457</v>
       </c>
       <c r="V45" t="n">
-        <v>41.87813499450684</v>
+        <v>41.87853500366211</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-4.532521451873365</v>
+        <v>-4.390158557299085</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.59437786102295</v>
+        <v>40.5946778678894</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-1.513456668531731</v>
+        <v>-1.366378504510343</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2298607165344155</v>
+        <v>0.2301740576421104</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13437,7 +13445,7 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.5</v>
+        <v>9.51</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
@@ -13493,10 +13501,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.69000053405762</v>
+        <v>16.67000007629395</v>
       </c>
       <c r="D46" t="n">
-        <v>16.69000053405762</v>
+        <v>16.67000007629395</v>
       </c>
       <c r="E46" t="n">
         <v>16.79999923706055</v>
@@ -13508,67 +13516,67 @@
         <v>16.79999923706055</v>
       </c>
       <c r="H46" t="n">
-        <v>2529900</v>
+        <v>8034100</v>
       </c>
       <c r="I46" t="n">
-        <v>0.001199787502827565</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>16.54333347744412</v>
+        <v>16.54111120435927</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8865628974563725</v>
+        <v>0.779203224875906</v>
       </c>
       <c r="M46" t="n">
-        <v>16.51900005340576</v>
+        <v>16.5170000076294</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.035174526902431</v>
+        <v>0.9263187539739515</v>
       </c>
       <c r="P46" t="n">
-        <v>16.99884627415584</v>
+        <v>16.99807702578031</v>
       </c>
       <c r="Q46" t="n">
         <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.816862951268486</v>
+        <v>-1.930082732233681</v>
       </c>
       <c r="S46" t="n">
-        <v>17.982200050354</v>
+        <v>17.98180004119873</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-7.185992329514468</v>
+        <v>-7.295153777148424</v>
       </c>
       <c r="V46" t="n">
-        <v>18.50043023427327</v>
+        <v>18.50029689788818</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.785878908165692</v>
+        <v>-9.893337559372723</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.3646789264679</v>
+        <v>18.36457892417908</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-9.119018084202205</v>
+        <v>-9.227430995730728</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.1727996003822144</v>
+        <v>0.1724884567653878</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13724,7 +13732,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>27.82</v>
+        <v>27.78</v>
       </c>
       <c r="CA46" t="n">
         <v>0.24</v>
@@ -13784,10 +13792,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.03999996185303</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="D47" t="n">
-        <v>15.03999996185303</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="E47" t="n">
         <v>15.10000038146973</v>
@@ -13799,88 +13807,88 @@
         <v>15.02000045776367</v>
       </c>
       <c r="H47" t="n">
-        <v>4116000</v>
+        <v>8752300</v>
       </c>
       <c r="I47" t="n">
-        <v>0.002666664123535112</v>
+        <v>-0.006666692097981763</v>
       </c>
       <c r="J47" t="n">
-        <v>14.84666665395101</v>
+        <v>14.83111106024848</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1.302200099242934</v>
+        <v>0.4644868344788565</v>
       </c>
       <c r="M47" t="n">
-        <v>14.73900003433227</v>
+        <v>14.725</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>2.0422004669219</v>
+        <v>1.18845241786264</v>
       </c>
       <c r="P47" t="n">
-        <v>14.24538469314575</v>
+        <v>14.24000006455642</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>5.578054126468126</v>
+        <v>4.634828307456313</v>
       </c>
       <c r="S47" t="n">
-        <v>14.70360004425049</v>
+        <v>14.70080003738403</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>2.287874510937078</v>
+        <v>1.355025445143648</v>
       </c>
       <c r="V47" t="n">
-        <v>14.68586669921875</v>
+        <v>14.6849333635966</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>2.411388240730231</v>
+        <v>1.46453681204176</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.9188500213623</v>
+        <v>14.91815001964569</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.812059510734728</v>
+        <v>-0.1216665678486577</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4696917828807515</v>
+        <v>0.4698723739009605</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AF47" t="n">
         <v>14.8</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AG47" t="n">
         <v>14.9</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>15</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AI47" t="n">
         <v>15.1</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>15.3</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14007,13 +14015,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>10.16</v>
+        <v>10.07</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14028,7 +14036,7 @@
         <v>7</v>
       </c>
       <c r="CG47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CH47" t="n">
         <v>10</v>
@@ -14041,7 +14049,7 @@
         <v>1</v>
       </c>
       <c r="CL47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CM47" t="n">
         <v>9</v>
@@ -14050,7 +14058,7 @@
         <v>0</v>
       </c>
       <c r="CO47" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -14063,10 +14071,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.82999992370605</v>
+        <v>16.01000022888184</v>
       </c>
       <c r="D48" t="n">
-        <v>15.82999992370605</v>
+        <v>16.01000022888184</v>
       </c>
       <c r="E48" t="n">
         <v>16.36000061035156</v>
@@ -14078,67 +14086,67 @@
         <v>16.25</v>
       </c>
       <c r="H48" t="n">
-        <v>6152100</v>
+        <v>17767700</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.02823824223256022</v>
+        <v>-0.01718850036273578</v>
       </c>
       <c r="J48" t="n">
-        <v>16.56444464789497</v>
+        <v>16.58444468180339</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-4.433862648587169</v>
+        <v>-3.463754523851116</v>
       </c>
       <c r="M48" t="n">
-        <v>16.58900012969971</v>
+        <v>16.60700016021729</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-4.575322201817297</v>
+        <v>-3.594869185137882</v>
       </c>
       <c r="P48" t="n">
-        <v>17.1750001173753</v>
+        <v>17.18192320603591</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-7.831151001324073</v>
+        <v>-6.820674048539469</v>
       </c>
       <c r="S48" t="n">
-        <v>18.46000011444092</v>
+        <v>18.46360012054443</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-14.24702152995904</v>
+        <v>-13.28884873829389</v>
       </c>
       <c r="V48" t="n">
-        <v>18.87600007375081</v>
+        <v>18.87720007578532</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-16.13689414146889</v>
+        <v>-15.18869236641389</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.51130004405975</v>
+        <v>19.51220004558563</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-18.86752862208418</v>
+        <v>-17.94876953148152</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.393952949741052</v>
+        <v>0.3900096462158647</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14286,13 +14294,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>58.63</v>
+        <v>59.3</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14324,16 +14332,16 @@
         <v>0</v>
       </c>
       <c r="CL48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN48" t="n">
         <v>0</v>
       </c>
       <c r="CO48" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49">
@@ -14346,82 +14354,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.090000152587891</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="D49" t="n">
-        <v>6.090000152587891</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="E49" t="n">
         <v>6.429999828338623</v>
       </c>
       <c r="F49" t="n">
-        <v>6.010000228881836</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="G49" t="n">
         <v>6.380000114440918</v>
       </c>
       <c r="H49" t="n">
-        <v>14455100</v>
+        <v>19886600</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.04094484345661142</v>
+        <v>-0.05826769938833432</v>
       </c>
       <c r="J49" t="n">
-        <v>6.56444443596734</v>
+        <v>6.552222198910183</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-7.227485707395352</v>
+        <v>-8.73325358123345</v>
       </c>
       <c r="M49" t="n">
-        <v>6.569000005722046</v>
+        <v>6.557999992370606</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-7.291822997669567</v>
+        <v>-8.81366230511663</v>
       </c>
       <c r="P49" t="n">
-        <v>7.319999914902907</v>
+        <v>7.315769140536968</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-16.80327563680486</v>
+        <v>-18.25876535745137</v>
       </c>
       <c r="S49" t="n">
-        <v>8.062599964141846</v>
+        <v>8.060399961471557</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-24.46605090575037</v>
+        <v>-25.81013290087729</v>
       </c>
       <c r="V49" t="n">
-        <v>8.826114075978596</v>
+        <v>8.825380741755168</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-31.00021028322522</v>
+        <v>-32.24088349207923</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.718014013767242</v>
+        <v>8.71746401309967</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-30.14463910047937</v>
+        <v>-31.40206819222444</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4377025514603108</v>
+        <v>0.4497007297331133</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14573,13 +14581,13 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>33.83</v>
+        <v>33.22</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="CC49" t="n">
         <v>2</v>
@@ -14633,13 +14641,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.09000015258789</v>
+        <v>14.10999965667725</v>
       </c>
       <c r="D50" t="n">
-        <v>14.09000015258789</v>
+        <v>14.10999965667725</v>
       </c>
       <c r="E50" t="n">
-        <v>14.14000034332275</v>
+        <v>14.23999977111816</v>
       </c>
       <c r="F50" t="n">
         <v>13.76000022888184</v>
@@ -14648,67 +14656,67 @@
         <v>14.09000015258789</v>
       </c>
       <c r="H50" t="n">
-        <v>8880600</v>
+        <v>21315900</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.002830853611398565</v>
+        <v>-0.001415460552136261</v>
       </c>
       <c r="J50" t="n">
-        <v>14.57555558946398</v>
+        <v>14.57777775658501</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-3.331299681139234</v>
+        <v>-3.208843677812728</v>
       </c>
       <c r="M50" t="n">
-        <v>14.59200000762939</v>
+        <v>14.59399995803833</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-3.440240232860707</v>
+        <v>-3.316433484669827</v>
       </c>
       <c r="P50" t="n">
-        <v>15.22884610983042</v>
+        <v>15.22961532152616</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-7.478215677203445</v>
+        <v>-7.351568908417565</v>
       </c>
       <c r="S50" t="n">
-        <v>15.69560005187988</v>
+        <v>15.69600004196167</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-10.22961781636177</v>
+        <v>-10.1044876468171</v>
       </c>
       <c r="V50" t="n">
-        <v>15.84006669362386</v>
+        <v>15.84020002365112</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-11.04835336167131</v>
+        <v>-10.9228441837256</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.44050001144409</v>
+        <v>15.44060000896454</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-8.746477496552874</v>
+        <v>-8.617543045702694</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.2990976192368708</v>
+        <v>0.2993044309685574</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14856,7 +14864,7 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.49</v>
+        <v>8.5</v>
       </c>
       <c r="CA50" t="n">
         <v>1.08</v>
@@ -14916,10 +14924,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.809999942779541</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="D51" t="n">
-        <v>5.809999942779541</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="E51" t="n">
         <v>5.980000019073486</v>
@@ -14931,67 +14939,67 @@
         <v>5.96999979019165</v>
       </c>
       <c r="H51" t="n">
-        <v>4605100</v>
+        <v>7496800</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.02680064539951565</v>
+        <v>-0.02010048404963671</v>
       </c>
       <c r="J51" t="n">
-        <v>6.108888891008165</v>
+        <v>6.113333331214057</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-4.892689219942548</v>
+        <v>-4.307526063349678</v>
       </c>
       <c r="M51" t="n">
-        <v>6.111999988555908</v>
+        <v>6.115999984741211</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-4.94110023465038</v>
+        <v>-4.349249195099496</v>
       </c>
       <c r="P51" t="n">
-        <v>6.5</v>
+        <v>6.50153846007127</v>
       </c>
       <c r="Q51" t="n">
         <v>-1</v>
       </c>
       <c r="R51" t="n">
-        <v>-10.61538549569937</v>
+        <v>-10.02129818103944</v>
       </c>
       <c r="S51" t="n">
-        <v>7.097399997711181</v>
+        <v>7.098199996948242</v>
       </c>
       <c r="T51" t="n">
         <v>-1</v>
       </c>
       <c r="U51" t="n">
-        <v>-18.1390376102067</v>
+        <v>-17.58474110129776</v>
       </c>
       <c r="V51" t="n">
-        <v>7.949133358001709</v>
+        <v>7.949400024414063</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-26.91027208731989</v>
+        <v>-26.40954176835802</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.782100007534027</v>
+        <v>7.782300007343292</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-25.34148960878492</v>
+        <v>-24.82942190467377</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4449643633126337</v>
+        <v>0.4431175675651919</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15143,10 +15151,10 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>-4.3</v>
+        <v>-4.33</v>
       </c>
       <c r="CA51" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CB51" t="n">
         <v>0.63</v>
@@ -15203,10 +15211,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>29.54000091552734</v>
+        <v>29.79000091552734</v>
       </c>
       <c r="D52" t="n">
-        <v>29.54000091552734</v>
+        <v>29.79000091552734</v>
       </c>
       <c r="E52" t="n">
         <v>30.04000091552734</v>
@@ -15218,67 +15226,67 @@
         <v>29.85000038146973</v>
       </c>
       <c r="H52" t="n">
-        <v>1495600</v>
+        <v>2666700</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.01270050667772826</v>
+        <v>-0.00434489172577246</v>
       </c>
       <c r="J52" t="n">
-        <v>29.84333356221517</v>
+        <v>29.87111133999295</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.01641676877504</v>
+        <v>-0.2715346728898171</v>
       </c>
       <c r="M52" t="n">
-        <v>29.83400020599365</v>
+        <v>29.85900020599365</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.9854504539664296</v>
+        <v>-0.2310837268170092</v>
       </c>
       <c r="P52" t="n">
-        <v>30.78769221672645</v>
+        <v>30.79730760134183</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-4.052565201757</v>
+        <v>-3.270762168088365</v>
       </c>
       <c r="S52" t="n">
-        <v>31.57119998931885</v>
+        <v>31.57619998931885</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-6.433708805742891</v>
+        <v>-5.656789209580997</v>
       </c>
       <c r="V52" t="n">
-        <v>30.6221333694458</v>
+        <v>30.62380003611247</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-3.533824508119312</v>
+        <v>-2.722716056145492</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.89020005226135</v>
+        <v>29.89145005226135</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-1.171618577733522</v>
+        <v>-0.3393918212620567</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.2940585786386757</v>
+        <v>0.2931777518042438</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15430,13 +15438,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>12.41</v>
+        <v>12.52</v>
       </c>
       <c r="CA52" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15471,13 +15479,13 @@
         <v>6</v>
       </c>
       <c r="CM52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN52" t="n">
         <v>0</v>
       </c>
       <c r="CO52" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
@@ -15490,10 +15498,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.880000114440918</v>
+        <v>9.949999809265137</v>
       </c>
       <c r="D53" t="n">
-        <v>9.880000114440918</v>
+        <v>9.949999809265137</v>
       </c>
       <c r="E53" t="n">
         <v>10.05000019073486</v>
@@ -15505,67 +15513,67 @@
         <v>9.970000267028809</v>
       </c>
       <c r="H53" t="n">
-        <v>11707100</v>
+        <v>21574200</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.02178220383361951</v>
+        <v>-0.01485154124150267</v>
       </c>
       <c r="J53" t="n">
-        <v>10.10222223069933</v>
+        <v>10.10999997456869</v>
       </c>
       <c r="K53" t="n">
         <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.199734980914453</v>
+        <v>-1.582593132601612</v>
       </c>
       <c r="M53" t="n">
-        <v>10.06700000762939</v>
+        <v>10.07399997711182</v>
       </c>
       <c r="N53" t="n">
         <v>-1</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.857553323202108</v>
+        <v>-1.230893072547234</v>
       </c>
       <c r="P53" t="n">
-        <v>10.15384611716637</v>
+        <v>10.15653841312115</v>
       </c>
       <c r="Q53" t="n">
         <v>-1</v>
       </c>
       <c r="R53" t="n">
-        <v>-2.696968218402313</v>
+        <v>-2.03355312070881</v>
       </c>
       <c r="S53" t="n">
-        <v>10.0803999710083</v>
+        <v>10.08179996490479</v>
       </c>
       <c r="T53" t="n">
         <v>-1</v>
       </c>
       <c r="U53" t="n">
-        <v>-1.988014931389057</v>
+        <v>-1.30730778331698</v>
       </c>
       <c r="V53" t="n">
-        <v>8.935733289718629</v>
+        <v>8.936199954350789</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>10.56731209523402</v>
+        <v>11.344865380063</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.914099957942963</v>
+        <v>8.914449956417084</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>10.83564421596242</v>
+        <v>11.61653111421205</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3401634791776192</v>
+        <v>0.3370631160836532</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15717,13 +15725,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>-5.85</v>
+        <v>-5.89</v>
       </c>
       <c r="CA53" t="n">
         <v>0.29</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CC53" t="n">
         <v>3</v>
@@ -15758,13 +15766,13 @@
         <v>8</v>
       </c>
       <c r="CM53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
@@ -15777,82 +15785,82 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47.13000106811523</v>
+        <v>46.72999954223633</v>
       </c>
       <c r="D54" t="n">
-        <v>47.13000106811523</v>
+        <v>46.72999954223633</v>
       </c>
       <c r="E54" t="n">
-        <v>47.52000045776367</v>
+        <v>47.59000015258789</v>
       </c>
       <c r="F54" t="n">
-        <v>46.88999938964844</v>
+        <v>46.72999954223633</v>
       </c>
       <c r="G54" t="n">
         <v>47.15999984741211</v>
       </c>
       <c r="H54" t="n">
-        <v>5897000</v>
+        <v>23751300</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.008624312989405025</v>
+        <v>-0.01703831210963347</v>
       </c>
       <c r="J54" t="n">
-        <v>49.12777752346463</v>
+        <v>49.08333290947808</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-4.066490600750682</v>
+        <v>-4.794567173304809</v>
       </c>
       <c r="M54" t="n">
-        <v>49.3939998626709</v>
+        <v>49.35399971008301</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-4.583550230494007</v>
+        <v>-5.316692027516867</v>
       </c>
       <c r="P54" t="n">
-        <v>50.89230786837064</v>
+        <v>50.87692319429838</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-7.392682623052485</v>
+        <v>-8.150893158819759</v>
       </c>
       <c r="S54" t="n">
-        <v>51.71820014953613</v>
+        <v>51.71020011901855</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-8.871536650840021</v>
+        <v>-9.630982988500465</v>
       </c>
       <c r="V54" t="n">
-        <v>41.6114001083374</v>
+        <v>41.60873343149821</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>13.26223329522649</v>
+        <v>12.30815189116348</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.53960007667541</v>
+        <v>39.53760006904602</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>19.19695944501329</v>
+        <v>18.19128996355354</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.3424777314594623</v>
+        <v>0.3445987885443809</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16004,13 +16012,13 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="CB54" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CC54" t="n">
         <v>1</v>
@@ -16075,7 +16083,7 @@
         <v>42.20000076293945</v>
       </c>
       <c r="H55" t="n">
-        <v>31048500</v>
+        <v>73196700</v>
       </c>
       <c r="I55" t="n">
         <v>-0.01199713812444136</v>
@@ -16347,82 +16355,82 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.079999923706055</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="D56" t="n">
-        <v>6.079999923706055</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="E56" t="n">
         <v>6.21999979019165</v>
       </c>
       <c r="F56" t="n">
-        <v>6.079999923706055</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="G56" t="n">
         <v>6.199999809265137</v>
       </c>
       <c r="H56" t="n">
-        <v>2973700</v>
+        <v>5550000</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.01618121479130386</v>
+        <v>-0.0194174577495646</v>
       </c>
       <c r="J56" t="n">
-        <v>6.064444330003527</v>
+        <v>6.06222210990058</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2565048478649151</v>
+        <v>-0.03665598324763197</v>
       </c>
       <c r="M56" t="n">
-        <v>6.053999900817871</v>
+        <v>6.051999902725219</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.4294685053541394</v>
+        <v>0.1321883705040911</v>
       </c>
       <c r="P56" t="n">
-        <v>6.234999986795279</v>
+        <v>6.234230756759644</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.485967336286912</v>
+        <v>-2.794744384320195</v>
       </c>
       <c r="S56" t="n">
-        <v>6.308599996566772</v>
+        <v>6.308199996948242</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-3.623626049917968</v>
+        <v>-3.934562225179521</v>
       </c>
       <c r="V56" t="n">
-        <v>6.351666536331177</v>
+        <v>6.351533203125</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-4.277091863548002</v>
+        <v>-4.589966721767632</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.828113424777984</v>
+        <v>6.828013424873352</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-10.95637190731428</v>
+        <v>-11.24797850127332</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3194606021941033</v>
+        <v>0.3206883252100807</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16574,13 +16582,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>6.08</v>
+        <v>6.06</v>
       </c>
       <c r="CA56" t="n">
         <v>0.2</v>
       </c>
       <c r="CB56" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CC56" t="n">
         <v>9</v>
@@ -16612,16 +16620,16 @@
         <v>1</v>
       </c>
       <c r="CL56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
@@ -16634,13 +16642,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.09999847412109</v>
+        <v>62.25</v>
       </c>
       <c r="D57" t="n">
-        <v>62.09999847412109</v>
+        <v>62.25</v>
       </c>
       <c r="E57" t="n">
-        <v>62.45999908447266</v>
+        <v>62.84999847412109</v>
       </c>
       <c r="F57" t="n">
         <v>61.02999877929688</v>
@@ -16649,67 +16657,67 @@
         <v>62.27999877929688</v>
       </c>
       <c r="H57" t="n">
-        <v>4724900</v>
+        <v>10048600</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.01381614625562355</v>
+        <v>-0.01143403536200671</v>
       </c>
       <c r="J57" t="n">
-        <v>65.71777725219727</v>
+        <v>65.73444408840604</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-5.505023038427874</v>
+        <v>-5.300788858455727</v>
       </c>
       <c r="M57" t="n">
-        <v>66.02799949645996</v>
+        <v>66.04299964904786</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-5.948992930717913</v>
+        <v>-5.743227396096236</v>
       </c>
       <c r="P57" t="n">
-        <v>65.80153861412636</v>
+        <v>65.80730790358324</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-5.625309404559443</v>
+        <v>-5.405642651109786</v>
       </c>
       <c r="S57" t="n">
-        <v>65.97739990234375</v>
+        <v>65.98039993286133</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-5.876863037891428</v>
+        <v>-5.65380012345669</v>
       </c>
       <c r="V57" t="n">
-        <v>51.8641332244873</v>
+        <v>51.86513323465983</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>19.73592271431424</v>
+        <v>20.02282866671649</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.33994995117187</v>
+        <v>48.34069995880127</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>28.46516915480514</v>
+        <v>28.7734767040052</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3832914719159162</v>
+        <v>0.3826229284366564</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16861,13 +16869,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>20.91</v>
+        <v>20.96</v>
       </c>
       <c r="CA57" t="n">
         <v>0.44</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CC57" t="n">
         <v>10</v>
@@ -16898,13 +16906,13 @@
         <v>6</v>
       </c>
       <c r="CM57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN57" t="n">
         <v>0</v>
       </c>
       <c r="CO57" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58">
@@ -16917,10 +16925,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.33000183105469</v>
+        <v>48.31000137329102</v>
       </c>
       <c r="D58" t="n">
-        <v>48.33000183105469</v>
+        <v>48.31000137329102</v>
       </c>
       <c r="E58" t="n">
         <v>48.59999847412109</v>
@@ -16932,67 +16940,67 @@
         <v>48.29000091552734</v>
       </c>
       <c r="H58" t="n">
-        <v>867800</v>
+        <v>2523200</v>
       </c>
       <c r="I58" t="n">
-        <v>0.001035688753564301</v>
+        <v>0.0006214290545303314</v>
       </c>
       <c r="J58" t="n">
-        <v>48.75222227308485</v>
+        <v>48.75</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.8660537352843219</v>
+        <v>-0.902561285556891</v>
       </c>
       <c r="M58" t="n">
-        <v>48.74700012207031</v>
+        <v>48.74500007629395</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-0.8554337497105318</v>
+        <v>-0.892396558256412</v>
       </c>
       <c r="P58" t="n">
-        <v>49.55884654705341</v>
+        <v>49.55807729867789</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.479566821298</v>
+        <v>-2.518410708036422</v>
       </c>
       <c r="S58" t="n">
-        <v>50.2684001159668</v>
+        <v>50.26800010681152</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-3.856097032012793</v>
+        <v>-3.895119617569962</v>
       </c>
       <c r="V58" t="n">
-        <v>49.25693336486816</v>
+        <v>49.25680002848307</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-1.881829562850119</v>
+        <v>-1.922168420694325</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.49865001678467</v>
+        <v>49.49855001449585</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.360969815002424</v>
+        <v>-2.401178702925159</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.2836920607937705</v>
+        <v>0.2836383160840877</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17182,7 +17190,7 @@
         <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM58" t="n">
         <v>6</v>
@@ -17191,7 +17199,7 @@
         <v>0</v>
       </c>
       <c r="CO58" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59">
@@ -17204,82 +17212,82 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18.8700008392334</v>
+        <v>18.69000053405762</v>
       </c>
       <c r="D59" t="n">
-        <v>18.8700008392334</v>
+        <v>18.69000053405762</v>
       </c>
       <c r="E59" t="n">
         <v>19.01000022888184</v>
       </c>
       <c r="F59" t="n">
-        <v>18.70000076293945</v>
+        <v>18.69000053405762</v>
       </c>
       <c r="G59" t="n">
         <v>18.8700008392334</v>
       </c>
       <c r="H59" t="n">
-        <v>11191100</v>
+        <v>23348500</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.004221631687873595</v>
+        <v>-0.01372032814849899</v>
       </c>
       <c r="J59" t="n">
-        <v>18.59000015258789</v>
+        <v>18.57000011867947</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1.506189802836173</v>
+        <v>0.6462057868133199</v>
       </c>
       <c r="M59" t="n">
-        <v>18.64300022125244</v>
+        <v>18.62500019073486</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1.217618491052647</v>
+        <v>0.3489951283602644</v>
       </c>
       <c r="P59" t="n">
-        <v>20.23192317669208</v>
+        <v>20.22500008803148</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-6.731551546358518</v>
+        <v>-7.589614572522168</v>
       </c>
       <c r="S59" t="n">
-        <v>21.68080005645752</v>
+        <v>21.677200050354</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-12.96446261164121</v>
+        <v>-13.78037527613075</v>
       </c>
       <c r="V59" t="n">
-        <v>22.86513062795003</v>
+        <v>22.86393062591553</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-17.47258676857521</v>
+        <v>-18.2555229026408</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.57703415870667</v>
+        <v>21.57613415718079</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-12.54590088499693</v>
+        <v>-13.37650944371158</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3573533398179006</v>
+        <v>0.3575823380928891</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17431,13 +17439,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>25.5</v>
+        <v>25.26</v>
       </c>
       <c r="CA59" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17469,16 +17477,16 @@
         <v>0</v>
       </c>
       <c r="CL59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60">
@@ -17491,10 +17499,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.6899995803833</v>
+        <v>13.72000026702881</v>
       </c>
       <c r="D60" t="n">
-        <v>13.6899995803833</v>
+        <v>13.72000026702881</v>
       </c>
       <c r="E60" t="n">
         <v>13.90999984741211</v>
@@ -17506,67 +17514,67 @@
         <v>13.85999965667725</v>
       </c>
       <c r="H60" t="n">
-        <v>5243500</v>
+        <v>21917900</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.01155240409238512</v>
+        <v>-0.009386289592803854</v>
       </c>
       <c r="J60" t="n">
-        <v>14.30111111534966</v>
+        <v>14.30444452497694</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.273175210214569</v>
+        <v>-4.085752906571362</v>
       </c>
       <c r="M60" t="n">
-        <v>14.36099996566772</v>
+        <v>14.36400003433227</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-4.672379269469802</v>
+        <v>-4.483429168506007</v>
       </c>
       <c r="P60" t="n">
-        <v>15.29384627709022</v>
+        <v>15.29500014965351</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-10.4868760130631</v>
+        <v>-10.29748196936355</v>
       </c>
       <c r="S60" t="n">
-        <v>15.77700008392334</v>
+        <v>15.77760009765625</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-13.2281200002444</v>
+        <v>-13.04127255027269</v>
       </c>
       <c r="V60" t="n">
-        <v>15.614333375295</v>
+        <v>15.61453337987264</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-12.32414954042407</v>
+        <v>-12.13313947175592</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.50380001068115</v>
+        <v>15.50395001411438</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-11.69907009280471</v>
+        <v>-11.50642091506688</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3137305064227877</v>
+        <v>0.3135156651476538</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17718,10 +17726,10 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>24.45</v>
+        <v>24.5</v>
       </c>
       <c r="CA60" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="CB60" t="n">
         <v>1.83</v>
@@ -17778,10 +17786,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>33.88000106811523</v>
+        <v>34.02000045776367</v>
       </c>
       <c r="D61" t="n">
-        <v>33.88000106811523</v>
+        <v>34.02000045776367</v>
       </c>
       <c r="E61" t="n">
         <v>34.43000030517578</v>
@@ -17793,91 +17801,91 @@
         <v>34.29999923706055</v>
       </c>
       <c r="H61" t="n">
-        <v>7287700</v>
+        <v>22103300</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.01711633686376346</v>
+        <v>-0.0130548519583219</v>
       </c>
       <c r="J61" t="n">
-        <v>34.4455557929145</v>
+        <v>34.46111128065321</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.641880096809465</v>
+        <v>-1.280024951305575</v>
       </c>
       <c r="M61" t="n">
-        <v>34.47800025939942</v>
+        <v>34.49200019836426</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-1.734436993981848</v>
+        <v>-1.368432499959719</v>
       </c>
       <c r="P61" t="n">
-        <v>36.29500022301307</v>
+        <v>36.30038481492262</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-6.653806695299563</v>
+        <v>-6.281983975612055</v>
       </c>
       <c r="S61" t="n">
-        <v>37.76899993896485</v>
+        <v>37.77179992675782</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-10.29680128447743</v>
+        <v>-9.932805628191261</v>
       </c>
       <c r="V61" t="n">
-        <v>41.06613327026367</v>
+        <v>41.067066599528</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-17.49892582984426</v>
+        <v>-17.15989654309841</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.705149974823</v>
+        <v>40.70584997177124</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-16.7672859845235</v>
+        <v>-16.42478788342237</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3743705106673904</v>
+        <v>0.3734354652073562</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="AE61" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="AF61" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="AG61" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="AH61" t="n">
-        <v>34</v>
+        <v>34.7</v>
       </c>
       <c r="AI61" t="n">
-        <v>34.4</v>
+        <v>34.9</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK61" t="n">
         <v>0</v>
@@ -18001,13 +18009,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>16.77</v>
+        <v>16.84</v>
       </c>
       <c r="CA61" t="n">
         <v>0.09</v>
       </c>
       <c r="CB61" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18019,7 +18027,7 @@
         <v>7</v>
       </c>
       <c r="CF61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CG61" t="n">
         <v>2</v>
@@ -18028,7 +18036,7 @@
         <v>7</v>
       </c>
       <c r="CI61" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CJ61" t="inlineStr">
         <is>
@@ -18039,7 +18047,7 @@
         <v>0</v>
       </c>
       <c r="CL61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM61" t="n">
         <v>5</v>
@@ -18048,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62">
@@ -18061,10 +18069,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11.38000011444092</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="D62" t="n">
-        <v>11.38000011444092</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="E62" t="n">
         <v>11.63000011444092</v>
@@ -18076,67 +18084,67 @@
         <v>11.53999996185303</v>
       </c>
       <c r="H62" t="n">
-        <v>2023100</v>
+        <v>2568300</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.01727114081026082</v>
+        <v>-0.0181347184395978</v>
       </c>
       <c r="J62" t="n">
-        <v>11.95222229427761</v>
+        <v>11.95111115773519</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-4.787579796860542</v>
+        <v>-4.862403708796493</v>
       </c>
       <c r="M62" t="n">
-        <v>12.00600004196167</v>
+        <v>12.00500001907349</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-5.214059014932914</v>
+        <v>-5.289463827617821</v>
       </c>
       <c r="P62" t="n">
-        <v>12.40076927038339</v>
+        <v>12.40038464619563</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-8.231498656945153</v>
+        <v>-8.309296768085863</v>
       </c>
       <c r="S62" t="n">
-        <v>12.96580009460449</v>
+        <v>12.96560009002686</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-12.23063728109984</v>
+        <v>-12.30641230169601</v>
       </c>
       <c r="V62" t="n">
-        <v>11.94813334147135</v>
+        <v>11.94806667327881</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-4.754995703458343</v>
+        <v>-4.838161717096388</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.14785000801086</v>
+        <v>12.14780000686645</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-6.320870714271172</v>
+        <v>-6.402806441229905</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3525714617987601</v>
+        <v>0.3528315877361741</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18344,10 +18352,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>41.77000045776367</v>
+        <v>42.02000045776367</v>
       </c>
       <c r="D63" t="n">
-        <v>41.77000045776367</v>
+        <v>42.02000045776367</v>
       </c>
       <c r="E63" t="n">
         <v>42.90000152587891</v>
@@ -18359,88 +18367,88 @@
         <v>42.90000152587891</v>
       </c>
       <c r="H63" t="n">
-        <v>5693100</v>
+        <v>21837400</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.02452123410891716</v>
+        <v>-0.01868284079313631</v>
       </c>
       <c r="J63" t="n">
-        <v>43.32888921101888</v>
+        <v>43.35666698879666</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-3.597804563286088</v>
+        <v>-3.082954996006458</v>
       </c>
       <c r="M63" t="n">
-        <v>43.29300041198731</v>
+        <v>43.31800041198731</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-3.517889588918248</v>
+        <v>-2.996444761712596</v>
       </c>
       <c r="P63" t="n">
-        <v>45.24076960637019</v>
+        <v>45.25038499098558</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-7.671773002106081</v>
+        <v>-7.138910605656593</v>
       </c>
       <c r="S63" t="n">
-        <v>46.53460014343262</v>
+        <v>46.53960014343262</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-10.23883233332428</v>
+        <v>-9.711298919070584</v>
       </c>
       <c r="V63" t="n">
-        <v>45.59673342386881</v>
+        <v>45.59840009053548</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-8.392559463704776</v>
+        <v>-7.847642956039929</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.44770004272461</v>
+        <v>43.44895004272461</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-3.861423236008264</v>
+        <v>-3.28880118749892</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.495020262662431</v>
+        <v>0.4934878718476189</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="AE63" t="n">
-        <v>41</v>
+        <v>41.9</v>
       </c>
       <c r="AF63" t="n">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="AG63" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="AH63" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="AI63" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="AJ63" t="n">
         <v>3</v>
@@ -18567,13 +18575,13 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>20.89</v>
+        <v>21.01</v>
       </c>
       <c r="CA63" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CC63" t="n">
         <v>10</v>
@@ -18601,7 +18609,7 @@
         <v>0</v>
       </c>
       <c r="CL63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM63" t="n">
         <v>3</v>
@@ -18610,7 +18618,7 @@
         <v>-1</v>
       </c>
       <c r="CO63" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -18623,13 +18631,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.47999954223633</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="D64" t="n">
-        <v>27.47999954223633</v>
+        <v>27.15999984741211</v>
       </c>
       <c r="E64" t="n">
-        <v>27.55999946594238</v>
+        <v>27.60000038146973</v>
       </c>
       <c r="F64" t="n">
         <v>27.07999992370605</v>
@@ -18638,67 +18646,67 @@
         <v>27.53000068664551</v>
       </c>
       <c r="H64" t="n">
-        <v>1446800</v>
+        <v>3265000</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0095518087964932</v>
+        <v>-0.002204242007932233</v>
       </c>
       <c r="J64" t="n">
-        <v>27.33555539449056</v>
+        <v>27.29999987284343</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.528411241920045</v>
+        <v>-0.5128206083641077</v>
       </c>
       <c r="M64" t="n">
-        <v>27.28699989318848</v>
+        <v>27.25499992370606</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.7072952314410711</v>
+        <v>-0.3485601781686896</v>
       </c>
       <c r="P64" t="n">
-        <v>28.05269226661095</v>
+        <v>28.04038458604079</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.041489347731019</v>
+        <v>-3.13970279518548</v>
       </c>
       <c r="S64" t="n">
-        <v>29.35759994506836</v>
+        <v>29.35119995117187</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-6.395619554545498</v>
+        <v>-7.46545322646095</v>
       </c>
       <c r="V64" t="n">
-        <v>31.96439999898275</v>
+        <v>31.96226666768392</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-14.0293590897659</v>
+        <v>-15.02480055686175</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.01240000724793</v>
+        <v>31.0108000087738</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-11.39028409341437</v>
+        <v>-12.41760986582802</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2550969023070511</v>
+        <v>0.2516807807143414</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18868,13 +18876,13 @@
         <v>18881600000</v>
       </c>
       <c r="BZ64" t="n">
-        <v>6.65</v>
+        <v>6.58</v>
       </c>
       <c r="CA64" t="n">
         <v>0</v>
       </c>
       <c r="CB64" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="CC64" t="n">
         <v>4</v>
@@ -18906,16 +18914,16 @@
         <v>0</v>
       </c>
       <c r="CL64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
@@ -18928,10 +18936,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27.95999908447266</v>
+        <v>27.95000076293945</v>
       </c>
       <c r="D65" t="n">
-        <v>27.95999908447266</v>
+        <v>27.95000076293945</v>
       </c>
       <c r="E65" t="n">
         <v>28.45000076293945</v>
@@ -18943,67 +18951,67 @@
         <v>28.1200008392334</v>
       </c>
       <c r="H65" t="n">
-        <v>12108900</v>
+        <v>28279600</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.007102299858777639</v>
+        <v>-0.007457353892420415</v>
       </c>
       <c r="J65" t="n">
-        <v>28.59111107720269</v>
+        <v>28.59000015258789</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-2.20737134358257</v>
+        <v>-2.238542798995076</v>
       </c>
       <c r="M65" t="n">
-        <v>28.64799995422363</v>
+        <v>28.64700012207031</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-2.4015668488213</v>
+        <v>-2.433062296787843</v>
       </c>
       <c r="P65" t="n">
-        <v>30.70315405038687</v>
+        <v>30.70276949955867</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-8.934440290441909</v>
+        <v>-8.965864583189429</v>
       </c>
       <c r="S65" t="n">
-        <v>31.3411909866333</v>
+        <v>31.34099102020264</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-10.78833252891598</v>
+        <v>-10.81966506763403</v>
       </c>
       <c r="V65" t="n">
-        <v>28.75873279571533</v>
+        <v>28.75866614023844</v>
       </c>
       <c r="W65" t="n">
         <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>-2.77736059135984</v>
+        <v>-2.811901544235824</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.58453762054443</v>
+        <v>27.58448762893677</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.361130170434995</v>
+        <v>1.325067693551264</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2678909562761259</v>
+        <v>0.2679003693981196</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19215,10 +19223,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15.5600004196167</v>
+        <v>15.5</v>
       </c>
       <c r="D66" t="n">
-        <v>15.5600004196167</v>
+        <v>15.5</v>
       </c>
       <c r="E66" t="n">
         <v>15.80000019073486</v>
@@ -19230,67 +19238,67 @@
         <v>15.5</v>
       </c>
       <c r="H66" t="n">
-        <v>2860900</v>
+        <v>4660300</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.02138359792897926</v>
+        <v>-0.02515720931616272</v>
       </c>
       <c r="J66" t="n">
-        <v>16.17555554707845</v>
+        <v>16.1688888337877</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-3.805465139482821</v>
+        <v>-4.13688807353258</v>
       </c>
       <c r="M66" t="n">
-        <v>16.28600006103516</v>
+        <v>16.28000001907349</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-4.457814311050128</v>
+        <v>-4.791154902700533</v>
       </c>
       <c r="P66" t="n">
-        <v>16.91576935694768</v>
+        <v>16.91346164850088</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-8.014822788856096</v>
+        <v>-8.357021630909973</v>
       </c>
       <c r="S66" t="n">
-        <v>17.60579998016357</v>
+        <v>17.60459997177124</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-11.62003182389823</v>
+        <v>-11.95482984643752</v>
       </c>
       <c r="V66" t="n">
-        <v>16.0400146484375</v>
+        <v>16.03961464564005</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-2.992604678622029</v>
+        <v>-3.364261907543606</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.7427664232254</v>
+        <v>15.74246642112732</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-1.160952266553785</v>
+        <v>-1.540206055652853</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.191125888383533</v>
+        <v>0.194155058468505</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19444,13 +19452,13 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>23.94</v>
+        <v>23.85</v>
       </c>
       <c r="CA66" t="n">
         <v>0.82</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CC66" t="n">
         <v>3</v>
@@ -19465,7 +19473,7 @@
         <v>3</v>
       </c>
       <c r="CG66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CH66" t="n">
         <v>7</v>
@@ -19482,16 +19490,16 @@
         <v>0</v>
       </c>
       <c r="CL66" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM66" t="n">
         <v>2</v>
       </c>
-      <c r="CM66" t="n">
-        <v>3</v>
-      </c>
       <c r="CN66" t="n">
         <v>1</v>
       </c>
       <c r="CO66" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="67">
@@ -19504,10 +19512,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.64999961853027</v>
+        <v>18.53000068664551</v>
       </c>
       <c r="D67" t="n">
-        <v>18.64999961853027</v>
+        <v>18.53000068664551</v>
       </c>
       <c r="E67" t="n">
         <v>18.85000038146973</v>
@@ -19519,67 +19527,67 @@
         <v>18.79999923706055</v>
       </c>
       <c r="H67" t="n">
-        <v>2775700</v>
+        <v>4143400</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.004271218668513765</v>
+        <v>-0.01067799575434158</v>
       </c>
       <c r="J67" t="n">
-        <v>19.00666660732693</v>
+        <v>18.99333339267307</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-1.87653624996592</v>
+        <v>-2.439449129062821</v>
       </c>
       <c r="M67" t="n">
-        <v>18.96099987030029</v>
+        <v>18.94899997711182</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-1.640210188794715</v>
+        <v>-2.211194738363039</v>
       </c>
       <c r="P67" t="n">
-        <v>18.58538451561561</v>
+        <v>18.58076917208158</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R67" t="n">
-        <v>0.3476662151400468</v>
+        <v>-0.2732313445471092</v>
       </c>
       <c r="S67" t="n">
-        <v>18.70439990997314</v>
+        <v>18.70199993133545</v>
       </c>
       <c r="T67" t="n">
         <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>-0.2908422173644012</v>
+        <v>-0.919683698649552</v>
       </c>
       <c r="V67" t="n">
-        <v>21.50305455525716</v>
+        <v>21.50225456237793</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-13.26813792615041</v>
+        <v>-13.82298710635169</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.3254909324646</v>
+        <v>22.32489093780518</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-16.4632048856297</v>
+        <v>-16.99847162403542</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5140985241549075</v>
+        <v>0.5149624306925418</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19729,13 +19737,13 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.65</v>
+        <v>16.54</v>
       </c>
       <c r="CA67" t="n">
         <v>0.36</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CC67" t="n">
         <v>10</v>
@@ -19770,13 +19778,13 @@
         <v>9</v>
       </c>
       <c r="CM67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN67" t="n">
         <v>-1</v>
       </c>
       <c r="CO67" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68">
@@ -19789,13 +19797,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.41999816894531</v>
+        <v>41.90999984741211</v>
       </c>
       <c r="D68" t="n">
-        <v>41.41999816894531</v>
+        <v>41.90999984741211</v>
       </c>
       <c r="E68" t="n">
-        <v>41.79000091552734</v>
+        <v>41.90999984741211</v>
       </c>
       <c r="F68" t="n">
         <v>41.02999877929688</v>
@@ -19804,67 +19812,67 @@
         <v>41.65000152587891</v>
       </c>
       <c r="H68" t="n">
-        <v>2474600</v>
+        <v>13172400</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.006476384424505488</v>
+        <v>0.005277074309188778</v>
       </c>
       <c r="J68" t="n">
-        <v>41.72222179836697</v>
+        <v>41.77666642930772</v>
       </c>
       <c r="K68" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.7243708901271655</v>
+        <v>0.3191576291277454</v>
       </c>
       <c r="M68" t="n">
-        <v>41.74699974060059</v>
+        <v>41.79599990844726</v>
       </c>
       <c r="N68" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.7832935868137408</v>
+        <v>0.2727532280949331</v>
       </c>
       <c r="P68" t="n">
-        <v>42.97423069293682</v>
+        <v>42.99307691133939</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.616661657300964</v>
+        <v>-2.51918946429634</v>
       </c>
       <c r="S68" t="n">
-        <v>46.09799980163574</v>
+        <v>46.10779983520508</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-10.14794926638973</v>
+        <v>-9.104316412399681</v>
       </c>
       <c r="V68" t="n">
-        <v>49.55359992980957</v>
+        <v>49.55686660766602</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-16.41374546427533</v>
+        <v>-15.4304888176102</v>
       </c>
       <c r="Y68" t="n">
-        <v>49.91014995574951</v>
+        <v>49.91259996414185</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-17.01087212587338</v>
+        <v>-16.03322632457327</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2051817229684479</v>
+        <v>0.207118050018933</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20016,13 +20024,13 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="CA68" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="CB68" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CC68" t="n">
         <v>3</v>
@@ -20057,13 +20065,13 @@
         <v>4</v>
       </c>
       <c r="CM68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN68" t="n">
         <v>1</v>
       </c>
       <c r="CO68" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69">
@@ -20076,10 +20084,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39.11000061035156</v>
+        <v>39.15999984741211</v>
       </c>
       <c r="D69" t="n">
-        <v>39.11000061035156</v>
+        <v>39.15999984741211</v>
       </c>
       <c r="E69" t="n">
         <v>39.52999877929688</v>
@@ -20091,67 +20099,67 @@
         <v>39.52999877929688</v>
       </c>
       <c r="H69" t="n">
-        <v>1216700</v>
+        <v>1820300</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.002804706958894676</v>
+        <v>-0.001529866685963888</v>
       </c>
       <c r="J69" t="n">
-        <v>38.88555526733398</v>
+        <v>38.89111073811849</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5771946458641022</v>
+        <v>0.691389636835623</v>
       </c>
       <c r="M69" t="n">
-        <v>38.85199966430664</v>
+        <v>38.8569995880127</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.6640609190624208</v>
+        <v>0.7797829544535553</v>
       </c>
       <c r="P69" t="n">
-        <v>40.49115386376014</v>
+        <v>40.49307691133939</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-3.410999987937412</v>
+        <v>-3.292111060974916</v>
       </c>
       <c r="S69" t="n">
-        <v>41.88800018310547</v>
+        <v>41.88900016784668</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-6.63196992124333</v>
+        <v>-6.514837569528119</v>
       </c>
       <c r="V69" t="n">
-        <v>41.78166681925456</v>
+        <v>41.78200014750163</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-6.394350470651386</v>
+        <v>-6.275430306910048</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.11905012130737</v>
+        <v>40.11930011749268</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-2.515138090021483</v>
+        <v>-2.391119155297272</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2519639921334049</v>
+        <v>0.2520858169130202</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20303,13 +20311,13 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.6</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
       </c>
       <c r="CB69" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CC69" t="n">
         <v>6</v>
@@ -20359,82 +20367,82 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.13999938964844</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="D70" t="n">
-        <v>22.13999938964844</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="E70" t="n">
         <v>22.40999984741211</v>
       </c>
       <c r="F70" t="n">
-        <v>22.02000045776367</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="G70" t="n">
         <v>22.38999938964844</v>
       </c>
       <c r="H70" t="n">
-        <v>3514700</v>
+        <v>12314300</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.008952585567296167</v>
+        <v>-0.01969563702114152</v>
       </c>
       <c r="J70" t="n">
-        <v>22.46444426642524</v>
+        <v>22.43777762518989</v>
       </c>
       <c r="K70" t="n">
         <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>-1.44425952820791</v>
+        <v>-2.396752546722253</v>
       </c>
       <c r="M70" t="n">
-        <v>22.42499980926514</v>
+        <v>22.40099983215332</v>
       </c>
       <c r="N70" t="n">
         <v>-1</v>
       </c>
       <c r="O70" t="n">
-        <v>-1.27090489204352</v>
+        <v>-2.236508269170807</v>
       </c>
       <c r="P70" t="n">
-        <v>23.60846152672401</v>
+        <v>23.59923076629639</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-6.220067052710395</v>
+        <v>-7.200366675480359</v>
       </c>
       <c r="S70" t="n">
-        <v>25.21959995269775</v>
+        <v>25.21479995727539</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-12.21113962483726</v>
+        <v>-13.14624880769151</v>
       </c>
       <c r="V70" t="n">
-        <v>24.84580000559489</v>
+        <v>24.84420000712077</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-10.89037428996912</v>
+        <v>-11.85065483189894</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.33835000038147</v>
+        <v>24.33715000152588</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-9.032455407612174</v>
+        <v>-10.01411579762955</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3778257593024321</v>
+        <v>0.3796571812471876</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20586,13 +20594,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2214</v>
+        <v>2190</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CC70" t="n">
         <v>1</v>
@@ -20627,13 +20635,13 @@
         <v>2</v>
       </c>
       <c r="CM70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71">
@@ -20646,13 +20654,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>33.66999816894531</v>
+        <v>33.06999969482422</v>
       </c>
       <c r="D71" t="n">
-        <v>33.66999816894531</v>
+        <v>33.06999969482422</v>
       </c>
       <c r="E71" t="n">
-        <v>33.70000076293945</v>
+        <v>33.7599983215332</v>
       </c>
       <c r="F71" t="n">
         <v>31.39999961853027</v>
@@ -20661,67 +20669,67 @@
         <v>31.80999946594238</v>
       </c>
       <c r="H71" t="n">
-        <v>11207400</v>
+        <v>106771100</v>
       </c>
       <c r="I71" t="n">
-        <v>0.06047238327386806</v>
+        <v>0.0415747935377706</v>
       </c>
       <c r="J71" t="n">
-        <v>31.81999948289659</v>
+        <v>31.75333298577203</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>5.813949453528762</v>
+        <v>4.146546473222708</v>
       </c>
       <c r="M71" t="n">
-        <v>31.7839994430542</v>
+        <v>31.72399959564209</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>5.933799266735336</v>
+        <v>4.242844900827154</v>
       </c>
       <c r="P71" t="n">
-        <v>32.28730744581956</v>
+        <v>32.26423058143029</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>4.282459060564288</v>
+        <v>2.497406877130645</v>
       </c>
       <c r="S71" t="n">
-        <v>33.4289998626709</v>
+        <v>33.41699989318847</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U71" t="n">
-        <v>0.7209258645620695</v>
+        <v>-1.038394228905589</v>
       </c>
       <c r="V71" t="n">
-        <v>39.39946660359701</v>
+        <v>39.39546661376953</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-14.54199492672476</v>
+        <v>-16.05633201647224</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.35419998168945</v>
+        <v>40.35119998931885</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-16.56383180877597</v>
+        <v>-18.04456942153393</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4896238748957832</v>
+        <v>0.4717070597977834</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20873,13 +20881,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>21.86</v>
+        <v>21.47</v>
       </c>
       <c r="CA71" t="n">
         <v>0.17</v>
       </c>
       <c r="CB71" t="n">
-        <v>4.07</v>
+        <v>3.99</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20917,7 +20925,7 @@
         <v>10</v>
       </c>
       <c r="CN71" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO71" t="n">
         <v>60</v>
@@ -20933,82 +20941,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>26.07999992370605</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="D72" t="n">
-        <v>26.07999992370605</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="E72" t="n">
         <v>27.06999969482422</v>
       </c>
       <c r="F72" t="n">
-        <v>26.03000068664551</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="G72" t="n">
         <v>27.06999969482422</v>
       </c>
       <c r="H72" t="n">
-        <v>2230900</v>
+        <v>10123700</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.03084354992242311</v>
+        <v>-0.03864730635733271</v>
       </c>
       <c r="J72" t="n">
-        <v>28.00222248501248</v>
+        <v>27.9788892534044</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-6.864535707246977</v>
+        <v>-7.537427219039444</v>
       </c>
       <c r="M72" t="n">
-        <v>28.13000030517578</v>
+        <v>28.10900039672851</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-7.287594593778003</v>
+        <v>-7.965418641339178</v>
       </c>
       <c r="P72" t="n">
-        <v>28.98538479438195</v>
+        <v>28.97730790651762</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-10.0236201495556</v>
+        <v>-10.7232427432823</v>
       </c>
       <c r="S72" t="n">
-        <v>28.9588000869751</v>
+        <v>28.95460010528565</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-9.941020189451331</v>
+        <v>-10.65322696509684</v>
       </c>
       <c r="V72" t="n">
-        <v>25.18673332214355</v>
+        <v>25.18533332824707</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>3.546575850617212</v>
+        <v>2.718516773484306</v>
       </c>
       <c r="Y72" t="n">
-        <v>23.89789999961853</v>
+        <v>23.89685000419617</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>9.13092750460231</v>
+        <v>8.256949492049184</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2567394842341222</v>
+        <v>0.2643731282080991</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21160,13 +21168,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>9.699999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="CA72" t="n">
         <v>0.48</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21194,7 +21202,7 @@
         <v>0</v>
       </c>
       <c r="CL72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM72" t="n">
         <v>1</v>
@@ -21203,7 +21211,7 @@
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
@@ -21216,13 +21224,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>11.06999969482422</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="D73" t="n">
-        <v>11.06999969482422</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E73" t="n">
-        <v>11.09000015258789</v>
+        <v>11.14999961853027</v>
       </c>
       <c r="F73" t="n">
         <v>10.60000038146973</v>
@@ -21231,67 +21239,67 @@
         <v>10.63000011444092</v>
       </c>
       <c r="H73" t="n">
-        <v>20347600</v>
+        <v>34539800</v>
       </c>
       <c r="I73" t="n">
-        <v>0.03943662829463146</v>
+        <v>0.04037561695566727</v>
       </c>
       <c r="J73" t="n">
-        <v>10.0577777226766</v>
+        <v>10.05888885921902</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>10.06407180649294</v>
+        <v>10.15133061691183</v>
       </c>
       <c r="M73" t="n">
-        <v>9.954999923706055</v>
+        <v>9.955999946594238</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>11.20039959481056</v>
+        <v>11.2896743987661</v>
       </c>
       <c r="P73" t="n">
-        <v>9.099999959652241</v>
+        <v>9.100384583840004</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>21.64834883413848</v>
+        <v>21.75309539534571</v>
       </c>
       <c r="S73" t="n">
-        <v>8.034199962615967</v>
+        <v>8.034399967193604</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>37.78596184230128</v>
+        <v>37.90699951394468</v>
       </c>
       <c r="V73" t="n">
-        <v>6.691999985376994</v>
+        <v>6.692066653569539</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>65.42139448615958</v>
+        <v>65.56918060276638</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.116349989175797</v>
+        <v>6.116399990320206</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>80.99029183115707</v>
+        <v>81.15231085673314</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.550736551076428</v>
+        <v>0.5510893505165911</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21443,7 +21451,7 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>-5.32</v>
+        <v>-5.33</v>
       </c>
       <c r="CA73" t="n">
         <v>-0.04</v>
@@ -21503,88 +21511,88 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>82.83999633789062</v>
+        <v>82.81999969482422</v>
       </c>
       <c r="D74" t="n">
-        <v>82.83999633789062</v>
+        <v>82.81999969482422</v>
       </c>
       <c r="E74" t="n">
         <v>84.27999877929688</v>
       </c>
       <c r="F74" t="n">
-        <v>82.55000305175781</v>
+        <v>82.37999725341797</v>
       </c>
       <c r="G74" t="n">
         <v>84.01000213623047</v>
       </c>
       <c r="H74" t="n">
-        <v>10296000</v>
+        <v>20834800</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.01333971842299797</v>
+        <v>-0.01357788711385621</v>
       </c>
       <c r="J74" t="n">
-        <v>82.85110897488065</v>
+        <v>82.84888712565105</v>
       </c>
       <c r="K74" t="n">
         <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-0.0134127800189008</v>
+        <v>-0.03486761479730697</v>
       </c>
       <c r="M74" t="n">
-        <v>82.74899826049804</v>
+        <v>82.7469985961914</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.1099687963667152</v>
+        <v>0.08822205019068252</v>
       </c>
       <c r="P74" t="n">
-        <v>82.55230771578275</v>
+        <v>82.55153861412636</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3484925256097686</v>
+        <v>0.3252042120653116</v>
       </c>
       <c r="S74" t="n">
-        <v>82.74280029296875</v>
+        <v>82.74240036010742</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>0.117467676435568</v>
+        <v>0.09378424408655056</v>
       </c>
       <c r="V74" t="n">
-        <v>77.5554000600179</v>
+        <v>77.55526674906413</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>6.813963017124694</v>
+        <v>6.788362888099559</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.3782000541687</v>
+        <v>72.37810007095337</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>14.45434713199857</v>
+        <v>14.42687720959033</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3041426250477751</v>
+        <v>0.3042205669854699</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AE74" t="n">
         <v>82.7</v>
@@ -21782,82 +21790,82 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3.130000114440918</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="D75" t="n">
-        <v>3.130000114440918</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="E75" t="n">
         <v>3.210000038146973</v>
       </c>
       <c r="F75" t="n">
-        <v>3.079999923706055</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="G75" t="n">
         <v>3.190000057220459</v>
       </c>
       <c r="H75" t="n">
-        <v>9981800</v>
+        <v>16119300</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.01880875915463798</v>
+        <v>-0.0407523862410808</v>
       </c>
       <c r="J75" t="n">
-        <v>3.270000007417467</v>
+        <v>3.262222210566203</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-4.281342283149296</v>
+        <v>-6.19891150062286</v>
       </c>
       <c r="M75" t="n">
-        <v>3.276999998092651</v>
+        <v>3.269999980926514</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-4.485806644409314</v>
+        <v>-6.422019552656749</v>
       </c>
       <c r="P75" t="n">
-        <v>3.62346155826862</v>
+        <v>3.620769243973952</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-13.61850914912122</v>
+        <v>-15.48757359027228</v>
       </c>
       <c r="S75" t="n">
-        <v>3.732600011825562</v>
+        <v>3.731200008392334</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-16.14423981877234</v>
+        <v>-17.98885248989891</v>
       </c>
       <c r="V75" t="n">
-        <v>3.751994791030884</v>
+        <v>3.751528123219808</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-16.57770629311212</v>
+        <v>-18.43323994188139</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.737496099472046</v>
+        <v>3.737146098613739</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-16.25409014117612</v>
+        <v>-18.11933860668116</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.5087492418935832</v>
+        <v>0.5159910364030784</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -22009,13 +22017,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>12.52</v>
+        <v>12.24</v>
       </c>
       <c r="CA75" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="CB75" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="CC75" t="n">
         <v>6</v>
@@ -22030,7 +22038,7 @@
         <v>6</v>
       </c>
       <c r="CG75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CH75" t="n">
         <v>9</v>
@@ -22046,13 +22054,13 @@
         <v>1</v>
       </c>
       <c r="CM75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN75" t="n">
         <v>-1</v>
       </c>
       <c r="CO75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
@@ -22065,10 +22073,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>29.8700008392334</v>
+        <v>29.75</v>
       </c>
       <c r="D76" t="n">
-        <v>29.8700008392334</v>
+        <v>29.75</v>
       </c>
       <c r="E76" t="n">
         <v>30.95000076293945</v>
@@ -22080,67 +22088,67 @@
         <v>30.89999961853027</v>
       </c>
       <c r="H76" t="n">
-        <v>4349200</v>
+        <v>13523500</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.03364603731196014</v>
+        <v>-0.03752830323967893</v>
       </c>
       <c r="J76" t="n">
-        <v>32.01333321465386</v>
+        <v>31.99999978807237</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-6.695124062993132</v>
+        <v>-7.031249384292289</v>
       </c>
       <c r="M76" t="n">
-        <v>32.1379997253418</v>
+        <v>32.12599964141846</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-7.057062995491951</v>
+        <v>-7.395877693888788</v>
       </c>
       <c r="P76" t="n">
-        <v>32.70846132131723</v>
+        <v>32.70384590442364</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-8.678061784073925</v>
+        <v>-9.03210562163299</v>
       </c>
       <c r="S76" t="n">
-        <v>32.33019992828369</v>
+        <v>32.32779991149902</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-7.609600604102718</v>
+        <v>-7.973941680399029</v>
       </c>
       <c r="V76" t="n">
-        <v>28.50060521443685</v>
+        <v>28.49980520884196</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>4.804794896435703</v>
+        <v>4.386678371998741</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.82544651985168</v>
+        <v>26.82484651565552</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>11.34950099387403</v>
+        <v>10.90464201775508</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.2703625413687186</v>
+        <v>0.2742230559924004</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22292,13 +22300,13 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>11.9</v>
+        <v>11.85</v>
       </c>
       <c r="CA76" t="n">
         <v>0.51</v>
       </c>
       <c r="CB76" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CC76" t="n">
         <v>5</v>
@@ -22348,10 +22356,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>21.88999938964844</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="D77" t="n">
-        <v>21.88999938964844</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="E77" t="n">
         <v>22.14999961853027</v>
@@ -22363,67 +22371,67 @@
         <v>22.13999938964844</v>
       </c>
       <c r="H77" t="n">
-        <v>3124100</v>
+        <v>3933400</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.01173815951962021</v>
+        <v>-0.01399546145739172</v>
       </c>
       <c r="J77" t="n">
-        <v>22.2977778116862</v>
+        <v>22.29222234090169</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.828785027286648</v>
+        <v>-2.028609715972845</v>
       </c>
       <c r="M77" t="n">
-        <v>22.34799995422363</v>
+        <v>22.34300003051758</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-2.049402924258708</v>
+        <v>-2.251263828683067</v>
       </c>
       <c r="P77" t="n">
-        <v>24.09884614210862</v>
+        <v>24.09692309452937</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-9.165778060222571</v>
+        <v>-9.366021267893171</v>
       </c>
       <c r="S77" t="n">
-        <v>25.29700008392334</v>
+        <v>25.29600009918213</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-13.46800285793614</v>
+        <v>-13.66223882449296</v>
       </c>
       <c r="V77" t="n">
-        <v>29.07286668141683</v>
+        <v>29.07253335316976</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-24.70642943635011</v>
+        <v>-24.8775471773371</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.85815001487732</v>
+        <v>28.85790001869202</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-24.14621388286004</v>
+        <v>-24.3188168978285</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4599148009378761</v>
+        <v>0.4601529523944254</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22573,13 +22581,13 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>8.83</v>
+        <v>8.81</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
       </c>
       <c r="CB77" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CC77" t="n">
         <v>8</v>
@@ -22594,7 +22602,7 @@
         <v>8</v>
       </c>
       <c r="CG77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CH77" t="n">
         <v>8</v>
@@ -22611,7 +22619,7 @@
         <v>1</v>
       </c>
       <c r="CL77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM77" t="n">
         <v>4</v>
@@ -22620,7 +22628,7 @@
         <v>0</v>
       </c>
       <c r="CO77" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -22633,13 +22641,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.31000137329102</v>
+        <v>33.81999969482422</v>
       </c>
       <c r="D78" t="n">
-        <v>33.31000137329102</v>
+        <v>33.81999969482422</v>
       </c>
       <c r="E78" t="n">
-        <v>33.79000091552734</v>
+        <v>33.81999969482422</v>
       </c>
       <c r="F78" t="n">
         <v>33.04000091552734</v>
@@ -22648,67 +22656,67 @@
         <v>33.79000091552734</v>
       </c>
       <c r="H78" t="n">
-        <v>2998500</v>
+        <v>14444900</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.008630866488087308</v>
+        <v>0.006547655675418262</v>
       </c>
       <c r="J78" t="n">
-        <v>34.25777816772461</v>
+        <v>34.31444464789497</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.766603221590493</v>
+        <v>-1.440923663909797</v>
       </c>
       <c r="M78" t="n">
-        <v>34.36100044250488</v>
+        <v>34.4120002746582</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-3.058697522420709</v>
+        <v>-1.720331788646267</v>
       </c>
       <c r="P78" t="n">
-        <v>36.65884619492751</v>
+        <v>36.67846151498648</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-9.135161548264634</v>
+        <v>-7.793298034036463</v>
       </c>
       <c r="S78" t="n">
-        <v>38.77680000305176</v>
+        <v>38.78699996948242</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-14.09811699090823</v>
+        <v>-12.80583772543954</v>
       </c>
       <c r="V78" t="n">
-        <v>36.99693341573079</v>
+        <v>37.00033340454102</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-9.965507143551863</v>
+        <v>-8.595419059998196</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.10120010375977</v>
+        <v>36.10375009536743</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-7.731595410807576</v>
+        <v>-6.325521294909048</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3073916839930121</v>
+        <v>0.3099780764308688</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22860,13 +22868,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>16.91</v>
+        <v>17.17</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
       </c>
       <c r="CB78" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CC78" t="n">
         <v>5</v>
@@ -22898,16 +22906,16 @@
         <v>0</v>
       </c>
       <c r="CL78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
       </c>
       <c r="CO78" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79">
@@ -22920,13 +22928,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>44.13000106811523</v>
+        <v>44.09999847412109</v>
       </c>
       <c r="D79" t="n">
-        <v>44.13000106811523</v>
+        <v>44.09999847412109</v>
       </c>
       <c r="E79" t="n">
-        <v>44.27999877929688</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="F79" t="n">
         <v>43.09999847412109</v>
@@ -22935,67 +22943,67 @@
         <v>43.59999847412109</v>
       </c>
       <c r="H79" t="n">
-        <v>3489000</v>
+        <v>25787800</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00937785535143032</v>
+        <v>0.008691611226168572</v>
       </c>
       <c r="J79" t="n">
-        <v>43.07222281561958</v>
+        <v>43.06888919406467</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2.455824620483876</v>
+        <v>2.394093043380659</v>
       </c>
       <c r="M79" t="n">
-        <v>42.99900054931641</v>
+        <v>42.99600028991699</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2.630294900695799</v>
+        <v>2.567676473997514</v>
       </c>
       <c r="P79" t="n">
-        <v>44.26500026996319</v>
+        <v>44.26384632404034</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-0.3049795572678673</v>
+        <v>-0.3701617991346019</v>
       </c>
       <c r="S79" t="n">
-        <v>46.69660018920899</v>
+        <v>46.6960001373291</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-5.496329734272307</v>
+        <v>-5.559366231740148</v>
       </c>
       <c r="V79" t="n">
-        <v>47.06793329874674</v>
+        <v>47.06773328145345</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-6.241897667322769</v>
+        <v>-6.305242679918391</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.53369997024536</v>
+        <v>44.53354995727539</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-0.906502047662445</v>
+        <v>-0.9735390140023361</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.326269377809694</v>
+        <v>0.3260323035505227</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23147,7 +23155,7 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>29.42</v>
+        <v>29.4</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
@@ -23207,10 +23215,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.560000419616699</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="D80" t="n">
-        <v>9.560000419616699</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="E80" t="n">
         <v>9.659999847412109</v>
@@ -23222,67 +23230,67 @@
         <v>9.560000419616699</v>
       </c>
       <c r="H80" t="n">
-        <v>2064000</v>
+        <v>3099000</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.002087630923656492</v>
+        <v>-0.004175361395781008</v>
       </c>
       <c r="J80" t="n">
-        <v>9.606666564941406</v>
+        <v>9.604444291856554</v>
       </c>
       <c r="K80" t="n">
         <v>-1</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.4857683464835824</v>
+        <v>-0.6709844739082711</v>
       </c>
       <c r="M80" t="n">
-        <v>9.601999950408935</v>
+        <v>9.599999904632568</v>
       </c>
       <c r="N80" t="n">
         <v>-1</v>
       </c>
       <c r="O80" t="n">
-        <v>-0.4374039888476246</v>
+        <v>-0.6249994101623636</v>
       </c>
       <c r="P80" t="n">
-        <v>9.932692307692308</v>
+        <v>9.931923059316782</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-3.752173897373025</v>
+        <v>-3.946094780668942</v>
       </c>
       <c r="S80" t="n">
-        <v>10.6510000038147</v>
+        <v>10.65059999465942</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-10.2431657478852</v>
+        <v>-10.42758185795438</v>
       </c>
       <c r="V80" t="n">
-        <v>12.16266666412353</v>
+        <v>12.16253332773844</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-21.39881258263842</v>
+        <v>-21.5623940770986</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.36520000457764</v>
+        <v>12.36510000228882</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-22.68624513895808</v>
+        <v>-22.84736912692058</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4262666889768775</v>
+        <v>0.4261119461241666</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23434,7 +23442,7 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>22.23</v>
+        <v>22.19</v>
       </c>
       <c r="CA80" t="n">
         <v>1.64</v>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,82 +897,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.46999931335449</v>
+        <v>16.45000076293945</v>
       </c>
       <c r="D2" t="n">
-        <v>16.46999931335449</v>
+        <v>16.45000076293945</v>
       </c>
       <c r="E2" t="n">
         <v>16.6299991607666</v>
       </c>
       <c r="F2" t="n">
-        <v>16.44000053405762</v>
+        <v>16.42000007629395</v>
       </c>
       <c r="G2" t="n">
         <v>16.48999977111816</v>
       </c>
       <c r="H2" t="n">
-        <v>11367400</v>
+        <v>15802600</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002434510495176845</v>
+        <v>0.00121731329228103</v>
       </c>
       <c r="J2" t="n">
-        <v>16.40111117892795</v>
+        <v>16.39888911777073</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4200211417080537</v>
+        <v>0.3116774849909837</v>
       </c>
       <c r="M2" t="n">
-        <v>16.38299999237061</v>
+        <v>16.3810001373291</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.531034126987731</v>
+        <v>0.4212235213472172</v>
       </c>
       <c r="P2" t="n">
-        <v>15.92038459044236</v>
+        <v>15.9196154154264</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3.45227038825484</v>
+        <v>3.331646736887242</v>
       </c>
       <c r="S2" t="n">
-        <v>15.60039999008179</v>
+        <v>15.60000001907349</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>5.574211711402064</v>
+        <v>5.448722710427604</v>
       </c>
       <c r="V2" t="n">
-        <v>14.72819999059041</v>
+        <v>14.72806666692098</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>11.8262878279551</v>
+        <v>11.691514812911</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.09625</v>
+        <v>14.09615000724792</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.83958012488777</v>
+        <v>16.69853651160942</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4974688535545104</v>
+        <v>0.4974898619927849</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.64</v>
+        <v>16.62</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.06</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.61000061035156</v>
+        <v>27.6299991607666</v>
       </c>
       <c r="D3" t="n">
-        <v>27.61000061035156</v>
+        <v>27.6299991607666</v>
       </c>
       <c r="E3" t="n">
         <v>27.97999954223633</v>
@@ -1199,67 +1199,67 @@
         <v>27.82999992370605</v>
       </c>
       <c r="H3" t="n">
-        <v>7016800</v>
+        <v>8215200</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.006119513034269608</v>
+        <v>-0.005399622828339834</v>
       </c>
       <c r="J3" t="n">
-        <v>28.34333335028754</v>
+        <v>28.34555541144477</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.5873200264518</v>
+        <v>-2.524403703831667</v>
       </c>
       <c r="M3" t="n">
-        <v>28.375</v>
+        <v>28.3769998550415</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.696033091272026</v>
+        <v>-2.632416034432156</v>
       </c>
       <c r="P3" t="n">
-        <v>29.27538460951585</v>
+        <v>29.27615378453181</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-5.688683586493211</v>
+        <v>-5.622851402819744</v>
       </c>
       <c r="S3" t="n">
-        <v>30.28559997558594</v>
+        <v>30.28599994659424</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.834559551044888</v>
+        <v>-8.769731197619951</v>
       </c>
       <c r="V3" t="n">
-        <v>29.37386665344238</v>
+        <v>29.37399997711181</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.004882039879862</v>
+        <v>-5.937226178607396</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.09049997329712</v>
+        <v>28.09059996604919</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.710540443930587</v>
+        <v>-1.639697286064671</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2550162962301336</v>
+        <v>0.2550364980569664</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>16.84</v>
+        <v>16.85</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.15</v>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.090000152587891</v>
+        <v>9.050000190734863</v>
       </c>
       <c r="D4" t="n">
-        <v>9.090000152587891</v>
+        <v>9.050000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>9.140000343322754</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="F4" t="n">
         <v>8.619999885559082</v>
@@ -1486,67 +1486,67 @@
         <v>8.619999885559082</v>
       </c>
       <c r="H4" t="n">
-        <v>9985000</v>
+        <v>12772700</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05697671504456658</v>
+        <v>0.05232555689587448</v>
       </c>
       <c r="J4" t="n">
-        <v>8.868888749016655</v>
+        <v>8.864444308810764</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>2.493112833281977</v>
+        <v>2.093260169051621</v>
       </c>
       <c r="M4" t="n">
-        <v>8.842999839782715</v>
+        <v>8.838999843597412</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.793173326702724</v>
+        <v>2.387151836984034</v>
       </c>
       <c r="P4" t="n">
-        <v>8.865384542025053</v>
+        <v>8.863846081953783</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>2.533625129266309</v>
+        <v>2.100150510962482</v>
       </c>
       <c r="S4" t="n">
-        <v>8.987599945068359</v>
+        <v>8.986799945831299</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.139349861424576</v>
+        <v>0.7032563903114467</v>
       </c>
       <c r="V4" t="n">
-        <v>8.639866609573364</v>
+        <v>8.639599943161011</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>5.209959405111167</v>
+        <v>4.750222814410746</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.877249948978424</v>
+        <v>8.877049949169159</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.396577823450265</v>
+        <v>1.948285100974245</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4867863430344366</v>
+        <v>0.4821502210126094</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>17.48</v>
+        <v>17.4</v>
       </c>
       <c r="CA4" t="n">
         <v>0.98</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.36999988555908</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="D5" t="n">
-        <v>12.36999988555908</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="E5" t="n">
         <v>12.44999980926514</v>
@@ -1769,67 +1769,67 @@
         <v>12.05000019073486</v>
       </c>
       <c r="H5" t="n">
-        <v>2460300</v>
+        <v>2895000</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02570476410914058</v>
+        <v>0.01741293788061471</v>
       </c>
       <c r="J5" t="n">
-        <v>12.41555553012424</v>
+        <v>12.40444448259142</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3669239322769389</v>
+        <v>-1.08383753110771</v>
       </c>
       <c r="M5" t="n">
-        <v>12.43400001525879</v>
+        <v>12.42400007247925</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5147187519797908</v>
+        <v>-1.239533272836224</v>
       </c>
       <c r="P5" t="n">
-        <v>13.00999997212337</v>
+        <v>13.00615384028508</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-4.919293527560468</v>
+        <v>-5.660039021230539</v>
       </c>
       <c r="S5" t="n">
-        <v>12.99559993743896</v>
+        <v>12.99359994888306</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.813937447224686</v>
+        <v>-5.568891561738336</v>
       </c>
       <c r="V5" t="n">
-        <v>12.13999996821086</v>
+        <v>12.13933330535889</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.894562750827764</v>
+        <v>1.076394799598277</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.73919996738434</v>
+        <v>11.73869997024536</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.373448956720465</v>
+        <v>4.526059008791625</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2411080232366082</v>
+        <v>0.2329762110047888</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1977,13 +1977,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-10.06</v>
+        <v>-9.98</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2014,13 +2014,13 @@
         <v>7</v>
       </c>
       <c r="CM5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>52.34000015258789</v>
+        <v>52.36000061035156</v>
       </c>
       <c r="D6" t="n">
-        <v>52.34000015258789</v>
+        <v>52.36000061035156</v>
       </c>
       <c r="E6" t="n">
         <v>52.45999908447266</v>
@@ -2048,67 +2048,67 @@
         <v>51.25</v>
       </c>
       <c r="H6" t="n">
-        <v>8004200</v>
+        <v>9420600</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0232648795935404</v>
+        <v>0.02365589537393209</v>
       </c>
       <c r="J6" t="n">
-        <v>53.08666695488824</v>
+        <v>53.08888922797309</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.406505333881379</v>
+        <v>-1.37295887749987</v>
       </c>
       <c r="M6" t="n">
-        <v>53.27800025939941</v>
+        <v>53.28000030517578</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.760576790128376</v>
+        <v>-1.726726144059066</v>
       </c>
       <c r="P6" t="n">
-        <v>56.53923064011794</v>
+        <v>56.53999988849346</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-7.427109353961463</v>
+        <v>-7.392994846808581</v>
       </c>
       <c r="S6" t="n">
-        <v>58.76240005493164</v>
+        <v>58.76280006408692</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-10.92943769543114</v>
+        <v>-10.89600809823977</v>
       </c>
       <c r="V6" t="n">
-        <v>58.14000002543131</v>
+        <v>58.1401333618164</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.975919969567276</v>
+        <v>-9.94172599414942</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.66235000610352</v>
+        <v>55.66245000839233</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-5.968755996021226</v>
+        <v>-5.932993243277748</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2881829918944778</v>
+        <v>0.2885330573442928</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2117,10 +2117,10 @@
         <v>44.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AF6" t="n">
         <v>45.3</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>45.6</v>
       </c>
       <c r="AG6" t="n">
         <v>67.8</v>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57.47999954223633</v>
+        <v>57.27999877929688</v>
       </c>
       <c r="D7" t="n">
-        <v>57.47999954223633</v>
+        <v>57.27999877929688</v>
       </c>
       <c r="E7" t="n">
         <v>57.59999847412109</v>
@@ -2331,67 +2331,67 @@
         <v>56.20000076293945</v>
       </c>
       <c r="H7" t="n">
-        <v>2632200</v>
+        <v>2854000</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02277577868185654</v>
+        <v>0.01921704629352283</v>
       </c>
       <c r="J7" t="n">
-        <v>58.3033332824707</v>
+        <v>58.28111097547743</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.412155521615633</v>
+        <v>-1.717730117742245</v>
       </c>
       <c r="M7" t="n">
-        <v>58.52000007629395</v>
+        <v>58.5</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.777171108512892</v>
+        <v>-2.085472172142094</v>
       </c>
       <c r="P7" t="n">
-        <v>62.14230816180889</v>
+        <v>62.13461582477276</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-7.502631874298325</v>
+        <v>-7.813063589491724</v>
       </c>
       <c r="S7" t="n">
-        <v>64.50800003051758</v>
+        <v>64.50400001525878</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-10.8947734931426</v>
+        <v>-11.19930738288018</v>
       </c>
       <c r="V7" t="n">
-        <v>58.79885342915853</v>
+        <v>58.79752009073894</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.242992524524594</v>
+        <v>-2.58092740833313</v>
       </c>
       <c r="Y7" t="n">
-        <v>54.23040866851807</v>
+        <v>54.22940866470337</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.992193224250438</v>
+        <v>5.625342760890292</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3041544721531711</v>
+        <v>0.3013549086010704</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.58</v>
+        <v>17.52</v>
       </c>
       <c r="CA7" t="n">
         <v>0.27</v>
@@ -2584,13 +2584,13 @@
         <v>3</v>
       </c>
       <c r="CM7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.73999977111816</v>
+        <v>18.98999977111816</v>
       </c>
       <c r="D8" t="n">
-        <v>18.73999977111816</v>
+        <v>18.98999977111816</v>
       </c>
       <c r="E8" t="n">
         <v>19.01000022888184</v>
@@ -2618,67 +2618,67 @@
         <v>18.93000030517578</v>
       </c>
       <c r="H8" t="n">
-        <v>1453900</v>
+        <v>2675000</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.002129974124856604</v>
+        <v>0.01118205946722828</v>
       </c>
       <c r="J8" t="n">
-        <v>19.93222215440538</v>
+        <v>19.95999993218316</v>
       </c>
       <c r="K8" t="n">
         <v>-1</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.981382176315518</v>
+        <v>-4.859720262328175</v>
       </c>
       <c r="M8" t="n">
-        <v>19.89899997711182</v>
+        <v>19.92399997711182</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.824414328995204</v>
+        <v>-4.687814731312022</v>
       </c>
       <c r="P8" t="n">
-        <v>20.33807688492995</v>
+        <v>20.34769226954533</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-7.857562555464254</v>
+        <v>-6.672464279692527</v>
       </c>
       <c r="S8" t="n">
-        <v>21.98520004272461</v>
+        <v>21.99020004272461</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-14.76084031666728</v>
+        <v>-13.64335142826066</v>
       </c>
       <c r="V8" t="n">
-        <v>24.96906669616699</v>
+        <v>24.97073336283366</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-24.94713559319801</v>
+        <v>-23.9509729442596</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.3816500377655</v>
+        <v>26.3829000377655</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-28.96577831829422</v>
+        <v>-28.02156038974054</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4496177847082978</v>
+        <v>0.4520354918006124</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2830,13 +2830,13 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="CA8" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="CC8" t="n">
         <v>10</v>
@@ -2864,16 +2864,16 @@
         <v>1</v>
       </c>
       <c r="CL8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CM8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN8" t="n">
         <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -2886,82 +2886,82 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.39999961853027</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="D9" t="n">
-        <v>16.39999961853027</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="E9" t="n">
         <v>16.65999984741211</v>
       </c>
       <c r="F9" t="n">
-        <v>16.36000061035156</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="G9" t="n">
         <v>16.42000007629395</v>
       </c>
       <c r="H9" t="n">
-        <v>32175800</v>
+        <v>38607100</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009230745755709036</v>
+        <v>0.00184619610126191</v>
       </c>
       <c r="J9" t="n">
-        <v>16.66777780320909</v>
+        <v>16.65444458855523</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.606562001488056</v>
+        <v>-2.248312154264427</v>
       </c>
       <c r="M9" t="n">
-        <v>16.68000011444092</v>
+        <v>16.66800022125244</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6786600359087</v>
+        <v>-2.327810951863421</v>
       </c>
       <c r="P9" t="n">
-        <v>17.21846166023841</v>
+        <v>17.21384631670438</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-4.753398171441554</v>
+        <v>-5.424967859464788</v>
       </c>
       <c r="S9" t="n">
-        <v>17.84440008163452</v>
+        <v>17.84200010299683</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-8.094418733588174</v>
+        <v>-8.754620599340534</v>
       </c>
       <c r="V9" t="n">
-        <v>16.08053340911865</v>
+        <v>16.07973341623942</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.986664255990821</v>
+        <v>1.24546387195593</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.29110005378723</v>
+        <v>15.29050005912781</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.25192798976157</v>
+        <v>6.471342491686581</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3496130476004444</v>
+        <v>0.3475766067890351</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>16.73</v>
+        <v>16.61</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3154,13 +3154,13 @@
         <v>5</v>
       </c>
       <c r="CM9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN9" t="n">
         <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -3173,82 +3173,82 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>19.88999938964844</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>19.88999938964844</v>
       </c>
       <c r="E10" t="n">
         <v>20.18000030517578</v>
       </c>
       <c r="F10" t="n">
-        <v>19.96999931335449</v>
+        <v>19.88999938964844</v>
       </c>
       <c r="G10" t="n">
         <v>20.13999938964844</v>
       </c>
       <c r="H10" t="n">
-        <v>16044000</v>
+        <v>19240300</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.003984059960658093</v>
+        <v>-0.009462178026868773</v>
       </c>
       <c r="J10" t="n">
-        <v>20.73111110263401</v>
+        <v>20.71888881259494</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.526637327900455</v>
+        <v>-4.000646127521218</v>
       </c>
       <c r="M10" t="n">
-        <v>20.72800006866455</v>
+        <v>20.71700000762939</v>
       </c>
       <c r="N10" t="n">
         <v>-1</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.512157787789184</v>
+        <v>-3.991893699263406</v>
       </c>
       <c r="P10" t="n">
-        <v>21.20653849381667</v>
+        <v>21.20230770111084</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-5.689464568526673</v>
+        <v>-6.189459798254165</v>
       </c>
       <c r="S10" t="n">
-        <v>22.43299995422363</v>
+        <v>22.4307999420166</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-10.8456290250451</v>
+        <v>-11.32728462175272</v>
       </c>
       <c r="V10" t="n">
-        <v>22.93273331960042</v>
+        <v>22.93199998219808</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.78841592377407</v>
+        <v>-13.265308716689</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.47475001335144</v>
+        <v>22.47420001029968</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-11.0112460066576</v>
+        <v>-11.49852105733211</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2549869493237068</v>
+        <v>0.2550150202250509</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.97</v>
+        <v>7.92</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>9</v>
       </c>
       <c r="CF10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CG10" t="n">
         <v>10</v>
@@ -3443,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="CI10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CJ10" t="inlineStr"/>
       <c r="CK10" t="n">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.47999954223633</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="D11" t="n">
-        <v>15.47999954223633</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E11" t="n">
         <v>15.55000019073486</v>
@@ -3487,67 +3487,67 @@
         <v>15.36999988555908</v>
       </c>
       <c r="H11" t="n">
-        <v>2315000</v>
+        <v>3257800</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01242639508550236</v>
+        <v>0.009156333791500382</v>
       </c>
       <c r="J11" t="n">
-        <v>15.52333333757189</v>
+        <v>15.51777786678738</v>
       </c>
       <c r="K11" t="n">
         <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2791526432707273</v>
+        <v>-0.5656580624180017</v>
       </c>
       <c r="M11" t="n">
-        <v>15.51999998092651</v>
+        <v>15.51500005722046</v>
       </c>
       <c r="N11" t="n">
         <v>-1</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.257734785691653</v>
+        <v>-0.5478553124794825</v>
       </c>
       <c r="P11" t="n">
-        <v>15.85615385495699</v>
+        <v>15.85423080737774</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.372292273154695</v>
+        <v>-2.67581888617735</v>
       </c>
       <c r="S11" t="n">
-        <v>16.46419996261597</v>
+        <v>16.46319997787475</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.977821106487959</v>
+        <v>-6.275813171725502</v>
       </c>
       <c r="V11" t="n">
-        <v>16.62599998474121</v>
+        <v>16.62566665649414</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.892821144933493</v>
+        <v>-7.191689668885068</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.10309999942779</v>
+        <v>16.10285000324249</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-3.869444126991742</v>
+        <v>-4.178451006692772</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2150279889496136</v>
+        <v>0.2128604431997216</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3719,13 +3719,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.91</v>
+        <v>6.89</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CC11" t="n">
         <v>2</v>
@@ -3756,13 +3756,13 @@
         <v>6</v>
       </c>
       <c r="CM11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN11" t="n">
         <v>1</v>
       </c>
       <c r="CO11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.79999923706055</v>
+        <v>17.75</v>
       </c>
       <c r="D12" t="n">
-        <v>17.79999923706055</v>
+        <v>17.75</v>
       </c>
       <c r="E12" t="n">
         <v>17.89999961853027</v>
@@ -3790,67 +3790,67 @@
         <v>17.60000038146973</v>
       </c>
       <c r="H12" t="n">
-        <v>17606800</v>
+        <v>21455400</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01714281354631697</v>
+        <v>0.01428571428571423</v>
       </c>
       <c r="J12" t="n">
-        <v>17.81444443596734</v>
+        <v>17.80888896518283</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.08108700194785141</v>
+        <v>-0.3306717521680613</v>
       </c>
       <c r="M12" t="n">
-        <v>17.81900005340576</v>
+        <v>17.81400012969971</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1066323378880282</v>
+        <v>-0.3592687169290253</v>
       </c>
       <c r="P12" t="n">
-        <v>18.25692308866061</v>
+        <v>18.25500004108136</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.502742928702238</v>
+        <v>-2.766365598164314</v>
       </c>
       <c r="S12" t="n">
-        <v>18.97620006561279</v>
+        <v>18.97520008087158</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.198294835032159</v>
+        <v>-6.45684933834597</v>
       </c>
       <c r="V12" t="n">
-        <v>19.29653333028158</v>
+        <v>19.29620000203451</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.755455695622568</v>
+        <v>-8.012976657950695</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.71779999732971</v>
+        <v>18.71755000114441</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-4.903358089092202</v>
+        <v>-5.169212856838919</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2544321670995803</v>
+        <v>0.2523214929635227</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4018,13 +4018,13 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.95</v>
+        <v>7.92</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="CC12" t="n">
         <v>2</v>
@@ -4074,13 +4074,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35.29999923706055</v>
+        <v>35.13000106811523</v>
       </c>
       <c r="D13" t="n">
-        <v>35.29999923706055</v>
+        <v>35.13000106811523</v>
       </c>
       <c r="E13" t="n">
-        <v>35.29999923706055</v>
+        <v>35.31000137329102</v>
       </c>
       <c r="F13" t="n">
         <v>34.95999908447266</v>
@@ -4089,67 +4089,67 @@
         <v>35.13999938964844</v>
       </c>
       <c r="H13" t="n">
-        <v>2220500</v>
+        <v>3066300</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007707692468526206</v>
+        <v>0.002854761413165097</v>
       </c>
       <c r="J13" t="n">
-        <v>34.85777833726671</v>
+        <v>34.83888965182834</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.268643387180693</v>
+        <v>0.8355932671683698</v>
       </c>
       <c r="M13" t="n">
-        <v>34.8430004119873</v>
+        <v>34.82600059509277</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.311594350858537</v>
+        <v>0.8729123868024574</v>
       </c>
       <c r="P13" t="n">
-        <v>34.42961546090933</v>
+        <v>34.42307706979605</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>2.528008996032588</v>
+        <v>2.053633952844565</v>
       </c>
       <c r="S13" t="n">
-        <v>34.725</v>
+        <v>34.72160003662109</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.65586533350769</v>
+        <v>1.176216047254161</v>
       </c>
       <c r="V13" t="n">
-        <v>34.86846669514974</v>
+        <v>34.86733337402344</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.237601141695261</v>
+        <v>0.753334622049091</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.30124997138977</v>
+        <v>34.30039998054504</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.911699330210468</v>
+        <v>2.418633858616033</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1688529007361442</v>
+        <v>0.1676129044620688</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4317,13 +4317,13 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="CC13" t="n">
         <v>2</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.539999961853027</v>
+        <v>3.5</v>
       </c>
       <c r="D14" t="n">
-        <v>3.539999961853027</v>
+        <v>3.5</v>
       </c>
       <c r="E14" t="n">
         <v>3.569999933242798</v>
@@ -4388,67 +4388,67 @@
         <v>3.559999942779541</v>
       </c>
       <c r="H14" t="n">
-        <v>16699600</v>
+        <v>18872000</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01142856052943642</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.795555591583252</v>
+        <v>3.79111115137736</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.733022967623664</v>
+        <v>-7.678781754304287</v>
       </c>
       <c r="M14" t="n">
-        <v>3.84200005531311</v>
+        <v>3.838000059127808</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.86049164789694</v>
+        <v>-8.80667154561271</v>
       </c>
       <c r="P14" t="n">
-        <v>3.992307717983539</v>
+        <v>3.990769257912269</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-11.3294812945673</v>
+        <v>-12.29761046543217</v>
       </c>
       <c r="S14" t="n">
-        <v>4.061000022888184</v>
+        <v>4.060200023651123</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-12.82935380691333</v>
+        <v>-13.79735038638231</v>
       </c>
       <c r="V14" t="n">
-        <v>5.248066674868266</v>
+        <v>5.247800008455912</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-32.54658941729458</v>
+        <v>-33.30538522122867</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.49200000166893</v>
+        <v>5.491800001859665</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-35.54260814316681</v>
+        <v>-36.26861868941313</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.544866983817698</v>
+        <v>0.5429281185454533</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4600,13 +4600,13 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>4.99</v>
+        <v>4.93</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.87</v>
+        <v>3.91</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CC14" t="n">
         <v>8</v>
@@ -4621,7 +4621,7 @@
         <v>10</v>
       </c>
       <c r="CG14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CH14" t="n">
         <v>10</v>
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53.27000045776367</v>
+        <v>53.25</v>
       </c>
       <c r="D15" t="n">
-        <v>53.27000045776367</v>
+        <v>53.25</v>
       </c>
       <c r="E15" t="n">
         <v>53.81000137329102</v>
@@ -4675,67 +4675,67 @@
         <v>53.09999847412109</v>
       </c>
       <c r="H15" t="n">
-        <v>7531000</v>
+        <v>8930300</v>
       </c>
       <c r="I15" t="n">
-        <v>0.009857828583197614</v>
+        <v>0.009478672985782088</v>
       </c>
       <c r="J15" t="n">
-        <v>54.3066669040256</v>
+        <v>54.30444463094076</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.90891193542406</v>
+        <v>-1.941728044742717</v>
       </c>
       <c r="M15" t="n">
-        <v>54.29600028991699</v>
+        <v>54.29400024414063</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.889641643352964</v>
+        <v>-1.922864845924287</v>
       </c>
       <c r="P15" t="n">
-        <v>56.09653854370117</v>
+        <v>56.09576929532565</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-5.038703205787871</v>
+        <v>-5.073055118191913</v>
       </c>
       <c r="S15" t="n">
-        <v>57.66539985656738</v>
+        <v>57.66499984741211</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.622247326362949</v>
+        <v>-7.656290399886731</v>
       </c>
       <c r="V15" t="n">
-        <v>55.96226654052735</v>
+        <v>55.96213320414225</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.810859618800392</v>
+        <v>-4.846372089228196</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.45874994277954</v>
+        <v>53.45864994049072</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.3530750068377955</v>
+        <v>-0.3903015521772221</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.2861596852756749</v>
+        <v>0.2859822307571595</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4948,13 +4948,13 @@
         <v>5</v>
       </c>
       <c r="CM15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN15" t="n">
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.75</v>
+        <v>23.61000061035156</v>
       </c>
       <c r="D16" t="n">
-        <v>23.75</v>
+        <v>23.61000061035156</v>
       </c>
       <c r="E16" t="n">
         <v>23.76000022888184</v>
@@ -4982,67 +4982,67 @@
         <v>22.92000007629395</v>
       </c>
       <c r="H16" t="n">
-        <v>1307600</v>
+        <v>1755700</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03847831781697919</v>
+        <v>0.03235678810508391</v>
       </c>
       <c r="J16" t="n">
-        <v>23.22555584377713</v>
+        <v>23.21000035603841</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.258047814874532</v>
+        <v>1.723396157592417</v>
       </c>
       <c r="M16" t="n">
-        <v>23.20600032806396</v>
+        <v>23.19200038909912</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.344219875228365</v>
+        <v>1.80234656019113</v>
       </c>
       <c r="P16" t="n">
-        <v>23.06000012617845</v>
+        <v>23.05461553426889</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.992193712255198</v>
+        <v>2.408997344835925</v>
       </c>
       <c r="S16" t="n">
-        <v>23.36579998016357</v>
+        <v>23.3629999923706</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.644283611785578</v>
+        <v>1.057229885124423</v>
       </c>
       <c r="V16" t="n">
-        <v>22.04379997253418</v>
+        <v>22.04286664326986</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>7.740044954099047</v>
+        <v>7.109483500686984</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.71919995307922</v>
+        <v>20.71849995613098</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>14.62797817379213</v>
+        <v>13.95612935464922</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2705789736113304</v>
+        <v>0.2630563540880829</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5198,7 +5198,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.93</v>
+        <v>11.86</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.6299991607666</v>
+        <v>20.56999969482422</v>
       </c>
       <c r="D17" t="n">
-        <v>20.6299991607666</v>
+        <v>20.56999969482422</v>
       </c>
       <c r="E17" t="n">
         <v>20.79000091552734</v>
@@ -5273,67 +5273,67 @@
         <v>20.64999961853027</v>
       </c>
       <c r="H17" t="n">
-        <v>10100300</v>
+        <v>11630800</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.006740553390057302</v>
+        <v>-0.009629309510423956</v>
       </c>
       <c r="J17" t="n">
-        <v>20.19222217135959</v>
+        <v>20.18555556403266</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.168047606112153</v>
+        <v>1.904550655403181</v>
       </c>
       <c r="M17" t="n">
-        <v>20.14799995422363</v>
+        <v>20.1420000076294</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.392293069476247</v>
+        <v>2.124911563065761</v>
       </c>
       <c r="P17" t="n">
-        <v>19.07384615678054</v>
+        <v>19.07153848501352</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>8.158569546986044</v>
+        <v>7.857054694293233</v>
       </c>
       <c r="S17" t="n">
-        <v>19.55099994659424</v>
+        <v>19.54979995727539</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>5.518895284741297</v>
+        <v>5.218466377039143</v>
       </c>
       <c r="V17" t="n">
-        <v>17.44393329620361</v>
+        <v>17.443533299764</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>18.26460701530189</v>
+        <v>17.92335498394995</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.62629995822907</v>
+        <v>17.62599996089935</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>17.04100809390357</v>
+        <v>16.70259696162311</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3553101899181755</v>
+        <v>0.3560281843641236</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>41.26</v>
+        <v>41.14</v>
       </c>
       <c r="CA17" t="n">
         <v>1.11</v>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.989999771118164</v>
+        <v>10.01000022888184</v>
       </c>
       <c r="D18" t="n">
-        <v>9.989999771118164</v>
+        <v>10.01000022888184</v>
       </c>
       <c r="E18" t="n">
         <v>10.39000034332275</v>
@@ -5552,67 +5552,67 @@
         <v>10.22999954223633</v>
       </c>
       <c r="H18" t="n">
-        <v>5993000</v>
+        <v>6764600</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02346038923338001</v>
+        <v>-0.02150531018561508</v>
       </c>
       <c r="J18" t="n">
-        <v>11.2455554538303</v>
+        <v>11.24777772691515</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-11.16490588541345</v>
+        <v>-11.0046404550776</v>
       </c>
       <c r="M18" t="n">
-        <v>11.33899993896484</v>
+        <v>11.34099998474121</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-11.89699422442921</v>
+        <v>-11.73617633057203</v>
       </c>
       <c r="P18" t="n">
-        <v>10.64846145189725</v>
+        <v>10.64923070027278</v>
       </c>
       <c r="Q18" t="n">
         <v>-1</v>
       </c>
       <c r="R18" t="n">
-        <v>-6.183632102661851</v>
+        <v>-6.002597646556477</v>
       </c>
       <c r="S18" t="n">
-        <v>10.04179992675781</v>
+        <v>10.04219993591309</v>
       </c>
       <c r="T18" t="n">
         <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5158453267090083</v>
+        <v>-0.3206439548778223</v>
       </c>
       <c r="V18" t="n">
-        <v>9.13046664873759</v>
+        <v>9.13059998512268</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>9.41390134204604</v>
+        <v>9.631352213348986</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.831299982070924</v>
+        <v>8.831399984359741</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.12037629114176</v>
+        <v>13.345565217399</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9846101507881797</v>
+        <v>0.984123274357357</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>-0.87</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="CB18" t="n">
         <v>-0.51</v>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.5</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="D19" t="n">
-        <v>11.5</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E19" t="n">
         <v>11.59000015258789</v>
@@ -5835,67 +5835,67 @@
         <v>11.39999961853027</v>
       </c>
       <c r="H19" t="n">
-        <v>2578700</v>
+        <v>3300400</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01500441989750145</v>
+        <v>0.01147397310823584</v>
       </c>
       <c r="J19" t="n">
-        <v>11.433333184984</v>
+        <v>11.4288887447781</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5830916840905297</v>
+        <v>0.2722162588474282</v>
       </c>
       <c r="M19" t="n">
-        <v>11.40499982833862</v>
+        <v>11.40099983215332</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.832969514171541</v>
+        <v>0.5175002794689822</v>
       </c>
       <c r="P19" t="n">
-        <v>11.32269221085769</v>
+        <v>11.32115375078642</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.565950798983027</v>
+        <v>1.226432309082568</v>
       </c>
       <c r="S19" t="n">
-        <v>11.8431999206543</v>
+        <v>11.84239992141724</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.89786479121882</v>
+        <v>-3.229074223195968</v>
       </c>
       <c r="V19" t="n">
-        <v>13.03813330968221</v>
+        <v>13.03786664326986</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-11.7971896217688</v>
+        <v>-12.10218395612581</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.9203999710083</v>
+        <v>13.92019997119904</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-17.38743122359424</v>
+        <v>-17.67359619935223</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.596683897592006</v>
+        <v>0.5957897878455236</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -6047,13 +6047,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>6.05</v>
+        <v>6.03</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CC19" t="n">
         <v>6</v>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.97000026702881</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>10.97000026702881</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
         <v>11.10000038146973</v>
@@ -6122,67 +6122,67 @@
         <v>10.84000015258789</v>
       </c>
       <c r="H20" t="n">
-        <v>8420500</v>
+        <v>9914000</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0148010953932769</v>
+        <v>0.01757627872414447</v>
       </c>
       <c r="J20" t="n">
-        <v>11.08888901604546</v>
+        <v>11.09222231970893</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.072143014910012</v>
+        <v>-0.8314142743521111</v>
       </c>
       <c r="M20" t="n">
-        <v>11.13300008773804</v>
+        <v>11.13600006103516</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.464114070103682</v>
+        <v>-1.221264909211168</v>
       </c>
       <c r="P20" t="n">
-        <v>11.59230782435491</v>
+        <v>11.59346166023841</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-5.368280128126496</v>
+        <v>-5.118934082248982</v>
       </c>
       <c r="S20" t="n">
-        <v>12.27880012512207</v>
+        <v>12.27940011978149</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-10.65902078995076</v>
+        <v>-10.41907672444393</v>
       </c>
       <c r="V20" t="n">
-        <v>11.70033337275187</v>
+        <v>11.70053337097168</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-6.241985441405355</v>
+        <v>-5.987191769476606</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.51510003566742</v>
+        <v>11.51525003433228</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-4.733782311488333</v>
+        <v>-4.47450148972951</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2334960631051387</v>
+        <v>0.2358873777100202</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6197,13 +6197,13 @@
         <v>10.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="AJ20" t="n">
         <v>2</v>
@@ -6330,7 +6330,7 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
       <c r="CA20" t="n">
         <v>0.57</v>
@@ -6367,13 +6367,13 @@
         <v>3</v>
       </c>
       <c r="CM20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN20" t="n">
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -6401,7 +6401,7 @@
         <v>4.539999961853027</v>
       </c>
       <c r="H21" t="n">
-        <v>9215800</v>
+        <v>10510800</v>
       </c>
       <c r="I21" t="n">
         <v>0.05286349118323885</v>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.5</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="E22" t="n">
         <v>2.519999980926514</v>
@@ -6688,67 +6688,67 @@
         <v>2.490000009536743</v>
       </c>
       <c r="H22" t="n">
-        <v>12708900</v>
+        <v>16916200</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0121457372640803</v>
+        <v>0.008097158176053387</v>
       </c>
       <c r="J22" t="n">
-        <v>2.509999990463257</v>
+        <v>2.508888880411784</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3984059960658085</v>
+        <v>-0.7528779382186235</v>
       </c>
       <c r="M22" t="n">
-        <v>2.512999987602234</v>
+        <v>2.511999988555908</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5173094972689533</v>
+        <v>-0.8757953471095451</v>
       </c>
       <c r="P22" t="n">
-        <v>2.625769230035635</v>
+        <v>2.625384615017818</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-4.789805158693559</v>
+        <v>-5.156753212715675</v>
       </c>
       <c r="S22" t="n">
-        <v>2.865000004768372</v>
+        <v>2.864800004959106</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-12.73996524121755</v>
+        <v>-13.08293754445568</v>
       </c>
       <c r="V22" t="n">
-        <v>3.280133204460144</v>
+        <v>3.280066537857055</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-23.78358303862057</v>
+        <v>-24.08690553077869</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.150781619548797</v>
+        <v>3.150731619596481</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-20.65460885994351</v>
+        <v>-20.97073600144842</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4292971068666449</v>
+        <v>0.4277586124068904</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -6763,13 +6763,13 @@
         <v>2.4</v>
       </c>
       <c r="AG22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>2.8</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.7</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
@@ -6896,10 +6896,10 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>7.58</v>
+        <v>7.55</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="n">
         <v>0.38</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.41999816894531</v>
+        <v>43.5</v>
       </c>
       <c r="D23" t="n">
-        <v>43.41999816894531</v>
+        <v>43.5</v>
       </c>
       <c r="E23" t="n">
         <v>43.70999908447266</v>
@@ -6971,67 +6971,67 @@
         <v>42.95000076293945</v>
       </c>
       <c r="H23" t="n">
-        <v>1179800</v>
+        <v>1646000</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01330221038790613</v>
+        <v>0.01516923101576007</v>
       </c>
       <c r="J23" t="n">
-        <v>43.41888851589627</v>
+        <v>43.42777760823568</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002555691974094918</v>
+        <v>0.1663045998251226</v>
       </c>
       <c r="M23" t="n">
-        <v>43.51399955749512</v>
+        <v>43.52199974060058</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2160256228012365</v>
+        <v>-0.05054855183977566</v>
       </c>
       <c r="P23" t="n">
-        <v>46.19730758666992</v>
+        <v>46.20038458017203</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-6.011842600381311</v>
+        <v>-5.844939614054556</v>
       </c>
       <c r="S23" t="n">
-        <v>48.51079971313477</v>
+        <v>48.51239974975586</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.4941612471729</v>
+        <v>-10.33220326269488</v>
       </c>
       <c r="V23" t="n">
-        <v>48.88306666056315</v>
+        <v>48.88360000610351</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-11.17578921460183</v>
+        <v>-11.01310051925662</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.36909997940064</v>
+        <v>46.36949998855591</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.360058340070125</v>
+        <v>-6.188334981537665</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2705221940675301</v>
+        <v>0.2718335377306536</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7183,7 +7183,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="CA23" t="n">
         <v>0.52</v>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.63000011444092</v>
+        <v>14.64999961853027</v>
       </c>
       <c r="D24" t="n">
-        <v>14.63000011444092</v>
+        <v>14.64999961853027</v>
       </c>
       <c r="E24" t="n">
         <v>14.71000003814697</v>
@@ -7258,67 +7258,67 @@
         <v>14.51000022888184</v>
       </c>
       <c r="H24" t="n">
-        <v>10472100</v>
+        <v>14016700</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01526719426498246</v>
+        <v>0.01665508491738565</v>
       </c>
       <c r="J24" t="n">
-        <v>14.66333325703939</v>
+        <v>14.66555542416043</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.227323092329423</v>
+        <v>-0.1060703476973442</v>
       </c>
       <c r="M24" t="n">
-        <v>14.70899991989136</v>
+        <v>14.71099987030029</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5370848180072847</v>
+        <v>-0.4146574149128498</v>
       </c>
       <c r="P24" t="n">
-        <v>15.13192301530104</v>
+        <v>15.13269222699679</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-3.316980269808364</v>
+        <v>-3.189733863782605</v>
       </c>
       <c r="S24" t="n">
-        <v>15.57239992141724</v>
+        <v>15.57279991149902</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.051731343479081</v>
+        <v>-5.92571854909245</v>
       </c>
       <c r="V24" t="n">
-        <v>14.19926661809285</v>
+        <v>14.19939994812012</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>3.03349115086844</v>
+        <v>3.173371213266036</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.55599995613098</v>
+        <v>13.55609995365143</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>7.922692252770308</v>
+        <v>8.069427553786932</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2347829394298691</v>
+        <v>0.2358159355817102</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>16.08</v>
+        <v>16.1</v>
       </c>
       <c r="CA24" t="n">
         <v>0.42</v>
@@ -7507,13 +7507,13 @@
         <v>6</v>
       </c>
       <c r="CM24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN24" t="n">
         <v>0</v>
       </c>
       <c r="CO24" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.910000085830688</v>
+        <v>3.880000114440918</v>
       </c>
       <c r="D25" t="n">
-        <v>3.910000085830688</v>
+        <v>3.880000114440918</v>
       </c>
       <c r="E25" t="n">
         <v>3.970000028610229</v>
@@ -7541,67 +7541,67 @@
         <v>3.890000104904175</v>
       </c>
       <c r="H25" t="n">
-        <v>26418900</v>
+        <v>30628200</v>
       </c>
       <c r="I25" t="n">
-        <v>0.007731951161061623</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>4.100000063578288</v>
+        <v>4.096666733423869</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.634145726860709</v>
+        <v>-5.288851475645123</v>
       </c>
       <c r="M25" t="n">
-        <v>4.122000074386596</v>
+        <v>4.11900007724762</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.143134030327644</v>
+        <v>-5.80237820647008</v>
       </c>
       <c r="P25" t="n">
-        <v>4.594230761894813</v>
+        <v>4.59307691684136</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-14.89325877444443</v>
+        <v>-15.52503507585111</v>
       </c>
       <c r="S25" t="n">
-        <v>4.937400007247925</v>
+        <v>4.936800007820129</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-20.80852108212927</v>
+        <v>-21.40657696696624</v>
       </c>
       <c r="V25" t="n">
-        <v>5.535000003178914</v>
+        <v>5.534800003369649</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-29.35862540948401</v>
+        <v>-29.89809727399852</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.720149993896484</v>
+        <v>5.719999994039536</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-31.64514759223556</v>
+        <v>-32.16783009643304</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4717073639559126</v>
+        <v>0.4698036634472098</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.63</v>
+        <v>-1.62</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>52.90999984741211</v>
+        <v>52.93999862670898</v>
       </c>
       <c r="D26" t="n">
-        <v>52.90999984741211</v>
+        <v>52.93999862670898</v>
       </c>
       <c r="E26" t="n">
         <v>53.06000137329102</v>
@@ -7828,67 +7828,67 @@
         <v>52.27999877929688</v>
       </c>
       <c r="H26" t="n">
-        <v>3466100</v>
+        <v>5289300</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01360151482941618</v>
+        <v>0.01417620407957743</v>
       </c>
       <c r="J26" t="n">
-        <v>52.35555521647135</v>
+        <v>52.35888841417101</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.05899866527693</v>
+        <v>1.109859720361635</v>
       </c>
       <c r="M26" t="n">
-        <v>52.39999961853027</v>
+        <v>52.40299949645996</v>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9732828866309455</v>
+        <v>1.024748841495797</v>
       </c>
       <c r="P26" t="n">
-        <v>53.19269209641676</v>
+        <v>53.19384589562049</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.5314494113068161</v>
+        <v>-0.4772117237201048</v>
       </c>
       <c r="S26" t="n">
-        <v>55.03499992370605</v>
+        <v>55.035599899292</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.861179393549177</v>
+        <v>-3.807719505951946</v>
       </c>
       <c r="V26" t="n">
-        <v>49.1619999440511</v>
+        <v>49.16219993591309</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>7.623774272052446</v>
+        <v>7.684356468426076</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.82004992485047</v>
+        <v>44.82019991874695</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.04984585275121</v>
+        <v>18.11638217295359</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3335783740146318</v>
+        <v>0.3338230168625892</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8040,13 +8040,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.86</v>
+        <v>14.87</v>
       </c>
       <c r="CA26" t="n">
         <v>0.34</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8100,10 +8100,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.079999923706055</v>
+        <v>7.130000114440918</v>
       </c>
       <c r="D27" t="n">
-        <v>7.079999923706055</v>
+        <v>7.130000114440918</v>
       </c>
       <c r="E27" t="n">
         <v>7.300000190734863</v>
@@ -8115,67 +8115,67 @@
         <v>6.550000190734863</v>
       </c>
       <c r="H27" t="n">
-        <v>27763600</v>
+        <v>30455100</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08091598741033468</v>
+        <v>0.08854960409413093</v>
       </c>
       <c r="J27" t="n">
-        <v>6.685555617014567</v>
+        <v>6.691111193762885</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>5.89994802657294</v>
+        <v>6.559283024427137</v>
       </c>
       <c r="M27" t="n">
-        <v>6.630000066757202</v>
+        <v>6.635000085830688</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>6.787328090766547</v>
+        <v>7.460437410804597</v>
       </c>
       <c r="P27" t="n">
-        <v>6.483076939216027</v>
+        <v>6.48500002347506</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>9.207402443109228</v>
+        <v>9.946030665088987</v>
       </c>
       <c r="S27" t="n">
-        <v>6.490599975585938</v>
+        <v>6.491599979400635</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>9.080823811929788</v>
+        <v>9.834249446455045</v>
       </c>
       <c r="V27" t="n">
-        <v>8.065266663233439</v>
+        <v>8.065599997838339</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-12.21617065705775</v>
+        <v>-11.59987953342803</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.007099986076355</v>
+        <v>8.007349987030029</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-11.57847490330389</v>
+        <v>-10.95680685882602</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.5477936046386901</v>
+        <v>0.5577113614874006</v>
       </c>
       <c r="AC27" t="n">
         <v>1</v>
@@ -8327,13 +8327,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>-4.69</v>
+        <v>-4.72</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="CC27" t="n">
         <v>2</v>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31.26000022888184</v>
+        <v>31.32999992370605</v>
       </c>
       <c r="D28" t="n">
-        <v>31.26000022888184</v>
+        <v>31.32999992370605</v>
       </c>
       <c r="E28" t="n">
         <v>31.86000061035156</v>
@@ -8398,67 +8398,67 @@
         <v>31.32999992370605</v>
       </c>
       <c r="H28" t="n">
-        <v>2245200</v>
+        <v>3201800</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.001915691779278639</v>
+        <v>0.000319292113003744</v>
       </c>
       <c r="J28" t="n">
-        <v>31.51777797275119</v>
+        <v>31.52555571662055</v>
       </c>
       <c r="K28" t="n">
         <v>-1</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.8178804485906991</v>
+        <v>-0.6203087890736168</v>
       </c>
       <c r="M28" t="n">
-        <v>31.49600009918213</v>
+        <v>31.50300006866455</v>
       </c>
       <c r="N28" t="n">
         <v>-1</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.7493010844460277</v>
+        <v>-0.5491545077656805</v>
       </c>
       <c r="P28" t="n">
-        <v>30.68230783022367</v>
+        <v>30.68500012617845</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.882819251585462</v>
+        <v>2.102003568112536</v>
       </c>
       <c r="S28" t="n">
-        <v>32.82100002288819</v>
+        <v>32.82240001678467</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.756100645677354</v>
+        <v>-4.546895084806211</v>
       </c>
       <c r="V28" t="n">
-        <v>34.74633324940999</v>
+        <v>34.74679991404216</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-10.03367174171495</v>
+        <v>-9.83342350601696</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.2772499370575</v>
+        <v>34.27759993553162</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-8.80248477843516</v>
+        <v>-8.599201861767831</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.4815241199505283</v>
+        <v>0.4816285610309761</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8606,13 +8606,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>9.029999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8666,10 +8666,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.72999954223633</v>
+        <v>17.76000022888184</v>
       </c>
       <c r="D29" t="n">
-        <v>17.72999954223633</v>
+        <v>17.76000022888184</v>
       </c>
       <c r="E29" t="n">
         <v>17.85000038146973</v>
@@ -8681,67 +8681,67 @@
         <v>17.47999954223633</v>
       </c>
       <c r="H29" t="n">
-        <v>3876600</v>
+        <v>5145700</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01604577461632783</v>
+        <v>0.01776501159820953</v>
       </c>
       <c r="J29" t="n">
-        <v>17.58666674296061</v>
+        <v>17.59000015258789</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8150083319972304</v>
+        <v>0.9664586402458581</v>
       </c>
       <c r="M29" t="n">
-        <v>17.62200012207031</v>
+        <v>17.62500019073486</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.612866981147931</v>
+        <v>0.7659576549561707</v>
       </c>
       <c r="P29" t="n">
-        <v>17.6280769935021</v>
+        <v>17.62923086606539</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.578183024568113</v>
+        <v>0.741775768948395</v>
       </c>
       <c r="S29" t="n">
-        <v>18.06040012359619</v>
+        <v>18.0610001373291</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-1.829420052151507</v>
+        <v>-1.666573867219843</v>
       </c>
       <c r="V29" t="n">
-        <v>17.12080010096232</v>
+        <v>17.12100010553996</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>3.558241657408091</v>
+        <v>3.732259327158761</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.43220008850098</v>
+        <v>16.4323500919342</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>7.897904399566877</v>
+        <v>8.079490331692162</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2120207465134155</v>
+        <v>0.213352075700757</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>12.14</v>
+        <v>12.16</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CC29" t="n">
         <v>2</v>
@@ -8961,82 +8961,82 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>22.45000076293945</v>
+        <v>22.35000038146973</v>
       </c>
       <c r="D30" t="n">
-        <v>22.45000076293945</v>
+        <v>22.35000038146973</v>
       </c>
       <c r="E30" t="n">
         <v>22.85000038146973</v>
       </c>
       <c r="F30" t="n">
-        <v>22.35000038146973</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="G30" t="n">
         <v>22.48999977111816</v>
       </c>
       <c r="H30" t="n">
-        <v>5469100</v>
+        <v>6286700</v>
       </c>
       <c r="I30" t="n">
-        <v>0.003127864378814182</v>
+        <v>-0.001340428079616096</v>
       </c>
       <c r="J30" t="n">
-        <v>22.26333363850911</v>
+        <v>22.25222248501248</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8384509142308307</v>
+        <v>0.4394073289672747</v>
       </c>
       <c r="M30" t="n">
-        <v>22.25100021362305</v>
+        <v>22.24100017547607</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.8943442874741809</v>
+        <v>0.4900867997557091</v>
       </c>
       <c r="P30" t="n">
-        <v>22.49576928065373</v>
+        <v>22.49192311213567</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.2034538901216416</v>
+        <v>-0.6309942016001472</v>
       </c>
       <c r="S30" t="n">
-        <v>24.7803999710083</v>
+        <v>24.77839996337891</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-9.404203365544083</v>
+        <v>-9.800469705462088</v>
       </c>
       <c r="V30" t="n">
-        <v>28.55346660614014</v>
+        <v>28.55279993693034</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-21.37556860394736</v>
+        <v>-21.72396251562663</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.57784996986389</v>
+        <v>28.57734996795654</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-21.44265301058834</v>
+        <v>-21.79120734941999</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.3989484705167724</v>
+        <v>0.3982015582403813</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9184,13 +9184,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="CA30" t="n">
         <v>0.48</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="CC30" t="n">
         <v>8</v>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.39999961853027</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="D31" t="n">
-        <v>13.39999961853027</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="E31" t="n">
         <v>13.64000034332275</v>
@@ -9255,67 +9255,67 @@
         <v>13.47999954223633</v>
       </c>
       <c r="H31" t="n">
-        <v>4827200</v>
+        <v>5467600</v>
       </c>
       <c r="I31" t="n">
-        <v>0.002243809515929396</v>
+        <v>-0.001495849234146696</v>
       </c>
       <c r="J31" t="n">
-        <v>13.30666648017036</v>
+        <v>13.30111100938585</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7014013502104538</v>
+        <v>0.3675585599532037</v>
       </c>
       <c r="M31" t="n">
-        <v>13.30999984741211</v>
+        <v>13.30499992370605</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6761816089401576</v>
+        <v>0.3382221572470144</v>
       </c>
       <c r="P31" t="n">
-        <v>13.12384616411649</v>
+        <v>13.12192311653724</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>2.10421130330562</v>
+        <v>1.738139012909208</v>
       </c>
       <c r="S31" t="n">
-        <v>13.48520002365112</v>
+        <v>13.48420003890991</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.631806758308515</v>
+        <v>-0.995236328836261</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9772000058492</v>
+        <v>14.97686667760213</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-10.53067587201191</v>
+        <v>-10.86252773128695</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.02739999294281</v>
+        <v>15.02714999675751</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-10.82955384948027</v>
+        <v>-11.16079639618736</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4408909574935851</v>
+        <v>0.4406239542894172</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9467,13 +9467,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>8.32</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
       </c>
       <c r="CB31" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC31" t="n">
         <v>9</v>
@@ -9523,10 +9523,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>33.93000030517578</v>
+        <v>33.93999862670898</v>
       </c>
       <c r="D32" t="n">
-        <v>33.93000030517578</v>
+        <v>33.93999862670898</v>
       </c>
       <c r="E32" t="n">
         <v>33.97999954223633</v>
@@ -9538,67 +9538,67 @@
         <v>32.84000015258789</v>
       </c>
       <c r="H32" t="n">
-        <v>2353100</v>
+        <v>2871000</v>
       </c>
       <c r="I32" t="n">
-        <v>0.03445125287803208</v>
+        <v>0.03475607976113482</v>
       </c>
       <c r="J32" t="n">
-        <v>32.6955557929145</v>
+        <v>32.6966667175293</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>3.775572802860266</v>
+        <v>3.802625875967699</v>
       </c>
       <c r="M32" t="n">
-        <v>32.6620002746582</v>
+        <v>32.66300010681152</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>3.882187312028752</v>
+        <v>3.909617964429288</v>
       </c>
       <c r="P32" t="n">
-        <v>33.38153883127066</v>
+        <v>33.38192338209886</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.64300836063118</v>
+        <v>1.671788764902001</v>
       </c>
       <c r="S32" t="n">
-        <v>33.95560009002686</v>
+        <v>33.95580005645752</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.07539193765741589</v>
+        <v>-0.04653528917670173</v>
       </c>
       <c r="V32" t="n">
-        <v>32.30597138722737</v>
+        <v>32.30603804270427</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>5.027023947004705</v>
+        <v>5.057756020236344</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.38665698051453</v>
+        <v>31.38670697212219</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>8.103262880912146</v>
+        <v>8.134945972046822</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2400835702716263</v>
+        <v>0.2405005445234016</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9806,10 +9806,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>72.27999877929688</v>
+        <v>71.94999694824219</v>
       </c>
       <c r="D33" t="n">
-        <v>72.27999877929688</v>
+        <v>71.94999694824219</v>
       </c>
       <c r="E33" t="n">
         <v>73.19000244140625</v>
@@ -9821,67 +9821,67 @@
         <v>72.30000305175781</v>
       </c>
       <c r="H33" t="n">
-        <v>2539800</v>
+        <v>3173400</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001524187517561781</v>
+        <v>-0.003048375035123563</v>
       </c>
       <c r="J33" t="n">
-        <v>72.63666534423828</v>
+        <v>72.59999847412109</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.4910282751157407</v>
+        <v>-0.8953189249867615</v>
       </c>
       <c r="M33" t="n">
-        <v>72.41099853515625</v>
+        <v>72.37799835205078</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.180911406429199</v>
+        <v>-0.5913418629329456</v>
       </c>
       <c r="P33" t="n">
-        <v>74.45153779249925</v>
+        <v>74.43884541438176</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.916714788691917</v>
+        <v>-3.343480748908446</v>
       </c>
       <c r="S33" t="n">
-        <v>77.36159957885742</v>
+        <v>77.35499954223633</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-6.568634603244845</v>
+        <v>-6.987269893322118</v>
       </c>
       <c r="V33" t="n">
-        <v>85.38186655680339</v>
+        <v>85.37966654459636</v>
       </c>
       <c r="W33" t="n">
         <v>-1</v>
       </c>
       <c r="X33" t="n">
-        <v>-15.345023839213</v>
+        <v>-15.72935353330228</v>
       </c>
       <c r="Y33" t="n">
-        <v>83.67079998016358</v>
+        <v>83.6691499710083</v>
       </c>
       <c r="Z33" t="n">
         <v>-1</v>
       </c>
       <c r="AA33" t="n">
-        <v>-13.61383087477017</v>
+        <v>-14.00654007698996</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4754585875264315</v>
+        <v>0.4751176949240001</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10033,13 +10033,13 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>31.56</v>
+        <v>31.42</v>
       </c>
       <c r="CA33" t="n">
         <v>0.06</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CC33" t="n">
         <v>8</v>
@@ -10074,13 +10074,13 @@
         <v>5</v>
       </c>
       <c r="CM33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
       </c>
       <c r="CO33" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
@@ -10093,10 +10093,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25.3700008392334</v>
+        <v>25.35000038146973</v>
       </c>
       <c r="D34" t="n">
-        <v>25.3700008392334</v>
+        <v>25.35000038146973</v>
       </c>
       <c r="E34" t="n">
         <v>25.47999954223633</v>
@@ -10108,67 +10108,67 @@
         <v>24.98999977111816</v>
       </c>
       <c r="H34" t="n">
-        <v>3628700</v>
+        <v>5430700</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01969460188887306</v>
+        <v>0.01889072494199562</v>
       </c>
       <c r="J34" t="n">
-        <v>25.19777743021647</v>
+        <v>25.19555515713162</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6834865078631911</v>
+        <v>0.6129859944538361</v>
       </c>
       <c r="M34" t="n">
-        <v>25.19899959564209</v>
+        <v>25.19699954986572</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6786033030489125</v>
+        <v>0.6072184559165866</v>
       </c>
       <c r="P34" t="n">
-        <v>25.9815381857065</v>
+        <v>25.98076893733098</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.35373803545449</v>
+        <v>-2.427828665821048</v>
       </c>
       <c r="S34" t="n">
-        <v>25.92539989471436</v>
+        <v>25.92499988555908</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-2.142296966436349</v>
+        <v>-2.217934451793943</v>
       </c>
       <c r="V34" t="n">
-        <v>22.20946666717529</v>
+        <v>22.2093333307902</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>14.23057212233399</v>
+        <v>14.14120362778031</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.5819500207901</v>
+        <v>20.58185001850128</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>23.2633487769955</v>
+        <v>23.16677246546008</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.2864028436396307</v>
+        <v>0.2858811606009989</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10320,7 +10320,7 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>37.87</v>
+        <v>37.84</v>
       </c>
       <c r="CA34" t="n">
         <v>0.38</v>
@@ -10376,10 +10376,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>48.56999969482422</v>
+        <v>48.54999923706055</v>
       </c>
       <c r="D35" t="n">
-        <v>48.56999969482422</v>
+        <v>48.54999923706055</v>
       </c>
       <c r="E35" t="n">
         <v>48.7599983215332</v>
@@ -10391,67 +10391,67 @@
         <v>47.86000061035156</v>
       </c>
       <c r="H35" t="n">
-        <v>1170800</v>
+        <v>2007600</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01356430615016468</v>
+        <v>0.0131469343111017</v>
       </c>
       <c r="J35" t="n">
-        <v>48.32777828640408</v>
+        <v>48.32555601331923</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5012053460944618</v>
+        <v>0.4644400235756378</v>
       </c>
       <c r="M35" t="n">
-        <v>48.36500053405761</v>
+        <v>48.36300048828125</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.423858489616367</v>
+        <v>0.3866566319114274</v>
       </c>
       <c r="P35" t="n">
-        <v>50.22115399287297</v>
+        <v>50.22038474449744</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-3.287766542128984</v>
+        <v>-3.326110534467617</v>
       </c>
       <c r="S35" t="n">
-        <v>52.11080001831055</v>
+        <v>52.11040000915527</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-6.794753337584865</v>
+        <v>-6.832418809813774</v>
       </c>
       <c r="V35" t="n">
-        <v>50.48505439758301</v>
+        <v>50.48492106119792</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-3.793310169931146</v>
+        <v>-3.832672773305624</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.97215427398682</v>
+        <v>48.972054271698</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.82119029706687</v>
+        <v>-0.8618283241619433</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2486962559953933</v>
+        <v>0.2484224215155507</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.85</v>
+        <v>12.84</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
@@ -10640,13 +10640,13 @@
         <v>5</v>
       </c>
       <c r="CM35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39.02000045776367</v>
+        <v>39.06999969482422</v>
       </c>
       <c r="D36" t="n">
-        <v>39.02000045776367</v>
+        <v>39.06999969482422</v>
       </c>
       <c r="E36" t="n">
         <v>39.27999877929688</v>
@@ -10674,67 +10674,67 @@
         <v>38.77000045776367</v>
       </c>
       <c r="H36" t="n">
-        <v>6554200</v>
+        <v>9843500</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01535259297170577</v>
+        <v>0.01665363998350644</v>
       </c>
       <c r="J36" t="n">
-        <v>38.34444427490234</v>
+        <v>38.34999974568685</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.761809815310066</v>
+        <v>1.877444469131566</v>
       </c>
       <c r="M36" t="n">
-        <v>38.36499977111816</v>
+        <v>38.36999969482422</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.707287086024183</v>
+        <v>1.82434194831236</v>
       </c>
       <c r="P36" t="n">
-        <v>40.09076925424429</v>
+        <v>40.09269230182354</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-2.670861189243112</v>
+        <v>-2.550820481948043</v>
       </c>
       <c r="S36" t="n">
-        <v>41.26479995727539</v>
+        <v>41.2657999420166</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-5.439986385093189</v>
+        <v>-5.321113973987524</v>
       </c>
       <c r="V36" t="n">
-        <v>40.1</v>
+        <v>40.10033332824707</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-2.693265691362417</v>
+        <v>-2.569389199308904</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.10240001678467</v>
+        <v>39.10265001296997</v>
       </c>
       <c r="Z36" t="n">
         <v>-1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.2107276253775446</v>
+        <v>-0.08349899082268226</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2626716566457561</v>
+        <v>0.263562370725503</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10886,13 +10886,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>31.72</v>
+        <v>31.76</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CC36" t="n">
         <v>8</v>
@@ -10907,7 +10907,7 @@
         <v>2</v>
       </c>
       <c r="CG36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CH36" t="n">
         <v>5</v>
@@ -10942,10 +10942,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15.3100004196167</v>
+        <v>15.32999992370605</v>
       </c>
       <c r="D37" t="n">
-        <v>15.3100004196167</v>
+        <v>15.32999992370605</v>
       </c>
       <c r="E37" t="n">
         <v>15.5</v>
@@ -10957,67 +10957,67 @@
         <v>15.34000015258789</v>
       </c>
       <c r="H37" t="n">
-        <v>1643500</v>
+        <v>1955400</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.001306303301189304</v>
       </c>
       <c r="J37" t="n">
-        <v>15.67555544111464</v>
+        <v>15.67777760823568</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-2.332006817054419</v>
+        <v>-2.218284333532913</v>
       </c>
       <c r="M37" t="n">
-        <v>15.68799991607666</v>
+        <v>15.6899998664856</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-2.409481759829665</v>
+        <v>-2.294454721752513</v>
       </c>
       <c r="P37" t="n">
-        <v>15.93153843512902</v>
+        <v>15.93230764682476</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-3.901305690239112</v>
+        <v>-3.780417353657784</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06579996109009</v>
+        <v>16.06619995117187</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-4.704400299417821</v>
+        <v>-4.58229095681161</v>
       </c>
       <c r="V37" t="n">
-        <v>15.86000003814697</v>
+        <v>15.86013336817424</v>
       </c>
       <c r="W37" t="n">
         <v>-1</v>
       </c>
       <c r="X37" t="n">
-        <v>-3.467841218205532</v>
+        <v>-3.342553509240811</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.71630001068115</v>
+        <v>15.7164000082016</v>
       </c>
       <c r="Z37" t="n">
         <v>-1</v>
       </c>
       <c r="AA37" t="n">
-        <v>-2.585211473364105</v>
+        <v>-2.458578836717709</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2387535149673357</v>
+        <v>0.2389110676613078</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11165,7 +11165,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>13.2</v>
+        <v>13.22</v>
       </c>
       <c r="CA37" t="n">
         <v>0.38</v>
@@ -11206,13 +11206,13 @@
         <v>7</v>
       </c>
       <c r="CM37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -11225,13 +11225,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>24.5</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="D38" t="n">
-        <v>24.5</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="E38" t="n">
-        <v>24.5</v>
+        <v>24.64999961853027</v>
       </c>
       <c r="F38" t="n">
         <v>23.23999977111816</v>
@@ -11240,79 +11240,79 @@
         <v>23.25</v>
       </c>
       <c r="H38" t="n">
-        <v>16337600</v>
+        <v>19016700</v>
       </c>
       <c r="I38" t="n">
-        <v>0.05877271591286015</v>
+        <v>0.06525498136172492</v>
       </c>
       <c r="J38" t="n">
-        <v>23.66111119588216</v>
+        <v>23.6777778201633</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>3.545432829307843</v>
+        <v>4.106051698563767</v>
       </c>
       <c r="M38" t="n">
-        <v>23.6420000076294</v>
+        <v>23.65699996948242</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>3.629134557540495</v>
+        <v>4.19748763718487</v>
       </c>
       <c r="P38" t="n">
-        <v>23.38961542569674</v>
+        <v>23.39538464179406</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>4.747340022886179</v>
+        <v>5.36266018253421</v>
       </c>
       <c r="S38" t="n">
-        <v>21.80620010375976</v>
+        <v>21.80920009613037</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>12.35336685631798</v>
+        <v>13.02569333069647</v>
       </c>
       <c r="V38" t="n">
-        <v>20.76046667734782</v>
+        <v>20.76146667480469</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>18.01276137367599</v>
+        <v>18.7295676390944</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.8131000328064</v>
+        <v>19.81385003089905</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>23.6555610148491</v>
+        <v>24.40792465921267</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3183680330286218</v>
+        <v>0.3283690304468783</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="AF38" t="n">
-        <v>19.2</v>
+        <v>24.5</v>
       </c>
       <c r="AG38" t="n">
         <v>26.8</v>
@@ -11452,13 +11452,13 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>29.52</v>
+        <v>29.7</v>
       </c>
       <c r="CA38" t="n">
         <v>0.17</v>
       </c>
       <c r="CB38" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="CC38" t="n">
         <v>1</v>
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.52999973297119</v>
+        <v>10.56999969482422</v>
       </c>
       <c r="D39" t="n">
-        <v>10.52999973297119</v>
+        <v>10.56999969482422</v>
       </c>
       <c r="E39" t="n">
-        <v>10.52999973297119</v>
+        <v>10.56999969482422</v>
       </c>
       <c r="F39" t="n">
         <v>9.960000038146973</v>
@@ -11523,67 +11523,67 @@
         <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>14501000</v>
+        <v>16330500</v>
       </c>
       <c r="I39" t="n">
-        <v>0.05405405147397579</v>
+        <v>0.05805805175119993</v>
       </c>
       <c r="J39" t="n">
-        <v>10.23777770996094</v>
+        <v>10.24222215016683</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>2.854350145988556</v>
+        <v>3.200258106606775</v>
       </c>
       <c r="M39" t="n">
-        <v>10.23899993896484</v>
+        <v>10.24299993515015</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>2.842072426418706</v>
+        <v>3.192421768469714</v>
       </c>
       <c r="P39" t="n">
-        <v>10.16884616705087</v>
+        <v>10.17038462712214</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>3.551568781623696</v>
+        <v>3.929203096571095</v>
       </c>
       <c r="S39" t="n">
-        <v>9.573599996566772</v>
+        <v>9.574399995803834</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>9.989969674389968</v>
+        <v>10.39855969519475</v>
       </c>
       <c r="V39" t="n">
-        <v>9.135406462351481</v>
+        <v>9.135673128763834</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>15.26580427884692</v>
+        <v>15.70028333811968</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.659774949550629</v>
+        <v>8.659974949359894</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>21.59669037955324</v>
+        <v>22.055776796508</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.3230494035701803</v>
+        <v>0.3286397422829939</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11739,7 +11739,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>24.49</v>
+        <v>24.58</v>
       </c>
       <c r="CA39" t="n">
         <v>0.59</v>
@@ -11799,10 +11799,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12.27999973297119</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="D40" t="n">
-        <v>12.27999973297119</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="E40" t="n">
         <v>12.43000030517578</v>
@@ -11814,67 +11814,67 @@
         <v>12.22999954223633</v>
       </c>
       <c r="H40" t="n">
-        <v>3870600</v>
+        <v>4529100</v>
       </c>
       <c r="I40" t="n">
-        <v>0.00655737089809616</v>
+        <v>0.002458994544279225</v>
       </c>
       <c r="J40" t="n">
-        <v>12.32222207387288</v>
+        <v>12.31666649712457</v>
       </c>
       <c r="K40" t="n">
         <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3426520042291591</v>
+        <v>-0.7036559357068751</v>
       </c>
       <c r="M40" t="n">
-        <v>12.41699991226196</v>
+        <v>12.41199989318848</v>
       </c>
       <c r="N40" t="n">
         <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.103327536915592</v>
+        <v>-1.466325753451117</v>
       </c>
       <c r="P40" t="n">
-        <v>12.31576919555664</v>
+        <v>12.31384611129761</v>
       </c>
       <c r="Q40" t="n">
         <v>-1</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.2904362855253438</v>
+        <v>-0.680912919517099</v>
       </c>
       <c r="S40" t="n">
-        <v>11.83779996871948</v>
+        <v>11.83679996490478</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>3.735489410365016</v>
+        <v>3.321840180600758</v>
       </c>
       <c r="V40" t="n">
-        <v>14.67393330891927</v>
+        <v>14.67359997431437</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-16.31419146830232</v>
+        <v>-16.65303972001065</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.37454998016358</v>
+        <v>20.3742999792099</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-39.72873145700466</v>
+        <v>-39.97340004458599</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6826020253257143</v>
+        <v>0.6824173083032218</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12022,7 +12022,7 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-14.45</v>
+        <v>-14.39</v>
       </c>
       <c r="CA40" t="n">
         <v>0.8100000000000001</v>
@@ -12082,10 +12082,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21.61000061035156</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="D41" t="n">
-        <v>21.61000061035156</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="E41" t="n">
         <v>21.75</v>
@@ -12097,67 +12097,67 @@
         <v>21.51000022888184</v>
       </c>
       <c r="H41" t="n">
-        <v>1864400</v>
+        <v>2134000</v>
       </c>
       <c r="I41" t="n">
-        <v>0.008399454158304787</v>
+        <v>0.01259918123745707</v>
       </c>
       <c r="J41" t="n">
-        <v>22.28666665818956</v>
+        <v>22.29666667514377</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-3.036192258878457</v>
+        <v>-2.676031897043514</v>
       </c>
       <c r="M41" t="n">
-        <v>22.325</v>
+        <v>22.33400001525879</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-3.202684836051229</v>
+        <v>-2.838717882538643</v>
       </c>
       <c r="P41" t="n">
-        <v>22.68000001173753</v>
+        <v>22.68346155606783</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-4.717810409313108</v>
+        <v>-4.335585160569568</v>
       </c>
       <c r="S41" t="n">
-        <v>22.86880001068115</v>
+        <v>22.87060001373291</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-5.504440109413927</v>
+        <v>-5.118358285705485</v>
       </c>
       <c r="V41" t="n">
-        <v>23.65220003763835</v>
+        <v>23.6528000386556</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-8.634289512337041</v>
+        <v>-8.256101909814905</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.48154998779297</v>
+        <v>23.48199998855591</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-7.970297439540168</v>
+        <v>-7.588788120623984</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3000721527220338</v>
+        <v>0.3016462458330472</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12305,7 +12305,7 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="CA41" t="n">
         <v>0.41</v>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>25.70000076293945</v>
+        <v>25.70999908447266</v>
       </c>
       <c r="D42" t="n">
-        <v>25.70000076293945</v>
+        <v>25.70999908447266</v>
       </c>
       <c r="E42" t="n">
         <v>25.90999984741211</v>
@@ -12376,67 +12376,67 @@
         <v>25.71999931335449</v>
       </c>
       <c r="H42" t="n">
-        <v>1837000</v>
+        <v>2119500</v>
       </c>
       <c r="I42" t="n">
-        <v>0.001168706137761655</v>
+        <v>0.001558200547714383</v>
       </c>
       <c r="J42" t="n">
-        <v>26.11555565728082</v>
+        <v>26.11666658189561</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.591215977920457</v>
+        <v>-1.557118693336099</v>
       </c>
       <c r="M42" t="n">
-        <v>26.16800003051758</v>
+        <v>26.1689998626709</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.788441099940144</v>
+        <v>-1.753986704142213</v>
       </c>
       <c r="P42" t="n">
-        <v>26.844999900231</v>
+        <v>26.8453844510592</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.265223101310906</v>
+        <v>-4.229350369917102</v>
       </c>
       <c r="S42" t="n">
-        <v>27.60059986114502</v>
+        <v>27.60079982757568</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-6.886078953961984</v>
+        <v>-6.850528806828084</v>
       </c>
       <c r="V42" t="n">
-        <v>27.00919990539551</v>
+        <v>27.00926656087239</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-4.847234079653439</v>
+        <v>-4.81045078907086</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.08969990730286</v>
+        <v>26.08974989891052</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-1.493689639007013</v>
+        <v>-1.455555595240581</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.274344556011054</v>
+        <v>0.2744281109248093</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12625,13 +12625,13 @@
         <v>5</v>
       </c>
       <c r="CM42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN42" t="n">
         <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
@@ -12644,10 +12644,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.45999908447266</v>
+        <v>27.5</v>
       </c>
       <c r="D43" t="n">
-        <v>27.45999908447266</v>
+        <v>27.5</v>
       </c>
       <c r="E43" t="n">
         <v>27.60000038146973</v>
@@ -12659,67 +12659,67 @@
         <v>27.29000091552734</v>
       </c>
       <c r="H43" t="n">
-        <v>3596600</v>
+        <v>4320800</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0223379918275155</v>
+        <v>0.02382722915508007</v>
       </c>
       <c r="J43" t="n">
-        <v>27.59000015258789</v>
+        <v>27.5944446987576</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.4711890808128195</v>
+        <v>-0.3422598272537347</v>
       </c>
       <c r="M43" t="n">
-        <v>27.69500007629394</v>
+        <v>27.69900016784668</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.8485321941646831</v>
+        <v>-0.7184380903310803</v>
       </c>
       <c r="P43" t="n">
-        <v>28.66153849088229</v>
+        <v>28.66307698763334</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-4.192166470030419</v>
+        <v>-4.057753423106485</v>
       </c>
       <c r="S43" t="n">
-        <v>29.13140003204346</v>
+        <v>29.132200050354</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-5.737454930872953</v>
+        <v>-5.602735281004534</v>
       </c>
       <c r="V43" t="n">
-        <v>28.03113329569499</v>
+        <v>28.03139996846517</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-2.037499537380616</v>
+        <v>-1.895731105342528</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.88390000343323</v>
+        <v>26.88410000801086</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.142914833658284</v>
+        <v>2.290945175049976</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2525499236625841</v>
+        <v>0.2539297895581197</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12871,13 +12871,13 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>7.71</v>
+        <v>7.72</v>
       </c>
       <c r="CA43" t="n">
         <v>0.83</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="CC43" t="n">
         <v>7</v>
@@ -12905,16 +12905,16 @@
         <v>0</v>
       </c>
       <c r="CL43" t="n">
+        <v>7</v>
+      </c>
+      <c r="CM43" t="n">
         <v>6</v>
       </c>
-      <c r="CM43" t="n">
-        <v>5</v>
-      </c>
       <c r="CN43" t="n">
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
@@ -12927,10 +12927,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12.93000030517578</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="D44" t="n">
-        <v>12.93000030517578</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="E44" t="n">
         <v>13</v>
@@ -12942,67 +12942,67 @@
         <v>12.77999973297119</v>
       </c>
       <c r="H44" t="n">
-        <v>26035800</v>
+        <v>31104800</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01332288975270979</v>
+        <v>0.01097173880385616</v>
       </c>
       <c r="J44" t="n">
-        <v>12.95666662851969</v>
+        <v>12.95333321889242</v>
       </c>
       <c r="K44" t="n">
         <v>-1</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.20581160346609</v>
+        <v>-0.4117364963973563</v>
       </c>
       <c r="M44" t="n">
-        <v>12.96099996566772</v>
+        <v>12.95799989700317</v>
       </c>
       <c r="N44" t="n">
         <v>-1</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.2391764568633445</v>
+        <v>-0.4476020908621364</v>
       </c>
       <c r="P44" t="n">
-        <v>13.21961542276236</v>
+        <v>13.21846155019907</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.190798357778995</v>
+        <v>-2.409220849638123</v>
       </c>
       <c r="S44" t="n">
-        <v>13.66500001907349</v>
+        <v>13.66440000534058</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-5.378702618893519</v>
+        <v>-5.594101362017694</v>
       </c>
       <c r="V44" t="n">
-        <v>12.95360117594401</v>
+        <v>12.95340117136637</v>
       </c>
       <c r="W44" t="n">
         <v>-1</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.1821954408482026</v>
+        <v>-0.4122589282121848</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.43730860233307</v>
+        <v>12.43715859889984</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.961401285405835</v>
+        <v>3.721436982168686</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.233705945260257</v>
+        <v>0.2322505154150879</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13154,13 +13154,13 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.56</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
       </c>
       <c r="CB44" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CC44" t="n">
         <v>2</v>
@@ -13214,10 +13214,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39.79000091552734</v>
+        <v>39.56000137329102</v>
       </c>
       <c r="D45" t="n">
-        <v>39.79000091552734</v>
+        <v>39.56000137329102</v>
       </c>
       <c r="E45" t="n">
         <v>39.9900016784668</v>
@@ -13229,67 +13229,67 @@
         <v>39.63000106811523</v>
       </c>
       <c r="H45" t="n">
-        <v>17553200</v>
+        <v>22953700</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01092480433200738</v>
+        <v>0.005081320117837018</v>
       </c>
       <c r="J45" t="n">
-        <v>39.93777804904514</v>
+        <v>39.91222254435221</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.3700184154870007</v>
+        <v>-0.8824894947150386</v>
       </c>
       <c r="M45" t="n">
-        <v>39.91100006103515</v>
+        <v>39.88800010681152</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.3031724219457491</v>
+        <v>-0.8222992695602659</v>
       </c>
       <c r="P45" t="n">
-        <v>40.77999995304988</v>
+        <v>40.77115381681002</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.427658260574609</v>
+        <v>-2.970611155526446</v>
       </c>
       <c r="S45" t="n">
-        <v>42.45459983825683</v>
+        <v>42.44999984741211</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-6.27634916565238</v>
+        <v>-6.808005852789837</v>
       </c>
       <c r="V45" t="n">
-        <v>41.91455121358236</v>
+        <v>41.91301788330078</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-5.068765468176014</v>
+        <v>-5.614046968799324</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.62494245529174</v>
+        <v>40.62379245758056</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-2.055243624488243</v>
+        <v>-2.618640505807921</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.237265015947064</v>
+        <v>0.2343826170884237</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13461,13 +13461,13 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.449999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CC45" t="n">
         <v>10</v>
@@ -13495,7 +13495,7 @@
         <v>0</v>
       </c>
       <c r="CL45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM45" t="n">
         <v>6</v>
@@ -13504,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="CO45" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
@@ -13517,13 +13517,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.80999946594238</v>
+        <v>16.90999984741211</v>
       </c>
       <c r="D46" t="n">
-        <v>16.80999946594238</v>
+        <v>16.90999984741211</v>
       </c>
       <c r="E46" t="n">
-        <v>16.80999946594238</v>
+        <v>16.90999984741211</v>
       </c>
       <c r="F46" t="n">
         <v>16.6200008392334</v>
@@ -13532,67 +13532,67 @@
         <v>16.75</v>
       </c>
       <c r="H46" t="n">
-        <v>3373900</v>
+        <v>4729000</v>
       </c>
       <c r="I46" t="n">
-        <v>0.01021635111355246</v>
+        <v>0.01622598964346333</v>
       </c>
       <c r="J46" t="n">
-        <v>16.63333320617676</v>
+        <v>16.64444435967339</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1.062121810317732</v>
+        <v>1.595460214833672</v>
       </c>
       <c r="M46" t="n">
-        <v>16.62199993133545</v>
+        <v>16.63199996948242</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1.131028368328419</v>
+        <v>1.671475940595127</v>
       </c>
       <c r="P46" t="n">
-        <v>16.89807693774884</v>
+        <v>16.9019231062669</v>
       </c>
       <c r="Q46" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.5212277830839805</v>
+        <v>0.04778593000586906</v>
       </c>
       <c r="S46" t="n">
-        <v>17.89480003356934</v>
+        <v>17.89680004119873</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-6.062099412074717</v>
+        <v>-5.513835945615924</v>
       </c>
       <c r="V46" t="n">
-        <v>18.49372594197591</v>
+        <v>18.49439261118571</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.104311815348737</v>
+        <v>-8.566881849449512</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.34945268630981</v>
+        <v>18.34995268821716</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-8.389641079136863</v>
+        <v>-7.847174678165095</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.1759662376161187</v>
+        <v>0.1808684332720215</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13748,13 +13748,13 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>28.02</v>
+        <v>28.18</v>
       </c>
       <c r="CA46" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CC46" t="n">
         <v>4</v>
@@ -13786,7 +13786,7 @@
         <v>-1</v>
       </c>
       <c r="CL46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM46" t="n">
         <v>9</v>
@@ -13795,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="CO46" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47">
@@ -13808,10 +13808,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.48999977111816</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="D47" t="n">
-        <v>15.48999977111816</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="E47" t="n">
         <v>15.52999973297119</v>
@@ -13823,88 +13823,88 @@
         <v>15</v>
       </c>
       <c r="H47" t="n">
-        <v>12078000</v>
+        <v>13827600</v>
       </c>
       <c r="I47" t="n">
-        <v>0.03129156451600212</v>
+        <v>0.03328894705469576</v>
       </c>
       <c r="J47" t="n">
-        <v>15.0722221798367</v>
+        <v>15.07555558946398</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>2.771838062740088</v>
+        <v>2.94811601245602</v>
       </c>
       <c r="M47" t="n">
-        <v>15.03499994277954</v>
+        <v>15.03800001144409</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>3.026270901697835</v>
+        <v>3.205216424742464</v>
       </c>
       <c r="P47" t="n">
-        <v>14.31269238545344</v>
+        <v>14.31384625801673</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>8.225617891859848</v>
+        <v>8.426485641980468</v>
       </c>
       <c r="S47" t="n">
-        <v>14.70620004653931</v>
+        <v>14.70680006027222</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>5.329722988252855</v>
+        <v>5.529417644618492</v>
       </c>
       <c r="V47" t="n">
-        <v>14.69546669642131</v>
+        <v>14.69566670099894</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>5.406654249982721</v>
+        <v>5.609366172605806</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.90500002384186</v>
+        <v>14.90515002727509</v>
       </c>
       <c r="Z47" t="n">
         <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.924855728551144</v>
+        <v>4.125087163587517</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4623388341216815</v>
+        <v>0.4635281509218351</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="AF47" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="AH47" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="AI47" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14031,13 +14031,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>10.47</v>
+        <v>10.49</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.09</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14087,10 +14087,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.85999965667725</v>
+        <v>15.85000038146973</v>
       </c>
       <c r="D48" t="n">
-        <v>15.85999965667725</v>
+        <v>15.85000038146973</v>
       </c>
       <c r="E48" t="n">
         <v>16.04999923706055</v>
@@ -14102,67 +14102,67 @@
         <v>15.84000015258789</v>
       </c>
       <c r="H48" t="n">
-        <v>4592000</v>
+        <v>6591300</v>
       </c>
       <c r="I48" t="n">
-        <v>0.001895118958672004</v>
+        <v>0.001263452802278353</v>
       </c>
       <c r="J48" t="n">
-        <v>16.30888907114665</v>
+        <v>16.30777804056804</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-2.752421777541967</v>
+        <v>-2.807112397283788</v>
       </c>
       <c r="M48" t="n">
-        <v>16.44500017166138</v>
+        <v>16.44400024414062</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-3.557315347385797</v>
+        <v>-3.612258902042733</v>
       </c>
       <c r="P48" t="n">
-        <v>17.00153853343083</v>
+        <v>17.00115394592285</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-6.71432690934959</v>
+        <v>-6.77103194356516</v>
       </c>
       <c r="S48" t="n">
-        <v>18.41560010910034</v>
+        <v>18.41540012359619</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-13.87736721737462</v>
+        <v>-13.93073039363041</v>
       </c>
       <c r="V48" t="n">
-        <v>18.87906674067179</v>
+        <v>18.87900007883708</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-15.99161190256545</v>
+        <v>-16.0442803364506</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.44860004425049</v>
+        <v>19.44855004787445</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-18.45171569885887</v>
+        <v>-18.5029200508344</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.3898897141549048</v>
+        <v>0.3897721454119942</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14310,13 +14310,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>58.74</v>
+        <v>58.7</v>
       </c>
       <c r="CA48" t="n">
         <v>2.23</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14348,7 +14348,7 @@
         <v>0</v>
       </c>
       <c r="CL48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CM48" t="n">
         <v>2</v>
@@ -14357,7 +14357,7 @@
         <v>0</v>
       </c>
       <c r="CO48" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -14370,82 +14370,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.730000019073486</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="D49" t="n">
-        <v>5.730000019073486</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E49" t="n">
         <v>5.929999828338623</v>
       </c>
       <c r="F49" t="n">
-        <v>5.690000057220459</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="G49" t="n">
         <v>5.849999904632568</v>
       </c>
       <c r="H49" t="n">
-        <v>15756100</v>
+        <v>18281600</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.01546394328751355</v>
+        <v>-0.02405504109852796</v>
       </c>
       <c r="J49" t="n">
-        <v>6.366666687859429</v>
+        <v>6.361111111111111</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-10</v>
+        <v>-10.70742627939282</v>
       </c>
       <c r="M49" t="n">
-        <v>6.403000020980835</v>
+        <v>6.398000001907349</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-10.51069810560857</v>
+        <v>-11.2222596648121</v>
       </c>
       <c r="P49" t="n">
-        <v>7.091538410920363</v>
+        <v>7.08961532666133</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-19.19947849045314</v>
+        <v>-19.88282062387338</v>
       </c>
       <c r="S49" t="n">
-        <v>7.938999948501587</v>
+        <v>7.93799994468689</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-27.82466234736566</v>
+        <v>-28.44545391890063</v>
       </c>
       <c r="V49" t="n">
-        <v>8.7963490041097</v>
+        <v>8.796015669504801</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-34.85933747744206</v>
+        <v>-35.42531025688366</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.708309254646302</v>
+        <v>8.708059253692626</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-34.20077478281728</v>
+        <v>-34.77306868427617</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4473896423899005</v>
+        <v>0.4480620540470766</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14597,10 +14597,10 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>31.83</v>
+        <v>31.56</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="CB49" t="n">
         <v>0.39</v>
@@ -14657,10 +14657,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>14.26000022888184</v>
+        <v>14.14999961853027</v>
       </c>
       <c r="D50" t="n">
-        <v>14.26000022888184</v>
+        <v>14.14999961853027</v>
       </c>
       <c r="E50" t="n">
         <v>14.35000038146973</v>
@@ -14672,67 +14672,67 @@
         <v>14.02000045776367</v>
       </c>
       <c r="H50" t="n">
-        <v>9304100</v>
+        <v>10538400</v>
       </c>
       <c r="I50" t="n">
-        <v>0.00920029111026377</v>
+        <v>0.001415393059262415</v>
       </c>
       <c r="J50" t="n">
-        <v>14.40888892279731</v>
+        <v>14.39666663275825</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-1.033311414316663</v>
+        <v>-1.71336199218996</v>
       </c>
       <c r="M50" t="n">
-        <v>14.49099998474121</v>
+        <v>14.47999992370606</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-1.594091202143501</v>
+        <v>-2.279007644437337</v>
       </c>
       <c r="P50" t="n">
-        <v>15.05384613917424</v>
+        <v>15.04961534646841</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-5.273376006060013</v>
+        <v>-5.977665921868531</v>
       </c>
       <c r="S50" t="n">
-        <v>15.65840005874634</v>
+        <v>15.65620004653931</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-8.930668680184828</v>
+        <v>-9.620472551013217</v>
       </c>
       <c r="V50" t="n">
-        <v>15.83033336003621</v>
+        <v>15.82960002263387</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-9.919772979125598</v>
+        <v>-10.61050438230928</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.45280000686646</v>
+        <v>15.4522500038147</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-7.718987998644898</v>
+        <v>-8.427577763516233</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.292709906178203</v>
+        <v>0.2898575128351831</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14884,13 +14884,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.59</v>
+        <v>8.52</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CB50" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CC50" t="n">
         <v>5</v>
@@ -14925,13 +14925,13 @@
         <v>4</v>
       </c>
       <c r="CM50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN50" t="n">
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51">
@@ -14944,10 +14944,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.949999809265137</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="D51" t="n">
-        <v>5.949999809265137</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="E51" t="n">
         <v>6.019999980926514</v>
@@ -14959,67 +14959,67 @@
         <v>5.78000020980835</v>
       </c>
       <c r="H51" t="n">
-        <v>13115500</v>
+        <v>15845900</v>
       </c>
       <c r="I51" t="n">
-        <v>0.04020979501920219</v>
+        <v>0.03671329472897344</v>
       </c>
       <c r="J51" t="n">
-        <v>6.015555487738715</v>
+        <v>6.013333267635769</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.089769325662413</v>
+        <v>-1.385811089926663</v>
       </c>
       <c r="M51" t="n">
-        <v>6.057999944686889</v>
+        <v>6.055999946594238</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.782768841331421</v>
+        <v>-2.080583212793374</v>
       </c>
       <c r="P51" t="n">
-        <v>6.38269228201646</v>
+        <v>6.381923051980825</v>
       </c>
       <c r="Q51" t="n">
         <v>-1</v>
       </c>
       <c r="R51" t="n">
-        <v>-6.779152959801232</v>
+        <v>-7.081301669751944</v>
       </c>
       <c r="S51" t="n">
-        <v>7.028399982452393</v>
+        <v>7.027999982833863</v>
       </c>
       <c r="T51" t="n">
         <v>-1</v>
       </c>
       <c r="U51" t="n">
-        <v>-15.34346616412935</v>
+        <v>-15.62322363655583</v>
       </c>
       <c r="V51" t="n">
-        <v>7.939266688028972</v>
+        <v>7.939133354822794</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-25.05605312091735</v>
+        <v>-25.30671090521084</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.775800006389618</v>
+        <v>7.775700006484985</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-23.48054471082286</v>
+        <v>-23.73677195116885</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4611365819090352</v>
+        <v>0.4580539528389659</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15171,10 +15171,10 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>-4.41</v>
+        <v>-4.39</v>
       </c>
       <c r="CA51" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CB51" t="n">
         <v>0.64</v>
@@ -15231,10 +15231,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>29.51000022888184</v>
+        <v>29.42000007629395</v>
       </c>
       <c r="D52" t="n">
-        <v>29.51000022888184</v>
+        <v>29.42000007629395</v>
       </c>
       <c r="E52" t="n">
         <v>29.76000022888184</v>
@@ -15246,67 +15246,67 @@
         <v>29.36000061035156</v>
       </c>
       <c r="H52" t="n">
-        <v>1168800</v>
+        <v>1466200</v>
       </c>
       <c r="I52" t="n">
-        <v>0.007167269532064147</v>
+        <v>0.0040955918893546</v>
       </c>
       <c r="J52" t="n">
-        <v>29.82444445292155</v>
+        <v>29.81444443596734</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.054317120763375</v>
+        <v>-1.322997517262292</v>
       </c>
       <c r="M52" t="n">
-        <v>29.85300006866455</v>
+        <v>29.84400005340576</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.148962713944272</v>
+        <v>-1.420721003729624</v>
       </c>
       <c r="P52" t="n">
-        <v>30.53692304171049</v>
+        <v>30.53346149738018</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.362888957168258</v>
+        <v>-3.646692403944359</v>
       </c>
       <c r="S52" t="n">
-        <v>31.52459995269776</v>
+        <v>31.522799949646</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-6.390563962235206</v>
+        <v>-6.670726828552759</v>
       </c>
       <c r="V52" t="n">
-        <v>30.64946670532226</v>
+        <v>30.64886670430501</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-3.717736714298397</v>
+        <v>-4.009501035933767</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.92135004997253</v>
+        <v>29.9209000492096</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-1.374770257370378</v>
+        <v>-1.674080566065334</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.2934630110050147</v>
+        <v>0.2924618082315888</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15458,13 +15458,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="CA52" t="n">
         <v>0.3</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15496,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="CL52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM52" t="n">
         <v>5</v>
@@ -15505,7 +15505,7 @@
         <v>0</v>
       </c>
       <c r="CO52" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -15518,10 +15518,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.840000152587891</v>
+        <v>9.859999656677246</v>
       </c>
       <c r="D53" t="n">
-        <v>9.840000152587891</v>
+        <v>9.859999656677246</v>
       </c>
       <c r="E53" t="n">
         <v>10</v>
@@ -15533,67 +15533,67 @@
         <v>9.850000381469727</v>
       </c>
       <c r="H53" t="n">
-        <v>7243800</v>
+        <v>8178200</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>0.002032469896262823</v>
       </c>
       <c r="J53" t="n">
-        <v>10.10333336724175</v>
+        <v>10.10555553436279</v>
       </c>
       <c r="K53" t="n">
         <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.606399344474496</v>
+        <v>-2.429909734804406</v>
       </c>
       <c r="M53" t="n">
-        <v>10.09300003051758</v>
+        <v>10.09499998092651</v>
       </c>
       <c r="N53" t="n">
         <v>-1</v>
       </c>
       <c r="O53" t="n">
-        <v>-2.506686586393611</v>
+        <v>-2.3278883080067</v>
       </c>
       <c r="P53" t="n">
-        <v>10.13269230035635</v>
+        <v>10.1334615120521</v>
       </c>
       <c r="Q53" t="n">
         <v>-1</v>
       </c>
       <c r="R53" t="n">
-        <v>-2.888592084831863</v>
+        <v>-2.698602595466625</v>
       </c>
       <c r="S53" t="n">
-        <v>10.09339996337891</v>
+        <v>10.09379995346069</v>
       </c>
       <c r="T53" t="n">
         <v>-1</v>
       </c>
       <c r="U53" t="n">
-        <v>-2.510549583989609</v>
+        <v>-2.316276306855961</v>
       </c>
       <c r="V53" t="n">
-        <v>8.953199955622354</v>
+        <v>8.953333285649618</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>9.904840742539779</v>
+        <v>10.12657903041351</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.92259996175766</v>
+        <v>8.922699959278107</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>10.28175862150288</v>
+        <v>10.50466452617299</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3355305979585387</v>
+        <v>0.3356252140219622</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15745,13 +15745,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>-5.82</v>
+        <v>-5.83</v>
       </c>
       <c r="CA53" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CC53" t="n">
         <v>3</v>
@@ -15820,7 +15820,7 @@
         <v>46.84999847412109</v>
       </c>
       <c r="H54" t="n">
-        <v>5495600</v>
+        <v>7738600</v>
       </c>
       <c r="I54" t="n">
         <v>-0.01837767066076379</v>
@@ -15880,7 +15880,7 @@
         <v>17.12222883733235</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.2892414832580537</v>
+        <v>0.2892414832580535</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16088,82 +16088,82 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>41.4900016784668</v>
+        <v>41.56999969482422</v>
       </c>
       <c r="D55" t="n">
-        <v>41.4900016784668</v>
+        <v>41.56999969482422</v>
       </c>
       <c r="E55" t="n">
         <v>41.97999954223633</v>
       </c>
       <c r="F55" t="n">
-        <v>41.45000076293945</v>
+        <v>41.43999862670898</v>
       </c>
       <c r="G55" t="n">
         <v>41.90000152587891</v>
       </c>
       <c r="H55" t="n">
-        <v>23238800</v>
+        <v>27273100</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.02076934801987318</v>
+        <v>-0.01888126639669374</v>
       </c>
       <c r="J55" t="n">
-        <v>43.05111100938585</v>
+        <v>43.05999967787001</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-3.62617664054873</v>
+        <v>-3.460287956786848</v>
       </c>
       <c r="M55" t="n">
-        <v>43.20599975585937</v>
+        <v>43.21399955749511</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-3.971666173885635</v>
+        <v>-3.80432239437499</v>
       </c>
       <c r="P55" t="n">
-        <v>45.45499992370605</v>
+        <v>45.45807677048903</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-8.722908925078229</v>
+        <v>-8.553105084702823</v>
       </c>
       <c r="S55" t="n">
-        <v>46.59099983215332</v>
+        <v>46.59259979248047</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-10.94846251864771</v>
+        <v>-10.77982366304197</v>
       </c>
       <c r="V55" t="n">
-        <v>38.59893342336019</v>
+        <v>38.59946674346924</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>7.490021093061933</v>
+        <v>7.695787537939437</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.66025005340576</v>
+        <v>36.66065004348755</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>13.17435537953279</v>
+        <v>13.39133279282584</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.2549218290772081</v>
+        <v>0.2538648047458719</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16315,10 +16315,10 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="CA55" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="CB55" t="n">
         <v>1.2</v>
@@ -16375,10 +16375,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.960000038146973</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="D56" t="n">
-        <v>5.960000038146973</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="E56" t="n">
         <v>6.139999866485596</v>
@@ -16390,67 +16390,67 @@
         <v>6.130000114440918</v>
       </c>
       <c r="H56" t="n">
-        <v>6582500</v>
+        <v>7734000</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.02614376640588656</v>
+        <v>-0.02777779076353937</v>
       </c>
       <c r="J56" t="n">
-        <v>6.092222107781304</v>
+        <v>6.091110971238878</v>
       </c>
       <c r="K56" t="n">
         <v>-1</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.170342237940583</v>
+        <v>-2.316673635401536</v>
       </c>
       <c r="M56" t="n">
-        <v>6.080999898910522</v>
+        <v>6.079999876022339</v>
       </c>
       <c r="N56" t="n">
         <v>-1</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.98980205188341</v>
+        <v>-2.138159036316479</v>
       </c>
       <c r="P56" t="n">
-        <v>6.181923059316782</v>
+        <v>6.181538435129019</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-3.589870320940811</v>
+        <v>-3.745647273631317</v>
       </c>
       <c r="S56" t="n">
-        <v>6.314599990844727</v>
+        <v>6.31439998626709</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-5.615556855729159</v>
+        <v>-5.77093908834523</v>
       </c>
       <c r="V56" t="n">
-        <v>6.325278663635254</v>
+        <v>6.325211995442708</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-5.774901706517848</v>
+        <v>-5.932009653556442</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.807140698432923</v>
+        <v>6.807090697288513</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-12.44488248172938</v>
+        <v>-12.59114835012825</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3199023678294644</v>
+        <v>0.3208656375643335</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16602,7 +16602,7 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
       <c r="CA56" t="n">
         <v>0.21</v>
@@ -16640,7 +16640,7 @@
         <v>1</v>
       </c>
       <c r="CL56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM56" t="n">
         <v>4</v>
@@ -16649,7 +16649,7 @@
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
@@ -16662,82 +16662,82 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.52999877929688</v>
+        <v>61.97999954223633</v>
       </c>
       <c r="D57" t="n">
-        <v>62.52999877929688</v>
+        <v>61.97999954223633</v>
       </c>
       <c r="E57" t="n">
         <v>63.18000030517578</v>
       </c>
       <c r="F57" t="n">
-        <v>62.20000076293945</v>
+        <v>61.97999954223633</v>
       </c>
       <c r="G57" t="n">
         <v>62.2400016784668</v>
       </c>
       <c r="H57" t="n">
-        <v>3038600</v>
+        <v>4011400</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.004616378811463706</v>
+        <v>-0.0133715402207667</v>
       </c>
       <c r="J57" t="n">
-        <v>64.33444425794814</v>
+        <v>64.27333323160808</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.804789097759762</v>
+        <v>-3.568095155587704</v>
       </c>
       <c r="M57" t="n">
-        <v>64.76399955749511</v>
+        <v>64.70899963378906</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-3.44944844892566</v>
+        <v>-4.217342420678891</v>
       </c>
       <c r="P57" t="n">
-        <v>65.80730775686411</v>
+        <v>65.78615394005409</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.980159634665174</v>
+        <v>-5.785646629055138</v>
       </c>
       <c r="S57" t="n">
-        <v>65.85039993286132</v>
+        <v>65.83939994812012</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-5.042340148199263</v>
+        <v>-5.861840188283772</v>
       </c>
       <c r="V57" t="n">
-        <v>52.2303998819987</v>
+        <v>52.2267332204183</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>19.71954823353353</v>
+        <v>18.67485427559721</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.57544994354248</v>
+        <v>48.57269994735718</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>28.72757504454055</v>
+        <v>27.60254136461409</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3614217344389113</v>
+        <v>0.363430008662792</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16889,13 +16889,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>21.05</v>
+        <v>20.87</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CC57" t="n">
         <v>10</v>
@@ -16923,7 +16923,7 @@
         <v>0</v>
       </c>
       <c r="CL57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM57" t="n">
         <v>2</v>
@@ -16932,7 +16932,7 @@
         <v>0</v>
       </c>
       <c r="CO57" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58">
@@ -16960,7 +16960,7 @@
         <v>48.2400016784668</v>
       </c>
       <c r="H58" t="n">
-        <v>1476000</v>
+        <v>1979200</v>
       </c>
       <c r="I58" t="n">
         <v>0.01541670163472486</v>
@@ -17232,10 +17232,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18.04999923706055</v>
+        <v>18.10000038146973</v>
       </c>
       <c r="D59" t="n">
-        <v>18.04999923706055</v>
+        <v>18.10000038146973</v>
       </c>
       <c r="E59" t="n">
         <v>18.15999984741211</v>
@@ -17247,67 +17247,67 @@
         <v>17.90999984741211</v>
       </c>
       <c r="H59" t="n">
-        <v>13075600</v>
+        <v>14971500</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01063822061679343</v>
+        <v>0.01343783666944898</v>
       </c>
       <c r="J59" t="n">
-        <v>18.37555567423503</v>
+        <v>18.38111135694716</v>
       </c>
       <c r="K59" t="n">
         <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.771682135473888</v>
+        <v>-1.529347002030897</v>
       </c>
       <c r="M59" t="n">
-        <v>18.45100002288818</v>
+        <v>18.4560001373291</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-2.173328195383459</v>
+        <v>-1.928910669757369</v>
       </c>
       <c r="P59" t="n">
-        <v>19.89192317082332</v>
+        <v>19.89384629176213</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-9.259657389308803</v>
+        <v>-9.017089425463292</v>
       </c>
       <c r="S59" t="n">
-        <v>21.4696000289917</v>
+        <v>21.47060005187988</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-15.92764088438284</v>
+        <v>-15.69867475648423</v>
       </c>
       <c r="V59" t="n">
-        <v>22.84810187021891</v>
+        <v>22.84843521118164</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-21.00000542895161</v>
+        <v>-20.78231960229867</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.58426259040833</v>
+        <v>21.58451259613037</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-16.37426036003817</v>
+        <v>-16.14357609022564</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.369581657949609</v>
+        <v>0.37089416078078</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17459,13 +17459,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>24.39</v>
+        <v>24.46</v>
       </c>
       <c r="CA59" t="n">
         <v>0.1</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17519,10 +17519,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14.25</v>
+        <v>14.1899995803833</v>
       </c>
       <c r="D60" t="n">
-        <v>14.25</v>
+        <v>14.1899995803833</v>
       </c>
       <c r="E60" t="n">
         <v>14.36999988555908</v>
@@ -17534,67 +17534,67 @@
         <v>14</v>
       </c>
       <c r="H60" t="n">
-        <v>6872500</v>
+        <v>8816000</v>
       </c>
       <c r="I60" t="n">
-        <v>0.02370689094090239</v>
+        <v>0.01939651599206305</v>
       </c>
       <c r="J60" t="n">
-        <v>14.14222229851617</v>
+        <v>14.13555558522542</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0.762098765023242</v>
+        <v>0.3851563868828915</v>
       </c>
       <c r="M60" t="n">
-        <v>14.23000011444092</v>
+        <v>14.22400007247925</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.1405473323839686</v>
+        <v>-0.2390360793215366</v>
       </c>
       <c r="P60" t="n">
-        <v>15.15769246908335</v>
+        <v>15.15538476063655</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-5.98832883656095</v>
+        <v>-6.369915350223683</v>
       </c>
       <c r="S60" t="n">
-        <v>15.69560009002686</v>
+        <v>15.69440008163452</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-9.210225042274139</v>
+        <v>-9.585587811105055</v>
       </c>
       <c r="V60" t="n">
-        <v>15.59533338546753</v>
+        <v>15.59493338267009</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-8.626512509961316</v>
+        <v>-9.008911854974777</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.48805001735687</v>
+        <v>15.48775001525879</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-7.993582251926077</v>
+        <v>-8.379205718047643</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3273376771162844</v>
+        <v>0.3243035435392648</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17746,13 +17746,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>25.45</v>
+        <v>25.34</v>
       </c>
       <c r="CA60" t="n">
         <v>0.66</v>
       </c>
       <c r="CB60" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CC60" t="n">
         <v>8</v>
@@ -17806,10 +17806,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34.27000045776367</v>
+        <v>34.25</v>
       </c>
       <c r="D61" t="n">
-        <v>34.27000045776367</v>
+        <v>34.25</v>
       </c>
       <c r="E61" t="n">
         <v>34.68000030517578</v>
@@ -17821,67 +17821,67 @@
         <v>34.02000045776367</v>
       </c>
       <c r="H61" t="n">
-        <v>5198500</v>
+        <v>6309800</v>
       </c>
       <c r="I61" t="n">
-        <v>0.01180990665760984</v>
+        <v>0.01121940006196764</v>
       </c>
       <c r="J61" t="n">
-        <v>34.35555564032661</v>
+        <v>34.35333336724175</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.2490286679063633</v>
+        <v>-0.300795751425648</v>
       </c>
       <c r="M61" t="n">
-        <v>34.41900024414063</v>
+        <v>34.41700019836426</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.432899809175369</v>
+        <v>-0.4852258982530193</v>
       </c>
       <c r="P61" t="n">
-        <v>35.97615403395433</v>
+        <v>35.9753847855788</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-4.7424568356595</v>
+        <v>-4.796014819195058</v>
       </c>
       <c r="S61" t="n">
-        <v>37.6507999420166</v>
+        <v>37.65039993286133</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-8.979356320342378</v>
+        <v>-9.031510791186715</v>
       </c>
       <c r="V61" t="n">
-        <v>40.97059992472331</v>
+        <v>40.97046658833822</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-16.35465304211039</v>
+        <v>-16.40319759075217</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.67849998474121</v>
+        <v>40.67839998245239</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-15.75402123820055</v>
+        <v>-15.80298139854428</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3672800260034953</v>
+        <v>0.367050451430911</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -18029,13 +18029,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>16.97</v>
+        <v>16.96</v>
       </c>
       <c r="CA61" t="n">
         <v>0.09</v>
       </c>
       <c r="CB61" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18070,13 +18070,13 @@
         <v>4</v>
       </c>
       <c r="CM61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN61" t="n">
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
@@ -18089,10 +18089,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11.22000026702881</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="D62" t="n">
-        <v>11.22000026702881</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="E62" t="n">
         <v>11.34000015258789</v>
@@ -18104,67 +18104,67 @@
         <v>11.30000019073486</v>
       </c>
       <c r="H62" t="n">
-        <v>1382900</v>
+        <v>1664200</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>-0.01069517671151177</v>
       </c>
       <c r="J62" t="n">
-        <v>11.77555571662055</v>
+        <v>11.76222239600288</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-4.717870332077894</v>
+        <v>-5.630075611885988</v>
       </c>
       <c r="M62" t="n">
-        <v>11.81700010299683</v>
+        <v>11.80500011444092</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-5.052042233769771</v>
+        <v>-5.97204342343694</v>
       </c>
       <c r="P62" t="n">
-        <v>12.22076925864586</v>
+        <v>12.21615387843205</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-8.189083440136462</v>
+        <v>-9.136701355186158</v>
       </c>
       <c r="S62" t="n">
-        <v>12.87100009918213</v>
+        <v>12.86860010147095</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-12.82728474423857</v>
+        <v>-13.74352848060809</v>
       </c>
       <c r="V62" t="n">
-        <v>11.93426667531331</v>
+        <v>11.93346667607625</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-5.985004589867297</v>
+        <v>-6.984276381962232</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.1301500082016</v>
+        <v>12.1295500087738</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-7.503202685518387</v>
+        <v>-8.48794577341584</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3361889629967964</v>
+        <v>0.3363106299138384</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6.16</v>
+        <v>6.1</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="CB62" t="n">
         <v>0.78</v>
@@ -18357,13 +18357,13 @@
         <v>2</v>
       </c>
       <c r="CM62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN62" t="n">
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
@@ -18376,10 +18376,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>41.95999908447266</v>
+        <v>41.83000183105469</v>
       </c>
       <c r="D63" t="n">
-        <v>41.95999908447266</v>
+        <v>41.83000183105469</v>
       </c>
       <c r="E63" t="n">
         <v>42.45000076293945</v>
@@ -18391,88 +18391,88 @@
         <v>41.70000076293945</v>
       </c>
       <c r="H63" t="n">
-        <v>10191400</v>
+        <v>11400400</v>
       </c>
       <c r="I63" t="n">
-        <v>0.01499755514263001</v>
+        <v>0.01185296750503584</v>
       </c>
       <c r="J63" t="n">
-        <v>42.99444452921549</v>
+        <v>42.98000038994683</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-2.405997928499604</v>
+        <v>-2.675659721867131</v>
       </c>
       <c r="M63" t="n">
-        <v>43.14200019836426</v>
+        <v>43.12900047302246</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-2.739792101564214</v>
+        <v>-3.011891367109945</v>
       </c>
       <c r="P63" t="n">
-        <v>44.65884648836576</v>
+        <v>44.65384659400353</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-6.043253724872162</v>
+        <v>-6.323855565285282</v>
       </c>
       <c r="S63" t="n">
-        <v>46.43500015258789</v>
+        <v>46.43240020751953</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-9.637129435576917</v>
+        <v>-9.912040635193142</v>
       </c>
       <c r="V63" t="n">
-        <v>45.65826675415039</v>
+        <v>45.65740010579427</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-8.099886247525058</v>
+        <v>-8.382865134394414</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.52045003890991</v>
+        <v>43.51980005264282</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-3.585557945844126</v>
+        <v>-3.882826252749564</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.4945088039249196</v>
+        <v>0.4934253960254968</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
       <c r="AD63" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="AE63" t="n">
         <v>41</v>
       </c>
-      <c r="AE63" t="n">
+      <c r="AF63" t="n">
         <v>41.7</v>
       </c>
-      <c r="AF63" t="n">
+      <c r="AG63" t="n">
         <v>41.9</v>
       </c>
-      <c r="AG63" t="n">
+      <c r="AH63" t="n">
         <v>42</v>
       </c>
-      <c r="AH63" t="n">
+      <c r="AI63" t="n">
         <v>42.2</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>42.3</v>
       </c>
       <c r="AJ63" t="n">
         <v>3</v>
@@ -18599,10 +18599,10 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>20.98</v>
+        <v>20.92</v>
       </c>
       <c r="CA63" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CB63" t="n">
         <v>1.79</v>
@@ -18655,10 +18655,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>27.51000022888184</v>
+        <v>27.36000061035156</v>
       </c>
       <c r="D64" t="n">
-        <v>27.51000022888184</v>
+        <v>27.36000061035156</v>
       </c>
       <c r="E64" t="n">
         <v>27.67000007629395</v>
@@ -18670,67 +18670,67 @@
         <v>27.23999977111816</v>
       </c>
       <c r="H64" t="n">
-        <v>4262200</v>
+        <v>4638600</v>
       </c>
       <c r="I64" t="n">
-        <v>0.01102540075351843</v>
+        <v>0.005512735425430515</v>
       </c>
       <c r="J64" t="n">
-        <v>27.35777748955621</v>
+        <v>27.34111086527507</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5564148600292584</v>
+        <v>0.06908916455361504</v>
       </c>
       <c r="M64" t="n">
-        <v>27.36699981689453</v>
+        <v>27.35199985504151</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0.5225286401289287</v>
+        <v>0.02925107982033891</v>
       </c>
       <c r="P64" t="n">
-        <v>27.85499990903414</v>
+        <v>27.84923069293682</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-1.23855566784767</v>
+        <v>-1.756709504759647</v>
       </c>
       <c r="S64" t="n">
-        <v>29.252799949646</v>
+        <v>29.24979995727539</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-5.957719342299237</v>
+        <v>-6.46089665462403</v>
       </c>
       <c r="V64" t="n">
-        <v>31.94266666412354</v>
+        <v>31.94166666666667</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-13.87694547187025</v>
+        <v>-14.34385407664525</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.0155500125885</v>
+        <v>31.01480001449585</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-11.30255559641484</v>
+        <v>-11.78404955839177</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2551244204685871</v>
+        <v>0.2527031723336103</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>18881600000</v>
       </c>
       <c r="BZ64" t="n">
-        <v>6.66</v>
+        <v>6.62</v>
       </c>
       <c r="CA64" t="n">
         <v>0</v>
@@ -18941,13 +18941,13 @@
         <v>6</v>
       </c>
       <c r="CM64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -18960,10 +18960,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27.86000061035156</v>
+        <v>27.69000053405762</v>
       </c>
       <c r="D65" t="n">
-        <v>27.86000061035156</v>
+        <v>27.69000053405762</v>
       </c>
       <c r="E65" t="n">
         <v>27.95000076293945</v>
@@ -18975,67 +18975,67 @@
         <v>27.52000045776367</v>
       </c>
       <c r="H65" t="n">
-        <v>10813100</v>
+        <v>14156800</v>
       </c>
       <c r="I65" t="n">
-        <v>0.02126099373560453</v>
+        <v>0.01502931954150633</v>
       </c>
       <c r="J65" t="n">
-        <v>28.30666690402561</v>
+        <v>28.28777800665961</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-1.577954392117156</v>
+        <v>-2.113200522364345</v>
       </c>
       <c r="M65" t="n">
-        <v>28.39100017547607</v>
+        <v>28.37400016784668</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-1.870309470756806</v>
+        <v>-2.410656339405291</v>
       </c>
       <c r="P65" t="n">
-        <v>30.17430796990028</v>
+        <v>30.16776950542743</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-7.669794322565079</v>
+        <v>-8.213298536784579</v>
       </c>
       <c r="S65" t="n">
-        <v>31.24544017791748</v>
+        <v>31.2420401763916</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-10.83498759591346</v>
+        <v>-11.36942281067202</v>
       </c>
       <c r="V65" t="n">
-        <v>28.7894500096639</v>
+        <v>28.78831667582194</v>
       </c>
       <c r="W65" t="n">
         <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>-3.228437497070431</v>
+        <v>-3.815145408229964</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.63357173919678</v>
+        <v>27.63272173881531</v>
       </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.8193977719992187</v>
+        <v>0.2072861145699323</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2817126629940579</v>
+        <v>0.2769717673005432</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19187,13 +19187,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>11.23</v>
+        <v>11.17</v>
       </c>
       <c r="CA65" t="n">
         <v>0.33</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CC65" t="n">
         <v>9</v>
@@ -19228,13 +19228,13 @@
         <v>3</v>
       </c>
       <c r="CM65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN65" t="n">
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
@@ -19247,10 +19247,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15.30000019073486</v>
+        <v>15.28999996185303</v>
       </c>
       <c r="D66" t="n">
-        <v>15.30000019073486</v>
+        <v>15.28999996185303</v>
       </c>
       <c r="E66" t="n">
         <v>15.4399995803833</v>
@@ -19262,67 +19262,67 @@
         <v>15.28999996185303</v>
       </c>
       <c r="H66" t="n">
-        <v>1454900</v>
+        <v>2029200</v>
       </c>
       <c r="I66" t="n">
-        <v>0.005917169780550235</v>
+        <v>0.005259692538160055</v>
       </c>
       <c r="J66" t="n">
-        <v>15.85777759552002</v>
+        <v>15.85666645897759</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-3.517374369928949</v>
+        <v>-3.573679868909236</v>
       </c>
       <c r="M66" t="n">
-        <v>15.92399988174438</v>
+        <v>15.9229998588562</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.91861150240831</v>
+        <v>-3.975380911977501</v>
       </c>
       <c r="P66" t="n">
-        <v>16.74461544477023</v>
+        <v>16.74423082058246</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-8.627342077817337</v>
+        <v>-8.684966627083611</v>
       </c>
       <c r="S66" t="n">
-        <v>17.49039999008179</v>
+        <v>17.49019998550415</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-12.523440290611</v>
+        <v>-12.57961615918998</v>
       </c>
       <c r="V66" t="n">
-        <v>16.05557762145996</v>
+        <v>16.05551095326742</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-4.70601213197829</v>
+        <v>-4.767901773058183</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.74248309612274</v>
+        <v>15.74243309497833</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-2.810756744575186</v>
+        <v>-2.873972088022574</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.1945807098947645</v>
+        <v>0.1942737411022359</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19476,13 +19476,13 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>23.54</v>
+        <v>23.52</v>
       </c>
       <c r="CA66" t="n">
         <v>0.83</v>
       </c>
       <c r="CB66" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CC66" t="n">
         <v>3</v>
@@ -19536,10 +19536,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.59000015258789</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="D67" t="n">
-        <v>18.59000015258789</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="E67" t="n">
         <v>18.8799991607666</v>
@@ -19551,67 +19551,67 @@
         <v>18.46999931335449</v>
       </c>
       <c r="H67" t="n">
-        <v>3224400</v>
+        <v>3881900</v>
       </c>
       <c r="I67" t="n">
-        <v>0.01307900632855152</v>
+        <v>0.01362397791841219</v>
       </c>
       <c r="J67" t="n">
-        <v>18.86333338419596</v>
+        <v>18.86444452073839</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-1.4490187181714</v>
+        <v>-1.401812488981312</v>
       </c>
       <c r="M67" t="n">
-        <v>18.9310001373291</v>
+        <v>18.93200016021729</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-1.801278232885375</v>
+        <v>-1.753643439350933</v>
       </c>
       <c r="P67" t="n">
-        <v>18.60730765416072</v>
+        <v>18.60769227834848</v>
       </c>
       <c r="Q67" t="n">
         <v>-1</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.09301453974164847</v>
+        <v>-0.04133718874805074</v>
       </c>
       <c r="S67" t="n">
-        <v>18.69799995422363</v>
+        <v>18.69819995880127</v>
       </c>
       <c r="T67" t="n">
         <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>-0.5776008230834681</v>
+        <v>-0.5251819830139273</v>
       </c>
       <c r="V67" t="n">
-        <v>21.4121212387085</v>
+        <v>21.41218790690104</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-13.18001637791412</v>
+        <v>-13.13358325481985</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.27389093399048</v>
+        <v>22.27394093513489</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-16.53905369439017</v>
+        <v>-16.4943445094168</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5086932872812859</v>
+        <v>0.5088153373814257</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19761,7 +19761,7 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.6</v>
+        <v>16.61</v>
       </c>
       <c r="CA67" t="n">
         <v>0.36</v>
@@ -19802,13 +19802,13 @@
         <v>8</v>
       </c>
       <c r="CM67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN67" t="n">
         <v>-1</v>
       </c>
       <c r="CO67" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
@@ -19821,10 +19821,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>40.63000106811523</v>
+        <v>40.43000030517578</v>
       </c>
       <c r="D68" t="n">
-        <v>40.63000106811523</v>
+        <v>40.43000030517578</v>
       </c>
       <c r="E68" t="n">
         <v>40.90000152587891</v>
@@ -19836,67 +19836,67 @@
         <v>40.81000137329102</v>
       </c>
       <c r="H68" t="n">
-        <v>4460800</v>
+        <v>5551300</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.000492016162679354</v>
+        <v>-0.005412083946985002</v>
       </c>
       <c r="J68" t="n">
-        <v>41.55777782864041</v>
+        <v>41.53555552164713</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.232498485243309</v>
+        <v>-2.661708029630586</v>
       </c>
       <c r="M68" t="n">
-        <v>41.62200012207031</v>
+        <v>41.60200004577636</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-2.383352676578999</v>
+        <v>-2.817171624707909</v>
       </c>
       <c r="P68" t="n">
-        <v>42.56807708740234</v>
+        <v>42.56038475036621</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-4.552885993200445</v>
+        <v>-5.005557298614644</v>
       </c>
       <c r="S68" t="n">
-        <v>45.65979988098145</v>
+        <v>45.65579986572266</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-11.01581440561955</v>
+        <v>-11.44608040143063</v>
       </c>
       <c r="V68" t="n">
-        <v>49.46413330078125</v>
+        <v>49.46279996236165</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-17.85967254080339</v>
+        <v>-18.26180415192692</v>
       </c>
       <c r="Y68" t="n">
-        <v>49.77814996719361</v>
+        <v>49.7771499633789</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-18.37784028757091</v>
+        <v>-18.77799284426655</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2168793878941253</v>
+        <v>0.2163796636189861</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20048,13 +20048,13 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="CA68" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CB68" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="CC68" t="n">
         <v>3</v>
@@ -20108,10 +20108,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>39.31999969482422</v>
+        <v>39.25</v>
       </c>
       <c r="D69" t="n">
-        <v>39.31999969482422</v>
+        <v>39.25</v>
       </c>
       <c r="E69" t="n">
         <v>39.33000183105469</v>
@@ -20123,67 +20123,67 @@
         <v>38.93999862670898</v>
       </c>
       <c r="H69" t="n">
-        <v>1016200</v>
+        <v>1197900</v>
       </c>
       <c r="I69" t="n">
-        <v>0.01079686767276611</v>
+        <v>0.008997389727305016</v>
       </c>
       <c r="J69" t="n">
-        <v>39.06999969482422</v>
+        <v>39.06222195095486</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0.6398771485865117</v>
+        <v>0.4807152273132419</v>
       </c>
       <c r="M69" t="n">
-        <v>39.0189998626709</v>
+        <v>39.01199989318847</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0.7714186248051089</v>
+        <v>0.6100689722730191</v>
       </c>
       <c r="P69" t="n">
-        <v>40.08730770991399</v>
+        <v>40.08461541395921</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-1.914092162642304</v>
+        <v>-2.082134019099416</v>
       </c>
       <c r="S69" t="n">
-        <v>41.77380020141602</v>
+        <v>41.77240020751953</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-5.874017912568606</v>
+        <v>-6.038437329405528</v>
       </c>
       <c r="V69" t="n">
-        <v>41.81706680297852</v>
+        <v>41.81660013834635</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-5.971406650588984</v>
+        <v>-6.13775421687797</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.17535013198852</v>
+        <v>40.1750001335144</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-2.129042894098526</v>
+        <v>-2.302427207069894</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2392806873677042</v>
+        <v>0.2383436130409215</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20335,7 +20335,7 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
@@ -20391,10 +20391,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.20999908447266</v>
+        <v>22.02000045776367</v>
       </c>
       <c r="D70" t="n">
-        <v>22.20999908447266</v>
+        <v>22.02000045776367</v>
       </c>
       <c r="E70" t="n">
         <v>22.3799991607666</v>
@@ -20406,67 +20406,67 @@
         <v>21.94000053405762</v>
       </c>
       <c r="H70" t="n">
-        <v>3212800</v>
+        <v>3989700</v>
       </c>
       <c r="I70" t="n">
-        <v>0.01974280919517168</v>
+        <v>0.01101927289035021</v>
       </c>
       <c r="J70" t="n">
-        <v>22.35777770148383</v>
+        <v>22.33666674296061</v>
       </c>
       <c r="K70" t="n">
         <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.6609718505313221</v>
+        <v>-1.417697138256936</v>
       </c>
       <c r="M70" t="n">
-        <v>22.37199993133545</v>
+        <v>22.35300006866455</v>
       </c>
       <c r="N70" t="n">
         <v>-1</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.724123222599715</v>
+        <v>-1.489731176477253</v>
       </c>
       <c r="P70" t="n">
-        <v>23.285384618319</v>
+        <v>23.27807697883019</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-4.618285467358425</v>
+        <v>-5.404555205357618</v>
       </c>
       <c r="S70" t="n">
-        <v>25.03439994812012</v>
+        <v>25.03059997558594</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-11.28207933683488</v>
+        <v>-12.02767620735703</v>
       </c>
       <c r="V70" t="n">
-        <v>24.82226666768392</v>
+        <v>24.82100001017253</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-10.52388816131837</v>
+        <v>-11.28479735409897</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.33355000495911</v>
+        <v>24.33260001182556</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-8.726843884487376</v>
+        <v>-9.504120204737571</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3787777528066927</v>
+        <v>0.3744528929158525</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20618,13 +20618,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2221</v>
+        <v>2202</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CC70" t="n">
         <v>1</v>
@@ -20656,16 +20656,16 @@
         <v>-1</v>
       </c>
       <c r="CL70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN70" t="n">
         <v>0</v>
       </c>
       <c r="CO70" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
@@ -20678,10 +20678,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>34.36000061035156</v>
+        <v>34.40999984741211</v>
       </c>
       <c r="D71" t="n">
-        <v>34.36000061035156</v>
+        <v>34.40999984741211</v>
       </c>
       <c r="E71" t="n">
         <v>34.68000030517578</v>
@@ -20693,67 +20693,67 @@
         <v>34.43000030517578</v>
       </c>
       <c r="H71" t="n">
-        <v>5253700</v>
+        <v>5922100</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.004057953323143071</v>
+        <v>-0.00260870007501135</v>
       </c>
       <c r="J71" t="n">
-        <v>32.43333329094781</v>
+        <v>32.43888876173231</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>5.940392565020416</v>
+        <v>6.076382887705714</v>
       </c>
       <c r="M71" t="n">
-        <v>32.39999980926514</v>
+        <v>32.40499973297119</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>6.049385224150337</v>
+        <v>6.187317176246991</v>
       </c>
       <c r="P71" t="n">
-        <v>32.42461527310885</v>
+        <v>32.4265383206881</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>5.968876796042707</v>
+        <v>6.116784675281111</v>
       </c>
       <c r="S71" t="n">
-        <v>33.43559989929199</v>
+        <v>33.4365998840332</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>2.764719980631014</v>
+        <v>2.911181061336718</v>
       </c>
       <c r="V71" t="n">
-        <v>39.30093327840169</v>
+        <v>39.30126660664876</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-12.57204920058598</v>
+        <v>-12.44557028706341</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.26684999465942</v>
+        <v>40.26709999084473</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-14.6692611542529</v>
+        <v>-14.5456219711981</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4843044492874279</v>
+        <v>0.4842324694218372</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20905,13 +20905,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="CA71" t="n">
         <v>0.17</v>
       </c>
       <c r="CB71" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20965,10 +20965,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>25.60000038146973</v>
+        <v>25.70999908447266</v>
       </c>
       <c r="D72" t="n">
-        <v>25.60000038146973</v>
+        <v>25.70999908447266</v>
       </c>
       <c r="E72" t="n">
         <v>25.90999984741211</v>
@@ -20980,67 +20980,67 @@
         <v>25.53000068664551</v>
       </c>
       <c r="H72" t="n">
-        <v>3641700</v>
+        <v>4640100</v>
       </c>
       <c r="I72" t="n">
-        <v>0.00747739217625254</v>
+        <v>0.01180634548847115</v>
       </c>
       <c r="J72" t="n">
-        <v>27.27000024583604</v>
+        <v>27.28222232394748</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-6.123945175326194</v>
+        <v>-5.762812210846835</v>
       </c>
       <c r="M72" t="n">
-        <v>27.44500026702881</v>
+        <v>27.4560001373291</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-6.722535498662696</v>
+        <v>-6.359269537162435</v>
       </c>
       <c r="P72" t="n">
-        <v>28.70769251309908</v>
+        <v>28.71192323244535</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-10.82529405737275</v>
+        <v>-10.45532242361399</v>
       </c>
       <c r="S72" t="n">
-        <v>28.91480010986328</v>
+        <v>28.91700008392334</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-11.46402436053095</v>
+        <v>-11.09036549484137</v>
       </c>
       <c r="V72" t="n">
-        <v>25.24853333791097</v>
+        <v>25.24926666259766</v>
       </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
       <c r="X72" t="n">
-        <v>1.392029544270693</v>
+        <v>1.824735854833736</v>
       </c>
       <c r="Y72" t="n">
-        <v>23.98460000038147</v>
+        <v>23.98514999389648</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>6.735156646608926</v>
+        <v>7.191320842334088</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2654229837965649</v>
+        <v>0.2674617603592762</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21192,13 +21192,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>9.52</v>
+        <v>9.56</v>
       </c>
       <c r="CA72" t="n">
         <v>0.49</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21226,7 +21226,7 @@
         <v>0</v>
       </c>
       <c r="CL72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM72" t="n">
         <v>1</v>
@@ -21235,7 +21235,7 @@
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
@@ -21248,10 +21248,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12.06999969482422</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="D73" t="n">
-        <v>12.06999969482422</v>
+        <v>12.03999996185303</v>
       </c>
       <c r="E73" t="n">
         <v>12.18000030517578</v>
@@ -21263,67 +21263,67 @@
         <v>11.1899995803833</v>
       </c>
       <c r="H73" t="n">
-        <v>18099600</v>
+        <v>20704700</v>
       </c>
       <c r="I73" t="n">
-        <v>0.08836785651510048</v>
+        <v>0.08566274086510739</v>
       </c>
       <c r="J73" t="n">
-        <v>10.54999997880724</v>
+        <v>10.54666667514377</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>14.4075802755483</v>
+        <v>14.15929158194334</v>
       </c>
       <c r="M73" t="n">
-        <v>10.45599994659424</v>
+        <v>10.45299997329712</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>15.43611090736184</v>
+        <v>15.18224426107342</v>
       </c>
       <c r="P73" t="n">
-        <v>9.421153802138109</v>
+        <v>9.419999966254601</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>28.11593938828342</v>
+        <v>27.81316353486295</v>
       </c>
       <c r="S73" t="n">
-        <v>8.240799970626831</v>
+        <v>8.240199975967407</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>46.46635930790735</v>
+        <v>46.1129583865411</v>
       </c>
       <c r="V73" t="n">
-        <v>6.780999984741211</v>
+        <v>6.780799986521403</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>77.99734142433945</v>
+        <v>77.56016968183174</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.188449989557267</v>
+        <v>6.188299990892411</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>95.04075681619476</v>
+        <v>94.56070293251486</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.5884255415329941</v>
+        <v>0.5856594146408503</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21475,13 +21475,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>-5.8</v>
+        <v>-5.79</v>
       </c>
       <c r="CA73" t="n">
         <v>-0.03</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21535,10 +21535,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>84.91999816894531</v>
+        <v>85</v>
       </c>
       <c r="D74" t="n">
-        <v>84.91999816894531</v>
+        <v>85</v>
       </c>
       <c r="E74" t="n">
         <v>85.08000183105469</v>
@@ -21550,67 +21550,67 @@
         <v>82.22000122070312</v>
       </c>
       <c r="H74" t="n">
-        <v>15588400</v>
+        <v>18358400</v>
       </c>
       <c r="I74" t="n">
-        <v>0.03941250111359285</v>
+        <v>0.04039171572856248</v>
       </c>
       <c r="J74" t="n">
-        <v>83.24888695610895</v>
+        <v>83.25777604844835</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>2.007367634497528</v>
+        <v>2.092566045167766</v>
       </c>
       <c r="M74" t="n">
-        <v>83.12399826049804</v>
+        <v>83.13199844360352</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>2.160627431345253</v>
+        <v>2.24703073590096</v>
       </c>
       <c r="P74" t="n">
-        <v>82.35076904296875</v>
+        <v>82.35384603647086</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>3.119860513550271</v>
+        <v>3.213151650934773</v>
       </c>
       <c r="S74" t="n">
-        <v>82.99960037231445</v>
+        <v>83.00120040893555</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>2.313743425289356</v>
+        <v>2.408157449791861</v>
       </c>
       <c r="V74" t="n">
-        <v>77.85473337809245</v>
+        <v>77.85526672363281</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>9.074932870865062</v>
+        <v>9.176942777332265</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.65500003814697</v>
+        <v>72.65540004730225</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>16.88114806187971</v>
+        <v>16.99061590007186</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3174965684581567</v>
+        <v>0.3186077444086372</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>24.19</v>
+        <v>24.22</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
@@ -21814,10 +21814,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.990000009536743</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="D75" t="n">
-        <v>2.990000009536743</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="E75" t="n">
         <v>3.029999971389771</v>
@@ -21829,67 +21829,67 @@
         <v>3.009999990463257</v>
       </c>
       <c r="H75" t="n">
-        <v>5634300</v>
+        <v>6333000</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.003333330154418945</v>
+        <v>-0.009999990463256836</v>
       </c>
       <c r="J75" t="n">
-        <v>3.188888867696126</v>
+        <v>3.18666664759318</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-6.236932875715871</v>
+        <v>-6.799161724261127</v>
       </c>
       <c r="M75" t="n">
-        <v>3.210999989509582</v>
+        <v>3.208999991416931</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-6.882590491898218</v>
+        <v>-7.447801914800611</v>
       </c>
       <c r="P75" t="n">
-        <v>3.524230782802289</v>
+        <v>3.523461552766653</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-15.15879084515437</v>
+        <v>-15.70789168174237</v>
       </c>
       <c r="S75" t="n">
-        <v>3.713800005912781</v>
+        <v>3.71340000629425</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-19.48947157153503</v>
+        <v>-20.01938860408118</v>
       </c>
       <c r="V75" t="n">
-        <v>3.751461456616719</v>
+        <v>3.751328123410543</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-20.29772812238101</v>
+        <v>-20.82803927292726</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.726546097993851</v>
+        <v>3.726446098089218</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-19.76484576035756</v>
+        <v>-20.29939651795489</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.4644066720612553</v>
+        <v>0.4636704763751223</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -22041,13 +22041,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>11.96</v>
+        <v>11.88</v>
       </c>
       <c r="CA75" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CB75" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CC75" t="n">
         <v>6</v>
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>30.13999938964844</v>
+        <v>30.1299991607666</v>
       </c>
       <c r="D76" t="n">
-        <v>30.13999938964844</v>
+        <v>30.1299991607666</v>
       </c>
       <c r="E76" t="n">
         <v>30.43000030517578</v>
@@ -22112,67 +22112,67 @@
         <v>29.85000038146973</v>
       </c>
       <c r="H76" t="n">
-        <v>6188100</v>
+        <v>8944800</v>
       </c>
       <c r="I76" t="n">
-        <v>0.007689720608816009</v>
+        <v>0.007355376612398379</v>
       </c>
       <c r="J76" t="n">
-        <v>31.33777766757541</v>
+        <v>31.33666653103299</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-3.822154495550886</v>
+        <v>-3.850656447683772</v>
       </c>
       <c r="M76" t="n">
-        <v>31.53799991607666</v>
+        <v>31.53699989318848</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-4.432749477291948</v>
+        <v>-4.461428598748118</v>
       </c>
       <c r="P76" t="n">
-        <v>32.45384590442364</v>
+        <v>32.45346128023588</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-7.129652743127772</v>
+        <v>-7.159366144049055</v>
       </c>
       <c r="S76" t="n">
-        <v>32.33019992828369</v>
+        <v>32.32999992370605</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-6.774472609181677</v>
+        <v>-6.804827615623646</v>
       </c>
       <c r="V76" t="n">
-        <v>28.60878761291504</v>
+        <v>28.60872094472249</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>5.352242805431419</v>
+        <v>5.317533136079412</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.92441541671753</v>
+        <v>26.92436541557312</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>11.94300386159669</v>
+        <v>11.90606982082978</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.2736175095265244</v>
+        <v>0.2735047945836827</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22324,7 +22324,7 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>12.01</v>
+        <v>12</v>
       </c>
       <c r="CA76" t="n">
         <v>0.5</v>
@@ -22380,10 +22380,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>21.47999954223633</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="D77" t="n">
-        <v>21.47999954223633</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="E77" t="n">
         <v>21.78000068664551</v>
@@ -22395,67 +22395,67 @@
         <v>21.61000061035156</v>
       </c>
       <c r="H77" t="n">
-        <v>2380900</v>
+        <v>2867700</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.003248245814498119</v>
+        <v>-0.006960539389361697</v>
       </c>
       <c r="J77" t="n">
-        <v>22.07888878716363</v>
+        <v>22.06999990675185</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-2.712497221669443</v>
+        <v>-3.035796515869492</v>
       </c>
       <c r="M77" t="n">
-        <v>22.13699989318848</v>
+        <v>22.12899990081787</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-2.967883426490449</v>
+        <v>-3.294320961430587</v>
       </c>
       <c r="P77" t="n">
-        <v>23.73500002347506</v>
+        <v>23.73192310333252</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-9.500739325925542</v>
+        <v>-9.826104166310859</v>
       </c>
       <c r="S77" t="n">
-        <v>25.16200004577637</v>
+        <v>25.16040004730225</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-14.63317898752683</v>
+        <v>-14.94571001137628</v>
       </c>
       <c r="V77" t="n">
-        <v>28.96846666971842</v>
+        <v>28.96793333689372</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-25.85040904256768</v>
+        <v>-26.12521104059876</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.79835000991821</v>
+        <v>28.79795001029968</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-25.41239503360932</v>
+        <v>-25.68915630842997</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4585772103931336</v>
+        <v>0.4583697254320304</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22607,7 +22607,7 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>8.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
@@ -22667,10 +22667,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>34</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="D78" t="n">
-        <v>34</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="E78" t="n">
         <v>34.04000091552734</v>
@@ -22682,67 +22682,67 @@
         <v>33.38999938964844</v>
       </c>
       <c r="H78" t="n">
-        <v>3866900</v>
+        <v>4803400</v>
       </c>
       <c r="I78" t="n">
-        <v>0.02255639097744355</v>
+        <v>0.01654133043791117</v>
       </c>
       <c r="J78" t="n">
-        <v>34.01000001695421</v>
+        <v>33.98777770996094</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.02940316656637288</v>
+        <v>-0.5524882341611809</v>
       </c>
       <c r="M78" t="n">
-        <v>34.14900016784668</v>
+        <v>34.12900009155273</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.4363236613497464</v>
+        <v>-0.9639920701152246</v>
       </c>
       <c r="P78" t="n">
-        <v>36.18346155606783</v>
+        <v>36.1757692190317</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-6.034418660261305</v>
+        <v>-6.567296378928924</v>
       </c>
       <c r="S78" t="n">
-        <v>38.50279991149903</v>
+        <v>38.49879989624024</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-11.69473368650846</v>
+        <v>-12.20505748709993</v>
       </c>
       <c r="V78" t="n">
-        <v>37.00906674702962</v>
+        <v>37.00773340861003</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-8.130620443897389</v>
+        <v>-8.667740161582518</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.1090500831604</v>
+        <v>36.1080500793457</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-5.840779744421916</v>
+        <v>-6.392067245983443</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.320372254002109</v>
+        <v>0.3161979275733012</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22894,13 +22894,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>17.26</v>
+        <v>17.16</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
       </c>
       <c r="CB78" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CC78" t="n">
         <v>5</v>
@@ -22954,10 +22954,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>42.16999816894531</v>
+        <v>42</v>
       </c>
       <c r="D79" t="n">
-        <v>42.16999816894531</v>
+        <v>42</v>
       </c>
       <c r="E79" t="n">
         <v>43.36000061035156</v>
@@ -22969,67 +22969,67 @@
         <v>42.88000106811523</v>
       </c>
       <c r="H79" t="n">
-        <v>7834000</v>
+        <v>9972500</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0193023681640625</v>
+        <v>-0.02325581395348841</v>
       </c>
       <c r="J79" t="n">
-        <v>43.1544443766276</v>
+        <v>43.13555569118924</v>
       </c>
       <c r="K79" t="n">
         <v>-1</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.281216273092521</v>
+        <v>-2.632528254228993</v>
       </c>
       <c r="M79" t="n">
-        <v>43.09700012207031</v>
+        <v>43.08000030517578</v>
       </c>
       <c r="N79" t="n">
         <v>-1</v>
       </c>
       <c r="O79" t="n">
-        <v>-2.15096630971833</v>
+        <v>-2.506964478934846</v>
       </c>
       <c r="P79" t="n">
-        <v>43.84423094529372</v>
+        <v>43.83769255418044</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-3.818593097088222</v>
+        <v>-4.192037598487127</v>
       </c>
       <c r="S79" t="n">
-        <v>46.54440010070801</v>
+        <v>46.5410001373291</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-9.398342061124033</v>
+        <v>-9.756988728067542</v>
       </c>
       <c r="V79" t="n">
-        <v>47.10746660868327</v>
+        <v>47.10633328755696</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-10.48128629109475</v>
+        <v>-10.84001434878352</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.59024993896485</v>
+        <v>44.58939994812012</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-5.427760044701195</v>
+        <v>-5.807209675691737</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.3238746399778037</v>
+        <v>0.325637410856925</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23179,13 +23179,13 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>28.11</v>
+        <v>28</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB79" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="CC79" t="n">
         <v>6</v>
@@ -23220,13 +23220,13 @@
         <v>4</v>
       </c>
       <c r="CM79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
       </c>
       <c r="CO79" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80">
@@ -23239,10 +23239,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.380000114440918</v>
+        <v>9.390000343322754</v>
       </c>
       <c r="D80" t="n">
-        <v>9.380000114440918</v>
+        <v>9.390000343322754</v>
       </c>
       <c r="E80" t="n">
         <v>9.560000419616699</v>
@@ -23254,67 +23254,67 @@
         <v>9.5</v>
       </c>
       <c r="H80" t="n">
-        <v>1967400</v>
+        <v>2256500</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.008456651520450165</v>
+        <v>-0.00739954487758443</v>
       </c>
       <c r="J80" t="n">
-        <v>9.575555483500162</v>
+        <v>9.576666620042589</v>
       </c>
       <c r="K80" t="n">
         <v>-1</v>
       </c>
       <c r="L80" t="n">
-        <v>-2.042235245738064</v>
+        <v>-1.949177977326364</v>
       </c>
       <c r="M80" t="n">
-        <v>9.595999908447265</v>
+        <v>9.59699993133545</v>
       </c>
       <c r="N80" t="n">
         <v>-1</v>
       </c>
       <c r="O80" t="n">
-        <v>-2.250935765601711</v>
+        <v>-2.156919761318488</v>
       </c>
       <c r="P80" t="n">
-        <v>9.839230757493238</v>
+        <v>9.839615381681002</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-4.667342949575457</v>
+        <v>-4.569437126529588</v>
       </c>
       <c r="S80" t="n">
-        <v>10.62680000305176</v>
+        <v>10.62700000762939</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-11.73259954316246</v>
+        <v>-11.64015868465764</v>
       </c>
       <c r="V80" t="n">
-        <v>12.12153333028158</v>
+        <v>12.12159999847412</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-22.61704968456308</v>
+        <v>-22.53497603860236</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.3254000043869</v>
+        <v>12.32545000553131</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-23.89699229962229</v>
+        <v>-23.8161662323989</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4251519212831161</v>
+        <v>0.425132038970673</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>21.81</v>
+        <v>21.84</v>
       </c>
       <c r="CA80" t="n">
         <v>1.67</v>
@@ -23507,13 +23507,13 @@
         <v>2</v>
       </c>
       <c r="CM80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
       </c>
       <c r="CO80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.20999908447266</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="D2" t="n">
-        <v>16.20999908447266</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="E2" t="n">
         <v>16.31999969482422</v>
@@ -912,67 +912,67 @@
         <v>16.21999931335449</v>
       </c>
       <c r="H2" t="n">
-        <v>12203000</v>
+        <v>18826100</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.014589767011288</v>
+        <v>-0.02188453456869222</v>
       </c>
       <c r="J2" t="n">
-        <v>16.37777794731988</v>
+        <v>16.36444473266602</v>
       </c>
       <c r="K2" t="n">
         <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.024429952505721</v>
+        <v>-1.677078474470266</v>
       </c>
       <c r="M2" t="n">
-        <v>16.38000011444092</v>
+        <v>16.36800022125244</v>
       </c>
       <c r="N2" t="n">
         <v>-1</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.037857318562444</v>
+        <v>-1.698436369175942</v>
       </c>
       <c r="P2" t="n">
-        <v>15.98384615091177</v>
+        <v>15.97923080737774</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.414884323995974</v>
+        <v>0.6932082435345061</v>
       </c>
       <c r="S2" t="n">
-        <v>15.63479999542236</v>
+        <v>15.63240001678467</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>3.678966723070993</v>
+        <v>2.927254518256264</v>
       </c>
       <c r="V2" t="n">
-        <v>14.75566666285197</v>
+        <v>14.75486666997274</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>9.856094304990181</v>
+        <v>9.048766840653661</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.11660000324249</v>
+        <v>14.11600000858307</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.8293433316048</v>
+        <v>13.98413249365652</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4999249733079386</v>
+        <v>0.5025133604089852</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,13 +1124,13 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.37</v>
+        <v>16.25</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CC2" t="n">
         <v>4</v>
@@ -1142,7 +1142,7 @@
         <v>10</v>
       </c>
       <c r="CF2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CG2" t="n">
         <v>2</v>
@@ -1151,7 +1151,7 @@
         <v>4</v>
       </c>
       <c r="CI2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
@@ -1165,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="CM2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO2" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.90999984741211</v>
+        <v>27.05999946594238</v>
       </c>
       <c r="D3" t="n">
-        <v>26.90999984741211</v>
+        <v>27.05999946594238</v>
       </c>
       <c r="E3" t="n">
         <v>27.42000007629395</v>
@@ -1199,67 +1199,67 @@
         <v>27.42000007629395</v>
       </c>
       <c r="H3" t="n">
-        <v>3831800</v>
+        <v>6645400</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02605860786188008</v>
+        <v>-0.02062973985296368</v>
       </c>
       <c r="J3" t="n">
-        <v>28.14444435967339</v>
+        <v>28.16111098395454</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.386103688833348</v>
+        <v>-3.910042890848795</v>
       </c>
       <c r="M3" t="n">
-        <v>28.2019998550415</v>
+        <v>28.21699981689453</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.581235423978029</v>
+        <v>-4.100366298543942</v>
       </c>
       <c r="P3" t="n">
-        <v>29.10846145336444</v>
+        <v>29.11423066946177</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-7.552654782096807</v>
+        <v>-7.055763302975023</v>
       </c>
       <c r="S3" t="n">
-        <v>30.24819995880127</v>
+        <v>30.25119995117187</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-11.03602897341284</v>
+        <v>-10.54900463578427</v>
       </c>
       <c r="V3" t="n">
-        <v>29.39139998118083</v>
+        <v>29.39239997863769</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-8.44260612069362</v>
+        <v>-7.935386407338268</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.11149996757507</v>
+        <v>28.11224996566773</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4.274051977122613</v>
+        <v>-3.743031955857005</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2611741464818915</v>
+        <v>0.2582148403330922</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>16.41</v>
+        <v>16.5</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.16</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM3" t="n">
         <v>4</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.680000305175781</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="D4" t="n">
-        <v>8.680000305175781</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="E4" t="n">
         <v>9.090000152587891</v>
@@ -1486,67 +1486,67 @@
         <v>8.829999923706055</v>
       </c>
       <c r="H4" t="n">
-        <v>8296000</v>
+        <v>12232600</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04088396439349007</v>
+        <v>-0.0309391963613268</v>
       </c>
       <c r="J4" t="n">
-        <v>8.886666615804037</v>
+        <v>8.896666632758247</v>
       </c>
       <c r="K4" t="n">
         <v>-1</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.325577402225495</v>
+        <v>-1.423748694012883</v>
       </c>
       <c r="M4" t="n">
-        <v>8.845999908447265</v>
+        <v>8.854999923706055</v>
       </c>
       <c r="N4" t="n">
         <v>-1</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.876549909445133</v>
+        <v>-0.9599036326903615</v>
       </c>
       <c r="P4" t="n">
-        <v>8.829230712010311</v>
+        <v>8.832692256340614</v>
       </c>
       <c r="Q4" t="n">
         <v>-1</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.690185835007497</v>
+        <v>-0.7097699858379943</v>
       </c>
       <c r="S4" t="n">
-        <v>9.013199949264527</v>
+        <v>9.014999952316284</v>
       </c>
       <c r="T4" t="n">
         <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.696796320555769</v>
+        <v>-2.717687141969011</v>
       </c>
       <c r="V4" t="n">
-        <v>8.644999945958455</v>
+        <v>8.645599946975707</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4048624573293254</v>
+        <v>1.438888122870879</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.870799949169159</v>
+        <v>8.871249949932098</v>
       </c>
       <c r="Z4" t="n">
         <v>-1</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.150873033849086</v>
+        <v>-1.141321603380154</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4943280618798461</v>
+        <v>0.4884607859065336</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>16.69</v>
+        <v>16.87</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -1754,103 +1754,103 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.9399995803833</v>
+        <v>12.07999992370605</v>
       </c>
       <c r="D5" t="n">
-        <v>11.9399995803833</v>
+        <v>12.07999992370605</v>
       </c>
       <c r="E5" t="n">
         <v>12.15999984741211</v>
       </c>
       <c r="F5" t="n">
-        <v>11.9399995803833</v>
+        <v>11.93000030517578</v>
       </c>
       <c r="G5" t="n">
         <v>12.10000038146973</v>
       </c>
       <c r="H5" t="n">
-        <v>884700</v>
+        <v>2212200</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02689493602843085</v>
+        <v>-0.01548496552315914</v>
       </c>
       <c r="J5" t="n">
-        <v>12.32666662004259</v>
+        <v>12.34222221374512</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.136833757072538</v>
+        <v>-2.124595437497749</v>
       </c>
       <c r="M5" t="n">
-        <v>12.3579999923706</v>
+        <v>12.37200002670288</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.382427676366424</v>
+        <v>-2.360168948970205</v>
       </c>
       <c r="P5" t="n">
-        <v>12.93384614357582</v>
+        <v>12.93923077216515</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-7.684075967504482</v>
+        <v>-6.640509498504908</v>
       </c>
       <c r="S5" t="n">
-        <v>13.00639993667603</v>
+        <v>13.00919994354248</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-8.199043251665987</v>
+        <v>-7.142637701541846</v>
       </c>
       <c r="V5" t="n">
-        <v>12.14279996871948</v>
+        <v>12.14373330434163</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.67012870885303</v>
+        <v>-0.5248252661542979</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.75019996643066</v>
+        <v>11.75089996814728</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.615288373771328</v>
+        <v>2.800636176385257</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2357169654343923</v>
+        <v>0.2294146196834713</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="AJ5" t="n">
         <v>1</v>
@@ -1977,13 +1977,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.82</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2011,16 +2011,16 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
+        <v>7</v>
+      </c>
+      <c r="CM5" t="n">
         <v>6</v>
       </c>
-      <c r="CM5" t="n">
-        <v>5</v>
-      </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -2033,82 +2033,82 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.72999954223633</v>
+        <v>50.86999893188477</v>
       </c>
       <c r="D6" t="n">
-        <v>50.72999954223633</v>
+        <v>50.86999893188477</v>
       </c>
       <c r="E6" t="n">
         <v>51.59999847412109</v>
       </c>
       <c r="F6" t="n">
-        <v>50.66999816894531</v>
+        <v>50.56999969482422</v>
       </c>
       <c r="G6" t="n">
         <v>51.25</v>
       </c>
       <c r="H6" t="n">
-        <v>6103400</v>
+        <v>8683900</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03113065410837645</v>
+        <v>-0.02845686900492939</v>
       </c>
       <c r="J6" t="n">
-        <v>52.65000025431315</v>
+        <v>52.66555574205186</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.646724981581613</v>
+        <v>-3.409356997885814</v>
       </c>
       <c r="M6" t="n">
-        <v>52.85300025939942</v>
+        <v>52.86700019836426</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.016802654047121</v>
+        <v>-3.777406054791212</v>
       </c>
       <c r="P6" t="n">
-        <v>56.08923061077412</v>
+        <v>56.09461520268367</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.554830776210254</v>
+        <v>-9.31393548546697</v>
       </c>
       <c r="S6" t="n">
-        <v>58.66440002441406</v>
+        <v>58.66720001220703</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-13.52506883028842</v>
+        <v>-13.29056283357631</v>
       </c>
       <c r="V6" t="n">
-        <v>58.11760002136231</v>
+        <v>58.11853335062663</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.71146860230036</v>
+        <v>-12.47198440988138</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.69130001068115</v>
+        <v>55.6920000076294</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-8.908573632673841</v>
+        <v>-8.658337059333569</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2944603020635632</v>
+        <v>0.2926932356930769</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>15.51</v>
+        <v>15.56</v>
       </c>
       <c r="CA6" t="n">
         <v>0.31</v>
@@ -2294,7 +2294,7 @@
         <v>-1</v>
       </c>
       <c r="CL6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CM6" t="n">
         <v>5</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -2316,82 +2316,82 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.68000030517578</v>
+        <v>55.83000183105469</v>
       </c>
       <c r="D7" t="n">
-        <v>55.68000030517578</v>
+        <v>55.83000183105469</v>
       </c>
       <c r="E7" t="n">
         <v>56.7400016784668</v>
       </c>
       <c r="F7" t="n">
-        <v>55.63000106811523</v>
+        <v>55.5099983215332</v>
       </c>
       <c r="G7" t="n">
         <v>56.47000122070312</v>
       </c>
       <c r="H7" t="n">
-        <v>741400</v>
+        <v>1426400</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02793293485019055</v>
+        <v>-0.02531419307163585</v>
       </c>
       <c r="J7" t="n">
-        <v>57.78000005086263</v>
+        <v>57.7966668870714</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.634475153752617</v>
+        <v>-3.402730921939435</v>
       </c>
       <c r="M7" t="n">
-        <v>58.02099990844727</v>
+        <v>58.03600006103515</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.034745362826225</v>
+        <v>-3.801085925391941</v>
       </c>
       <c r="P7" t="n">
-        <v>61.63653901907114</v>
+        <v>61.64230830852802</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.663973364974835</v>
+        <v>-9.429086348262562</v>
       </c>
       <c r="S7" t="n">
-        <v>64.39720001220704</v>
+        <v>64.40020004272461</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-13.53661293562272</v>
+        <v>-13.30771986109398</v>
       </c>
       <c r="V7" t="n">
-        <v>58.86659632364909</v>
+        <v>58.86759633382162</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.413249988080464</v>
+        <v>-5.16004507053691</v>
       </c>
       <c r="Y7" t="n">
-        <v>54.31578084945679</v>
+        <v>54.31653085708618</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.511644745566866</v>
+        <v>2.786391085893625</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3065621016707557</v>
+        <v>0.3051329942349409</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.03</v>
+        <v>17.07</v>
       </c>
       <c r="CA7" t="n">
         <v>0.28</v>
@@ -2584,13 +2584,13 @@
         <v>2</v>
       </c>
       <c r="CM7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -2603,82 +2603,82 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.48999977111816</v>
+        <v>17.52000045776367</v>
       </c>
       <c r="D8" t="n">
-        <v>17.48999977111816</v>
+        <v>17.52000045776367</v>
       </c>
       <c r="E8" t="n">
         <v>18.63999938964844</v>
       </c>
       <c r="F8" t="n">
-        <v>17.47999954223633</v>
+        <v>17.23999977111816</v>
       </c>
       <c r="G8" t="n">
         <v>18.63999938964844</v>
       </c>
       <c r="H8" t="n">
-        <v>2075600</v>
+        <v>3412400</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07898894250021771</v>
+        <v>-0.07740912749194495</v>
       </c>
       <c r="J8" t="n">
-        <v>19.68666648864746</v>
+        <v>19.68999989827474</v>
       </c>
       <c r="K8" t="n">
         <v>-1</v>
       </c>
       <c r="L8" t="n">
-        <v>-11.15814461933426</v>
+        <v>-11.02081996811592</v>
       </c>
       <c r="M8" t="n">
-        <v>19.71299991607666</v>
+        <v>19.71599998474121</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>-11.276823184814</v>
+        <v>-11.13815950840478</v>
       </c>
       <c r="P8" t="n">
-        <v>20.17807689079871</v>
+        <v>20.179230763362</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-13.321770623772</v>
+        <v>-13.17805587726618</v>
       </c>
       <c r="S8" t="n">
-        <v>21.8076000213623</v>
+        <v>21.80820003509521</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-19.79860345024075</v>
+        <v>-19.66324396525475</v>
       </c>
       <c r="V8" t="n">
-        <v>24.9132666905721</v>
+        <v>24.91346669514974</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-29.79644143681534</v>
+        <v>-29.67658547024072</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.30525003433227</v>
+        <v>26.3054000377655</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-33.51137226108436</v>
+        <v>-33.39770376952648</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5006166581099022</v>
+        <v>0.4986577671056154</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2693,21 +2693,21 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AF8" t="n">
+        <v>17.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>17.5</v>
+        <v>21.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>21.8</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
+        <v>23.1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
       <c r="AK8" t="n">
         <v>-1</v>
       </c>
@@ -2830,7 +2830,7 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="CA8" t="n">
         <v>0.6</v>
@@ -2886,82 +2886,82 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.5600004196167</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="D9" t="n">
-        <v>15.5600004196167</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="E9" t="n">
         <v>16.15999984741211</v>
       </c>
       <c r="F9" t="n">
-        <v>15.52999973297119</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="G9" t="n">
         <v>15.85999965667725</v>
       </c>
       <c r="H9" t="n">
-        <v>20437600</v>
+        <v>32987900</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04422605876297203</v>
+        <v>-0.04729732342058823</v>
       </c>
       <c r="J9" t="n">
-        <v>16.49222236209446</v>
+        <v>16.48666678534614</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.652494381960101</v>
+        <v>-5.923978261830303</v>
       </c>
       <c r="M9" t="n">
-        <v>16.54500017166138</v>
+        <v>16.54000015258789</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.953458699455363</v>
+        <v>-6.227327171728579</v>
       </c>
       <c r="P9" t="n">
-        <v>17.09230789771447</v>
+        <v>17.09038481345544</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-8.964895128659986</v>
+        <v>-9.247214745740234</v>
       </c>
       <c r="S9" t="n">
-        <v>17.82940010070801</v>
+        <v>17.82840009689331</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-12.72841300477176</v>
+        <v>-13.0039703810297</v>
       </c>
       <c r="V9" t="n">
-        <v>16.10046675364176</v>
+        <v>16.10013341903687</v>
       </c>
       <c r="W9" t="n">
         <v>-1</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.356836433967467</v>
+        <v>-3.665393166601051</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.30480006217956</v>
+        <v>15.30455006122589</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.667453063093404</v>
+        <v>1.342412333809496</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3650680540159675</v>
+        <v>0.3679006714156236</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>15.88</v>
+        <v>15.83</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3173,82 +3173,82 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.54000091552734</v>
+        <v>19.57999992370605</v>
       </c>
       <c r="D10" t="n">
-        <v>19.54000091552734</v>
+        <v>19.57999992370605</v>
       </c>
       <c r="E10" t="n">
         <v>19.8700008392334</v>
       </c>
       <c r="F10" t="n">
-        <v>19.53000068664551</v>
+        <v>19.45999908447266</v>
       </c>
       <c r="G10" t="n">
         <v>19.77000045776367</v>
       </c>
       <c r="H10" t="n">
-        <v>14213300</v>
+        <v>23900400</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01759670612676068</v>
+        <v>-0.01558569509578367</v>
       </c>
       <c r="J10" t="n">
-        <v>20.5766667260064</v>
+        <v>20.58111106024848</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.038064834713185</v>
+        <v>-4.864222993655718</v>
       </c>
       <c r="M10" t="n">
-        <v>20.60100002288818</v>
+        <v>20.60499992370605</v>
       </c>
       <c r="N10" t="n">
         <v>-1</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.150231086753288</v>
+        <v>-4.974520765810516</v>
       </c>
       <c r="P10" t="n">
-        <v>21.08807695828951</v>
+        <v>21.089615381681</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-7.341001485456149</v>
+        <v>-7.158098574363953</v>
       </c>
       <c r="S10" t="n">
-        <v>22.35619995117187</v>
+        <v>22.35699993133545</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-12.59694868446062</v>
+        <v>-12.42116570272546</v>
       </c>
       <c r="V10" t="n">
-        <v>22.92433331807455</v>
+        <v>22.92459997812907</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.76305703459148</v>
+        <v>-14.58956779012017</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.47550001144409</v>
+        <v>22.47570000648498</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-13.06088449388021</v>
+        <v>-12.88369252990307</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2569011863090035</v>
+        <v>0.2562515659379511</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.78</v>
+        <v>7.8</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3472,82 +3472,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.13000011444092</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="D11" t="n">
-        <v>15.13000011444092</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="E11" t="n">
         <v>15.34000015258789</v>
       </c>
       <c r="F11" t="n">
-        <v>15.13000011444092</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="G11" t="n">
         <v>15.25</v>
       </c>
       <c r="H11" t="n">
-        <v>2376300</v>
+        <v>3618000</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01944265617637297</v>
+        <v>-0.01814651206141493</v>
       </c>
       <c r="J11" t="n">
-        <v>15.46888902452257</v>
+        <v>15.47111119164361</v>
       </c>
       <c r="K11" t="n">
         <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.190777304979154</v>
+        <v>-2.07555597743216</v>
       </c>
       <c r="M11" t="n">
-        <v>15.47900009155273</v>
+        <v>15.48100004196167</v>
       </c>
       <c r="N11" t="n">
         <v>-1</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.254667452985378</v>
+        <v>-2.138107502966285</v>
       </c>
       <c r="P11" t="n">
-        <v>15.78346160741953</v>
+        <v>15.78423081911527</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.140165885229058</v>
+        <v>-4.018131816831532</v>
       </c>
       <c r="S11" t="n">
-        <v>16.44959997177124</v>
+        <v>16.44999996185303</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-8.022078710697246</v>
+        <v>-7.902737667704615</v>
       </c>
       <c r="V11" t="n">
-        <v>16.62499999364217</v>
+        <v>16.62513332366943</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.992480479837466</v>
+        <v>-8.872913536512772</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.10940000534058</v>
+        <v>16.10950000286102</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-6.079679507461279</v>
+        <v>-5.956115237346554</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2155788771903611</v>
+        <v>0.2148974326895715</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.75</v>
+        <v>6.76</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM11" t="n">
         <v>7</v>
@@ -3762,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="CO11" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -3775,82 +3775,82 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.34000015258789</v>
+        <v>17.3799991607666</v>
       </c>
       <c r="D12" t="n">
-        <v>17.34000015258789</v>
+        <v>17.3799991607666</v>
       </c>
       <c r="E12" t="n">
         <v>17.6200008392334</v>
       </c>
       <c r="F12" t="n">
-        <v>17.32999992370605</v>
+        <v>17.30999946594238</v>
       </c>
       <c r="G12" t="n">
         <v>17.51000022888184</v>
       </c>
       <c r="H12" t="n">
-        <v>17134200</v>
+        <v>24286100</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02309858295279488</v>
+        <v>-0.02084511770329001</v>
       </c>
       <c r="J12" t="n">
-        <v>17.74666680230035</v>
+        <v>17.75111113654243</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.291510029701708</v>
+        <v>-2.090640821981304</v>
       </c>
       <c r="M12" t="n">
-        <v>17.76200008392334</v>
+        <v>17.76599998474121</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.375858176678019</v>
+        <v>-2.172694046527837</v>
       </c>
       <c r="P12" t="n">
-        <v>18.16307698763334</v>
+        <v>18.16461541102483</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-4.531593603913341</v>
+        <v>-4.319476259222146</v>
       </c>
       <c r="S12" t="n">
-        <v>18.95540008544922</v>
+        <v>18.95620006561279</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.522109401960673</v>
+        <v>-8.314962383761056</v>
       </c>
       <c r="V12" t="n">
-        <v>19.29319999694824</v>
+        <v>19.29346665700277</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.12377337439774</v>
+        <v>-9.917696649615078</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.72360000610352</v>
+        <v>18.72380000114441</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-7.389603778464615</v>
+        <v>-7.176966429334176</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2568814945855208</v>
+        <v>0.2556799064428381</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.74</v>
+        <v>7.76</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>9</v>
       </c>
       <c r="CF12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CG12" t="n">
         <v>8</v>
@@ -4045,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="CI12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CJ12" t="inlineStr"/>
       <c r="CK12" t="n">
@@ -4055,13 +4055,13 @@
         <v>6</v>
       </c>
       <c r="CM12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN12" t="n">
         <v>0</v>
       </c>
       <c r="CO12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -4080,7 +4080,7 @@
         <v>35.0099983215332</v>
       </c>
       <c r="E13" t="n">
-        <v>35.09999847412109</v>
+        <v>35.11000061035156</v>
       </c>
       <c r="F13" t="n">
         <v>34.70000076293945</v>
@@ -4089,7 +4089,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>2032900</v>
+        <v>4222500</v>
       </c>
       <c r="I13" t="n">
         <v>-0.003415961939464585</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.680000066757202</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="D14" t="n">
-        <v>3.680000066757202</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="E14" t="n">
         <v>3.789999961853027</v>
@@ -4388,67 +4388,67 @@
         <v>3.609999895095825</v>
       </c>
       <c r="H14" t="n">
-        <v>22953500</v>
+        <v>28040200</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05142859050205772</v>
+        <v>0.03142854145595009</v>
       </c>
       <c r="J14" t="n">
-        <v>3.752222246593899</v>
+        <v>3.744444449742635</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.924784170294209</v>
+        <v>-3.59050738904808</v>
       </c>
       <c r="M14" t="n">
-        <v>3.780000042915344</v>
+        <v>3.773000025749206</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.645501984730581</v>
+        <v>-4.320173059659979</v>
       </c>
       <c r="P14" t="n">
-        <v>3.981153873296885</v>
+        <v>3.978461559002216</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-7.564485476425206</v>
+        <v>-9.261410684556157</v>
       </c>
       <c r="S14" t="n">
-        <v>4.061000022888184</v>
+        <v>4.059600019454956</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-9.38192450095123</v>
+        <v>-11.07498576718144</v>
       </c>
       <c r="V14" t="n">
-        <v>5.226400009791056</v>
+        <v>5.225933341979981</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-29.5882431527792</v>
+        <v>-30.92143242439287</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.485900001525879</v>
+        <v>5.485550000667572</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-32.91893644190331</v>
+        <v>-34.19073940340529</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5671123929176147</v>
+        <v>0.5531558163557808</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4600,13 +4600,13 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="CC14" t="n">
         <v>8</v>
@@ -4638,16 +4638,16 @@
         <v>1</v>
       </c>
       <c r="CL14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CN14" t="n">
         <v>-1</v>
       </c>
       <c r="CO14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -4660,82 +4660,82 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>51.02000045776367</v>
+        <v>50.75</v>
       </c>
       <c r="D15" t="n">
-        <v>51.02000045776367</v>
+        <v>50.75</v>
       </c>
       <c r="E15" t="n">
         <v>52.84000015258789</v>
       </c>
       <c r="F15" t="n">
-        <v>51.0099983215332</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="G15" t="n">
         <v>52.65000152587891</v>
       </c>
       <c r="H15" t="n">
-        <v>4997200</v>
+        <v>12567300</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04187792567579962</v>
+        <v>-0.04694835680751175</v>
       </c>
       <c r="J15" t="n">
-        <v>53.93222257826064</v>
+        <v>53.902222527398</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.399781394640393</v>
+        <v>-5.848038132000507</v>
       </c>
       <c r="M15" t="n">
-        <v>53.97600021362305</v>
+        <v>53.94900016784668</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.476507603676247</v>
+        <v>-5.929674614717446</v>
       </c>
       <c r="P15" t="n">
-        <v>55.73076937748836</v>
+        <v>55.72038474449744</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-8.452725437570457</v>
+        <v>-8.920226892346225</v>
       </c>
       <c r="S15" t="n">
-        <v>57.63059982299805</v>
+        <v>57.62519981384278</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-11.47064126616353</v>
+        <v>-11.93089106164142</v>
       </c>
       <c r="V15" t="n">
-        <v>55.98693321228027</v>
+        <v>55.98513320922851</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.87159283342768</v>
+        <v>-9.35093463056289</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.49224994659424</v>
+        <v>53.49089994430542</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-4.621696584643225</v>
+        <v>-5.124049038545316</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.3011272738446046</v>
+        <v>0.3064801504717059</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4907,13 +4907,13 @@
         <v>3510880000</v>
       </c>
       <c r="BZ15" t="n">
-        <v>11.47</v>
+        <v>11.4</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CC15" t="n">
         <v>6</v>
@@ -4945,16 +4945,16 @@
         <v>0</v>
       </c>
       <c r="CL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CM15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN15" t="n">
         <v>0</v>
       </c>
       <c r="CO15" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -4967,106 +4967,106 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.64999961853027</v>
+        <v>22.72999954223633</v>
       </c>
       <c r="D16" t="n">
-        <v>22.64999961853027</v>
+        <v>22.72999954223633</v>
       </c>
       <c r="E16" t="n">
         <v>23.28000068664551</v>
       </c>
       <c r="F16" t="n">
-        <v>22.61000061035156</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="G16" t="n">
         <v>23.15999984741211</v>
       </c>
       <c r="H16" t="n">
-        <v>1154400</v>
+        <v>1532500</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.04066077793324518</v>
+        <v>-0.03727238650427678</v>
       </c>
       <c r="J16" t="n">
-        <v>23.16222254435221</v>
+        <v>23.171111424764</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.211458442043334</v>
+        <v>-1.903714821621514</v>
       </c>
       <c r="M16" t="n">
-        <v>23.1540002822876</v>
+        <v>23.1620002746582</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.17673256289487</v>
+        <v>-1.865127049905673</v>
       </c>
       <c r="P16" t="n">
-        <v>23.00846165877122</v>
+        <v>23.01153857891376</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.557957439993803</v>
+        <v>-1.223468981493557</v>
       </c>
       <c r="S16" t="n">
-        <v>23.38879997253418</v>
+        <v>23.3903999710083</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.158778367729388</v>
+        <v>-2.823382368794541</v>
       </c>
       <c r="V16" t="n">
-        <v>22.07599997202555</v>
+        <v>22.07653330485026</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>2.600107117376727</v>
+        <v>2.960003857319837</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.75099995613098</v>
+        <v>20.75139995574951</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.151364591652955</v>
+        <v>9.534776404030575</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2843367461118289</v>
+        <v>0.2806202061212513</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="AH16" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -5198,7 +5198,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.38</v>
+        <v>11.42</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
@@ -5239,13 +5239,13 @@
         <v>9</v>
       </c>
       <c r="CM16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN16" t="n">
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.75</v>
+        <v>20.86000061035156</v>
       </c>
       <c r="D17" t="n">
-        <v>20.75</v>
+        <v>20.86000061035156</v>
       </c>
       <c r="E17" t="n">
         <v>21.04000091552734</v>
@@ -5273,88 +5273,88 @@
         <v>20.45999908447266</v>
       </c>
       <c r="H17" t="n">
-        <v>4632700</v>
+        <v>6910500</v>
       </c>
       <c r="I17" t="n">
-        <v>0.008750622646876982</v>
+        <v>0.01409824598102993</v>
       </c>
       <c r="J17" t="n">
-        <v>20.25222227308485</v>
+        <v>20.26444456312392</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.457891880718153</v>
+        <v>2.938921150157774</v>
       </c>
       <c r="M17" t="n">
-        <v>20.24200000762939</v>
+        <v>20.25300006866455</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.509633396794472</v>
+        <v>2.997089515770863</v>
       </c>
       <c r="P17" t="n">
-        <v>19.13923080150898</v>
+        <v>19.14346159421481</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>8.416060264888115</v>
+        <v>8.966711729165526</v>
       </c>
       <c r="S17" t="n">
-        <v>19.62699996948242</v>
+        <v>19.62919998168945</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>5.721710053822308</v>
+        <v>6.270253651754667</v>
       </c>
       <c r="V17" t="n">
-        <v>17.48513329823812</v>
+        <v>17.48586663564046</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>18.67224370597658</v>
+        <v>19.29634970355882</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.63004995822907</v>
+        <v>17.63059996128082</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>17.6967736856279</v>
+        <v>18.31702072625401</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3343896634001115</v>
+        <v>0.3358529569562365</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="AF17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>20.8</v>
+        <v>27.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="AI17" t="n">
-        <v>27.9</v>
+        <v>29.2</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
@@ -5481,13 +5481,13 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>41.5</v>
+        <v>41.72</v>
       </c>
       <c r="CA17" t="n">
         <v>1.1</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="CC17" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.890000343322754</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="D18" t="n">
-        <v>9.890000343322754</v>
+        <v>9.449999809265137</v>
       </c>
       <c r="E18" t="n">
         <v>10.03999996185303</v>
@@ -5552,88 +5552,88 @@
         <v>9.699999809265137</v>
       </c>
       <c r="H18" t="n">
-        <v>4873300</v>
+        <v>7920200</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01198800028124336</v>
+        <v>-0.05594409658462651</v>
       </c>
       <c r="J18" t="n">
-        <v>11.01000001695421</v>
+        <v>10.96111106872559</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-10.17256741059744</v>
+        <v>-13.78611392573127</v>
       </c>
       <c r="M18" t="n">
-        <v>11.11199998855591</v>
+        <v>11.06799993515015</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.99711704906115</v>
+        <v>-14.61872185910037</v>
       </c>
       <c r="P18" t="n">
-        <v>10.70499996038584</v>
+        <v>10.68807686292208</v>
       </c>
       <c r="Q18" t="n">
         <v>-1</v>
       </c>
       <c r="R18" t="n">
-        <v>-7.613261280513887</v>
+        <v>-11.58372146397962</v>
       </c>
       <c r="S18" t="n">
-        <v>10.03599994659424</v>
+        <v>10.02719993591309</v>
       </c>
       <c r="T18" t="n">
         <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.454758908413802</v>
+        <v>-5.756344047560753</v>
       </c>
       <c r="V18" t="n">
-        <v>9.152933320999146</v>
+        <v>9.149999984105428</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>8.052795715583214</v>
+        <v>3.278686619462758</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.841149985790253</v>
+        <v>8.838949983119965</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.86327976810984</v>
+        <v>6.913149495269385</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9850567851384979</v>
+        <v>0.9997228469492395</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG18" t="n">
         <v>9.5</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AH18" t="n">
         <v>9.6</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AI18" t="n">
         <v>9.699999999999999</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>10.3</v>
       </c>
       <c r="AJ18" t="n">
         <v>2</v>
@@ -5760,13 +5760,13 @@
       <c r="BX18" t="inlineStr"/>
       <c r="BY18" t="inlineStr"/>
       <c r="BZ18" t="n">
-        <v>-0.86</v>
+        <v>-0.82</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.46</v>
+        <v>5.71</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="CC18" t="n">
         <v>1</v>
@@ -5798,7 +5798,7 @@
         <v>-1</v>
       </c>
       <c r="CL18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM18" t="n">
         <v>1</v>
@@ -5807,7 +5807,7 @@
         <v>-1</v>
       </c>
       <c r="CO18" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.75</v>
+        <v>10.85999965667725</v>
       </c>
       <c r="D19" t="n">
-        <v>10.75</v>
+        <v>10.85999965667725</v>
       </c>
       <c r="E19" t="n">
         <v>11.1899995803833</v>
@@ -5835,88 +5835,90 @@
         <v>11.18000030517578</v>
       </c>
       <c r="H19" t="n">
-        <v>5105500</v>
+        <v>7505600</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.06195462790432738</v>
+        <v>-0.05235605405519206</v>
       </c>
       <c r="J19" t="n">
-        <v>11.38222206963433</v>
+        <v>11.39444425370958</v>
       </c>
       <c r="K19" t="n">
         <v>-1</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.554469643682165</v>
+        <v>-4.690396346959538</v>
       </c>
       <c r="M19" t="n">
-        <v>11.36099987030029</v>
+        <v>11.37199983596802</v>
       </c>
       <c r="N19" t="n">
         <v>-1</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.378046626842746</v>
+        <v>-4.502287958810792</v>
       </c>
       <c r="P19" t="n">
-        <v>11.30384606581468</v>
+        <v>11.30807682184073</v>
       </c>
       <c r="Q19" t="n">
         <v>-1</v>
       </c>
       <c r="R19" t="n">
-        <v>-4.89962498241754</v>
+        <v>-3.962452433096778</v>
       </c>
       <c r="S19" t="n">
-        <v>11.83279993057251</v>
+        <v>11.83499992370606</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-9.150834434163546</v>
+        <v>-8.238278608484302</v>
       </c>
       <c r="V19" t="n">
-        <v>12.99873330434163</v>
+        <v>12.99946663538615</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-17.29963413889373</v>
+        <v>-16.45811354202033</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.89554996967316</v>
+        <v>13.89609996795654</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-22.63710307644012</v>
+        <v>-21.84857850965621</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.6170728704959232</v>
+        <v>0.6100334837531014</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="AH19" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AI19" t="n">
         <v>20.9</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -6043,7 +6045,7 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>5.66</v>
+        <v>5.72</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
@@ -6084,13 +6086,13 @@
         <v>6</v>
       </c>
       <c r="CM19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN19" t="n">
         <v>-1</v>
       </c>
       <c r="CO19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -6103,82 +6105,82 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.84000015258789</v>
+        <v>10.81999969482422</v>
       </c>
       <c r="D20" t="n">
-        <v>10.84000015258789</v>
+        <v>10.81999969482422</v>
       </c>
       <c r="E20" t="n">
         <v>11.05000019073486</v>
       </c>
       <c r="F20" t="n">
-        <v>10.84000015258789</v>
+        <v>10.72999954223633</v>
       </c>
       <c r="G20" t="n">
         <v>10.89999961853027</v>
       </c>
       <c r="H20" t="n">
-        <v>5673700</v>
+        <v>12353600</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01454544067382812</v>
+        <v>-0.01636366410688916</v>
       </c>
       <c r="J20" t="n">
-        <v>11.03444459703234</v>
+        <v>11.03222232394748</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.762158872017352</v>
+        <v>-1.923661642157045</v>
       </c>
       <c r="M20" t="n">
-        <v>11.06700010299683</v>
+        <v>11.06500005722046</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.051142570672478</v>
+        <v>-2.214192147575864</v>
       </c>
       <c r="P20" t="n">
-        <v>11.51807704338661</v>
+        <v>11.51730779501108</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-5.887066810236788</v>
+        <v>-6.0544366148564</v>
       </c>
       <c r="S20" t="n">
-        <v>12.25140012741089</v>
+        <v>12.25100011825561</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-11.52031572020228</v>
+        <v>-11.68068247178461</v>
       </c>
       <c r="V20" t="n">
-        <v>11.70120004018148</v>
+        <v>11.70106670379639</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.35992791026783</v>
+        <v>-7.529800754715023</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5150000333786</v>
+        <v>11.51490003108978</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-5.861918183535257</v>
+        <v>-6.034792611219894</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.233211367230701</v>
+        <v>0.2337312356354988</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6326,10 +6328,10 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="CB20" t="n">
         <v>1.07</v>
@@ -6395,13 +6397,13 @@
         <v>4.75</v>
       </c>
       <c r="F21" t="n">
-        <v>4.46999979019165</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="G21" t="n">
         <v>4.710000038146973</v>
       </c>
       <c r="H21" t="n">
-        <v>6183800</v>
+        <v>9918300</v>
       </c>
       <c r="I21" t="n">
         <v>-0.06066954518016909</v>
@@ -6673,10 +6675,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.369999885559082</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="D22" t="n">
-        <v>2.369999885559082</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="E22" t="n">
         <v>2.460000038146973</v>
@@ -6688,88 +6690,88 @@
         <v>2.460000038146973</v>
       </c>
       <c r="H22" t="n">
-        <v>15217200</v>
+        <v>23165200</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.04819282068998332</v>
+        <v>-0.0361445437046628</v>
       </c>
       <c r="J22" t="n">
-        <v>2.493333313200209</v>
+        <v>2.496666669845581</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.946527886511388</v>
+        <v>-3.871825408080136</v>
       </c>
       <c r="M22" t="n">
-        <v>2.494999980926514</v>
+        <v>2.498000001907349</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.010023900722162</v>
+        <v>-3.923134766416702</v>
       </c>
       <c r="P22" t="n">
-        <v>2.604230761528015</v>
+        <v>2.605384615751413</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-8.994244267028767</v>
+        <v>-7.883078726353314</v>
       </c>
       <c r="S22" t="n">
-        <v>2.856000003814697</v>
+        <v>2.856600008010864</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-17.01681084056287</v>
+        <v>-15.98403386413825</v>
       </c>
       <c r="V22" t="n">
-        <v>3.275502904256185</v>
+        <v>3.275702905654907</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-27.64470205538494</v>
+        <v>-26.73327940625304</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.149536168575287</v>
+        <v>3.149686169624329</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-24.75082809951769</v>
+        <v>-23.80192926796622</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4391069807355398</v>
+        <v>0.4314653440705368</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
@@ -6896,10 +6898,10 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>7.18</v>
+        <v>7.27</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="CB22" t="n">
         <v>0.36</v>
@@ -6956,10 +6958,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.20000076293945</v>
+        <v>43.2400016784668</v>
       </c>
       <c r="D23" t="n">
-        <v>43.20000076293945</v>
+        <v>43.2400016784668</v>
       </c>
       <c r="E23" t="n">
         <v>43.34000015258789</v>
@@ -6971,67 +6973,67 @@
         <v>43.2599983215332</v>
       </c>
       <c r="H23" t="n">
-        <v>1124500</v>
+        <v>1724100</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.006896534185299896</v>
+        <v>-0.005976972908809275</v>
       </c>
       <c r="J23" t="n">
-        <v>43.37222205268012</v>
+        <v>43.37666659884982</v>
       </c>
       <c r="K23" t="n">
         <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3970773956000879</v>
+        <v>-0.3150655204718985</v>
       </c>
       <c r="M23" t="n">
-        <v>43.40499992370606</v>
+        <v>43.40900001525879</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4722938857895081</v>
+        <v>-0.3893163554391685</v>
       </c>
       <c r="P23" t="n">
-        <v>45.83115386962891</v>
+        <v>45.83269236637996</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-5.740970681589251</v>
+        <v>-5.656858792382445</v>
       </c>
       <c r="S23" t="n">
-        <v>48.4631997680664</v>
+        <v>48.46399978637695</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.86019707802084</v>
+        <v>-10.77913117146101</v>
       </c>
       <c r="V23" t="n">
-        <v>48.90060000101725</v>
+        <v>48.90086667378743</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-11.6575241161851</v>
+        <v>-11.5762058637604</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.38965000152588</v>
+        <v>46.38985000610352</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.875777761810038</v>
+        <v>-6.78995152435779</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2680598396759467</v>
+        <v>0.2681098646431019</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7183,7 +7185,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.640000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="CA23" t="n">
         <v>0.52</v>
@@ -7243,82 +7245,82 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.31999969482422</v>
+        <v>14.32999992370605</v>
       </c>
       <c r="D24" t="n">
-        <v>14.31999969482422</v>
+        <v>14.32999992370605</v>
       </c>
       <c r="E24" t="n">
         <v>14.47999954223633</v>
       </c>
       <c r="F24" t="n">
-        <v>14.25</v>
+        <v>14.22000026702881</v>
       </c>
       <c r="G24" t="n">
         <v>14.31999969482422</v>
       </c>
       <c r="H24" t="n">
-        <v>11253100</v>
+        <v>17534000</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.02252559264838816</v>
+        <v>-0.02184298315062494</v>
       </c>
       <c r="J24" t="n">
-        <v>14.60111098819309</v>
+        <v>14.60222212473551</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.925273313764857</v>
+        <v>-1.864251883748069</v>
       </c>
       <c r="M24" t="n">
-        <v>14.63099985122681</v>
+        <v>14.63199987411499</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.125624766351913</v>
+        <v>-2.063969061011232</v>
       </c>
       <c r="P24" t="n">
-        <v>15.05653839844924</v>
+        <v>15.056923022637</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-4.891819647608242</v>
+        <v>-4.827833003051618</v>
       </c>
       <c r="S24" t="n">
-        <v>15.56259990692139</v>
+        <v>15.56279991149902</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.984528417674785</v>
+        <v>-7.921453689590131</v>
       </c>
       <c r="V24" t="n">
-        <v>14.21026661554972</v>
+        <v>14.21033328374227</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>0.7722098553338776</v>
+        <v>0.8421100165236346</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.57109995365143</v>
+        <v>13.57114995479584</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>5.518342239983961</v>
+        <v>5.591640881118195</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2348267297431494</v>
+        <v>0.2344021134017141</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7470,7 +7472,7 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>15.74</v>
+        <v>15.75</v>
       </c>
       <c r="CA24" t="n">
         <v>0.42</v>
@@ -7504,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="CL24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM24" t="n">
         <v>7</v>
@@ -7513,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="CO24" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -7526,10 +7528,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.630000114440918</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="D25" t="n">
-        <v>3.630000114440918</v>
+        <v>3.609999895095825</v>
       </c>
       <c r="E25" t="n">
         <v>3.799999952316284</v>
@@ -7541,67 +7543,67 @@
         <v>3.799999952316284</v>
       </c>
       <c r="H25" t="n">
-        <v>39216200</v>
+        <v>60025500</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.06443298779026541</v>
+        <v>-0.0695876833457254</v>
       </c>
       <c r="J25" t="n">
-        <v>4.01111117998759</v>
+        <v>4.00888893339369</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-9.501383742443434</v>
+        <v>-9.950114481225821</v>
       </c>
       <c r="M25" t="n">
-        <v>4.050000071525574</v>
+        <v>4.048000049591065</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-10.37036912758493</v>
+        <v>-10.82016178679363</v>
       </c>
       <c r="P25" t="n">
-        <v>4.540384613550627</v>
+        <v>4.539615374345046</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-20.05082336841457</v>
+        <v>-20.47784674672667</v>
       </c>
       <c r="S25" t="n">
-        <v>4.907400012016296</v>
+        <v>4.907000007629395</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-26.03007487564754</v>
+        <v>-26.4316305383533</v>
       </c>
       <c r="V25" t="n">
-        <v>5.519333338737487</v>
+        <v>5.519200003941854</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-34.23118533240724</v>
+        <v>-34.59197179813132</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.709249993562699</v>
+        <v>5.709149992465973</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-36.41896714045066</v>
+        <v>-36.76817214717202</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4920146237976084</v>
+        <v>0.4969837443742346</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7753,13 +7755,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.51</v>
+        <v>-1.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7813,10 +7815,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>52.72000122070312</v>
+        <v>52.97999954223633</v>
       </c>
       <c r="D26" t="n">
-        <v>52.72000122070312</v>
+        <v>52.97999954223633</v>
       </c>
       <c r="E26" t="n">
         <v>54.15999984741211</v>
@@ -7828,67 +7830,67 @@
         <v>52.68999862670898</v>
       </c>
       <c r="H26" t="n">
-        <v>3912900</v>
+        <v>6392800</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.003402652173605802</v>
+        <v>0.001512249793004017</v>
       </c>
       <c r="J26" t="n">
-        <v>52.53000005086263</v>
+        <v>52.55888875325521</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3617003039339846</v>
+        <v>0.801217070927962</v>
       </c>
       <c r="M26" t="n">
-        <v>52.39099998474121</v>
+        <v>52.41699981689453</v>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6279728122344148</v>
+        <v>1.074078499930353</v>
       </c>
       <c r="P26" t="n">
-        <v>53.06576919555664</v>
+        <v>53.07576913100023</v>
       </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.6515838366147114</v>
+        <v>-0.1804393800257977</v>
       </c>
       <c r="S26" t="n">
-        <v>55.02019996643067</v>
+        <v>55.02539993286133</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.180644103676388</v>
+        <v>-3.717193138297354</v>
       </c>
       <c r="V26" t="n">
-        <v>49.27206662495931</v>
+        <v>49.27379994710287</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>6.997747064250859</v>
+        <v>7.521643549131986</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.95254994392395</v>
+        <v>44.95384993553161</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>17.27922283934656</v>
+        <v>17.85419851295279</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.330721240589851</v>
+        <v>0.3309737702943895</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8040,13 +8042,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.81</v>
+        <v>14.88</v>
       </c>
       <c r="CA26" t="n">
         <v>0.34</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8078,7 +8080,7 @@
         <v>0</v>
       </c>
       <c r="CL26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM26" t="n">
         <v>10</v>
@@ -8087,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="CO26" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27">
@@ -8100,82 +8102,82 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.590000152587891</v>
+        <v>6.679999828338623</v>
       </c>
       <c r="D27" t="n">
-        <v>6.590000152587891</v>
+        <v>6.679999828338623</v>
       </c>
       <c r="E27" t="n">
         <v>6.980000019073486</v>
       </c>
       <c r="F27" t="n">
-        <v>6.590000152587891</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="G27" t="n">
         <v>6.980000019073486</v>
       </c>
       <c r="H27" t="n">
-        <v>15858500</v>
+        <v>23735700</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.07573631881987286</v>
+        <v>-0.06311364360161453</v>
       </c>
       <c r="J27" t="n">
-        <v>6.718888971540663</v>
+        <v>6.728888935512966</v>
       </c>
       <c r="K27" t="n">
         <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.918305533827232</v>
+        <v>-0.726555418626718</v>
       </c>
       <c r="M27" t="n">
-        <v>6.681000089645385</v>
+        <v>6.690000057220459</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.362070585787477</v>
+        <v>-0.1494802510658094</v>
       </c>
       <c r="P27" t="n">
-        <v>6.49230771798354</v>
+        <v>6.495769243973952</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.504741285348279</v>
+        <v>2.836162699830806</v>
       </c>
       <c r="S27" t="n">
-        <v>6.50359998703003</v>
+        <v>6.505399980545044</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.328497535675115</v>
+        <v>2.68392179290643</v>
       </c>
       <c r="V27" t="n">
-        <v>8.052133334477743</v>
+        <v>8.05273333231608</v>
       </c>
       <c r="W27" t="n">
         <v>-1</v>
       </c>
       <c r="X27" t="n">
-        <v>-18.15833296785175</v>
+        <v>-17.04680196559594</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.003199987411499</v>
+        <v>8.003649985790252</v>
       </c>
       <c r="Z27" t="n">
         <v>-1</v>
       </c>
       <c r="AA27" t="n">
-        <v>-17.6579347891653</v>
+        <v>-16.53808149783722</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.6016162775364101</v>
+        <v>0.5888683960936406</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -8327,13 +8329,13 @@
       <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="n">
-        <v>-4.36</v>
+        <v>-4.42</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CC27" t="n">
         <v>2</v>
@@ -8364,13 +8366,13 @@
         <v>10</v>
       </c>
       <c r="CM27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN27" t="n">
         <v>-1</v>
       </c>
       <c r="CO27" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28">
@@ -8383,82 +8385,82 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29.28000068664551</v>
+        <v>29.46999931335449</v>
       </c>
       <c r="D28" t="n">
-        <v>29.28000068664551</v>
+        <v>29.46999931335449</v>
       </c>
       <c r="E28" t="n">
         <v>30.97999954223633</v>
       </c>
       <c r="F28" t="n">
-        <v>29.28000068664551</v>
+        <v>29.21999931335449</v>
       </c>
       <c r="G28" t="n">
         <v>30.97999954223633</v>
       </c>
       <c r="H28" t="n">
-        <v>2217500</v>
+        <v>3713500</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.06543246862600216</v>
+        <v>-0.05936803750019104</v>
       </c>
       <c r="J28" t="n">
-        <v>31.31222237481011</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="K28" t="n">
         <v>-1</v>
       </c>
       <c r="L28" t="n">
-        <v>-6.490186687609484</v>
+        <v>-5.946810702060128</v>
       </c>
       <c r="M28" t="n">
-        <v>31.30100021362305</v>
+        <v>31.32000007629394</v>
       </c>
       <c r="N28" t="n">
         <v>-1</v>
       </c>
       <c r="O28" t="n">
-        <v>-6.456661171159466</v>
+        <v>-5.906771259364441</v>
       </c>
       <c r="P28" t="n">
-        <v>30.64961550785945</v>
+        <v>30.65692314734826</v>
       </c>
       <c r="Q28" t="n">
         <v>-1</v>
       </c>
       <c r="R28" t="n">
-        <v>-4.468619910950382</v>
+        <v>-3.87163391540952</v>
       </c>
       <c r="S28" t="n">
-        <v>32.74680000305176</v>
+        <v>32.75059997558593</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-10.58668119047715</v>
+        <v>-10.01691775013887</v>
       </c>
       <c r="V28" t="n">
-        <v>34.7231999206543</v>
+        <v>34.72446657816569</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-15.67597239438473</v>
+        <v>-15.13188763600804</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.26519993782043</v>
+        <v>34.26614993095398</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-14.54886958261253</v>
+        <v>-13.99675956377852</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.5132973094766842</v>
+        <v>0.5073615615972338</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8606,13 +8608,13 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>8.460000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="CA28" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="CB28" t="n">
-        <v>5.84</v>
+        <v>5.88</v>
       </c>
       <c r="CC28" t="n">
         <v>9</v>
@@ -8644,16 +8646,16 @@
         <v>1</v>
       </c>
       <c r="CL28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN28" t="n">
         <v>-1</v>
       </c>
       <c r="CO28" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -8666,10 +8668,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.46999931335449</v>
+        <v>17.42000007629395</v>
       </c>
       <c r="D29" t="n">
-        <v>17.46999931335449</v>
+        <v>17.42000007629395</v>
       </c>
       <c r="E29" t="n">
         <v>17.79999923706055</v>
@@ -8681,67 +8683,67 @@
         <v>17.60000038146973</v>
       </c>
       <c r="H29" t="n">
-        <v>2647500</v>
+        <v>4430200</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01632888016835354</v>
+        <v>-0.01914415248908452</v>
       </c>
       <c r="J29" t="n">
-        <v>17.55666669209798</v>
+        <v>17.55111122131348</v>
       </c>
       <c r="K29" t="n">
         <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.493643698222603</v>
+        <v>-0.7470247516881684</v>
       </c>
       <c r="M29" t="n">
-        <v>17.57800006866455</v>
+        <v>17.5730001449585</v>
       </c>
       <c r="N29" t="n">
         <v>-1</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.6144086636032406</v>
+        <v>-0.8706542275221237</v>
       </c>
       <c r="P29" t="n">
-        <v>17.60000008803148</v>
+        <v>17.59807704045222</v>
       </c>
       <c r="Q29" t="n">
         <v>-1</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.7386407615156054</v>
+        <v>-1.011911493221326</v>
       </c>
       <c r="S29" t="n">
-        <v>18.0634001159668</v>
+        <v>18.06240013122559</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.285100251351789</v>
+        <v>-3.556559760964907</v>
       </c>
       <c r="V29" t="n">
-        <v>17.13846676508586</v>
+        <v>17.13813343683879</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.934435284164558</v>
+        <v>1.644675252961221</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.45065008640289</v>
+        <v>16.45040009021759</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>6.196406960197475</v>
+        <v>5.894081485914356</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2159240620450414</v>
+        <v>0.2176092679888878</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8901,13 +8903,13 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>11.97</v>
+        <v>11.93</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
       </c>
       <c r="CB29" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC29" t="n">
         <v>2</v>
@@ -8961,82 +8963,82 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>20.77000045776367</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="D30" t="n">
-        <v>20.77000045776367</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="E30" t="n">
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>20.77000045776367</v>
+        <v>20.64999961853027</v>
       </c>
       <c r="G30" t="n">
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>5937800</v>
+        <v>8565500</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.07069350768405469</v>
+        <v>-0.07516779760633296</v>
       </c>
       <c r="J30" t="n">
-        <v>22.10222244262695</v>
+        <v>22.09111128913032</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.027547629300487</v>
+        <v>-6.432954839784879</v>
       </c>
       <c r="M30" t="n">
-        <v>22.1040002822876</v>
+        <v>22.09400024414062</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-6.035105897066457</v>
+        <v>-6.445189427497748</v>
       </c>
       <c r="P30" t="n">
-        <v>22.32692315028264</v>
+        <v>22.32307698176457</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.973297135656856</v>
+        <v>-7.405237668718357</v>
       </c>
       <c r="S30" t="n">
-        <v>24.69279998779297</v>
+        <v>24.69079998016358</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-15.88641033810891</v>
+        <v>-16.28460765588768</v>
       </c>
       <c r="V30" t="n">
-        <v>28.49279993693034</v>
+        <v>28.49213326772054</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-27.10438951686501</v>
+        <v>-27.45365928878511</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.557649974823</v>
+        <v>28.55714997291565</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-27.26992425470959</v>
+        <v>-27.61882717323712</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4379645267004506</v>
+        <v>0.4435739081996701</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -9184,7 +9186,7 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="CA30" t="n">
         <v>0.52</v>
@@ -9240,82 +9242,82 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12.46000003814697</v>
+        <v>12.44999980926514</v>
       </c>
       <c r="D31" t="n">
-        <v>12.46000003814697</v>
+        <v>12.44999980926514</v>
       </c>
       <c r="E31" t="n">
         <v>13.19999980926514</v>
       </c>
       <c r="F31" t="n">
-        <v>12.4399995803833</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="G31" t="n">
         <v>13.19999980926514</v>
       </c>
       <c r="H31" t="n">
-        <v>4080600</v>
+        <v>7422200</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.06666669047875873</v>
+        <v>-0.067415771272473</v>
       </c>
       <c r="J31" t="n">
-        <v>13.22777769300673</v>
+        <v>13.2266665564643</v>
       </c>
       <c r="K31" t="n">
         <v>-1</v>
       </c>
       <c r="L31" t="n">
-        <v>-5.804283022277158</v>
+        <v>-5.871976464240591</v>
       </c>
       <c r="M31" t="n">
-        <v>13.21699991226196</v>
+        <v>13.21599988937378</v>
       </c>
       <c r="N31" t="n">
         <v>-1</v>
       </c>
       <c r="O31" t="n">
-        <v>-5.727471280473341</v>
+        <v>-5.796005497280154</v>
       </c>
       <c r="P31" t="n">
-        <v>13.0976923429049</v>
+        <v>13.09730771871713</v>
       </c>
       <c r="Q31" t="n">
         <v>-1</v>
       </c>
       <c r="R31" t="n">
-        <v>-4.868737851392326</v>
+        <v>-4.942297480931454</v>
       </c>
       <c r="S31" t="n">
-        <v>13.46520004272461</v>
+        <v>13.46500003814697</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-7.465169484212428</v>
+        <v>-7.538063319764528</v>
       </c>
       <c r="V31" t="n">
-        <v>14.95453334172567</v>
+        <v>14.95446667353312</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-16.6807833221952</v>
+        <v>-16.74728306226037</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.01954999923706</v>
+        <v>15.01949999809265</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-17.04145571085754</v>
+        <v>-17.10776117150251</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4771880974673497</v>
+        <v>0.4780265338888682</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9467,13 +9469,13 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>7.74</v>
+        <v>7.73</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
       </c>
       <c r="CB31" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CC31" t="n">
         <v>9</v>
@@ -9523,13 +9525,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>33.75</v>
+        <v>33.91999816894531</v>
       </c>
       <c r="D32" t="n">
-        <v>33.75</v>
+        <v>33.91999816894531</v>
       </c>
       <c r="E32" t="n">
-        <v>33.84999847412109</v>
+        <v>34.02999877929688</v>
       </c>
       <c r="F32" t="n">
         <v>33.2599983215332</v>
@@ -9538,67 +9540,67 @@
         <v>33.5</v>
       </c>
       <c r="H32" t="n">
-        <v>872200</v>
+        <v>1444800</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.005598074083581928</v>
+        <v>-0.0005892887027971749</v>
       </c>
       <c r="J32" t="n">
-        <v>32.85333336724175</v>
+        <v>32.87222205268012</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>2.729301842023491</v>
+        <v>3.187421022485346</v>
       </c>
       <c r="M32" t="n">
-        <v>32.80200004577637</v>
+        <v>32.8189998626709</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>2.890067535213294</v>
+        <v>3.354758861883277</v>
       </c>
       <c r="P32" t="n">
-        <v>33.28769258352426</v>
+        <v>33.29423097463754</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.388823858294574</v>
+        <v>1.879506376898925</v>
       </c>
       <c r="S32" t="n">
-        <v>34.00460006713868</v>
+        <v>34.00800003051758</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.7487224276597657</v>
+        <v>-0.258768117776101</v>
       </c>
       <c r="V32" t="n">
-        <v>32.34375232696533</v>
+        <v>32.34488564809163</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>4.34781857967131</v>
+        <v>4.869742122419937</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.41542126655579</v>
+        <v>31.41627125740051</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>7.431314428782017</v>
+        <v>7.969522834302029</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2405846612920387</v>
+        <v>0.2406112406903298</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9750,13 +9752,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="CA32" t="n">
         <v>0.64</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CC32" t="n">
         <v>2</v>
@@ -9806,82 +9808,82 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69.63999938964844</v>
+        <v>69.55000305175781</v>
       </c>
       <c r="D33" t="n">
-        <v>69.63999938964844</v>
+        <v>69.55000305175781</v>
       </c>
       <c r="E33" t="n">
         <v>71.09999847412109</v>
       </c>
       <c r="F33" t="n">
-        <v>69.47000122070312</v>
+        <v>69.41999816894531</v>
       </c>
       <c r="G33" t="n">
         <v>70.98000335693359</v>
       </c>
       <c r="H33" t="n">
-        <v>4043700</v>
+        <v>5947200</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.03210559633873877</v>
+        <v>-0.03335641415260704</v>
       </c>
       <c r="J33" t="n">
-        <v>72.46999867757161</v>
+        <v>72.45999908447266</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-3.905063253159704</v>
+        <v>-4.016003408063005</v>
       </c>
       <c r="M33" t="n">
-        <v>72.30399856567382</v>
+        <v>72.29499893188476</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-3.684442394435034</v>
+        <v>-3.796937437834729</v>
       </c>
       <c r="P33" t="n">
-        <v>74.1053839463454</v>
+        <v>74.10192254873422</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-6.02572217955181</v>
+        <v>-6.142781914980374</v>
       </c>
       <c r="S33" t="n">
-        <v>77.30119949340821</v>
+        <v>77.29939956665039</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-9.910842462946608</v>
+        <v>-10.02517038726901</v>
       </c>
       <c r="V33" t="n">
-        <v>85.27899988810222</v>
+        <v>85.27839991251628</v>
       </c>
       <c r="W33" t="n">
         <v>-1</v>
       </c>
       <c r="X33" t="n">
-        <v>-18.33863028292346</v>
+        <v>-18.44358814998124</v>
       </c>
       <c r="Y33" t="n">
-        <v>83.62129997253417</v>
+        <v>83.62084999084473</v>
       </c>
       <c r="Z33" t="n">
         <v>-1</v>
       </c>
       <c r="AA33" t="n">
-        <v>-16.71978382000515</v>
+        <v>-16.82695995152821</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.48092062502281</v>
+        <v>0.4815220933069248</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10033,7 +10035,7 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>30.41</v>
+        <v>30.37</v>
       </c>
       <c r="CA33" t="n">
         <v>0.06</v>
@@ -10093,82 +10095,82 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>24.34000015258789</v>
+        <v>24.40999984741211</v>
       </c>
       <c r="D34" t="n">
-        <v>24.34000015258789</v>
+        <v>24.40999984741211</v>
       </c>
       <c r="E34" t="n">
         <v>25.06999969482422</v>
       </c>
       <c r="F34" t="n">
-        <v>24.22999954223633</v>
+        <v>24.20999908447266</v>
       </c>
       <c r="G34" t="n">
         <v>24.78000068664551</v>
       </c>
       <c r="H34" t="n">
-        <v>11563200</v>
+        <v>15396700</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.03984221750229733</v>
+        <v>-0.03708088835946277</v>
       </c>
       <c r="J34" t="n">
-        <v>25.06444401211209</v>
+        <v>25.07222175598145</v>
       </c>
       <c r="K34" t="n">
         <v>-1</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.890324872852228</v>
+        <v>-2.641257384425257</v>
       </c>
       <c r="M34" t="n">
-        <v>25.10999965667725</v>
+        <v>25.11699962615967</v>
       </c>
       <c r="N34" t="n">
         <v>-1</v>
       </c>
       <c r="O34" t="n">
-        <v>-3.066505434557413</v>
+        <v>-2.814825772466905</v>
       </c>
       <c r="P34" t="n">
-        <v>25.87038436302772</v>
+        <v>25.8730766589825</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-5.915583583779116</v>
+        <v>-5.654823470955258</v>
       </c>
       <c r="S34" t="n">
-        <v>25.91199989318848</v>
+        <v>25.91339988708496</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-6.066686273080061</v>
+        <v>-5.801631766668078</v>
       </c>
       <c r="V34" t="n">
-        <v>22.26093332926432</v>
+        <v>22.26139999389649</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>9.339531243240454</v>
+        <v>9.6516834255919</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.63420001983643</v>
+        <v>20.63455001831055</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>17.95950475031229</v>
+        <v>18.29673933161289</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3047779211147696</v>
+        <v>0.3020193358225748</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10320,13 +10322,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>36.33</v>
+        <v>36.43</v>
       </c>
       <c r="CA34" t="n">
         <v>0.39</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CC34" t="n">
         <v>10</v>
@@ -10376,105 +10378,103 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47.31000137329102</v>
+        <v>47.09999847412109</v>
       </c>
       <c r="D35" t="n">
-        <v>47.31000137329102</v>
+        <v>47.09999847412109</v>
       </c>
       <c r="E35" t="n">
         <v>48.15999984741211</v>
       </c>
       <c r="F35" t="n">
-        <v>47.20000076293945</v>
+        <v>47.02999877929688</v>
       </c>
       <c r="G35" t="n">
         <v>47.45999908447266</v>
       </c>
       <c r="H35" t="n">
-        <v>1361400</v>
+        <v>2428100</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.02554063611236845</v>
+        <v>-0.02986613358857892</v>
       </c>
       <c r="J35" t="n">
-        <v>48.1944448682997</v>
+        <v>48.17111121283637</v>
       </c>
       <c r="K35" t="n">
         <v>-1</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.835156515290484</v>
+        <v>-2.223558294062883</v>
       </c>
       <c r="M35" t="n">
-        <v>48.22400054931641</v>
+        <v>48.20300025939942</v>
       </c>
       <c r="N35" t="n">
         <v>-1</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.895320101223639</v>
+        <v>-2.288243012556551</v>
       </c>
       <c r="P35" t="n">
-        <v>49.951538672814</v>
+        <v>49.94346163823054</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-5.288200062915454</v>
+        <v>-5.69336419791304</v>
       </c>
       <c r="S35" t="n">
-        <v>52.07980003356933</v>
+        <v>52.07559997558594</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-9.158634743612353</v>
+        <v>-9.554573550371966</v>
       </c>
       <c r="V35" t="n">
-        <v>50.4938362121582</v>
+        <v>50.4924361928304</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-6.305393049341262</v>
+        <v>-6.718704769470034</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.99592247009277</v>
+        <v>48.99487245559693</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-3.440941637196129</v>
+        <v>-3.867494467289652</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2540095877295298</v>
+        <v>0.2571409642730532</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="AE35" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AF35" t="n">
         <v>46.1</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AG35" t="n">
         <v>47.3</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>47.7</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>58.6</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Foguete</t>
-        </is>
       </c>
       <c r="AJ35" t="n">
         <v>1</v>
@@ -10601,7 +10601,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.52</v>
+        <v>12.46</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
@@ -10635,7 +10635,7 @@
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM35" t="n">
         <v>7</v>
@@ -10644,7 +10644,7 @@
         <v>0</v>
       </c>
       <c r="CO35" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -10657,82 +10657,82 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.11000061035156</v>
+        <v>38.2599983215332</v>
       </c>
       <c r="D36" t="n">
-        <v>38.11000061035156</v>
+        <v>38.2599983215332</v>
       </c>
       <c r="E36" t="n">
         <v>38.72000122070312</v>
       </c>
       <c r="F36" t="n">
-        <v>38.0099983215332</v>
+        <v>37.95999908447266</v>
       </c>
       <c r="G36" t="n">
         <v>38.65999984741211</v>
       </c>
       <c r="H36" t="n">
-        <v>3484500</v>
+        <v>6011200</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.02457125907272095</v>
+        <v>-0.02073205476370454</v>
       </c>
       <c r="J36" t="n">
-        <v>38.3466665479872</v>
+        <v>38.36333296034071</v>
       </c>
       <c r="K36" t="n">
         <v>-1</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.6171747349654771</v>
+        <v>-0.2693578238218656</v>
       </c>
       <c r="M36" t="n">
-        <v>38.32599983215332</v>
+        <v>38.34099960327148</v>
       </c>
       <c r="N36" t="n">
         <v>-1</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.5635840493339153</v>
+        <v>-0.2112654405895295</v>
       </c>
       <c r="P36" t="n">
-        <v>39.88961542569674</v>
+        <v>39.89538456843449</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-4.461348640124406</v>
+        <v>-4.099186571559508</v>
       </c>
       <c r="S36" t="n">
-        <v>41.22839996337891</v>
+        <v>41.23139991760254</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-7.563716651136737</v>
+        <v>-7.206647365860555</v>
       </c>
       <c r="V36" t="n">
-        <v>40.11060000101725</v>
+        <v>40.11159998575847</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-4.987707465395565</v>
+        <v>-4.616125172974079</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.11480001449585</v>
+        <v>39.11555000305176</v>
       </c>
       <c r="Z36" t="n">
         <v>-1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-2.568847095656657</v>
+        <v>-2.187241855098052</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2696837791118362</v>
+        <v>0.2675366542729897</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10884,13 +10884,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>30.98</v>
+        <v>31.11</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CC36" t="n">
         <v>8</v>
@@ -10940,82 +10940,82 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14.78999996185303</v>
+        <v>14.77000045776367</v>
       </c>
       <c r="D37" t="n">
-        <v>14.78999996185303</v>
+        <v>14.77000045776367</v>
       </c>
       <c r="E37" t="n">
         <v>15.11999988555908</v>
       </c>
       <c r="F37" t="n">
-        <v>14.77999973297119</v>
+        <v>14.75</v>
       </c>
       <c r="G37" t="n">
         <v>15.03999996185303</v>
       </c>
       <c r="H37" t="n">
-        <v>1376200</v>
+        <v>2028000</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.03522504661059911</v>
+        <v>-0.03652964570967865</v>
       </c>
       <c r="J37" t="n">
-        <v>15.5777776506212</v>
+        <v>15.57555548350016</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.057060810832414</v>
+        <v>-5.171918437129568</v>
       </c>
       <c r="M37" t="n">
-        <v>15.58899984359741</v>
+        <v>15.58699989318848</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-5.125408235041732</v>
+        <v>-5.241543857210352</v>
       </c>
       <c r="P37" t="n">
-        <v>15.88615380800687</v>
+        <v>15.88538459631113</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-6.900058122321387</v>
+        <v>-7.021448752373733</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06379995346069</v>
+        <v>16.06339996337891</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-7.929630568720119</v>
+        <v>-8.051841506554693</v>
       </c>
       <c r="V37" t="n">
-        <v>15.86240003585815</v>
+        <v>15.86226670583089</v>
       </c>
       <c r="W37" t="n">
         <v>-1</v>
       </c>
       <c r="X37" t="n">
-        <v>-6.760641968307985</v>
+        <v>-6.885940504743301</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.72050000667572</v>
+        <v>15.72040000915527</v>
       </c>
       <c r="Z37" t="n">
         <v>-1</v>
       </c>
       <c r="AA37" t="n">
-        <v>-5.919023214449641</v>
+        <v>-6.045644836251663</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2563912843964521</v>
+        <v>0.2578014849384653</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>12.75</v>
+        <v>12.73</v>
       </c>
       <c r="CA37" t="n">
         <v>0.4</v>
@@ -11192,12 +11192,16 @@
       <c r="CI37" t="n">
         <v>28</v>
       </c>
-      <c r="CJ37" t="inlineStr"/>
+      <c r="CJ37" t="inlineStr">
+        <is>
+          <t>melhor</t>
+        </is>
+      </c>
       <c r="CK37" t="n">
         <v>0</v>
       </c>
       <c r="CL37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM37" t="n">
         <v>3</v>
@@ -11206,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
@@ -11234,7 +11238,7 @@
         <v>24.03000068664551</v>
       </c>
       <c r="H38" t="n">
-        <v>7150600</v>
+        <v>10897600</v>
       </c>
       <c r="I38" t="n">
         <v>-0.02271803142428497</v>
@@ -11500,10 +11504,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.27999973297119</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="D39" t="n">
-        <v>10.27999973297119</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="E39" t="n">
         <v>10.44999980926514</v>
@@ -11515,67 +11519,67 @@
         <v>10.27000045776367</v>
       </c>
       <c r="H39" t="n">
-        <v>8095600</v>
+        <v>12008500</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.02743613720206928</v>
+        <v>-0.02649004172708713</v>
       </c>
       <c r="J39" t="n">
-        <v>10.24222215016683</v>
+        <v>10.24333328670926</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3688416659049525</v>
+        <v>0.4555809504345836</v>
       </c>
       <c r="M39" t="n">
-        <v>10.24599990844727</v>
+        <v>10.24699993133545</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3318351047016421</v>
+        <v>0.4196353157579735</v>
       </c>
       <c r="P39" t="n">
-        <v>10.20230770111084</v>
+        <v>10.2026923252986</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0.7615142979062703</v>
+        <v>0.8557313478711519</v>
       </c>
       <c r="S39" t="n">
-        <v>9.62359998703003</v>
+        <v>9.623799991607665</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>6.820729735502392</v>
+        <v>6.922421193565066</v>
       </c>
       <c r="V39" t="n">
-        <v>9.152105159759522</v>
+        <v>9.152171827952067</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>12.32388126581913</v>
+        <v>12.43232923606031</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.677024092674255</v>
+        <v>8.677074093818664</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>18.4737949690641</v>
+        <v>18.58836112951222</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.3400209303703725</v>
+        <v>0.3392945949591128</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11731,7 +11735,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.91</v>
+        <v>23.93</v>
       </c>
       <c r="CA39" t="n">
         <v>0.6</v>
@@ -11791,82 +11795,82 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11.32999992370605</v>
+        <v>11.14999961853027</v>
       </c>
       <c r="D40" t="n">
-        <v>11.32999992370605</v>
+        <v>11.14999961853027</v>
       </c>
       <c r="E40" t="n">
         <v>12.0600004196167</v>
       </c>
       <c r="F40" t="n">
-        <v>11.30000019073486</v>
+        <v>11.0600004196167</v>
       </c>
       <c r="G40" t="n">
         <v>11.97999954223633</v>
       </c>
       <c r="H40" t="n">
-        <v>7710900</v>
+        <v>12911100</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.07358950549606502</v>
+        <v>-0.08830743778658967</v>
       </c>
       <c r="J40" t="n">
-        <v>12.20444424947103</v>
+        <v>12.18444421556261</v>
       </c>
       <c r="K40" t="n">
         <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>-7.16496636709103</v>
+        <v>-8.489879215919332</v>
       </c>
       <c r="M40" t="n">
-        <v>12.21799983978272</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="N40" t="n">
         <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>-7.267964705526242</v>
+        <v>-8.606559075004688</v>
       </c>
       <c r="P40" t="n">
-        <v>12.24384612303514</v>
+        <v>12.23692303437453</v>
       </c>
       <c r="Q40" t="n">
         <v>-1</v>
       </c>
       <c r="R40" t="n">
-        <v>-7.463718427576485</v>
+        <v>-8.882326159860607</v>
       </c>
       <c r="S40" t="n">
-        <v>11.88419996261597</v>
+        <v>11.88059995651245</v>
       </c>
       <c r="T40" t="n">
         <v>-1</v>
       </c>
       <c r="U40" t="n">
-        <v>-4.663334853446208</v>
+        <v>-6.149523935293296</v>
       </c>
       <c r="V40" t="n">
-        <v>14.53339996973673</v>
+        <v>14.53219996770223</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-22.04164237343774</v>
+        <v>-23.27383573504966</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.25654997348785</v>
+        <v>20.25564997196198</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-44.0674747746533</v>
+        <v>-44.9536320287713</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.7145991672516935</v>
+        <v>0.7285554186755404</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12018,10 +12022,10 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-13.33</v>
+        <v>-13.12</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="CB40" t="n">
         <v>0.12</v>
@@ -12059,13 +12063,13 @@
         <v>8</v>
       </c>
       <c r="CM40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN40" t="n">
         <v>-1</v>
       </c>
       <c r="CO40" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41">
@@ -12078,10 +12082,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21.13999938964844</v>
+        <v>21.15999984741211</v>
       </c>
       <c r="D41" t="n">
-        <v>21.13999938964844</v>
+        <v>21.15999984741211</v>
       </c>
       <c r="E41" t="n">
         <v>22.23999977111816</v>
@@ -12093,67 +12097,67 @@
         <v>21.75</v>
       </c>
       <c r="H41" t="n">
-        <v>3436500</v>
+        <v>5754100</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.02580651399088518</v>
+        <v>-0.02488483394201479</v>
       </c>
       <c r="J41" t="n">
-        <v>22.12444432576497</v>
+        <v>22.12666659884983</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-4.449580390003748</v>
+        <v>-4.368786175356237</v>
       </c>
       <c r="M41" t="n">
-        <v>22.18099994659424</v>
+        <v>22.1829999923706</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-4.693208419152625</v>
+        <v>-4.611640198847473</v>
       </c>
       <c r="P41" t="n">
-        <v>22.62307695242075</v>
+        <v>22.62384620079627</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-6.555596154720313</v>
+        <v>-6.470369098127272</v>
       </c>
       <c r="S41" t="n">
-        <v>22.85060001373291</v>
+        <v>22.85100002288818</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-7.486020599268403</v>
+        <v>-7.400114541080573</v>
       </c>
       <c r="V41" t="n">
-        <v>23.6402666982015</v>
+        <v>23.64040003458659</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-10.57630753693348</v>
+        <v>-10.49220903007386</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.47304998397827</v>
+        <v>23.47314998626709</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.939273319497367</v>
+        <v>-9.854451320799647</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3088395572535917</v>
+        <v>0.3082675614921007</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12357,10 +12361,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>24.88999938964844</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="D42" t="n">
-        <v>24.88999938964844</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="E42" t="n">
         <v>25.36000061035156</v>
@@ -12372,67 +12376,67 @@
         <v>25.25</v>
       </c>
       <c r="H42" t="n">
-        <v>1894600</v>
+        <v>2424200</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.03189419385547354</v>
+        <v>-0.03072730596306494</v>
       </c>
       <c r="J42" t="n">
-        <v>25.93666648864746</v>
+        <v>25.93999989827474</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-4.035472713724225</v>
+        <v>-3.932150447111733</v>
       </c>
       <c r="M42" t="n">
-        <v>25.9939998626709</v>
+        <v>25.99699993133545</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-4.24713579616455</v>
+        <v>-4.142785159388114</v>
       </c>
       <c r="P42" t="n">
-        <v>26.71076906644381</v>
+        <v>26.7119229390071</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-6.816612701289712</v>
+        <v>-6.708325966665734</v>
       </c>
       <c r="S42" t="n">
-        <v>27.58219982147217</v>
+        <v>27.58279983520508</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-9.760644362121944</v>
+        <v>-9.653841433140126</v>
       </c>
       <c r="V42" t="n">
-        <v>27.01679988861084</v>
+        <v>27.01699989318848</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-7.872140696644735</v>
+        <v>-7.761778973183571</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.10529989242554</v>
+        <v>26.10544989585877</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-4.655378439570122</v>
+        <v>-4.541005132238205</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.2846890635538755</v>
+        <v>0.2837895761718014</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12584,7 +12588,7 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>10.37</v>
+        <v>10.38</v>
       </c>
       <c r="CA42" t="n">
         <v>0.04</v>
@@ -12640,10 +12644,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>26.95999908447266</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="D43" t="n">
-        <v>26.95999908447266</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="E43" t="n">
         <v>27.23999977111816</v>
@@ -12655,67 +12659,67 @@
         <v>26.92000007629395</v>
       </c>
       <c r="H43" t="n">
-        <v>961300</v>
+        <v>1717600</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01963639692826702</v>
+        <v>-0.01454544067382812</v>
       </c>
       <c r="J43" t="n">
-        <v>27.43333350287543</v>
+        <v>27.44888920254177</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.725398841351766</v>
+        <v>-1.271048961208022</v>
       </c>
       <c r="M43" t="n">
-        <v>27.5310001373291</v>
+        <v>27.54500026702881</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-2.074029457732009</v>
+        <v>-1.615537779071084</v>
       </c>
       <c r="P43" t="n">
-        <v>28.57653852609488</v>
+        <v>28.58192319136399</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-5.656876322323169</v>
+        <v>-5.184825387614329</v>
       </c>
       <c r="S43" t="n">
-        <v>29.1266000366211</v>
+        <v>29.12940006256104</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-7.438564574733594</v>
+        <v>-6.966843384116323</v>
       </c>
       <c r="V43" t="n">
-        <v>28.04873329162598</v>
+        <v>28.04966663360596</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-3.881580661178605</v>
+        <v>-3.385659674822822</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.90994999885559</v>
+        <v>26.91065000534057</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.1859872858150738</v>
+        <v>0.703626170648328</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2579275943842685</v>
+        <v>0.2557156598347208</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12867,7 +12871,7 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>7.57</v>
+        <v>7.61</v>
       </c>
       <c r="CA43" t="n">
         <v>0.84</v>
@@ -12908,13 +12912,13 @@
         <v>7</v>
       </c>
       <c r="CM43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN43" t="n">
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
@@ -12942,7 +12946,7 @@
         <v>12.76000022888184</v>
       </c>
       <c r="H44" t="n">
-        <v>11183400</v>
+        <v>20104600</v>
       </c>
       <c r="I44" t="n">
         <v>-0.02170540629853857</v>
@@ -13195,13 +13199,13 @@
         <v>7</v>
       </c>
       <c r="CM44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN44" t="n">
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -13214,82 +13218,82 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38.7599983215332</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="D45" t="n">
-        <v>38.7599983215332</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="E45" t="n">
         <v>39.29999923706055</v>
       </c>
       <c r="F45" t="n">
-        <v>38.65999984741211</v>
+        <v>38.63999938964844</v>
       </c>
       <c r="G45" t="n">
         <v>39.22999954223633</v>
       </c>
       <c r="H45" t="n">
-        <v>22672500</v>
+        <v>35292400</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.02022252335658248</v>
+        <v>-0.02148640695933446</v>
       </c>
       <c r="J45" t="n">
-        <v>39.76111136542426</v>
+        <v>39.75555589463976</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.517819571717541</v>
+        <v>-2.629964005378357</v>
       </c>
       <c r="M45" t="n">
-        <v>39.79700012207032</v>
+        <v>39.79200019836426</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.60572856586248</v>
+        <v>-2.719142311263052</v>
       </c>
       <c r="P45" t="n">
-        <v>40.56999984154334</v>
+        <v>40.5680767939641</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-4.461428462113803</v>
+        <v>-4.580147387632368</v>
       </c>
       <c r="S45" t="n">
-        <v>42.39419982910156</v>
+        <v>42.39319984436035</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-8.5724026452167</v>
+        <v>-8.68818766549815</v>
       </c>
       <c r="V45" t="n">
-        <v>41.92475120544434</v>
+        <v>41.92441787719726</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-7.548650362652983</v>
+        <v>-7.667175730716427</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.6347283744812</v>
+        <v>40.6344783782959</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-4.61361531857891</v>
+        <v>-4.736074807966926</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2380523685244186</v>
+        <v>0.2387426993473114</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13461,7 +13465,7 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.210000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
@@ -13517,13 +13521,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.79000091552734</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="D46" t="n">
-        <v>16.79000091552734</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="E46" t="n">
-        <v>16.82999992370605</v>
+        <v>16.84000015258789</v>
       </c>
       <c r="F46" t="n">
         <v>16.6299991607666</v>
@@ -13532,67 +13536,67 @@
         <v>16.69000053405762</v>
       </c>
       <c r="H46" t="n">
-        <v>2452800</v>
+        <v>4131700</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.007096329566385506</v>
+        <v>-0.007687709162605083</v>
       </c>
       <c r="J46" t="n">
-        <v>16.67555554707845</v>
+        <v>16.67444441053603</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.6863061810791976</v>
+        <v>0.6330422382336436</v>
       </c>
       <c r="M46" t="n">
-        <v>16.65900001525879</v>
+        <v>16.65799999237061</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7863671297710736</v>
+        <v>0.7323850061878909</v>
       </c>
       <c r="P46" t="n">
-        <v>16.86038464766282</v>
+        <v>16.86000002347506</v>
       </c>
       <c r="Q46" t="n">
         <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.4174503346531631</v>
+        <v>-0.4744919141053646</v>
       </c>
       <c r="S46" t="n">
-        <v>17.86460006713867</v>
+        <v>17.86440006256104</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-6.015243260821808</v>
+        <v>-6.070169566948605</v>
       </c>
       <c r="V46" t="n">
-        <v>18.49008833567301</v>
+        <v>18.49002166748047</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.194587874767933</v>
+        <v>-9.248344926725965</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.34429873466492</v>
+        <v>18.34424873352051</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-8.472920342277478</v>
+        <v>-8.527185111792804</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.1810285859072314</v>
+        <v>0.1811351175037324</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13748,13 +13752,13 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>27.98</v>
+        <v>27.97</v>
       </c>
       <c r="CA46" t="n">
         <v>0.24</v>
       </c>
       <c r="CB46" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CC46" t="n">
         <v>4</v>
@@ -13808,103 +13812,103 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>14.67000007629395</v>
+        <v>14.72999954223633</v>
       </c>
       <c r="D47" t="n">
-        <v>14.67000007629395</v>
+        <v>14.72999954223633</v>
       </c>
       <c r="E47" t="n">
         <v>15.13000011444092</v>
       </c>
       <c r="F47" t="n">
-        <v>14.65999984741211</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="G47" t="n">
         <v>15.03999996185303</v>
       </c>
       <c r="H47" t="n">
-        <v>9496900</v>
+        <v>14333900</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.05476806420095981</v>
+        <v>-0.05090211934447186</v>
       </c>
       <c r="J47" t="n">
-        <v>15.05555555555556</v>
+        <v>15.06222216288249</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.560885102106635</v>
+        <v>-2.20566804189655</v>
       </c>
       <c r="M47" t="n">
-        <v>15.03500003814697</v>
+        <v>15.04099998474121</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.427668512982671</v>
+        <v>-2.067684614190453</v>
       </c>
       <c r="P47" t="n">
-        <v>14.34076932760385</v>
+        <v>14.34307699937087</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>2.295767689787546</v>
+        <v>2.697625780593879</v>
       </c>
       <c r="S47" t="n">
-        <v>14.70340005874634</v>
+        <v>14.70460004806518</v>
       </c>
       <c r="T47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.2271582240770527</v>
+        <v>0.1727316219966508</v>
       </c>
       <c r="V47" t="n">
-        <v>14.69700003306071</v>
+        <v>14.69740002950033</v>
       </c>
       <c r="W47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>-0.1837106668437609</v>
+        <v>0.2218046230664559</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.89805002689362</v>
+        <v>14.89835002422333</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-1.530736909783495</v>
+        <v>-1.129994138366179</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4879104693277648</v>
+        <v>0.4842974314242477</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="AG47" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="AH47" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="AI47" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14031,13 +14035,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>9.91</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14068,13 +14072,13 @@
         <v>10</v>
       </c>
       <c r="CM47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN47" t="n">
         <v>0</v>
       </c>
       <c r="CO47" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
@@ -14087,82 +14091,82 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.61999988555908</v>
+        <v>15.36999988555908</v>
       </c>
       <c r="D48" t="n">
-        <v>15.61999988555908</v>
+        <v>15.36999988555908</v>
       </c>
       <c r="E48" t="n">
         <v>16.20000076293945</v>
       </c>
       <c r="F48" t="n">
-        <v>15.47999954223633</v>
+        <v>15.36999988555908</v>
       </c>
       <c r="G48" t="n">
         <v>15.75</v>
       </c>
       <c r="H48" t="n">
-        <v>3659600</v>
+        <v>5780500</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.01451107194795642</v>
+        <v>-0.03028394223080366</v>
       </c>
       <c r="J48" t="n">
-        <v>16.12111144595676</v>
+        <v>16.09333366817898</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-3.10841818864393</v>
+        <v>-4.494617445545996</v>
       </c>
       <c r="M48" t="n">
-        <v>16.23900022506714</v>
+        <v>16.21400022506714</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-3.81181310997547</v>
+        <v>-5.205380089999116</v>
       </c>
       <c r="P48" t="n">
-        <v>16.90346163969773</v>
+        <v>16.89384625508235</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-7.592892991364836</v>
+        <v>-9.020126894222416</v>
       </c>
       <c r="S48" t="n">
-        <v>18.39580011367798</v>
+        <v>18.39080011367798</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-15.0893150119357</v>
+        <v>-16.42560524526721</v>
       </c>
       <c r="V48" t="n">
-        <v>18.87840007781982</v>
+        <v>18.87673341115316</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-17.25993823008882</v>
+        <v>-18.5770146201363</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.41940004348755</v>
+        <v>19.41815004348755</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-19.56497188080034</v>
+        <v>-20.84724934590839</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.3901296791137916</v>
+        <v>0.3953428269057723</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14310,13 +14314,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>57.85</v>
+        <v>56.93</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14351,13 +14355,13 @@
         <v>2</v>
       </c>
       <c r="CM48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CN48" t="n">
         <v>0</v>
       </c>
       <c r="CO48" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
@@ -14370,82 +14374,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.380000114440918</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="D49" t="n">
-        <v>5.380000114440918</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="E49" t="n">
         <v>5.550000190734863</v>
       </c>
       <c r="F49" t="n">
-        <v>5.380000114440918</v>
+        <v>5.329999923706055</v>
       </c>
       <c r="G49" t="n">
         <v>5.550000190734863</v>
       </c>
       <c r="H49" t="n">
-        <v>13577800</v>
+        <v>20647000</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.05281685263456315</v>
+        <v>-0.05809857987312272</v>
       </c>
       <c r="J49" t="n">
-        <v>6.2066666815016</v>
+        <v>6.203333324856228</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-13.31901017859532</v>
+        <v>-13.75604655652511</v>
       </c>
       <c r="M49" t="n">
-        <v>6.263000011444092</v>
+        <v>6.259999990463257</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-14.09867308621601</v>
+        <v>-14.53674260730064</v>
       </c>
       <c r="P49" t="n">
-        <v>6.968461495179397</v>
+        <v>6.967307640955998</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-22.79500836500762</v>
+        <v>-23.21280786880133</v>
       </c>
       <c r="S49" t="n">
-        <v>7.87879994392395</v>
+        <v>7.878199939727783</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-31.71548772995666</v>
+        <v>-32.09108748746192</v>
       </c>
       <c r="V49" t="n">
-        <v>8.778929958343506</v>
+        <v>8.778729956944783</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-38.71690354098612</v>
+        <v>-39.05724483072604</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.702911639213562</v>
+        <v>8.702761638164521</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-38.18160705895572</v>
+        <v>-38.52526212862099</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4552708203718622</v>
+        <v>0.4590380589806157</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14460,21 +14464,21 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AF49" t="n">
+        <v>5.3</v>
       </c>
       <c r="AG49" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="AI49" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ49" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1</v>
+      </c>
       <c r="AK49" t="n">
         <v>-1</v>
       </c>
@@ -14597,10 +14601,10 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>29.89</v>
+        <v>29.72</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="CB49" t="n">
         <v>0.37</v>
@@ -14657,10 +14661,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13.89999961853027</v>
+        <v>13.98999977111816</v>
       </c>
       <c r="D50" t="n">
-        <v>13.89999961853027</v>
+        <v>13.98999977111816</v>
       </c>
       <c r="E50" t="n">
         <v>14.07999992370605</v>
@@ -14672,88 +14676,88 @@
         <v>13.97000026702881</v>
       </c>
       <c r="H50" t="n">
-        <v>8850900</v>
+        <v>13783800</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.01766784499927543</v>
+        <v>-0.01130741001593949</v>
       </c>
       <c r="J50" t="n">
-        <v>14.2744443681505</v>
+        <v>14.28444438510471</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.623182661005681</v>
+        <v>-2.061295532737567</v>
       </c>
       <c r="M50" t="n">
-        <v>14.34699993133545</v>
+        <v>14.35599994659424</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-3.115636125632634</v>
+        <v>-2.549457904970964</v>
       </c>
       <c r="P50" t="n">
-        <v>14.96576918088473</v>
+        <v>14.96923072521503</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-7.121381797841207</v>
+        <v>-6.541625097991134</v>
       </c>
       <c r="S50" t="n">
-        <v>15.63880002975464</v>
+        <v>15.6406000328064</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-11.11850274903506</v>
+        <v>-10.55330523270254</v>
       </c>
       <c r="V50" t="n">
-        <v>15.82060002009074</v>
+        <v>15.82120002110799</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-12.13987079580721</v>
+        <v>-11.57434485087551</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.45630000114441</v>
+        <v>15.45675000190735</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-10.06903581386816</v>
+        <v>-9.489383153691357</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.2914303471594425</v>
+        <v>0.290060956207694</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="AE50" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="AG50" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="AH50" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="AI50" t="n">
-        <v>14.1</v>
+        <v>17.8</v>
       </c>
       <c r="AJ50" t="n">
         <v>3</v>
@@ -14880,13 +14884,13 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.369999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="CB50" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CC50" t="n">
         <v>5</v>
@@ -14921,13 +14925,13 @@
         <v>4</v>
       </c>
       <c r="CM50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN50" t="n">
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -14940,10 +14944,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.539999961853027</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="D51" t="n">
-        <v>5.539999961853027</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="E51" t="n">
         <v>5.760000228881836</v>
@@ -14955,67 +14959,67 @@
         <v>5.670000076293945</v>
       </c>
       <c r="H51" t="n">
-        <v>15678800</v>
+        <v>19960800</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.06576726438031955</v>
+        <v>-0.04384481611654967</v>
       </c>
       <c r="J51" t="n">
-        <v>5.936666594611274</v>
+        <v>5.951111051771376</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-6.681639038282892</v>
+        <v>-4.7236721518372</v>
       </c>
       <c r="M51" t="n">
-        <v>5.965999937057495</v>
+        <v>5.978999948501587</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-7.140462281241255</v>
+        <v>-5.168086216242243</v>
       </c>
       <c r="P51" t="n">
-        <v>6.329615354537964</v>
+        <v>6.334615358939538</v>
       </c>
       <c r="Q51" t="n">
         <v>-1</v>
       </c>
       <c r="R51" t="n">
-        <v>-12.47493486502033</v>
+        <v>-10.49180171149104</v>
       </c>
       <c r="S51" t="n">
-        <v>6.995599985122681</v>
+        <v>6.998199987411499</v>
       </c>
       <c r="T51" t="n">
         <v>-1</v>
       </c>
       <c r="U51" t="n">
-        <v>-20.80736500607856</v>
+        <v>-18.97916483533974</v>
       </c>
       <c r="V51" t="n">
-        <v>7.930266688664754</v>
+        <v>7.93113335609436</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-30.1410636067043</v>
+        <v>-28.50958593531829</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.768800005912781</v>
+        <v>7.769450006484985</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-28.68911598140548</v>
+        <v>-27.0218603432505</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4869845038173138</v>
+        <v>0.4691163363983237</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15167,13 +15171,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="CA51" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="CB51" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="CC51" t="n">
         <v>7</v>
@@ -15208,13 +15212,13 @@
         <v>1</v>
       </c>
       <c r="CM51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
@@ -15227,10 +15231,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>28.42000007629395</v>
+        <v>28.51000022888184</v>
       </c>
       <c r="D52" t="n">
-        <v>28.42000007629395</v>
+        <v>28.51000022888184</v>
       </c>
       <c r="E52" t="n">
         <v>28.8799991607666</v>
@@ -15242,67 +15246,67 @@
         <v>28.82999992370605</v>
       </c>
       <c r="H52" t="n">
-        <v>2388100</v>
+        <v>3251400</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.03399048257670745</v>
+        <v>-0.03093133395826775</v>
       </c>
       <c r="J52" t="n">
-        <v>29.6244445376926</v>
+        <v>29.63444455464681</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-4.065711543945348</v>
+        <v>-3.794382998107029</v>
       </c>
       <c r="M52" t="n">
-        <v>29.675</v>
+        <v>29.68400001525879</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-4.229148858318636</v>
+        <v>-3.95499186690968</v>
       </c>
       <c r="P52" t="n">
-        <v>30.37692297421969</v>
+        <v>30.38038451854999</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-6.442136682463021</v>
+        <v>-6.156552391646379</v>
       </c>
       <c r="S52" t="n">
-        <v>31.492799949646</v>
+        <v>31.49459995269775</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-9.757150454278966</v>
+        <v>-9.47654432283165</v>
       </c>
       <c r="V52" t="n">
-        <v>30.65473336537679</v>
+        <v>30.65533336639404</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-7.290010526096695</v>
+        <v>-6.998237833107473</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.93040004730225</v>
+        <v>29.93085004806519</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-5.046374150099072</v>
+        <v>-4.747108140602899</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.303741259969038</v>
+        <v>0.3014294064728594</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15454,13 +15458,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>11.94</v>
+        <v>11.98</v>
       </c>
       <c r="CA52" t="n">
         <v>0.31</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15492,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="CL52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM52" t="n">
         <v>4</v>
@@ -15501,7 +15505,7 @@
         <v>0</v>
       </c>
       <c r="CO52" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53">
@@ -15514,10 +15518,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.689999580383301</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="D53" t="n">
-        <v>9.689999580383301</v>
+        <v>9.680000305175781</v>
       </c>
       <c r="E53" t="n">
         <v>9.859999656677246</v>
@@ -15529,67 +15533,67 @@
         <v>9.729999542236328</v>
       </c>
       <c r="H53" t="n">
-        <v>13360700</v>
+        <v>16432700</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.01724138764840832</v>
+        <v>-0.01825551295831618</v>
       </c>
       <c r="J53" t="n">
-        <v>10.04888884226481</v>
+        <v>10.0477778116862</v>
       </c>
       <c r="K53" t="n">
         <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>-3.571432299778765</v>
+        <v>-3.660287014733424</v>
       </c>
       <c r="M53" t="n">
-        <v>10.06399993896484</v>
+        <v>10.06300001144409</v>
       </c>
       <c r="N53" t="n">
         <v>-1</v>
       </c>
       <c r="O53" t="n">
-        <v>-3.716219801766139</v>
+        <v>-3.806019137759584</v>
       </c>
       <c r="P53" t="n">
-        <v>10.11153841018677</v>
+        <v>10.11115382267879</v>
       </c>
       <c r="Q53" t="n">
         <v>-1</v>
       </c>
       <c r="R53" t="n">
-        <v>-4.168889170996885</v>
+        <v>-4.26413765495239</v>
       </c>
       <c r="S53" t="n">
-        <v>10.10339994430542</v>
+        <v>10.10319995880127</v>
       </c>
       <c r="T53" t="n">
         <v>-1</v>
       </c>
       <c r="U53" t="n">
-        <v>-4.091695530227162</v>
+        <v>-4.188768462974184</v>
       </c>
       <c r="V53" t="n">
-        <v>8.961199947992961</v>
+        <v>8.961133286158244</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>8.132835296835093</v>
+        <v>8.022054756488563</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.927399957180024</v>
+        <v>8.927349960803985</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>8.542236562280854</v>
+        <v>8.430837232508507</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3387785578717417</v>
+        <v>0.3392025698389699</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -15799,82 +15803,82 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>46.72000122070312</v>
+        <v>46.22000122070312</v>
       </c>
       <c r="D54" t="n">
-        <v>46.72000122070312</v>
+        <v>46.22000122070312</v>
       </c>
       <c r="E54" t="n">
         <v>46.84999847412109</v>
       </c>
       <c r="F54" t="n">
-        <v>46.25</v>
+        <v>46.20000076293945</v>
       </c>
       <c r="G54" t="n">
         <v>46.5</v>
       </c>
       <c r="H54" t="n">
-        <v>5434400</v>
+        <v>7878200</v>
       </c>
       <c r="I54" t="n">
-        <v>0.005379814793045945</v>
+        <v>-0.005379814793045945</v>
       </c>
       <c r="J54" t="n">
-        <v>47.84777789645725</v>
+        <v>47.7922223409017</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.357009510858859</v>
+        <v>-3.289700798979224</v>
       </c>
       <c r="M54" t="n">
-        <v>48.09300003051758</v>
+        <v>48.04300003051758</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-2.854882849776919</v>
+        <v>-3.794514931741265</v>
       </c>
       <c r="P54" t="n">
-        <v>50.22769253070538</v>
+        <v>50.20846176147461</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-6.983580437938526</v>
+        <v>-7.943801504454504</v>
       </c>
       <c r="S54" t="n">
-        <v>51.45000015258789</v>
+        <v>51.44000015258789</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-9.193389539080206</v>
+        <v>-10.14774283903682</v>
       </c>
       <c r="V54" t="n">
-        <v>41.91533345540365</v>
+        <v>41.91200012207031</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>11.46279265656198</v>
+        <v>10.27868172858751</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.74540009498596</v>
+        <v>39.74290009498596</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>17.54819704682514</v>
+        <v>16.29750498890826</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.2834101065944567</v>
+        <v>0.282279341748757</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16026,13 +16030,13 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.6</v>
+        <v>5.54</v>
       </c>
       <c r="CA54" t="n">
         <v>0.54</v>
       </c>
       <c r="CB54" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CC54" t="n">
         <v>1</v>
@@ -16060,16 +16064,16 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CM54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
       </c>
       <c r="CO54" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
@@ -16082,10 +16086,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>41.72999954223633</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="D55" t="n">
-        <v>41.72999954223633</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="E55" t="n">
         <v>41.86999893188477</v>
@@ -16097,67 +16101,67 @@
         <v>41.65000152587891</v>
       </c>
       <c r="H55" t="n">
-        <v>21322500</v>
+        <v>38379800</v>
       </c>
       <c r="I55" t="n">
-        <v>0.00384892587410901</v>
+        <v>-0.003848925874108899</v>
       </c>
       <c r="J55" t="n">
-        <v>42.70222176445855</v>
+        <v>42.66666624281142</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-2.276748567287454</v>
+        <v>-2.945311893476171</v>
       </c>
       <c r="M55" t="n">
-        <v>42.92699966430664</v>
+        <v>42.89499969482422</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-2.788455124818815</v>
+        <v>-3.461941620182118</v>
       </c>
       <c r="P55" t="n">
-        <v>45.24115371704102</v>
+        <v>45.22884603647086</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-7.76097399452954</v>
+        <v>-8.443386298158858</v>
       </c>
       <c r="S55" t="n">
-        <v>46.51379981994629</v>
+        <v>46.50739982604981</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-10.28469034185107</v>
+        <v>-10.9604062959945</v>
       </c>
       <c r="V55" t="n">
-        <v>38.67866673787435</v>
+        <v>38.67653340657552</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>7.888929639278635</v>
+        <v>7.067506314751211</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.71645004272461</v>
+        <v>36.71485004425049</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>13.65477733734544</v>
+        <v>12.78814920257825</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.247232659449193</v>
+        <v>0.2461531354093682</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16309,13 +16313,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="CA55" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CC55" t="n">
         <v>1</v>
@@ -16324,7 +16328,7 @@
         <v>9</v>
       </c>
       <c r="CE55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CF55" t="n">
         <v>10</v>
@@ -16350,13 +16354,13 @@
         <v>4</v>
       </c>
       <c r="CM55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN55" t="n">
         <v>0</v>
       </c>
       <c r="CO55" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -16369,82 +16373,82 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.670000076293945</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="D56" t="n">
-        <v>5.670000076293945</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="E56" t="n">
         <v>5.880000114440918</v>
       </c>
       <c r="F56" t="n">
-        <v>5.650000095367432</v>
+        <v>5.630000114440918</v>
       </c>
       <c r="G56" t="n">
         <v>5.880000114440918</v>
       </c>
       <c r="H56" t="n">
-        <v>8566400</v>
+        <v>12481800</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.04705878015914977</v>
+        <v>-0.05210083238940943</v>
       </c>
       <c r="J56" t="n">
-        <v>6.056666533152263</v>
+        <v>6.05333317650689</v>
       </c>
       <c r="K56" t="n">
         <v>-1</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.384146373947259</v>
+        <v>-6.828193624389447</v>
       </c>
       <c r="M56" t="n">
-        <v>6.048999881744384</v>
+        <v>6.045999860763549</v>
       </c>
       <c r="N56" t="n">
         <v>-1</v>
       </c>
       <c r="O56" t="n">
-        <v>-6.265495335753665</v>
+        <v>-6.715183652463399</v>
       </c>
       <c r="P56" t="n">
-        <v>6.14461535673875</v>
+        <v>6.143461502515352</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-7.724084468921205</v>
+        <v>-8.195080832257538</v>
       </c>
       <c r="S56" t="n">
-        <v>6.312399988174438</v>
+        <v>6.311799983978272</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-10.17679350300925</v>
+        <v>-10.64355840169141</v>
       </c>
       <c r="V56" t="n">
-        <v>6.310102907816569</v>
+        <v>6.309902906417847</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-10.14409496760669</v>
+        <v>-10.61669331315523</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.794804339408874</v>
+        <v>6.794654338359833</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-16.55388745473109</v>
+        <v>-16.99357192249695</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.3380211960640782</v>
+        <v>0.343453406476761</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16596,7 +16600,7 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="CA56" t="n">
         <v>0.22</v>
@@ -16634,7 +16638,7 @@
         <v>1</v>
       </c>
       <c r="CL56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM56" t="n">
         <v>2</v>
@@ -16643,7 +16647,7 @@
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
@@ -16656,10 +16660,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>63</v>
+        <v>62.54999923706055</v>
       </c>
       <c r="D57" t="n">
-        <v>63</v>
+        <v>62.54999923706055</v>
       </c>
       <c r="E57" t="n">
         <v>63.29999923706055</v>
@@ -16671,67 +16675,67 @@
         <v>62.59000015258789</v>
       </c>
       <c r="H57" t="n">
-        <v>5451000</v>
+        <v>7758700</v>
       </c>
       <c r="I57" t="n">
-        <v>0.01645692909482177</v>
+        <v>0.009196510148984371</v>
       </c>
       <c r="J57" t="n">
-        <v>63.71777767605252</v>
+        <v>63.66777759128146</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.126495151324601</v>
+        <v>-1.755642173340103</v>
       </c>
       <c r="M57" t="n">
-        <v>64.14599990844727</v>
+        <v>64.10099983215332</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.786549293927759</v>
+        <v>-2.41961997340763</v>
       </c>
       <c r="P57" t="n">
-        <v>65.73423092181866</v>
+        <v>65.71692320016714</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.159523711581315</v>
+        <v>-4.819038702497476</v>
       </c>
       <c r="S57" t="n">
-        <v>65.74159996032715</v>
+        <v>65.73259994506836</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-4.170266561783731</v>
+        <v>-4.841738666456915</v>
       </c>
       <c r="V57" t="n">
-        <v>52.40533322652181</v>
+        <v>52.40233322143555</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>20.21677207486267</v>
+        <v>19.36491257506455</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.69334995269775</v>
+        <v>48.69109994888306</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>29.38111684901568</v>
+        <v>28.46290041245085</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3663656822386525</v>
+        <v>0.3643009932470603</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16883,13 +16887,13 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>21.21</v>
+        <v>21.06</v>
       </c>
       <c r="CA57" t="n">
         <v>0.44</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CC57" t="n">
         <v>10</v>
@@ -16920,13 +16924,13 @@
         <v>8</v>
       </c>
       <c r="CM57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CN57" t="n">
         <v>0</v>
       </c>
       <c r="CO57" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58">
@@ -16939,82 +16943,82 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.06999969482422</v>
+        <v>48.02000045776367</v>
       </c>
       <c r="D58" t="n">
-        <v>48.06999969482422</v>
+        <v>48.02000045776367</v>
       </c>
       <c r="E58" t="n">
         <v>48.91999816894531</v>
       </c>
       <c r="F58" t="n">
-        <v>47.90999984741211</v>
+        <v>47.86999893188477</v>
       </c>
       <c r="G58" t="n">
         <v>48.15999984741211</v>
       </c>
       <c r="H58" t="n">
-        <v>1304800</v>
+        <v>1884600</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.01374644974496553</v>
+        <v>-0.01477228551309673</v>
       </c>
       <c r="J58" t="n">
-        <v>48.58222240871854</v>
+        <v>48.57666693793403</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.054341873422395</v>
+        <v>-1.14595445768563</v>
       </c>
       <c r="M58" t="n">
-        <v>48.67000007629395</v>
+        <v>48.66500015258789</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.232793056357469</v>
+        <v>-1.325387224497773</v>
       </c>
       <c r="P58" t="n">
-        <v>49.17307721651517</v>
+        <v>49.17115416893592</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.243255017037003</v>
+        <v>-2.341115905510908</v>
       </c>
       <c r="S58" t="n">
-        <v>50.29220008850098</v>
+        <v>50.29120010375976</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-4.418578606158157</v>
+        <v>-4.516097530602171</v>
       </c>
       <c r="V58" t="n">
-        <v>49.27926671346029</v>
+        <v>49.27893338521321</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-2.453906275975017</v>
+        <v>-2.554708150049574</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.40550003051758</v>
+        <v>49.40525003433228</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.703141016422114</v>
+        <v>-2.803850958361669</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.278112893317304</v>
+        <v>0.2784225479444939</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17166,7 +17170,7 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>8.43</v>
+        <v>8.42</v>
       </c>
       <c r="CA58" t="n">
         <v>-0.42</v>
@@ -17226,82 +17230,82 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17.34000015258789</v>
+        <v>17.52000045776367</v>
       </c>
       <c r="D59" t="n">
-        <v>17.34000015258789</v>
+        <v>17.52000045776367</v>
       </c>
       <c r="E59" t="n">
         <v>17.97999954223633</v>
       </c>
       <c r="F59" t="n">
-        <v>17.30999946594238</v>
+        <v>17.29000091552734</v>
       </c>
       <c r="G59" t="n">
         <v>17.95000076293945</v>
       </c>
       <c r="H59" t="n">
-        <v>6078000</v>
+        <v>11242300</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.04198896203670266</v>
+        <v>-0.03204419400453951</v>
       </c>
       <c r="J59" t="n">
-        <v>18.23555586073134</v>
+        <v>18.25555589463976</v>
       </c>
       <c r="K59" t="n">
         <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>-4.911041456498444</v>
+        <v>-4.029214125942115</v>
       </c>
       <c r="M59" t="n">
-        <v>18.27700023651123</v>
+        <v>18.29500026702881</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-5.126662317657211</v>
+        <v>-4.236128985807332</v>
       </c>
       <c r="P59" t="n">
-        <v>19.69807705512414</v>
+        <v>19.70500014378474</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-11.97110203162106</v>
+        <v>-11.08855452970019</v>
       </c>
       <c r="S59" t="n">
-        <v>21.36780006408691</v>
+        <v>21.37140007019043</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-18.8498577271349</v>
+        <v>-18.02127890441218</v>
       </c>
       <c r="V59" t="n">
-        <v>22.8369110361735</v>
+        <v>22.83811103820801</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-24.07029074500726</v>
+        <v>-23.28612279512598</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.58533024787903</v>
+        <v>21.58623024940491</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-19.66766339240181</v>
+        <v>-18.83714638758351</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3798263477646325</v>
+        <v>0.3734997253329962</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17453,13 +17457,13 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>23.43</v>
+        <v>23.68</v>
       </c>
       <c r="CA59" t="n">
         <v>0.1</v>
       </c>
       <c r="CB59" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="CC59" t="n">
         <v>7</v>
@@ -17494,13 +17498,13 @@
         <v>1</v>
       </c>
       <c r="CM59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN59" t="n">
         <v>0</v>
       </c>
       <c r="CO59" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
@@ -17513,82 +17517,82 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.77999973297119</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="D60" t="n">
-        <v>13.77999973297119</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="E60" t="n">
         <v>14.15999984741211</v>
       </c>
       <c r="F60" t="n">
-        <v>13.75</v>
+        <v>13.6899995803833</v>
       </c>
       <c r="G60" t="n">
         <v>13.84000015258789</v>
       </c>
       <c r="H60" t="n">
-        <v>6595600</v>
+        <v>9764900</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.02889357713434371</v>
+        <v>-0.02748410156315895</v>
       </c>
       <c r="J60" t="n">
-        <v>14.03666665818956</v>
+        <v>14.03888893127441</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.828546131845487</v>
+        <v>-1.70162141540545</v>
       </c>
       <c r="M60" t="n">
-        <v>14.1</v>
+        <v>14.10200004577637</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-2.269505439920626</v>
+        <v>-2.141539172182568</v>
       </c>
       <c r="P60" t="n">
-        <v>15.0853847356943</v>
+        <v>15.08615398406982</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-8.653309316230883</v>
+        <v>-8.525392188712052</v>
       </c>
       <c r="S60" t="n">
-        <v>15.64760005950928</v>
+        <v>15.64800006866455</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-11.93537871261682</v>
+        <v>-11.80981511899624</v>
       </c>
       <c r="V60" t="n">
-        <v>15.58433338165283</v>
+        <v>15.58446671803792</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-11.5778686485612</v>
+        <v>-11.45028931428026</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.47705001354218</v>
+        <v>15.47715001583099</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-10.96494667321028</v>
+        <v>-10.83629623916959</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3316654517850135</v>
+        <v>0.3308336396760026</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17740,7 +17744,7 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>24.61</v>
+        <v>24.64</v>
       </c>
       <c r="CA60" t="n">
         <v>0.68</v>
@@ -17778,7 +17782,7 @@
         <v>0</v>
       </c>
       <c r="CL60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CM60" t="n">
         <v>7</v>
@@ -17787,7 +17791,7 @@
         <v>0</v>
       </c>
       <c r="CO60" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">
@@ -17800,103 +17804,103 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>32.83000183105469</v>
+        <v>32.93000030517578</v>
       </c>
       <c r="D61" t="n">
-        <v>32.83000183105469</v>
+        <v>32.93000030517578</v>
       </c>
       <c r="E61" t="n">
         <v>33.86999893188477</v>
       </c>
       <c r="F61" t="n">
-        <v>32.81000137329102</v>
+        <v>32.61000061035156</v>
       </c>
       <c r="G61" t="n">
         <v>33.40000152587891</v>
       </c>
       <c r="H61" t="n">
-        <v>3935100</v>
+        <v>7597700</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0414598005531478</v>
+        <v>-0.03854013707515969</v>
       </c>
       <c r="J61" t="n">
-        <v>34.15777799818251</v>
+        <v>34.16888893975152</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.887185422888082</v>
+        <v>-3.625779687364767</v>
       </c>
       <c r="M61" t="n">
-        <v>34.20100021362305</v>
+        <v>34.21100006103516</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-4.008649963465862</v>
+        <v>-3.744408972476602</v>
       </c>
       <c r="P61" t="n">
-        <v>35.76000022888184</v>
+        <v>35.76384632404034</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-8.193507771458886</v>
+        <v>-7.923773056142605</v>
       </c>
       <c r="S61" t="n">
-        <v>37.56239997863769</v>
+        <v>37.56439994812012</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-12.5987640573403</v>
+        <v>-12.33721195958106</v>
       </c>
       <c r="V61" t="n">
-        <v>40.90859992980957</v>
+        <v>40.90926658630371</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-19.74792125033864</v>
+        <v>-19.50478937160746</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.65839998245239</v>
+        <v>40.658899974823</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-19.25407333976825</v>
+        <v>-19.00912143327327</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.38115938323516</v>
+        <v>0.3788737174291846</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="AE61" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="AF61" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="AG61" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="AH61" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="AI61" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="AJ61" t="n">
         <v>2</v>
@@ -18023,13 +18027,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>16.25</v>
+        <v>16.3</v>
       </c>
       <c r="CA61" t="n">
         <v>0.1</v>
       </c>
       <c r="CB61" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18041,7 +18045,7 @@
         <v>7</v>
       </c>
       <c r="CF61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CG61" t="n">
         <v>2</v>
@@ -18050,7 +18054,7 @@
         <v>7</v>
       </c>
       <c r="CI61" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CJ61" t="inlineStr">
         <is>
@@ -18070,7 +18074,7 @@
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62">
@@ -18083,10 +18087,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10.97999954223633</v>
+        <v>10.92000007629395</v>
       </c>
       <c r="D62" t="n">
-        <v>10.97999954223633</v>
+        <v>10.92000007629395</v>
       </c>
       <c r="E62" t="n">
         <v>11.14000034332275</v>
@@ -18098,67 +18102,67 @@
         <v>11.09000015258789</v>
       </c>
       <c r="H62" t="n">
-        <v>1273800</v>
+        <v>1806400</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.01081088604588942</v>
+        <v>-0.01621624315223202</v>
       </c>
       <c r="J62" t="n">
-        <v>11.6244445376926</v>
+        <v>11.61777793036567</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-5.543877760065356</v>
+        <v>-6.006121465344289</v>
       </c>
       <c r="M62" t="n">
-        <v>11.68400011062622</v>
+        <v>11.67800016403198</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-6.02533859743485</v>
+        <v>-6.490838132308495</v>
       </c>
       <c r="P62" t="n">
-        <v>12.13461538461539</v>
+        <v>12.13230771284837</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-9.515059239890801</v>
+        <v>-9.992391103553738</v>
       </c>
       <c r="S62" t="n">
-        <v>12.8338000869751</v>
+        <v>12.83260009765625</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-14.44467369115539</v>
+        <v>-14.90422834661249</v>
       </c>
       <c r="V62" t="n">
-        <v>11.92366667429606</v>
+        <v>11.92326667785644</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-7.914236097307247</v>
+        <v>-8.414360163777413</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.1207500076294</v>
+        <v>12.12045001029968</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-9.411550148918364</v>
+        <v>-9.904334682174527</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.3349783838046582</v>
+        <v>0.336066498292959</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18310,13 +18314,13 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="CA62" t="n">
         <v>0.47</v>
       </c>
       <c r="CB62" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="CC62" t="n">
         <v>8</v>
@@ -18370,108 +18374,106 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>40.27000045776367</v>
+        <v>40.63999938964844</v>
       </c>
       <c r="D63" t="n">
-        <v>40.27000045776367</v>
+        <v>40.63999938964844</v>
       </c>
       <c r="E63" t="n">
         <v>41.31999969482422</v>
       </c>
       <c r="F63" t="n">
-        <v>40.2599983215332</v>
+        <v>40.18000030517578</v>
       </c>
       <c r="G63" t="n">
         <v>40.84000015258789</v>
       </c>
       <c r="H63" t="n">
-        <v>3657400</v>
+        <v>6333900</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.03729383946937503</v>
+        <v>-0.028448539070414</v>
       </c>
       <c r="J63" t="n">
-        <v>42.56111145019531</v>
+        <v>42.60222244262695</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-5.383108932934426</v>
+        <v>-4.605917110594572</v>
       </c>
       <c r="M63" t="n">
-        <v>42.70900039672851</v>
+        <v>42.74600028991699</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-5.710739929075154</v>
+        <v>-4.926778847108467</v>
       </c>
       <c r="P63" t="n">
-        <v>44.34423123873197</v>
+        <v>44.35846196688139</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-9.18773573733692</v>
+        <v>-8.382758130814368</v>
       </c>
       <c r="S63" t="n">
-        <v>46.37360023498535</v>
+        <v>46.38100021362305</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-13.16179840748483</v>
+        <v>-12.37791508922302</v>
       </c>
       <c r="V63" t="n">
-        <v>45.67393343607585</v>
+        <v>45.67640009562174</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-11.83154716874865</v>
+        <v>-11.02626453798855</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.54715005874634</v>
+        <v>43.54900005340576</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-7.525520261513555</v>
+        <v>-6.679833429447081</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.4965626196488022</v>
+        <v>0.4926752221450961</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AD63" t="n">
+        <v>39.4</v>
       </c>
       <c r="AE63" t="n">
-        <v>26.7</v>
+        <v>40.2</v>
       </c>
       <c r="AF63" t="n">
-        <v>39.4</v>
+        <v>40.4</v>
       </c>
       <c r="AG63" t="n">
-        <v>40.4</v>
+        <v>40.9</v>
       </c>
       <c r="AH63" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="AI63" t="n">
-        <v>41</v>
+        <v>41.7</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK63" t="n">
         <v>0</v>
@@ -18595,13 +18597,13 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>20.14</v>
+        <v>20.32</v>
       </c>
       <c r="CA63" t="n">
         <v>0.71</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CC63" t="n">
         <v>10</v>
@@ -18651,82 +18653,82 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>26.78000068664551</v>
+        <v>26.70999908447266</v>
       </c>
       <c r="D64" t="n">
-        <v>26.78000068664551</v>
+        <v>26.70999908447266</v>
       </c>
       <c r="E64" t="n">
         <v>27.15999984741211</v>
       </c>
       <c r="F64" t="n">
-        <v>26.73999977111816</v>
+        <v>26.67000007629395</v>
       </c>
       <c r="G64" t="n">
         <v>27.14999961853027</v>
       </c>
       <c r="H64" t="n">
-        <v>2117400</v>
+        <v>3130500</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.02119882714792831</v>
+        <v>-0.02375736518196492</v>
       </c>
       <c r="J64" t="n">
-        <v>27.2511109246148</v>
+        <v>27.24333296881782</v>
       </c>
       <c r="K64" t="n">
         <v>-1</v>
       </c>
       <c r="L64" t="n">
-        <v>-1.72877443151779</v>
+        <v>-1.957667532660577</v>
       </c>
       <c r="M64" t="n">
-        <v>27.28499984741211</v>
+        <v>27.27799968719482</v>
       </c>
       <c r="N64" t="n">
         <v>-1</v>
       </c>
       <c r="O64" t="n">
-        <v>-1.850830726006029</v>
+        <v>-2.082266329040273</v>
       </c>
       <c r="P64" t="n">
-        <v>27.73807687025804</v>
+        <v>27.7353845009437</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-3.454010846151416</v>
+        <v>-3.697029750700423</v>
       </c>
       <c r="S64" t="n">
-        <v>29.2003999710083</v>
+        <v>29.19899993896484</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-8.288925106388593</v>
+        <v>-8.524267473868921</v>
       </c>
       <c r="V64" t="n">
-        <v>31.93053333282471</v>
+        <v>31.93006665547689</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-16.1304309968554</v>
+        <v>-16.34843931686202</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.01370001792908</v>
+        <v>31.01335000991821</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-13.65106172058175</v>
+        <v>-13.87580162758723</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2566860032536271</v>
+        <v>0.2581595510019785</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18898,7 +18900,7 @@
         <v>18881600000</v>
       </c>
       <c r="BZ64" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="CA64" t="n">
         <v>0</v>
@@ -18939,13 +18941,13 @@
         <v>6</v>
       </c>
       <c r="CM64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -18958,82 +18960,82 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27.10000038146973</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="D65" t="n">
-        <v>27.10000038146973</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="E65" t="n">
         <v>27.93000030517578</v>
       </c>
       <c r="F65" t="n">
-        <v>27.05999946594238</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="G65" t="n">
         <v>27.17000007629395</v>
       </c>
       <c r="H65" t="n">
-        <v>14593300</v>
+        <v>20456500</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.02130733626610859</v>
+        <v>-0.01841820942742689</v>
       </c>
       <c r="J65" t="n">
-        <v>28.1188890669081</v>
+        <v>28.12777794731988</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-3.623502632034833</v>
+        <v>-3.369543246249938</v>
       </c>
       <c r="M65" t="n">
-        <v>28.16900024414063</v>
+        <v>28.17700023651123</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-3.794951377066569</v>
+        <v>-3.538346605269764</v>
       </c>
       <c r="P65" t="n">
-        <v>29.90346182309664</v>
+        <v>29.90653874323918</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-9.37503978038287</v>
+        <v>-9.116863912176312</v>
       </c>
       <c r="S65" t="n">
-        <v>31.19004016876221</v>
+        <v>31.19164016723633</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-13.11328797642518</v>
+        <v>-12.8612661615479</v>
       </c>
       <c r="V65" t="n">
-        <v>28.80078214009603</v>
+        <v>28.80131547292073</v>
       </c>
       <c r="W65" t="n">
         <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>-5.905331842563049</v>
+        <v>-5.629309429527026</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.65205818176269</v>
+        <v>27.65245818138122</v>
       </c>
       <c r="Z65" t="n">
         <v>-1</v>
       </c>
       <c r="AA65" t="n">
-        <v>-1.996443796928885</v>
+        <v>-1.708556516409652</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2359094894525756</v>
+        <v>0.2347005127689267</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19185,7 +19187,7 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>10.93</v>
+        <v>10.96</v>
       </c>
       <c r="CA65" t="n">
         <v>0.34</v>
@@ -19254,13 +19256,13 @@
         <v>15.31999969482422</v>
       </c>
       <c r="F66" t="n">
-        <v>15</v>
+        <v>14.97000026702881</v>
       </c>
       <c r="G66" t="n">
         <v>15.19999980926514</v>
       </c>
       <c r="H66" t="n">
-        <v>3223300</v>
+        <v>5652400</v>
       </c>
       <c r="I66" t="n">
         <v>-0.01896664241834844</v>
@@ -19515,13 +19517,13 @@
         <v>2</v>
       </c>
       <c r="CM66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN66" t="n">
         <v>1</v>
       </c>
       <c r="CO66" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
@@ -19534,10 +19536,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>17.96999931335449</v>
+        <v>18.15999984741211</v>
       </c>
       <c r="D67" t="n">
-        <v>17.96999931335449</v>
+        <v>18.15999984741211</v>
       </c>
       <c r="E67" t="n">
         <v>18.43000030517578</v>
@@ -19549,67 +19551,67 @@
         <v>18.1299991607666</v>
       </c>
       <c r="H67" t="n">
-        <v>3844100</v>
+        <v>6173700</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.03387102447282064</v>
+        <v>-0.02365594220610712</v>
       </c>
       <c r="J67" t="n">
-        <v>18.69444444444444</v>
+        <v>18.71555561489529</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-3.875189408504937</v>
+        <v>-2.96841717614318</v>
       </c>
       <c r="M67" t="n">
-        <v>18.775</v>
+        <v>18.79400005340576</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-4.2876201685513</v>
+        <v>-3.373418134468721</v>
       </c>
       <c r="P67" t="n">
-        <v>18.62807684678298</v>
+        <v>18.63538455963135</v>
       </c>
       <c r="Q67" t="n">
         <v>-1</v>
       </c>
       <c r="R67" t="n">
-        <v>-3.53271858840401</v>
+        <v>-2.550978815049699</v>
       </c>
       <c r="S67" t="n">
-        <v>18.69479995727539</v>
+        <v>18.69859996795654</v>
       </c>
       <c r="T67" t="n">
         <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>-3.877017382252486</v>
+        <v>-2.880430200482513</v>
       </c>
       <c r="V67" t="n">
-        <v>21.36185456593831</v>
+        <v>21.36312123616537</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-15.87809355275813</v>
+        <v>-14.99369569335557</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.24919093132019</v>
+        <v>22.25014093399048</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-19.23302124187302</v>
+        <v>-18.38254013182477</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5180688854001723</v>
+        <v>0.5132674563437077</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19759,13 +19761,13 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.04</v>
+        <v>16.21</v>
       </c>
       <c r="CA67" t="n">
         <v>0.37</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CC67" t="n">
         <v>10</v>
@@ -19800,13 +19802,13 @@
         <v>9</v>
       </c>
       <c r="CM67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CN67" t="n">
         <v>-1</v>
       </c>
       <c r="CO67" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68">
@@ -19819,13 +19821,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>40.97999954223633</v>
+        <v>41.08000183105469</v>
       </c>
       <c r="D68" t="n">
-        <v>40.97999954223633</v>
+        <v>41.08000183105469</v>
       </c>
       <c r="E68" t="n">
-        <v>41.13000106811523</v>
+        <v>41.25</v>
       </c>
       <c r="F68" t="n">
         <v>40.18000030517578</v>
@@ -19834,67 +19836,67 @@
         <v>40.18000030517578</v>
       </c>
       <c r="H68" t="n">
-        <v>3660700</v>
+        <v>5405700</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01360374061115555</v>
+        <v>0.01607720803790591</v>
       </c>
       <c r="J68" t="n">
-        <v>41.39333343505859</v>
+        <v>41.40444480048286</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.9985518404086475</v>
+        <v>-0.7835945415801966</v>
       </c>
       <c r="M68" t="n">
-        <v>41.47999992370605</v>
+        <v>41.49000015258789</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-1.205401114728479</v>
+        <v>-0.9881858761758249</v>
       </c>
       <c r="P68" t="n">
-        <v>42.3942309159499</v>
+        <v>42.39807715782752</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.335905247384724</v>
+        <v>-3.108809208177716</v>
       </c>
       <c r="S68" t="n">
-        <v>45.47179985046387</v>
+        <v>45.47379989624024</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-9.878210941724396</v>
+        <v>-9.662262830929217</v>
       </c>
       <c r="V68" t="n">
-        <v>49.41453328450521</v>
+        <v>49.41519996643066</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-17.06893333122642</v>
+        <v>-16.86768067525447</v>
       </c>
       <c r="Y68" t="n">
-        <v>49.71274995803833</v>
+        <v>49.71324996948242</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-17.5664199288375</v>
+        <v>-17.36609081829782</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2233060273523847</v>
+        <v>0.2252057983454621</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20046,7 +20048,7 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
       <c r="CA68" t="n">
         <v>1.32</v>
@@ -20090,7 +20092,7 @@
         <v>8</v>
       </c>
       <c r="CN68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO68" t="n">
         <v>48</v>
@@ -20106,82 +20108,82 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>38.88999938964844</v>
+        <v>38.88000106811523</v>
       </c>
       <c r="D69" t="n">
-        <v>38.88999938964844</v>
+        <v>38.88000106811523</v>
       </c>
       <c r="E69" t="n">
         <v>39.31000137329102</v>
       </c>
       <c r="F69" t="n">
-        <v>38.81000137329102</v>
+        <v>38.75</v>
       </c>
       <c r="G69" t="n">
         <v>39.04000091552734</v>
       </c>
       <c r="H69" t="n">
-        <v>647800</v>
+        <v>1167900</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.009171990072651237</v>
+        <v>-0.009426724379229645</v>
       </c>
       <c r="J69" t="n">
-        <v>39.11444430881076</v>
+        <v>39.11333338419596</v>
       </c>
       <c r="K69" t="n">
         <v>-1</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.57381594735264</v>
+        <v>-0.5965544122480916</v>
       </c>
       <c r="M69" t="n">
-        <v>39.04499969482422</v>
+        <v>39.0439998626709</v>
       </c>
       <c r="N69" t="n">
         <v>-1</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.3969786307779877</v>
+        <v>-0.4200358445151582</v>
       </c>
       <c r="P69" t="n">
-        <v>39.90307690547063</v>
+        <v>39.90269235464243</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-2.538845608879095</v>
+        <v>-2.562963113961927</v>
       </c>
       <c r="S69" t="n">
-        <v>41.73360015869141</v>
+        <v>41.73340019226075</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-6.813696298019392</v>
+        <v>-6.837207395036699</v>
       </c>
       <c r="V69" t="n">
-        <v>41.83226679484049</v>
+        <v>41.83220013936361</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-7.033487856687098</v>
+        <v>-7.057240741374223</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.20355012893677</v>
+        <v>40.2035001373291</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-3.267250616116347</v>
+        <v>-3.291999613697796</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2281329103975499</v>
+        <v>0.2281709004249645</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20389,10 +20391,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.26000022888184</v>
+        <v>22.29000091552734</v>
       </c>
       <c r="D70" t="n">
-        <v>22.26000022888184</v>
+        <v>22.29000091552734</v>
       </c>
       <c r="E70" t="n">
         <v>22.34000015258789</v>
@@ -20404,67 +20406,67 @@
         <v>21.79999923706055</v>
       </c>
       <c r="H70" t="n">
-        <v>2515000</v>
+        <v>4070300</v>
       </c>
       <c r="I70" t="n">
-        <v>0.01089917194045964</v>
+        <v>0.01226160091511153</v>
       </c>
       <c r="J70" t="n">
-        <v>22.29333347744412</v>
+        <v>22.2966668870714</v>
       </c>
       <c r="K70" t="n">
         <v>-1</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.14952114988101</v>
+        <v>-0.02989671764759364</v>
       </c>
       <c r="M70" t="n">
-        <v>22.32900009155274</v>
+        <v>22.33200016021728</v>
       </c>
       <c r="N70" t="n">
         <v>-1</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.3090145657574839</v>
+        <v>-0.1880675460712129</v>
       </c>
       <c r="P70" t="n">
-        <v>23.14307697002704</v>
+        <v>23.14423084259033</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-3.81572745183751</v>
+        <v>-3.690897886703682</v>
       </c>
       <c r="S70" t="n">
-        <v>24.95319999694824</v>
+        <v>24.95380001068115</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-10.79300357627793</v>
+        <v>-10.67492363493177</v>
       </c>
       <c r="V70" t="n">
-        <v>24.81126668294271</v>
+        <v>24.81146668752034</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-10.28269328875023</v>
+        <v>-10.16250189377658</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.33350001335144</v>
+        <v>24.33365001678467</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-8.521173622092606</v>
+        <v>-8.398448649699782</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3770606997208327</v>
+        <v>0.3776100157579323</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20616,7 +20618,7 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
@@ -20676,82 +20678,82 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>33.22999954223633</v>
+        <v>33.29999923706055</v>
       </c>
       <c r="D71" t="n">
-        <v>33.22999954223633</v>
+        <v>33.29999923706055</v>
       </c>
       <c r="E71" t="n">
         <v>35.09999847412109</v>
       </c>
       <c r="F71" t="n">
-        <v>33.04999923706055</v>
+        <v>33.04000091552734</v>
       </c>
       <c r="G71" t="n">
         <v>34.06999969482422</v>
       </c>
       <c r="H71" t="n">
-        <v>4339800</v>
+        <v>6647300</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.03429236589387918</v>
+        <v>-0.03225808239679617</v>
       </c>
       <c r="J71" t="n">
-        <v>32.54555532667372</v>
+        <v>32.55333307054308</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>2.103034373488319</v>
+        <v>2.293670405114725</v>
       </c>
       <c r="M71" t="n">
-        <v>32.51799983978272</v>
+        <v>32.52499980926514</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2.189555649061003</v>
+        <v>2.382780729716221</v>
       </c>
       <c r="P71" t="n">
-        <v>32.49961522909311</v>
+        <v>32.50230752504789</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>2.247362954898589</v>
+        <v>2.454261782483956</v>
       </c>
       <c r="S71" t="n">
-        <v>33.42199989318848</v>
+        <v>33.42339988708496</v>
       </c>
       <c r="T71" t="n">
         <v>-1</v>
       </c>
       <c r="U71" t="n">
-        <v>-0.5744729566326151</v>
+        <v>-0.3692043611401059</v>
       </c>
       <c r="V71" t="n">
-        <v>39.24613327026367</v>
+        <v>39.24659993489583</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-15.32923940964573</v>
+        <v>-15.15188757166174</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.22154998779297</v>
+        <v>40.22189998626709</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-17.38259825312187</v>
+        <v>-17.2092833793776</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4921226101169948</v>
+        <v>0.4909660200397436</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20903,13 +20905,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>21.58</v>
+        <v>21.62</v>
       </c>
       <c r="CA71" t="n">
         <v>0.17</v>
       </c>
       <c r="CB71" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20963,82 +20965,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>25</v>
+        <v>24.84000015258789</v>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>24.84000015258789</v>
       </c>
       <c r="E72" t="n">
         <v>25.46999931335449</v>
       </c>
       <c r="F72" t="n">
-        <v>24.95000076293945</v>
+        <v>24.79000091552734</v>
       </c>
       <c r="G72" t="n">
         <v>25.04999923706055</v>
       </c>
       <c r="H72" t="n">
-        <v>3293600</v>
+        <v>5204400</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.02761567910367813</v>
+        <v>-0.03383893282245176</v>
       </c>
       <c r="J72" t="n">
-        <v>26.8211112552219</v>
+        <v>26.80333349439833</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-6.78984266495423</v>
+        <v>-7.324959569751874</v>
       </c>
       <c r="M72" t="n">
-        <v>27.05400009155273</v>
+        <v>27.03800010681152</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-7.592223274199178</v>
+        <v>-8.129299302983226</v>
       </c>
       <c r="P72" t="n">
-        <v>28.55230786250188</v>
+        <v>28.5461540222168</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-12.44140361475707</v>
+        <v>-12.98302344597627</v>
       </c>
       <c r="S72" t="n">
-        <v>28.8938000869751</v>
+        <v>28.89060009002685</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-13.4762477599143</v>
+        <v>-14.02047698842104</v>
       </c>
       <c r="V72" t="n">
-        <v>25.27993333180746</v>
+        <v>25.27886666615804</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-1.107334137844585</v>
+        <v>-1.736100432689418</v>
       </c>
       <c r="Y72" t="n">
-        <v>24.02534999847412</v>
+        <v>24.02454999923706</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>4.056756723992706</v>
+        <v>3.394236950855383</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2742040975364445</v>
+        <v>0.2790625485254272</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21190,13 +21192,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>9.289999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="CA72" t="n">
         <v>0.5</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21224,16 +21226,16 @@
         <v>0</v>
       </c>
       <c r="CL72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CM72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN72" t="n">
         <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
@@ -21246,82 +21248,82 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>11.36999988555908</v>
+        <v>11.42000007629395</v>
       </c>
       <c r="D73" t="n">
-        <v>11.36999988555908</v>
+        <v>11.42000007629395</v>
       </c>
       <c r="E73" t="n">
         <v>11.89000034332275</v>
       </c>
       <c r="F73" t="n">
-        <v>11.36999988555908</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="G73" t="n">
         <v>11.80000019073486</v>
       </c>
       <c r="H73" t="n">
-        <v>9301700</v>
+        <v>11883100</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.05564784704457992</v>
+        <v>-0.05149500726939038</v>
       </c>
       <c r="J73" t="n">
-        <v>10.7211110856798</v>
+        <v>10.72666666242811</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>6.052439851556128</v>
+        <v>6.463642766996236</v>
       </c>
       <c r="M73" t="n">
-        <v>10.6289999961853</v>
+        <v>10.63400001525879</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>6.971492046662149</v>
+        <v>7.39138668334889</v>
       </c>
       <c r="P73" t="n">
-        <v>9.544230717879076</v>
+        <v>9.546153802138109</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>19.12955817654133</v>
+        <v>19.62933253533103</v>
       </c>
       <c r="S73" t="n">
-        <v>8.341399974822998</v>
+        <v>8.342399978637696</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>36.30805284337597</v>
+        <v>36.89106378904189</v>
       </c>
       <c r="V73" t="n">
-        <v>6.82366665204366</v>
+        <v>6.82399998664856</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>66.62595735320414</v>
+        <v>67.35052899527625</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.223599990606308</v>
+        <v>6.223849991559982</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>82.69168813420812</v>
+        <v>83.48771406412978</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.6229030610724772</v>
+        <v>0.618869533533267</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21473,13 +21475,13 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>-5.47</v>
+        <v>-5.49</v>
       </c>
       <c r="CA73" t="n">
         <v>-0.03</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="CC73" t="n">
         <v>1</v>
@@ -21533,103 +21535,103 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>82.05000305175781</v>
+        <v>82.11000061035156</v>
       </c>
       <c r="D74" t="n">
-        <v>82.05000305175781</v>
+        <v>82.11000061035156</v>
       </c>
       <c r="E74" t="n">
         <v>83.79000091552734</v>
       </c>
       <c r="F74" t="n">
-        <v>81.80999755859375</v>
+        <v>81.80000305175781</v>
       </c>
       <c r="G74" t="n">
         <v>83.61000061035156</v>
       </c>
       <c r="H74" t="n">
-        <v>11789700</v>
+        <v>16056000</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.03470584644990804</v>
+        <v>-0.03399999281939337</v>
       </c>
       <c r="J74" t="n">
-        <v>83.19333224826389</v>
+        <v>83.19999864366319</v>
       </c>
       <c r="K74" t="n">
         <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.374303884227372</v>
+        <v>-1.31009381139533</v>
       </c>
       <c r="M74" t="n">
-        <v>83.13699874877929</v>
+        <v>83.14299850463867</v>
       </c>
       <c r="N74" t="n">
         <v>-1</v>
       </c>
       <c r="O74" t="n">
-        <v>-1.307475267787964</v>
+        <v>-1.242435217475918</v>
       </c>
       <c r="P74" t="n">
-        <v>82.22115384615384</v>
+        <v>82.22346144456129</v>
       </c>
       <c r="Q74" t="n">
         <v>-1</v>
       </c>
       <c r="R74" t="n">
-        <v>-0.2081590763324385</v>
+        <v>-0.1379908267255723</v>
       </c>
       <c r="S74" t="n">
-        <v>83.13120040893554</v>
+        <v>83.13240036010743</v>
       </c>
       <c r="T74" t="n">
         <v>-1</v>
       </c>
       <c r="U74" t="n">
-        <v>-1.300591537063278</v>
+        <v>-1.229845096890141</v>
       </c>
       <c r="V74" t="n">
-        <v>77.98973340352376</v>
+        <v>77.99013338724772</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>5.206159158444568</v>
+        <v>5.28254927151783</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.7952000617981</v>
+        <v>72.79550004959107</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>12.7134797103422</v>
+        <v>12.79543454528796</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.3317260104295859</v>
+        <v>0.331134331136372</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
       </c>
       <c r="AD74" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="AE74" t="n">
-        <v>80.8</v>
+        <v>81.7</v>
       </c>
       <c r="AF74" t="n">
-        <v>81.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AG74" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AH74" t="n">
-        <v>82.2</v>
+        <v>82.7</v>
       </c>
       <c r="AI74" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="AJ74" t="n">
         <v>2</v>
@@ -21756,7 +21758,7 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>23.38</v>
+        <v>23.39</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
@@ -21812,10 +21814,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.890000104904175</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="D75" t="n">
-        <v>2.890000104904175</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E75" t="n">
         <v>2.940000057220459</v>
@@ -21827,67 +21829,67 @@
         <v>2.940000057220459</v>
       </c>
       <c r="H75" t="n">
-        <v>8330300</v>
+        <v>11121200</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.02693600098835336</v>
+        <v>-0.01683500061772081</v>
       </c>
       <c r="J75" t="n">
-        <v>3.133333338631524</v>
+        <v>3.136666668785943</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-7.765954254762581</v>
+        <v>-6.907542795290365</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15699999332428</v>
+        <v>3.159999990463257</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-8.457392745793371</v>
+        <v>-7.59493401562091</v>
       </c>
       <c r="P75" t="n">
-        <v>3.477692328966581</v>
+        <v>3.478846174020034</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-16.89891366085978</v>
+        <v>-16.06412211898135</v>
       </c>
       <c r="S75" t="n">
-        <v>3.707400007247925</v>
+        <v>3.70800000667572</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-22.04779362210019</v>
+        <v>-21.2513465200403</v>
       </c>
       <c r="V75" t="n">
-        <v>3.748794790903727</v>
+        <v>3.748994790712992</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-22.90855418609141</v>
+        <v>-22.1124530893623</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.720896098613739</v>
+        <v>3.721046098470688</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-22.33053468004989</v>
+        <v>-21.52744150377402</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.4413315549479148</v>
+        <v>0.4398829327696821</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -21902,21 +21904,21 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>Abismo</t>
-        </is>
+      <c r="AF75" t="n">
+        <v>2.9</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AH75" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AI75" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AJ75" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>1</v>
+      </c>
       <c r="AK75" t="n">
         <v>-1</v>
       </c>
@@ -22039,13 +22041,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>11.56</v>
+        <v>11.68</v>
       </c>
       <c r="CA75" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CB75" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CC75" t="n">
         <v>6</v>
@@ -22076,13 +22078,13 @@
         <v>1</v>
       </c>
       <c r="CM75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN75" t="n">
         <v>0</v>
       </c>
       <c r="CO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -22104,13 +22106,13 @@
         <v>30.05999946594238</v>
       </c>
       <c r="F76" t="n">
-        <v>29.23999977111816</v>
+        <v>29.17000007629395</v>
       </c>
       <c r="G76" t="n">
         <v>29.35000038146973</v>
       </c>
       <c r="H76" t="n">
-        <v>5342900</v>
+        <v>10419400</v>
       </c>
       <c r="I76" t="n">
         <v>-0.02821103543965275</v>
@@ -22356,16 +22358,16 @@
         <v>0</v>
       </c>
       <c r="CL76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CM76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN76" t="n">
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
@@ -22378,82 +22380,82 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>20.1200008392334</v>
+        <v>20.11000061035156</v>
       </c>
       <c r="D77" t="n">
-        <v>20.1200008392334</v>
+        <v>20.11000061035156</v>
       </c>
       <c r="E77" t="n">
         <v>21.18000030517578</v>
       </c>
       <c r="F77" t="n">
-        <v>20.11000061035156</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="G77" t="n">
         <v>21.18000030517578</v>
       </c>
       <c r="H77" t="n">
-        <v>2468500</v>
+        <v>4052100</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.05981302813615585</v>
+        <v>-0.06028032855952481</v>
       </c>
       <c r="J77" t="n">
-        <v>21.82555558946397</v>
+        <v>21.82444445292155</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-7.814484919934464</v>
+        <v>-7.855612756917083</v>
       </c>
       <c r="M77" t="n">
-        <v>21.875</v>
+        <v>21.87399997711181</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-8.022853306361608</v>
+        <v>-8.064365770348539</v>
       </c>
       <c r="P77" t="n">
-        <v>23.5265385554387</v>
+        <v>23.52615393125094</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-14.47955341232212</v>
+        <v>-14.52066211452239</v>
       </c>
       <c r="S77" t="n">
-        <v>25.05100006103516</v>
+        <v>25.05080005645752</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-19.68384180187496</v>
+        <v>-19.72312035931296</v>
       </c>
       <c r="V77" t="n">
-        <v>28.90306667327881</v>
+        <v>28.90300000508626</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-30.38800668914987</v>
+        <v>-30.42244539731978</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.76315001487732</v>
+        <v>28.76310001373291</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-30.04938322531913</v>
+        <v>-30.08402918756996</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4821146402906664</v>
+        <v>0.4825366215117649</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22665,10 +22667,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.70999908447266</v>
+        <v>33.66999816894531</v>
       </c>
       <c r="D78" t="n">
-        <v>33.70999908447266</v>
+        <v>33.66999816894531</v>
       </c>
       <c r="E78" t="n">
         <v>33.97999954223633</v>
@@ -22680,67 +22682,67 @@
         <v>33.2599983215332</v>
       </c>
       <c r="H78" t="n">
-        <v>3385500</v>
+        <v>6591400</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.002662726468029231</v>
+        <v>-0.003846185534013058</v>
       </c>
       <c r="J78" t="n">
-        <v>33.81222195095486</v>
+        <v>33.80777740478516</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.3023251965827145</v>
+        <v>-0.4075371006801011</v>
       </c>
       <c r="M78" t="n">
-        <v>33.95999984741211</v>
+        <v>33.95599975585937</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.7361624383473058</v>
+        <v>-0.8422711419789939</v>
       </c>
       <c r="P78" t="n">
-        <v>35.94499998826247</v>
+        <v>35.94346149151142</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-6.21783531651031</v>
+        <v>-6.325109569936719</v>
       </c>
       <c r="S78" t="n">
-        <v>38.36759986877441</v>
+        <v>38.36679985046387</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-12.13941137895456</v>
+        <v>-12.24183851617682</v>
       </c>
       <c r="V78" t="n">
-        <v>37.01160006205241</v>
+        <v>37.01133338928223</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-8.920449189022898</v>
+        <v>-9.027870423345792</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.11115007400512</v>
+        <v>36.11095006942749</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-6.649334027333994</v>
+        <v>-6.759589254198969</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3136572749118233</v>
+        <v>0.3135560565561536</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22892,7 +22894,7 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>17.11</v>
+        <v>17.09</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
@@ -22952,10 +22954,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>41.91999816894531</v>
+        <v>41.93999862670898</v>
       </c>
       <c r="D79" t="n">
-        <v>41.91999816894531</v>
+        <v>41.93999862670898</v>
       </c>
       <c r="E79" t="n">
         <v>42.45000076293945</v>
@@ -22967,67 +22969,67 @@
         <v>41.59999847412109</v>
       </c>
       <c r="H79" t="n">
-        <v>3532100</v>
+        <v>5015600</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.00190480550130212</v>
+        <v>-0.001428604125976562</v>
       </c>
       <c r="J79" t="n">
-        <v>43.07444424099393</v>
+        <v>43.07666651407877</v>
       </c>
       <c r="K79" t="n">
         <v>-1</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.680118321642624</v>
+        <v>-2.638709025913812</v>
       </c>
       <c r="M79" t="n">
-        <v>43.01399993896484</v>
+        <v>43.01599998474121</v>
       </c>
       <c r="N79" t="n">
         <v>-1</v>
       </c>
       <c r="O79" t="n">
-        <v>-2.543362095066435</v>
+        <v>-2.50139798775784</v>
       </c>
       <c r="P79" t="n">
-        <v>43.5965386904203</v>
+        <v>43.59730793879582</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-3.84558171780591</v>
+        <v>-3.801402862794775</v>
       </c>
       <c r="S79" t="n">
-        <v>46.46020011901855</v>
+        <v>46.46060012817383</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       </c>
       <c r="U79" t="n">
-        <v>-9.772239332681439</v>
+        <v>-9.72996794917322</v>
       </c>
       <c r="V79" t="n">
-        <v>47.11899993896484</v>
+        <v>47.11913327534994</v>
       </c>
       <c r="W79" t="n">
         <v>-1</v>
       </c>
       <c r="X79" t="n">
-        <v>-11.03376934305483</v>
+        <v>-10.99157452318925</v>
       </c>
       <c r="Y79" t="n">
-        <v>44.61589994430542</v>
+        <v>44.61599994659424</v>
       </c>
       <c r="Z79" t="n">
         <v>-1</v>
       </c>
       <c r="AA79" t="n">
-        <v>-6.042468668625835</v>
+        <v>-5.997851271042788</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.3257203304566146</v>
+        <v>0.3257578505798084</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -23177,7 +23179,7 @@
       <c r="BX79" t="inlineStr"/>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="n">
-        <v>27.95</v>
+        <v>27.96</v>
       </c>
       <c r="CA79" t="n">
         <v>-0.02</v>
@@ -23237,10 +23239,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8.75</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="D80" t="n">
-        <v>8.75</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="E80" t="n">
         <v>9.239999771118164</v>
@@ -23252,67 +23254,67 @@
         <v>9.199999809265137</v>
       </c>
       <c r="H80" t="n">
-        <v>3438900</v>
+        <v>4885600</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.06815764855406625</v>
+        <v>-0.0521832488686671</v>
       </c>
       <c r="J80" t="n">
-        <v>9.467777782016331</v>
+        <v>9.484444406297472</v>
       </c>
       <c r="K80" t="n">
         <v>-1</v>
       </c>
       <c r="L80" t="n">
-        <v>-7.581269845387808</v>
+        <v>-6.162140476875372</v>
       </c>
       <c r="M80" t="n">
-        <v>9.49399995803833</v>
+        <v>9.508999919891357</v>
       </c>
       <c r="N80" t="n">
         <v>-1</v>
       </c>
       <c r="O80" t="n">
-        <v>-7.836527926339457</v>
+        <v>-6.404462156815768</v>
       </c>
       <c r="P80" t="n">
-        <v>9.786153830014742</v>
+        <v>9.791923046112061</v>
       </c>
       <c r="Q80" t="n">
         <v>-1</v>
       </c>
       <c r="R80" t="n">
-        <v>-10.58795772080338</v>
+        <v>-9.108766719075987</v>
       </c>
       <c r="S80" t="n">
-        <v>10.59659999847412</v>
+        <v>10.59959999084473</v>
       </c>
       <c r="T80" t="n">
         <v>-1</v>
       </c>
       <c r="U80" t="n">
-        <v>-17.42634428722445</v>
+        <v>-16.03457086854657</v>
       </c>
       <c r="V80" t="n">
-        <v>12.09539999643962</v>
+        <v>12.09639999389649</v>
       </c>
       <c r="W80" t="n">
         <v>-1</v>
       </c>
       <c r="X80" t="n">
-        <v>-27.65844864514082</v>
+        <v>-26.42439384427622</v>
       </c>
       <c r="Y80" t="n">
-        <v>12.30420000553131</v>
+        <v>12.30495000362396</v>
       </c>
       <c r="Z80" t="n">
         <v>-1</v>
       </c>
       <c r="AA80" t="n">
-        <v>-28.88607145473523</v>
+        <v>-27.67138740174392</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.4582140644761113</v>
+        <v>0.4425111118271851</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -23464,13 +23466,13 @@
       <c r="BX80" t="inlineStr"/>
       <c r="BY80" t="inlineStr"/>
       <c r="BZ80" t="n">
-        <v>20.35</v>
+        <v>20.7</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CB80" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CC80" t="n">
         <v>5</v>
@@ -23505,13 +23507,13 @@
         <v>2</v>
       </c>
       <c r="CM80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN80" t="n">
         <v>0</v>
       </c>
       <c r="CO80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/latest.xlsx
+++ b/site/data/latest.xlsx
@@ -897,82 +897,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.09000015258789</v>
+        <v>16.06999969482422</v>
       </c>
       <c r="D2" t="n">
-        <v>16.09000015258789</v>
+        <v>16.06999969482422</v>
       </c>
       <c r="E2" t="n">
         <v>16.31999969482422</v>
       </c>
       <c r="F2" t="n">
-        <v>16.09000015258789</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="G2" t="n">
         <v>16.21999931335449</v>
       </c>
       <c r="H2" t="n">
-        <v>18826100</v>
+        <v>24072000</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02188453456869222</v>
+        <v>-0.02310036781100622</v>
       </c>
       <c r="J2" t="n">
-        <v>16.36444473266602</v>
+        <v>16.36222245958116</v>
       </c>
       <c r="K2" t="n">
         <v>-1</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.677078474470266</v>
+        <v>-1.785960100950877</v>
       </c>
       <c r="M2" t="n">
-        <v>16.36800022125244</v>
+        <v>16.36600017547607</v>
       </c>
       <c r="N2" t="n">
         <v>-1</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.698436369175942</v>
+        <v>-1.808630560174395</v>
       </c>
       <c r="P2" t="n">
-        <v>15.97923080737774</v>
+        <v>15.97846155900222</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6932082435345061</v>
+        <v>0.5728845388774624</v>
       </c>
       <c r="S2" t="n">
-        <v>15.63240001678467</v>
+        <v>15.63200000762939</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2.927254518256264</v>
+        <v>2.801942726337345</v>
       </c>
       <c r="V2" t="n">
-        <v>14.75486666997274</v>
+        <v>14.75473333358765</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>9.048766840653661</v>
+        <v>8.914199474161304</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.11600000858307</v>
+        <v>14.11590000629425</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.98413249365652</v>
+        <v>13.84325255675259</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5025133604089852</v>
+        <v>0.503029879468823</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="n">
-        <v>16.25</v>
+        <v>16.23</v>
       </c>
       <c r="CA2" t="n">
         <v>-0.07000000000000001</v>
@@ -1165,13 +1165,13 @@
         <v>10</v>
       </c>
       <c r="CM2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.05999946594238</v>
+        <v>27.28000068664551</v>
       </c>
       <c r="D3" t="n">
-        <v>27.05999946594238</v>
+        <v>27.28000068664551</v>
       </c>
       <c r="E3" t="n">
         <v>27.42000007629395</v>
@@ -1199,67 +1199,67 @@
         <v>27.42000007629395</v>
       </c>
       <c r="H3" t="n">
-        <v>6645400</v>
+        <v>7531700</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02062973985296368</v>
+        <v>-0.01266733567687095</v>
       </c>
       <c r="J3" t="n">
-        <v>28.16111098395454</v>
+        <v>28.18555556403266</v>
       </c>
       <c r="K3" t="n">
         <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.910042890848795</v>
+        <v>-3.21283316672574</v>
       </c>
       <c r="M3" t="n">
-        <v>28.21699981689453</v>
+        <v>28.23899993896485</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.100366298543942</v>
+        <v>-3.396009966330597</v>
       </c>
       <c r="P3" t="n">
-        <v>29.11423066946177</v>
+        <v>29.12269225487342</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-7.055763302975023</v>
+        <v>-6.327339354827523</v>
       </c>
       <c r="S3" t="n">
-        <v>30.25119995117187</v>
+        <v>30.25559997558594</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.54900463578427</v>
+        <v>-9.834871201832128</v>
       </c>
       <c r="V3" t="n">
-        <v>29.39239997863769</v>
+        <v>29.39386665344238</v>
       </c>
       <c r="W3" t="n">
         <v>-1</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.935386407338268</v>
+        <v>-7.191520570327267</v>
       </c>
       <c r="Y3" t="n">
-        <v>28.11224996566773</v>
+        <v>28.11334997177124</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3.743031955857005</v>
+        <v>-2.964247540625722</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2582148403330922</v>
+        <v>0.2555704165625106</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1411,13 +1411,13 @@
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
-        <v>16.5</v>
+        <v>16.63</v>
       </c>
       <c r="CA3" t="n">
         <v>-0.16</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CC3" t="n">
         <v>9</v>
@@ -1452,13 +1452,13 @@
         <v>5</v>
       </c>
       <c r="CM3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.770000457763672</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="D4" t="n">
-        <v>8.770000457763672</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="E4" t="n">
         <v>9.090000152587891</v>
@@ -1486,67 +1486,67 @@
         <v>8.829999923706055</v>
       </c>
       <c r="H4" t="n">
-        <v>12232600</v>
+        <v>14404600</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0309391963613268</v>
+        <v>-0.02872930645327687</v>
       </c>
       <c r="J4" t="n">
-        <v>8.896666632758247</v>
+        <v>8.898888799879286</v>
       </c>
       <c r="K4" t="n">
         <v>-1</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.423748694012883</v>
+        <v>-1.223622864325887</v>
       </c>
       <c r="M4" t="n">
-        <v>8.854999923706055</v>
+        <v>8.85699987411499</v>
       </c>
       <c r="N4" t="n">
         <v>-1</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9599036326903615</v>
+        <v>-0.75646283407741</v>
       </c>
       <c r="P4" t="n">
-        <v>8.832692256340614</v>
+        <v>8.833461468036358</v>
       </c>
       <c r="Q4" t="n">
         <v>-1</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.7097699858379943</v>
+        <v>-0.4920099141270367</v>
       </c>
       <c r="S4" t="n">
-        <v>9.014999952316284</v>
+        <v>9.015399942398071</v>
       </c>
       <c r="T4" t="n">
         <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.717687141969011</v>
+        <v>-2.500166182145969</v>
       </c>
       <c r="V4" t="n">
-        <v>8.645599946975707</v>
+        <v>8.64573327700297</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.438888122870879</v>
+        <v>1.668646027212019</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.871249949932098</v>
+        <v>8.871349947452545</v>
       </c>
       <c r="Z4" t="n">
         <v>-1</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.141321603380154</v>
+        <v>-0.916996692514401</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4884607859065336</v>
+        <v>0.4873789107169805</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
-        <v>16.87</v>
+        <v>16.9</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12.07999992370605</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="D5" t="n">
-        <v>12.07999992370605</v>
+        <v>11.97000026702881</v>
       </c>
       <c r="E5" t="n">
         <v>12.15999984741211</v>
@@ -1769,88 +1769,88 @@
         <v>12.10000038146973</v>
       </c>
       <c r="H5" t="n">
-        <v>2212200</v>
+        <v>2983100</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01548496552315914</v>
+        <v>-0.02444989238325923</v>
       </c>
       <c r="J5" t="n">
-        <v>12.34222221374512</v>
+        <v>12.33000002966987</v>
       </c>
       <c r="K5" t="n">
         <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.124595437497749</v>
+        <v>-2.919706097119115</v>
       </c>
       <c r="M5" t="n">
-        <v>12.37200002670288</v>
+        <v>12.36100006103516</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.360168948970205</v>
+        <v>-3.163172818345604</v>
       </c>
       <c r="P5" t="n">
-        <v>12.93923077216515</v>
+        <v>12.9350000161391</v>
       </c>
       <c r="Q5" t="n">
         <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-6.640509498504908</v>
+        <v>-7.460376868235458</v>
       </c>
       <c r="S5" t="n">
-        <v>13.00919994354248</v>
+        <v>13.00699995040894</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-7.142637701541846</v>
+        <v>-7.972627718411919</v>
       </c>
       <c r="V5" t="n">
-        <v>12.14373330434163</v>
+        <v>12.14299997329712</v>
       </c>
       <c r="W5" t="n">
         <v>-1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5248252661542979</v>
+        <v>-1.424686705498994</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.75089996814728</v>
+        <v>11.75034996986389</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.800636176385257</v>
+        <v>1.869308554453724</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2294146196834713</v>
+        <v>0.2339875820607886</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>11.9</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>12</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>12.1</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>12.2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>12.4</v>
       </c>
       <c r="AJ5" t="n">
         <v>1</v>
@@ -1977,13 +1977,13 @@
       <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="inlineStr"/>
       <c r="BZ5" t="n">
-        <v>-9.82</v>
+        <v>-9.73</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="CC5" t="n">
         <v>10</v>
@@ -2011,16 +2011,16 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN5" t="n">
         <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50.86999893188477</v>
+        <v>50.75</v>
       </c>
       <c r="D6" t="n">
-        <v>50.86999893188477</v>
+        <v>50.75</v>
       </c>
       <c r="E6" t="n">
         <v>51.59999847412109</v>
@@ -2048,67 +2048,67 @@
         <v>51.25</v>
       </c>
       <c r="H6" t="n">
-        <v>8683900</v>
+        <v>10270200</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02845686900492939</v>
+        <v>-0.03074867440000117</v>
       </c>
       <c r="J6" t="n">
-        <v>52.66555574205186</v>
+        <v>52.652222527398</v>
       </c>
       <c r="K6" t="n">
         <v>-1</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.409356997885814</v>
+        <v>-3.612805758404911</v>
       </c>
       <c r="M6" t="n">
-        <v>52.86700019836426</v>
+        <v>52.85500030517578</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.777406054791212</v>
+        <v>-3.982594443329609</v>
       </c>
       <c r="P6" t="n">
-        <v>56.09461520268367</v>
+        <v>56.08999985914964</v>
       </c>
       <c r="Q6" t="n">
         <v>-1</v>
       </c>
       <c r="R6" t="n">
-        <v>-9.31393548546697</v>
+        <v>-9.520413393758565</v>
       </c>
       <c r="S6" t="n">
-        <v>58.66720001220703</v>
+        <v>58.66480003356934</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-13.29056283357631</v>
+        <v>-13.49156569022703</v>
       </c>
       <c r="V6" t="n">
-        <v>58.11853335062663</v>
+        <v>58.1177333577474</v>
       </c>
       <c r="W6" t="n">
         <v>-1</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.47198440988138</v>
+        <v>-12.67725517166137</v>
       </c>
       <c r="Y6" t="n">
-        <v>55.6920000076294</v>
+        <v>55.69140001296997</v>
       </c>
       <c r="Z6" t="n">
         <v>-1</v>
       </c>
       <c r="AA6" t="n">
-        <v>-8.658337059333569</v>
+        <v>-8.872824191561298</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.2926932356930769</v>
+        <v>0.2941960094942165</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
       <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr"/>
       <c r="BZ6" t="n">
-        <v>15.56</v>
+        <v>15.52</v>
       </c>
       <c r="CA6" t="n">
         <v>0.31</v>
@@ -2297,13 +2297,13 @@
         <v>3</v>
       </c>
       <c r="CM6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN6" t="n">
         <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.83000183105469</v>
+        <v>55.52000045776367</v>
       </c>
       <c r="D7" t="n">
-        <v>55.83000183105469</v>
+        <v>55.52000045776367</v>
       </c>
       <c r="E7" t="n">
         <v>56.7400016784668</v>
@@ -2331,67 +2331,67 @@
         <v>56.47000122070312</v>
       </c>
       <c r="H7" t="n">
-        <v>1426400</v>
+        <v>1787400</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02531419307163585</v>
+        <v>-0.03072622833520955</v>
       </c>
       <c r="J7" t="n">
-        <v>57.7966668870714</v>
+        <v>57.76222229003906</v>
       </c>
       <c r="K7" t="n">
         <v>-1</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.402730921939435</v>
+        <v>-3.881813654981304</v>
       </c>
       <c r="M7" t="n">
-        <v>58.03600006103515</v>
+        <v>58.00499992370605</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.801085925391941</v>
+        <v>-4.284112523421943</v>
       </c>
       <c r="P7" t="n">
-        <v>61.64230830852802</v>
+        <v>61.63038517878606</v>
       </c>
       <c r="Q7" t="n">
         <v>-1</v>
       </c>
       <c r="R7" t="n">
-        <v>-9.429086348262562</v>
+        <v>-9.914565199124628</v>
       </c>
       <c r="S7" t="n">
-        <v>64.40020004272461</v>
+        <v>64.39400001525878</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-13.30771986109398</v>
+        <v>-13.78078633939859</v>
       </c>
       <c r="V7" t="n">
-        <v>58.86759633382162</v>
+        <v>58.86552965799967</v>
       </c>
       <c r="W7" t="n">
         <v>-1</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.16004507053691</v>
+        <v>-5.683341710629375</v>
       </c>
       <c r="Y7" t="n">
-        <v>54.31653085708618</v>
+        <v>54.31498085021973</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.786391085893625</v>
+        <v>2.218576880045187</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3051329942349409</v>
+        <v>0.3082851837732157</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       <c r="BX7" t="inlineStr"/>
       <c r="BY7" t="inlineStr"/>
       <c r="BZ7" t="n">
-        <v>17.07</v>
+        <v>16.98</v>
       </c>
       <c r="CA7" t="n">
         <v>0.28</v>
@@ -2584,13 +2584,13 @@
         <v>2</v>
       </c>
       <c r="CM7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.52000045776367</v>
+        <v>17.3799991607666</v>
       </c>
       <c r="D8" t="n">
-        <v>17.52000045776367</v>
+        <v>17.3799991607666</v>
       </c>
       <c r="E8" t="n">
         <v>18.63999938964844</v>
@@ -2618,67 +2618,67 @@
         <v>18.63999938964844</v>
       </c>
       <c r="H8" t="n">
-        <v>3412400</v>
+        <v>4221700</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07740912749194495</v>
+        <v>-0.08478149709091665</v>
       </c>
       <c r="J8" t="n">
-        <v>19.68999989827474</v>
+        <v>19.6744441986084</v>
       </c>
       <c r="K8" t="n">
         <v>-1</v>
       </c>
       <c r="L8" t="n">
-        <v>-11.02081996811592</v>
+        <v>-11.66205771649746</v>
       </c>
       <c r="M8" t="n">
-        <v>19.71599998474121</v>
+        <v>19.7019998550415</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>-11.13815950840478</v>
+        <v>-11.78560913287556</v>
       </c>
       <c r="P8" t="n">
-        <v>20.179230763362</v>
+        <v>20.17384609809289</v>
       </c>
       <c r="Q8" t="n">
         <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>-13.17805587726618</v>
+        <v>-13.84885620590909</v>
       </c>
       <c r="S8" t="n">
-        <v>21.80820003509521</v>
+        <v>21.80540000915527</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-19.66324396525475</v>
+        <v>-20.29497668710783</v>
       </c>
       <c r="V8" t="n">
-        <v>24.91346669514974</v>
+        <v>24.91253335316976</v>
       </c>
       <c r="W8" t="n">
         <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-29.67658547024072</v>
+        <v>-30.235922158614</v>
       </c>
       <c r="Y8" t="n">
-        <v>26.3054000377655</v>
+        <v>26.30470003128052</v>
       </c>
       <c r="Z8" t="n">
         <v>-1</v>
       </c>
       <c r="AA8" t="n">
-        <v>-33.39770376952648</v>
+        <v>-33.92816059449837</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4986577671056154</v>
+        <v>0.5080876140303167</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2830,10 +2830,10 @@
       <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="CB8" t="n">
         <v>0.45</v>
@@ -2845,7 +2845,7 @@
         <v>4</v>
       </c>
       <c r="CE8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CF8" t="n">
         <v>10</v>
@@ -2870,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="CN8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO8" t="n">
         <v>12</v>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.51000022888184</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="D9" t="n">
-        <v>15.51000022888184</v>
+        <v>15.52000045776367</v>
       </c>
       <c r="E9" t="n">
         <v>16.15999984741211</v>
@@ -2901,67 +2901,67 @@
         <v>15.85999965667725</v>
       </c>
       <c r="H9" t="n">
-        <v>32987900</v>
+        <v>41223100</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04729732342058823</v>
+        <v>-0.04668305877316481</v>
       </c>
       <c r="J9" t="n">
-        <v>16.48666678534614</v>
+        <v>16.48777792188856</v>
       </c>
       <c r="K9" t="n">
         <v>-1</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.923978261830303</v>
+        <v>-5.869665813730469</v>
       </c>
       <c r="M9" t="n">
-        <v>16.54000015258789</v>
+        <v>16.54100017547607</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.227327171728579</v>
+        <v>-6.17253918675457</v>
       </c>
       <c r="P9" t="n">
-        <v>17.09038481345544</v>
+        <v>17.0907694376432</v>
       </c>
       <c r="Q9" t="n">
         <v>-1</v>
       </c>
       <c r="R9" t="n">
-        <v>-9.247214745740234</v>
+        <v>-9.190744662553543</v>
       </c>
       <c r="S9" t="n">
-        <v>17.82840009689331</v>
+        <v>17.82860010147095</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-13.0039703810297</v>
+        <v>-12.9488553816225</v>
       </c>
       <c r="V9" t="n">
-        <v>16.10013341903687</v>
+        <v>16.10020008722941</v>
       </c>
       <c r="W9" t="n">
         <v>-1</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.665393166601051</v>
+        <v>-3.603679620888375</v>
       </c>
       <c r="Y9" t="n">
-        <v>15.30455006122589</v>
+        <v>15.3046000623703</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.342412333809496</v>
+        <v>1.407422569133191</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3679006714156236</v>
+        <v>0.3673186279372122</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -3113,13 +3113,13 @@
       <c r="BX9" t="inlineStr"/>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="n">
-        <v>15.83</v>
+        <v>15.84</v>
       </c>
       <c r="CA9" t="n">
         <v>-0.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="CC9" t="n">
         <v>4</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.57999992370605</v>
+        <v>19.53000068664551</v>
       </c>
       <c r="D10" t="n">
-        <v>19.57999992370605</v>
+        <v>19.53000068664551</v>
       </c>
       <c r="E10" t="n">
         <v>19.8700008392334</v>
@@ -3188,67 +3188,67 @@
         <v>19.77000045776367</v>
       </c>
       <c r="H10" t="n">
-        <v>23900400</v>
+        <v>26784700</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01558569509578367</v>
+        <v>-0.01809948285821905</v>
       </c>
       <c r="J10" t="n">
-        <v>20.58111106024848</v>
+        <v>20.57555558946397</v>
       </c>
       <c r="K10" t="n">
         <v>-1</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.864222993655718</v>
+        <v>-5.081539102418496</v>
       </c>
       <c r="M10" t="n">
-        <v>20.60499992370605</v>
+        <v>20.6</v>
       </c>
       <c r="N10" t="n">
         <v>-1</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.974520765810516</v>
+        <v>-5.19417142405094</v>
       </c>
       <c r="P10" t="n">
-        <v>21.089615381681</v>
+        <v>21.08769233410175</v>
       </c>
       <c r="Q10" t="n">
         <v>-1</v>
       </c>
       <c r="R10" t="n">
-        <v>-7.158098574363953</v>
+        <v>-7.386733563715913</v>
       </c>
       <c r="S10" t="n">
-        <v>22.35699993133545</v>
+        <v>22.35599994659424</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-12.42116570272546</v>
+        <v>-12.64089849123143</v>
       </c>
       <c r="V10" t="n">
-        <v>22.92459997812907</v>
+        <v>22.924266649882</v>
       </c>
       <c r="W10" t="n">
         <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.58956779012017</v>
+        <v>-14.80643204459482</v>
       </c>
       <c r="Y10" t="n">
-        <v>22.47570000648498</v>
+        <v>22.47545001029968</v>
       </c>
       <c r="Z10" t="n">
         <v>-1</v>
       </c>
       <c r="AA10" t="n">
-        <v>-12.88369252990307</v>
+        <v>-13.1051850899732</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2562515659379511</v>
+        <v>0.2570839914558147</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>19842000000</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.8</v>
+        <v>7.78</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
@@ -3472,82 +3472,82 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.14999961853027</v>
+        <v>15.10999965667725</v>
       </c>
       <c r="D11" t="n">
-        <v>15.14999961853027</v>
+        <v>15.10999965667725</v>
       </c>
       <c r="E11" t="n">
         <v>15.34000015258789</v>
       </c>
       <c r="F11" t="n">
-        <v>15.11999988555908</v>
+        <v>15.10999965667725</v>
       </c>
       <c r="G11" t="n">
         <v>15.25</v>
       </c>
       <c r="H11" t="n">
-        <v>3618000</v>
+        <v>5022100</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01814651206141493</v>
+        <v>-0.02073886209783127</v>
       </c>
       <c r="J11" t="n">
-        <v>15.47111119164361</v>
+        <v>15.46666675143772</v>
       </c>
       <c r="K11" t="n">
         <v>-1</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.07555597743216</v>
+        <v>-2.306037237967366</v>
       </c>
       <c r="M11" t="n">
-        <v>15.48100004196167</v>
+        <v>15.47700004577637</v>
       </c>
       <c r="N11" t="n">
         <v>-1</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.138107502966285</v>
+        <v>-2.371263087249749</v>
       </c>
       <c r="P11" t="n">
-        <v>15.78423081911527</v>
+        <v>15.782692359044</v>
       </c>
       <c r="Q11" t="n">
         <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.018131816831532</v>
+        <v>-4.262217668972565</v>
       </c>
       <c r="S11" t="n">
-        <v>16.44999996185303</v>
+        <v>16.44919996261597</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-7.902737667704615</v>
+        <v>-8.141431248828617</v>
       </c>
       <c r="V11" t="n">
-        <v>16.62513332366943</v>
+        <v>16.62486665725708</v>
       </c>
       <c r="W11" t="n">
         <v>-1</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.872913536512772</v>
+        <v>-9.112055042670459</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.10950000286102</v>
+        <v>16.10930000305176</v>
       </c>
       <c r="Z11" t="n">
         <v>-1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-5.956115237346554</v>
+        <v>-6.203251203871075</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2148974326895715</v>
+        <v>0.21632345651</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.76</v>
+        <v>6.75</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CM11" t="n">
         <v>7</v>
@@ -3762,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="CO11" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.3799991607666</v>
+        <v>17.3700008392334</v>
       </c>
       <c r="D12" t="n">
-        <v>17.3799991607666</v>
+        <v>17.3700008392334</v>
       </c>
       <c r="E12" t="n">
         <v>17.6200008392334</v>
@@ -3790,67 +3790,67 @@
         <v>17.51000022888184</v>
       </c>
       <c r="H12" t="n">
-        <v>24286100</v>
+        <v>30092300</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02084511770329001</v>
+        <v>-0.0214084034234705</v>
       </c>
       <c r="J12" t="n">
-        <v>17.75111113654243</v>
+        <v>17.75000021192763</v>
       </c>
       <c r="K12" t="n">
         <v>-1</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.090640821981304</v>
+        <v>-2.140841510744757</v>
       </c>
       <c r="M12" t="n">
-        <v>17.76599998474121</v>
+        <v>17.76500015258789</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.172694046527837</v>
+        <v>-2.223469237048962</v>
       </c>
       <c r="P12" t="n">
-        <v>18.16461541102483</v>
+        <v>18.16423086019663</v>
       </c>
       <c r="Q12" t="n">
         <v>-1</v>
       </c>
       <c r="R12" t="n">
-        <v>-4.319476259222146</v>
+        <v>-4.372494641122572</v>
       </c>
       <c r="S12" t="n">
-        <v>18.95620006561279</v>
+        <v>18.95600009918213</v>
       </c>
       <c r="T12" t="n">
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.314962383761056</v>
+        <v>-8.366740091002432</v>
       </c>
       <c r="V12" t="n">
-        <v>19.29346665700277</v>
+        <v>19.29340000152588</v>
       </c>
       <c r="W12" t="n">
         <v>-1</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.917696649615078</v>
+        <v>-9.969207926754029</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.72380000114441</v>
+        <v>18.72375000953674</v>
       </c>
       <c r="Z12" t="n">
         <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>-7.176966429334176</v>
+        <v>-7.230117736104293</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2556799064428381</v>
+        <v>0.2559651679509053</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>22961600000</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.76</v>
+        <v>7.75</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35.0099983215332</v>
+        <v>35.04000091552734</v>
       </c>
       <c r="D13" t="n">
-        <v>35.0099983215332</v>
+        <v>35.04000091552734</v>
       </c>
       <c r="E13" t="n">
         <v>35.11000061035156</v>
@@ -4089,67 +4089,67 @@
         <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>4222500</v>
+        <v>5341800</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.003415961939464585</v>
+        <v>-0.00256191716058829</v>
       </c>
       <c r="J13" t="n">
-        <v>34.86888927883572</v>
+        <v>34.87222290039062</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4046846504603978</v>
+        <v>0.481122226179735</v>
       </c>
       <c r="M13" t="n">
-        <v>34.85600051879883</v>
+        <v>34.85900077819824</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4418114541033421</v>
+        <v>0.5192350133062404</v>
       </c>
       <c r="P13" t="n">
-        <v>34.46384620666504</v>
+        <v>34.46500015258789</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.584710283330311</v>
+        <v>1.668361411268637</v>
       </c>
       <c r="S13" t="n">
-        <v>34.74</v>
+        <v>34.74060005187988</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7771972410282127</v>
+        <v>0.8618183428045368</v>
       </c>
       <c r="V13" t="n">
-        <v>34.88673337300619</v>
+        <v>34.88693339029948</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3533290067862669</v>
+        <v>0.4387531673116978</v>
       </c>
       <c r="Y13" t="n">
-        <v>34.30049996376037</v>
+        <v>34.30064997673035</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.068478181141496</v>
+        <v>2.155501249389074</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1651600610200799</v>
+        <v>0.1650342326619707</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
       <c r="BX13" t="inlineStr"/>
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
@@ -4354,13 +4354,13 @@
         <v>10</v>
       </c>
       <c r="CM13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN13" t="n">
         <v>1</v>
       </c>
       <c r="CO13" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.609999895095825</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="D14" t="n">
-        <v>3.609999895095825</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="E14" t="n">
         <v>3.789999961853027</v>
@@ -4388,67 +4388,67 @@
         <v>3.609999895095825</v>
       </c>
       <c r="H14" t="n">
-        <v>28040200</v>
+        <v>30322000</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03142854145595009</v>
+        <v>0.02285712105887283</v>
       </c>
       <c r="J14" t="n">
-        <v>3.744444449742635</v>
+        <v>3.741111119588216</v>
       </c>
       <c r="K14" t="n">
         <v>-1</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.59050738904808</v>
+        <v>-4.306506562678499</v>
       </c>
       <c r="M14" t="n">
-        <v>3.773000025749206</v>
+        <v>3.770000028610229</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.320173059659979</v>
+        <v>-5.039790542766021</v>
       </c>
       <c r="P14" t="n">
-        <v>3.978461559002216</v>
+        <v>3.977307713948763</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
       </c>
       <c r="R14" t="n">
-        <v>-9.261410684556157</v>
+        <v>-9.989365138868077</v>
       </c>
       <c r="S14" t="n">
-        <v>4.059600019454956</v>
+        <v>4.059000020027161</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-11.07498576718144</v>
+        <v>-11.80093850597962</v>
       </c>
       <c r="V14" t="n">
-        <v>5.225933341979981</v>
+        <v>5.225733342170716</v>
       </c>
       <c r="W14" t="n">
         <v>-1</v>
       </c>
       <c r="X14" t="n">
-        <v>-30.92143242439287</v>
+        <v>-31.49287020031987</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.485550000667572</v>
+        <v>5.485400000810623</v>
       </c>
       <c r="Z14" t="n">
         <v>-1</v>
       </c>
       <c r="AA14" t="n">
-        <v>-34.19073940340529</v>
+        <v>-34.73584564157566</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5531558163557808</v>
+        <v>0.5489424039140703</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -4600,13 +4600,13 @@
       <c r="BX14" t="inlineStr"/>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CC14" t="n">
         <v>8</v>
@@ -4641,13 +4641,13 @@
         <v>4</v>
       </c>
       <c r="CM14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN14" t="n">
         <v>-1</v>
       </c>
       <c r="CO14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>50.75</v>
+        <v>50.70999908447266</v>
       </c>
       <c r="D15" t="n">
-        <v>50.75</v>
+        <v>50.70999908447266</v>
       </c>
       <c r="E15" t="n">
         <v>52.84000015258789</v>
@@ -4675,67 +4675,67 @@
         <v>52.65000152587891</v>
       </c>
       <c r="H15" t="n">
-        <v>12567300</v>
+        <v>14857700</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04694835680751175</v>
+        <v>-0.04769954770943363</v>
       </c>
       <c r="J15" t="n">
-        <v>53.902222527398</v>
+        <v>53.8977779812283</v>
       </c>
       <c r="K15" t="n">
         <v>-1</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.848038132000507</v>
+        <v>-5.914490385607169</v>
       </c>
       <c r="M15" t="n">
-        <v>53.94900016784668</v>
+        <v>53.94500007629394</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.929674614717446</v>
+        <v>-5.99685047223293</v>
       </c>
       <c r="P15" t="n">
-        <v>55.72038474449744</v>
+        <v>55.71884624774639</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>-8.920226892346225</v>
+        <v>-8.989502655892347</v>
       </c>
       <c r="S15" t="n">
-        <v>57.62519981384278</v>
+        <v>57.62439979553223</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-11.93089106164142</v>
+        <v>-11.99908499801097</v>
       </c>
       <c r="V15" t="n">
-        <v>55.98513320922851</v>
+        <v>55.98486653645833</v>
       </c>
       <c r="W15" t="n">
         <v>-1</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.35093463056289</v>
+        <v>-9.421952356625859</v>
       </c>
       <c r="Y15" t="n">
-        <v>53.49089994430542</v>
+        <v>53.49069993972778</v>
       </c>
       <c r="Z15" t="n">
         <v>-1</v>
       </c>
       <c r="AA15" t="n">
-        <v>-5.124049038545316</v>
+        <v>-5.198475358124615</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.3064801504717059</v>
+        <v>0.3073250256431093</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.72999954223633</v>
+        <v>22.78000068664551</v>
       </c>
       <c r="D16" t="n">
-        <v>22.72999954223633</v>
+        <v>22.78000068664551</v>
       </c>
       <c r="E16" t="n">
         <v>23.28000068664551</v>
@@ -4982,67 +4982,67 @@
         <v>23.15999984741211</v>
       </c>
       <c r="H16" t="n">
-        <v>1532500</v>
+        <v>2005800</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.03727238650427678</v>
+        <v>-0.03515459137015653</v>
       </c>
       <c r="J16" t="n">
-        <v>23.171111424764</v>
+        <v>23.17666710747613</v>
       </c>
       <c r="K16" t="n">
         <v>-1</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.903714821621514</v>
+        <v>-1.7114903492861</v>
       </c>
       <c r="M16" t="n">
-        <v>23.1620002746582</v>
+        <v>23.16700038909912</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.865127049905673</v>
+        <v>-1.670478249034396</v>
       </c>
       <c r="P16" t="n">
-        <v>23.01153857891376</v>
+        <v>23.01346169985258</v>
       </c>
       <c r="Q16" t="n">
         <v>-1</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.223468981493557</v>
+        <v>-1.014454132333185</v>
       </c>
       <c r="S16" t="n">
-        <v>23.3903999710083</v>
+        <v>23.39139999389648</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.823382368794541</v>
+        <v>-2.61377817236467</v>
       </c>
       <c r="V16" t="n">
-        <v>22.07653330485026</v>
+        <v>22.07686664581299</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>2.960003857319837</v>
+        <v>3.184935852144007</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.75139995574951</v>
+        <v>20.75164996147156</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.534776404030575</v>
+        <v>9.77440699385291</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2806202061212513</v>
+        <v>0.2784480522386233</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -5198,7 +5198,7 @@
       <c r="BX16" t="inlineStr"/>
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="n">
-        <v>11.42</v>
+        <v>11.45</v>
       </c>
       <c r="CA16" t="n">
         <v>-0.03</v>
@@ -5239,13 +5239,13 @@
         <v>9</v>
       </c>
       <c r="CM16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CN16" t="n">
         <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.86000061035156</v>
+        <v>20.75</v>
       </c>
       <c r="D17" t="n">
-        <v>20.86000061035156</v>
+        <v>20.75</v>
       </c>
       <c r="E17" t="n">
         <v>21.04000091552734</v>
@@ -5273,88 +5273,88 @@
         <v>20.45999908447266</v>
       </c>
       <c r="H17" t="n">
-        <v>6910500</v>
+        <v>7648700</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01409824598102993</v>
+        <v>0.008750622646876982</v>
       </c>
       <c r="J17" t="n">
-        <v>20.26444456312392</v>
+        <v>20.25222227308485</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>2.938921150157774</v>
+        <v>2.457891880718153</v>
       </c>
       <c r="M17" t="n">
-        <v>20.25300006866455</v>
+        <v>20.24200000762939</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.997089515770863</v>
+        <v>2.509633396794472</v>
       </c>
       <c r="P17" t="n">
-        <v>19.14346159421481</v>
+        <v>19.13923080150898</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>8.966711729165526</v>
+        <v>8.416060264888115</v>
       </c>
       <c r="S17" t="n">
-        <v>19.62919998168945</v>
+        <v>19.62699996948242</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>6.270253651754667</v>
+        <v>5.721710053822308</v>
       </c>
       <c r="V17" t="n">
-        <v>17.48586663564046</v>
+        <v>17.48513329823812</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>19.29634970355882</v>
+        <v>18.67224370597658</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.63059996128082</v>
+        <v>17.63004995822907</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>18.31702072625401</v>
+        <v>17.6967736856279</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3358529569562365</v>
+        <v>0.3343896634001115</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AE17" t="n">
         <v>20</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AF17" t="n">
         <v>20.7</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
         <v>20.8</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
         <v>27.1</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
         <v>27.9</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>29.2</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
@@ -5481,13 +5481,13 @@
       <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr"/>
       <c r="BZ17" t="n">
-        <v>41.72</v>
+        <v>41.5</v>
       </c>
       <c r="CA17" t="n">
         <v>1.1</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="CC17" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.449999809265137</v>
+        <v>9.430000305175781</v>
       </c>
       <c r="D18" t="n">
-        <v>9.449999809265137</v>
+        <v>9.430000305175781</v>
       </c>
       <c r="E18" t="n">
         <v>10.03999996185303</v>
@@ -5552,67 +5552,67 @@
         <v>9.699999809265137</v>
       </c>
       <c r="H18" t="n">
-        <v>7920200</v>
+        <v>8420400</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05594409658462651</v>
+        <v>-0.05794204899542177</v>
       </c>
       <c r="J18" t="n">
-        <v>10.96111106872559</v>
+        <v>10.95888890160455</v>
       </c>
       <c r="K18" t="n">
         <v>-1</v>
       </c>
       <c r="L18" t="n">
-        <v>-13.78611392573127</v>
+        <v>-13.95112780279132</v>
       </c>
       <c r="M18" t="n">
-        <v>11.06799993515015</v>
+        <v>11.06599998474121</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-14.61872185910037</v>
+        <v>-14.78402025864171</v>
       </c>
       <c r="P18" t="n">
-        <v>10.68807686292208</v>
+        <v>10.68730765122634</v>
       </c>
       <c r="Q18" t="n">
         <v>-1</v>
       </c>
       <c r="R18" t="n">
-        <v>-11.58372146397962</v>
+        <v>-11.76449099326044</v>
       </c>
       <c r="S18" t="n">
-        <v>10.02719993591309</v>
+        <v>10.0267999458313</v>
       </c>
       <c r="T18" t="n">
         <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.756344047560753</v>
+        <v>-5.952044958308358</v>
       </c>
       <c r="V18" t="n">
-        <v>9.149999984105428</v>
+        <v>9.149866654078165</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>3.278686619462758</v>
+        <v>3.061614575254584</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.838949983119965</v>
+        <v>8.838849985599518</v>
       </c>
       <c r="Z18" t="n">
         <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.913149495269385</v>
+        <v>6.688090877652414</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9997228469492395</v>
+        <v>1.000769756623286</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>-0.82</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="CB18" t="n">
         <v>-0.48</v>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10.85999965667725</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="D19" t="n">
-        <v>10.85999965667725</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="E19" t="n">
         <v>11.1899995803833</v>
@@ -5835,86 +5835,88 @@
         <v>11.18000030517578</v>
       </c>
       <c r="H19" t="n">
-        <v>7505600</v>
+        <v>8516500</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.05235605405519206</v>
+        <v>-0.04450263762514794</v>
       </c>
       <c r="J19" t="n">
-        <v>11.39444425370958</v>
+        <v>11.40444427066379</v>
       </c>
       <c r="K19" t="n">
         <v>-1</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.690396346959538</v>
+        <v>-3.984801456460659</v>
       </c>
       <c r="M19" t="n">
-        <v>11.37199983596802</v>
+        <v>11.38099985122681</v>
       </c>
       <c r="N19" t="n">
         <v>-1</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.502287958810792</v>
+        <v>-3.787013861661823</v>
       </c>
       <c r="P19" t="n">
-        <v>11.30807682184073</v>
+        <v>11.31153836617103</v>
       </c>
       <c r="Q19" t="n">
         <v>-1</v>
       </c>
       <c r="R19" t="n">
-        <v>-3.962452433096778</v>
+        <v>-3.196192641552031</v>
       </c>
       <c r="S19" t="n">
-        <v>11.83499992370606</v>
+        <v>11.83679992675781</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-8.238278608484302</v>
+        <v>-7.491890738881292</v>
       </c>
       <c r="V19" t="n">
-        <v>12.99946663538615</v>
+        <v>13.0000666364034</v>
       </c>
       <c r="W19" t="n">
         <v>-1</v>
       </c>
       <c r="X19" t="n">
-        <v>-16.45811354202033</v>
+        <v>-15.76966399077964</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.89609996795654</v>
+        <v>13.89654996871948</v>
       </c>
       <c r="Z19" t="n">
         <v>-1</v>
       </c>
       <c r="AA19" t="n">
-        <v>-21.84857850965621</v>
+        <v>-21.20346536433071</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.6100334837531014</v>
+        <v>0.6051649241675121</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AH19" t="n">
         <v>20.9</v>
       </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
       <c r="AI19" t="inlineStr">
         <is>
           <t>Foguete</t>
@@ -5924,7 +5926,7 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -6045,13 +6047,13 @@
       <c r="BX19" t="inlineStr"/>
       <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
-        <v>5.72</v>
+        <v>5.76</v>
       </c>
       <c r="CA19" t="n">
         <v>0.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="CC19" t="n">
         <v>6</v>
@@ -6083,16 +6085,16 @@
         <v>1</v>
       </c>
       <c r="CL19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN19" t="n">
         <v>-1</v>
       </c>
       <c r="CO19" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6105,10 +6107,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10.81999969482422</v>
+        <v>10.85999965667725</v>
       </c>
       <c r="D20" t="n">
-        <v>10.81999969482422</v>
+        <v>10.85999965667725</v>
       </c>
       <c r="E20" t="n">
         <v>11.05000019073486</v>
@@ -6120,67 +6122,67 @@
         <v>10.89999961853027</v>
       </c>
       <c r="H20" t="n">
-        <v>12353600</v>
+        <v>14765200</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.01636366410688916</v>
+        <v>-0.01272730393843213</v>
       </c>
       <c r="J20" t="n">
-        <v>11.03222232394748</v>
+        <v>11.03666676415337</v>
       </c>
       <c r="K20" t="n">
         <v>-1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.923661642157045</v>
+        <v>-1.600728836444849</v>
       </c>
       <c r="M20" t="n">
-        <v>11.06500005722046</v>
+        <v>11.06900005340576</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.214192147575864</v>
+        <v>-1.888159686693742</v>
       </c>
       <c r="P20" t="n">
-        <v>11.51730779501108</v>
+        <v>11.51884625508235</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-6.0544366148564</v>
+        <v>-5.719727339137001</v>
       </c>
       <c r="S20" t="n">
-        <v>12.25100011825561</v>
+        <v>12.25180011749268</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-11.68068247178461</v>
+        <v>-11.3599670862102</v>
       </c>
       <c r="V20" t="n">
-        <v>11.70106670379639</v>
+        <v>11.70133337020874</v>
       </c>
       <c r="W20" t="n">
         <v>-1</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.529800754715023</v>
+        <v>-7.19006703691996</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.51490003108978</v>
+        <v>11.51510003089905</v>
       </c>
       <c r="Z20" t="n">
         <v>-1</v>
       </c>
       <c r="AA20" t="n">
-        <v>-6.034792611219894</v>
+        <v>-5.689055001380251</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2337312356354988</v>
+        <v>0.2328096656809364</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -6328,13 +6330,13 @@
       <c r="BX20" t="inlineStr"/>
       <c r="BY20" t="inlineStr"/>
       <c r="BZ20" t="n">
-        <v>6.4</v>
+        <v>6.43</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="CB20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CC20" t="n">
         <v>5</v>
@@ -6388,10 +6390,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.489999771118164</v>
+        <v>4.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4.489999771118164</v>
+        <v>4.5</v>
       </c>
       <c r="E21" t="n">
         <v>4.75</v>
@@ -6403,67 +6405,67 @@
         <v>4.710000038146973</v>
       </c>
       <c r="H21" t="n">
-        <v>9918300</v>
+        <v>10611100</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.06066954518016909</v>
+        <v>-0.05857744717956315</v>
       </c>
       <c r="J21" t="n">
-        <v>4.586666636996799</v>
+        <v>4.587777773539226</v>
       </c>
       <c r="K21" t="n">
         <v>-1</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.107562496452319</v>
+        <v>-1.913296107006283</v>
       </c>
       <c r="M21" t="n">
-        <v>4.570999956130981</v>
+        <v>4.571999979019165</v>
       </c>
       <c r="N21" t="n">
         <v>-1</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.772045193397416</v>
+        <v>-1.574802697934645</v>
       </c>
       <c r="P21" t="n">
-        <v>4.624230751624475</v>
+        <v>4.624615375812237</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.902774271356498</v>
+        <v>-2.694610593218256</v>
       </c>
       <c r="S21" t="n">
-        <v>4.776799993515015</v>
+        <v>4.776999998092651</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.004024091153298</v>
+        <v>-5.79861834212374</v>
       </c>
       <c r="V21" t="n">
-        <v>5.308333333333334</v>
+        <v>5.308400001525879</v>
       </c>
       <c r="W21" t="n">
         <v>-1</v>
       </c>
       <c r="X21" t="n">
-        <v>-15.41601687061544</v>
+        <v>-15.22869416949565</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.304150011539459</v>
+        <v>5.304200012683868</v>
       </c>
       <c r="Z21" t="n">
         <v>-1</v>
       </c>
       <c r="AA21" t="n">
-        <v>-15.34930646097995</v>
+        <v>-15.16157027941621</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5623546556778937</v>
+        <v>0.560527803750496</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -6615,13 +6617,13 @@
       <c r="BX21" t="inlineStr"/>
       <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
-        <v>10.95</v>
+        <v>10.98</v>
       </c>
       <c r="CA21" t="n">
         <v>0.01</v>
       </c>
       <c r="CB21" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CC21" t="n">
         <v>3</v>
@@ -6675,10 +6677,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.400000095367432</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="D22" t="n">
-        <v>2.400000095367432</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="E22" t="n">
         <v>2.460000038146973</v>
@@ -6690,88 +6692,88 @@
         <v>2.460000038146973</v>
       </c>
       <c r="H22" t="n">
-        <v>23165200</v>
+        <v>27278500</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0361445437046628</v>
+        <v>-0.04016060411629196</v>
       </c>
       <c r="J22" t="n">
-        <v>2.496666669845581</v>
+        <v>2.495555559794108</v>
       </c>
       <c r="K22" t="n">
         <v>-1</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.871825408080136</v>
+        <v>-4.229737722154414</v>
       </c>
       <c r="M22" t="n">
-        <v>2.498000001907349</v>
+        <v>2.497000002861023</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.923134766416702</v>
+        <v>-4.285138079064849</v>
       </c>
       <c r="P22" t="n">
-        <v>2.605384615751413</v>
+        <v>2.605000000733596</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-7.883078726353314</v>
+        <v>-8.253354923949127</v>
       </c>
       <c r="S22" t="n">
-        <v>2.856600008010864</v>
+        <v>2.856400008201599</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-15.98403386413825</v>
+        <v>-16.32824191143563</v>
       </c>
       <c r="V22" t="n">
-        <v>3.275702905654907</v>
+        <v>3.275636239051819</v>
       </c>
       <c r="W22" t="n">
         <v>-1</v>
       </c>
       <c r="X22" t="n">
-        <v>-26.73327940625304</v>
+        <v>-27.03707217514496</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.149686169624329</v>
+        <v>3.149636169672013</v>
       </c>
       <c r="Z22" t="n">
         <v>-1</v>
       </c>
       <c r="AA22" t="n">
-        <v>-23.80192926796622</v>
+        <v>-24.11821632232978</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4314653440705368</v>
+        <v>0.4337152198084168</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
         <v>2.3</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
         <v>2.4</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
         <v>2.5</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.8</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
@@ -6898,7 +6900,7 @@
       <c r="BX22" t="inlineStr"/>
       <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
-        <v>7.27</v>
+        <v>7.24</v>
       </c>
       <c r="CA22" t="n">
         <v>1.08</v>
@@ -6958,13 +6960,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.2400016784668</v>
+        <v>43.29999923706055</v>
       </c>
       <c r="D23" t="n">
-        <v>43.2400016784668</v>
+        <v>43.29999923706055</v>
       </c>
       <c r="E23" t="n">
-        <v>43.34000015258789</v>
+        <v>43.40000152587891</v>
       </c>
       <c r="F23" t="n">
         <v>42.52999877929688</v>
@@ -6973,67 +6975,67 @@
         <v>43.2599983215332</v>
       </c>
       <c r="H23" t="n">
-        <v>1724100</v>
+        <v>2132100</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.005976972908809275</v>
+        <v>-0.004597718688263308</v>
       </c>
       <c r="J23" t="n">
-        <v>43.37666659884982</v>
+        <v>43.38333299424913</v>
       </c>
       <c r="K23" t="n">
         <v>-1</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3150655204718985</v>
+        <v>-0.1920870330539845</v>
       </c>
       <c r="M23" t="n">
-        <v>43.40900001525879</v>
+        <v>43.41499977111816</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3893163554391685</v>
+        <v>-0.2648866397878423</v>
       </c>
       <c r="P23" t="n">
-        <v>45.83269236637996</v>
+        <v>45.83499996478741</v>
       </c>
       <c r="Q23" t="n">
         <v>-1</v>
       </c>
       <c r="R23" t="n">
-        <v>-5.656858792382445</v>
+        <v>-5.530709566214392</v>
       </c>
       <c r="S23" t="n">
-        <v>48.46399978637695</v>
+        <v>48.46519973754883</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.77913117146101</v>
+        <v>-10.65754506008256</v>
       </c>
       <c r="V23" t="n">
-        <v>48.90086667378743</v>
+        <v>48.90126665751139</v>
       </c>
       <c r="W23" t="n">
         <v>-1</v>
       </c>
       <c r="X23" t="n">
-        <v>-11.5762058637604</v>
+        <v>-11.45423790283451</v>
       </c>
       <c r="Y23" t="n">
-        <v>46.38985000610352</v>
+        <v>46.39014999389649</v>
       </c>
       <c r="Z23" t="n">
         <v>-1</v>
       </c>
       <c r="AA23" t="n">
-        <v>-6.78995152435779</v>
+        <v>-6.661221740482641</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2681098646431019</v>
+        <v>0.2682345302846805</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -7185,7 +7187,7 @@
       <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="n">
-        <v>8.65</v>
+        <v>8.66</v>
       </c>
       <c r="CA23" t="n">
         <v>0.52</v>
@@ -7245,10 +7247,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.32999992370605</v>
+        <v>14.40999984741211</v>
       </c>
       <c r="D24" t="n">
-        <v>14.32999992370605</v>
+        <v>14.40999984741211</v>
       </c>
       <c r="E24" t="n">
         <v>14.47999954223633</v>
@@ -7260,67 +7262,67 @@
         <v>14.31999969482422</v>
       </c>
       <c r="H24" t="n">
-        <v>17534000</v>
+        <v>20508800</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.02184298315062494</v>
+        <v>-0.01638223736296873</v>
       </c>
       <c r="J24" t="n">
-        <v>14.60222212473551</v>
+        <v>14.6111110051473</v>
       </c>
       <c r="K24" t="n">
         <v>-1</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.864251883748069</v>
+        <v>-1.376426184595686</v>
       </c>
       <c r="M24" t="n">
-        <v>14.63199987411499</v>
+        <v>14.6399998664856</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.063969061011232</v>
+        <v>-1.57103839597711</v>
       </c>
       <c r="P24" t="n">
-        <v>15.056923022637</v>
+        <v>15.05999994277954</v>
       </c>
       <c r="Q24" t="n">
         <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-4.827833003051618</v>
+        <v>-4.316069706753695</v>
       </c>
       <c r="S24" t="n">
-        <v>15.56279991149902</v>
+        <v>15.56439990997314</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.921453689590131</v>
+        <v>-7.416926249892447</v>
       </c>
       <c r="V24" t="n">
-        <v>14.21033328374227</v>
+        <v>14.21086661656698</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>0.8421100165236346</v>
+        <v>1.401274364316277</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.57114995479584</v>
+        <v>13.57154995441437</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>5.591640881118195</v>
+        <v>6.177996587081218</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.2344021134017141</v>
+        <v>0.2315863731396083</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -7472,13 +7474,13 @@
       <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="n">
-        <v>15.75</v>
+        <v>15.84</v>
       </c>
       <c r="CA24" t="n">
         <v>0.42</v>
       </c>
       <c r="CB24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CC24" t="n">
         <v>3</v>
@@ -7506,16 +7508,16 @@
         <v>0</v>
       </c>
       <c r="CL24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CM24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN24" t="n">
         <v>0</v>
       </c>
       <c r="CO24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
@@ -7528,82 +7530,82 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.609999895095825</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="D25" t="n">
-        <v>3.609999895095825</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="E25" t="n">
         <v>3.799999952316284</v>
       </c>
       <c r="F25" t="n">
-        <v>3.589999914169312</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="G25" t="n">
         <v>3.799999952316284</v>
       </c>
       <c r="H25" t="n">
-        <v>60025500</v>
+        <v>66516200</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0695876833457254</v>
+        <v>-0.07731963450678692</v>
       </c>
       <c r="J25" t="n">
-        <v>4.00888893339369</v>
+        <v>4.005555603239271</v>
       </c>
       <c r="K25" t="n">
         <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>-9.950114481225821</v>
+        <v>-10.62413611707379</v>
       </c>
       <c r="M25" t="n">
-        <v>4.048000049591065</v>
+        <v>4.045000052452087</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
       </c>
       <c r="O25" t="n">
-        <v>-10.82016178679363</v>
+        <v>-11.49567670497676</v>
       </c>
       <c r="P25" t="n">
-        <v>4.539615374345046</v>
+        <v>4.538461529291594</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
       </c>
       <c r="R25" t="n">
-        <v>-20.47784674672667</v>
+        <v>-21.11864558947015</v>
       </c>
       <c r="S25" t="n">
-        <v>4.907000007629395</v>
+        <v>4.906400008201599</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-26.4316305383533</v>
+        <v>-27.03407961597745</v>
       </c>
       <c r="V25" t="n">
-        <v>5.519200003941854</v>
+        <v>5.519000004132589</v>
       </c>
       <c r="W25" t="n">
         <v>-1</v>
       </c>
       <c r="X25" t="n">
-        <v>-34.59197179813132</v>
+        <v>-35.1331777310133</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.709149992465973</v>
+        <v>5.708999992609024</v>
       </c>
       <c r="Z25" t="n">
         <v>-1</v>
       </c>
       <c r="AA25" t="n">
-        <v>-36.76817214717202</v>
+        <v>-37.29199635066057</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.4969837443742346</v>
+        <v>0.5051746227412829</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -7618,21 +7620,21 @@
           <t>Abismo</t>
         </is>
       </c>
-      <c r="AF25" t="n">
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Abismo</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>3.6</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>4.9</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>5</v>
       </c>
-      <c r="AI25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1</v>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="n">
         <v>-1</v>
       </c>
@@ -7755,13 +7757,13 @@
       <c r="BX25" t="inlineStr"/>
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="n">
-        <v>-1.5</v>
+        <v>-1.49</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CC25" t="n">
         <v>5</v>
@@ -7799,7 +7801,7 @@
         <v>1</v>
       </c>
       <c r="CN25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO25" t="n">
         <v>27</v>
@@ -7815,13 +7817,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>52.97999954223633</v>
+        <v>60</v>
       </c>
       <c r="D26" t="n">
-        <v>52.97999954223633</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>54.15999984741211</v>
+        <v>60</v>
       </c>
       <c r="F26" t="n">
         <v>52.29999923706055</v>
@@ -7830,67 +7832,67 @@
         <v>52.68999862670898</v>
       </c>
       <c r="H26" t="n">
-        <v>6392800</v>
+        <v>9377400</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001512249793004017</v>
+        <v>0.1342154682291974</v>
       </c>
       <c r="J26" t="n">
-        <v>52.55888875325521</v>
+        <v>53.33888880411784</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.801217070927962</v>
+        <v>12.48828264935267</v>
       </c>
       <c r="M26" t="n">
-        <v>52.41699981689453</v>
+        <v>53.1189998626709</v>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.074078499930353</v>
+        <v>12.95393391275932</v>
       </c>
       <c r="P26" t="n">
-        <v>53.07576913100023</v>
+        <v>53.34576914860652</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.1804393800257977</v>
+        <v>12.47377431724086</v>
       </c>
       <c r="S26" t="n">
-        <v>55.02539993286133</v>
+        <v>55.1657999420166</v>
       </c>
       <c r="T26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.717193138297354</v>
+        <v>8.763038083494669</v>
       </c>
       <c r="V26" t="n">
-        <v>49.27379994710287</v>
+        <v>49.32059995015462</v>
       </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>7.521643549131986</v>
+        <v>21.65302137573024</v>
       </c>
       <c r="Y26" t="n">
-        <v>44.95384993553161</v>
+        <v>44.98894993782044</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>17.85419851295279</v>
+        <v>33.36608230004578</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3309737702943895</v>
+        <v>0.5171645670495625</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -8042,13 +8044,13 @@
       <c r="BX26" t="inlineStr"/>
       <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
-        <v>14.88</v>
+        <v>16.85</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="CC26" t="n">
         <v>6</v>
@@ -8060,7 +8062,7 @@
         <v>6</v>
       </c>
       <c r="CF26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CG26" t="n">
         <v>3</v>
@@ -8069,7 +8071,7 @@
         <v>3</v>
       </c>
       <c r="CI26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CJ26" t="inlineStr">
         <is>
@@ -8080,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="CL26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CM26" t="n">
         <v>10</v>
       </c>
       <c r="CN26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO26" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
@@ -8117,7 +8119,7 @@
         <v>6.980000019073486</v>
       </c>
       <c r="H27" t="n">
-        <v>23735700</v>
+        <v>25238100</v>
       </c>
       <c r="I27" t="n">
         <v>-0.06311364360161453</v>
@@ -8385,10 +8387,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29.46999931335449</v>
+        <v>29.45000076293945</v>
       </c>
       <c r="D28" t="n">
-        <v>29.46999931335449</v>
+        <v>29.45000076293945</v>
       </c>
       <c r="E28" t="n">
         <v>30.97999954223633</v>
@@ -8400,67 +8402,67 @@
         <v>30.97999954223633</v>
       </c>
       <c r="H28" t="n">
-        <v>3713500</v>
+        <v>4025700</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.05936803750019104</v>
+        <v>-0.06000635701706747</v>
       </c>
       <c r="J28" t="n">
-        <v>31.33333333333333</v>
+        <v>31.33111127217611</v>
       </c>
       <c r="K28" t="n">
         <v>-1</v>
       </c>
       <c r="L28" t="n">
-        <v>-5.946810702060128</v>
+        <v>-6.003969961024621</v>
       </c>
       <c r="M28" t="n">
-        <v>31.32000007629394</v>
+        <v>31.31800022125244</v>
       </c>
       <c r="N28" t="n">
         <v>-1</v>
       </c>
       <c r="O28" t="n">
-        <v>-5.906771259364441</v>
+        <v>-5.964619212964179</v>
       </c>
       <c r="P28" t="n">
-        <v>30.65692314734826</v>
+        <v>30.65615397233229</v>
       </c>
       <c r="Q28" t="n">
         <v>-1</v>
       </c>
       <c r="R28" t="n">
-        <v>-3.87163391540952</v>
+        <v>-3.934457044029122</v>
       </c>
       <c r="S28" t="n">
-        <v>32.75059997558593</v>
+        <v>32.75020000457764</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-10.01691775013887</v>
+        <v>-10.07688270965337</v>
       </c>
       <c r="V28" t="n">
-        <v>34.72446657816569</v>
+        <v>34.72433325449626</v>
       </c>
       <c r="W28" t="n">
         <v>-1</v>
       </c>
       <c r="X28" t="n">
-        <v>-15.13188763600804</v>
+        <v>-15.18915410960083</v>
       </c>
       <c r="Y28" t="n">
-        <v>34.26614993095398</v>
+        <v>34.2660499382019</v>
       </c>
       <c r="Z28" t="n">
         <v>-1</v>
       </c>
       <c r="AA28" t="n">
-        <v>-13.99675956377852</v>
+        <v>-14.05487117408657</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.5073615615972338</v>
+        <v>0.5079609649800978</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -8608,7 +8610,7 @@
       <c r="BX28" t="inlineStr"/>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
-        <v>8.52</v>
+        <v>8.51</v>
       </c>
       <c r="CA28" t="n">
         <v>-0.04</v>
@@ -8649,13 +8651,13 @@
         <v>5</v>
       </c>
       <c r="CM28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN28" t="n">
         <v>-1</v>
       </c>
       <c r="CO28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -8668,10 +8670,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17.42000007629395</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="D29" t="n">
-        <v>17.42000007629395</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="E29" t="n">
         <v>17.79999923706055</v>
@@ -8683,67 +8685,67 @@
         <v>17.60000038146973</v>
       </c>
       <c r="H29" t="n">
-        <v>4430200</v>
+        <v>5773800</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01914415248908452</v>
+        <v>-0.01745492465919296</v>
       </c>
       <c r="J29" t="n">
-        <v>17.55111122131348</v>
+        <v>17.55444463094075</v>
       </c>
       <c r="K29" t="n">
         <v>-1</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.7470247516881684</v>
+        <v>-0.5949710754005419</v>
       </c>
       <c r="M29" t="n">
-        <v>17.5730001449585</v>
+        <v>17.57600021362305</v>
       </c>
       <c r="N29" t="n">
         <v>-1</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.8706542275221237</v>
+        <v>-0.7168835295412228</v>
       </c>
       <c r="P29" t="n">
-        <v>17.59807704045222</v>
+        <v>17.59923091301551</v>
       </c>
       <c r="Q29" t="n">
         <v>-1</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.011911493221326</v>
+        <v>-0.8479356331741428</v>
       </c>
       <c r="S29" t="n">
-        <v>18.06240013122559</v>
+        <v>18.0630001449585</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.556559760964907</v>
+        <v>-3.393674235174805</v>
       </c>
       <c r="V29" t="n">
-        <v>17.13813343683879</v>
+        <v>17.13833344141642</v>
       </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.644675252961221</v>
+        <v>1.818539256389178</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.45040009021759</v>
+        <v>16.45055009365082</v>
       </c>
       <c r="Z29" t="n">
         <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>5.894081485914356</v>
+        <v>6.075484792902933</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.2176092679888878</v>
+        <v>0.2165627922840674</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -8903,7 +8905,7 @@
       <c r="BX29" t="inlineStr"/>
       <c r="BY29" t="inlineStr"/>
       <c r="BZ29" t="n">
-        <v>11.93</v>
+        <v>11.95</v>
       </c>
       <c r="CA29" t="n">
         <v>-0.02</v>
@@ -8941,16 +8943,16 @@
         <v>0</v>
       </c>
       <c r="CL29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN29" t="n">
         <v>1</v>
       </c>
       <c r="CO29" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
@@ -8963,10 +8965,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>20.67000007629395</v>
+        <v>20.86000061035156</v>
       </c>
       <c r="D30" t="n">
-        <v>20.67000007629395</v>
+        <v>20.86000061035156</v>
       </c>
       <c r="E30" t="n">
         <v>22</v>
@@ -8978,91 +8980,91 @@
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>8565500</v>
+        <v>9863600</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.07516779760633296</v>
+        <v>-0.06666665528800242</v>
       </c>
       <c r="J30" t="n">
-        <v>22.09111128913032</v>
+        <v>22.11222245958116</v>
       </c>
       <c r="K30" t="n">
         <v>-1</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.432954839784879</v>
+        <v>-5.663030260836649</v>
       </c>
       <c r="M30" t="n">
-        <v>22.09400024414062</v>
+        <v>22.11300029754639</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
       </c>
       <c r="O30" t="n">
-        <v>-6.445189427497748</v>
+        <v>-5.666348619973804</v>
       </c>
       <c r="P30" t="n">
-        <v>22.32307698176457</v>
+        <v>22.33038469461294</v>
       </c>
       <c r="Q30" t="n">
         <v>-1</v>
       </c>
       <c r="R30" t="n">
-        <v>-7.405237668718357</v>
+        <v>-6.584678698419825</v>
       </c>
       <c r="S30" t="n">
-        <v>24.69079998016358</v>
+        <v>24.69459999084473</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-16.28460765588768</v>
+        <v>-15.52808865871406</v>
       </c>
       <c r="V30" t="n">
-        <v>28.49213326772054</v>
+        <v>28.49339993794759</v>
       </c>
       <c r="W30" t="n">
         <v>-1</v>
       </c>
       <c r="X30" t="n">
-        <v>-27.45365928878511</v>
+        <v>-26.79006136235025</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.55714997291565</v>
+        <v>28.55809997558594</v>
       </c>
       <c r="Z30" t="n">
         <v>-1</v>
       </c>
       <c r="AA30" t="n">
-        <v>-27.61882717323712</v>
+        <v>-26.95592273931182</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4435739081996701</v>
+        <v>0.4331859821501012</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AH30" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -9186,13 +9188,13 @@
       <c r="BX30" t="inlineStr"/>
       <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
-        <v>4.77</v>
+        <v>4.82</v>
       </c>
       <c r="CA30" t="n">
         <v>0.52</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="CC30" t="n">
         <v>8</v>
@@ -9242,10 +9244,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12.44999980926514</v>
+        <v>12.43000030517578</v>
       </c>
       <c r="D31" t="n">
-        <v>12.44999980926514</v>
+        <v>12.43000030517578</v>
       </c>
       <c r="E31" t="n">
         <v>13.19999980926514</v>
@@ -9257,67 +9259,67 @@
         <v>13.19999980926514</v>
       </c>
       <c r="H31" t="n">
-        <v>7422200</v>
+        <v>8474900</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.067415771272473</v>
+        <v>-0.06891386142362499</v>
       </c>
       <c r="J31" t="n">
-        <v>13.2266665564643</v>
+        <v>13.22444438934326</v>
       </c>
       <c r="K31" t="n">
         <v>-1</v>
       </c>
       <c r="L31" t="n">
-        <v>-5.871976464240591</v>
+        <v>-6.00739101604656</v>
       </c>
       <c r="M31" t="n">
-        <v>13.21599988937378</v>
+        <v>13.21399993896484</v>
       </c>
       <c r="N31" t="n">
         <v>-1</v>
       </c>
       <c r="O31" t="n">
-        <v>-5.796005497280154</v>
+        <v>-5.933098512262281</v>
       </c>
       <c r="P31" t="n">
-        <v>13.09730771871713</v>
+        <v>13.09653850702139</v>
       </c>
       <c r="Q31" t="n">
         <v>-1</v>
       </c>
       <c r="R31" t="n">
-        <v>-4.942297480931454</v>
+        <v>-5.089422685912475</v>
       </c>
       <c r="S31" t="n">
-        <v>13.46500003814697</v>
+        <v>13.46460004806519</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-7.538063319764528</v>
+        <v>-7.683850535449609</v>
       </c>
       <c r="V31" t="n">
-        <v>14.95446667353312</v>
+        <v>14.95433334350586</v>
       </c>
       <c r="W31" t="n">
         <v>-1</v>
       </c>
       <c r="X31" t="n">
-        <v>-16.74728306226037</v>
+        <v>-16.8802779792675</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.01949999809265</v>
+        <v>15.0194000005722</v>
       </c>
       <c r="Z31" t="n">
         <v>-1</v>
       </c>
       <c r="AA31" t="n">
-        <v>-17.10776117150251</v>
+        <v>-17.24036709387707</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4780265338888682</v>
+        <v>0.4797284049363585</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -9469,7 +9471,7 @@
       <c r="BX31" t="inlineStr"/>
       <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
-        <v>7.73</v>
+        <v>7.72</v>
       </c>
       <c r="CA31" t="n">
         <v>0.11</v>
@@ -9506,13 +9508,13 @@
         <v>7</v>
       </c>
       <c r="CM31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CN31" t="n">
         <v>0</v>
       </c>
       <c r="CO31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
@@ -9525,13 +9527,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>33.91999816894531</v>
+        <v>34.09000015258789</v>
       </c>
       <c r="D32" t="n">
-        <v>33.91999816894531</v>
+        <v>34.09000015258789</v>
       </c>
       <c r="E32" t="n">
-        <v>34.02999877929688</v>
+        <v>34.09000015258789</v>
       </c>
       <c r="F32" t="n">
         <v>33.2599983215332</v>
@@ -9540,67 +9542,67 @@
         <v>33.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1444800</v>
+        <v>2297500</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0005892887027971749</v>
+        <v>0.004419609073315067</v>
       </c>
       <c r="J32" t="n">
-        <v>32.87222205268012</v>
+        <v>32.89111116197374</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>3.187421022485346</v>
+        <v>3.645024288508128</v>
       </c>
       <c r="M32" t="n">
-        <v>32.8189998626709</v>
+        <v>32.83600006103516</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>3.354758861883277</v>
+        <v>3.818979440924025</v>
       </c>
       <c r="P32" t="n">
-        <v>33.29423097463754</v>
+        <v>33.30076951246996</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.879506376898925</v>
+        <v>2.370007215065696</v>
       </c>
       <c r="S32" t="n">
-        <v>34.00800003051758</v>
+        <v>34.01140007019043</v>
       </c>
       <c r="T32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.258768117776101</v>
+        <v>0.2310992262454588</v>
       </c>
       <c r="V32" t="n">
-        <v>32.34488564809163</v>
+        <v>32.34601899464925</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>4.869742122419937</v>
+        <v>5.391640802001429</v>
       </c>
       <c r="Y32" t="n">
-        <v>31.41627125740051</v>
+        <v>31.41712126731873</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>7.969522834302029</v>
+        <v>8.507714193564873</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2406112406903298</v>
+        <v>0.2415120095533986</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -9752,13 +9754,13 @@
       <c r="BX32" t="inlineStr"/>
       <c r="BY32" t="inlineStr"/>
       <c r="BZ32" t="n">
-        <v>15.08</v>
+        <v>15.15</v>
       </c>
       <c r="CA32" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CC32" t="n">
         <v>2</v>
@@ -9808,10 +9810,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69.55000305175781</v>
+        <v>69.66999816894531</v>
       </c>
       <c r="D33" t="n">
-        <v>69.55000305175781</v>
+        <v>69.66999816894531</v>
       </c>
       <c r="E33" t="n">
         <v>71.09999847412109</v>
@@ -9823,67 +9825,67 @@
         <v>70.98000335693359</v>
       </c>
       <c r="H33" t="n">
-        <v>5947200</v>
+        <v>6850800</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.03335641415260704</v>
+        <v>-0.03168865706744939</v>
       </c>
       <c r="J33" t="n">
-        <v>72.45999908447266</v>
+        <v>72.47333187527127</v>
       </c>
       <c r="K33" t="n">
         <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>-4.016003408063005</v>
+        <v>-3.868090004680035</v>
       </c>
       <c r="M33" t="n">
-        <v>72.29499893188476</v>
+        <v>72.30699844360352</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>-3.796937437834729</v>
+        <v>-3.646950269571704</v>
       </c>
       <c r="P33" t="n">
-        <v>74.10192254873422</v>
+        <v>74.10653774554913</v>
       </c>
       <c r="Q33" t="n">
         <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>-6.142781914980374</v>
+        <v>-5.986704697819027</v>
       </c>
       <c r="S33" t="n">
-        <v>77.29939956665039</v>
+        <v>77.30179946899415</v>
       </c>
       <c r="T33" t="n">
         <v>-1</v>
       </c>
       <c r="U33" t="n">
-        <v>-10.02517038726901</v>
+        <v>-9.87273433797613</v>
       </c>
       <c r="V33" t="n">
-        <v>85.27839991251628</v>
+        <v>85.2791998799642</v>
       </c>
       <c r="W33" t="n">
         <v>-1</v>
       </c>
       <c r="X33" t="n">
-        <v>-18.44358814998124</v>
+        <v>-18.30364465542572</v>
       </c>
       <c r="Y33" t="n">
-        <v>83.62084999084473</v>
+        <v>83.62144996643066</v>
       </c>
       <c r="Z33" t="n">
         <v>-1</v>
       </c>
       <c r="AA33" t="n">
-        <v>-16.82695995152821</v>
+        <v>-16.68405869915683</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4815220933069248</v>
+        <v>0.4807260435538858</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -10035,7 +10037,7 @@
       <c r="BX33" t="inlineStr"/>
       <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
-        <v>30.37</v>
+        <v>30.42</v>
       </c>
       <c r="CA33" t="n">
         <v>0.06</v>
@@ -10095,10 +10097,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>24.40999984741211</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="D34" t="n">
-        <v>24.40999984741211</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="E34" t="n">
         <v>25.06999969482422</v>
@@ -10110,67 +10112,67 @@
         <v>24.78000068664551</v>
       </c>
       <c r="H34" t="n">
-        <v>15396700</v>
+        <v>18053800</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.03708088835946277</v>
+        <v>-0.04418149200708077</v>
       </c>
       <c r="J34" t="n">
-        <v>25.07222175598145</v>
+        <v>25.05222172207302</v>
       </c>
       <c r="K34" t="n">
         <v>-1</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.641257384425257</v>
+        <v>-3.282032982776345</v>
       </c>
       <c r="M34" t="n">
-        <v>25.11699962615967</v>
+        <v>25.09899959564209</v>
       </c>
       <c r="N34" t="n">
         <v>-1</v>
       </c>
       <c r="O34" t="n">
-        <v>-2.814825772466905</v>
+        <v>-3.462289602796147</v>
       </c>
       <c r="P34" t="n">
-        <v>25.8730766589825</v>
+        <v>25.86615357032189</v>
       </c>
       <c r="Q34" t="n">
         <v>-1</v>
       </c>
       <c r="R34" t="n">
-        <v>-5.654823470955258</v>
+        <v>-6.325463210590543</v>
       </c>
       <c r="S34" t="n">
-        <v>25.91339988708496</v>
+        <v>25.90979988098145</v>
       </c>
       <c r="T34" t="n">
         <v>-1</v>
       </c>
       <c r="U34" t="n">
-        <v>-5.801631766668078</v>
+        <v>-6.483262497052864</v>
       </c>
       <c r="V34" t="n">
-        <v>22.26139999389649</v>
+        <v>22.26019999186198</v>
       </c>
       <c r="W34" t="n">
         <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>9.6516834255919</v>
+        <v>8.848975081510869</v>
       </c>
       <c r="Y34" t="n">
-        <v>20.63455001831055</v>
+        <v>20.63365001678467</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>18.29673933161289</v>
+        <v>17.42953632792148</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.3020193358225748</v>
+        <v>0.3094815681211575</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -10322,13 +10324,13 @@
       <c r="BX34" t="inlineStr"/>
       <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
-        <v>36.43</v>
+        <v>36.16</v>
       </c>
       <c r="CA34" t="n">
         <v>0.39</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CC34" t="n">
         <v>10</v>
@@ -10356,16 +10358,16 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CM34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
@@ -10378,10 +10380,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47.09999847412109</v>
+        <v>47.15000152587891</v>
       </c>
       <c r="D35" t="n">
-        <v>47.09999847412109</v>
+        <v>47.15000152587891</v>
       </c>
       <c r="E35" t="n">
         <v>48.15999984741211</v>
@@ -10393,67 +10395,67 @@
         <v>47.45999908447266</v>
       </c>
       <c r="H35" t="n">
-        <v>2428100</v>
+        <v>2891500</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.02986613358857892</v>
+        <v>-0.02883620459694991</v>
       </c>
       <c r="J35" t="n">
-        <v>48.17111121283637</v>
+        <v>48.17666710747613</v>
       </c>
       <c r="K35" t="n">
         <v>-1</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.223558294062883</v>
+        <v>-2.131043185919978</v>
       </c>
       <c r="M35" t="n">
-        <v>48.20300025939942</v>
+        <v>48.20800056457519</v>
       </c>
       <c r="N35" t="n">
         <v>-1</v>
       </c>
       <c r="O35" t="n">
-        <v>-2.288243012556551</v>
+        <v>-2.19465446877243</v>
       </c>
       <c r="P35" t="n">
-        <v>49.94346163823054</v>
+        <v>49.94538483252892</v>
       </c>
       <c r="Q35" t="n">
         <v>-1</v>
       </c>
       <c r="R35" t="n">
-        <v>-5.69336419791304</v>
+        <v>-5.596880104184144</v>
       </c>
       <c r="S35" t="n">
-        <v>52.07559997558594</v>
+        <v>52.07660003662109</v>
       </c>
       <c r="T35" t="n">
         <v>-1</v>
       </c>
       <c r="U35" t="n">
-        <v>-9.554573550371966</v>
+        <v>-9.460292160543748</v>
       </c>
       <c r="V35" t="n">
-        <v>50.4924361928304</v>
+        <v>50.49276954650879</v>
       </c>
       <c r="W35" t="n">
         <v>-1</v>
       </c>
       <c r="X35" t="n">
-        <v>-6.718704769470034</v>
+        <v>-6.620290490405495</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.99487245559693</v>
+        <v>48.99512247085571</v>
       </c>
       <c r="Z35" t="n">
         <v>-1</v>
       </c>
       <c r="AA35" t="n">
-        <v>-3.867494467289652</v>
+        <v>-3.765927814701062</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.2571409642730532</v>
+        <v>0.2563432265988712</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -10601,7 +10603,7 @@
       <c r="BX35" t="inlineStr"/>
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
-        <v>12.46</v>
+        <v>12.47</v>
       </c>
       <c r="CA35" t="n">
         <v>0.28</v>
@@ -10657,13 +10659,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38.2599983215332</v>
+        <v>39.81000137329102</v>
       </c>
       <c r="D36" t="n">
-        <v>38.2599983215332</v>
+        <v>39.81000137329102</v>
       </c>
       <c r="E36" t="n">
-        <v>38.72000122070312</v>
+        <v>39.81000137329102</v>
       </c>
       <c r="F36" t="n">
         <v>37.95999908447266</v>
@@ -10672,67 +10674,67 @@
         <v>38.65999984741211</v>
       </c>
       <c r="H36" t="n">
-        <v>6011200</v>
+        <v>10907000</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.02073205476370454</v>
+        <v>0.01894040655866269</v>
       </c>
       <c r="J36" t="n">
-        <v>38.36333296034071</v>
+        <v>38.53555552164713</v>
       </c>
       <c r="K36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.2693578238218656</v>
+        <v>3.307194704713598</v>
       </c>
       <c r="M36" t="n">
-        <v>38.34099960327148</v>
+        <v>38.49599990844727</v>
       </c>
       <c r="N36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.2112654405895295</v>
+        <v>3.413345459187343</v>
       </c>
       <c r="P36" t="n">
-        <v>39.89538456843449</v>
+        <v>39.95500007042518</v>
       </c>
       <c r="Q36" t="n">
         <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-4.099186571559508</v>
+        <v>-0.362905010333091</v>
       </c>
       <c r="S36" t="n">
-        <v>41.23139991760254</v>
+        <v>41.2623999786377</v>
       </c>
       <c r="T36" t="n">
         <v>-1</v>
       </c>
       <c r="U36" t="n">
-        <v>-7.206647365860555</v>
+        <v>-3.519908212073494</v>
       </c>
       <c r="V36" t="n">
-        <v>40.11159998575847</v>
+        <v>40.12193333943685</v>
       </c>
       <c r="W36" t="n">
         <v>-1</v>
       </c>
       <c r="X36" t="n">
-        <v>-4.616125172974079</v>
+        <v>-0.7774599581402254</v>
       </c>
       <c r="Y36" t="n">
-        <v>39.11555000305176</v>
+        <v>39.12330001831054</v>
       </c>
       <c r="Z36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>-2.187241855098052</v>
+        <v>1.755223497657611</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.2675366542729897</v>
+        <v>0.2723170477249919</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -10884,13 +10886,13 @@
       <c r="BX36" t="inlineStr"/>
       <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
-        <v>31.11</v>
+        <v>32.37</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="CC36" t="n">
         <v>8</v>
@@ -10918,16 +10920,16 @@
         <v>0</v>
       </c>
       <c r="CL36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CM36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN36" t="n">
         <v>0</v>
       </c>
       <c r="CO36" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
@@ -10940,82 +10942,82 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>14.77000045776367</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="D37" t="n">
-        <v>14.77000045776367</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="E37" t="n">
         <v>15.11999988555908</v>
       </c>
       <c r="F37" t="n">
-        <v>14.75</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="G37" t="n">
         <v>15.03999996185303</v>
       </c>
       <c r="H37" t="n">
-        <v>2028000</v>
+        <v>2480200</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.03652964570967865</v>
+        <v>-0.04109589808064484</v>
       </c>
       <c r="J37" t="n">
-        <v>15.57555548350016</v>
+        <v>15.56777763366699</v>
       </c>
       <c r="K37" t="n">
         <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>-5.171918437129568</v>
+        <v>-5.574192057607457</v>
       </c>
       <c r="M37" t="n">
-        <v>15.58699989318848</v>
+        <v>15.57999982833862</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>-5.241543857210352</v>
+        <v>-5.648267193641719</v>
       </c>
       <c r="P37" t="n">
-        <v>15.88538459631113</v>
+        <v>15.88269226367657</v>
       </c>
       <c r="Q37" t="n">
         <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>-7.021448752373733</v>
+        <v>-7.446423029401824</v>
       </c>
       <c r="S37" t="n">
-        <v>16.06339996337891</v>
+        <v>16.06199995040894</v>
       </c>
       <c r="T37" t="n">
         <v>-1</v>
       </c>
       <c r="U37" t="n">
-        <v>-8.051841506554693</v>
+        <v>-8.479642294539557</v>
       </c>
       <c r="V37" t="n">
-        <v>15.86226670583089</v>
+        <v>15.8618000348409</v>
       </c>
       <c r="W37" t="n">
         <v>-1</v>
       </c>
       <c r="X37" t="n">
-        <v>-6.885940504743301</v>
+        <v>-7.324516908697865</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.72040000915527</v>
+        <v>15.72005000591278</v>
       </c>
       <c r="Z37" t="n">
         <v>-1</v>
       </c>
       <c r="AA37" t="n">
-        <v>-6.045644836251663</v>
+        <v>-6.48884829414647</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.2578014849384653</v>
+        <v>0.2631060237574293</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -11163,13 +11165,13 @@
       <c r="BX37" t="inlineStr"/>
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="n">
-        <v>12.73</v>
+        <v>12.67</v>
       </c>
       <c r="CA37" t="n">
         <v>0.4</v>
       </c>
       <c r="CB37" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CC37" t="n">
         <v>9</v>
@@ -11192,11 +11194,7 @@
       <c r="CI37" t="n">
         <v>28</v>
       </c>
-      <c r="CJ37" t="inlineStr">
-        <is>
-          <t>melhor</t>
-        </is>
-      </c>
+      <c r="CJ37" t="inlineStr"/>
       <c r="CK37" t="n">
         <v>0</v>
       </c>
@@ -11223,10 +11221,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>24.09000015258789</v>
+        <v>24.1299991607666</v>
       </c>
       <c r="D38" t="n">
-        <v>24.09000015258789</v>
+        <v>24.1299991607666</v>
       </c>
       <c r="E38" t="n">
         <v>24.23999977111816</v>
@@ -11238,67 +11236,67 @@
         <v>24.03000068664551</v>
       </c>
       <c r="H38" t="n">
-        <v>10897600</v>
+        <v>13006900</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.02271803142428497</v>
+        <v>-0.02109535358259274</v>
       </c>
       <c r="J38" t="n">
-        <v>23.74333339267307</v>
+        <v>23.74777772691515</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.460059353004744</v>
+        <v>1.609504006003287</v>
       </c>
       <c r="M38" t="n">
-        <v>23.71900005340576</v>
+        <v>23.72299995422363</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.564147301095261</v>
+        <v>1.715631274831698</v>
       </c>
       <c r="P38" t="n">
-        <v>23.48884619199313</v>
+        <v>23.49038461538462</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.55931668878519</v>
+        <v>2.722878130156628</v>
       </c>
       <c r="S38" t="n">
-        <v>21.94200008392334</v>
+        <v>21.94280006408691</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>9.789445175685541</v>
+        <v>9.967730145157763</v>
       </c>
       <c r="V38" t="n">
-        <v>20.80206667582194</v>
+        <v>20.80233333587647</v>
       </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>15.8058020292161</v>
+        <v>15.9965988966782</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.85195003509521</v>
+        <v>19.85215003013611</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>21.34828120159708</v>
+        <v>21.54854322648479</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.3369099108560378</v>
+        <v>0.3358183078683623</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -11448,7 +11446,7 @@
       <c r="BX38" t="inlineStr"/>
       <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
-        <v>29.02</v>
+        <v>29.07</v>
       </c>
       <c r="CA38" t="n">
         <v>0.17</v>
@@ -11504,10 +11502,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10.28999996185303</v>
+        <v>10.32999992370605</v>
       </c>
       <c r="D39" t="n">
-        <v>10.28999996185303</v>
+        <v>10.32999992370605</v>
       </c>
       <c r="E39" t="n">
         <v>10.44999980926514</v>
@@ -11519,67 +11517,67 @@
         <v>10.27000045776367</v>
       </c>
       <c r="H39" t="n">
-        <v>12008500</v>
+        <v>13307300</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.02649004172708713</v>
+        <v>-0.02270575005178899</v>
       </c>
       <c r="J39" t="n">
-        <v>10.24333328670926</v>
+        <v>10.24777772691515</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4555809504345836</v>
+        <v>0.8023417269771129</v>
       </c>
       <c r="M39" t="n">
-        <v>10.24699993133545</v>
+        <v>10.25099992752075</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.4196353157579735</v>
+        <v>0.7706564895509586</v>
       </c>
       <c r="P39" t="n">
-        <v>10.2026923252986</v>
+        <v>10.20423078536987</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0.8557313478711519</v>
+        <v>1.232519539998064</v>
       </c>
       <c r="S39" t="n">
-        <v>9.623799991607665</v>
+        <v>9.624599990844727</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>6.922421193565066</v>
+        <v>7.329135065689275</v>
       </c>
       <c r="V39" t="n">
-        <v>9.152171827952067</v>
+        <v>9.15243849436442</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>12.43232923606031</v>
+        <v>12.86609497640125</v>
       </c>
       <c r="Y39" t="n">
-        <v>8.677074093818664</v>
+        <v>8.677274093627929</v>
       </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>18.58836112951222</v>
+        <v>19.04660164292596</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.3392945949591128</v>
+        <v>0.3365970815685393</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -11735,7 +11733,7 @@
       <c r="BX39" t="inlineStr"/>
       <c r="BY39" t="inlineStr"/>
       <c r="BZ39" t="n">
-        <v>23.93</v>
+        <v>24.02</v>
       </c>
       <c r="CA39" t="n">
         <v>0.6</v>
@@ -11776,13 +11774,13 @@
         <v>10</v>
       </c>
       <c r="CM39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
       </c>
       <c r="CO39" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40">
@@ -11795,10 +11793,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11.14999961853027</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="D40" t="n">
-        <v>11.14999961853027</v>
+        <v>11.22000026702881</v>
       </c>
       <c r="E40" t="n">
         <v>12.0600004196167</v>
@@ -11810,67 +11808,67 @@
         <v>11.97999954223633</v>
       </c>
       <c r="H40" t="n">
-        <v>12911100</v>
+        <v>14416900</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.08830743778658967</v>
+        <v>-0.08258375413011954</v>
       </c>
       <c r="J40" t="n">
-        <v>12.18444421556261</v>
+        <v>12.19222206539578</v>
       </c>
       <c r="K40" t="n">
         <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>-8.489879215919332</v>
+        <v>-7.974114916479011</v>
       </c>
       <c r="M40" t="n">
-        <v>12.19999980926514</v>
+        <v>12.20699987411499</v>
       </c>
       <c r="N40" t="n">
         <v>-1</v>
       </c>
       <c r="O40" t="n">
-        <v>-8.606559075004688</v>
+        <v>-8.085521563567141</v>
       </c>
       <c r="P40" t="n">
-        <v>12.23692303437453</v>
+        <v>12.23961536700909</v>
       </c>
       <c r="Q40" t="n">
         <v>-1</v>
       </c>
       <c r="R40" t="n">
-        <v>-8.882326159860607</v>
+        <v>-8.330450503604657</v>
       </c>
       <c r="S40" t="n">
-        <v>11.88059995651245</v>
+        <v>11.88199996948242</v>
       </c>
       <c r="T40" t="n">
         <v>-1</v>
       </c>
       <c r="U40" t="n">
-        <v>-6.149523935293296</v>
+        <v>-5.571450127536483</v>
       </c>
       <c r="V40" t="n">
-        <v>14.53219996770223</v>
+        <v>14.53266663869222</v>
       </c>
       <c r="W40" t="n">
         <v>-1</v>
       </c>
       <c r="X40" t="n">
-        <v>-23.27383573504966</v>
+        <v>-22.7946216205336</v>
       </c>
       <c r="Y40" t="n">
-        <v>20.25564997196198</v>
+        <v>20.25599997520447</v>
       </c>
       <c r="Z40" t="n">
         <v>-1</v>
       </c>
       <c r="AA40" t="n">
-        <v>-44.9536320287713</v>
+        <v>-44.60900335326174</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.7285554186755404</v>
+        <v>0.7228609013757151</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -12022,10 +12020,10 @@
       <c r="BX40" t="inlineStr"/>
       <c r="BY40" t="inlineStr"/>
       <c r="BZ40" t="n">
-        <v>-13.12</v>
+        <v>-13.2</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="CB40" t="n">
         <v>0.12</v>
@@ -12082,10 +12080,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21.15999984741211</v>
+        <v>21.30999946594238</v>
       </c>
       <c r="D41" t="n">
-        <v>21.15999984741211</v>
+        <v>21.30999946594238</v>
       </c>
       <c r="E41" t="n">
         <v>22.23999977111816</v>
@@ -12097,67 +12095,67 @@
         <v>21.75</v>
       </c>
       <c r="H41" t="n">
-        <v>5754100</v>
+        <v>6091500</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.02488483394201479</v>
+        <v>-0.01797240936798206</v>
       </c>
       <c r="J41" t="n">
-        <v>22.12666659884983</v>
+        <v>22.14333322313097</v>
       </c>
       <c r="K41" t="n">
         <v>-1</v>
       </c>
       <c r="L41" t="n">
-        <v>-4.368786175356237</v>
+        <v>-3.763361860616728</v>
       </c>
       <c r="M41" t="n">
-        <v>22.1829999923706</v>
+        <v>22.19799995422363</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
       </c>
       <c r="O41" t="n">
-        <v>-4.611640198847473</v>
+        <v>-4.000362600740925</v>
       </c>
       <c r="P41" t="n">
-        <v>22.62384620079627</v>
+        <v>22.62961541689359</v>
       </c>
       <c r="Q41" t="n">
         <v>-1</v>
       </c>
       <c r="R41" t="n">
-        <v>-6.470369098127272</v>
+        <v>-5.831367111816149</v>
       </c>
       <c r="S41" t="n">
-        <v>22.85100002288818</v>
+        <v>22.85400001525879</v>
       </c>
       <c r="T41" t="n">
         <v>-1</v>
       </c>
       <c r="U41" t="n">
-        <v>-7.400114541080573</v>
+        <v>-6.755931339308368</v>
       </c>
       <c r="V41" t="n">
-        <v>23.64040003458659</v>
+        <v>23.64140003204346</v>
       </c>
       <c r="W41" t="n">
         <v>-1</v>
       </c>
       <c r="X41" t="n">
-        <v>-10.49220903007386</v>
+        <v>-9.86151650469559</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.47314998626709</v>
+        <v>23.47389998435974</v>
       </c>
       <c r="Z41" t="n">
         <v>-1</v>
       </c>
       <c r="AA41" t="n">
-        <v>-9.854451320799647</v>
+        <v>-9.218325543940832</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.3082675614921007</v>
+        <v>0.3046907763486478</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -12305,13 +12303,13 @@
       <c r="BX41" t="inlineStr"/>
       <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
-        <v>8.85</v>
+        <v>8.92</v>
       </c>
       <c r="CA41" t="n">
         <v>0.42</v>
       </c>
       <c r="CB41" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CC41" t="n">
         <v>4</v>
@@ -12361,82 +12359,82 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>24.92000007629395</v>
+        <v>24.70999908447266</v>
       </c>
       <c r="D42" t="n">
-        <v>24.92000007629395</v>
+        <v>24.70999908447266</v>
       </c>
       <c r="E42" t="n">
         <v>25.36000061035156</v>
       </c>
       <c r="F42" t="n">
-        <v>24.84000015258789</v>
+        <v>24.70999908447266</v>
       </c>
       <c r="G42" t="n">
         <v>25.25</v>
       </c>
       <c r="H42" t="n">
-        <v>2424200</v>
+        <v>2814000</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.03072730596306494</v>
+        <v>-0.03889537283585287</v>
       </c>
       <c r="J42" t="n">
-        <v>25.93999989827474</v>
+        <v>25.91666645473904</v>
       </c>
       <c r="K42" t="n">
         <v>-1</v>
       </c>
       <c r="L42" t="n">
-        <v>-3.932150447111733</v>
+        <v>-4.655951305981857</v>
       </c>
       <c r="M42" t="n">
-        <v>25.99699993133545</v>
+        <v>25.97599983215332</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
       </c>
       <c r="O42" t="n">
-        <v>-4.142785159388114</v>
+        <v>-4.873732506394603</v>
       </c>
       <c r="P42" t="n">
-        <v>26.7119229390071</v>
+        <v>26.7038459777832</v>
       </c>
       <c r="Q42" t="n">
         <v>-1</v>
       </c>
       <c r="R42" t="n">
-        <v>-6.708325966665734</v>
+        <v>-7.466515853069882</v>
       </c>
       <c r="S42" t="n">
-        <v>27.58279983520508</v>
+        <v>27.57859981536865</v>
       </c>
       <c r="T42" t="n">
         <v>-1</v>
       </c>
       <c r="U42" t="n">
-        <v>-9.653841433140126</v>
+        <v>-10.40154594540879</v>
       </c>
       <c r="V42" t="n">
-        <v>27.01699989318848</v>
+        <v>27.01559988657634</v>
       </c>
       <c r="W42" t="n">
         <v>-1</v>
       </c>
       <c r="X42" t="n">
-        <v>-7.761778973183571</v>
+        <v>-8.534331318881057</v>
       </c>
       <c r="Y42" t="n">
-        <v>26.10544989585877</v>
+        <v>26.10439989089966</v>
       </c>
       <c r="Z42" t="n">
         <v>-1</v>
       </c>
       <c r="AA42" t="n">
-        <v>-4.541005132238205</v>
+        <v>-5.341631342818602</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.2837895761718014</v>
+        <v>0.2908542543835674</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -12588,13 +12586,13 @@
       <c r="BX42" t="inlineStr"/>
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
-        <v>10.38</v>
+        <v>10.3</v>
       </c>
       <c r="CA42" t="n">
         <v>0.04</v>
       </c>
       <c r="CB42" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CC42" t="n">
         <v>7</v>
@@ -12625,13 +12623,13 @@
         <v>5</v>
       </c>
       <c r="CM42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CN42" t="n">
         <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
@@ -12644,10 +12642,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27.10000038146973</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="D43" t="n">
-        <v>27.10000038146973</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="E43" t="n">
         <v>27.23999977111816</v>
@@ -12659,67 +12657,67 @@
         <v>26.92000007629395</v>
       </c>
       <c r="H43" t="n">
-        <v>1717600</v>
+        <v>2281400</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.01454544067382812</v>
+        <v>-0.01163635253906248</v>
       </c>
       <c r="J43" t="n">
-        <v>27.44888920254177</v>
+        <v>27.45777808295356</v>
       </c>
       <c r="K43" t="n">
         <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.271048961208022</v>
+        <v>-1.011654245797221</v>
       </c>
       <c r="M43" t="n">
-        <v>27.54500026702881</v>
+        <v>27.55300025939941</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>-1.615537779071084</v>
+        <v>-1.353754403193854</v>
       </c>
       <c r="P43" t="n">
-        <v>28.58192319136399</v>
+        <v>28.58500011150653</v>
       </c>
       <c r="Q43" t="n">
         <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>-5.184825387614329</v>
+        <v>-4.915164599790183</v>
       </c>
       <c r="S43" t="n">
-        <v>29.12940006256104</v>
+        <v>29.13100006103516</v>
       </c>
       <c r="T43" t="n">
         <v>-1</v>
       </c>
       <c r="U43" t="n">
-        <v>-6.966843384116323</v>
+        <v>-6.697331886209357</v>
       </c>
       <c r="V43" t="n">
-        <v>28.04966663360596</v>
+        <v>28.05019996643066</v>
       </c>
       <c r="W43" t="n">
         <v>-1</v>
       </c>
       <c r="X43" t="n">
-        <v>-3.385659674822822</v>
+        <v>-3.102293966874756</v>
       </c>
       <c r="Y43" t="n">
-        <v>26.91065000534057</v>
+        <v>26.91105000495911</v>
       </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.703626170648328</v>
+        <v>0.9994047061229925</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.2557156598347208</v>
+        <v>0.2548269437536368</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -12871,13 +12869,13 @@
       <c r="BX43" t="inlineStr"/>
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
-        <v>7.61</v>
+        <v>7.63</v>
       </c>
       <c r="CA43" t="n">
         <v>0.84</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="CC43" t="n">
         <v>7</v>
@@ -12931,10 +12929,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12.61999988555908</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="D44" t="n">
-        <v>12.61999988555908</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="E44" t="n">
         <v>12.78999996185303</v>
@@ -12946,67 +12944,67 @@
         <v>12.76000022888184</v>
       </c>
       <c r="H44" t="n">
-        <v>20104600</v>
+        <v>25043200</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.02170540629853857</v>
+        <v>-0.02325575549859793</v>
       </c>
       <c r="J44" t="n">
-        <v>12.91222212049696</v>
+        <v>12.90999995337592</v>
       </c>
       <c r="K44" t="n">
         <v>-1</v>
       </c>
       <c r="L44" t="n">
-        <v>-2.263144424026007</v>
+        <v>-2.401236042027503</v>
       </c>
       <c r="M44" t="n">
-        <v>12.91999988555908</v>
+        <v>12.91799993515015</v>
       </c>
       <c r="N44" t="n">
         <v>-1</v>
       </c>
       <c r="O44" t="n">
-        <v>-2.321981444715925</v>
+        <v>-2.46167793216298</v>
       </c>
       <c r="P44" t="n">
-        <v>13.16153845420251</v>
+        <v>13.16076924250676</v>
       </c>
       <c r="Q44" t="n">
         <v>-1</v>
       </c>
       <c r="R44" t="n">
-        <v>-4.114553709110721</v>
+        <v>-4.260912494581692</v>
       </c>
       <c r="S44" t="n">
-        <v>13.65479999542236</v>
+        <v>13.65440000534058</v>
       </c>
       <c r="T44" t="n">
         <v>-1</v>
       </c>
       <c r="U44" t="n">
-        <v>-7.578288295765505</v>
+        <v>-7.722050206954887</v>
       </c>
       <c r="V44" t="n">
-        <v>12.96407046000163</v>
+        <v>12.96393712997437</v>
       </c>
       <c r="W44" t="n">
         <v>-1</v>
       </c>
       <c r="X44" t="n">
-        <v>-2.654031968617534</v>
+        <v>-2.807301091141269</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.44623899459839</v>
+        <v>12.44613899707794</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.396091550516624</v>
+        <v>1.236217789532224</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.2375543507263646</v>
+        <v>0.2385390930500014</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -13158,7 +13156,7 @@
       <c r="BX44" t="inlineStr"/>
       <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
-        <v>8.359999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="CA44" t="n">
         <v>0.03</v>
@@ -13218,10 +13216,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38.70999908447266</v>
+        <v>38.72000122070312</v>
       </c>
       <c r="D45" t="n">
-        <v>38.70999908447266</v>
+        <v>38.72000122070312</v>
       </c>
       <c r="E45" t="n">
         <v>39.29999923706055</v>
@@ -13233,67 +13231,67 @@
         <v>39.22999954223633</v>
       </c>
       <c r="H45" t="n">
-        <v>35292400</v>
+        <v>40828600</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.02148640695933446</v>
+        <v>-0.02123357238190138</v>
       </c>
       <c r="J45" t="n">
-        <v>39.75555589463976</v>
+        <v>39.75666724310981</v>
       </c>
       <c r="K45" t="n">
         <v>-1</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.629964005378357</v>
+        <v>-2.607527477259423</v>
       </c>
       <c r="M45" t="n">
-        <v>39.79200019836426</v>
+        <v>39.79300041198731</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.719142311263052</v>
+        <v>-2.696452090003624</v>
       </c>
       <c r="P45" t="n">
-        <v>40.5680767939641</v>
+        <v>40.56846149151142</v>
       </c>
       <c r="Q45" t="n">
         <v>-1</v>
       </c>
       <c r="R45" t="n">
-        <v>-4.580147387632368</v>
+        <v>-4.556397267357721</v>
       </c>
       <c r="S45" t="n">
-        <v>42.39319984436035</v>
+        <v>42.39339988708496</v>
       </c>
       <c r="T45" t="n">
         <v>-1</v>
       </c>
       <c r="U45" t="n">
-        <v>-8.68818766549815</v>
+        <v>-8.66502492408241</v>
       </c>
       <c r="V45" t="n">
-        <v>41.92441787719726</v>
+        <v>41.92448455810547</v>
       </c>
       <c r="W45" t="n">
         <v>-1</v>
       </c>
       <c r="X45" t="n">
-        <v>-7.667175730716427</v>
+        <v>-7.643465080557098</v>
       </c>
       <c r="Y45" t="n">
-        <v>40.6344783782959</v>
+        <v>40.63452838897705</v>
       </c>
       <c r="Z45" t="n">
         <v>-1</v>
       </c>
       <c r="AA45" t="n">
-        <v>-4.736074807966926</v>
+        <v>-4.711577183687168</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.2387426993473114</v>
+        <v>0.2386002616961905</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -13465,7 +13463,7 @@
         <v>13582000000</v>
       </c>
       <c r="BZ45" t="n">
-        <v>9.19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA45" t="n">
         <v>0</v>
@@ -13521,10 +13519,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.78000068664551</v>
+        <v>16.76000022888184</v>
       </c>
       <c r="D46" t="n">
-        <v>16.78000068664551</v>
+        <v>16.76000022888184</v>
       </c>
       <c r="E46" t="n">
         <v>16.84000015258789</v>
@@ -13536,67 +13534,67 @@
         <v>16.69000053405762</v>
       </c>
       <c r="H46" t="n">
-        <v>4131700</v>
+        <v>5058200</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.007687709162605083</v>
+        <v>-0.008870468355044347</v>
       </c>
       <c r="J46" t="n">
-        <v>16.67444441053603</v>
+        <v>16.67222213745117</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.6330422382336436</v>
+        <v>0.5264930535773408</v>
       </c>
       <c r="M46" t="n">
-        <v>16.65799999237061</v>
+        <v>16.65599994659424</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0.7323850061878909</v>
+        <v>0.6244013125664218</v>
       </c>
       <c r="P46" t="n">
-        <v>16.86000002347506</v>
+        <v>16.85923077509953</v>
       </c>
       <c r="Q46" t="n">
         <v>-1</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.4744919141053646</v>
+        <v>-0.5885828810425746</v>
       </c>
       <c r="S46" t="n">
-        <v>17.86440006256104</v>
+        <v>17.86400005340576</v>
       </c>
       <c r="T46" t="n">
         <v>-1</v>
       </c>
       <c r="U46" t="n">
-        <v>-6.070169566948605</v>
+        <v>-6.18002586891757</v>
       </c>
       <c r="V46" t="n">
-        <v>18.49002166748047</v>
+        <v>18.48988833109538</v>
       </c>
       <c r="W46" t="n">
         <v>-1</v>
       </c>
       <c r="X46" t="n">
-        <v>-9.248344926725965</v>
+        <v>-9.355860193618925</v>
       </c>
       <c r="Y46" t="n">
-        <v>18.34424873352051</v>
+        <v>18.34414873123169</v>
       </c>
       <c r="Z46" t="n">
         <v>-1</v>
       </c>
       <c r="AA46" t="n">
-        <v>-8.527185111792804</v>
+        <v>-8.635715538289194</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.1811351175037324</v>
+        <v>0.1813965846740261</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -13752,7 +13750,7 @@
       <c r="BX46" t="inlineStr"/>
       <c r="BY46" t="inlineStr"/>
       <c r="BZ46" t="n">
-        <v>27.97</v>
+        <v>27.93</v>
       </c>
       <c r="CA46" t="n">
         <v>0.24</v>
@@ -13793,13 +13791,13 @@
         <v>8</v>
       </c>
       <c r="CM46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CN46" t="n">
         <v>1</v>
       </c>
       <c r="CO46" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
@@ -13812,10 +13810,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>14.72999954223633</v>
+        <v>14.64000034332275</v>
       </c>
       <c r="D47" t="n">
-        <v>14.72999954223633</v>
+        <v>14.64000034332275</v>
       </c>
       <c r="E47" t="n">
         <v>15.13000011444092</v>
@@ -13827,88 +13825,88 @@
         <v>15.03999996185303</v>
       </c>
       <c r="H47" t="n">
-        <v>14333900</v>
+        <v>16910600</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.05090211934447186</v>
+        <v>-0.05670103662920378</v>
       </c>
       <c r="J47" t="n">
-        <v>15.06222216288249</v>
+        <v>15.05222225189209</v>
       </c>
       <c r="K47" t="n">
         <v>-1</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.20566804189655</v>
+        <v>-2.73861162605089</v>
       </c>
       <c r="M47" t="n">
-        <v>15.04099998474121</v>
+        <v>15.03200006484985</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.067684614190453</v>
+        <v>-2.607768226689501</v>
       </c>
       <c r="P47" t="n">
-        <v>14.34307699937087</v>
+        <v>14.33961549172035</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>2.697625780593879</v>
+        <v>2.094790141171141</v>
       </c>
       <c r="S47" t="n">
-        <v>14.70460004806518</v>
+        <v>14.70280006408691</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U47" t="n">
-        <v>0.1727316219966508</v>
+        <v>-0.4271276252851607</v>
       </c>
       <c r="V47" t="n">
-        <v>14.69740002950033</v>
+        <v>14.6968000348409</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X47" t="n">
-        <v>0.2218046230664559</v>
+        <v>-0.3864765893493518</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.89835002422333</v>
+        <v>14.89790002822876</v>
       </c>
       <c r="Z47" t="n">
         <v>-1</v>
       </c>
       <c r="AA47" t="n">
-        <v>-1.129994138366179</v>
+        <v>-1.731114347776087</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.4842974314242477</v>
+        <v>0.489803118522216</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AE47" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AF47" t="n">
         <v>14.6</v>
       </c>
-      <c r="AF47" t="n">
+      <c r="AG47" t="n">
         <v>14.7</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>14.8</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>14.9</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>15</v>
       </c>
       <c r="AJ47" t="n">
         <v>1</v>
@@ -14035,13 +14033,13 @@
       <c r="BX47" t="inlineStr"/>
       <c r="BY47" t="inlineStr"/>
       <c r="BZ47" t="n">
-        <v>9.949999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="CA47" t="n">
         <v>-0.1</v>
       </c>
       <c r="CB47" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CC47" t="n">
         <v>5</v>
@@ -14069,16 +14067,16 @@
         <v>1</v>
       </c>
       <c r="CL47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CM47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CN47" t="n">
         <v>0</v>
       </c>
       <c r="CO47" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -14091,10 +14089,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.36999988555908</v>
+        <v>15.77999973297119</v>
       </c>
       <c r="D48" t="n">
-        <v>15.36999988555908</v>
+        <v>15.77999973297119</v>
       </c>
       <c r="E48" t="n">
         <v>16.20000076293945</v>
@@ -14106,67 +14104,67 @@
         <v>15.75</v>
       </c>
       <c r="H48" t="n">
-        <v>5780500</v>
+        <v>10193900</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.03028394223080366</v>
+        <v>-0.004416444593930313</v>
       </c>
       <c r="J48" t="n">
-        <v>16.09333366817898</v>
+        <v>16.13888920678033</v>
       </c>
       <c r="K48" t="n">
         <v>-1</v>
       </c>
       <c r="L48" t="n">
-        <v>-4.494617445545996</v>
+        <v>-2.223755731951847</v>
       </c>
       <c r="M48" t="n">
-        <v>16.21400022506714</v>
+        <v>16.25500020980835</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
       </c>
       <c r="O48" t="n">
-        <v>-5.205380089999116</v>
+        <v>-2.9221806872112</v>
       </c>
       <c r="P48" t="n">
-        <v>16.89384625508235</v>
+        <v>16.90961547998281</v>
       </c>
       <c r="Q48" t="n">
         <v>-1</v>
       </c>
       <c r="R48" t="n">
-        <v>-9.020126894222416</v>
+        <v>-6.680315991506931</v>
       </c>
       <c r="S48" t="n">
-        <v>18.39080011367798</v>
+        <v>18.39900011062622</v>
       </c>
       <c r="T48" t="n">
         <v>-1</v>
       </c>
       <c r="U48" t="n">
-        <v>-16.42560524526721</v>
+        <v>-14.23447123163201</v>
       </c>
       <c r="V48" t="n">
-        <v>18.87673341115316</v>
+        <v>18.87946674346924</v>
       </c>
       <c r="W48" t="n">
         <v>-1</v>
       </c>
       <c r="X48" t="n">
-        <v>-18.5770146201363</v>
+        <v>-16.41713218181975</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.41815004348755</v>
+        <v>19.42020004272461</v>
       </c>
       <c r="Z48" t="n">
         <v>-1</v>
       </c>
       <c r="AA48" t="n">
-        <v>-20.84724934590839</v>
+        <v>-18.74440171442593</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.3953428269057723</v>
+        <v>0.3895817477648486</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -14314,13 +14312,13 @@
       <c r="BX48" t="inlineStr"/>
       <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
-        <v>56.93</v>
+        <v>58.44</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="CB48" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="CC48" t="n">
         <v>7</v>
@@ -14355,13 +14353,13 @@
         <v>2</v>
       </c>
       <c r="CM48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CN48" t="n">
         <v>0</v>
       </c>
       <c r="CO48" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
@@ -14374,82 +14372,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.349999904632568</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="D49" t="n">
-        <v>5.349999904632568</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="E49" t="n">
         <v>5.550000190734863</v>
       </c>
       <c r="F49" t="n">
-        <v>5.329999923706055</v>
+        <v>5.320000171661377</v>
       </c>
       <c r="G49" t="n">
         <v>5.550000190734863</v>
       </c>
       <c r="H49" t="n">
-        <v>20647000</v>
+        <v>22882900</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.05809857987312272</v>
+        <v>-0.05985909965250491</v>
       </c>
       <c r="J49" t="n">
-        <v>6.203333324856228</v>
+        <v>6.202222241295709</v>
       </c>
       <c r="K49" t="n">
         <v>-1</v>
       </c>
       <c r="L49" t="n">
-        <v>-13.75604655652511</v>
+        <v>-13.9018251066039</v>
       </c>
       <c r="M49" t="n">
-        <v>6.259999990463257</v>
+        <v>6.259000015258789</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
       </c>
       <c r="O49" t="n">
-        <v>-14.53674260730064</v>
+        <v>-14.68285445647025</v>
       </c>
       <c r="P49" t="n">
-        <v>6.967307640955998</v>
+        <v>6.966923035108126</v>
       </c>
       <c r="Q49" t="n">
         <v>-1</v>
       </c>
       <c r="R49" t="n">
-        <v>-23.21280786880133</v>
+        <v>-23.35210069526748</v>
       </c>
       <c r="S49" t="n">
-        <v>7.878199939727783</v>
+        <v>7.87799994468689</v>
       </c>
       <c r="T49" t="n">
         <v>-1</v>
       </c>
       <c r="U49" t="n">
-        <v>-32.09108748746192</v>
+        <v>-32.2162961401223</v>
       </c>
       <c r="V49" t="n">
-        <v>8.778729956944783</v>
+        <v>8.778663291931153</v>
       </c>
       <c r="W49" t="n">
         <v>-1</v>
       </c>
       <c r="X49" t="n">
-        <v>-39.05724483072604</v>
+        <v>-39.17069176697876</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.702761638164521</v>
+        <v>8.702711639404297</v>
       </c>
       <c r="Z49" t="n">
         <v>-1</v>
       </c>
       <c r="AA49" t="n">
-        <v>-38.52526212862099</v>
+        <v>-38.6398128095002</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4590380589806157</v>
+        <v>0.4604000285898127</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -14601,7 +14599,7 @@
       <c r="BX49" t="inlineStr"/>
       <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
-        <v>29.72</v>
+        <v>29.67</v>
       </c>
       <c r="CA49" t="n">
         <v>0.83</v>
@@ -14661,10 +14659,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13.98999977111816</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="D50" t="n">
-        <v>13.98999977111816</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="E50" t="n">
         <v>14.07999992370605</v>
@@ -14676,67 +14674,67 @@
         <v>13.97000026702881</v>
       </c>
       <c r="H50" t="n">
-        <v>13783800</v>
+        <v>15160900</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.01130741001593949</v>
+        <v>-0.01201413999130574</v>
       </c>
       <c r="J50" t="n">
-        <v>14.28444438510471</v>
+        <v>14.28333324856228</v>
       </c>
       <c r="K50" t="n">
         <v>-1</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.061295532737567</v>
+        <v>-2.123689905201135</v>
       </c>
       <c r="M50" t="n">
-        <v>14.35599994659424</v>
+        <v>14.35499992370606</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
       </c>
       <c r="O50" t="n">
-        <v>-2.549457904970964</v>
+        <v>-2.61233286982082</v>
       </c>
       <c r="P50" t="n">
-        <v>14.96923072521503</v>
+        <v>14.96884610102727</v>
       </c>
       <c r="Q50" t="n">
         <v>-1</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.541625097991134</v>
+        <v>-6.606030632669004</v>
       </c>
       <c r="S50" t="n">
-        <v>15.6406000328064</v>
+        <v>15.64040002822876</v>
       </c>
       <c r="T50" t="n">
         <v>-1</v>
       </c>
       <c r="U50" t="n">
-        <v>-10.55330523270254</v>
+        <v>-10.61609986314697</v>
       </c>
       <c r="V50" t="n">
-        <v>15.82120002110799</v>
+        <v>15.82113335291545</v>
       </c>
       <c r="W50" t="n">
         <v>-1</v>
       </c>
       <c r="X50" t="n">
-        <v>-11.57434485087551</v>
+        <v>-11.63718028038644</v>
       </c>
       <c r="Y50" t="n">
-        <v>15.45675000190735</v>
+        <v>15.45670000076294</v>
       </c>
       <c r="Z50" t="n">
         <v>-1</v>
       </c>
       <c r="AA50" t="n">
-        <v>-9.489383153691357</v>
+        <v>-9.553788702981372</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.290060956207694</v>
+        <v>0.2901556019437816</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -14884,7 +14882,7 @@
       <c r="BX50" t="inlineStr"/>
       <c r="BY50" t="inlineStr"/>
       <c r="BZ50" t="n">
-        <v>8.43</v>
+        <v>8.42</v>
       </c>
       <c r="CA50" t="n">
         <v>1.09</v>
@@ -14944,10 +14942,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.670000076293945</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="D51" t="n">
-        <v>5.670000076293945</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="E51" t="n">
         <v>5.760000228881836</v>
@@ -14959,67 +14957,67 @@
         <v>5.670000076293945</v>
       </c>
       <c r="H51" t="n">
-        <v>19960800</v>
+        <v>20990000</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.04384481611654967</v>
+        <v>-0.03541316091501601</v>
       </c>
       <c r="J51" t="n">
-        <v>5.951111051771376</v>
+        <v>5.956666575537787</v>
       </c>
       <c r="K51" t="n">
         <v>-1</v>
       </c>
       <c r="L51" t="n">
-        <v>-4.7236721518372</v>
+        <v>-3.973141392839668</v>
       </c>
       <c r="M51" t="n">
-        <v>5.978999948501587</v>
+        <v>5.983999919891358</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
       </c>
       <c r="O51" t="n">
-        <v>-5.168086216242243</v>
+        <v>-4.411766932384923</v>
       </c>
       <c r="P51" t="n">
-        <v>6.334615358939538</v>
+        <v>6.33653842485868</v>
       </c>
       <c r="Q51" t="n">
         <v>-1</v>
       </c>
       <c r="R51" t="n">
-        <v>-10.49180171149104</v>
+        <v>-9.729896567001086</v>
       </c>
       <c r="S51" t="n">
-        <v>6.998199987411499</v>
+        <v>6.999199981689453</v>
       </c>
       <c r="T51" t="n">
         <v>-1</v>
       </c>
       <c r="U51" t="n">
-        <v>-18.97916483533974</v>
+        <v>-18.27637722660172</v>
       </c>
       <c r="V51" t="n">
-        <v>7.93113335609436</v>
+        <v>7.931466687520345</v>
       </c>
       <c r="W51" t="n">
         <v>-1</v>
       </c>
       <c r="X51" t="n">
-        <v>-28.50958593531829</v>
+        <v>-27.8821936024556</v>
       </c>
       <c r="Y51" t="n">
-        <v>7.769450006484985</v>
+        <v>7.769700005054474</v>
       </c>
       <c r="Z51" t="n">
         <v>-1</v>
       </c>
       <c r="AA51" t="n">
-        <v>-27.0218603432505</v>
+        <v>-26.38068668712329</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.4691163363983237</v>
+        <v>0.4643806160279134</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -15171,13 +15169,13 @@
       <c r="BX51" t="inlineStr"/>
       <c r="BY51" t="inlineStr"/>
       <c r="BZ51" t="n">
-        <v>-4.2</v>
+        <v>-4.24</v>
       </c>
       <c r="CA51" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CB51" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="CC51" t="n">
         <v>7</v>
@@ -15212,13 +15210,13 @@
         <v>1</v>
       </c>
       <c r="CM51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CN51" t="n">
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
@@ -15231,10 +15229,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>28.51000022888184</v>
+        <v>28.64999961853027</v>
       </c>
       <c r="D52" t="n">
-        <v>28.51000022888184</v>
+        <v>28.64999961853027</v>
       </c>
       <c r="E52" t="n">
         <v>28.8799991607666</v>
@@ -15246,67 +15244,67 @@
         <v>28.82999992370605</v>
       </c>
       <c r="H52" t="n">
-        <v>3251400</v>
+        <v>3731100</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.03093133395826775</v>
+        <v>-0.02617268714367282</v>
       </c>
       <c r="J52" t="n">
-        <v>29.63444455464681</v>
+        <v>29.65000004238552</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>-3.794382998107029</v>
+        <v>-3.372682706326212</v>
       </c>
       <c r="M52" t="n">
-        <v>29.68400001525879</v>
+        <v>29.69799995422363</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
       </c>
       <c r="O52" t="n">
-        <v>-3.95499186690968</v>
+        <v>-3.528858297894614</v>
       </c>
       <c r="P52" t="n">
-        <v>30.38038451854999</v>
+        <v>30.38576911045955</v>
       </c>
       <c r="Q52" t="n">
         <v>-1</v>
       </c>
       <c r="R52" t="n">
-        <v>-6.156552391646379</v>
+        <v>-5.712442181796806</v>
       </c>
       <c r="S52" t="n">
-        <v>31.49459995269775</v>
+        <v>31.49739994049072</v>
       </c>
       <c r="T52" t="n">
         <v>-1</v>
       </c>
       <c r="U52" t="n">
-        <v>-9.47654432283165</v>
+        <v>-9.040112286538429</v>
       </c>
       <c r="V52" t="n">
-        <v>30.65533336639404</v>
+        <v>30.65626669565837</v>
       </c>
       <c r="W52" t="n">
         <v>-1</v>
       </c>
       <c r="X52" t="n">
-        <v>-6.998237833107473</v>
+        <v>-6.544394648720313</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.93085004806519</v>
+        <v>29.93155004501343</v>
       </c>
       <c r="Z52" t="n">
         <v>-1</v>
       </c>
       <c r="AA52" t="n">
-        <v>-4.747108140602899</v>
+        <v>-4.281603941512742</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.3014294064728594</v>
+        <v>0.2983217614723749</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -15458,13 +15456,13 @@
       <c r="BX52" t="inlineStr"/>
       <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
-        <v>11.98</v>
+        <v>12.04</v>
       </c>
       <c r="CA52" t="n">
         <v>0.31</v>
       </c>
       <c r="CB52" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CC52" t="n">
         <v>8</v>
@@ -15499,13 +15497,13 @@
         <v>6</v>
       </c>
       <c r="CM52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CN52" t="n">
         <v>0</v>
       </c>
       <c r="CO52" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -15518,10 +15516,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.680000305175781</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="D53" t="n">
-        <v>9.680000305175781</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="E53" t="n">
         <v>9.859999656677246</v>
@@ -15533,86 +15531,88 @@
         <v>9.729999542236328</v>
       </c>
       <c r="H53" t="n">
-        <v>16432700</v>
+        <v>18093300</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.01825551295831618</v>
+        <v>-0.006085138745593244</v>
       </c>
       <c r="J53" t="n">
-        <v>10.0477778116862</v>
+        <v>10.06111113230387</v>
       </c>
       <c r="K53" t="n">
         <v>-1</v>
       </c>
       <c r="L53" t="n">
-        <v>-3.660287014733424</v>
+        <v>-2.595249551817828</v>
       </c>
       <c r="M53" t="n">
-        <v>10.06300001144409</v>
+        <v>10.075</v>
       </c>
       <c r="N53" t="n">
         <v>-1</v>
       </c>
       <c r="O53" t="n">
-        <v>-3.806019137759584</v>
+        <v>-2.729526642830134</v>
       </c>
       <c r="P53" t="n">
-        <v>10.11115382267879</v>
+        <v>10.1157692028926</v>
       </c>
       <c r="Q53" t="n">
         <v>-1</v>
       </c>
       <c r="R53" t="n">
-        <v>-4.26413765495239</v>
+        <v>-3.121552161030325</v>
       </c>
       <c r="S53" t="n">
-        <v>10.10319995880127</v>
+        <v>10.10559995651245</v>
       </c>
       <c r="T53" t="n">
         <v>-1</v>
       </c>
       <c r="U53" t="n">
-        <v>-4.188768462974184</v>
+        <v>-3.024063559735979</v>
       </c>
       <c r="V53" t="n">
-        <v>8.961133286158244</v>
+        <v>8.961933285395304</v>
       </c>
       <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="X53" t="n">
-        <v>8.022054756488563</v>
+        <v>9.351407544009549</v>
       </c>
       <c r="Y53" t="n">
-        <v>8.927349960803985</v>
+        <v>8.92794996023178</v>
       </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
       <c r="AA53" t="n">
-        <v>8.430837232508507</v>
+        <v>9.767642453054739</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.3392025698389699</v>
+        <v>0.3357811599375046</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="AF53" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG53" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH53" t="n">
         <v>36.9</v>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Foguete</t>
+        </is>
+      </c>
       <c r="AI53" t="inlineStr">
         <is>
           <t>Foguete</t>
@@ -15622,7 +15622,7 @@
         <v>1</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
@@ -15743,13 +15743,13 @@
       <c r="BX53" t="inlineStr"/>
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="n">
-        <v>-5.73</v>
+        <v>-5.8</v>
       </c>
       <c r="CA53" t="n">
         <v>0.3</v>
       </c>
       <c r="CB53" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CC53" t="n">
         <v>3</v>
@@ -15781,16 +15781,16 @@
         <v>0</v>
       </c>
       <c r="CL53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CM53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CN53" t="n">
         <v>0</v>
       </c>
       <c r="CO53" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54">
@@ -15803,82 +15803,82 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>46.22000122070312</v>
+        <v>45.95000076293945</v>
       </c>
       <c r="D54" t="n">
-        <v>46.22000122070312</v>
+        <v>45.95000076293945</v>
       </c>
       <c r="E54" t="n">
         <v>46.84999847412109</v>
       </c>
       <c r="F54" t="n">
-        <v>46.20000076293945</v>
+        <v>45.95000076293945</v>
       </c>
       <c r="G54" t="n">
         <v>46.5</v>
       </c>
       <c r="H54" t="n">
-        <v>7878200</v>
+        <v>10451200</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.005379814793045945</v>
+        <v>-0.01119002462027063</v>
       </c>
       <c r="J54" t="n">
-        <v>47.7922223409017</v>
+        <v>47.76222229003906</v>
       </c>
       <c r="K54" t="n">
         <v>-1</v>
       </c>
       <c r="L54" t="n">
-        <v>-3.289700798979224</v>
+        <v>-3.794257135052849</v>
       </c>
       <c r="M54" t="n">
-        <v>48.04300003051758</v>
+        <v>48.01599998474121</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
       </c>
       <c r="O54" t="n">
-        <v>-3.794514931741265</v>
+        <v>-4.302730803187074</v>
       </c>
       <c r="P54" t="n">
-        <v>50.20846176147461</v>
+        <v>50.1980771284837</v>
       </c>
       <c r="Q54" t="n">
         <v>-1</v>
       </c>
       <c r="R54" t="n">
-        <v>-7.943801504454504</v>
+        <v>-8.462627671317263</v>
       </c>
       <c r="S54" t="n">
-        <v>51.44000015258789</v>
+        <v>51.43460014343262</v>
       </c>
       <c r="T54" t="n">
         <v>-1</v>
       </c>
       <c r="U54" t="n">
-        <v>-10.14774283903682</v>
+        <v>-10.66324879594395</v>
       </c>
       <c r="V54" t="n">
-        <v>41.91200012207031</v>
+        <v>41.91020011901855</v>
       </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
       <c r="X54" t="n">
-        <v>10.27868172858751</v>
+        <v>9.63918242444198</v>
       </c>
       <c r="Y54" t="n">
-        <v>39.74290009498596</v>
+        <v>39.74155009269715</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>16.29750498890826</v>
+        <v>15.62206470497778</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.282279341748757</v>
+        <v>0.2830987681001177</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -16030,13 +16030,13 @@
       <c r="BX54" t="inlineStr"/>
       <c r="BY54" t="inlineStr"/>
       <c r="BZ54" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="CA54" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="CB54" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CC54" t="n">
         <v>1</v>
@@ -16064,16 +16064,16 @@
         <v>0</v>
       </c>
       <c r="CL54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CM54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN54" t="n">
         <v>0</v>
       </c>
       <c r="CO54" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55">
@@ -16086,82 +16086,82 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>41.40999984741211</v>
+        <v>41.25</v>
       </c>
       <c r="D55" t="n">
-        <v>41.40999984741211</v>
+        <v>41.25</v>
       </c>
       <c r="E55" t="n">
         <v>41.86999893188477</v>
       </c>
       <c r="F55" t="n">
-        <v>41.38999938964844</v>
+        <v>41.25</v>
       </c>
       <c r="G55" t="n">
         <v>41.65000152587891</v>
       </c>
       <c r="H55" t="n">
-        <v>38379800</v>
+        <v>42591300</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.003848925874108899</v>
+        <v>-0.00769785174821791</v>
       </c>
       <c r="J55" t="n">
-        <v>42.66666624281142</v>
+        <v>42.64888848198785</v>
       </c>
       <c r="K55" t="n">
         <v>-1</v>
       </c>
       <c r="L55" t="n">
-        <v>-2.945311893476171</v>
+        <v>-3.280011582432323</v>
       </c>
       <c r="M55" t="n">
-        <v>42.89499969482422</v>
+        <v>42.87899971008301</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
       </c>
       <c r="O55" t="n">
-        <v>-3.461941620182118</v>
+        <v>-3.79906182769452</v>
       </c>
       <c r="P55" t="n">
-        <v>45.22884603647086</v>
+        <v>45.22269219618578</v>
       </c>
       <c r="Q55" t="n">
         <v>-1</v>
       </c>
       <c r="R55" t="n">
-        <v>-8.443386298158858</v>
+        <v>-8.784731742531783</v>
       </c>
       <c r="S55" t="n">
-        <v>46.50739982604981</v>
+        <v>46.50419982910157</v>
       </c>
       <c r="T55" t="n">
         <v>-1</v>
       </c>
       <c r="U55" t="n">
-        <v>-10.9604062959945</v>
+        <v>-11.2983340180247</v>
       </c>
       <c r="V55" t="n">
-        <v>38.67653340657552</v>
+        <v>38.6754667409261</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
       <c r="X55" t="n">
-        <v>7.067506314751211</v>
+        <v>6.65676067032319</v>
       </c>
       <c r="Y55" t="n">
-        <v>36.71485004425049</v>
+        <v>36.71405004501343</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>12.78814920257825</v>
+        <v>12.35480680945101</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.2461531354093682</v>
+        <v>0.2463703995294896</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -16313,13 +16313,13 @@
       <c r="BX55" t="inlineStr"/>
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
       <c r="CA55" t="n">
         <v>0.61</v>
       </c>
       <c r="CB55" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CC55" t="n">
         <v>1</v>
@@ -16354,13 +16354,13 @@
         <v>4</v>
       </c>
       <c r="CM55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CN55" t="n">
         <v>0</v>
       </c>
       <c r="CO55" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -16373,10 +16373,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.639999866485596</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="D56" t="n">
-        <v>5.639999866485596</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="E56" t="n">
         <v>5.880000114440918</v>
@@ -16388,67 +16388,67 @@
         <v>5.880000114440918</v>
       </c>
       <c r="H56" t="n">
-        <v>12481800</v>
+        <v>15093900</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.05210083238940943</v>
+        <v>-0.03697475583933196</v>
       </c>
       <c r="J56" t="n">
-        <v>6.05333317650689</v>
+        <v>6.063333193461101</v>
       </c>
       <c r="K56" t="n">
         <v>-1</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.828193624389447</v>
+        <v>-5.497523618644144</v>
       </c>
       <c r="M56" t="n">
-        <v>6.045999860763549</v>
+        <v>6.054999876022339</v>
       </c>
       <c r="N56" t="n">
         <v>-1</v>
       </c>
       <c r="O56" t="n">
-        <v>-6.715183652463399</v>
+        <v>-5.367462652408044</v>
       </c>
       <c r="P56" t="n">
-        <v>6.143461502515352</v>
+        <v>6.146923046845656</v>
       </c>
       <c r="Q56" t="n">
         <v>-1</v>
       </c>
       <c r="R56" t="n">
-        <v>-8.195080832257538</v>
+        <v>-6.782629692852874</v>
       </c>
       <c r="S56" t="n">
-        <v>6.311799983978272</v>
+        <v>6.313599987030029</v>
       </c>
       <c r="T56" t="n">
         <v>-1</v>
       </c>
       <c r="U56" t="n">
-        <v>-10.64355840169141</v>
+        <v>-9.243537271214947</v>
       </c>
       <c r="V56" t="n">
-        <v>6.309902906417847</v>
+        <v>6.310502907435099</v>
       </c>
       <c r="W56" t="n">
         <v>-1</v>
       </c>
       <c r="X56" t="n">
-        <v>-10.61669331315523</v>
+        <v>-9.198995656553114</v>
       </c>
       <c r="Y56" t="n">
-        <v>6.794654338359833</v>
+        <v>6.795104339122772</v>
       </c>
       <c r="Z56" t="n">
         <v>-1</v>
       </c>
       <c r="AA56" t="n">
-        <v>-16.99357192249695</v>
+        <v>-15.67458374284194</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.343453406476761</v>
+        <v>0.3288401244443543</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -16600,13 +16600,13 @@
       <c r="BX56" t="inlineStr"/>
       <c r="BY56" t="inlineStr"/>
       <c r="BZ56" t="n">
-        <v>5.64</v>
+        <v>5.73</v>
       </c>
       <c r="CA56" t="n">
         <v>0.22</v>
       </c>
       <c r="CB56" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CC56" t="n">
         <v>9</v>
@@ -16638,16 +16638,16 @@
         <v>1</v>
       </c>
       <c r="CL56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CM56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN56" t="n">
         <v>0</v>
       </c>
       <c r="CO56" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
@@ -16660,10 +16660,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>62.54999923706055</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="D57" t="n">
-        <v>62.54999923706055</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="E57" t="n">
         <v>63.29999923706055</v>
@@ -16675,67 +16675,67 @@
         <v>62.59000015258789</v>
       </c>
       <c r="H57" t="n">
-        <v>7758700</v>
+        <v>8895000</v>
       </c>
       <c r="I57" t="n">
-        <v>0.009196510148984371</v>
+        <v>0.009841894399109874</v>
       </c>
       <c r="J57" t="n">
-        <v>63.66777759128146</v>
+        <v>63.67222213745117</v>
       </c>
       <c r="K57" t="n">
         <v>-1</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.755642173340103</v>
+        <v>-1.699676795521688</v>
       </c>
       <c r="M57" t="n">
-        <v>64.10099983215332</v>
+        <v>64.10499992370606</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
       </c>
       <c r="O57" t="n">
-        <v>-2.41961997340763</v>
+        <v>-2.363309839983202</v>
       </c>
       <c r="P57" t="n">
-        <v>65.71692320016714</v>
+        <v>65.7184616969182</v>
       </c>
       <c r="Q57" t="n">
         <v>-1</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.819038702497476</v>
+        <v>-4.76039983826495</v>
       </c>
       <c r="S57" t="n">
-        <v>65.73259994506836</v>
+        <v>65.7333999633789</v>
       </c>
       <c r="T57" t="n">
         <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>-4.841738666456915</v>
+        <v>-4.7820435464197</v>
       </c>
       <c r="V57" t="n">
-        <v>52.40233322143555</v>
+        <v>52.40259989420573</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>19.36491257506455</v>
+        <v>19.44063897392352</v>
       </c>
       <c r="Y57" t="n">
-        <v>48.69109994888306</v>
+        <v>48.69129995346069</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>28.46290041245085</v>
+        <v>28.54452481739371</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.3643009932470603</v>
+        <v>0.3644358004388149</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       <c r="BX57" t="inlineStr"/>
       <c r="BY57" t="inlineStr"/>
       <c r="BZ57" t="n">
-        <v>21.06</v>
+        <v>21.07</v>
       </c>
       <c r="CA57" t="n">
         <v>0.44</v>
@@ -16924,13 +16924,13 @@
         <v>8</v>
       </c>
       <c r="CM57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CN57" t="n">
         <v>0</v>
       </c>
       <c r="CO57" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>48.02000045776367</v>
+        <v>48.15999984741211</v>
       </c>
       <c r="D58" t="n">
-        <v>48.02000045776367</v>
+        <v>48.15999984741211</v>
       </c>
       <c r="E58" t="n">
         <v>48.91999816894531</v>
@@ -16958,67 +16958,67 @@
         <v>48.15999984741211</v>
       </c>
       <c r="H58" t="n">
-        <v>1884600</v>
+        <v>2169500</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.01477228551309673</v>
+        <v>-0.01189991405582846</v>
       </c>
       <c r="J58" t="n">
-        <v>48.57666693793403</v>
+        <v>48.59222242567274</v>
       </c>
       <c r="K58" t="n">
         <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.14595445768563</v>
+        <v>-0.8894892159373203</v>
       </c>
       <c r="M58" t="n">
-        <v>48.66500015258789</v>
+        <v>48.67900009155274</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.325387224497773</v>
+        <v>-1.06616866238937</v>
       </c>
       <c r="P58" t="n">
-        <v>49.17115416893592</v>
+        <v>49.17653876084547</v>
       </c>
       <c r="Q58" t="n">
         <v>-1</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.341115905510908</v>
+        <v>-2.067121719112807</v>
       </c>
       <c r="S58" t="n">
-        <v>50.29120010375976</v>
+        <v>50.29400009155273</v>
       </c>
       <c r="T58" t="n">
         <v>-1</v>
       </c>
       <c r="U58" t="n">
-        <v>-4.516097530602171</v>
+        <v>-4.243051338640779</v>
       </c>
       <c r="V58" t="n">
-        <v>49.27893338521321</v>
+        <v>49.27986671447754</v>
       </c>
       <c r="W58" t="n">
         <v>-1</v>
       </c>
       <c r="X58" t="n">
-        <v>-2.554708150049574</v>
+        <v>-2.272463262844897</v>
       </c>
       <c r="Y58" t="n">
-        <v>49.40525003433228</v>
+        <v>49.40595003128052</v>
       </c>
       <c r="Z58" t="n">
         <v>-1</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.803850958361669</v>
+        <v>-2.521862615898606</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.2784225479444939</v>
+        <v>0.2776348833299134</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -17170,7 +17170,7 @@
       <c r="BX58" t="inlineStr"/>
       <c r="BY58" t="inlineStr"/>
       <c r="BZ58" t="n">
-        <v>8.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="CA58" t="n">
         <v>-0.42</v>
@@ -17230,10 +17230,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17.52000045776367</v>
+        <v>17.51000022888184</v>
       </c>
       <c r="D59" t="n">
-        <v>17.52000045776367</v>
+        <v>17.51000022888184</v>
       </c>
       <c r="E59" t="n">
         <v>17.97999954223633</v>
@@ -17245,67 +17245,67 @@
         <v>17.95000076293945</v>
       </c>
       <c r="H59" t="n">
-        <v>11242300</v>
+        <v>13414700</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.03204419400453951</v>
+        <v>-0.03259669282614586</v>
       </c>
       <c r="J59" t="n">
-        <v>18.25555589463976</v>
+        <v>18.25444475809733</v>
       </c>
       <c r="K59" t="n">
         <v>-1</v>
       </c>
       <c r="L59" t="n">
-        <v>-4.029214125942115</v>
+        <v>-4.078154877240373</v>
       </c>
       <c r="M59" t="n">
-        <v>18.29500026702881</v>
+        <v>18.29400024414063</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
       </c>
       <c r="O59" t="n">
-        <v>-4.236128985807332</v>
+        <v>-4.285558132699257</v>
       </c>
       <c r="P59" t="n">
-        <v>19.70500014378474</v>
+        <v>19.70461551959698</v>
       </c>
       <c r="Q59" t="n">
         <v>-1</v>
       </c>
       <c r="R59" t="n">
-        <v>-11.08855452970019</v>
+        <v>-11.13756971574765</v>
       </c>
       <c r="S59" t="n">
-        <v>21.37140007019043</v>
+        <v>21.37120006561279</v>
       </c>
       <c r="T59" t="n">
         <v>-1</v>
       </c>
       <c r="U59" t="n">
-        <v>-18.02127890441218</v>
+        <v>-18.06730471324256</v>
       </c>
       <c r="V59" t="n">
-        <v>22.83811103820801</v>
+        <v>22.83804437001546</v>
       </c>
       <c r="W59" t="n">
         <v>-1</v>
       </c>
       <c r="X59" t="n">
-        <v>-23.28612279512598</v>
+        <v>-23.32968644254377</v>
       </c>
       <c r="Y59" t="n">
-        <v>21.58623024940491</v>
+        <v>21.5861802482605</v>
       </c>
       <c r="Z59" t="n">
         <v>-1</v>
       </c>
       <c r="AA59" t="n">
-        <v>-18.83714638758351</v>
+        <v>-18.88328538212376</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.3734997253329962</v>
+        <v>0.3737957187016354</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -17457,7 +17457,7 @@
       <c r="BX59" t="inlineStr"/>
       <c r="BY59" t="inlineStr"/>
       <c r="BZ59" t="n">
-        <v>23.68</v>
+        <v>23.66</v>
       </c>
       <c r="CA59" t="n">
         <v>0.1</v>
@@ -17517,10 +17517,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>13.80000019073486</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="D60" t="n">
-        <v>13.80000019073486</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="E60" t="n">
         <v>14.15999984741211</v>
@@ -17532,67 +17532,67 @@
         <v>13.84000015258789</v>
       </c>
       <c r="H60" t="n">
-        <v>9764900</v>
+        <v>11975600</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.02748410156315895</v>
+        <v>-0.02114159590781628</v>
       </c>
       <c r="J60" t="n">
-        <v>14.03888893127441</v>
+        <v>14.04888894822862</v>
       </c>
       <c r="K60" t="n">
         <v>-1</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.70162141540545</v>
+        <v>-1.13096918547359</v>
       </c>
       <c r="M60" t="n">
-        <v>14.10200004577637</v>
+        <v>14.11100006103516</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>-2.141539172182568</v>
+        <v>-1.566152056952016</v>
       </c>
       <c r="P60" t="n">
-        <v>15.08615398406982</v>
+        <v>15.08961552840013</v>
       </c>
       <c r="Q60" t="n">
         <v>-1</v>
       </c>
       <c r="R60" t="n">
-        <v>-8.525392188712052</v>
+        <v>-7.949938703339265</v>
       </c>
       <c r="S60" t="n">
-        <v>15.64800006866455</v>
+        <v>15.64980007171631</v>
       </c>
       <c r="T60" t="n">
         <v>-1</v>
       </c>
       <c r="U60" t="n">
-        <v>-11.80981511899624</v>
+        <v>-11.24487035188404</v>
       </c>
       <c r="V60" t="n">
-        <v>15.58446671803792</v>
+        <v>15.58506671905518</v>
       </c>
       <c r="W60" t="n">
         <v>-1</v>
       </c>
       <c r="X60" t="n">
-        <v>-11.45028931428026</v>
+        <v>-10.87622149002377</v>
       </c>
       <c r="Y60" t="n">
-        <v>15.47715001583099</v>
+        <v>15.47760001659393</v>
       </c>
       <c r="Z60" t="n">
         <v>-1</v>
       </c>
       <c r="AA60" t="n">
-        <v>-10.83629623916959</v>
+        <v>-10.25740212674492</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.3308336396760026</v>
+        <v>0.3276951569943158</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -17744,13 +17744,13 @@
       <c r="BX60" t="inlineStr"/>
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="n">
-        <v>24.64</v>
+        <v>24.8</v>
       </c>
       <c r="CA60" t="n">
         <v>0.68</v>
       </c>
       <c r="CB60" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CC60" t="n">
         <v>8</v>
@@ -17785,13 +17785,13 @@
         <v>4</v>
       </c>
       <c r="CM60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CN60" t="n">
         <v>0</v>
       </c>
       <c r="CO60" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
@@ -17804,10 +17804,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>32.93000030517578</v>
+        <v>33.11000061035156</v>
       </c>
       <c r="D61" t="n">
-        <v>32.93000030517578</v>
+        <v>33.11000061035156</v>
       </c>
       <c r="E61" t="n">
         <v>33.86999893188477</v>
@@ -17819,91 +17819,91 @@
         <v>33.40000152587891</v>
       </c>
       <c r="H61" t="n">
-        <v>7597700</v>
+        <v>8765500</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.03854013707515969</v>
+        <v>-0.03328465371236311</v>
       </c>
       <c r="J61" t="n">
-        <v>34.16888893975152</v>
+        <v>34.18888897365994</v>
       </c>
       <c r="K61" t="n">
         <v>-1</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.625779687364767</v>
+        <v>-3.155669563113282</v>
       </c>
       <c r="M61" t="n">
-        <v>34.21100006103516</v>
+        <v>34.22900009155273</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.744408972476602</v>
+        <v>-3.269156207333459</v>
       </c>
       <c r="P61" t="n">
-        <v>35.76384632404034</v>
+        <v>35.77076941270094</v>
       </c>
       <c r="Q61" t="n">
         <v>-1</v>
       </c>
       <c r="R61" t="n">
-        <v>-7.923773056142605</v>
+        <v>-7.438388511164189</v>
       </c>
       <c r="S61" t="n">
-        <v>37.56439994812012</v>
+        <v>37.56799995422363</v>
       </c>
       <c r="T61" t="n">
         <v>-1</v>
       </c>
       <c r="U61" t="n">
-        <v>-12.33721195958106</v>
+        <v>-11.86648038038786</v>
       </c>
       <c r="V61" t="n">
-        <v>40.90926658630371</v>
+        <v>40.91046658833822</v>
       </c>
       <c r="W61" t="n">
         <v>-1</v>
       </c>
       <c r="X61" t="n">
-        <v>-19.50478937160746</v>
+        <v>-19.06716453879366</v>
       </c>
       <c r="Y61" t="n">
-        <v>40.658899974823</v>
+        <v>40.65979997634888</v>
       </c>
       <c r="Z61" t="n">
         <v>-1</v>
       </c>
       <c r="AA61" t="n">
-        <v>-19.00912143327327</v>
+        <v>-18.56821570787094</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.3788737174291846</v>
+        <v>0.3752055626758646</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="AE61" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="AF61" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="AG61" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="AH61" t="n">
-        <v>33.1</v>
+        <v>33.4</v>
       </c>
       <c r="AI61" t="n">
-        <v>33.3</v>
+        <v>33.6</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK61" t="n">
         <v>0</v>
@@ -18027,13 +18027,13 @@
       <c r="BX61" t="inlineStr"/>
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="n">
-        <v>16.3</v>
+        <v>16.39</v>
       </c>
       <c r="CA61" t="n">
         <v>0.1</v>
       </c>
       <c r="CB61" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CC61" t="n">
         <v>9</v>
@@ -18045,7 +18045,7 @@
         <v>7</v>
       </c>
       <c r="CF61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CG61" t="n">
         <v>2</v>
@@ -18054,7 +18054,7 @@
         <v>7</v>
       </c>
       <c r="CI61" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CJ61" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>0</v>
       </c>
       <c r="CO61" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62">
@@ -18087,82 +18087,82 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10.92000007629395</v>
+        <v>10.86999988555908</v>
       </c>
       <c r="D62" t="n">
-        <v>10.92000007629395</v>
+        <v>10.86999988555908</v>
       </c>
       <c r="E62" t="n">
         <v>11.14000034332275</v>
       </c>
       <c r="F62" t="n">
-        <v>10.88000011444092</v>
+        <v>10.86999988555908</v>
       </c>
       <c r="G62" t="n">
         <v>11.09000015258789</v>
       </c>
       <c r="H62" t="n">
-        <v>1806400</v>
+        <v>2088700</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.01621624315223202</v>
+        <v>-0.0207207646852523</v>
       </c>
       <c r="J62" t="n">
-        <v>11.61777793036567</v>
+        <v>11.61222235361735</v>
       </c>
       <c r="K62" t="n">
         <v>-1</v>
       </c>
       <c r="L62" t="n">
-        <v>-6.006121465344289</v>
+        <v>-6.391734893252851</v>
       </c>
       <c r="M62" t="n">
-        <v>11.67800016403198</v>
+        <v>11.6730001449585</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
       </c>
       <c r="O62" t="n">
-        <v>-6.490838132308495</v>
+        <v>-6.879124898719599</v>
       </c>
       <c r="P62" t="n">
-        <v>12.13230771284837</v>
+        <v>12.13038462858934</v>
       </c>
       <c r="Q62" t="n">
         <v>-1</v>
       </c>
       <c r="R62" t="n">
-        <v>-9.992391103553738</v>
+        <v>-10.39031145030417</v>
       </c>
       <c r="S62" t="n">
-        <v>12.83260009765625</v>
+        <v>12.83160009384155</v>
       </c>
       <c r="T62" t="n">
         <v>-1</v>
       </c>
       <c r="U62" t="n">
-        <v>-14.90422834661249</v>
+        <v>-15.28726108931597</v>
       </c>
       <c r="V62" t="n">
-        <v>11.92326667785644</v>
+        <v>11.92293334325155</v>
       </c>
       <c r="W62" t="n">
         <v>-1</v>
       </c>
       <c r="X62" t="n">
-        <v>-8.414360163777413</v>
+        <v>-8.831161152875449</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.12045001029968</v>
+        <v>12.12020000934601</v>
       </c>
       <c r="Z62" t="n">
         <v>-1</v>
       </c>
       <c r="AA62" t="n">
-        <v>-9.904334682174527</v>
+        <v>-10.31501231681726</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.336066498292959</v>
+        <v>0.337526512824357</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -18314,10 +18314,10 @@
       <c r="BX62" t="inlineStr"/>
       <c r="BY62" t="inlineStr"/>
       <c r="BZ62" t="n">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="CA62" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="CB62" t="n">
         <v>0.76</v>
@@ -18374,10 +18374,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>40.63999938964844</v>
+        <v>40.43999862670898</v>
       </c>
       <c r="D63" t="n">
-        <v>40.63999938964844</v>
+        <v>40.43999862670898</v>
       </c>
       <c r="E63" t="n">
         <v>41.31999969482422</v>
@@ -18389,67 +18389,67 @@
         <v>40.84000015258789</v>
       </c>
       <c r="H63" t="n">
-        <v>6333900</v>
+        <v>7366000</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.028448539070414</v>
+        <v>-0.03322981457088447</v>
       </c>
       <c r="J63" t="n">
-        <v>42.60222244262695</v>
+        <v>42.58000013563368</v>
       </c>
       <c r="K63" t="n">
         <v>-1</v>
       </c>
       <c r="L63" t="n">
-        <v>-4.605917110594572</v>
+        <v>-5.025837252484664</v>
       </c>
       <c r="M63" t="n">
-        <v>42.74600028991699</v>
+        <v>42.72600021362305</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>-4.926778847108467</v>
+        <v>-5.350375826158371</v>
       </c>
       <c r="P63" t="n">
-        <v>44.35846196688139</v>
+        <v>44.35076962984525</v>
       </c>
       <c r="Q63" t="n">
         <v>-1</v>
       </c>
       <c r="R63" t="n">
-        <v>-8.382758130814368</v>
+        <v>-8.817819929114753</v>
       </c>
       <c r="S63" t="n">
-        <v>46.38100021362305</v>
+        <v>46.37700019836426</v>
       </c>
       <c r="T63" t="n">
         <v>-1</v>
       </c>
       <c r="U63" t="n">
-        <v>-12.37791508922302</v>
+        <v>-12.80160757759549</v>
       </c>
       <c r="V63" t="n">
-        <v>45.67640009562174</v>
+        <v>45.67506675720215</v>
       </c>
       <c r="W63" t="n">
         <v>-1</v>
       </c>
       <c r="X63" t="n">
-        <v>-11.02626453798855</v>
+        <v>-11.46154456286084</v>
       </c>
       <c r="Y63" t="n">
-        <v>43.54900005340576</v>
+        <v>43.54800004959107</v>
       </c>
       <c r="Z63" t="n">
         <v>-1</v>
       </c>
       <c r="AA63" t="n">
-        <v>-6.679833429447081</v>
+        <v>-7.136955587725706</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.4926752221450961</v>
+        <v>0.4946153532231259</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -18597,13 +18597,13 @@
       <c r="BX63" t="inlineStr"/>
       <c r="BY63" t="inlineStr"/>
       <c r="BZ63" t="n">
-        <v>20.32</v>
+        <v>20.22</v>
       </c>
       <c r="CA63" t="n">
         <v>0.71</v>
       </c>
       <c r="CB63" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CC63" t="n">
         <v>10</v>
@@ -18653,10 +18653,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>26.70999908447266</v>
+        <v>26.71999931335449</v>
       </c>
       <c r="D64" t="n">
-        <v>26.70999908447266</v>
+        <v>26.71999931335449</v>
       </c>
       <c r="E64" t="n">
         <v>27.15999984741211</v>
@@ -18668,67 +18668,67 @@
         <v>27.14999961853027</v>
       </c>
       <c r="H64" t="n">
-        <v>3130500</v>
+        <v>3457600</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.02375736518196492</v>
+        <v>-0.0233918597485312</v>
       </c>
       <c r="J64" t="n">
-        <v>27.24333296881782</v>
+        <v>27.24444410536024</v>
       </c>
       <c r="K64" t="n">
         <v>-1</v>
       </c>
       <c r="L64" t="n">
-        <v>-1.957667532660577</v>
+        <v>-1.924960516638216</v>
       </c>
       <c r="M64" t="n">
-        <v>27.27799968719482</v>
+        <v>27.27899971008301</v>
       </c>
       <c r="N64" t="n">
         <v>-1</v>
       </c>
       <c r="O64" t="n">
-        <v>-2.082266329040273</v>
+        <v>-2.049196827851036</v>
       </c>
       <c r="P64" t="n">
-        <v>27.7353845009437</v>
+        <v>27.73576912513146</v>
       </c>
       <c r="Q64" t="n">
         <v>-1</v>
       </c>
       <c r="R64" t="n">
-        <v>-3.697029750700423</v>
+        <v>-3.662309875721376</v>
       </c>
       <c r="S64" t="n">
-        <v>29.19899993896484</v>
+        <v>29.19919994354248</v>
       </c>
       <c r="T64" t="n">
         <v>-1</v>
       </c>
       <c r="U64" t="n">
-        <v>-8.524267473868921</v>
+        <v>-8.490645753930236</v>
       </c>
       <c r="V64" t="n">
-        <v>31.93006665547689</v>
+        <v>31.93013332366943</v>
       </c>
       <c r="W64" t="n">
         <v>-1</v>
       </c>
       <c r="X64" t="n">
-        <v>-16.34843931686202</v>
+        <v>-16.31729488098545</v>
       </c>
       <c r="Y64" t="n">
-        <v>31.01335000991821</v>
+        <v>31.01340001106262</v>
       </c>
       <c r="Z64" t="n">
         <v>-1</v>
       </c>
       <c r="AA64" t="n">
-        <v>-13.87580162758723</v>
+        <v>-13.84369561601325</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.2581595510019785</v>
+        <v>0.2579365079311752</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -18960,10 +18960,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27.18000030517578</v>
+        <v>27.22999954223633</v>
       </c>
       <c r="D65" t="n">
-        <v>27.18000030517578</v>
+        <v>27.22999954223633</v>
       </c>
       <c r="E65" t="n">
         <v>27.93000030517578</v>
@@ -18975,67 +18975,67 @@
         <v>27.17000007629395</v>
       </c>
       <c r="H65" t="n">
-        <v>20456500</v>
+        <v>24886400</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.01841820942742689</v>
+        <v>-0.01661253098408233</v>
       </c>
       <c r="J65" t="n">
-        <v>28.12777794731988</v>
+        <v>28.13333341810439</v>
       </c>
       <c r="K65" t="n">
         <v>-1</v>
       </c>
       <c r="L65" t="n">
-        <v>-3.369543246249938</v>
+        <v>-3.210902392699555</v>
       </c>
       <c r="M65" t="n">
-        <v>28.17700023651123</v>
+        <v>28.18200016021729</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
       </c>
       <c r="O65" t="n">
-        <v>-3.538346605269764</v>
+        <v>-3.378044895922026</v>
       </c>
       <c r="P65" t="n">
-        <v>29.90653874323918</v>
+        <v>29.90846179081844</v>
       </c>
       <c r="Q65" t="n">
         <v>-1</v>
       </c>
       <c r="R65" t="n">
-        <v>-9.116863912176312</v>
+        <v>-8.95553327789116</v>
       </c>
       <c r="S65" t="n">
-        <v>31.19164016723633</v>
+        <v>31.19264015197754</v>
       </c>
       <c r="T65" t="n">
         <v>-1</v>
       </c>
       <c r="U65" t="n">
-        <v>-12.8612661615479</v>
+        <v>-12.70376790946306</v>
       </c>
       <c r="V65" t="n">
-        <v>28.80131547292073</v>
+        <v>28.8016488011678</v>
       </c>
       <c r="W65" t="n">
         <v>-1</v>
       </c>
       <c r="X65" t="n">
-        <v>-5.629309429527026</v>
+        <v>-5.45680308020335</v>
       </c>
       <c r="Y65" t="n">
-        <v>27.65245818138122</v>
+        <v>27.65270817756653</v>
       </c>
       <c r="Z65" t="n">
         <v>-1</v>
       </c>
       <c r="AA65" t="n">
-        <v>-1.708556516409652</v>
+        <v>-1.528633769306996</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.2347005127689267</v>
+        <v>0.2340938857574748</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -19187,13 +19187,13 @@
       <c r="BX65" t="inlineStr"/>
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="n">
-        <v>10.96</v>
+        <v>10.98</v>
       </c>
       <c r="CA65" t="n">
         <v>0.34</v>
       </c>
       <c r="CB65" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CC65" t="n">
         <v>9</v>
@@ -19202,7 +19202,7 @@
         <v>8</v>
       </c>
       <c r="CE65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CF65" t="n">
         <v>7</v>
@@ -19247,10 +19247,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>15</v>
+        <v>14.97999954223633</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>14.97999954223633</v>
       </c>
       <c r="E66" t="n">
         <v>15.31999969482422</v>
@@ -19262,67 +19262,67 @@
         <v>15.19999980926514</v>
       </c>
       <c r="H66" t="n">
-        <v>5652400</v>
+        <v>6066200</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.01896664241834844</v>
+        <v>-0.02027471683388604</v>
       </c>
       <c r="J66" t="n">
-        <v>15.68999979231093</v>
+        <v>15.68777751922607</v>
       </c>
       <c r="K66" t="n">
         <v>-1</v>
       </c>
       <c r="L66" t="n">
-        <v>-4.397704279442178</v>
+        <v>-4.51165231099391</v>
       </c>
       <c r="M66" t="n">
-        <v>15.77099981307983</v>
+        <v>15.76899976730347</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
       </c>
       <c r="O66" t="n">
-        <v>-4.888718674895919</v>
+        <v>-5.00348935703015</v>
       </c>
       <c r="P66" t="n">
-        <v>16.65807698323177</v>
+        <v>16.65730773485624</v>
       </c>
       <c r="Q66" t="n">
         <v>-1</v>
       </c>
       <c r="R66" t="n">
-        <v>-9.953591791542369</v>
+        <v>-10.0695035435412</v>
       </c>
       <c r="S66" t="n">
-        <v>17.4260000038147</v>
+        <v>17.42559999465943</v>
       </c>
       <c r="T66" t="n">
         <v>-1</v>
       </c>
       <c r="U66" t="n">
-        <v>-13.92172617516139</v>
+        <v>-14.03452651944622</v>
       </c>
       <c r="V66" t="n">
-        <v>16.06152577082316</v>
+        <v>16.06139243443807</v>
       </c>
       <c r="W66" t="n">
         <v>-1</v>
       </c>
       <c r="X66" t="n">
-        <v>-6.609121611294815</v>
+        <v>-6.732871366016001</v>
       </c>
       <c r="Y66" t="n">
-        <v>15.74045532226562</v>
+        <v>15.74035531997681</v>
       </c>
       <c r="Z66" t="n">
         <v>-1</v>
       </c>
       <c r="AA66" t="n">
-        <v>-4.70415440408649</v>
+        <v>-4.830613809432093</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.1955020024263074</v>
+        <v>0.1963079804623834</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -19476,7 +19476,7 @@
       <c r="BX66" t="inlineStr"/>
       <c r="BY66" t="inlineStr"/>
       <c r="BZ66" t="n">
-        <v>23.08</v>
+        <v>23.05</v>
       </c>
       <c r="CA66" t="n">
         <v>0.85</v>
@@ -19536,10 +19536,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.15999984741211</v>
+        <v>18.22999954223633</v>
       </c>
       <c r="D67" t="n">
-        <v>18.15999984741211</v>
+        <v>18.22999954223633</v>
       </c>
       <c r="E67" t="n">
         <v>18.43000030517578</v>
@@ -19551,67 +19551,67 @@
         <v>18.1299991607666</v>
       </c>
       <c r="H67" t="n">
-        <v>6173700</v>
+        <v>6815900</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.02365594220610712</v>
+        <v>-0.0198925178303766</v>
       </c>
       <c r="J67" t="n">
-        <v>18.71555561489529</v>
+        <v>18.72333335876465</v>
       </c>
       <c r="K67" t="n">
         <v>-1</v>
       </c>
       <c r="L67" t="n">
-        <v>-2.96841717614318</v>
+        <v>-2.6348610425044</v>
       </c>
       <c r="M67" t="n">
-        <v>18.79400005340576</v>
+        <v>18.80100002288818</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
       </c>
       <c r="O67" t="n">
-        <v>-3.373418134468721</v>
+        <v>-3.037075048969325</v>
       </c>
       <c r="P67" t="n">
-        <v>18.63538455963135</v>
+        <v>18.63807685558612</v>
       </c>
       <c r="Q67" t="n">
         <v>-1</v>
       </c>
       <c r="R67" t="n">
-        <v>-2.550978815049699</v>
+        <v>-2.189481868283471</v>
       </c>
       <c r="S67" t="n">
-        <v>18.69859996795654</v>
+        <v>18.69999996185303</v>
       </c>
       <c r="T67" t="n">
         <v>-1</v>
       </c>
       <c r="U67" t="n">
-        <v>-2.880430200482513</v>
+        <v>-2.513371233023927</v>
       </c>
       <c r="V67" t="n">
-        <v>21.36312123616537</v>
+        <v>21.36358790079753</v>
       </c>
       <c r="W67" t="n">
         <v>-1</v>
       </c>
       <c r="X67" t="n">
-        <v>-14.99369569335557</v>
+        <v>-14.6678936755011</v>
       </c>
       <c r="Y67" t="n">
-        <v>22.25014093399048</v>
+        <v>22.2504909324646</v>
       </c>
       <c r="Z67" t="n">
         <v>-1</v>
       </c>
       <c r="AA67" t="n">
-        <v>-18.38254013182477</v>
+        <v>-18.06922553947864</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5132674563437077</v>
+        <v>0.5119189527389436</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -19761,13 +19761,13 @@
       <c r="BX67" t="inlineStr"/>
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="n">
-        <v>16.21</v>
+        <v>16.28</v>
       </c>
       <c r="CA67" t="n">
         <v>0.37</v>
       </c>
       <c r="CB67" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CC67" t="n">
         <v>10</v>
@@ -19821,10 +19821,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>41.08000183105469</v>
+        <v>41.22000122070312</v>
       </c>
       <c r="D68" t="n">
-        <v>41.08000183105469</v>
+        <v>41.22000122070312</v>
       </c>
       <c r="E68" t="n">
         <v>41.25</v>
@@ -19836,67 +19836,67 @@
         <v>40.18000030517578</v>
       </c>
       <c r="H68" t="n">
-        <v>5405700</v>
+        <v>6497300</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01607720803790591</v>
+        <v>0.01953996808222169</v>
       </c>
       <c r="J68" t="n">
-        <v>41.40444480048286</v>
+        <v>41.42000028822157</v>
       </c>
       <c r="K68" t="n">
         <v>-1</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.7835945415801966</v>
+        <v>-0.4828562678096375</v>
       </c>
       <c r="M68" t="n">
-        <v>41.49000015258789</v>
+        <v>41.50400009155273</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.9881858761758249</v>
+        <v>-0.6842686734366358</v>
       </c>
       <c r="P68" t="n">
-        <v>42.39807715782752</v>
+        <v>42.40346174973708</v>
       </c>
       <c r="Q68" t="n">
         <v>-1</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.108809208177716</v>
+        <v>-2.790952625563146</v>
       </c>
       <c r="S68" t="n">
-        <v>45.47379989624024</v>
+        <v>45.47659988403321</v>
       </c>
       <c r="T68" t="n">
         <v>-1</v>
       </c>
       <c r="U68" t="n">
-        <v>-9.662262830929217</v>
+        <v>-9.359975623033701</v>
       </c>
       <c r="V68" t="n">
-        <v>49.41519996643066</v>
+        <v>49.41613329569498</v>
       </c>
       <c r="W68" t="n">
         <v>-1</v>
       </c>
       <c r="X68" t="n">
-        <v>-16.86768067525447</v>
+        <v>-16.58594375636</v>
       </c>
       <c r="Y68" t="n">
-        <v>49.71324996948242</v>
+        <v>49.71394996643066</v>
       </c>
       <c r="Z68" t="n">
         <v>-1</v>
       </c>
       <c r="AA68" t="n">
-        <v>-17.36609081829782</v>
+        <v>-17.08564447496744</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.2252057983454621</v>
+        <v>0.2282174071084935</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -20048,10 +20048,10 @@
       <c r="BX68" t="inlineStr"/>
       <c r="BY68" t="inlineStr"/>
       <c r="BZ68" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="CA68" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CB68" t="n">
         <v>1.08</v>
@@ -20069,7 +20069,7 @@
         <v>10</v>
       </c>
       <c r="CG68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CH68" t="n">
         <v>3</v>
@@ -20089,13 +20089,13 @@
         <v>5</v>
       </c>
       <c r="CM68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CN68" t="n">
         <v>0</v>
       </c>
       <c r="CO68" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
@@ -20108,10 +20108,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>38.88000106811523</v>
+        <v>38.79000091552734</v>
       </c>
       <c r="D69" t="n">
-        <v>38.88000106811523</v>
+        <v>38.79000091552734</v>
       </c>
       <c r="E69" t="n">
         <v>39.31000137329102</v>
@@ -20123,67 +20123,67 @@
         <v>39.04000091552734</v>
       </c>
       <c r="H69" t="n">
-        <v>1167900</v>
+        <v>1433900</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.009426724379229645</v>
+        <v>-0.01171972189739257</v>
       </c>
       <c r="J69" t="n">
-        <v>39.11333338419596</v>
+        <v>39.10333336724175</v>
       </c>
       <c r="K69" t="n">
         <v>-1</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.5965544122480916</v>
+        <v>-0.8012934569330057</v>
       </c>
       <c r="M69" t="n">
-        <v>39.0439998626709</v>
+        <v>39.03499984741211</v>
       </c>
       <c r="N69" t="n">
         <v>-1</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.4200358445151582</v>
+        <v>-0.6276391260214345</v>
       </c>
       <c r="P69" t="n">
-        <v>39.90269235464243</v>
+        <v>39.89923081031213</v>
       </c>
       <c r="Q69" t="n">
         <v>-1</v>
       </c>
       <c r="R69" t="n">
-        <v>-2.562963113961927</v>
+        <v>-2.780078393135582</v>
       </c>
       <c r="S69" t="n">
-        <v>41.73340019226075</v>
+        <v>41.73160018920898</v>
       </c>
       <c r="T69" t="n">
         <v>-1</v>
       </c>
       <c r="U69" t="n">
-        <v>-6.837207395036699</v>
+        <v>-7.048853291856952</v>
       </c>
       <c r="V69" t="n">
-        <v>41.83220013936361</v>
+        <v>41.83160013834635</v>
       </c>
       <c r="W69" t="n">
         <v>-1</v>
       </c>
       <c r="X69" t="n">
-        <v>-7.057240741374223</v>
+        <v>-7.271056361123572</v>
       </c>
       <c r="Y69" t="n">
-        <v>40.2035001373291</v>
+        <v>40.20305013656616</v>
       </c>
       <c r="Z69" t="n">
         <v>-1</v>
       </c>
       <c r="AA69" t="n">
-        <v>-3.291999613697796</v>
+        <v>-3.514781132871304</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.2281709004249645</v>
+        <v>0.2286199324729443</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -20335,7 +20335,7 @@
       <c r="BX69" t="inlineStr"/>
       <c r="BY69" t="inlineStr"/>
       <c r="BZ69" t="n">
-        <v>8.550000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="CA69" t="n">
         <v>0.25</v>
@@ -20391,10 +20391,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22.29000091552734</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="D70" t="n">
-        <v>22.29000091552734</v>
+        <v>22.34000015258789</v>
       </c>
       <c r="E70" t="n">
         <v>22.34000015258789</v>
@@ -20406,67 +20406,67 @@
         <v>21.79999923706055</v>
       </c>
       <c r="H70" t="n">
-        <v>4070300</v>
+        <v>4917900</v>
       </c>
       <c r="I70" t="n">
-        <v>0.01226160091511153</v>
+        <v>0.01453222925394604</v>
       </c>
       <c r="J70" t="n">
-        <v>22.2966668870714</v>
+        <v>22.3022223578559</v>
       </c>
       <c r="K70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>-0.02989671764759364</v>
+        <v>0.1693902702870323</v>
       </c>
       <c r="M70" t="n">
-        <v>22.33200016021728</v>
+        <v>22.33700008392334</v>
       </c>
       <c r="N70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.1880675460712129</v>
+        <v>0.01343093814424408</v>
       </c>
       <c r="P70" t="n">
-        <v>23.14423084259033</v>
+        <v>23.14615389016958</v>
       </c>
       <c r="Q70" t="n">
         <v>-1</v>
       </c>
       <c r="R70" t="n">
-        <v>-3.690897886703682</v>
+        <v>-3.482884203600124</v>
       </c>
       <c r="S70" t="n">
-        <v>24.95380001068115</v>
+        <v>24.95479999542236</v>
       </c>
       <c r="T70" t="n">
         <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>-10.67492363493177</v>
+        <v>-10.47814385735058</v>
       </c>
       <c r="V70" t="n">
-        <v>24.81146668752034</v>
+        <v>24.81180001576741</v>
       </c>
       <c r="W70" t="n">
         <v>-1</v>
       </c>
       <c r="X70" t="n">
-        <v>-10.16250189377658</v>
+        <v>-9.962194849260202</v>
       </c>
       <c r="Y70" t="n">
-        <v>24.33365001678467</v>
+        <v>24.33390001296997</v>
       </c>
       <c r="Z70" t="n">
         <v>-1</v>
       </c>
       <c r="AA70" t="n">
-        <v>-8.398448649699782</v>
+        <v>-8.193918193628356</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.3776100157579323</v>
+        <v>0.3786152574425538</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -20618,13 +20618,13 @@
       <c r="BX70" t="inlineStr"/>
       <c r="BY70" t="inlineStr"/>
       <c r="BZ70" t="n">
-        <v>2229</v>
+        <v>2234</v>
       </c>
       <c r="CA70" t="n">
         <v>-0.06</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CC70" t="n">
         <v>1</v>
@@ -20678,10 +20678,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>33.29999923706055</v>
+        <v>33.61999893188477</v>
       </c>
       <c r="D71" t="n">
-        <v>33.29999923706055</v>
+        <v>33.61999893188477</v>
       </c>
       <c r="E71" t="n">
         <v>35.09999847412109</v>
@@ -20693,67 +20693,67 @@
         <v>34.06999969482422</v>
       </c>
       <c r="H71" t="n">
-        <v>6647300</v>
+        <v>8422800</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.03225808239679617</v>
+        <v>-0.02295846902152077</v>
       </c>
       <c r="J71" t="n">
-        <v>32.55333307054308</v>
+        <v>32.58888859219022</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>2.293670405114725</v>
+        <v>3.163993570316635</v>
       </c>
       <c r="M71" t="n">
-        <v>32.52499980926514</v>
+        <v>32.55699977874756</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2.382780729716221</v>
+        <v>3.265040268947344</v>
       </c>
       <c r="P71" t="n">
-        <v>32.50230752504789</v>
+        <v>32.51461520561805</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>2.454261782483956</v>
+        <v>3.399651877398572</v>
       </c>
       <c r="S71" t="n">
-        <v>33.42339988708496</v>
+        <v>33.42979988098145</v>
       </c>
       <c r="T71" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>-0.3692043611401059</v>
+        <v>0.5689506116712445</v>
       </c>
       <c r="V71" t="n">
-        <v>39.24659993489583</v>
+        <v>39.24873326619466</v>
       </c>
       <c r="W71" t="n">
         <v>-1</v>
       </c>
       <c r="X71" t="n">
-        <v>-15.15188757166174</v>
+        <v>-14.34118725854009</v>
       </c>
       <c r="Y71" t="n">
-        <v>40.22189998626709</v>
+        <v>40.22349998474121</v>
       </c>
       <c r="Z71" t="n">
         <v>-1</v>
       </c>
       <c r="AA71" t="n">
-        <v>-17.2092833793776</v>
+        <v>-16.41702252504502</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4909660200397436</v>
+        <v>0.4865543426798651</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -20905,13 +20905,13 @@
       <c r="BX71" t="inlineStr"/>
       <c r="BY71" t="inlineStr"/>
       <c r="BZ71" t="n">
-        <v>21.62</v>
+        <v>21.83</v>
       </c>
       <c r="CA71" t="n">
         <v>0.17</v>
       </c>
       <c r="CB71" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="CC71" t="n">
         <v>7</v>
@@ -20965,10 +20965,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>24.84000015258789</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="D72" t="n">
-        <v>24.84000015258789</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="E72" t="n">
         <v>25.46999931335449</v>
@@ -20980,67 +20980,67 @@
         <v>25.04999923706055</v>
       </c>
       <c r="H72" t="n">
-        <v>5204400</v>
+        <v>6188400</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.03383893282245176</v>
+        <v>-0.03072730596306494</v>
       </c>
       <c r="J72" t="n">
-        <v>26.80333349439833</v>
+        <v>26.81222237481011</v>
       </c>
       <c r="K72" t="n">
         <v>-1</v>
       </c>
       <c r="L72" t="n">
-        <v>-7.324959569751874</v>
+        <v>-7.057312415452349</v>
       </c>
       <c r="M72" t="n">
-        <v>27.03800010681152</v>
+        <v>27.04600009918213</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
       </c>
       <c r="O72" t="n">
-        <v>-8.129299302983226</v>
+        <v>-7.860681857175898</v>
       </c>
       <c r="P72" t="n">
-        <v>28.5461540222168</v>
+        <v>28.54923094235934</v>
       </c>
       <c r="Q72" t="n">
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>-12.98302344597627</v>
+        <v>-12.71218434357401</v>
       </c>
       <c r="S72" t="n">
-        <v>28.89060009002685</v>
+        <v>28.89220008850098</v>
       </c>
       <c r="T72" t="n">
         <v>-1</v>
       </c>
       <c r="U72" t="n">
-        <v>-14.02047698842104</v>
+        <v>-13.74834730494601</v>
       </c>
       <c r="V72" t="n">
-        <v>25.27886666615804</v>
+        <v>25.27939999898275</v>
       </c>
       <c r="W72" t="n">
         <v>-1</v>
       </c>
       <c r="X72" t="n">
-        <v>-1.736100432689418</v>
+        <v>-1.421710652560045</v>
       </c>
       <c r="Y72" t="n">
-        <v>24.02454999923706</v>
+        <v>24.02494999885559</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.394236950855383</v>
+        <v>3.725502352683317</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.2790625485254272</v>
+        <v>0.2764969545677853</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -21192,13 +21192,13 @@
       <c r="BX72" t="inlineStr"/>
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="n">
-        <v>9.23</v>
+        <v>9.26</v>
       </c>
       <c r="CA72" t="n">
         <v>0.5</v>
       </c>
       <c r="CB72" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CC72" t="n">
         <v>4</v>
@@ -21248,10 +21248,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>11.42000007629395</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="D73" t="n">
-        <v>11.42000007629395</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="E73" t="n">
         <v>11.89000034332275</v>
@@ -21263,67 +21263,67 @@
         <v>11.80000019073486</v>
       </c>
       <c r="H73" t="n">
-        <v>11883100</v>
+        <v>13107700</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.05149500726939038</v>
+        <v>-0.04817275129100496</v>
       </c>
       <c r="J73" t="n">
-        <v>10.72666666242811</v>
+        <v>10.73111110263401</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>6.463642766996236</v>
+        <v>6.792296981568448</v>
       </c>
       <c r="M73" t="n">
-        <v>10.63400001525879</v>
+        <v>10.63800001144409</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>7.39138668334889</v>
+        <v>7.72701659915956</v>
       </c>
       <c r="P73" t="n">
-        <v>9.546153802138109</v>
+        <v>9.547692262209379</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>19.62933253533103</v>
+        <v>20.02900516082487</v>
       </c>
       <c r="S73" t="n">
-        <v>8.342399978637696</v>
+        <v>8.343199977874756</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>36.89106378904189</v>
+        <v>37.35736969673059</v>
       </c>
       <c r="V73" t="n">
-        <v>6.82399998664856</v>
+        <v>6.824266653060914</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>67.35052899527625</v>
+        <v>67.93013258071878</v>
       </c>
       <c r="Y73" t="n">
-        <v>6.223849991559982</v>
+        <v>6.224049991369247</v>
       </c>
       <c r="Z73" t="n">
         <v>1</v>
       </c>
       <c r="AA73" t="n">
-        <v>83.48771406412978</v>
+        <v>84.12448572936114</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.618869533533267</v>
+        <v>0.6157931037298374</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -21475,7 +21475,7 @@
       <c r="BX73" t="inlineStr"/>
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="n">
-        <v>-5.49</v>
+        <v>-5.51</v>
       </c>
       <c r="CA73" t="n">
         <v>-0.03</v>
@@ -21535,103 +21535,103 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>82.11000061035156</v>
+        <v>81.79000091552734</v>
       </c>
       <c r="D74" t="n">
-        <v>82.11000061035156</v>
+        <v>81.79000091552734</v>
       </c>
       <c r="E74" t="n">
         <v>83.79000091552734</v>
       </c>
       <c r="F74" t="n">
-        <v>81.80000305175781</v>
+        <v>81.79000091552734</v>
       </c>
       <c r="G74" t="n">
         <v>83.61000061035156</v>
       </c>
       <c r="H74" t="n">
-        <v>16056000</v>
+        <v>19158300</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.03399999281939337</v>
+        <v>-0.03776469511144298</v>
       </c>
       <c r="J74" t="n">
-        <v>83.19999864366319</v>
+        <v>83.16444312201605</v>
       </c>
       <c r="K74" t="n">
         <v>-1</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.31009381139533</v>
+        <v>-1.652680105693937</v>
       </c>
       <c r="M74" t="n">
-        <v>83.14299850463867</v>
+        <v>83.11099853515626</v>
       </c>
       <c r="N74" t="n">
         <v>-1</v>
       </c>
       <c r="O74" t="n">
-        <v>-1.242435217475918</v>
+        <v>-1.589437791521811</v>
       </c>
       <c r="P74" t="n">
-        <v>82.22346144456129</v>
+        <v>82.21115376399113</v>
       </c>
       <c r="Q74" t="n">
         <v>-1</v>
       </c>
       <c r="R74" t="n">
-        <v>-0.1379908267255723</v>
+        <v>-0.5122818853422513</v>
       </c>
       <c r="S74" t="n">
-        <v>83.13240036010743</v>
+        <v>83.12600036621093</v>
       </c>
       <c r="T74" t="n">
         <v>-1</v>
       </c>
       <c r="U74" t="n">
-        <v>-1.229845096890141</v>
+        <v>-1.607198042487131</v>
       </c>
       <c r="V74" t="n">
-        <v>77.99013338724772</v>
+        <v>77.98800005594889</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>5.28254927151783</v>
+        <v>4.875110089822647</v>
       </c>
       <c r="Y74" t="n">
-        <v>72.79550004959107</v>
+        <v>72.79390005111695</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
       <c r="AA74" t="n">
-        <v>12.79543454528796</v>
+        <v>12.35831691679275</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.331134331136372</v>
+        <v>0.3344226325303087</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
       </c>
       <c r="AD74" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AE74" t="n">
         <v>80.8</v>
       </c>
-      <c r="AE74" t="n">
+      <c r="AF74" t="n">
         <v>81.7</v>
       </c>
-      <c r="AF74" t="n">
+      <c r="AG74" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="AG74" t="n">
+      <c r="AH74" t="n">
         <v>82.2</v>
       </c>
-      <c r="AH74" t="n">
+      <c r="AI74" t="n">
         <v>82.7</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>82.8</v>
       </c>
       <c r="AJ74" t="n">
         <v>2</v>
@@ -21758,13 +21758,13 @@
       <c r="BX74" t="inlineStr"/>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="n">
-        <v>23.39</v>
+        <v>23.3</v>
       </c>
       <c r="CA74" t="n">
         <v>0.19</v>
       </c>
       <c r="CB74" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CC74" t="n">
         <v>1</v>
@@ -21814,10 +21814,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.920000076293945</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="D75" t="n">
-        <v>2.920000076293945</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="E75" t="n">
         <v>2.940000057220459</v>
@@ -21829,67 +21829,67 @@
         <v>2.940000057220459</v>
       </c>
       <c r="H75" t="n">
-        <v>11121200</v>
+        <v>12222800</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.01683500061772081</v>
+        <v>-0.01010100037063255</v>
       </c>
       <c r="J75" t="n">
-        <v>3.136666668785943</v>
+        <v>3.138888888888889</v>
       </c>
       <c r="K75" t="n">
         <v>-1</v>
       </c>
       <c r="L75" t="n">
-        <v>-6.907542795290365</v>
+        <v>-6.336281362888031</v>
       </c>
       <c r="M75" t="n">
-        <v>3.159999990463257</v>
+        <v>3.161999988555908</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
       </c>
       <c r="O75" t="n">
-        <v>-7.59493401562091</v>
+        <v>-7.020870719131055</v>
       </c>
       <c r="P75" t="n">
-        <v>3.478846174020034</v>
+        <v>3.479615404055669</v>
       </c>
       <c r="Q75" t="n">
         <v>-1</v>
       </c>
       <c r="R75" t="n">
-        <v>-16.06412211898135</v>
+        <v>-15.50790199992392</v>
       </c>
       <c r="S75" t="n">
-        <v>3.70800000667572</v>
+        <v>3.708400006294251</v>
       </c>
       <c r="T75" t="n">
         <v>-1</v>
       </c>
       <c r="U75" t="n">
-        <v>-21.2513465200403</v>
+        <v>-20.72052496412442</v>
       </c>
       <c r="V75" t="n">
-        <v>3.748994790712992</v>
+        <v>3.749128123919169</v>
       </c>
       <c r="W75" t="n">
         <v>-1</v>
       </c>
       <c r="X75" t="n">
-        <v>-22.1124530893623</v>
+        <v>-21.58176621216359</v>
       </c>
       <c r="Y75" t="n">
-        <v>3.721046098470688</v>
+        <v>3.72114609837532</v>
       </c>
       <c r="Z75" t="n">
         <v>-1</v>
       </c>
       <c r="AA75" t="n">
-        <v>-21.52744150377402</v>
+        <v>-20.99208202268423</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.4398829327696821</v>
+        <v>0.4399980059661048</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -22041,13 +22041,13 @@
       <c r="BX75" t="inlineStr"/>
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="n">
-        <v>11.68</v>
+        <v>11.76</v>
       </c>
       <c r="CA75" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CB75" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CC75" t="n">
         <v>6</v>
@@ -22078,13 +22078,13 @@
         <v>1</v>
       </c>
       <c r="CM75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CN75" t="n">
         <v>0</v>
       </c>
       <c r="CO75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>29.28000068664551</v>
+        <v>29.47999954223633</v>
       </c>
       <c r="D76" t="n">
-        <v>29.28000068664551</v>
+        <v>29.47999954223633</v>
       </c>
       <c r="E76" t="n">
         <v>30.05999946594238</v>
@@ -22112,67 +22112,67 @@
         <v>29.35000038146973</v>
       </c>
       <c r="H76" t="n">
-        <v>10419400</v>
+        <v>12162100</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.02821103543965275</v>
+        <v>-0.02157317081431132</v>
       </c>
       <c r="J76" t="n">
-        <v>30.87777773539225</v>
+        <v>30.8999998304579</v>
       </c>
       <c r="K76" t="n">
         <v>-1</v>
       </c>
       <c r="L76" t="n">
-        <v>-5.174520855868998</v>
+        <v>-4.595470213633752</v>
       </c>
       <c r="M76" t="n">
-        <v>31.13099994659424</v>
+        <v>31.15099983215332</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
       </c>
       <c r="O76" t="n">
-        <v>-5.945839398426488</v>
+        <v>-5.364194725436152</v>
       </c>
       <c r="P76" t="n">
-        <v>32.31192288031945</v>
+        <v>32.31961514399602</v>
       </c>
       <c r="Q76" t="n">
         <v>-1</v>
       </c>
       <c r="R76" t="n">
-        <v>-9.383292368281264</v>
+        <v>-8.786043983222374</v>
       </c>
       <c r="S76" t="n">
-        <v>32.33379993438721</v>
+        <v>32.33779991149903</v>
       </c>
       <c r="T76" t="n">
         <v>-1</v>
       </c>
       <c r="U76" t="n">
-        <v>-9.444603646767682</v>
+        <v>-8.837337039266206</v>
       </c>
       <c r="V76" t="n">
-        <v>28.65877454121907</v>
+        <v>28.66010786692301</v>
       </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
       <c r="X76" t="n">
-        <v>2.167664721786838</v>
+        <v>2.860741763849263</v>
       </c>
       <c r="Y76" t="n">
-        <v>26.97180195808411</v>
+        <v>26.97280195236206</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
       <c r="AA76" t="n">
-        <v>8.557821728590801</v>
+        <v>9.295280461786456</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.2819079868106652</v>
+        <v>0.2776162414457831</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -22324,13 +22324,13 @@
       <c r="BX76" t="inlineStr"/>
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="n">
-        <v>11.67</v>
+        <v>11.75</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="CB76" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CC76" t="n">
         <v>5</v>
@@ -22361,13 +22361,13 @@
         <v>6</v>
       </c>
       <c r="CM76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CN76" t="n">
         <v>0</v>
       </c>
       <c r="CO76" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77">
@@ -22380,10 +22380,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>20.11000061035156</v>
+        <v>20.5</v>
       </c>
       <c r="D77" t="n">
-        <v>20.11000061035156</v>
+        <v>20.5</v>
       </c>
       <c r="E77" t="n">
         <v>21.18000030517578</v>
@@ -22395,67 +22395,67 @@
         <v>21.18000030517578</v>
       </c>
       <c r="H77" t="n">
-        <v>4052100</v>
+        <v>5222200</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.06028032855952481</v>
+        <v>-0.04205605769034515</v>
       </c>
       <c r="J77" t="n">
-        <v>21.82444445292155</v>
+        <v>21.86777771843804</v>
       </c>
       <c r="K77" t="n">
         <v>-1</v>
       </c>
       <c r="L77" t="n">
-        <v>-7.855612756917083</v>
+        <v>-6.254763223081356</v>
       </c>
       <c r="M77" t="n">
-        <v>21.87399997711181</v>
+        <v>21.91299991607666</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
       </c>
       <c r="O77" t="n">
-        <v>-8.064365770348539</v>
+        <v>-6.448226721527075</v>
       </c>
       <c r="P77" t="n">
-        <v>23.52615393125094</v>
+        <v>23.54115390777588</v>
       </c>
       <c r="Q77" t="n">
         <v>-1</v>
       </c>
       <c r="R77" t="n">
-        <v>-14.52066211452239</v>
+        <v>-12.91845726717481</v>
       </c>
       <c r="S77" t="n">
-        <v>25.05080005645752</v>
+        <v>25.05860004425049</v>
       </c>
       <c r="T77" t="n">
         <v>-1</v>
       </c>
       <c r="U77" t="n">
-        <v>-19.72312035931296</v>
+        <v>-18.1917586624973</v>
       </c>
       <c r="V77" t="n">
-        <v>28.90300000508626</v>
+        <v>28.90560000101725</v>
       </c>
       <c r="W77" t="n">
         <v>-1</v>
       </c>
       <c r="X77" t="n">
-        <v>-30.42244539731978</v>
+        <v>-29.07948633040463</v>
       </c>
       <c r="Y77" t="n">
-        <v>28.76310001373291</v>
+        <v>28.76505001068115</v>
       </c>
       <c r="Z77" t="n">
         <v>-1</v>
       </c>
       <c r="AA77" t="n">
-        <v>-30.08402918756996</v>
+        <v>-28.73295894709775</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.4825366215117649</v>
+        <v>0.4687054097933242</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -22607,13 +22607,13 @@
       <c r="BX77" t="inlineStr"/>
       <c r="BY77" t="inlineStr"/>
       <c r="BZ77" t="n">
-        <v>8.109999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="CA77" t="n">
         <v>0.04</v>
       </c>
       <c r="CB77" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CC77" t="n">
         <v>8</v>
@@ -22648,13 +22648,13 @@
         <v>1</v>
       </c>
       <c r="CM77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
       </c>
       <c r="CO77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -22667,10 +22667,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.66999816894531</v>
+        <v>33.75</v>
       </c>
       <c r="D78" t="n">
-        <v>33.66999816894531</v>
+        <v>33.75</v>
       </c>
       <c r="E78" t="n">
         <v>33.97999954223633</v>
@@ -22682,67 +22682,67 @@
         <v>33.2599983215332</v>
       </c>
       <c r="H78" t="n">
-        <v>6591400</v>
+        <v>7623600</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.003846185534013058</v>
+        <v>-0.001479267402045514</v>
       </c>
       <c r="J78" t="n">
-        <v>33.80777740478516</v>
+        <v>33.81666649712457</v>
       </c>
       <c r="K78" t="n">
         <v>-1</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.4075371006801011</v>
+        <v>-0.197140948621396</v>
       </c>
       <c r="M78" t="n">
-        <v>33.95599975585937</v>
+        <v>33.96399993896485</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.8422711419789939</v>
+        <v>-0.630078728504935</v>
       </c>
       <c r="P78" t="n">
-        <v>35.94346149151142</v>
+        <v>35.94653848501352</v>
       </c>
       <c r="Q78" t="n">
         <v>-1</v>
       </c>
       <c r="R78" t="n">
-        <v>-6.325109569936719</v>
+        <v>-6.11057024566991</v>
       </c>
       <c r="S78" t="n">
-        <v>38.36679985046387</v>
+        <v>38.36839988708496</v>
       </c>
       <c r="T78" t="n">
         <v>-1</v>
       </c>
       <c r="U78" t="n">
-        <v>-12.24183851617682</v>
+        <v>-12.03698851314241</v>
       </c>
       <c r="V78" t="n">
-        <v>37.01133338928223</v>
+        <v>37.01186673482259</v>
       </c>
       <c r="W78" t="n">
         <v>-1</v>
       </c>
       <c r="X78" t="n">
-        <v>-9.027870423345792</v>
+        <v>-8.813029502653173</v>
       </c>
       <c r="Y78" t="n">
-        <v>36.11095006942749</v>
+        <v>36.11135007858277</v>
       </c>
       <c r="Z78" t="n">
         <v>-1</v>
       </c>
       <c r="AA78" t="n">
-        <v>-6.759589254198969</v>
+        <v>-6.539080021777577</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3135560565561536</v>
+        <v>0.3137959548388711</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -22894,13 +22894,13 @@
       <c r="BX78" t="inlineStr"/>
       <c r="BY78" t="inlineStr"/>
       <c r="BZ78" t="n">
-        <v>17.09</v>
+        <v>17.13</v>
       </c>
       <c r="CA78" t="n">
         <v>0.1</v>
       </c>
       <c r="CB78" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CC78" t="n">
         <v>5</v>
@@ -22954,10 +22954,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>41.93999862670898</v>
+        <v>41.77999877929688</v>
       </c>
       <c r="D79" t="n">
-        <v>41.93999862670898</v>
+        <v>41.77999877929688</v>
       </c>
       <c r="E79" t="n">
         <v>42.45000076293945</v>
@@ -22969,67 +22969,67 @@
         <v>41.59999847412109</v>
       </c>
       <c r="H79" t="n">
-        <v>5015600</v>
+        <v>6565000</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.001428604125976562</v>
+        <v>-0.005238124302455405</v>
       </c>
       <c r="J79" t="n">
-        <v>43.07666651407877</v>
+        <v>43.05888875325521</v>
       </c>
       <c r="K79" t="n">
         <v>-1</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.638709025913812</v>
+        <v>-2.970095167311193</v>
       </c>
       <c r="M79" t="n">
-        <v>43.01599998474121</v>
+        <v>43</v>
       </c>
       <c r="N79" t="n">
         <v>-1</v>
       </c>
       <c r="O79" t="n">
-        <v>-2.50139798775784</v>
+        <v>-2.837212141170058</v>
       </c>
       <c r="P79" t="n">
-        <v>43.59730793879582</v>
+        <v>43.59115409851074</v>
       </c>
       <c r="Q79" t="n">
         <v>-1</v>
       </c>
       <c r="R79" t="n">
-        <v>-3.801402862794775</v>
+        <v>-4.154868933088752</v>
       </c>
       <c r="S79" t="n">
-        <v>46.46060012817383</v>
+        <v>46.45740013122558</v>
       </c>
       <c r="T79" t="n">
         <v>-1</v>
       <